--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.06" customWidth="1" style="20" min="1" max="1"/>
@@ -675,6 +675,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="M3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="138" customHeight="1" s="22">
       <c r="A4" s="27" t="n">
@@ -1575,6 +1580,11 @@
           <t>Publicitaire américain considéré comme le père de la propagande politique.</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="148.5" customHeight="1" s="22">
       <c r="A20" s="27" t="n">
@@ -1908,6 +1918,11 @@
           <t>philosophe germano-américain, figure de l'École de Francfort et du freudo-marxisme.</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="171.75" customHeight="1" s="22">
       <c r="A26" s="27" t="n">
@@ -1965,6 +1980,11 @@
           <t>philosophe américain métaphysicien néo-classique.</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="213" customHeight="1" s="22">
       <c r="A27" s="20" t="n">
@@ -2018,6 +2038,11 @@
           <t>philosophe des sciences américain d'origine hongroise, théoricien classique de la réduction interthéorique.</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="245.25" customHeight="1" s="22">
       <c r="A28" s="27" t="n">
@@ -2075,6 +2100,11 @@
           <t>philosophe et écrivaine américaine qui développa le concept de l'Objectivisme.</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="252" customHeight="1" s="22">
       <c r="A29" s="27" t="n">
@@ -2131,6 +2161,11 @@
           <t>philosophe allemande impliquée dans la compréhension du contrôle par les forces politiques.</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="187.5" customHeight="1" s="22">
       <c r="A30" s="27" t="n">
@@ -2189,6 +2224,11 @@
           <t>philosophe américain nominaliste qui appartient à la philosophie analytique, la méréologie.</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="150" customHeight="1" s="22">
       <c r="A31" s="27" t="n">
@@ -2471,6 +2511,11 @@
           <t>philosophe américain célèbre pour "La Structure des révolutions scientifiques".</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="164.25" customHeight="1" s="22">
       <c r="A36" s="27" t="n">
@@ -2585,6 +2630,11 @@
           <t>philosophe américain connu pour son travail en philosophie de l’esprit, de la langue, des sciences.</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="222" customHeight="1" s="22">
       <c r="A38" s="27" t="n">
@@ -2643,6 +2693,11 @@
           <t>philosophe américain connu pour avoir renouvelé la philosophie du langage ordinaire.</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="281.25" customHeight="1" s="22">
       <c r="A39" s="27" t="n">
@@ -2699,6 +2754,11 @@
           <t>économiste et philosophe politique américain connu comme une figure du libertarianisme et de l’anarcho-capitalisme.</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="281.25" customHeight="1" s="22">
       <c r="A40" s="27" t="n">
@@ -2754,6 +2814,11 @@
           <t>Philosophe et écrivain américain d’origine roumaine, survivant de la Shoah, militant des droits humains et prix Nobel de la paix.</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="229.5" customHeight="1" s="22">
       <c r="A41" s="27" t="n">
@@ -3202,7 +3267,11 @@
           <t>philosophe américain connu pour son libertarianisme et sa critique des théories égalitaristes.</t>
         </is>
       </c>
-      <c r="M48" s="21" t="n"/>
+      <c r="M48" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="180.75" customHeight="1" s="22">
       <c r="A49" s="27" t="n">

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -680,6 +680,21 @@
           <t xml:space="preserve">Traditions</t>
         </is>
       </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Groupe</t>
+        </is>
+      </c>
+      <c r="O3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importance</t>
+        </is>
+      </c>
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nationalite</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="138" customHeight="1" s="22">
       <c r="A4" s="27" t="n">
@@ -738,6 +753,16 @@
           <t>Intellectuelle religieuse mexicaine défenseuse du droit des femmes à apprendre.</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexicaine</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="126" customHeight="1" s="22">
       <c r="A5" s="27" t="n">
@@ -793,6 +818,16 @@
           <t>philosophe vénézuélien devenu une référence majeure au Chili.</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vénézuélienne</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="148.5" customHeight="1" s="22">
       <c r="A6" s="27" t="n">
@@ -850,6 +885,11 @@
           <t>philosophe américain souvent considéré comme le père du transcendantalisme.</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="120" customHeight="1" s="22">
       <c r="A7" s="27" t="n">
@@ -906,6 +946,16 @@
           <t>philosophe et diplomate argentin à l'origine de la constitution d'Argentine.</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentine</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="164.25" customHeight="1" s="22">
       <c r="A8" s="27" t="n">
@@ -963,6 +1013,11 @@
           <t>philosophe américain naturaliste et abolitionniste appartenant au courant transcendantaliste.</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="241.5" customHeight="1" s="22">
       <c r="A9" s="27" t="n">
@@ -1020,6 +1075,11 @@
           <t>philosophe américain fondateur du courant pragmatiste et père de la sémiotique.</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="201.75" customHeight="1" s="22">
       <c r="A10" s="27" t="n">
@@ -1076,6 +1136,11 @@
           <t>philosophe américain connu pour sa philosophie du Pragmatisme.</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="157.5" customHeight="1" s="22">
       <c r="A11" s="27" t="n">
@@ -1133,6 +1198,11 @@
           <t>philosophe américain connu pour son idéalisme absolu et sa réflexion sur la morale.</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="183.75" customHeight="1" s="22">
       <c r="A12" s="27" t="n">
@@ -1189,6 +1259,11 @@
           <t>philosophe et psychologue américain figure majeure du pragmatisme moderne.</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="183.75" customHeight="1" s="22">
       <c r="A13" s="27" t="n">
@@ -1244,6 +1319,16 @@
           <t>philosophe argentin fondateur de la philosophie argentine moderne.</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentine</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="183.75" customHeight="1" s="22">
       <c r="A14" s="27" t="n">
@@ -1299,6 +1384,16 @@
           <t>philosophe brésilien connu pour avoir développé un spiritualisme philosophique brésilien.</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brésilienne</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="182.25" customHeight="1" s="22">
       <c r="A15" s="27" t="n">
@@ -1354,6 +1449,16 @@
           <t>philosophe uruguayen et l’une des figures majeures de la pensée hispano‑américaine.</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uruguayenne</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="178.5" customHeight="1" s="22">
       <c r="A16" s="27" t="n">
@@ -1411,6 +1516,11 @@
           <t>philosophe idéaliste américain figure majeure du "personnalisme de Harvard".</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="108.75" customHeight="1" s="22">
       <c r="A17" s="27" t="n">
@@ -1468,6 +1578,16 @@
           <t>philosophe mexicain connu pour sa critique du positivisme et pour son humanisme spiritualiste.</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexicaine</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="183" customHeight="1" s="22">
       <c r="A18" s="27" t="n">
@@ -1524,6 +1644,16 @@
           <t>philosophe mexicain &amp; l'un des grands humanistes de la langue espagnole au XXe siècle.</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexicaine</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="148.5" customHeight="1" s="22">
       <c r="A19" s="27" t="n">
@@ -1585,6 +1715,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="148.5" customHeight="1" s="22">
       <c r="A20" s="27" t="n">
@@ -1640,6 +1775,16 @@
           <t>philosophe argentin figure centrale de la réaction ibéro-américaine.</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentine</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="120.75" customHeight="1" s="22">
       <c r="A21" s="27" t="n">
@@ -1695,6 +1840,16 @@
           <t>philosophe militant péruvien fondateur du Parti socialiste péruvien.</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Péruvienne</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="135" customHeight="1" s="22">
       <c r="A22" s="27" t="n">
@@ -1747,6 +1902,11 @@
           <t>Analytique ; Phénoménologie</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="123.75" customHeight="1" s="22">
       <c r="A23" s="27" t="n">
@@ -1803,6 +1963,11 @@
           <t>philosophe américain spécialisé en métaphysique et en philosophie de la religion.</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="126.75" customHeight="1" s="22">
       <c r="A24" s="27" t="n">
@@ -1860,6 +2025,16 @@
           <t>philosophe mexicain précurseur de la philosophie de la mexicanité.</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexicaine</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="165" customHeight="1" s="22">
       <c r="A25" s="27" t="n">
@@ -1923,6 +2098,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="171.75" customHeight="1" s="22">
       <c r="A26" s="27" t="n">
@@ -1985,6 +2165,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="213" customHeight="1" s="22">
       <c r="A27" s="20" t="n">
@@ -2043,6 +2228,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="245.25" customHeight="1" s="22">
       <c r="A28" s="27" t="n">
@@ -2102,7 +2292,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">juive;russe</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -2166,6 +2361,14 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O29">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" ht="187.5" customHeight="1" s="22">
       <c r="A30" s="27" t="n">
@@ -2229,6 +2432,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="150" customHeight="1" s="22">
       <c r="A31" s="27" t="n">
@@ -2285,6 +2493,11 @@
           <t>philosophe américain figure centrale de la philosophie analytique.</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="174" customHeight="1" s="22">
       <c r="A32" s="27" t="n">
@@ -2342,6 +2555,16 @@
           <t>philosophe mexicain père de la philosophie latino-américaine contemporaine.</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexicaine</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="298.5" customHeight="1" s="22">
       <c r="A33" s="27" t="n">
@@ -2397,6 +2620,11 @@
           <t xml:space="preserve"> philosophe américain reconnu pour ses travaux en épistémologie, métaphysique, philosophie de la conscience et  de la perception.</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="174.75" customHeight="1" s="22">
       <c r="A34" s="27" t="n">
@@ -2454,6 +2682,11 @@
           <t>philosophe politique américain le plus étudié du XXème siècle.</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="183" customHeight="1" s="22">
       <c r="A35" s="27" t="n">
@@ -2516,6 +2749,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="164.25" customHeight="1" s="22">
       <c r="A36" s="27" t="n">
@@ -2573,6 +2811,11 @@
           <t>philosophe américain figure majeure de la philosophie et de la théologie du process.</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="244.5" customHeight="1" s="22">
       <c r="A37" s="27" t="n">
@@ -2635,6 +2878,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="222" customHeight="1" s="22">
       <c r="A38" s="27" t="n">
@@ -2698,6 +2946,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="281.25" customHeight="1" s="22">
       <c r="A39" s="27" t="n">
@@ -2759,6 +3012,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="281.25" customHeight="1" s="22">
       <c r="A40" s="27" t="n">
@@ -2819,6 +3077,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="229.5" customHeight="1" s="22">
       <c r="A41" s="27" t="n">
@@ -2876,6 +3139,11 @@
           <t>philosophe jésuite américain dont la pensée s’inscrit entre foi chrétienne &amp; pensée moderne.</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="144" customHeight="1" s="22">
       <c r="A42" s="27" t="n">
@@ -2933,6 +3201,11 @@
           <t>philosophe américain représentant majeur de la pensée pragmatique contemporaine.</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="171.75" customHeight="1" s="22">
       <c r="A43" s="27" t="n">
@@ -2986,6 +3259,11 @@
           <t>philosophe américain connu pour ses travaux en philosophie des mathématiques et en philosophie de Kant.</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="189.75" customHeight="1" s="22">
       <c r="A44" s="27" t="n">
@@ -3043,6 +3321,19 @@
           <t>philosophe argentin de la décolonialité &amp; de la philosophie latino-américaine de la libération.</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O44">
+        <v>3</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentine</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="199.5" customHeight="1" s="22">
       <c r="A45" s="27" t="n">
@@ -3098,6 +3389,11 @@
           <t>philosophe américain majeur de la technologie et de la phénoménologie.</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="255" customHeight="1" s="22">
       <c r="A46" s="37" t="n">
@@ -3153,7 +3449,16 @@
           <t>intellectuel palestinien-américain,  célèbre pour son essai L’Orientalisme.</t>
         </is>
       </c>
-      <c r="M46" s="34" t="n"/>
+      <c r="M46" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N46" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="187.5" customHeight="1" s="22">
       <c r="A47" s="27" t="n">
@@ -3211,6 +3516,11 @@
           <t>philosophe analytique américain connu pour ses travaux en métaphysique &amp; philosophie des religions.</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="167.25" customHeight="1" s="22">
       <c r="A48" s="27" t="n">
@@ -3272,6 +3582,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N48" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="180.75" customHeight="1" s="22">
       <c r="A49" s="27" t="n">
@@ -3328,6 +3643,11 @@
           <t>philosophe américain spécialiste de la philosophie morale &amp; théoricien des droits des animaux.</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="178.5" customHeight="1" s="22">
       <c r="A50" s="27" t="n">
@@ -3384,6 +3704,11 @@
           <t>philosophe américain figure majeure de la philosophie analytique contemporaine.</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="332.25" customHeight="1" s="22">
       <c r="A51" s="27" t="n">
@@ -3442,6 +3767,11 @@
           <t>philosophe américain spécialisé en philosophie des sciences et de l'esprit.</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="207" customHeight="1" s="22">
       <c r="A52" s="27" t="n">
@@ -3499,6 +3829,11 @@
           <t>philosophe américaine reconnue en philosophie des religions médiévales.</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="180" customHeight="1" s="22">
       <c r="A53" s="20" t="n">
@@ -3551,6 +3886,11 @@
       <c r="L53" s="21" t="inlineStr">
         <is>
           <t>philosophe politique américaine, figure centrale du féminisme contemporain.</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.06" customWidth="1" style="20" min="1" max="1"/>
@@ -753,6 +753,11 @@
           <t>Intellectuelle religieuse mexicaine défenseuse du droit des femmes à apprendre.</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
@@ -1902,6 +1907,11 @@
           <t>Analytique ; Phénoménologie</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -2292,7 +2302,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive;russe</t>
+          <t xml:space="preserve">juive;russe;femme</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2358,7 +2368,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">juive;femme</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3829,6 +3839,11 @@
           <t>philosophe américaine reconnue en philosophie des religions médiévales.</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -3888,6 +3903,11 @@
           <t>philosophe politique américaine, figure centrale du féminisme contemporain.</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -3895,13 +3915,58 @@
       </c>
     </row>
     <row r="54" ht="213" customHeight="1" s="22">
-      <c r="E54" s="20" t="n"/>
+      <c r="A54" s="20">
+        <v>1952</v>
+      </c>
+      <c r="B54" s="20">
+        <v>2021</v>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1952 - 2021</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell HOOKS</t>
+        </is>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bell_hooks"  title=" Wikipedia"&gt;bell HOOKS&lt;/a&gt; (1952-2021), de son vrai nom Gloria Jean Watkins, est une autrice, professeure et militante féministe afro-américaine. Née dans le Kentucky, dans le Sud ségrégationniste, elle prit le nom de son arrière-grand-mère, qu'elle écrivait en minuscules pour que l'attention se porte sur ses idées plutôt que sur sa personne.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ne suis-je pas une femme ?&lt;/em&gt; (1981), elle montre que les femmes noires ont été oubliées à la fois par le mouvement féministe, dominé par des femmes blanches de classe moyenne, et par le mouvement pour les droits civiques, dominé par des hommes. Elle développe l'idée que le sexisme, le racisme et l'exploitation économique forment un même système de domination, qu'elle appelle le « patriarcat capitaliste suprémaciste blanc ».&lt;/p&gt; &lt;p&gt;Ses idées ont profondément influencé ce que l'on appelle aujourd'hui l'intersectionnalité, c'est-à-dire l'étude de la manière dont différentes formes de discrimination se croisent et se renforcent. Elle écrivait dans un style simple et direct, refusant le jargon universitaire, pour que ses livres soient lus au-delà des cercles savants. Elle a aussi consacré plusieurs ouvrages à l'amour, qu'elle considérait comme une force politique capable de transformer la société.&lt;/p&gt; &lt;p&gt;Elle a écrit une quarantaine de livres, sur le féminisme, l'amour, les médias, la culture populaire et l'éducation. Dans &lt;em&gt;Apprendre à transgresser&lt;/em&gt; (1994), inspirée par Paulo Freire, elle défend une pédagogie de la liberté où l'enseignement devient une pratique d'émancipation. Pour elle, le féminisme n'est pas une guerre contre les hommes mais un mouvement pour mettre fin à toute forme de domination, porté par une « éthique de l'amour ».&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="G54" s="20" t="n"/>
       <c r="H54" s="20" t="n"/>
       <c r="I54" s="20" t="n"/>
-      <c r="J54" s="20" t="n"/>
-      <c r="K54" s="20" t="n"/>
-      <c r="L54" s="20" t="n"/>
+      <c r="J54" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K54" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Féminisme</t>
+        </is>
+      </c>
+      <c r="L54" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penseuse féministe afro-américaine, théoricienne de l'intersection du sexe, de la race et de la classe.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme ; sud</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O54">
+        <v>2</v>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="22">
       <c r="E55" s="20" t="n"/>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="500">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES AMÉRICAINS ET LATINO-AMÉRICAINS — Données source</t>
   </si>
@@ -367,6 +367,7 @@
         <sz val="9"/>
         <rFont val="Microsoft YaHei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">｜</t>
     </r>
@@ -1571,10 +1572,57 @@
     <t xml:space="preserve">1952 - 2021</t>
   </si>
   <si>
-    <t xml:space="preserve">bell HOOKS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bell_hooks"  title=" Wikipedia"&gt;bell HOOKS&lt;/a&gt; (1952-2021), de son vrai nom Gloria Jean Watkins, est une autrice, professeure et militante féministe afro-américaine. Née dans le Kentucky, dans le Sud ségrégationniste, elle prit le nom de son arrière-grand-mère, qu'elle écrivait en minuscules pour que l'attention se porte sur ses idées plutôt que sur sa personne.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ne suis-je pas une femme ?&lt;/em&gt; (1981), elle montre que les femmes noires ont été oubliées à la fois par le mouvement féministe, dominé par des femmes blanches de classe moyenne, et par le mouvement pour les droits civiques, dominé par des hommes. Elle développe l'idée que le sexisme, le racisme et l'exploitation économique forment un même système de domination, qu'elle appelle le « patriarcat capitaliste suprémaciste blanc ».&lt;/p&gt; &lt;p&gt;Ses idées ont profondément influencé ce que l'on appelle aujourd'hui l'intersectionnalité, c'est-à-dire l'étude de la manière dont différentes formes de discrimination se croisent et se renforcent. Elle écrivait dans un style simple et direct, refusant le jargon universitaire, pour que ses livres soient lus au-delà des cercles savants. Elle a aussi consacré plusieurs ouvrages à l'amour, qu'elle considérait comme une force politique capable de transformer la société.&lt;/p&gt; &lt;p&gt;Elle a écrit une quarantaine de livres, sur le féminisme, l'amour, les médias, la culture populaire et l'éducation. Dans &lt;em&gt;Apprendre à transgresser&lt;/em&gt; (1994), inspirée par Paulo Freire, elle défend une pédagogie de la liberté où l'enseignement devient une pratique d'émancipation. Pour elle, le féminisme n'est pas une guerre contre les hommes mais un mouvement pour mettre fin à toute forme de domination, porté par une « éthique de l'amour ».&lt;/p&gt;</t>
+    <t xml:space="preserve">Bell HOOKS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bell_hooks"  title=" Wikipedia"&gt;Bell HOOKS&lt;/a&gt; , de son vrai nom Gloria Jean Watkins, est une autrice, professeure et militante féministe afro-américaine. Née dans le Kentucky, dans le Sud ségrégationniste, elle prit le nom de son arrière-grand-mère, qu'elle écrivait en minuscules pour que l'attention se porte sur ses idées plutôt que sur sa personne.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ne suis-je pas une femme ?&lt;/em&gt; (1981), elle montre que les femmes noires ont été oubliées à la fois par le mouvement féministe, dominé par des femmes blanches de classe moyenne, et par le mouvement pour les droits civiques, dominé par des hommes. Elle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;a href="https://www.youtube.com/watch?v=pCwMdHBSQgM" title=" bell hooks, un féminisme anticapitaliste et intersectionnel par META "&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">développe l'idée &lt;/a&gt; que le sexisme, le racisme et l'exploitation économique forment un même système de domination, qu'elle appelle le « patriarcat capitaliste suprémaciste blanc ».&lt;/p&gt; &lt;p&gt;Ses idées ont profondément influencé ce que l'on appelle aujourd'hui l'intersectionnalité, c'est-à-dire l'étude de la manière dont différentes formes de discrimination se croisent et se renforcent. Elle écrivait dans un style simple et direct, refusant le jargon universitaire, pour que ses livres soient lus au-delà des cercles savants. Elle a aussi consacré plusieurs ouvrages à l'amour, qu'elle considérait comme une force politique capable de transformer la société.&lt;/p&gt; &lt;p&gt;Elle a écrit une quarantaine de livres, sur le féminisme, l'amour, les médias, la culture populaire et l'éducation. Dans &lt;em&gt;Apprendre à transgresser&lt;/em&gt; (1994), inspirée par Paulo Freire, elle défend une pédagogie de la liberté où l'enseignement devient une pratique d'émancipation. Pour elle, le féminisme n'est pas une guerre contre les hommes mais un mouvement pour mettre fin à toute forme de domination, porté par une « éthique de l'amour ».&lt;/p&gt;  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">  &lt;audio controls title="Lire bell hooks aujourd’hui par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23875-15.11.2023-ITEMA_23552434-2023C49162S0319-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">IFFd_Zqo5cc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’amour, selon bell hooks par France Culture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/bhooks-mini.webp</t>
   </si>
   <si>
     <t xml:space="preserve">Féminisme</t>
@@ -1593,7 +1641,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1683,6 +1731,7 @@
       <sz val="9"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1711,6 +1760,18 @@
       <name val="Georgia"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1793,71 +1854,71 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2113,7 +2174,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD59"/>
+  <dimension ref="A1:P1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
@@ -2126,9 +2187,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="26.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="8.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="28.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="23.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="26.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -2246,10 +2308,10 @@
       <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="0" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="0" t="s">
+      <c r="P4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2288,10 +2350,10 @@
       <c r="L5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="N5" s="0" t="s">
+      <c r="N5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="0" t="s">
+      <c r="P5" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2330,7 +2392,7 @@
       <c r="L6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N6" s="0" t="s">
+      <c r="N6" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2369,10 +2431,10 @@
       <c r="L7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="N7" s="0" t="s">
+      <c r="N7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P7" s="0" t="s">
+      <c r="P7" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2411,7 +2473,7 @@
       <c r="L8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="N8" s="0" t="s">
+      <c r="N8" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2450,7 +2512,7 @@
       <c r="L9" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N9" s="0" t="s">
+      <c r="N9" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2489,7 +2551,7 @@
       <c r="L10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="N10" s="0" t="s">
+      <c r="N10" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2528,7 +2590,7 @@
       <c r="L11" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="N11" s="0" t="s">
+      <c r="N11" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2567,7 +2629,7 @@
       <c r="L12" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="N12" s="0" t="s">
+      <c r="N12" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2606,10 +2668,10 @@
       <c r="L13" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="N13" s="0" t="s">
+      <c r="N13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P13" s="0" t="s">
+      <c r="P13" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2648,10 +2710,10 @@
       <c r="L14" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="N14" s="0" t="s">
+      <c r="N14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P14" s="0" t="s">
+      <c r="P14" s="1" t="s">
         <v>130</v>
       </c>
     </row>
@@ -2690,10 +2752,10 @@
       <c r="L15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="N15" s="0" t="s">
+      <c r="N15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P15" s="0" t="s">
+      <c r="P15" s="1" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2732,7 +2794,7 @@
       <c r="L16" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="N16" s="0" t="s">
+      <c r="N16" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2771,10 +2833,10 @@
       <c r="L17" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="N17" s="0" t="s">
+      <c r="N17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P17" s="0" t="s">
+      <c r="P17" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2813,10 +2875,10 @@
       <c r="L18" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N18" s="0" t="s">
+      <c r="N18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P18" s="0" t="s">
+      <c r="P18" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2858,7 +2920,7 @@
       <c r="M19" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="N19" s="0" t="s">
+      <c r="N19" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2897,10 +2959,10 @@
       <c r="L20" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="N20" s="0" t="s">
+      <c r="N20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P20" s="0" t="s">
+      <c r="P20" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2939,10 +3001,10 @@
       <c r="L21" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="N21" s="0" t="s">
+      <c r="N21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P21" s="0" t="s">
+      <c r="P21" s="1" t="s">
         <v>193</v>
       </c>
     </row>
@@ -2981,7 +3043,7 @@
       <c r="M22" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N22" s="0" t="s">
+      <c r="N22" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3020,7 +3082,7 @@
       <c r="L23" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="N23" s="0" t="s">
+      <c r="N23" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3059,10 +3121,10 @@
       <c r="L24" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="N24" s="0" t="s">
+      <c r="N24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P24" s="0" t="s">
+      <c r="P24" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3104,7 +3166,7 @@
       <c r="M25" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="N25" s="0" t="s">
+      <c r="N25" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3146,7 +3208,7 @@
       <c r="M26" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="N26" s="0" t="s">
+      <c r="N26" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3187,7 +3249,7 @@
       <c r="M27" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="N27" s="0" t="s">
+      <c r="N27" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3229,7 +3291,7 @@
       <c r="M28" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="N28" s="0" t="s">
+      <c r="N28" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3271,10 +3333,10 @@
       <c r="M29" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="N29" s="0" t="s">
+      <c r="N29" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O29" s="0" t="n">
+      <c r="O29" s="1" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3316,7 +3378,7 @@
       <c r="M30" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="N30" s="0" t="s">
+      <c r="N30" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3355,7 +3417,7 @@
       <c r="L31" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="N31" s="0" t="s">
+      <c r="N31" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3394,10 +3456,10 @@
       <c r="L32" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="N32" s="0" t="s">
+      <c r="N32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P32" s="0" t="s">
+      <c r="P32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3436,7 +3498,7 @@
       <c r="L33" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="N33" s="0" t="s">
+      <c r="N33" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3475,7 +3537,7 @@
       <c r="L34" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="N34" s="0" t="s">
+      <c r="N34" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3517,7 +3579,7 @@
       <c r="M35" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="N35" s="0" t="s">
+      <c r="N35" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3556,7 +3618,7 @@
       <c r="L36" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="N36" s="0" t="s">
+      <c r="N36" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3598,7 +3660,7 @@
       <c r="M37" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="N37" s="0" t="s">
+      <c r="N37" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3640,7 +3702,7 @@
       <c r="M38" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="N38" s="0" t="s">
+      <c r="N38" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3682,7 +3744,7 @@
       <c r="M39" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="N39" s="0" t="s">
+      <c r="N39" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3724,7 +3786,7 @@
       <c r="M40" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="N40" s="0" t="s">
+      <c r="N40" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3763,7 +3825,7 @@
       <c r="L41" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="N41" s="0" t="s">
+      <c r="N41" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3802,7 +3864,7 @@
       <c r="L42" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="N42" s="0" t="s">
+      <c r="N42" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3825,10 +3887,10 @@
       <c r="F43" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="2" t="s">
         <v>389</v>
       </c>
       <c r="I43" s="1"/>
@@ -3838,13 +3900,13 @@
       <c r="K43" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="L43" s="1" t="s">
+      <c r="L43" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="N43" s="0" t="s">
+      <c r="N43" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P43" s="0" t="s">
+      <c r="P43" s="1" t="s">
         <v>392</v>
       </c>
     </row>
@@ -3881,7 +3943,7 @@
       <c r="L44" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="N44" s="0" t="s">
+      <c r="N44" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3920,13 +3982,13 @@
       <c r="L45" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="N45" s="0" t="s">
+      <c r="N45" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O45" s="0" t="n">
+      <c r="O45" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="P45" s="0" t="s">
+      <c r="P45" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3965,7 +4027,7 @@
       <c r="L46" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="N46" s="0" t="s">
+      <c r="N46" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4046,7 +4108,7 @@
       <c r="L48" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="N48" s="0" t="s">
+      <c r="N48" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4127,7 +4189,7 @@
       <c r="L50" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="N50" s="0" t="s">
+      <c r="N50" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4150,10 +4212,10 @@
       <c r="F51" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" s="2" t="s">
         <v>454</v>
       </c>
       <c r="J51" s="1" t="s">
@@ -4162,20 +4224,18 @@
       <c r="K51" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="L51" s="1" t="s">
+      <c r="L51" s="2" t="s">
         <v>457</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="N51" s="0" t="s">
+      <c r="N51" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P51" s="0" t="s">
+      <c r="P51" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="XFC51" s="0"/>
-      <c r="XFD51" s="0"/>
     </row>
     <row r="52" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
@@ -4212,7 +4272,7 @@
       <c r="L52" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="N52" s="0" t="s">
+      <c r="N52" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4251,7 +4311,7 @@
       <c r="L53" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="N53" s="0" t="s">
+      <c r="N53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4293,7 +4353,7 @@
       <c r="M54" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N54" s="0" t="s">
+      <c r="N54" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4334,83 +4394,68 @@
       <c r="M55" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N55" s="0" t="s">
+      <c r="N55" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E56" s="14"/>
-    </row>
-    <row r="57" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
+    <row r="56" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="n">
         <v>1952</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B56" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
+      <c r="F56" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O56" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E57" s="1"/>
       <c r="I57" s="1"/>
-      <c r="J57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="N57" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="O57" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0"/>
-      <c r="B58" s="0"/>
-      <c r="C58" s="0"/>
-      <c r="D58" s="0"/>
-      <c r="E58" s="0"/>
-      <c r="F58" s="0"/>
-      <c r="G58" s="0"/>
-      <c r="H58" s="0"/>
-      <c r="I58" s="0"/>
-      <c r="J58" s="0"/>
-      <c r="K58" s="0"/>
-      <c r="L58" s="0"/>
-      <c r="M58" s="0"/>
-      <c r="XFC58" s="0"/>
-      <c r="XFD58" s="0"/>
-    </row>
-    <row r="59" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0"/>
-      <c r="B59" s="0"/>
-      <c r="C59" s="0"/>
-      <c r="D59" s="0"/>
-      <c r="E59" s="0"/>
-      <c r="F59" s="0"/>
-      <c r="G59" s="0"/>
-      <c r="H59" s="0"/>
-      <c r="I59" s="0"/>
-      <c r="J59" s="0"/>
-      <c r="K59" s="0"/>
-      <c r="L59" s="0"/>
-      <c r="M59" s="0"/>
-    </row>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+    </row>
+    <row r="58" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -4454,6 +4499,7 @@
     <hyperlink ref="H48" r:id="rId35" display="https://www.laphilo.fr/pho/rmadams-mini.webp"/>
     <hyperlink ref="E49" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Nozick&quot;  title=&quot; Wikipedia&quot;&gt;Robert NOZICK&lt;/a&gt; était un philosophe américain connu pour &lt;a href=&quot;https://www.youtube.com/watch?v=Q-t3cpFAk4o&quot;  title=&quot; Libertarianisme par Vadim Media&quot;&gt; son libertarianisme &lt;/a&gt; et sa critique des théories égalitaristes comme celle de John Rawls. Professeur à Harvard, il a marqué la philosophie politique, morale et épistémologique par son œuvre principale, Anarchie, État et utopie (1974), qui défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Minarchisme&quot;  title=&quot; Minarchisme par Wikipédia&quot;&gt; Etat Minimal. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il argue que seul l'État minimal, ou &quot;État gardien de nuit&quot;, est légitime, car il se limite à protéger les individus contre la force, la fraude et le vol, sans redistribuer les richesses. Il rejette l'anarcho-capitalisme en montrant, via des agences de protection privée, comment un État dominant émerge naturellement pour monopoliser la coercition légitime, justifié par le droit naturel à la personne. &lt;/p&gt; &lt;p&gt; Contrairement à la justice distributive de Rawls, il propose une théorie de l'entitlement : une acquisition initiale juste et des transferts volontaires rendent la distribution légitime, sans besoin d'égalisation par l'État. Toute intervention redistributive viole les droits individuels, traitant les personnes comme des moyens plutôt que des fins, en écho à Kant. &lt;/p&gt; &lt;p&gt; Dans Anarchie, État et utopie, Il réfute l'utilitarisme via l'expérience de pensée de la &lt;a href=&quot;https://www.youtube.com/watch?v=2FVwXaNWPQ0&quot;  title=&quot; La machine à expérience par Monsieur Phi&quot;&gt;&quot;machine à expérience&quot; :&lt;/a&gt;  même si elle offre un bonheur parfait et indistinguable de la réalité, les gens préfèrent vivre des actions réelles et façonner leur identité plutôt que des simulations. Cela prouve que le bonheur n'est pas le seul bien suprême. &lt;/p&gt; &lt;p&gt; Plus tard, dans Explications philosophiques (1981), il développe une théorie du suivi (tracking theory) en épistémologie, où la connaissance repose sur des conditionnels contrefactuels fiables, contournant le scepticisme sans justification traditionnelle. Son anti-coercitivisme intellectuel invite à une philosophie ouverte, non imposée. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Qui a peur des Libertariens par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-14.06.2022-ITEMA_23058436-2022C12410S0165-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;"/>
     <hyperlink ref="H55" r:id="rId37" display="https://www.laphilo.fr/pho/imyoung-mini.webp"/>
+    <hyperlink ref="H56" r:id="rId38" display="https://www.laphilo.fr/pho/bhooks-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -4444,10 +4444,63 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E57" s="1"/>
+      <c r="A57" s="1">
+        <v>1934</v>
+      </c>
+      <c r="B57" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1934 – 2019</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jaegwon KIM</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jaegwon_Kim"  title=" Wikipedia"&gt;Jaegwon KIM&lt;/a&gt; était un philosophe américain d’origine sud-coréenne, l’une des figures majeures de la philosophie de l’esprit et de la métaphysique analytique. Né à Daegu, il étudia à l’université nationale de Séoul avant de partir aux États-Unis, où il enseigna notamment à l’université du Michigan puis à l’université Brown.&lt;/p&gt; &lt;p&gt;Il est célèbre pour avoir clarifié la notion de « survenance » : les propriétés mentales dépendent des propriétés physiques, en ce sens que deux êtres physiquement identiques ne peuvent différer mentalement. Son « argument de l’exclusion causale » pose un dilemme au physicalisme non réductionniste : si tout effet physique a une cause physique suffisante, les états mentaux ne semblent plus rien causer par eux-mêmes, à moins d’être réductibles à des états physiques. Ses ouvrages, comme &lt;em&gt;Philosophy of Mind&lt;/em&gt; et &lt;em&gt;Mind in a Physical World&lt;/em&gt;, sont devenus des références.&lt;/p&gt; &lt;p&gt;Arrivé aux États-Unis en 1955, il étudia au Dartmouth College, puis soutint sa thèse à Princeton sous la direction de Carl Hempel, l’un des grands théoriciens de l’explication scientifique. Avant ses travaux sur l’esprit, il proposa une théorie des événements, conçus comme l’exemplification d’une propriété par un objet à un moment donné. Ses réflexions l’amenèrent à une position de plus en plus exigeante : dans &lt;em&gt;Physicalism, or Something Near Enough&lt;/em&gt; (2005), il admet que le physicalisme peut rendre compte de presque tout le mental, à l’exception des qualités vécues de l’expérience, comme la sensation d’une couleur ou d’une douleur, qui résistent à la réduction. Cette honnêteté face aux limites de sa propre thèse a fait de lui un interlocuteur respecté même de ses adversaires.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/jkim-mini.webp</t>
+        </is>
+      </c>
       <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe de l’esprit d’origine coréenne, théoricien de la survenance et de l’exclusion causale.</t>
+        </is>
+      </c>
+      <c r="M57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="N57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coréenne</t>
+        </is>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E58" s="1"/>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="509">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES AMÉRICAINS ET LATINO-AMÉRICAINS — Données source</t>
   </si>
@@ -1336,6 +1336,62 @@
     <t xml:space="preserve">philosophe américain majeur de la technologie et de la phénoménologie.</t>
   </si>
   <si>
+    <t xml:space="preserve">1934 – 2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaegwon KIM</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jaegwon_Kim"  title=" Wikipedia"&gt;Jaegwon KIM&lt;/a&gt; était un philosophe américain d’origine sud-coréenne, l’une des figures majeures de la philosophie de l’esprit et de la métaphysique analytique. Né à Daegu, il étudia à l’université nationale de Séoul avant de partir aux États-Unis, où il enseigna notamment à l’université du Michigan puis à l’université Brown.&lt;/p&gt; &lt;p&gt;Il est célèbre pour avoir clarifié la notion de « survenance » : les propriétés mentales dépendent des propriétés physiques, en ce sens que deux êtres physiquement identiques ne peuvent différer mentalement. Son « argument de l’exclusion causale » pose un dilemme au physicalisme non réductionniste : si tout effet physique a une cause physique suffisante, les états mentaux ne semblent plus rien causer par eux-mêmes, à moins d’être réductibles à des états physiques. Ses ouvrages, comme &lt;em&gt;Philosophy of Mind&lt;/em&gt; et &lt;em&gt;Mind in a Physical World&lt;/em&gt;, sont devenus des références.&lt;/p&gt; &lt;p&gt;Arrivé aux États-Unis en 1955, il étudia au Dartmouth College, puis soutint sa thèse à Princeton sous la direction de Carl Hempel, l’un des grands théoriciens de l’explication scientifique. Avant ses travaux sur l’esprit, il proposa une théorie des événements, conçus comme l’exemplification d’une propriété par un objet à un moment donné. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;a href="https://www.youtube.com/watch?v=Vxp_MQpU1m4" title="jaegwon Kin par WikiAudio "&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ses réflexions &lt;/a&gt; l’amenèrent à une position de plus en plus exigeante : dans &lt;em&gt;Physicalism, or Something Near Enough&lt;/em&gt; (2005), il admet que le physicalisme peut rendre compte de presque tout le mental, à l’exception des qualités vécues de l’expérience, comme la sensation d’une couleur ou d’une douleur, qui résistent à la réduction. Cette honnêteté face aux limites de sa propre thèse a fait de lui un interlocuteur respecté même de ses adversaires.&lt;/p&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">i_xsEeVKm_Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Jaegwon Kim’s Epiphenomenalism? par paul Austin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/jkim-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe de l’esprit d’origine coréenne, théoricien de la survenance et de l’exclusion causale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asie-est</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coréenne</t>
+  </si>
+  <si>
     <t xml:space="preserve">1935 – 2003</t>
   </si>
   <si>
@@ -1591,6 +1647,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> &lt;a href="https://www.youtube.com/watch?v=pCwMdHBSQgM" title=" bell hooks, un féminisme anticapitaliste et intersectionnel par META "&gt;</t>
     </r>
@@ -1610,6 +1667,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">  &lt;audio controls title="Lire bell hooks aujourd’hui par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23875-15.11.2023-ITEMA_23552434-2023C49162S0319-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
 </t>
@@ -1748,6 +1806,19 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1760,18 +1831,6 @@
       <name val="Georgia"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1849,7 +1908,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1910,15 +1969,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2174,23 +2237,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P1048576"/>
+  <dimension ref="A1:XFD59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="110.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="97.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="36.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="26.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="30.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="22.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="8.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="16.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="14.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="26.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -3894,7 +3957,7 @@
         <v>389</v>
       </c>
       <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
+      <c r="J43" s="2" t="s">
         <v>338</v>
       </c>
       <c r="K43" s="1" t="s">
@@ -3992,7 +4055,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
         <v>1934</v>
       </c>
@@ -4031,135 +4094,140 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15" t="n">
+    <row r="47" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="I47" s="1"/>
+      <c r="J47" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="XFC47" s="0"/>
+      <c r="XFD47" s="0"/>
+    </row>
+    <row r="48" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="16" t="n">
         <v>1935</v>
       </c>
-      <c r="B47" s="15" t="n">
+      <c r="B48" s="16" t="n">
         <v>2003</v>
       </c>
-      <c r="C47" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>417</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="G47" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="I47" s="17"/>
-      <c r="J47" s="2" t="s">
+      <c r="C48" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="I48" s="18"/>
+      <c r="J48" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K47" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="L47" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="M47" s="14" t="s">
+      <c r="K48" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="L48" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="M48" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N47" s="14" t="s">
+      <c r="N48" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="n">
+    <row r="49" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
         <v>1937</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B49" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C48" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>426</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="I48" s="9"/>
-      <c r="J48" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
-        <v>1938</v>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>2002</v>
-      </c>
       <c r="C49" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="E49" s="13" t="s">
         <v>434</v>
       </c>
+      <c r="E49" s="11" t="s">
+        <v>435</v>
+      </c>
       <c r="F49" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="2" t="s">
-        <v>356</v>
+        <v>127</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="N49" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="N49" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
         <v>1938</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>440</v>
+      <c r="B50" s="7" t="n">
+        <v>2002</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>441</v>
@@ -4167,7 +4235,7 @@
       <c r="D50" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="13" t="s">
         <v>443</v>
       </c>
       <c r="F50" s="7" t="s">
@@ -4176,12 +4244,12 @@
       <c r="G50" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="10" t="s">
         <v>446</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="2" t="s">
-        <v>218</v>
+        <v>356</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>447</v>
@@ -4189,99 +4257,102 @@
       <c r="L50" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="N50" s="1" t="s">
+      <c r="M50" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="N50" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="B51" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C51" s="1" t="s">
+    <row r="51" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="C51" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="D51" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="E51" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="F51" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="G51" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="H51" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="I51" s="9"/>
+      <c r="J51" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>456</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="M51" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="N51" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P51" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="n">
-        <v>1941</v>
-      </c>
-      <c r="B52" s="7" t="s">
+    </row>
+    <row r="52" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="D52" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="E52" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="F52" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="G52" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="H52" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="H52" s="9" t="s">
+      <c r="J52" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="2" t="s">
+      <c r="K52" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="L52" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L52" s="2" t="s">
-        <v>467</v>
+      <c r="M52" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="332.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P52" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>322</v>
+        <v>467</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>468</v>
@@ -4303,93 +4374,91 @@
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="2" t="s">
-        <v>246</v>
+        <v>474</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="332.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>440</v>
+        <v>322</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="E54" s="11" t="s">
         <v>478</v>
       </c>
+      <c r="E54" s="9" t="s">
+        <v>479</v>
+      </c>
       <c r="F54" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
-        <v>127</v>
+        <v>246</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>28</v>
+        <v>484</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
-        <v>1949</v>
-      </c>
-      <c r="B55" s="1" t="n">
-        <v>2006</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="E55" s="14" t="s">
+    <row r="55" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="D55" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="E55" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="F55" s="7" t="s">
         <v>488</v>
       </c>
+      <c r="G55" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="I55" s="9"/>
       <c r="J55" s="2" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>28</v>
@@ -4398,117 +4467,112 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="n">
-        <v>1952</v>
+        <v>1949</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="E56" s="2" t="s">
         <v>493</v>
       </c>
+      <c r="E56" s="14" t="s">
+        <v>494</v>
+      </c>
       <c r="F56" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="J56" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>497</v>
+      <c r="K56" s="2" t="s">
+        <v>498</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>499</v>
+        <v>28</v>
       </c>
       <c r="N56" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O56" s="1" t="n">
+    </row>
+    <row r="57" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="n">
+        <v>1952</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O57" s="1" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1">
-        <v>1934</v>
-      </c>
-      <c r="B57" s="1">
-        <v>2019</v>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1934 – 2019</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jaegwon KIM</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jaegwon_Kim"  title=" Wikipedia"&gt;Jaegwon KIM&lt;/a&gt; était un philosophe américain d’origine sud-coréenne, l’une des figures majeures de la philosophie de l’esprit et de la métaphysique analytique. Né à Daegu, il étudia à l’université nationale de Séoul avant de partir aux États-Unis, où il enseigna notamment à l’université du Michigan puis à l’université Brown.&lt;/p&gt; &lt;p&gt;Il est célèbre pour avoir clarifié la notion de « survenance » : les propriétés mentales dépendent des propriétés physiques, en ce sens que deux êtres physiquement identiques ne peuvent différer mentalement. Son « argument de l’exclusion causale » pose un dilemme au physicalisme non réductionniste : si tout effet physique a une cause physique suffisante, les états mentaux ne semblent plus rien causer par eux-mêmes, à moins d’être réductibles à des états physiques. Ses ouvrages, comme &lt;em&gt;Philosophy of Mind&lt;/em&gt; et &lt;em&gt;Mind in a Physical World&lt;/em&gt;, sont devenus des références.&lt;/p&gt; &lt;p&gt;Arrivé aux États-Unis en 1955, il étudia au Dartmouth College, puis soutint sa thèse à Princeton sous la direction de Carl Hempel, l’un des grands théoriciens de l’explication scientifique. Avant ses travaux sur l’esprit, il proposa une théorie des événements, conçus comme l’exemplification d’une propriété par un objet à un moment donné. Ses réflexions l’amenèrent à une position de plus en plus exigeante : dans &lt;em&gt;Physicalism, or Something Near Enough&lt;/em&gt; (2005), il admet que le physicalisme peut rendre compte de presque tout le mental, à l’exception des qualités vécues de l’expérience, comme la sensation d’une couleur ou d’une douleur, qui résistent à la réduction. Cette honnêteté face aux limites de sa propre thèse a fait de lui un interlocuteur respecté même de ses adversaires.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/jkim-mini.webp</t>
-        </is>
-      </c>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Analytique</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe de l’esprit d’origine coréenne, théoricien de la survenance et de l’exclusion causale.</t>
-        </is>
-      </c>
-      <c r="M57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-      <c r="N57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coréenne</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0"/>
+      <c r="B58" s="0"/>
+      <c r="C58" s="0"/>
+      <c r="D58" s="0"/>
+      <c r="E58" s="0"/>
+      <c r="F58" s="0"/>
+      <c r="G58" s="0"/>
+      <c r="H58" s="0"/>
+      <c r="I58" s="0"/>
+      <c r="J58" s="0"/>
+      <c r="K58" s="0"/>
+      <c r="L58" s="0"/>
+      <c r="M58" s="0"/>
+      <c r="P58" s="0"/>
+    </row>
+    <row r="59" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I59" s="1"/>
+      <c r="K59" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -4547,12 +4611,12 @@
     <hyperlink ref="E44" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Charles_Parsons_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Charles Dacre PARSONS&lt;/a&gt; était un philosophe américain connu pour ses travaux en philosophie des mathématiques et en philosophie de Kant. Il a enseigné à Columbia puis à Harvard, où il est devenu professeur émérite. Il s’est formé à Harvard, avec une thèse dirigée par Willard Van Orman Quine, ce qui le place au croisement de la logique, de la philosophie analytique et des fondements des mathématiques. Son parcours intellectuel a été marqué très tôt par la rigueur mathématique, puisqu’il avait d’abord étudié les mathématiques avant de se tourner vers la philosophie. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la philosophie des mathématiques, domaine dans lequel il a travaillé sur la nature des objets mathématiques, la logique, la preuve et l’interprétation constructive des mathématiques prédicatives. Il a aussi beaucoup écrit sur Frege, Gödel, Hilbert et Quine, en lisant ces auteurs à la fois comme philosophes et comme figures majeures des fondements. &lt;/p&gt; &lt;p&gt; Il n’était pas seulement un spécialiste de logique ; il a aussi produit des travaux importants sur Kant, montrant comment les questions de connaissance, d’expérience et de structure de l’esprit se relient aux mathématiques. Cette double compétence, en philosophie des mathématiques et en histoire de la philosophie, explique pourquoi il est souvent vu comme un auteur à la fois technique et très large dans ses intérêts.&lt;/p&gt; &lt;p&gt; Son influence est restée forte dans le monde anglophone, au point d’être décrit comme l’un des philosophes des mathématiques les plus importants de sa génération. En plus de ses livres et articles, il a aussi contribué à l’édition de textes posthumes de Gödel, ce qui a renforcé son rôle dans l’étude contemporaine des fondements des mathématiques. &lt;/p&gt; &#10;&#10;&#10;"/>
     <hyperlink ref="I44" r:id="rId31" display="https://www.laphilo.fr/photo/cparsons.webp"/>
     <hyperlink ref="H46" r:id="rId32" display="https://www.laphilo.fr/pho/dihde-mini.webp"/>
-    <hyperlink ref="E47" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edward_Sa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Edward SAÏD&lt;/a&gt; était un intellectuel palestinien-américain, critique littéraire et professeur de littérature anglaise et comparée à l’université Columbia de New York. D’origine palestinienne et né à Jérusalem, il a grandi entre l’Égypte, les États-Unis et l’Europe, une expérience de déplacement qui a profondément marqué sa pensée sur l’identité, la colonisation et l’altérité.  &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est l’essai &lt;a href=&quot;https://www.youtube.com/watch?v=Ne4WRykmjhA&quot; title=&quot;Edward Said  Orientalisme par HD Doc&quot;&gt;L’Orientalisme : &lt;/a&gt;  L’Orient créé par l’Occident* (1978), considéré comme le texte fondateur des postcolonial studies. Dans cet ouvrage, Saïd montre que l’« Orient » n’est pas une réalité objective mais une invention de l’Occident : un discours façonné par des siècles de domination coloniale pour mieux contrôler et représenter l’Autre. &lt;/p&gt; &lt;p&gt; Pour lui, l’orientalisme est à la fois un savoir et un outil de pouvoir : il ne s’agit pas seulement de décrire l’Orient, mais de le hiérarchiser, de l’essentialiser et de le rendre  &lt;a href=&quot;https://www.youtube.com/watch?v=QBj-yWLnayM&quot; title=&quot;Edward Said writings on Orientalism par Middle East Eye&quot;&gt; inférieur à l’Occident. &lt;/a&gt; Il analyse quatre thèses principales : la domination politique et culturelle de l’Orient par l’Occident, la dépréciation de la langue arabe, la diabolisation de l’arabe et de l’islam, et la défense de la cause palestinienne. &lt;/p&gt; &lt;p&gt; Sa pensée articule critique littéraire, histoire, philosophie et sciences politiques, en s’inspirant notamment de Michel Foucault (discours–pouvoir) et de Jacques Derrida (déconstruction). Il montre que la violence du colonialisme n’est pas seulement matérielle (conquête, pillage), mais aussi épistémique : une violence de la raison qui classe, essentialise et dévalue les « Autres » de l’Occident. &lt;/p&gt; &lt;p&gt;  Intéressé par &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Edward-W-Said-1935-2003.html&quot; title=&quot;Edward Said par lesclesdumoyenorient&quot;&gt; l’engagement politique, &lt;/a&gt; il a aussi défendu la cause palestinienne et la légitimité des revendications d’autodétermination du peuple palestinien, tout en reconnaissance du droit à une patrie juive. Il rejetait le repli identitaire et prônait une vision universelle qui défend les différences et les droits, tissant des liens entre classicisme et excentricité, histoire et actualité. &lt;/p&gt;  &lt;audio controls title=&quot;Edward Said, une conscience morale par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-08.12.2017-ITEMA_21518070-2017C19327S0342-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &#10;&#10;&#10;"/>
-    <hyperlink ref="H47" r:id="rId34" display="https://laphilo.fr/pho/esaid-mini.webp"/>
-    <hyperlink ref="H48" r:id="rId35" display="https://www.laphilo.fr/pho/rmadams-mini.webp"/>
-    <hyperlink ref="E49" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Nozick&quot;  title=&quot; Wikipedia&quot;&gt;Robert NOZICK&lt;/a&gt; était un philosophe américain connu pour &lt;a href=&quot;https://www.youtube.com/watch?v=Q-t3cpFAk4o&quot;  title=&quot; Libertarianisme par Vadim Media&quot;&gt; son libertarianisme &lt;/a&gt; et sa critique des théories égalitaristes comme celle de John Rawls. Professeur à Harvard, il a marqué la philosophie politique, morale et épistémologique par son œuvre principale, Anarchie, État et utopie (1974), qui défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Minarchisme&quot;  title=&quot; Minarchisme par Wikipédia&quot;&gt; Etat Minimal. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il argue que seul l'État minimal, ou &quot;État gardien de nuit&quot;, est légitime, car il se limite à protéger les individus contre la force, la fraude et le vol, sans redistribuer les richesses. Il rejette l'anarcho-capitalisme en montrant, via des agences de protection privée, comment un État dominant émerge naturellement pour monopoliser la coercition légitime, justifié par le droit naturel à la personne. &lt;/p&gt; &lt;p&gt; Contrairement à la justice distributive de Rawls, il propose une théorie de l'entitlement : une acquisition initiale juste et des transferts volontaires rendent la distribution légitime, sans besoin d'égalisation par l'État. Toute intervention redistributive viole les droits individuels, traitant les personnes comme des moyens plutôt que des fins, en écho à Kant. &lt;/p&gt; &lt;p&gt; Dans Anarchie, État et utopie, Il réfute l'utilitarisme via l'expérience de pensée de la &lt;a href=&quot;https://www.youtube.com/watch?v=2FVwXaNWPQ0&quot;  title=&quot; La machine à expérience par Monsieur Phi&quot;&gt;&quot;machine à expérience&quot; :&lt;/a&gt;  même si elle offre un bonheur parfait et indistinguable de la réalité, les gens préfèrent vivre des actions réelles et façonner leur identité plutôt que des simulations. Cela prouve que le bonheur n'est pas le seul bien suprême. &lt;/p&gt; &lt;p&gt; Plus tard, dans Explications philosophiques (1981), il développe une théorie du suivi (tracking theory) en épistémologie, où la connaissance repose sur des conditionnels contrefactuels fiables, contournant le scepticisme sans justification traditionnelle. Son anti-coercitivisme intellectuel invite à une philosophie ouverte, non imposée. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Qui a peur des Libertariens par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-14.06.2022-ITEMA_23058436-2022C12410S0165-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;"/>
-    <hyperlink ref="H55" r:id="rId37" display="https://www.laphilo.fr/pho/imyoung-mini.webp"/>
-    <hyperlink ref="H56" r:id="rId38" display="https://www.laphilo.fr/pho/bhooks-mini.webp"/>
+    <hyperlink ref="E48" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edward_Sa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Edward SAÏD&lt;/a&gt; était un intellectuel palestinien-américain, critique littéraire et professeur de littérature anglaise et comparée à l’université Columbia de New York. D’origine palestinienne et né à Jérusalem, il a grandi entre l’Égypte, les États-Unis et l’Europe, une expérience de déplacement qui a profondément marqué sa pensée sur l’identité, la colonisation et l’altérité.  &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est l’essai &lt;a href=&quot;https://www.youtube.com/watch?v=Ne4WRykmjhA&quot; title=&quot;Edward Said  Orientalisme par HD Doc&quot;&gt;L’Orientalisme : &lt;/a&gt;  L’Orient créé par l’Occident* (1978), considéré comme le texte fondateur des postcolonial studies. Dans cet ouvrage, Saïd montre que l’« Orient » n’est pas une réalité objective mais une invention de l’Occident : un discours façonné par des siècles de domination coloniale pour mieux contrôler et représenter l’Autre. &lt;/p&gt; &lt;p&gt; Pour lui, l’orientalisme est à la fois un savoir et un outil de pouvoir : il ne s’agit pas seulement de décrire l’Orient, mais de le hiérarchiser, de l’essentialiser et de le rendre  &lt;a href=&quot;https://www.youtube.com/watch?v=QBj-yWLnayM&quot; title=&quot;Edward Said writings on Orientalism par Middle East Eye&quot;&gt; inférieur à l’Occident. &lt;/a&gt; Il analyse quatre thèses principales : la domination politique et culturelle de l’Orient par l’Occident, la dépréciation de la langue arabe, la diabolisation de l’arabe et de l’islam, et la défense de la cause palestinienne. &lt;/p&gt; &lt;p&gt; Sa pensée articule critique littéraire, histoire, philosophie et sciences politiques, en s’inspirant notamment de Michel Foucault (discours–pouvoir) et de Jacques Derrida (déconstruction). Il montre que la violence du colonialisme n’est pas seulement matérielle (conquête, pillage), mais aussi épistémique : une violence de la raison qui classe, essentialise et dévalue les « Autres » de l’Occident. &lt;/p&gt; &lt;p&gt;  Intéressé par &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Edward-W-Said-1935-2003.html&quot; title=&quot;Edward Said par lesclesdumoyenorient&quot;&gt; l’engagement politique, &lt;/a&gt; il a aussi défendu la cause palestinienne et la légitimité des revendications d’autodétermination du peuple palestinien, tout en reconnaissance du droit à une patrie juive. Il rejetait le repli identitaire et prônait une vision universelle qui défend les différences et les droits, tissant des liens entre classicisme et excentricité, histoire et actualité. &lt;/p&gt;  &lt;audio controls title=&quot;Edward Said, une conscience morale par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-08.12.2017-ITEMA_21518070-2017C19327S0342-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &#10;&#10;&#10;"/>
+    <hyperlink ref="H48" r:id="rId34" display="https://laphilo.fr/pho/esaid-mini.webp"/>
+    <hyperlink ref="H49" r:id="rId35" display="https://www.laphilo.fr/pho/rmadams-mini.webp"/>
+    <hyperlink ref="E50" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Nozick&quot;  title=&quot; Wikipedia&quot;&gt;Robert NOZICK&lt;/a&gt; était un philosophe américain connu pour &lt;a href=&quot;https://www.youtube.com/watch?v=Q-t3cpFAk4o&quot;  title=&quot; Libertarianisme par Vadim Media&quot;&gt; son libertarianisme &lt;/a&gt; et sa critique des théories égalitaristes comme celle de John Rawls. Professeur à Harvard, il a marqué la philosophie politique, morale et épistémologique par son œuvre principale, Anarchie, État et utopie (1974), qui défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Minarchisme&quot;  title=&quot; Minarchisme par Wikipédia&quot;&gt; Etat Minimal. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il argue que seul l'État minimal, ou &quot;État gardien de nuit&quot;, est légitime, car il se limite à protéger les individus contre la force, la fraude et le vol, sans redistribuer les richesses. Il rejette l'anarcho-capitalisme en montrant, via des agences de protection privée, comment un État dominant émerge naturellement pour monopoliser la coercition légitime, justifié par le droit naturel à la personne. &lt;/p&gt; &lt;p&gt; Contrairement à la justice distributive de Rawls, il propose une théorie de l'entitlement : une acquisition initiale juste et des transferts volontaires rendent la distribution légitime, sans besoin d'égalisation par l'État. Toute intervention redistributive viole les droits individuels, traitant les personnes comme des moyens plutôt que des fins, en écho à Kant. &lt;/p&gt; &lt;p&gt; Dans Anarchie, État et utopie, Il réfute l'utilitarisme via l'expérience de pensée de la &lt;a href=&quot;https://www.youtube.com/watch?v=2FVwXaNWPQ0&quot;  title=&quot; La machine à expérience par Monsieur Phi&quot;&gt;&quot;machine à expérience&quot; :&lt;/a&gt;  même si elle offre un bonheur parfait et indistinguable de la réalité, les gens préfèrent vivre des actions réelles et façonner leur identité plutôt que des simulations. Cela prouve que le bonheur n'est pas le seul bien suprême. &lt;/p&gt; &lt;p&gt; Plus tard, dans Explications philosophiques (1981), il développe une théorie du suivi (tracking theory) en épistémologie, où la connaissance repose sur des conditionnels contrefactuels fiables, contournant le scepticisme sans justification traditionnelle. Son anti-coercitivisme intellectuel invite à une philosophie ouverte, non imposée. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Qui a peur des Libertariens par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-14.06.2022-ITEMA_23058436-2022C12410S0165-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;"/>
+    <hyperlink ref="H56" r:id="rId37" display="https://www.laphilo.fr/pho/imyoung-mini.webp"/>
+    <hyperlink ref="H57" r:id="rId38" display="https://www.laphilo.fr/pho/bhooks-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2237,7 +2237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD59"/>
+  <dimension ref="A1:XFD60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
@@ -4554,24 +4554,183 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0"/>
-      <c r="B58" s="0"/>
-      <c r="C58" s="0"/>
-      <c r="D58" s="0"/>
-      <c r="E58" s="0"/>
+      <c r="A58" s="0">
+        <v>1535</v>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1616</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1535 – vers 1616</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe GUAMÁN POMA de Ayala</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Felipe_Guam%C3%A1n_Poma_de_Ayala" title=" Wikipedia"&gt;Felipe GUAMÁN POMA de Ayala&lt;/a&gt; est un noble andin de langue quechua, auteur de l’un des documents les plus extraordinaires de l’époque coloniale. Né dans la province de Lucanas, au Pérou, peu après la conquête espagnole, il descend par sa mère d’une lignée liée aux souverains de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_inca" title=" Wikipedia"&gt;Empire inca&lt;/a&gt;. Élevé parmi les Espagnols, il apprend leur langue, se fait chrétien et travaille comme interprète auprès d’un prêtre chargé d’extirper les « idolâtries », puis auprès de juges de Huamanga, avant d’être dépouillé de ses terres et banni vers 1600.&lt;/p&gt; &lt;p&gt;Il parcourt alors les Andes pendant des années et rédige, vers 1615, une lettre de près de 1 200 pages adressée au roi d’Espagne Philippe III : la &lt;em&gt;Nouvelle Chronique et bon gouvernement&lt;/em&gt;. Ses quelque 400 dessins à la plume racontent l’histoire des Incas, le calendrier, les travaux des champs, puis les abus des colons : prêtres, corregidors et propriétaires qui exploitent, volent et maltraitent les Indiens. Il y décrit un « monde à l’envers » (&lt;em&gt;mundo al revés&lt;/em&gt;), où l’ordre juste a été renversé par la conquête.&lt;/p&gt; &lt;p&gt;Il ne réclame pas le départ des Espagnols, mais un « bon gouvernement » : que les Andins se gouvernent eux-mêmes sous l’autorité lointaine du roi, et que les colons qui abusent soient chassés des villages. Il défend aussi la valeur de la civilisation andine, qui connaissait selon lui la justice et un ordre moral bien avant l’arrivée des Européens. Le manuscrit, qui n’atteignit sans doute jamais le roi, dormit pendant trois siècles avant d’être découvert en 1908 à la Bibliothèque royale de Copenhague. Il est aujourd’hui une source majeure sur le monde andin et l’une des premières critiques de la colonisation écrites par un colonisé.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="F58" s="0"/>
       <c r="G58" s="0"/>
-      <c r="H58" s="0"/>
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/guamanpoma-mini.webp</t>
+        </is>
+      </c>
       <c r="I58" s="0"/>
-      <c r="J58" s="0"/>
-      <c r="K58" s="0"/>
-      <c r="L58" s="0"/>
+      <c r="J58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme</t>
+        </is>
+      </c>
+      <c r="L58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chroniqueur andin, auteur d’une immense lettre illustrée au roi d’Espagne dénonçant la colonisation du Pérou.</t>
+        </is>
+      </c>
       <c r="M58" s="0"/>
-      <c r="P58" s="0"/>
+      <c r="N58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O58" s="1">
+        <v>2</v>
+      </c>
+      <c r="P58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Péruvienne</t>
+        </is>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1">
+        <v>1853</v>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1895</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1853 – 1895</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">José MARTÍ</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Mart%C3%AD" title=" Wikipedia"&gt;José MARTÍ&lt;/a&gt; est le grand penseur de l’indépendance cubaine et l’une des voix majeures de l’Amérique latine. Né à La Havane de parents espagnols, il est arrêté à seize ans pour ses idées indépendantistes et condamné aux travaux forcés dans une carrière, avant d’être déporté en Espagne, où il étudie le droit et la philosophie à Saragosse. Il vit ensuite au Mexique, au Guatemala et au Venezuela, puis s’installe en 1881 à New York, où il passe près de quinze ans comme journaliste, diplomate et organisateur de l’exil cubain. Il y écrit, pour de grands journaux d’Amérique latine, des chroniques sur la vie nord-américaine.&lt;/p&gt; &lt;p&gt;Dans son essai &lt;em&gt;Notre Amérique&lt;/em&gt; (1891), il appelle les nations latino-américaines à se penser à partir de leur propre réalité, métisse, indienne, noire et paysanne, plutôt qu’en copiant l’Europe ou les États-Unis : « Le gouvernement doit naître du pays. » Il y affirme aussi : « Il n’y a pas de haine des races, parce qu’il n’y a pas de races. » Observateur lucide de la puissance nord-américaine, il met en garde contre les ambitions des États-Unis sur Cuba et sur tout le continent.&lt;/p&gt; &lt;p&gt;Poète novateur, l’un des fondateurs du modernisme hispanique, il écrit les &lt;em&gt;Vers simples&lt;/em&gt; (1891), dont certains forment les paroles de la célèbre chanson &lt;em&gt;Guantanamera&lt;/em&gt;, et une revue pour les enfants, &lt;em&gt;L’Âge d’or&lt;/em&gt;. En 1892, il fonde le Parti révolutionnaire cubain et prépare la &lt;a href="https://fr.wikipedia.org/wiki/Guerre_d%27ind%C3%A9pendance_cubaine" title=" Wikipedia"&gt;guerre d’indépendance&lt;/a&gt;. Débarqué à Cuba avec les insurgés, il est tué au combat à Dos Ríos le 19 mai 1895. Il est considéré à Cuba comme le héros national et « l’Apôtre » de l’indépendance.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/marti-mini.webp</t>
+        </is>
+      </c>
       <c r="I59" s="1"/>
-      <c r="K59" s="1"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; esthetique</t>
+        </is>
+      </c>
+      <c r="K59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poète et penseur de l’indépendance cubaine, auteur de « Notre Amérique », héros national de Cuba.</t>
+        </is>
+      </c>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O59" s="1">
+        <v>2</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cubaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1">
+        <v>1921</v>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1997</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1921 – 1997</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paulo FREIRE</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paulo_Freire" title=" Wikipedia"&gt;Paulo FREIRE&lt;/a&gt; est un pédagogue et philosophe brésilien, l’un des penseurs de l’éducation les plus lus au monde. Né à Recife, dans le Nordeste, il connaît la faim pendant la crise des années 1930, ce qui le marque pour toute sa vie. Formé au droit et à la philosophie, lecteur de Marx comme des penseurs chrétiens, il se consacre à l’&lt;a href="https://fr.wikipedia.org/wiki/Alphab%C3%A9tisation" title=" Wikipedia"&gt;alphabétisation&lt;/a&gt; des adultes pauvres. En 1963, à Angicos, sa méthode permet à 300 travailleurs agricoles d’apprendre à lire et à écrire en une quarantaine d’heures.&lt;/p&gt; &lt;p&gt;Sa méthode part des « mots générateurs » tirés de la vie des apprenants, comme la brique, la terre ou le salaire, et fait de la lecture une prise de conscience : apprendre à lire le mot, c’est apprendre à lire le monde. Après le coup d’État militaire de 1964, il est emprisonné puis contraint à un exil de seize ans. Au Chili, il écrit &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_des_opprim%C3%A9s" title=" Wikipedia"&gt;&lt;em&gt;Pédagogie des opprimés&lt;/em&gt;&lt;/a&gt; (1968), où il critique l’éducation « bancaire », qui dépose des savoirs dans des élèves passifs comme on remplit un coffre, et lui oppose une éducation par le dialogue, où maître et élèves cherchent ensemble.&lt;/p&gt; &lt;p&gt;« Personne n’éduque autrui, personne ne s’éduque seul, les hommes s’éduquent ensemble par l’intermédiaire du monde. » L’éducation n’est jamais neutre : elle maintient l’oppression ou aide les opprimés à s’en libérer, sans devenir à leur tour oppresseurs. Rentré au Brésil en 1980, il dirige l’éducation de la ville de São Paulo. Son œuvre est à l’origine de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_critique" title=" Wikipedia"&gt;pédagogie critique&lt;/a&gt;, et il a été proclamé en 2012 patron de l’éducation brésilienne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/freire-mini.webp</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="K60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Marxisme</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pédagogue brésilien, auteur de Pédagogie des opprimés, penseur de l’éducation comme pratique de la liberté.</t>
+        </is>
+      </c>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O60" s="1">
+        <v>3</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brésilienne</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2237,7 +2237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD60"/>
+  <dimension ref="A1:XFD67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
@@ -4729,6 +4729,417 @@
       <c r="P60" t="inlineStr">
         <is>
           <t xml:space="preserve">Brésilienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1">
+        <v>1882</v>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1959</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1882 – 1959</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">José VASCONCELOS</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Vasconcelos" title=" Wikipedia"&gt;José VASCONCELOS&lt;/a&gt; est un philosophe, écrivain et homme politique mexicain, l’un des grands éducateurs de l’Amérique latine. Né à Oaxaca, avocat, il fonde en 1909 avec Antonio Caso et Alfonso Reyes l’Ateneo de la Juventud, cercle de jeunes intellectuels qui rejette le positivisme officiel du régime de Porfirio Díaz. Il prend part à la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_mexicaine" title=" Wikipedia"&gt;révolution mexicaine&lt;/a&gt; aux côtés de Francisco Madero. Recteur de l’université nationale en 1920, il lui donne sa devise, toujours en usage : « Par ma race parlera l’esprit. »&lt;/p&gt; &lt;p&gt;Ministre de l’Éducation de 1921 à 1924, il mène une véritable croisade pour instruire le peuple : écoles rurales, missions culturelles dans les villages, bibliothèques, éditions populaires des grands classiques. Il commande aussi aux peintres &lt;a href="https://fr.wikipedia.org/wiki/Diego_Rivera" title=" Wikipedia"&gt;Diego Rivera&lt;/a&gt; et José Clemente Orozco les fresques murales qui racontent l’histoire du Mexique sur les murs des bâtiments publics. Il est surnommé le « maître de la jeunesse d’Amérique ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Race cosmique&lt;/em&gt; (1925), il prophétise que l’Amérique latine, terre de tous les mélanges, verra naître une « cinquième race », synthèse de toutes les autres, porteuse d’une civilisation de l’amour et de la beauté. Sa philosophie, un « monisme esthétique », voit dans l’émotion esthétique la forme la plus haute de connaissance. Battu en 1929 dans une élection présidentielle qu’il juge truquée, il s’exile, puis évolue vers un conservatisme catholique, au point de manifester en 1940 des sympathies pour l’Allemagne nazie. Il meurt à Mexico en 1959.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vasconcelos-mini.webp</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; politique</t>
+        </is>
+      </c>
+      <c r="K61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monisme ; Spiritualisme</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et ministre mexicain de l’Éducation, auteur de La Race cosmique, penseur du métissage.</t>
+        </is>
+      </c>
+      <c r="N61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O61" s="1">
+        <v>2</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexicaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1">
+        <v>1907</v>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1972</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1907 – 1972</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abraham Joshua HESCHEL</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abraham_Joshua_Heschel" title=" Wikipedia"&gt;Abraham Joshua HESCHEL&lt;/a&gt; est un rabbin, théologien et philosophe juif, l’une des grandes voix religieuses du XXe siècle. Né à Varsovie dans une illustre famille du &lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;hassidisme&lt;/a&gt;, il étudie la philosophie à Berlin, où il soutient une thèse sur les prophètes d’Israël. Expulsé d’Allemagne vers la Pologne en 1938, il parvient à quitter Varsovie quelques semaines avant l’invasion allemande et gagne Londres, puis les États-Unis. Sa mère et ses sœurs sont assassinées pendant la Shoah. Il enseigne à partir de 1946 au Séminaire théologique juif de New York.&lt;/p&gt; &lt;p&gt;Pour Heschel, la religion commence par l’« étonnement radical » devant le monde, qui précède toute réflexion. Contre l’idée d’un Dieu impassible des philosophes, il parle du « pathos divin » : le Dieu des prophètes est concerné par le sort des hommes et souffre de l’injustice. La question n’est pas seulement de savoir si l’homme cherche Dieu, mais de comprendre que &lt;em&gt;Dieu est en quête de l’homme&lt;/em&gt;, titre de son livre de 1955. Dans &lt;em&gt;Les Bâtisseurs du temps&lt;/em&gt; (1951), il présente le &lt;a href="https://fr.wikipedia.org/wiki/Shabbat" title=" Wikipedia"&gt;shabbat&lt;/a&gt; comme « une cathédrale dans le temps » : le judaïsme sanctifie des moments plutôt que des lieux. Il consacre aussi un grand livre aux prophètes, témoins de la passion de Dieu pour la justice.&lt;/p&gt; &lt;p&gt;Sa foi le conduit à l’action. En 1965, il marche de Selma à Montgomery aux côtés de Martin Luther King et dira : « J’avais l’impression que mes jambes priaient. » Il s’oppose à la guerre du Vietnam et contribue au dialogue entre juifs et chrétiens lors du concile Vatican II. Il meurt à New York en 1972.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/heschel-mini.webp</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="K62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existentialisme ; Mysticisme</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rabbin et philosophe juif, penseur du « pathos divin » et du shabbat, militant des droits civiques.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O62" s="1">
+        <v>2</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1">
+        <v>1914</v>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1998</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1914 – 1998</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Octavio PAZ</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Octavio_Paz" title=" Wikipedia"&gt;Octavio PAZ&lt;/a&gt; est un poète, essayiste et diplomate mexicain, prix Nobel de littérature en 1990. Né à Mexico dans une famille marquée par la révolution, son père ayant été le représentant d’Emiliano Zapata aux États-Unis, il soutient les républicains pendant la guerre d’Espagne, puis rompt avec le communisme après l’assassinat de Trotski. Diplomate à Paris après la guerre, il y fréquente les surréalistes et André Breton.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Labyrinthe_de_la_solitude" title=" Wikipedia"&gt;&lt;em&gt;Le Labyrinthe de la solitude&lt;/em&gt;&lt;/a&gt; (1950), il interroge l’identité mexicaine : derrière les masques de la politesse et la violence des fêtes se cache une solitude née de l’histoire, celle d’un peuple issu de la conquête, qui a renié à la fois son passé indien et son passé espagnol. Il y évoque la figure de la &lt;a href="https://fr.wikipedia.org/wiki/La_Malinche" title=" Wikipedia"&gt;Malinche&lt;/a&gt;, compagne indienne de Cortés, symbole ambigu de l’origine métisse du pays. Mais cette solitude est aussi celle de l’homme moderne, et la poésie, l’amour et la fête sont des moyens de la dépasser. Dans &lt;em&gt;L’Arc et la Lyre&lt;/em&gt; (1956), il fait de la poésie une expérience de communion qui révèle l’homme à lui-même.&lt;/p&gt; &lt;p&gt;Ambassadeur du Mexique en Inde de 1962 à 1968, il découvre les philosophies et l’art de l’Orient, qui nourrissent sa poésie. Il démissionne après le &lt;a href="https://fr.wikipedia.org/wiki/Massacre_de_Tlatelolco" title=" Wikipedia"&gt;massacre de Tlatelolco&lt;/a&gt;, où des centaines d’étudiants sont tués par l’armée en 1968. Critique des totalitarismes de droite comme de gauche, il fonde la revue &lt;em&gt;Vuelta&lt;/em&gt; et consacre un grand livre à la poétesse et penseuse Juana Inés de la Cruz. Il meurt à Mexico en 1998, à quatre-vingt-quatre ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/paz-mini.webp</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; politique</t>
+        </is>
+      </c>
+      <c r="K63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poète et essayiste mexicain, prix Nobel 1990, auteur du Labyrinthe de la solitude.</t>
+        </is>
+      </c>
+      <c r="N63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O63" s="1">
+        <v>2</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexicaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1">
+        <v>1783</v>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1830</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1783 – 1830</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simón BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sim%C3%B3n_Bol%C3%ADvar" title=" Wikipedia"&gt;Simón BOLÍVAR&lt;/a&gt; est le chef militaire et politique des &lt;a href="https://fr.wikipedia.org/wiki/Guerres_d%27ind%C3%A9pendance_hispano-am%C3%A9ricaines" title=" Wikipedia"&gt;guerres d’indépendance&lt;/a&gt; de l’Amérique du Sud, surnommé le Libertador. Né à Caracas dans une riche famille créole, orphelin jeune, il est formé par son précepteur Simón Rodríguez, disciple de Rousseau, et découvre en Europe les idées des Lumières. À Rome, en 1805, il fait le serment de libérer son continent de la domination espagnole.&lt;/p&gt; &lt;p&gt;De 1813 à 1824, il mène une guerre longue et cruelle qui libère le Venezuela, la Colombie, l’Équateur, le Pérou et la Bolivie, qui porte son nom. Mais il est aussi un penseur politique. Dans sa &lt;a href="https://fr.wikipedia.org/wiki/Lettre_de_Jama%C3%AFque" title=" Wikipedia"&gt;&lt;em&gt;Lettre de Jamaïque&lt;/em&gt;&lt;/a&gt; (1815), écrite en exil, il analyse la situation de l’Amérique espagnole : un peuple ni européen ni indien, maintenu dans l’ignorance et l’inexpérience politique par trois siècles de colonisation. Dans son discours d’Angostura (1819), il plaide pour une république adaptée aux réalités du pays plutôt que copiée sur l’Europe ou les États-Unis, et réclame l’abolition de l’esclavage. Il affranchit ses propres esclaves, sans parvenir à imposer partout l’abolition.&lt;/p&gt; &lt;p&gt;Il rêve d’unir les nouvelles nations en une grande confédération et réunit à cette fin le congrès de Panama en 1826. Mais la &lt;a href="https://fr.wikipedia.org/wiki/Grande_Colombie" title=" Wikipedia"&gt;Grande Colombie&lt;/a&gt; qu’il préside se défait sous l’effet des rivalités régionales, et son autoritarisme croissant lui vaut de nombreux ennemis. Malade et désabusé, il meurt en 1830 à Santa Marta en disant avoir « labouré la mer ». Son rêve d’unité latino-américaine reste une référence majeure du continent.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/bolivar-mini.webp</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="K64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Républicanisme ; Libéralisme</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le Libertador, chef des indépendances sud-américaines et penseur de l’unité latino-américaine.</t>
+        </is>
+      </c>
+      <c r="N64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O64" s="1">
+        <v>2</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vénézuélienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1">
+        <v>1871</v>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1917</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1871 – 1917</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">José Enrique RODÓ</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Enrique_Rod%C3%B3" title=" Wikipedia"&gt;José Enrique RODÓ&lt;/a&gt; est un écrivain et essayiste uruguayen, l’un des grands maîtres à penser de l’Amérique latine au début du XXe siècle. Né à Montevideo, il doit interrompre ses études après la ruine de sa famille, se forme largement seul et devient professeur de littérature à l’université de Montevideo, puis député. Correspondant de &lt;a href="https://fr.wikipedia.org/wiki/Rub%C3%A9n_Dar%C3%ADo" title=" Wikipedia"&gt;Rubén Darío&lt;/a&gt;, il est le principal théoricien du modernisme, le grand mouvement de renouvellement de la littérature hispano-américaine.&lt;/p&gt; &lt;p&gt;Son essai &lt;em&gt;Ariel&lt;/em&gt; (1900), écrit deux ans après la victoire des États-Unis sur l’Espagne à Cuba, prend la forme d’un dernier cours donné par un vieux maître, Prospero, à ses élèves. Empruntant les personnages de &lt;em&gt;La Tempête&lt;/em&gt; de Shakespeare, il oppose Ariel, l’esprit, la beauté, le désintéressement, à Caliban, la matière, l’utilité, les appétits. Il met en garde la jeunesse latino-américaine contre l’utilitarisme et la « nordomanie », la fascination pour le modèle des États-Unis, puissant mais tourné vers le seul profit.&lt;/p&gt; &lt;p&gt;Rodó invite les jeunes à cultiver toutes les facultés de l’esprit, à préserver un temps libre pour la pensée et la beauté, et à construire une démocratie qui élève chacun au lieu de niveler par le bas. Le livre connut un immense succès et inspira tout un courant, l’« arielisme ». Plus tard, des penseurs comme Roberto Fernández Retamar ont renversé le symbole en faisant de Caliban la figure du colonisé. Dans &lt;em&gt;Motifs de Protée&lt;/em&gt; (1909), il médite sur la transformation continuelle de soi. Rodó meurt à Palerme en 1917, au cours d’un voyage en Europe.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rodo-mini.webp</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; ethique</t>
+        </is>
+      </c>
+      <c r="K65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Spiritualisme</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">essayiste uruguayen, auteur d’Ariel, maître à penser de la jeunesse latino-américaine.</t>
+        </is>
+      </c>
+      <c r="N65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O65" s="1">
+        <v>2</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uruguayenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1">
+        <v>1922</v>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1979</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1922 – 1979</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rodolfo KUSCH</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Rodolfo_Kusch" title=" Wikipedia (es)"&gt;Rodolfo KUSCH&lt;/a&gt; est un philosophe et anthropologue argentin qui a cherché à fonder une philosophie à partir de la pensée indigène et populaire de l’Amérique. Né à Buenos Aires de parents allemands, il étudie la philosophie à l’université de Buenos Aires, enseigne l’esthétique et écrit aussi pour le théâtre, notamment sur le tango. Persécuté pour ses sympathies péronistes après 1955, il part pour la Bolivie et le Pérou, puis s’installe dans le nord-ouest de l’Argentine, à Maimará, dans la province de Jujuy.&lt;/p&gt; &lt;p&gt;Au contact des communautés &lt;a href="https://fr.wikipedia.org/wiki/Quechuas" title=" Wikipedia"&gt;quechuas&lt;/a&gt; et &lt;a href="https://fr.wikipedia.org/wiki/Aymaras" title=" Wikipedia"&gt;aymaras&lt;/a&gt; des Andes, il mène de longues enquêtes de terrain, dont il tire &lt;em&gt;L’Amérique profonde&lt;/em&gt; (1962) et &lt;em&gt;La Pensée indigène et populaire en Amérique&lt;/em&gt; (1970). Il y oppose deux attitudes. Celle de l’Occident, l’« être », qui veut dominer le monde, le transformer et accumuler. Et celle de l’Amérique indienne, l’« être là » ou le simple « se tenir » (en espagnol &lt;em&gt;estar&lt;/em&gt;), qui accepte l’incertitude du monde, ses forces et ses menaces, et cherche à vivre en équilibre avec lui.&lt;/p&gt; &lt;p&gt;Pour Kusch, les classes moyennes des villes, qui se veulent européennes, vivent dans la peur de cette « Amérique profonde » qu’elles refoulent. Penser en Amérique, c’est accepter cette part indienne et populaire au lieu de la mépriser. Son œuvre, longtemps marginale, a nourri la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt; et les pensées décoloniales latino-américaines, et elle est aujourd’hui redécouverte. Il parle même de « phagocytose » : la culture populaire finirait par absorber ce que la modernité importée croit lui imposer. Il meurt en 1979 à Maimará, à cinquante-sept ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kusch-mini.webp</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buen Vivir (cosmovision andine)</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et anthropologue argentin, penseur de l’« Amérique profonde » et de la pensée indigène et populaire.</t>
+        </is>
+      </c>
+      <c r="N66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O66" s="1">
+        <v>2</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentine</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1">
+        <v>1925</v>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1974</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1925 – 1974</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Augusto SALAZAR BONDY</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Augusto_Salazar_Bondy" title=" Wikipedia (es)"&gt;Augusto SALAZAR BONDY&lt;/a&gt; est un philosophe et éducateur péruvien, l’une des figures fondatrices de la philosophie latino-américaine de la libération. Né à Lima, frère cadet de l’écrivain Sebastián Salazar Bondy, il étudie à l’université San Marcos, puis au Mexique auprès de José Gaos et de Leopoldo Zea, et à Paris, où il suit les cours de Jean Wahl, Jean Hyppolite et Gaston Bachelard. Professeur d’éthique à San Marcos, il écrit une grande histoire des idées au Pérou contemporain.&lt;/p&gt; &lt;p&gt;En 1968, il publie &lt;em&gt;Existe-t-il une philosophie de notre Amérique ?&lt;/em&gt;, qui provoque un vif débat avec Leopoldo Zea. Sa réponse est dure : jusqu’ici, il n’existe pas de philosophie latino-américaine authentique, mais seulement des imitations des courants européens, adoptés tour à tour sans être vraiment pensés. Ce n’est pas un manque de talent : c’est la conséquence de la domination et du sous-développement, qui produisent une culture dépendante et « aliénée », incapable de se penser elle-même.&lt;/p&gt; &lt;p&gt;Une philosophie authentique ne pourra naître qu’en prenant pour objet cette situation de domination, et en contribuant à la transformer. La philosophie devient ainsi une tâche de libération, comme le développera la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt;. Engagé dans la réforme de l’éducation sous le gouvernement péruvien de la fin des années 1960, il défend une école qui forme des personnes libres et critiques. Il meurt prématurément à Lima en 1974, à quarante-huit ans. Ses idées ont notamment inspiré Enrique Dussel.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/salazarbondy-mini.webp</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiers-mondisme</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe péruvien, auteur d’Existe-t-il une philosophie de notre Amérique ?, penseur de la domination.</t>
+        </is>
+      </c>
+      <c r="N67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O67" s="1">
+        <v>2</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2237,7 +2237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD67"/>
+  <dimension ref="A1:XFD71"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
@@ -5140,6 +5140,248 @@
       <c r="P67" t="inlineStr">
         <is>
           <t xml:space="preserve">Péruvienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1">
+        <v>1839</v>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1903</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1839 – 1903</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eugenio María de HOSTOS</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Eugenio_Mar%C3%ADa_de_Hostos" title=" Wikipedia (en)"&gt;Eugenio María de HOSTOS&lt;/a&gt; est un philosophe, éducateur, sociologue et écrivain de &lt;a href="https://fr.wikipedia.org/wiki/Porto_Rico" title=" Wikipedia"&gt;Porto Rico&lt;/a&gt;, surnommé « le Grand Citoyen des Amériques ». Né à Mayagüez dans une famille aisée, il fait ses études en Espagne, où il étudie le droit et la philosophie à Madrid et publie en 1863 un roman, &lt;em&gt;Le Pèlerinage de Bayoán&lt;/em&gt;, qui évoque déjà le destin des Antilles. Déçu que la République espagnole refuse l’autonomie de Porto Rico, il quitte l’Espagne en 1869 pour se consacrer à l’indépendance des colonies antillaises.&lt;/p&gt; &lt;p&gt;Il rêve d’une Confédération des Antilles, réunissant Porto Rico, Cuba et la République dominicaine, et parcourt pour la défendre les États-Unis, le Pérou, le Chili, l’Argentine, le Brésil et le Venezuela. Partout, il fonde ou réforme des écoles. En République dominicaine, il crée en 1880 la première école normale, qui forme des instituteurs à une pédagogie scientifique et laïque. Au Chili, il plaide pour que les femmes aient accès à l’enseignement supérieur et aux professions savantes.&lt;/p&gt; &lt;p&gt;Sa &lt;em&gt;Morale sociale&lt;/em&gt; (1888), inspirée du &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt;, fonde les devoirs de l’individu non sur la religion, mais sur la raison et sur les liens qui l’unissent à la famille, à la société et à l’humanité ; l’éducation doit former des consciences libres et responsables. Après la guerre de 1898, qui fait passer Porto Rico sous domination américaine, il milite pour que l’île puisse décider elle-même de son avenir. Il laisse aussi un traité de sociologie, l’un des premiers d’Amérique latine. Il meurt en exil à Saint-Domingue en 1903.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hostos-mini.webp</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="K68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positivisme</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">éducateur et penseur portoricain, apôtre d’une confédération des Antilles et d’une morale sociale laïque.</t>
+        </is>
+      </c>
+      <c r="N68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O68" s="1">
+        <v>2</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portoricaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1">
+        <v>1925</v>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2008</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1925 – 2008</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orlando FALS BORDA</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Orlando_Fals_Borda" title=" Wikipedia (en)"&gt;Orlando FALS BORDA&lt;/a&gt; est un sociologue colombien, l’un des grands penseurs latino-américains des sciences sociales et le fondateur de la « recherche-action participative ». Né à Barranquilla, sur la côte caraïbe, formé aux États-Unis, il fonde en 1959 à l’Université nationale de Colombie, avec le prêtre Camilo Torres, l’une des premières facultés de sociologie d’Amérique latine. Son livre &lt;em&gt;La Violence en Colombie&lt;/em&gt; (1962), écrit avec Germán Guzmán et Eduardo Umaña, étudie pour la première fois la guerre civile qui ravage les campagnes.&lt;/p&gt; &lt;p&gt;Déçu par une sociologie qui observe les pauvres de l’extérieur sans rien changer à leur sort, il quitte l’université dans les années 1970 pour travailler avec les paysans et les communautés de la côte caraïbe. Il y développe la &lt;a href="https://fr.wikipedia.org/wiki/Recherche-action" title=" Wikipedia"&gt;recherche-action&lt;/a&gt; participative : le chercheur ne doit pas monopoliser le savoir ni imposer sa technique, mais travailler avec les communautés comme avec des partenaires et des co-chercheurs, recueillir leurs savoirs, leur mémoire et leurs récits, et partager les résultats sous une forme que tous peuvent comprendre.&lt;/p&gt; &lt;p&gt;La science n’est pas, selon lui, une affaire d’experts neutres : elle doit servir la transformation de la société et la libération des opprimés. Il parle d’une « subversion positive » qui conteste l’ordre injuste pour en construire un meilleur. Ses idées se sont répandues dans le monde entier, en éducation, en santé et en développement. Il participe aussi à l’Assemblée constituante qui rédige la Constitution colombienne de 1991. Il meurt à Bogotá en 2008.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/falsborda-mini.webp</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; politique</t>
+        </is>
+      </c>
+      <c r="K69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiers-mondisme</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sociologue colombien, fondateur de la recherche-action participative, penseur d’un savoir construit avec le peuple.</t>
+        </is>
+      </c>
+      <c r="N69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O69" s="1">
+        <v>2</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colombienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1">
+        <v>1928</v>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928 – 2021</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humberto MATURANA</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Humberto_Maturana" title=" Wikipedia"&gt;Humberto MATURANA&lt;/a&gt; est un biologiste et philosophe chilien, l’un des penseurs les plus originaux de la biologie de la connaissance. Né à Santiago, il étudie la médecine et la biologie au Chili, puis en Angleterre et à Harvard. Au Massachusetts Institute of Technology, il participe en 1959 à une étude devenue célèbre sur ce que l’œil de la grenouille transmet à son cerveau, qui montre que la perception n’est pas une simple copie du monde extérieur. Il fonde ensuite à l’université du Chili un laboratoire d’« épistémologie expérimentale ».&lt;/p&gt; &lt;p&gt;Avec son élève Francisco Varela, il propose au début des années 1970 le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, du grec « se produire soi-même » : un être vivant est un système qui produit et renouvelle sans cesse ses propres composants, et maintient ainsi sa propre organisation. La cellule en est le modèle. Le vivant n’est donc pas défini par ce qu’il contient, mais par cette manière de s’entretenir lui-même, en échange constant avec son milieu.&lt;/p&gt; &lt;p&gt;Il en tire une théorie de la connaissance : « Tout ce qui est dit est dit par un observateur. » Connaître n’est pas refléter un monde tout fait, mais une activité du vivant, qui fait émerger un monde à travers son action. Dans &lt;em&gt;L’Arbre de la connaissance&lt;/em&gt; (1984), écrit avec Varela, il montre aussi que le langage et la société naissent de la coordination entre les êtres, et que l’amour, l’acceptation de l’autre, est le fondement biologique de la vie sociale. Ses idées ont nourri le &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_%28%C3%A9pist%C3%A9mologie%29" title=" Wikipedia"&gt;constructivisme&lt;/a&gt;, la thérapie familiale et la théorie des systèmes sociaux de &lt;a href="https://fr.wikipedia.org/wiki/Niklas_Luhmann" title=" Wikipedia"&gt;Niklas Luhmann&lt;/a&gt;. Il meurt à Santiago en 2021.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/maturana-mini.webp</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
+        </is>
+      </c>
+      <c r="K70" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Constructivisme</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">biologiste et philosophe chilien, inventeur avec Varela de l’autopoïèse, penseur de la connaissance comme fait biologique.</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N70" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O70" s="1">
+        <v>2</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chilienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1">
+        <v>1946</v>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2001</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1946 – 2001</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Francisco VARELA</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_Varela" title=" Wikipedia"&gt;Francisco VARELA&lt;/a&gt; est un biologiste, neuroscientifique et philosophe chilien, l’un des fondateurs des sciences cognitives « incarnées ». Né à Talcahuano, élève d’Humberto Maturana, il soutient une thèse de biologie à Harvard, puis invente avec son maître le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, qui définit le vivant par sa capacité à se produire lui-même. Après le coup d’État de Pinochet en 1973, il doit s’exiler aux États-Unis. Il s’installe en France en 1986 et dirige jusqu’à sa mort une équipe de recherche au CNRS, à Paris.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Inscription corporelle de l’esprit&lt;/em&gt; (1991), écrit avec Evan Thompson et Eleanor Rosch, il critique l’idée que l’esprit serait un ordinateur qui traite des représentations d’un monde extérieur déjà donné. Il propose à la place l’« &lt;a href="https://fr.wikipedia.org/wiki/%C3%89naction" title=" Wikipedia"&gt;énaction&lt;/a&gt; » : la cognition est une action incarnée, par laquelle un être vivant fait émerger son monde à travers son corps, ses sens et ses gestes. Il fonde aussi la « neurophénoménologie », qui veut unir les mesures du cerveau et la description rigoureuse de l’expérience vécue, à la manière de Husserl et de Merleau-Ponty.&lt;/p&gt; &lt;p&gt;Pratiquant du bouddhisme tibétain depuis les années 1970, il voit dans la méditation une méthode précise pour explorer l’expérience. En 1987, il cofonde le &lt;a href="https://fr.wikipedia.org/wiki/Mind_and_Life_Institute" title=" Wikipedia"&gt;Mind and Life Institute&lt;/a&gt;, qui organise des rencontres entre scientifiques et le dalaï-lama. Il est l’un des inspirateurs de l’idée d’un esprit « incarné », aujourd’hui centrale en &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_l%27esprit" title=" Wikipedia"&gt;philosophie de l’esprit&lt;/a&gt;. Il meurt à Paris en 2001, à cinquante-quatre ans, d’une maladie du foie.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/varela-mini.webp</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
+        </is>
+      </c>
+      <c r="K71" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Constructivisme ; Phénoménologie</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neurobiologiste et philosophe chilien, penseur de l’énaction et du dialogue entre sciences cognitives et bouddhisme.</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N71" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O71" s="1">
+        <v>2</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chilienne</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2237,7 +2237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD71"/>
+  <dimension ref="A1:XFD72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
@@ -2550,11 +2550,16 @@
       <c r="C9" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>76</v>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Charles Sanders PEIRCE</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Sanders_Peirce" title=" Wikipedia"&gt;Charles Sanders PEIRCE&lt;/a&gt;  était un philosophe, logicien, scientifique américain assez original, fondateur du  &lt;a href="https://www.youtube.com/watch?v=AGHmKg7wYf0"  title="Pragmatisme  par robertus"&gt;pragmatisme&lt;/a&gt; , père de la sémiotique moderne (théorie des signes) et un pionnier de la logique. Pourtant, en raison de  &lt;a href="https://laviedesidees.fr/Chevalier-Peirce-ou-l-invention-de-l-epistemologie" style="color:#88A1E9" title="les pepites de Charles s pierce par laviedesidees"&gt;sa personnalité difficile&lt;/a&gt; et de ses idées avant-gardistes, il vécut en marge du monde académique, mourant dans la pauvreté et l'isolement. &lt;/p&gt; &lt;p&gt;  Il cherchait à identifier les catégories les plus fondamentales et universelles de la pensée et de l'être, qu'il nomma Phanéroscopie.Il en déduit trois, présentes dans tous les phénomènes. Elles sont la clé de voûte de tout le système peircien et sont indispensables pour comprendre sa sémiotique et  &lt;a href="https://hal.science/hal-02953592/document"  title="Pragmatisme  par hal science"&gt;son pragmatisme&lt;/a&gt;: &lt;/p&gt; &lt;p&gt; - Priméité (Firstness) : C'est la catégorie de la qualité pure, de la potentialité, de la sensation immédiate et brute, existant en elle-même sans référence à quoi que ce soit d'autre. C'est le "sentiment de rouge", la qualité d'une odeur, la nouveauté d'une idée. C'est le domaine de la possibilité et de la liberté. &lt;/p&gt; &lt;p&gt; - Secondéité (Secondeity) : C'est la catégorie du fait brut, de l'action-réaction, de la résistance et de l'actualité. C'est le choc du "ici et maintenant", la rencontre avec un autre qui s'impose à nous. Exemples : une collision, la sensation de résistance en poussant une porte, un conflit. C'est le domaine de l'existence et de la dualité. &lt;/p&gt; &lt;p&gt; - Tiercéité (Thirdness) : C'est la catégorie de la médiation, de la loi, de l'habitude, de la généralisation et de la signification. Elle fait le lien entre la Priméité (la qualité) et la Secondéité (le fait) en leur donnant un sens et une régularité. Exemples : une loi scientifique, un symbole linguistique, une tendance, une règle de conduite. C'est le domaine de la pensée, de la continuité et de l'intelligibilité. &lt;/p&gt; &lt;p&gt; Il propose une méthode pour clarifier le sens de nos idées, le Pragmaticisme: le sens d'un concept réside dans ses conséquences pratiques observables. Si deux idées ne produisent aucune différence pratique, elles signifient la même chose. C'est avant tout une méthode logique pour trancher les disputes métaphysiques stériles.&lt;/p&gt; &lt;p&gt; Sa contribution la plus novatrice et la plus influente est &lt;a href="https://www.persee.fr/doc/lgge_0458-726x_1980_num_14_58_1844" title="La séméiotique de Charles S. Peirce  par Persée"&gt;la Sémiotique&lt;/a&gt; . Pour lui, "l'homme est un signe" et toute pensée est un &lt;a href="https://www.youtube.com/watch?v=e1jrx1RlS00" title="VOIR ET INTERPRÉTER LES SIGNES ! Introduction à la sémiologie CHARLES SANDERS PEIRCE  par Survivreauxscienceshumaines"&gt;processus sémiotique&lt;/a&gt;. Il définit le signe non pas de manière dyadique mais triadique,  Il crée dans l'esprit de la  personne un signe plus développé, appelé l'interprétant. La relation signe-objet-interprétant est fondamentale. Sa classification concerne la relation du signe à son objet : &lt;/p&gt; &lt;dd&gt; - Icône: Le signe ressemble à son objet ou partage des qualités avec lui (une photographie, un diagramme) . &lt;/dd&gt; &lt;dd&gt; - Index: Le signe est physiquement connecté à son objet . la fumée (indice du feu), une girouette (indice de la direction du vent). &lt;/dd&gt; &lt;dd&gt; - Symbole: La relation entre le signe et l'objet est arbitraire et conventionnelle. Elle repose sur une règle ou une habitude sociale. ("arbre" n'a rien d'un arbre). &lt;/dd&gt; &lt;p&gt; Bien que mort dans la misère et méconnu de son vivant, son influence est immense aujourd'hui en philosophie, en sciences cognitives, en linguistique et en sociologie. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F9" s="7" t="s">
         <v>77</v>
@@ -5382,6 +5387,69 @@
       <c r="P71" t="inlineStr">
         <is>
           <t xml:space="preserve">Chilienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1">
+        <v>1868</v>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1963</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1868 – 1963</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W. E. B. DU BOIS</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/W._E._B._Du_Bois" title=" Wikipedia"&gt;W. E. B. DU BOIS&lt;/a&gt; (William Edward Burghardt Du Bois) est un sociologue, historien et militant africain-américain, l’un des plus grands penseurs américains du XXe siècle. Né en 1868 dans le Massachusetts, il étudie à Fisk, à Berlin, puis à Harvard, où il devient en 1895 le premier Africain-Américain à obtenir un doctorat. Son étude &lt;em&gt;The Philadelphia Negro&lt;/em&gt; (1899) est l’une des premières grandes enquêtes de sociologie empirique aux États-Unis.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Les_%C3%82mes_du_peuple_noir" title=" Wikipedia"&gt;&lt;em&gt;Les Âmes du peuple noir&lt;/em&gt;&lt;/a&gt; (1903), il affirme que « le problème du XXe siècle est le problème de la ligne de couleur ». Il y décrit la « double conscience » des Noirs américains : le sentiment de se voir toujours à travers les yeux d’un monde qui les méprise, d’être à la fois américain et noir, « deux âmes, deux pensées, deux combats inconciliables dans un seul corps sombre ». Dans &lt;em&gt;Black Reconstruction&lt;/em&gt; (1935), il réhabilitera le rôle des anciens esclaves dans l’histoire américaine d’après la guerre de Sécession. Il y critique aussi Booker T. Washington, qui conseillait aux Noirs d’accepter la ségrégation en échange du progrès économique.&lt;/p&gt; &lt;p&gt;En 1909, il est l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/National_Association_for_the_Advancement_of_Colored_People" title=" Wikipedia"&gt;NAACP&lt;/a&gt;, la grande organisation de défense des droits civiques, dont il dirige la revue &lt;em&gt;The Crisis&lt;/em&gt;. Il organise plusieurs congrès panafricains et devient le « père du &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; ». Proche du socialisme, persécuté pendant le maccarthysme, il s’installe à la fin de sa vie au &lt;a href="https://fr.wikipedia.org/wiki/Ghana" title=" Wikipedia"&gt;Ghana&lt;/a&gt;, à l’invitation de Kwame Nkrumah, et y meurt en 1963, à la veille de la marche sur Washington de Martin Luther King.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dubois-mini.webp</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K72" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pan-africanisme</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sociologue et militant africain-américain, penseur de la « double conscience » et père du panafricanisme.</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N72" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O72" s="1">
+        <v>3</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2237,7 +2237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD72"/>
+  <dimension ref="A1:XFD74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
@@ -3518,8 +3518,10 @@
       <c r="J32" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>294</v>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
+        </is>
       </c>
       <c r="L32" s="2" t="s">
         <v>295</v>
@@ -3845,8 +3847,10 @@
       <c r="J40" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>365</v>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Hassidisme</t>
+        </is>
       </c>
       <c r="L40" s="14" t="s">
         <v>366</v>
@@ -4044,8 +4048,10 @@
       <c r="J45" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K45" s="2" t="s">
-        <v>294</v>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiers-mondisme ; Théologie de la libération ; Philosophie de la libération ; Pensée décoloniale</t>
+        </is>
       </c>
       <c r="L45" s="2" t="s">
         <v>407</v>
@@ -4715,7 +4721,7 @@
       </c>
       <c r="K60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Marxisme</t>
+          <t xml:space="preserve">Humanisme ; Marxisme ; Théologie de la libération</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -4831,7 +4837,7 @@
       </c>
       <c r="K62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Existentialisme ; Mysticisme</t>
+          <t xml:space="preserve">Existentialisme ; Mysticisme ; Hassidisme</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -5068,7 +5074,7 @@
       </c>
       <c r="K66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen Vivir (cosmovision andine)</t>
+          <t xml:space="preserve">Buen Vivir (cosmovision andine) ; Philosophie de la libération</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -5126,7 +5132,7 @@
       </c>
       <c r="K67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiers-mondisme</t>
+          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -5450,6 +5456,120 @@
       <c r="P72" t="inlineStr">
         <is>
           <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1">
+        <v>1928</v>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928 – 2024</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gustavo GUTIÉRREZ</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo GUTIÉRREZ&lt;/a&gt; est un prêtre et théologien péruvien, considéré comme le père de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;théologie de la libération&lt;/a&gt;. Né à Lima en 1928 dans un milieu modeste, il souffre adolescent d’une ostéomyélite qui le cloue longtemps au lit ; il lit alors beaucoup et commence des études de médecine pour devenir psychiatre. À vingt-quatre ans, il choisit la prêtrise et part étudier la philosophie et la psychologie à Louvain, puis la théologie à Lyon.&lt;/p&gt; &lt;p&gt;Ordonné prêtre en 1959, il devient vicaire dans un quartier pauvre de Lima, tout en enseignant à l’université catholique, et repense toute sa théologie au contact de ce peuple. En 1971, il publie &lt;em&gt;Théologie de la libération&lt;/em&gt;, traduit dans une vingtaine de langues. La pauvreté, écrit-il, n’est pas une fatalité mais le fruit d’injustices, et elle est contraire à la volonté de Dieu. La théologie est une « réflexion critique sur la pratique à la lumière de la Parole » : elle vient en second, après l’engagement aux côtés des pauvres. Le salut ne se joue pas seulement dans l’au-delà ; il touche toute l’existence, et la libération sociale et politique en fait partie, sans s’y réduire. Dans &lt;em&gt;Boire à son propre puits&lt;/em&gt; (1983), il montre que cet engagement est aussi une spiritualité, une manière de suivre le Christ.&lt;/p&gt; &lt;p&gt;Ses positions lui valent la méfiance de Rome dans les années 1980, sans condamnation. Entré chez les Dominicains en 1998, il enseigne dans de nombreuses universités d’Europe et des États-Unis. Le pape François le reçoit en 2013, signe de la réhabilitation de son œuvre, et l’« option préférentielle pour les pauvres » est devenue un principe de l’enseignement de l’Église. Il meurt à Lima en 2024, à quatre-vingt-seize ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ggutierrez-mini.webp</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; politique</t>
+        </is>
+      </c>
+      <c r="K73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de la libération</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prêtre et théologien péruvien, père de la théologie de la libération et de l’« option préférentielle pour les pauvres ».</t>
+        </is>
+      </c>
+      <c r="N73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O73" s="1">
+        <v>2</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Péruvienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1">
+        <v>1928</v>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2018</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928 – 2018</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aníbal QUIJANO</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal QUIJANO&lt;/a&gt; est un sociologue péruvien, l’un des grands penseurs latino-américains du XXe siècle et le fondateur de la pensée décoloniale. Né en 1928 à Yanama, dans les Andes péruviennes, il étudie à l’université de San Marcos, à Lima, où il enseigne ensuite la sociologie. Dans les années 1960 et 1970, il participe aux travaux de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_la_d%C3%A9pendance" title=" Wikipedia"&gt;théorie de la dépendance&lt;/a&gt;, qui explique le sous-développement de l’Amérique latine par sa place subordonnée dans l’économie mondiale, et étudie la condition des populations indiennes et métisses des villes.&lt;/p&gt; &lt;p&gt;En 1992, pour le cinquième centenaire de l’arrivée de Christophe Colomb, il publie l’article « Colonialité et modernité/rationalité », qui forge la notion de « colonialité du pouvoir ». La conquête de l’Amérique a donné naissance à la fois au capitalisme mondial et à une idée nouvelle, celle de « race », qui a permis de classer les peuples en supérieurs et inférieurs et de distribuer entre eux le travail : le salariat pour les Européens, le servage pour les Indiens, l’esclavage pour les Africains. Cette classification a survécu à l’indépendance des colonies : elle structure encore les rapports sociaux, le savoir et la manière dont chacun se perçoit. Quijano critique aussi l’« eurocentrisme », qui fait de l’histoire européenne le modèle de l’histoire universelle.&lt;/p&gt; &lt;p&gt;Professeur à l’université de Binghamton, aux États-Unis, il anime le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt; avec Walter Mignolo et Enrique Dussel. La philosophe argentine &lt;a href="https://fr.wikipedia.org/wiki/Mar%C3%ADa_Lugones" title=" Wikipedia"&gt;María Lugones&lt;/a&gt; a prolongé son concept dans celui de « colonialité du genre ». Il meurt à Lima en 2018.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/quijano-mini.webp</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée décoloniale</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sociologue péruvien, inventeur de la « colonialité du pouvoir » et fondateur de la pensée décoloniale.</t>
+        </is>
+      </c>
+      <c r="N74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O74" s="1"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2237,7 +2237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD74"/>
+  <dimension ref="A1:XFD75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
@@ -5570,6 +5570,62 @@
       <c r="P74" t="inlineStr">
         <is>
           <t xml:space="preserve">Péruvienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1">
+        <v>1840</v>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1910</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1840 – 1910</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">William Graham SUMNER</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/William_Graham_Sumner" title=" Wikipedia"&gt;William Graham SUMNER&lt;/a&gt; est un sociologue et économiste américain, l’un des fondateurs de la sociologie aux États-Unis et la figure majeure de ce qu’on appellera le &lt;a href="https://fr.wikipedia.org/wiki/Darwinisme_social" title=" Wikipedia"&gt;darwinisme social&lt;/a&gt; américain. Né en 1840 à Paterson, dans le New Jersey, fils d’un ouvrier anglais immigré, il étudie à Yale, puis en Europe, et devient d’abord pasteur épiscopalien. En 1872, il est nommé professeur à Yale, où il donne l’un des premiers cours intitulés « sociologie ».&lt;/p&gt; &lt;p&gt;Lecteur de Herbert Spencer, il applique à la société l’idée de lutte pour l’existence. Dans &lt;em&gt;Ce que les classes sociales se doivent les unes aux autres&lt;/em&gt; (1883), il répond : rien, sinon le respect de la liberté et des contrats. L’aide de l’État aux pauvres se fait toujours aux dépens de l’« homme oublié », le travailleur modeste qui paie ses impôts sans rien demander. La richesse récompense le travail, l’épargne et la tempérance, et la réussite des plus capables profite à toute la société. Ces positions ont fait de lui, aux yeux de ses critiques, le défenseur d’un capitalisme sans pitié pour les faibles.&lt;/p&gt; &lt;p&gt;Mais il défend aussi le libre-échange contre les monopoles protégés et s’oppose fermement à l’impérialisme : en 1898, il dénonce la guerre contre l’Espagne et la conquête des Philippines dans &lt;em&gt;La Conquête des États-Unis par l’Espagne&lt;/em&gt;. Dans &lt;em&gt;Folkways&lt;/em&gt; (1906), il étudie les coutumes et les mœurs des sociétés, et forge le mot « ethnocentrisme » pour désigner la tendance de chaque groupe à juger les autres d’après ses propres valeurs. Il meurt en 1910.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/sumner-mini.webp</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Darwinisme social ; Libéralisme</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sociologue américain de Yale, défenseur d’un libéralisme sans État-providence, inventeur du mot « ethnocentrisme ».</t>
+        </is>
+      </c>
+      <c r="N75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O75" s="1"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -3562,8 +3562,10 @@
       <c r="J33" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>303</v>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Méréologie ; Analytique ; Libertarianisme ; Particularisme</t>
+        </is>
       </c>
       <c r="L33" s="14" t="s">
         <v>304</v>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2439,8 +2439,10 @@
       <c r="F6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>46</v>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Ralph Waldo Emerson – la confiance en soi par Parole de Philosophe</t>
+        </is>
       </c>
       <c r="H6" s="9" t="s">
         <v>47</v>
@@ -3011,8 +3013,10 @@
       <c r="F20" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>181</v>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Francisco romero par Biografias de Filosofos</t>
+        </is>
       </c>
       <c r="H20" s="10" t="s">
         <v>182</v>
@@ -3299,8 +3303,10 @@
       <c r="F27" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>244</v>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ernest nagel on computers, logic and mind par Philosophy Overdose</t>
+        </is>
       </c>
       <c r="H27" s="2" t="s">
         <v>245</v>
@@ -3382,8 +3388,10 @@
       <c r="F29" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="G29" s="9" t="s">
-        <v>264</v>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Hannah ARENDT: la philosophe par Coursitout</t>
+        </is>
       </c>
       <c r="H29" s="9" t="s">
         <v>265</v>
@@ -3593,8 +3601,11 @@
       <c r="F34" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="G34" s="9" t="s">
-        <v>309</v>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"
+Philosophie - John Rawls et le voile d'ignorance" par Coursitout</t>
+        </is>
       </c>
       <c r="H34" s="9" t="s">
         <v>310</v>
@@ -3632,8 +3643,10 @@
       <c r="F35" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="G35" s="9" t="s">
-        <v>318</v>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Thomas Kuhn : de la routine à la révolution par Eric Finot</t>
+        </is>
       </c>
       <c r="H35" s="9" t="s">
         <v>319</v>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -3093,8 +3093,11 @@
       <c r="D22" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>197</v>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Susanne_Langer" title=" Wikipedia"&gt;Susanne LANGER&lt;/a&gt; était une philosophe américaine connue pour ses travaux sur le symbole, l’art et la perception. Elle a joué un rôle important dans la philosophie défendant l’idée que la pensée humaine ne se limite pas au langage discursif, mais s’exprime aussi à travers des formes symboliques non verbales, notamment artistiques. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=gwYNyxDTOhQ"   title=" suzanne langer par overthink podcast"&gt;Son œuvre &lt;/a&gt; la plus influente est sans doute Philosophy in a New Key (1942), où elle soutient que l’art n’est pas simplement une décoration ou une émotion brute, mais une forme de connaissance. Pour elle, la musique, la danse, la peinture ou la poésie donnent accès à des structures de sentiment que le langage ordinaire explique mal. Cette idée l’a rendue très importante pour l’esthétique et la théorie des symboles. &lt;/p&gt; &lt;p&gt; Elle s’inscrit dans une tradition marquée par Ernst Cassirer, qui voyait l’être humain comme un animal symbolique. Elle reprend cette intuition en affirmant que l’esprit humain construit le monde au moyen de symboles, et que ces symboles ne sont pas tous de même nature. Elle distingue ainsi les systèmes discursifs, qui avancent par étapes logiques, et les formes présentatives, plus propres à &lt;a href="https://www.youtube.com/watch?v=BM43-aqdboA"   title=" suzanne langer par philosophy overdose"&gt;l’art et à l’expérience sensible. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Son apport est aussi majeur en philosophie de l’art, car elle refuse de réduire l’œuvre à une simple expression subjective de l’artiste. Au contraire, elle cherche à montrer que l’œuvre organise une forme, un rythme et une structure qui rendent intelligible une expérience affective. Cette approche a eu une influence durable sur l’esthétique, la musique et plusieurs sciences humaines. &lt;/p&gt;
+</t>
+        </is>
       </c>
       <c r="F22" s="7" t="s">
         <v>198</v>
@@ -3112,6 +3115,11 @@
       <c r="K22" s="2" t="s">
         <v>202</v>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe américaine de l'art et des symboles, pour qui l'art est une forme de connaissance.</t>
+        </is>
+      </c>
       <c r="M22" s="1" t="s">
         <v>28</v>
       </c>
@@ -3614,8 +3622,10 @@
       <c r="J34" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>311</v>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Contractualisme ; Social-démocratie ; Déontologisme</t>
+        </is>
       </c>
       <c r="L34" s="2" t="s">
         <v>312</v>
@@ -4277,8 +4287,10 @@
       <c r="J50" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>447</v>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Minarchisme ; Déontologisme</t>
+        </is>
       </c>
       <c r="L50" s="2" t="s">
         <v>448</v>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Sanders_Peirce" title=" Wikipedia"&gt;Charles Sanders PEIRCE&lt;/a&gt;  était un philosophe, logicien, scientifique américain assez original, fondateur du  &lt;a href="https://www.youtube.com/watch?v=AGHmKg7wYf0"  title="Pragmatisme  par robertus"&gt;pragmatisme&lt;/a&gt; , père de la sémiotique moderne (théorie des signes) et un pionnier de la logique. Pourtant, en raison de  &lt;a href="https://laviedesidees.fr/Chevalier-Peirce-ou-l-invention-de-l-epistemologie" style="color:#88A1E9" title="les pepites de Charles s pierce par laviedesidees"&gt;sa personnalité difficile&lt;/a&gt; et de ses idées avant-gardistes, il vécut en marge du monde académique, mourant dans la pauvreté et l'isolement. &lt;/p&gt; &lt;p&gt;  Il cherchait à identifier les catégories les plus fondamentales et universelles de la pensée et de l'être, qu'il nomma Phanéroscopie.Il en déduit trois, présentes dans tous les phénomènes. Elles sont la clé de voûte de tout le système peircien et sont indispensables pour comprendre sa sémiotique et  &lt;a href="https://hal.science/hal-02953592/document"  title="Pragmatisme  par hal science"&gt;son pragmatisme&lt;/a&gt;: &lt;/p&gt; &lt;p&gt; - Priméité (Firstness) : C'est la catégorie de la qualité pure, de la potentialité, de la sensation immédiate et brute, existant en elle-même sans référence à quoi que ce soit d'autre. C'est le "sentiment de rouge", la qualité d'une odeur, la nouveauté d'une idée. C'est le domaine de la possibilité et de la liberté. &lt;/p&gt; &lt;p&gt; - Secondéité (Secondeity) : C'est la catégorie du fait brut, de l'action-réaction, de la résistance et de l'actualité. C'est le choc du "ici et maintenant", la rencontre avec un autre qui s'impose à nous. Exemples : une collision, la sensation de résistance en poussant une porte, un conflit. C'est le domaine de l'existence et de la dualité. &lt;/p&gt; &lt;p&gt; - Tiercéité (Thirdness) : C'est la catégorie de la médiation, de la loi, de l'habitude, de la généralisation et de la signification. Elle fait le lien entre la Priméité (la qualité) et la Secondéité (le fait) en leur donnant un sens et une régularité. Exemples : une loi scientifique, un symbole linguistique, une tendance, une règle de conduite. C'est le domaine de la pensée, de la continuité et de l'intelligibilité. &lt;/p&gt; &lt;p&gt; Il propose une méthode pour clarifier le sens de nos idées, le Pragmaticisme: le sens d'un concept réside dans ses conséquences pratiques observables. Si deux idées ne produisent aucune différence pratique, elles signifient la même chose. C'est avant tout une méthode logique pour trancher les disputes métaphysiques stériles.&lt;/p&gt; &lt;p&gt; Sa contribution la plus novatrice et la plus influente est &lt;a href="https://www.persee.fr/doc/lgge_0458-726x_1980_num_14_58_1844" title="La séméiotique de Charles S. Peirce  par Persée"&gt;la Sémiotique&lt;/a&gt; . Pour lui, "l'homme est un signe" et toute pensée est un &lt;a href="https://www.youtube.com/watch?v=e1jrx1RlS00" title="VOIR ET INTERPRÉTER LES SIGNES ! Introduction à la sémiologie CHARLES SANDERS PEIRCE  par Survivreauxscienceshumaines"&gt;processus sémiotique&lt;/a&gt;. Il définit le signe non pas de manière dyadique mais triadique,  Il crée dans l'esprit de la  personne un signe plus développé, appelé l'interprétant. La relation signe-objet-interprétant est fondamentale. Sa classification concerne la relation du signe à son objet : &lt;/p&gt; &lt;dd&gt; - Icône: Le signe ressemble à son objet ou partage des qualités avec lui (une photographie, un diagramme) . &lt;/dd&gt; &lt;dd&gt; - Index: Le signe est physiquement connecté à son objet . la fumée (indice du feu), une girouette (indice de la direction du vent). &lt;/dd&gt; &lt;dd&gt; - Symbole: La relation entre le signe et l'objet est arbitraire et conventionnelle. Elle repose sur une règle ou une habitude sociale. ("arbre" n'a rien d'un arbre). &lt;/dd&gt; &lt;p&gt; Bien que mort dans la misère et méconnu de son vivant, son influence est immense aujourd'hui en philosophie, en sciences cognitives, en linguistique et en sociologie. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Sanders_Peirce" title=" Wikipedia"&gt;Charles Sanders PEIRCE&lt;/a&gt;  était un philosophe, logicien, scientifique américain assez original, fondateur du  &lt;a href="https://www.youtube.com/watch?v=AGHmKg7wYf0"  title="Pragmatisme  par robertus"&gt;pragmatisme&lt;/a&gt;, père de la sémiotique moderne (théorie des signes) et un pionnier de la logique. Pourtant, en raison de  &lt;a href="https://laviedesidees.fr/Chevalier-Peirce-ou-l-invention-de-l-epistemologie" style="color:#88A1E9" title="les pepites de Charles s pierce par laviedesidees"&gt;sa personnalité difficile&lt;/a&gt; et de ses idées avant-gardistes, il vécut en marge du monde académique, mourant dans la pauvreté et l'isolement. &lt;/p&gt; &lt;p&gt;  Il cherchait à identifier les catégories les plus fondamentales et universelles de la pensée et de l'être, qu'il nomma Phanéroscopie.Il en déduit trois, présentes dans tous les phénomènes. Elles sont la clé de voûte de tout le système peircien et sont indispensables pour comprendre sa sémiotique et  &lt;a href="https://hal.science/hal-02953592/document"  title="Pragmatisme  par hal science"&gt;son pragmatisme&lt;/a&gt;: &lt;/p&gt; &lt;p&gt; - Priméité (Firstness) : C'est la catégorie de la qualité pure, de la potentialité, de la sensation immédiate et brute, existant en elle-même sans référence à quoi que ce soit d'autre. C'est le "sentiment de rouge", la qualité d'une odeur, la nouveauté d'une idée. C'est le domaine de la possibilité et de la liberté. &lt;/p&gt; &lt;p&gt; - Secondéité (Secondeity) : C'est la catégorie du fait brut, de l'action-réaction, de la résistance et de l'actualité. C'est le choc du "ici et maintenant", la rencontre avec un autre qui s'impose à nous. Exemples : une collision, la sensation de résistance en poussant une porte, un conflit. C'est le domaine de l'existence et de la dualité. &lt;/p&gt; &lt;p&gt; - Tiercéité (Thirdness) : C'est la catégorie de la médiation, de la loi, de l'habitude, de la généralisation et de la signification. Elle fait le lien entre la Priméité (la qualité) et la Secondéité (le fait) en leur donnant un sens et une régularité. Exemples : une loi scientifique, un symbole linguistique, une tendance, une règle de conduite. C'est le domaine de la pensée, de la continuité et de l'intelligibilité. &lt;/p&gt; &lt;p&gt; Il propose une méthode pour clarifier le sens de nos idées, le Pragmaticisme: le sens d'un concept réside dans ses conséquences pratiques observables. Si deux idées ne produisent aucune différence pratique, elles signifient la même chose. C'est avant tout une méthode logique pour trancher les disputes métaphysiques stériles.&lt;/p&gt; &lt;p&gt; Sa contribution la plus novatrice et la plus influente est &lt;a href="https://www.persee.fr/doc/lgge_0458-726x_1980_num_14_58_1844" title="La séméiotique de Charles S. Peirce  par Persée"&gt;la Sémiotique&lt;/a&gt;. Pour lui, "l'homme est un signe" et toute pensée est un &lt;a href="https://www.youtube.com/watch?v=e1jrx1RlS00" title="VOIR ET INTERPRÉTER LES SIGNES ! Introduction à la sémiologie CHARLES SANDERS PEIRCE  par Survivreauxscienceshumaines"&gt;processus sémiotique&lt;/a&gt;. Il définit le signe non pas de manière dyadique mais triadique,  Il crée dans l'esprit de la  personne un signe plus développé, appelé l'interprétant. La relation signe-objet-interprétant est fondamentale. Sa classification concerne la relation du signe à son objet : &lt;/p&gt; &lt;dd&gt; - Icône: Le signe ressemble à son objet ou partage des qualités avec lui (une photographie, un diagramme). &lt;/dd&gt; &lt;dd&gt; - Index: Le signe est physiquement connecté à son objet : la fumée (indice du feu), une girouette (indice de la direction du vent). &lt;/dd&gt; &lt;dd&gt; - Symbole: La relation entre le signe et l'objet est arbitraire et conventionnelle. Elle repose sur une règle ou une habitude sociale. ("arbre" n'a rien d'un arbre). &lt;/dd&gt; &lt;p&gt; Bien que mort dans la misère et méconnu de son vivant, son influence est immense aujourd'hui en philosophie, en sciences cognitives, en linguistique et en sociologie. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -2599,8 +2599,10 @@
       <c r="D10" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>86</v>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;a href="https://fr.wikipedia.org/wiki/William_James"  title=" Wikipedia"&gt;William JAMES&lt;/a&gt; est un philosophe Américain surtout connu pour la philosophie du &lt;a  href="https://www.youtube.com/watch?v=EKfQ2XunoYk&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Pragmatisme par Le Précepteur"&gt;Pragmatisme&lt;/a&gt; et fondateur de la psychologie moderne aux États-Unis. Professeur à Harvard, il a influencé des domaines variés comme la philosophie, la religion et les sciences cognitives par son approche empirique et anti-dogmatique.&lt;/p&gt; &lt;p&gt; Son pragmatisme, exposé dans Le Pragmatisme (1907), définit la vérité non comme une correspondance abstraite avec la réalité, mais comme ce qui "fonctionne" pratiquement et produit des effets concrets dans l'expérience. Il rejette les philosophies spéculatives fermées : pour lui, les idées doivent être testées par leurs conséquences observables, comme un "corridor" reliant les doctrines rivales à la vie quotidienne. &lt;/p&gt; &lt;p&gt; La vérité n'est pas quelque chose d'absolu ou d'universel, mais plutôt quelque chose qui est en constante évolution et qui dépend du contexte. Pour lui, la vérité doit être testée par l'expérience et l'action, et il a donc considéré que l'importance de l'expérience pratique et de l'observation était essentielle à la compréhension de la vérité. &lt;/p&gt; &lt;p&gt;Dans son livre &lt;a  href="https://www.persee.fr/doc/psy_0003-5033_1905_num_12_1_5996"  title="Les variétés de l'expérience religieuse par persée.fr"&gt;"Les Variétés de l'expérience religieuse"&lt;/a&gt;, il a étudié les différentes formes de religion et a mis en évidence leur importance pour la compréhension de la nature humaine valorisant les expériences mystiques subjectives si elles portent des fruits moraux et pratiques, sans exiger de preuves théologiques. Son pluralisme intellectuel – acceptant plusieurs vérités compatibles – en fait un penseur de l'ouverture et de l'adaptation, influençant Bergson et la philosophie contemporaine.  &lt;/p&gt; &lt;p&gt;En psychologie, il est considéré comme l'un des fondateurs du courant de la psychologie fonctionnaliste, qui s'intéresse à la façon dont les gens utilisent leur esprit pour s'adapter à leur environnement. Il a également étudié la théorie de l'émotion et a proposé que les émotions ne sont pas simplement des réponses physiologiques &lt;a  href="https://www.youtube.com/watch?v=C4vhWaWiPus"  title="L’art de stimuler l’intelligence par les rares livres"&gt;à des stimuli, &lt;/a&gt; mais plutôt des expériences subjectives qui sont influencées par la perception, la cognition et les actions.  Son œuvre majeure Les Principes de psychologie (1890) introduit une vision du "flux de conscience" (stream of consciousness), où l'esprit est un courant continu et fluide, non une série d'images statiques. Il critique le dualisme corps-esprit, voyant émotions et actions comme indissociables, et défend un indéterminisme qui laisse place à la liberté humaine.&lt;/p&gt;   &lt;audio controls title="William James par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/05/s18/NET_FC_82a4623d-00a5-4024-a797-fd01dd5050ec.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F10" s="7" t="s">
         <v>87</v>
@@ -2842,8 +2844,11 @@
       <c r="D16" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>144</v>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/William_Ernest_Hocking"  title=" Wikipedia"&gt;William Ernest HOCKING&lt;/a&gt; était un philosophe idéaliste américain de Harvard, disciple de Josiah Royce et figure majeure du « personnalisme de Harvard », courant qui met l’accent sur la personne spirituelle et la conscience en tant que cœur de la réalité. Il poursuit et révise l’idéalisme de Royce en le rendant plus compatible avec l’empirisme, le naturalisme et le pragmatisme américains. &lt;/p&gt; &lt;p&gt; Dans sa métaphysique, il défend l’idée que le  &lt;a href="https://www.youtube.com/watch?v=YQn-iAr8urc" title="man’s cosmic with william hocking par vedanta video"&gt;monde est une pluralité &lt;/a&gt; de substances spirituelles conscientes, toutes reliées à un Absolu ou à un « Autre Esprit » que l’on peut identifier à Dieu. Il soutient que la communication entre êtres humains suppose cette conscience globale de l’Univers, et que Dieu est la cause première de la créativité et de la réalité elle‑même, &lt;/p&gt; &lt;p&gt; En philosophie de la religion, il développe une théologie non dogmatique : la vérité religieuse se découvre dans l’expérience vivante du Divin plutôt que dans des croyances figées ou des institutions. Il critique la science qui voudrait exclure complètement le religieux, en affirmant que l’universel et le sens ultime ne sont accessibles que par une forme d’expérience spirituelle. &lt;/p&gt; &lt;p&gt; Il  est aussi connu pour sa théorie du &lt;a href="https://www.persee.fr/doc/linx_0246-8743_1994_hos_5_1_1294" title="aspect du comportement pragmatique de la negation"&gt;« pragmatisme négatif » : &lt;/a&gt; si une idée réussit pratiquement, elle peut être vraie, mais si elle échoue, elle ne peut pas l’être, car « la vérité fonctionne toujours ». Ce critère lui permet de garder une place pour le pragmatisme tout en refusant de réduire la vérité à l’utilité immédiate. &lt;/p&gt; &lt;p&gt; Il s’engage dans la réflexion politique et éthique, en défendant une forme de libéralisme renouvelé où la liberté ne se réduit pas à l’absence de contrainte, mais à la possibilité pour chaque individu de « devenir un homme entier » en développant ses capacités. Il insiste sur le droit fondamental de chacun à développer les puissances qui sont en lui, ce qui relie sa philosophie à des questions de justice sociale, de droits humains et de responsabilité mondiale. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F16" s="7" t="s">
         <v>145</v>
@@ -2923,8 +2928,10 @@
       <c r="D18" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>161</v>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alfonso_Reyes"  title=" Wikipedia"&gt;Alfonso REYES&lt;/a&gt; était un écrivain et philosophe &amp; diplomate  mexicain, souvent considéré comme l’un des grands humanistes de la langue espagnole au XXe siècle.  &lt;a href="https://www.persee.fr/doc/hispa_0007-4640_1960_num_62_1_3655"  title=" Alfonso Reyes par Persée"&gt;Sa pensée &lt;/a&gt; philosophique est inséparable de son travail d’essayiste, de critique littéraire et de médiateur entre les cultures européennes et latino‑américaines. &lt;/p&gt; &lt;p&gt; Son premier livre important, "Cuestiones estéticas" paru en  1911 est une série de réflexions sur l’esthétique et la critique littéraire, où il articule déjà l’idée que l’expérience artistique est une forme de connaissance privilégiée du monde. Il donne des conférences sur l’"esthétique classique", qui influenceront durablement l’orientation intellectuelle mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Il n’est pas un philosophe systématique au sens académique, mais un humaniste qui pense la littérature, l’histoire et le mythe comme voies d’accès à la réalité et à l’identité mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &lt;a href="https://www.youtube.com/watch?v=IeZKZ6PC9H4"  title=" Visión de Anáhuac de Alfonso Reyes par Literatubers"&gt;"Visión de Anáhuac"&lt;/a&gt;, il propose une méditation poétique et historique sur le Mexique préhispanique et la Conquête, en insistant sur la continuité d’une sensibilité mexicaine à travers les siècles. &lt;/p&gt; &lt;p&gt; Il défend une conception de l’homme formé par les lettres, la philosophie et les sciences, contre les réductions technocratiques ou purement utilitaires du savoir et pense l’Amérique latine comme espace de synthèse entre héritages indigènes, hispaniques et européens, et fait de la traduction et de la critique des instruments de ce dialogue. &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F18" s="7" t="s">
         <v>162</v>
@@ -2965,8 +2972,10 @@
       <c r="D19" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>170</v>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Edward_Bernays" title=" Wikipedia"&gt;Edward BERNAYS&lt;/a&gt;, neveu de Sigmund FREUD était un célèbre publicitaire et consultant en relations publiques américain qui développa le Propogandisme. &lt;/p&gt; &lt;p&gt;  Il est connu pour son livre &lt;a href="https://www.youtube.com/watch?v=-M7E75MAWWM&amp;ab_channel=EcoMan%28i%29a"   title="L'ouvrage Propaganda par Eco Man"&gt; "Propaganda"&lt;/a&gt;, publié en 1928, dans lequel il décrit les techniques qu'il utilisait pour influencer l'opinion publique et manipuler les masses à des fins commerciales et politiques.&lt;/p&gt; &lt;p&gt;  Il a été un pionnier de l'utilisation de la psychologie et de la sociologie pour influencer les opinions et les comportements des consommateurs par la &lt;a href="https://www.vivrelibre.net/wp-content/uploads/2017/07/VL57.pdf"  title="La manipulation des esprits par Michel LEBLANC"&gt; manipulation des esprits&lt;/a&gt;. Il a utilisé des techniques telles que la manipulation des symboles et des images pour renforcer l'association d'un produit avec des valeurs ou des sentiments positifs dans l'esprit des consommateurs. &lt;/p&gt; &lt;p&gt; Il a également joué un rôle important dans la promotion du consumérisme en encourageant les gens à dépenser de l'argent pour des produits inutiles et en stimulant la demande pour de nouveaux produits.  Il a également été impliqué dans des campagnes de relations publiques pour des entreprises et des gouvernements, y compris la promotion du tabac auprès des femmes et la campagne pour la guerre américaine en Irak. &lt;/p&gt; &lt;p&gt;  Il est considéré comme le fondateur de la &lt;a href="https://www.youtube.com/watch?v=UvkhFpb7M7Y&amp;t=342s&amp;ab_channel=LePr%C3%A9cepteur"  title="Comment manipuler l'opinion par le Précepteur"&gt; manipulation de l'opinion &lt;/a&gt; publique moderne, son influence est souvent critiquée pour avoir encouragé une culture de la manipulation et de la tromperie dans les relations publiques et la publicité. &lt;/p&gt;  &lt;audio controls title="Propaganda ou comment manipuler l'opinion publique par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2012/01/s02/NET_e7ddaac9-fb30-445c-9784-f05763b129ef.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F19" s="7" t="s">
         <v>171</v>
@@ -3007,8 +3016,11 @@
       <c r="D20" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>179</v>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher)"  title=" Wikipedia"&gt;Francisco ROMERO&lt;/a&gt; était un philosophe argentin d’origine espagnole, professeur à l’Université de Buenos Aires et à La Plata, et une figure centrale de la réaction  &lt;a href="https://fr.wikipedia.org/wiki/Ib%C3%A9ro-Am%C3%A9rique"  title="ibéro-amérique par wikipedia"&gt; ibéro-américaine &lt;/a&gt; contre le positivisme dominant au début du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa production philosophique couvre l’épistémologie, la philosophie de la culture et l’anthropologie philosophique ; son ouvrage majeur en langue espagnole, Teoría del hombre (1952), propose une réflexion systématique sur la condition humaine, la liberté et la créativité culturelle, et a été traduit en anglais sous le titre Theory of Man.https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher) &lt;/p&gt; &lt;p&gt; Il  prit position contre  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9ductionnisme"  title="Reductionnisme par wikipedia"&gt; le réductionnisme scientiste &lt;/a&gt; en défendant l’idée que la culture et les créations humaines (art, religion, langage) exigent des méthodes et des concepts propres, distincts des instruments des sciences naturelles ; il chercha donc à articuler rigueur philosophique et sensibilité littéraire. &lt;/p&gt; &lt;p&gt; Sur le plan méthodologique, il promut une philosophie qui dialogue avec l’histoire des idées et avec les problèmes concrets de la société ibéro-américaine : ses travaux montrent un intérêt marqué pour la responsabilité sociale des intellectuels et pour la formation culturelle des peuples. &lt;/p&gt; &lt;p&gt; Parmi ses autres ouvrages importants figurent Old and New Concepts of Reality (1932), The Problems of Philosophy of Culture (1938), Man and Culture (1950, traduction de El hombre y la cultura) et History of Modern Philosophy (1959); sa réputation lui valut le surnom de « doyen des philosophes ibéro-américains » et son héritage continue d’être étudié dans les études sur la philosophie latino‑américaine. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F20" s="7" t="s">
         <v>180</v>
@@ -3179,8 +3191,11 @@
       <c r="D24" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>214</v>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Samuel_Ramos"  title=" Wikipedia"&gt;Samuel RAMOS&lt;/a&gt; était un philosophe mexicain  précurseur de la philosophie de la mexicanité qui analyse le caractère national mexicain à travers une approche psychologique et historiciste. &lt;/p&gt; &lt;p&gt; Il applique le perspectivisme d'Ortega y Gasset et la psychologie adlérienne : le Mexicain souffre d'un complexe d'infériorité structurel se manifestant par dissimulation, susceptibilité, phallocratie et idéalisme primitif. Critique du positivisme porfirien, il lie philosophie à révolution mexicaine  en 1910, murale (Rivera) et Ateneo de la Juventud (Caso, Vasconcelos), prônant une culture créole authentique plutôt que folklorique ou importée. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://fr.slideshare.net/slideshow/samuel-ramos-hacia-un-nuevo-humanismo/15149441"  title="Samuel ramos hacia un nuevo humanismo par slideshare"&gt;Son projet &lt;/a&gt;: construire une "culture à la hauteur du monde civilisé" via éducation et réflexion existentielle, évitant à la fois servilité et isolationnisme. Précurseur de Hiperión (1950, avec Zea, Uranga, Villoro), il fonde l'étude de l'"être mexicain", influençant Paz (Labyrinthe de la solitude), Zea et la philosophie de la libération ; sa quête d'identité universelle mais située ouvre à la décolonialité. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F24" s="7" t="s">
         <v>215</v>
@@ -3518,8 +3533,11 @@
       <c r="D32" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="E32" s="10" t="s">
-        <v>290</v>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leopoldo_Zea_Aguilar" title=" Wikipedia"&gt;Leopoldo ZEA AGUILAR&lt;/a&gt; était un philosophe mexicain, considéré comme l'un des pères fondateurs de la philosophie latino-américaine contemporaine, engagé dans la quête d'une identité culturelle autonome face à l'eurocentrisme et au néocolonialisme. &lt;/p&gt; &lt;p&gt;  Il pose la question centrale : "Peut-on construire une philosophie latino-américaine ?" Réponse affirmative via une dialectique de la conscience : de la dépendance à la libération, où l'homme latino-américain réalise sa liberté par la reconnaissance de sa singularité culturelle. Relativiste culturel sans relativisme absolu, il définit l'homme comme ouvert et pluriel, rejetant l'eurocentrisme comme domination masquée ; la philosophie devient &lt;a href="https://ensayistas.org/antologia/XXA/zea/zea2.htm" title="Leopoldo Zea Aguilar | Autopercepción intelectual de un proceso histórico par ensayistas"&gt;"instrument de libération"&lt;/a&gt;, transformant l'histoire en projet éthique-politique de dignité, égalité et solidarité. Précurseur des critiques post-coloniales et postmodernes, il voit 1492 non comme "découverte" mais comme "occultation" culturelle, et la philosophie latino-américaine comme symbiose de nationalisme, christianisme et socialisme anti-impérialiste. &lt;/p&gt; &lt;p&gt; Mentor de générations, il fonde des centres intellectuels en Amérique latine et reçoit des prix mondiaux ; son discours sur la marginalité influence la philosophie de la libération et les études culturelles décoloniales. Il reste &lt;a href="https://www.youtube.com/watch?v=_kEH9wQFQv4" style="color:#88A1E9" title="Leopoldo Zea Aguilar | Doctorado en Educación par Miguel Morales"&gt;une référence &lt;/a&gt; pour une Amérique latine unie, non utopique mais réaliste, affirmant : "Se connaître égal en étant distinct est l'essence des relations humaines et internationales". &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F32" s="7" t="s">
         <v>291</v>
@@ -3603,8 +3621,10 @@
       <c r="D34" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>307</v>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Rawls_(philosophe)"  title=" Wikipedia"&gt;John RAWLS&lt;/a&gt; était un  philosophe politique américain connu grâce à son œuvre majeure "&lt;a href="https://www.youtube.com/watch?v=OIKwI5qu4y8" style="color:#88A1E9" title=" La THÉORIE DE LA JUSTICE en 8 minutes ! (John RAWLS) par Culture Philo"&gt; A Theory of Justice&lt;/a&gt;", publiée en 1971 ou il propose une conception de la  &lt;a href="https://www.youtube.com/watch?v=2w-AEMAU_EE"  title=" Le libéralisme égalitaire de John Rawls par Philoxime"&gt;"justice comme équité"&lt;/a&gt;. Il s’oppose à l’utilitarisme – doctrine selon laquelle une action est bonne si elle maximise le bonheur collectif – et cherche au contraire à fonder la justice sur des principes garantissant équitablement les libertés et droits fondamentaux pour tous. &lt;/p&gt; &lt;p&gt;  Il imagine une " &lt;a href="https://www.persee.fr/doc/rfsp_0035-2950_1991_num_41_1_394540"  title="La Théorie de la justice de John Rawls. Contrat social versus utilitarisme par Persée"&gt;position originelle&lt;/a&gt;", situation hypothétique où des individus rationnels, placés derrière un « voile d’ignorance » qui leur cache leurs avantages personnels, choisiraient des règles de justice justes pour tous. De cette expérience de pensée, il déduit deux principes essentiels dont le principe d’égale liberté où chaque personne doit avoir un droit égal aux libertés fondamentales et le principe de différence où les inégalités économiques et sociales ne sont justes que si elles profitent aux plus désavantagés.  &lt;/p&gt; &lt;p&gt; Il a ensuite  prolongé sa réflexion dans "Political Liberalism" (1993) et "The Law of Peoples" (1999). Dans le premier, il interroge comment un consensus moral peut se former dans des sociétés pluralistes sans imposer une doctrine particulière ; dans le second, il applique ses principes à la &lt;a href="https://www.youtube.com/watch?v=ah7y1xd3bL0" title="JOHN RAWLS : Qu'est-ce que la justice sociale ? par Parole de Philosophe"&gt;justice internationale&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;  Il a profondément marqué la philosophie morale, politique et économique contemporaine et sa pensée inspira la théorie économique critique, avec des débats persistants sur la compatibilité de sa vision avec le libéralisme ou la social-démocratie et il demeure aujourd’hui une référence incontournable pour toute réflexion sur la justice, l’égalité et la démocratie. &lt;/p&gt; &lt;audio controls title=" Avoir raison avec... John Rawls par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-13.07.2020-ITEMA_22381527-2020C35448S0195-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F34" s="7" t="s">
         <v>308</v>
@@ -3939,8 +3959,10 @@
       <c r="D42" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="E42" s="10" t="s">
-        <v>377</v>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_Rorty" title=" Wikipedia"&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href="https://www.youtube.com/watch?v=lfx4Jag1ic4"  title="Le pragmatisme : définition, exemples par le savoir partagé"&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href="https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism" title=" a bas l'autorité par laviedesidees"&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas "vrais" ou "faux". &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales, on trouve  &lt;a href="https://www.youtube.com/watch?v=MgU0dXZ3umM" title="L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli"&gt;" Contingence, ironie et solidarité "&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans " Achieving Our Country" (1998),  il y appelle la gauche américaine à abandonner le "culturalisme" pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la "post-vérité". Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F42" s="7" t="s">
         <v>378</v>
@@ -3978,8 +4000,12 @@
       <c r="D43" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>386</v>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Searle"  title=" Wikipedia"&gt;John SEARLE&lt;/a&gt; était un philosophe américain  connu pour ses travaux influents dans plusieurs domaines, notamment la philosophie du langage, la philosophie de l'esprit et la philosophie sociale. Il  a développé et systématisé la théorie des &lt;a href="https://www.youtube.com/watch?v=pIbkpLfrD6A" title="
+La théorie des actes de langage (2) - John Searle par Heraut du Mont Parnasse"&gt;actes de langage&lt;/a&gt; car, pour lui, parler une langue, ce n'est pas seulement émettre des sons ou des suites de symboles, mais accomplir des actions. &lt;/p&gt; &lt;p&gt; Défenseur du "naturalisme biologique" en philosophie de l'esprit. Il s'oppose au dualisme cartésien tout en refusant le matérialisme réducteur qui nierait l'existence de &lt;a href="https://www.youtube.com/watch?v=EriAhi0mj7w" title=" Conscience et matière grise par TEDx Talks"&gt;la conscience&lt;/a&gt; ou la réduirirait à de simples phénomènes physiques. Pour lui, les états mentaux (douleur, croyances, désirs, conscience) sont des phénomènes  &lt;a href="https://www.youtube.com/watch?v=Bq2bfSzkTfU"  title="John Searle - Une personne peut-elle être une âme ? par Closer To Truth"&gt;biologiques réels&lt;/a&gt;, causés par des processus neuronaux du cerveau, mais ils ne sont pas réductibles à ces processus au sens où ils émergent à un niveau supérieur et possèdent des propriétés irréductibles.&lt;/p&gt; &lt;p&gt; L'une des ses contributions les plus célèbres est son argument de la &lt;a href="https://www.youtube.com/watch?v=P5DtwDr9YEc" title=" La Chambre chinoise par Ian et frank"&gt;Chambre Chinoise&lt;/a&gt;. Cet argument vise à réfuter la thèse de l'IA forte (position selon laquelle un ordinateur programmé de manière appropriée n'est pas seulement un outil pour l'étude de l'esprit, mais qu'il est véritablement un esprit, capable de comprendre et de posséder d'autres états cognitifs) opposé à l'IA faible (position selon laquelle les ordinateurs sont des outils utiles pour étudier l'esprit, mais qu'ils ne sont pas eux-mêmes des esprits). &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://labo.nonmarchand.org/pmwiki/uploads/Textes/JohnSearleLaConstructionDeLaRealiteSociale/JohnSearle_LaConstructionDeLaRealiteSociale.pdf"  title=" La construction e la réalité sociale par nonmarchand"&gt;"La Construction de la Réalité Sociale"&lt;/a&gt;, il étend sa théorie des actes de langage et de l'intentionnalité pour expliquer comment nous construisons des faits institutionnels et sociaux. Il distingue les "Faits bruts" qui existent indépendamment de toute institution humaine (par exemple, la montagne Everest) des "Faits institutionnels" qui n'existent qu'en vertu d'institutions humaines et de l'accord collectif (par exemple, l'argent, le mariage, la propriété). &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F43" s="1" t="s">
         <v>387</v>
@@ -4354,8 +4380,10 @@
       <c r="D52" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>460</v>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saul_Kripke"  title=" Wikipedia"&gt;Saul KRIPKE&lt;/a&gt; était un philosophe américain de la tradition analytique connu pour ses apports décisifs en logique modale, en métaphysique et en philosophie du langage. Très jeune, il révolutionne la logique en introduisant la sémantique des mondes possibles, aujourd’hui appelée &lt;a href="https://www.youtube.com/watch?v=_sIgAdvhruU"title="Qui est Saul Kripke ? par Monsieur Phi"&gt;"cadres de Kripke"&lt;/a&gt;, qui permet de formaliser la modalité (le nécessaire et le possible) de façon rigoureuse. &lt;/p&gt; &lt;p&gt; Son œuvre la plus influente est "Naming and Necessity", où il critique la conception descriptiviste des noms défendue par Frege et Russell. Selon lui, un  &lt;a href="https://www.youtube.com/watch?v=d7-8Avem7EE" title="Saul Kripke, La logique des noms propres. par Jtgrandtour"&gt; nom propre&lt;/a&gt; n’équivaut pas à une description mais fonctionne comme un « désignateur rigide » : il désigne le même individu dans tous les mondes possibles. Cette idée bouleverse la philosophie du langage et entraîne une redéfinition de la notion de référence.&lt;/p&gt; &lt;p&gt;  Il montre également qu’il existe des vérités nécessaires découvertes empiriquement : par exemple, l’identité « l’eau est H₂O » est nécessaire, mais nous ne l’avons apprise qu’a posteriori. Ce concept de nécessité a posteriori a marqué un tournant dans la métaphysique contemporaine. À l’inverse, il identifie la possibilité de certaines vérités contingentes connues a priori, ce qui remet en cause des distinctions classiques entre connaissance et modalité. &lt;/p&gt; &lt;p&gt; Il s’oppose au physicalisme en arguant que l’on peut concevoir un monde où tous les états cérébraux existent sans que la conscience subjective "le qualia" ne soit présente. Cette critique alimente encore aujourd’hui les débats sur la nature de la conscience. Son ouvrage "Wittgenstein on Rules and Private Language" propose une lecture radicale de Wittgenstein, selon laquelle toute règle est sujette à un scepticisme profond sur son application. Bien que controversée, cette interprétation a largement stimulé les discussions en philosophie du langage et en épistémologie. &lt;/p&gt; &lt;p&gt; Connu aussi pour son ouvrage " On two Paradoxes of Knowledge" et son  &lt;a href="https://www.youtube.com/watch?v=AzaUSC--2G0"  title="Le Paradoxe de l'Examen selon Saul Kripke par Silogic"&gt;"paradoxe de l'examen"&lt;/a&gt;. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F52" s="1" t="s">
         <v>461</v>
@@ -4518,8 +4546,11 @@
       <c r="D56" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="E56" s="14" t="s">
-        <v>494</v>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iris_Marion_Young" title=" Wikipedia"&gt;Iris Marion YOUNG&lt;/a&gt; était une philosophe politique américaine majeure, figure centrale du féminisme contemporain et de la théorie de la justice. Professeure à l'Université de Chicago, elle articule phénoménologie existentialiste, marxisme, théorie critique et postmodernisme pour repenser l'oppression, la domination et la démocratie au-delà des approches universalistes traditionnelles. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est sa théorie des &lt;a href="https://www.youtube.com/watch?v=KyOut8zqJRI" title="les cinq visages de l’oppression par Eliot Goodine"&gt; cinq visages de l'oppression,&lt;/a&gt;  qu'elle développe dans Justice and the Politics of Difference (1990) ou elle développe également une,&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2018_num_116_4_8681" title="le féminisme phénoménologique par persée"&gt; phénoménologie féministe &lt;/a&gt; du corps, notamment dans son essai célèbre « Throwing Like a Girl » (1980). Elle y décrit comment les femmes vivent leur corps comme limité, fragmenté et constamment surveillé, ce qui produit une « immanence » sociale qui entrave leur capacité d'action et d'autodétermination. Le corps n'est pas seulement biologique mais politique, façonné par les normes sociales et les rapports de pouvoir. &lt;/p&gt; &lt;p&gt; Elle défend une conception de la justice fondée sur l'inclusion différenciée plutôt que sur l'universalisme abstrait. Pour Young, une société juste doit reconnaître les différences de groupe (genre, race, classe, sexualité) et créer des espaces où chacun puisse participer à la vie démocratique sans être forcé d'abandonner son identité particulière. Elle propose aussi le concept de responsabilité sociale diffuse, selon lequel tous les membres d'une société sont responsables des injustice structurelles, pas seulement les auteurs directs. &lt;/p&gt; &lt;p&gt; Elle évite tout essentialisme en conceptualisant « les femmes » comme un groupe social sériel, au sens de Sartre : un groupe dont les membres ne partagent pas une essence commune mais sont reliés par des conditions sociales similaires et des rapports de pouvoir. Cette approche permet un féminisme pluriel, Alliant diverses luttes (racisme, homophobie, validisme, écologie) dans des coalitions contre les rapports de domination. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F56" s="1" t="s">
         <v>495</v>
@@ -4559,8 +4590,11 @@
       <c r="D57" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>502</v>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bell_hooks"  title=" Wikipedia"&gt;Bell HOOKS&lt;/a&gt;, de son vrai nom Gloria Jean Watkins, est une autrice, professeure et militante féministe afro-américaine. Née dans le Kentucky, dans le Sud ségrégationniste, elle prit le nom de son arrière-grand-mère, qu'elle écrivait en minuscules pour que l'attention se porte sur ses idées plutôt que sur sa personne.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ne suis-je pas une femme ?&lt;/em&gt; (1981), elle montre que les femmes noires ont été oubliées à la fois par le mouvement féministe, dominé par des femmes blanches de classe moyenne, et par le mouvement pour les droits civiques, dominé par des hommes. Elle  &lt;a href="https://www.youtube.com/watch?v=pCwMdHBSQgM" title=" bell hooks, un féminisme anticapitaliste et intersectionnel par META "&gt;développe l'idée &lt;/a&gt; que le sexisme, le racisme et l'exploitation économique forment un même système de domination, qu'elle appelle le « patriarcat capitaliste suprémaciste blanc ».&lt;/p&gt; &lt;p&gt;Ses idées ont profondément influencé ce que l'on appelle aujourd'hui l'intersectionnalité, c'est-à-dire l'étude de la manière dont différentes formes de discrimination se croisent et se renforcent. Elle écrivait dans un style simple et direct, refusant le jargon universitaire, pour que ses livres soient lus au-delà des cercles savants. Elle a aussi consacré plusieurs ouvrages à l'amour, qu'elle considérait comme une force politique capable de transformer la société.&lt;/p&gt; &lt;p&gt;Elle a écrit une quarantaine de livres, sur le féminisme, l'amour, les médias, la culture populaire et l'éducation. Dans &lt;em&gt;Apprendre à transgresser&lt;/em&gt; (1994), inspirée par Paulo Freire, elle défend une pédagogie de la liberté où l'enseignement devient une pratique d'émancipation. Pour elle, le féminisme n'est pas une guerre contre les hommes mais un mouvement pour mettre fin à toute forme de domination, porté par une « éthique de l'amour ».&lt;/p&gt;    &lt;audio controls title="Lire bell hooks aujourd’hui par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23875-15.11.2023-ITEMA_23552434-2023C49162S0319-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
+</t>
+        </is>
       </c>
       <c r="F57" s="1" t="s">
         <v>503</v>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -3366,11 +3366,15 @@
       <c r="E28" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="F28" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>254</v>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D-fU2DMB8T0</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Ayn Rand - Faut-il ne penser qu'à soi ?" par Kosmos</t>
+        </is>
       </c>
       <c r="H28" s="9" t="s">
         <v>255</v>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2451,8 +2451,10 @@
       <c r="J6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>49</v>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcendantalisme ; Spiritualisme ; Individualisme</t>
+        </is>
       </c>
       <c r="L6" s="2" t="s">
         <v>50</v>
@@ -2532,8 +2534,10 @@
       <c r="J8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>71</v>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcendantalisme ; Anarchisme ; Individualisme</t>
+        </is>
       </c>
       <c r="L8" s="2" t="s">
         <v>72</v>
@@ -2617,8 +2621,10 @@
       <c r="J10" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>91</v>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pragmatisme ; Empirisme ; Épiphénoménisme ; Pluralisme</t>
+        </is>
       </c>
       <c r="L10" s="2" t="s">
         <v>92</v>
@@ -3383,8 +3389,10 @@
       <c r="J28" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>256</v>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Objectivisme ; Libéralisme ; Minarchisme</t>
+        </is>
       </c>
       <c r="L28" s="2" t="s">
         <v>257</v>
@@ -3472,8 +3480,10 @@
       <c r="J30" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>277</v>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Nominalisme ; Méréologie</t>
+        </is>
       </c>
       <c r="L30" s="2" t="s">
         <v>278</v>
@@ -3514,8 +3524,10 @@
       <c r="J31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>285</v>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Nominalisme ; Empirisme ; Holisme ; Ontologie</t>
+        </is>
       </c>
       <c r="L31" s="2" t="s">
         <v>286</v>
@@ -3602,7 +3614,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Méréologie ; Analytique ; Libertarianisme ; Particularisme</t>
+          <t xml:space="preserve">Méréologie ; Analytique ; Libertarianisme ; Particularisme ; Incompatibilisme</t>
         </is>
       </c>
       <c r="L33" s="14" t="s">
@@ -3770,8 +3782,10 @@
       <c r="J37" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>339</v>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Pragmatisme ; Réalisme scientifique ; Cognitivisme ; Essentialisme ; Computationnalisme</t>
+        </is>
       </c>
       <c r="L37" s="2" t="s">
         <v>340</v>
@@ -3854,8 +3868,10 @@
       <c r="J39" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>357</v>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libertarianisme ; Anarcho-Capitalisme ; Volontarisme</t>
+        </is>
       </c>
       <c r="L39" s="14" t="s">
         <v>358</v>
@@ -4613,8 +4629,10 @@
       <c r="J57" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>506</v>
+      <c r="K57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Féminisme ; Wokisme</t>
+        </is>
       </c>
       <c r="L57" s="2" t="s">
         <v>507</v>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2237,7 +2237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD75"/>
+  <dimension ref="A1:XFD76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
@@ -2420,292 +2420,321 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+    <row r="6" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1">
+        <v>1783</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1830</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1783 – 1830</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simón BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sim%C3%B3n_Bol%C3%ADvar" title=" Wikipedia"&gt;Simón BOLÍVAR&lt;/a&gt; est le chef militaire et politique des &lt;a href="https://fr.wikipedia.org/wiki/Guerres_d%27ind%C3%A9pendance_hispano-am%C3%A9ricaines" title=" Wikipedia"&gt;guerres d’indépendance&lt;/a&gt; de l’Amérique du Sud, surnommé le Libertador. Né à Caracas dans une riche famille créole, orphelin jeune, il est formé par son précepteur Simón Rodríguez, disciple de Rousseau, et découvre en Europe les idées des Lumières. À Rome, en 1805, il fait le serment de libérer son continent de la domination espagnole.&lt;/p&gt; &lt;p&gt;De 1813 à 1824, il mène une guerre longue et cruelle qui libère le Venezuela, la Colombie, l’Équateur, le Pérou et la Bolivie, qui porte son nom. Mais il est aussi un penseur politique. Dans sa &lt;a href="https://fr.wikipedia.org/wiki/Lettre_de_Jama%C3%AFque" title=" Wikipedia"&gt;&lt;em&gt;Lettre de Jamaïque&lt;/em&gt;&lt;/a&gt; (1815), écrite en exil, il analyse la situation de l’Amérique espagnole : un peuple ni européen ni indien, maintenu dans l’ignorance et &lt;a href="https://www.youtube.com/watch?v=CmJbaxJN7d0" title="Simón Bolívar : Le Libérateur qui mourut en exil par Nuits de Savoir"&gt;l’inexpérience politique&lt;/a&gt; par trois siècles de colonisation. Dans son discours d’Angostura (1819), il plaide pour une république adaptée aux réalités du pays plutôt que copiée sur l’Europe ou les États-Unis, et réclame l’abolition de l’esclavage. Il affranchit ses propres esclaves, sans parvenir à imposer partout l’abolition.&lt;/p&gt; &lt;p&gt;Il rêve d’unir les nouvelles nations en une grande confédération et réunit à cette fin le congrès de Panama en 1826. Mais la &lt;a href="https://fr.wikipedia.org/wiki/Grande_Colombie" title=" Wikipedia"&gt;Grande Colombie&lt;/a&gt; qu’il préside se défait sous l’effet des rivalités régionales, et son autoritarisme croissant lui vaut de nombreux ennemis. Malade et désabusé, il meurt en 1830 à Santa Marta en disant avoir « labouré la mer ». Son rêve d’unité latino-américaine reste une référence majeure du continent.&lt;/p&gt;  &lt;audio controls title="Simon Bolivar , encore et toujours par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16278-16.11.2019-ITEMA_22204790-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ewVfzO5CHS0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Simon Bolivar, le héros des indépendances de l'Amérique espagnole" par Nota Bene</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/bolivar-mini.webp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Républicanisme ; Libéralisme</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le Libertador, chef des indépendances sud-américaines et penseur de l’unité latino-américaine.</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O6" s="1">
+        <v>2</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vénézuélienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
         <v>1803</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">"Ralph Waldo Emerson – la confiance en soi par Parole de Philosophe</t>
         </is>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transcendantalisme ; Spiritualisme ; Individualisme</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
-        <v>1810</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcendantalisme ; Spiritualisme ; Individualisme</t>
+        </is>
       </c>
       <c r="L7" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
-        <v>1817</v>
+        <v>1810</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>66</v>
+        <v>54</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>1817</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Transcendantalisme ; Anarchisme ; Individualisme</t>
         </is>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="241.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+    <row r="10" customFormat="false" ht="241.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
         <v>1839</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B10" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Charles Sanders PEIRCE</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Sanders_Peirce" title=" Wikipedia"&gt;Charles Sanders PEIRCE&lt;/a&gt;  était un philosophe, logicien, scientifique américain assez original, fondateur du  &lt;a href="https://www.youtube.com/watch?v=AGHmKg7wYf0"  title="Pragmatisme  par robertus"&gt;pragmatisme&lt;/a&gt;, père de la sémiotique moderne (théorie des signes) et un pionnier de la logique. Pourtant, en raison de  &lt;a href="https://laviedesidees.fr/Chevalier-Peirce-ou-l-invention-de-l-epistemologie" style="color:#88A1E9" title="les pepites de Charles s pierce par laviedesidees"&gt;sa personnalité difficile&lt;/a&gt; et de ses idées avant-gardistes, il vécut en marge du monde académique, mourant dans la pauvreté et l'isolement. &lt;/p&gt; &lt;p&gt;  Il cherchait à identifier les catégories les plus fondamentales et universelles de la pensée et de l'être, qu'il nomma Phanéroscopie.Il en déduit trois, présentes dans tous les phénomènes. Elles sont la clé de voûte de tout le système peircien et sont indispensables pour comprendre sa sémiotique et  &lt;a href="https://hal.science/hal-02953592/document"  title="Pragmatisme  par hal science"&gt;son pragmatisme&lt;/a&gt;: &lt;/p&gt; &lt;p&gt; - Priméité (Firstness) : C'est la catégorie de la qualité pure, de la potentialité, de la sensation immédiate et brute, existant en elle-même sans référence à quoi que ce soit d'autre. C'est le "sentiment de rouge", la qualité d'une odeur, la nouveauté d'une idée. C'est le domaine de la possibilité et de la liberté. &lt;/p&gt; &lt;p&gt; - Secondéité (Secondeity) : C'est la catégorie du fait brut, de l'action-réaction, de la résistance et de l'actualité. C'est le choc du "ici et maintenant", la rencontre avec un autre qui s'impose à nous. Exemples : une collision, la sensation de résistance en poussant une porte, un conflit. C'est le domaine de l'existence et de la dualité. &lt;/p&gt; &lt;p&gt; - Tiercéité (Thirdness) : C'est la catégorie de la médiation, de la loi, de l'habitude, de la généralisation et de la signification. Elle fait le lien entre la Priméité (la qualité) et la Secondéité (le fait) en leur donnant un sens et une régularité. Exemples : une loi scientifique, un symbole linguistique, une tendance, une règle de conduite. C'est le domaine de la pensée, de la continuité et de l'intelligibilité. &lt;/p&gt; &lt;p&gt; Il propose une méthode pour clarifier le sens de nos idées, le Pragmaticisme: le sens d'un concept réside dans ses conséquences pratiques observables. Si deux idées ne produisent aucune différence pratique, elles signifient la même chose. C'est avant tout une méthode logique pour trancher les disputes métaphysiques stériles.&lt;/p&gt; &lt;p&gt; Sa contribution la plus novatrice et la plus influente est &lt;a href="https://www.persee.fr/doc/lgge_0458-726x_1980_num_14_58_1844" title="La séméiotique de Charles S. Peirce  par Persée"&gt;la Sémiotique&lt;/a&gt;. Pour lui, "l'homme est un signe" et toute pensée est un &lt;a href="https://www.youtube.com/watch?v=e1jrx1RlS00" title="VOIR ET INTERPRÉTER LES SIGNES ! Introduction à la sémiologie CHARLES SANDERS PEIRCE  par Survivreauxscienceshumaines"&gt;processus sémiotique&lt;/a&gt;. Il définit le signe non pas de manière dyadique mais triadique,  Il crée dans l'esprit de la  personne un signe plus développé, appelé l'interprétant. La relation signe-objet-interprétant est fondamentale. Sa classification concerne la relation du signe à son objet : &lt;/p&gt; &lt;dd&gt; - Icône: Le signe ressemble à son objet ou partage des qualités avec lui (une photographie, un diagramme). &lt;/dd&gt; &lt;dd&gt; - Index: Le signe est physiquement connecté à son objet : la fumée (indice du feu), une girouette (indice de la direction du vent). &lt;/dd&gt; &lt;dd&gt; - Symbole: La relation entre le signe et l'objet est arbitraire et conventionnelle. Elle repose sur une règle ou une habitude sociale. ("arbre" n'a rien d'un arbre). &lt;/dd&gt; &lt;p&gt; Bien que mort dans la misère et méconnu de son vivant, son influence est immense aujourd'hui en philosophie, en sciences cognitives, en linguistique et en sociologie. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="201.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
-        <v>1842</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;a href="https://fr.wikipedia.org/wiki/William_James"  title=" Wikipedia"&gt;William JAMES&lt;/a&gt; est un philosophe Américain surtout connu pour la philosophie du &lt;a  href="https://www.youtube.com/watch?v=EKfQ2XunoYk&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Pragmatisme par Le Précepteur"&gt;Pragmatisme&lt;/a&gt; et fondateur de la psychologie moderne aux États-Unis. Professeur à Harvard, il a influencé des domaines variés comme la philosophie, la religion et les sciences cognitives par son approche empirique et anti-dogmatique.&lt;/p&gt; &lt;p&gt; Son pragmatisme, exposé dans Le Pragmatisme (1907), définit la vérité non comme une correspondance abstraite avec la réalité, mais comme ce qui "fonctionne" pratiquement et produit des effets concrets dans l'expérience. Il rejette les philosophies spéculatives fermées : pour lui, les idées doivent être testées par leurs conséquences observables, comme un "corridor" reliant les doctrines rivales à la vie quotidienne. &lt;/p&gt; &lt;p&gt; La vérité n'est pas quelque chose d'absolu ou d'universel, mais plutôt quelque chose qui est en constante évolution et qui dépend du contexte. Pour lui, la vérité doit être testée par l'expérience et l'action, et il a donc considéré que l'importance de l'expérience pratique et de l'observation était essentielle à la compréhension de la vérité. &lt;/p&gt; &lt;p&gt;Dans son livre &lt;a  href="https://www.persee.fr/doc/psy_0003-5033_1905_num_12_1_5996"  title="Les variétés de l'expérience religieuse par persée.fr"&gt;"Les Variétés de l'expérience religieuse"&lt;/a&gt;, il a étudié les différentes formes de religion et a mis en évidence leur importance pour la compréhension de la nature humaine valorisant les expériences mystiques subjectives si elles portent des fruits moraux et pratiques, sans exiger de preuves théologiques. Son pluralisme intellectuel – acceptant plusieurs vérités compatibles – en fait un penseur de l'ouverture et de l'adaptation, influençant Bergson et la philosophie contemporaine.  &lt;/p&gt; &lt;p&gt;En psychologie, il est considéré comme l'un des fondateurs du courant de la psychologie fonctionnaliste, qui s'intéresse à la façon dont les gens utilisent leur esprit pour s'adapter à leur environnement. Il a également étudié la théorie de l'émotion et a proposé que les émotions ne sont pas simplement des réponses physiologiques &lt;a  href="https://www.youtube.com/watch?v=C4vhWaWiPus"  title="L’art de stimuler l’intelligence par les rares livres"&gt;à des stimuli, &lt;/a&gt; mais plutôt des expériences subjectives qui sont influencées par la perception, la cognition et les actions.  Son œuvre majeure Les Principes de psychologie (1890) introduit une vision du "flux de conscience" (stream of consciousness), où l'esprit est un courant continu et fluide, non une série d'images statiques. Il critique le dualisme corps-esprit, voyant émotions et actions comme indissociables, et défend un indéterminisme qui laisse place à la liberté humaine.&lt;/p&gt;   &lt;audio controls title="William James par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/05/s18/NET_FC_82a4623d-00a5-4024-a797-fd01dd5050ec.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pragmatisme ; Empirisme ; Épiphénoménisme ; Pluralisme</t>
-        </is>
+        <v>80</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="201.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
-        <v>1855</v>
+        <v>1842</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;a href="https://fr.wikipedia.org/wiki/William_James"  title=" Wikipedia"&gt;William JAMES&lt;/a&gt; est un philosophe Américain surtout connu pour la philosophie du &lt;a  href="https://www.youtube.com/watch?v=EKfQ2XunoYk&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Pragmatisme par Le Précepteur"&gt;Pragmatisme&lt;/a&gt; et fondateur de la psychologie moderne aux États-Unis. Professeur à Harvard, il a influencé des domaines variés comme la philosophie, la religion et les sciences cognitives par son approche empirique et anti-dogmatique.&lt;/p&gt; &lt;p&gt; Son pragmatisme, exposé dans Le Pragmatisme (1907), définit la vérité non comme une correspondance abstraite avec la réalité, mais comme ce qui "fonctionne" pratiquement et produit des effets concrets dans l'expérience. Il rejette les philosophies spéculatives fermées : pour lui, les idées doivent être testées par leurs conséquences observables, comme un "corridor" reliant les doctrines rivales à la vie quotidienne. &lt;/p&gt; &lt;p&gt; La vérité n'est pas quelque chose d'absolu ou d'universel, mais plutôt quelque chose qui est en constante évolution et qui dépend du contexte. Pour lui, la vérité doit être testée par l'expérience et l'action, et il a donc considéré que l'importance de l'expérience pratique et de l'observation était essentielle à la compréhension de la vérité. &lt;/p&gt; &lt;p&gt;Dans son livre &lt;a  href="https://www.persee.fr/doc/psy_0003-5033_1905_num_12_1_5996"  title="Les variétés de l'expérience religieuse par persée.fr"&gt;"Les Variétés de l'expérience religieuse"&lt;/a&gt;, il a étudié les différentes formes de religion et a mis en évidence leur importance pour la compréhension de la nature humaine valorisant les expériences mystiques subjectives si elles portent des fruits moraux et pratiques, sans exiger de preuves théologiques. Son pluralisme intellectuel – acceptant plusieurs vérités compatibles – en fait un penseur de l'ouverture et de l'adaptation, influençant Bergson et la philosophie contemporaine.  &lt;/p&gt; &lt;p&gt;En psychologie, il est considéré comme l'un des fondateurs du courant de la psychologie fonctionnaliste, qui s'intéresse à la façon dont les gens utilisent leur esprit pour s'adapter à leur environnement. Il a également étudié la théorie de l'émotion et a proposé que les émotions ne sont pas simplement des réponses physiologiques &lt;a  href="https://www.youtube.com/watch?v=C4vhWaWiPus"  title="L’art de stimuler l’intelligence par les rares livres"&gt;à des stimuli, &lt;/a&gt; mais plutôt des expériences subjectives qui sont influencées par la perception, la cognition et les actions.  Son œuvre majeure Les Principes de psychologie (1890) introduit une vision du "flux de conscience" (stream of consciousness), où l'esprit est un courant continu et fluide, non une série d'images statiques. Il critique le dualisme corps-esprit, voyant émotions et actions comme indissociables, et défend un indéterminisme qui laisse place à la liberté humaine.&lt;/p&gt;   &lt;audio controls title="William James par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/05/s18/NET_FC_82a4623d-00a5-4024-a797-fd01dd5050ec.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F11" s="7" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pragmatisme ; Empirisme ; Épiphénoménisme ; Pluralisme</t>
+        </is>
       </c>
       <c r="L11" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="183.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
-        <v>1859</v>
+        <v>1855</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>106</v>
+        <v>95</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>96</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>51</v>
@@ -2713,250 +2742,245 @@
     </row>
     <row r="13" customFormat="false" ht="183.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
-        <v>1860</v>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>1936</v>
+        <v>1859</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>115</v>
+        <v>105</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>118</v>
+        <v>108</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>109</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="183.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>1917</v>
+        <v>1936</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>123</v>
+        <v>114</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="2" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="182.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="183.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
-        <v>1872</v>
+        <v>1862</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>1958</v>
+        <v>1917</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>133</v>
+        <v>122</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>123</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="2" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="P15" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="182.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="I16" s="9"/>
+      <c r="J16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
+    <row r="17" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
         <v>1873</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B17" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/William_Ernest_Hocking"  title=" Wikipedia"&gt;William Ernest HOCKING&lt;/a&gt; était un philosophe idéaliste américain de Harvard, disciple de Josiah Royce et figure majeure du « personnalisme de Harvard », courant qui met l’accent sur la personne spirituelle et la conscience en tant que cœur de la réalité. Il poursuit et révise l’idéalisme de Royce en le rendant plus compatible avec l’empirisme, le naturalisme et le pragmatisme américains. &lt;/p&gt; &lt;p&gt; Dans sa métaphysique, il défend l’idée que le  &lt;a href="https://www.youtube.com/watch?v=YQn-iAr8urc" title="man’s cosmic with william hocking par vedanta video"&gt;monde est une pluralité &lt;/a&gt; de substances spirituelles conscientes, toutes reliées à un Absolu ou à un « Autre Esprit » que l’on peut identifier à Dieu. Il soutient que la communication entre êtres humains suppose cette conscience globale de l’Univers, et que Dieu est la cause première de la créativité et de la réalité elle‑même, &lt;/p&gt; &lt;p&gt; En philosophie de la religion, il développe une théologie non dogmatique : la vérité religieuse se découvre dans l’expérience vivante du Divin plutôt que dans des croyances figées ou des institutions. Il critique la science qui voudrait exclure complètement le religieux, en affirmant que l’universel et le sens ultime ne sont accessibles que par une forme d’expérience spirituelle. &lt;/p&gt; &lt;p&gt; Il  est aussi connu pour sa théorie du &lt;a href="https://www.persee.fr/doc/linx_0246-8743_1994_hos_5_1_1294" title="aspect du comportement pragmatique de la negation"&gt;« pragmatisme négatif » : &lt;/a&gt; si une idée réussit pratiquement, elle peut être vraie, mais si elle échoue, elle ne peut pas l’être, car « la vérité fonctionne toujours ». Ce critère lui permet de garder une place pour le pragmatisme tout en refusant de réduire la vérité à l’utilité immédiate. &lt;/p&gt; &lt;p&gt; Il s’engage dans la réflexion politique et éthique, en défendant une forme de libéralisme renouvelé où la liberté ne se réduit pas à l’absence de contrainte, mais à la possibilité pour chaque individu de « devenir un homme entier » en développant ses capacités. Il insiste sur le droit fondamental de chacun à développer les puissances qui sont en lui, ce qui relie sa philosophie à des questions de justice sociale, de droits humains et de responsabilité mondiale. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>1883</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>156</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="2" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
-        <v>1889</v>
+        <v>1883</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alfonso_Reyes"  title=" Wikipedia"&gt;Alfonso REYES&lt;/a&gt; était un écrivain et philosophe &amp; diplomate  mexicain, souvent considéré comme l’un des grands humanistes de la langue espagnole au XXe siècle.  &lt;a href="https://www.persee.fr/doc/hispa_0007-4640_1960_num_62_1_3655"  title=" Alfonso Reyes par Persée"&gt;Sa pensée &lt;/a&gt; philosophique est inséparable de son travail d’essayiste, de critique littéraire et de médiateur entre les cultures européennes et latino‑américaines. &lt;/p&gt; &lt;p&gt; Son premier livre important, "Cuestiones estéticas" paru en  1911 est une série de réflexions sur l’esthétique et la critique littéraire, où il articule déjà l’idée que l’expérience artistique est une forme de connaissance privilégiée du monde. Il donne des conférences sur l’"esthétique classique", qui influenceront durablement l’orientation intellectuelle mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Il n’est pas un philosophe systématique au sens académique, mais un humaniste qui pense la littérature, l’histoire et le mythe comme voies d’accès à la réalité et à l’identité mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &lt;a href="https://www.youtube.com/watch?v=IeZKZ6PC9H4"  title=" Visión de Anáhuac de Alfonso Reyes par Literatubers"&gt;"Visión de Anáhuac"&lt;/a&gt;, il propose une méditation poétique et historique sur le Mexique préhispanique et la Conquête, en insistant sur la continuité d’une sensibilité mexicaine à travers les siècles. &lt;/p&gt; &lt;p&gt; Il défend une conception de l’homme formé par les lettres, la philosophie et les sciences, contre les réductions technocratiques ou purement utilitaires du savoir et pense l’Amérique latine comme espace de synthèse entre héritages indigènes, hispaniques et européens, et fait de la traduction et de la critique des instruments de ce dialogue. &lt;/p&gt;</t>
-        </is>
+        <v>152</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>153</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="2" t="s">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>29</v>
@@ -2965,346 +2989,348 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Edward_Bernays" title=" Wikipedia"&gt;Edward BERNAYS&lt;/a&gt;, neveu de Sigmund FREUD était un célèbre publicitaire et consultant en relations publiques américain qui développa le Propogandisme. &lt;/p&gt; &lt;p&gt;  Il est connu pour son livre &lt;a href="https://www.youtube.com/watch?v=-M7E75MAWWM&amp;ab_channel=EcoMan%28i%29a"   title="L'ouvrage Propaganda par Eco Man"&gt; "Propaganda"&lt;/a&gt;, publié en 1928, dans lequel il décrit les techniques qu'il utilisait pour influencer l'opinion publique et manipuler les masses à des fins commerciales et politiques.&lt;/p&gt; &lt;p&gt;  Il a été un pionnier de l'utilisation de la psychologie et de la sociologie pour influencer les opinions et les comportements des consommateurs par la &lt;a href="https://www.vivrelibre.net/wp-content/uploads/2017/07/VL57.pdf"  title="La manipulation des esprits par Michel LEBLANC"&gt; manipulation des esprits&lt;/a&gt;. Il a utilisé des techniques telles que la manipulation des symboles et des images pour renforcer l'association d'un produit avec des valeurs ou des sentiments positifs dans l'esprit des consommateurs. &lt;/p&gt; &lt;p&gt; Il a également joué un rôle important dans la promotion du consumérisme en encourageant les gens à dépenser de l'argent pour des produits inutiles et en stimulant la demande pour de nouveaux produits.  Il a également été impliqué dans des campagnes de relations publiques pour des entreprises et des gouvernements, y compris la promotion du tabac auprès des femmes et la campagne pour la guerre américaine en Irak. &lt;/p&gt; &lt;p&gt;  Il est considéré comme le fondateur de la &lt;a href="https://www.youtube.com/watch?v=UvkhFpb7M7Y&amp;t=342s&amp;ab_channel=LePr%C3%A9cepteur"  title="Comment manipuler l'opinion par le Précepteur"&gt; manipulation de l'opinion &lt;/a&gt; publique moderne, son influence est souvent critiquée pour avoir encouragé une culture de la manipulation et de la tromperie dans les relations publiques et la publicité. &lt;/p&gt;  &lt;audio controls title="Propaganda ou comment manipuler l'opinion publique par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2012/01/s02/NET_e7ddaac9-fb30-445c-9784-f05763b129ef.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        <v>160</v>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alfonso_Reyes"  title=" Wikipedia"&gt;Alfonso REYES&lt;/a&gt; était un écrivain et philosophe &amp; diplomate  mexicain, souvent considéré comme l’un des grands humanistes de la langue espagnole au XXe siècle.  &lt;a href="https://www.persee.fr/doc/hispa_0007-4640_1960_num_62_1_3655"  title=" Alfonso Reyes par Persée"&gt;Sa pensée &lt;/a&gt; philosophique est inséparable de son travail d’essayiste, de critique littéraire et de médiateur entre les cultures européennes et latino‑américaines. &lt;/p&gt; &lt;p&gt; Son premier livre important, "Cuestiones estéticas" paru en  1911 est une série de réflexions sur l’esthétique et la critique littéraire, où il articule déjà l’idée que l’expérience artistique est une forme de connaissance privilégiée du monde. Il donne des conférences sur l’"esthétique classique", qui influenceront durablement l’orientation intellectuelle mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Il n’est pas un philosophe systématique au sens académique, mais un humaniste qui pense la littérature, l’histoire et le mythe comme voies d’accès à la réalité et à l’identité mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &lt;a href="https://www.youtube.com/watch?v=IeZKZ6PC9H4"  title=" Visión de Anáhuac de Alfonso Reyes par Literatubers"&gt;"Visión de Anáhuac"&lt;/a&gt;, il propose une méditation poétique et historique sur le Mexique préhispanique et la Conquête, en insistant sur la continuité d’une sensibilité mexicaine à travers les siècles. &lt;/p&gt; &lt;p&gt; Il défend une conception de l’homme formé par les lettres, la philosophie et les sciences, contre les réductions technocratiques ou purement utilitaires du savoir et pense l’Amérique latine comme espace de synthèse entre héritages indigènes, hispaniques et européens, et fait de la traduction et de la critique des instruments de ce dialogue. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F19" s="7" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="2" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>51</v>
+        <v>29</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
         <v>1891</v>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Edward_Bernays" title=" Wikipedia"&gt;Edward BERNAYS&lt;/a&gt;, neveu de Sigmund FREUD était un célèbre publicitaire et consultant en relations publiques américain qui développa le Propogandisme. &lt;/p&gt; &lt;p&gt;  Il est connu pour son livre &lt;a href="https://www.youtube.com/watch?v=-M7E75MAWWM&amp;ab_channel=EcoMan%28i%29a"   title="L'ouvrage Propaganda par Eco Man"&gt; "Propaganda"&lt;/a&gt;, publié en 1928, dans lequel il décrit les techniques qu'il utilisait pour influencer l'opinion publique et manipuler les masses à des fins commerciales et politiques.&lt;/p&gt; &lt;p&gt;  Il a été un pionnier de l'utilisation de la psychologie et de la sociologie pour influencer les opinions et les comportements des consommateurs par la &lt;a href="https://www.vivrelibre.net/wp-content/uploads/2017/07/VL57.pdf"  title="La manipulation des esprits par Michel LEBLANC"&gt; manipulation des esprits&lt;/a&gt;. Il a utilisé des techniques telles que la manipulation des symboles et des images pour renforcer l'association d'un produit avec des valeurs ou des sentiments positifs dans l'esprit des consommateurs. &lt;/p&gt; &lt;p&gt; Il a également joué un rôle important dans la promotion du consumérisme en encourageant les gens à dépenser de l'argent pour des produits inutiles et en stimulant la demande pour de nouveaux produits.  Il a également été impliqué dans des campagnes de relations publiques pour des entreprises et des gouvernements, y compris la promotion du tabac auprès des femmes et la campagne pour la guerre américaine en Irak. &lt;/p&gt; &lt;p&gt;  Il est considéré comme le fondateur de la &lt;a href="https://www.youtube.com/watch?v=UvkhFpb7M7Y&amp;t=342s&amp;ab_channel=LePr%C3%A9cepteur"  title="Comment manipuler l'opinion par le Précepteur"&gt; manipulation de l'opinion &lt;/a&gt; publique moderne, son influence est souvent critiquée pour avoir encouragé une culture de la manipulation et de la tromperie dans les relations publiques et la publicité. &lt;/p&gt;  &lt;audio controls title="Propaganda ou comment manipuler l'opinion publique par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2012/01/s02/NET_e7ddaac9-fb30-445c-9784-f05763b129ef.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B21" s="7" t="n">
         <v>1962</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher)"  title=" Wikipedia"&gt;Francisco ROMERO&lt;/a&gt; était un philosophe argentin d’origine espagnole, professeur à l’Université de Buenos Aires et à La Plata, et une figure centrale de la réaction  &lt;a href="https://fr.wikipedia.org/wiki/Ib%C3%A9ro-Am%C3%A9rique"  title="ibéro-amérique par wikipedia"&gt; ibéro-américaine &lt;/a&gt; contre le positivisme dominant au début du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa production philosophique couvre l’épistémologie, la philosophie de la culture et l’anthropologie philosophique ; son ouvrage majeur en langue espagnole, Teoría del hombre (1952), propose une réflexion systématique sur la condition humaine, la liberté et la créativité culturelle, et a été traduit en anglais sous le titre Theory of Man.https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher) &lt;/p&gt; &lt;p&gt; Il  prit position contre  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9ductionnisme"  title="Reductionnisme par wikipedia"&gt; le réductionnisme scientiste &lt;/a&gt; en défendant l’idée que la culture et les créations humaines (art, religion, langage) exigent des méthodes et des concepts propres, distincts des instruments des sciences naturelles ; il chercha donc à articuler rigueur philosophique et sensibilité littéraire. &lt;/p&gt; &lt;p&gt; Sur le plan méthodologique, il promut une philosophie qui dialogue avec l’histoire des idées et avec les problèmes concrets de la société ibéro-américaine : ses travaux montrent un intérêt marqué pour la responsabilité sociale des intellectuels et pour la formation culturelle des peuples. &lt;/p&gt; &lt;p&gt; Parmi ses autres ouvrages importants figurent Old and New Concepts of Reality (1932), The Problems of Philosophy of Culture (1938), Man and Culture (1950, traduction de El hombre y la cultura) et History of Modern Philosophy (1959); sa réputation lui valut le surnom de « doyen des philosophes ibéro-américains » et son héritage continue d’être étudié dans les études sur la philosophie latino‑américaine. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Francisco romero par Biografias de Filosofos</t>
         </is>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H21" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
-        <v>1894</v>
-      </c>
-      <c r="B21" s="7" t="n">
-        <v>1930</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="2" t="s">
-        <v>59</v>
+        <v>183</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>191</v>
+        <v>26</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>29</v>
       </c>
       <c r="P21" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="n">
+        <v>1894</v>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>1930</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="J22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
+    <row r="23" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B23" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D23" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Susanne_Langer" title=" Wikipedia"&gt;Susanne LANGER&lt;/a&gt; était une philosophe américaine connue pour ses travaux sur le symbole, l’art et la perception. Elle a joué un rôle important dans la philosophie défendant l’idée que la pensée humaine ne se limite pas au langage discursif, mais s’exprime aussi à travers des formes symboliques non verbales, notamment artistiques. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=gwYNyxDTOhQ"   title=" suzanne langer par overthink podcast"&gt;Son œuvre &lt;/a&gt; la plus influente est sans doute Philosophy in a New Key (1942), où elle soutient que l’art n’est pas simplement une décoration ou une émotion brute, mais une forme de connaissance. Pour elle, la musique, la danse, la peinture ou la poésie donnent accès à des structures de sentiment que le langage ordinaire explique mal. Cette idée l’a rendue très importante pour l’esthétique et la théorie des symboles. &lt;/p&gt; &lt;p&gt; Elle s’inscrit dans une tradition marquée par Ernst Cassirer, qui voyait l’être humain comme un animal symbolique. Elle reprend cette intuition en affirmant que l’esprit humain construit le monde au moyen de symboles, et que ces symboles ne sont pas tous de même nature. Elle distingue ainsi les systèmes discursifs, qui avancent par étapes logiques, et les formes présentatives, plus propres à &lt;a href="https://www.youtube.com/watch?v=BM43-aqdboA"   title=" suzanne langer par philosophy overdose"&gt;l’art et à l’expérience sensible. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Son apport est aussi majeur en philosophie de l’art, car elle refuse de réduire l’œuvre à une simple expression subjective de l’artiste. Au contraire, elle cherche à montrer que l’œuvre organise une forme, un rythme et une structure qui rendent intelligible une expérience affective. Cette approche a eu une influence durable sur l’esthétique, la musique et plusieurs sciences humaines. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G23" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H23" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe américaine de l'art et des symboles, pour qui l'art est une forme de connaissance.</t>
-        </is>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
-        <v>1897</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="2" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe américaine de l'art et des symboles, pour qui l'art est une forme de connaissance.</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
         <v>1897</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="I24" s="9"/>
+      <c r="J24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="n">
+        <v>1897</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C25" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Samuel_Ramos"  title=" Wikipedia"&gt;Samuel RAMOS&lt;/a&gt; était un philosophe mexicain  précurseur de la philosophie de la mexicanité qui analyse le caractère national mexicain à travers une approche psychologique et historiciste. &lt;/p&gt; &lt;p&gt; Il applique le perspectivisme d'Ortega y Gasset et la psychologie adlérienne : le Mexicain souffre d'un complexe d'infériorité structurel se manifestant par dissimulation, susceptibilité, phallocratie et idéalisme primitif. Critique du positivisme porfirien, il lie philosophie à révolution mexicaine  en 1910, murale (Rivera) et Ateneo de la Juventud (Caso, Vasconcelos), prônant une culture créole authentique plutôt que folklorique ou importée. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://fr.slideshare.net/slideshow/samuel-ramos-hacia-un-nuevo-humanismo/15149441"  title="Samuel ramos hacia un nuevo humanismo par slideshare"&gt;Son projet &lt;/a&gt;: construire une "culture à la hauteur du monde civilisé" via éducation et réflexion existentielle, évitant à la fois servilité et isolationnisme. Précurseur de Hiperión (1950, avec Zea, Uranga, Villoro), il fonde l'étude de l'"être mexicain", influençant Paz (Labyrinthe de la solitude), Zea et la philosophie de la libération ; sa quête d'identité universelle mais située ouvre à la décolonialité. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G25" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H25" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
-        <v>1898</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="2" t="s">
-        <v>37</v>
+        <v>218</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>29</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
-        <v>1901</v>
+        <v>1898</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="2" t="s">
-        <v>237</v>
+        <v>37</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>176</v>
@@ -3313,41 +3339,40 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
+    <row r="27" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="n">
         <v>1901</v>
       </c>
-      <c r="B27" s="1" t="n">
-        <v>1985</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ernest nagel on computers, logic and mind par Philosophy Overdose</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>245</v>
-      </c>
+      <c r="B27" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="I27" s="9"/>
       <c r="J27" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>176</v>
@@ -3356,481 +3381,482 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="n">
-        <v>1905</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D-fU2DMB8T0</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Ayn Rand - Faut-il ne penser qu'à soi ?" par Kosmos</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I28" s="9"/>
+    <row r="28" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>1985</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ernest nagel on computers, logic and mind par Philosophy Overdose</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>245</v>
+      </c>
       <c r="J28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Objectivisme ; Libéralisme ; Minarchisme</t>
-        </is>
+        <v>246</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>258</v>
+        <v>176</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="252" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>263</v>
+        <v>252</v>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D-fU2DMB8T0</t>
+        </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Hannah ARENDT: la philosophe par Coursitout</t>
+          <t xml:space="preserve">"Ayn Rand - Faut-il ne penser qu'à soi ?" par Kosmos</t>
         </is>
       </c>
       <c r="H29" s="9" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>266</v>
+        <v>70</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Objectivisme ; Libéralisme ; Minarchisme</t>
+        </is>
       </c>
       <c r="L29" s="2" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O29" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="30" customFormat="false" ht="252" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="n">
         <v>1906</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>274</v>
+        <v>263</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Hannah ARENDT: la philosophe par Coursitout</t>
+        </is>
       </c>
       <c r="H30" s="9" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Analytique ; Nominalisme ; Méréologie</t>
-        </is>
+        <v>37</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>176</v>
+        <v>268</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="O30" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="2" t="s">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytique ; Nominalisme ; Empirisme ; Holisme ; Ontologie</t>
+          <t xml:space="preserve">Analytique ; Nominalisme ; Méréologie</t>
         </is>
       </c>
       <c r="L31" s="2" t="s">
-        <v>286</v>
+        <v>278</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="I32" s="9"/>
+      <c r="J32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Nominalisme ; Empirisme ; Holisme ; Ontologie</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="n">
         <v>1912</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B33" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C33" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D33" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leopoldo_Zea_Aguilar" title=" Wikipedia"&gt;Leopoldo ZEA AGUILAR&lt;/a&gt; était un philosophe mexicain, considéré comme l'un des pères fondateurs de la philosophie latino-américaine contemporaine, engagé dans la quête d'une identité culturelle autonome face à l'eurocentrisme et au néocolonialisme. &lt;/p&gt; &lt;p&gt;  Il pose la question centrale : "Peut-on construire une philosophie latino-américaine ?" Réponse affirmative via une dialectique de la conscience : de la dépendance à la libération, où l'homme latino-américain réalise sa liberté par la reconnaissance de sa singularité culturelle. Relativiste culturel sans relativisme absolu, il définit l'homme comme ouvert et pluriel, rejetant l'eurocentrisme comme domination masquée ; la philosophie devient &lt;a href="https://ensayistas.org/antologia/XXA/zea/zea2.htm" title="Leopoldo Zea Aguilar | Autopercepción intelectual de un proceso histórico par ensayistas"&gt;"instrument de libération"&lt;/a&gt;, transformant l'histoire en projet éthique-politique de dignité, égalité et solidarité. Précurseur des critiques post-coloniales et postmodernes, il voit 1492 non comme "découverte" mais comme "occultation" culturelle, et la philosophie latino-américaine comme symbiose de nationalisme, christianisme et socialisme anti-impérialiste. &lt;/p&gt; &lt;p&gt; Mentor de générations, il fonde des centres intellectuels en Amérique latine et reçoit des prix mondiaux ; son discours sur la marginalité influence la philosophie de la libération et les études culturelles décoloniales. Il reste &lt;a href="https://www.youtube.com/watch?v=_kEH9wQFQv4" style="color:#88A1E9" title="Leopoldo Zea Aguilar | Doctorado en Educación par Miguel Morales"&gt;une référence &lt;/a&gt; pour une Amérique latine unie, non utopique mais réaliste, affirmant : "Se connaître égal en étant distinct est l'essence des relations humaines et internationales". &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F33" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G33" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H33" s="9" t="s">
         <v>293</v>
-      </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="n">
-        <v>1916</v>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>1999</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>301</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="n">
+        <v>1916</v>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>1999</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I34" s="9"/>
+      <c r="J34" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Méréologie ; Analytique ; Libertarianisme ; Particularisme ; Incompatibilisme</t>
         </is>
       </c>
-      <c r="L33" s="14" t="s">
+      <c r="L34" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="N34" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="174.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="n">
+    <row r="35" customFormat="false" ht="174.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="n">
         <v>1921</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B35" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D35" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Rawls_(philosophe)"  title=" Wikipedia"&gt;John RAWLS&lt;/a&gt; était un  philosophe politique américain connu grâce à son œuvre majeure "&lt;a href="https://www.youtube.com/watch?v=OIKwI5qu4y8" style="color:#88A1E9" title=" La THÉORIE DE LA JUSTICE en 8 minutes ! (John RAWLS) par Culture Philo"&gt; A Theory of Justice&lt;/a&gt;", publiée en 1971 ou il propose une conception de la  &lt;a href="https://www.youtube.com/watch?v=2w-AEMAU_EE"  title=" Le libéralisme égalitaire de John Rawls par Philoxime"&gt;"justice comme équité"&lt;/a&gt;. Il s’oppose à l’utilitarisme – doctrine selon laquelle une action est bonne si elle maximise le bonheur collectif – et cherche au contraire à fonder la justice sur des principes garantissant équitablement les libertés et droits fondamentaux pour tous. &lt;/p&gt; &lt;p&gt;  Il imagine une " &lt;a href="https://www.persee.fr/doc/rfsp_0035-2950_1991_num_41_1_394540"  title="La Théorie de la justice de John Rawls. Contrat social versus utilitarisme par Persée"&gt;position originelle&lt;/a&gt;", situation hypothétique où des individus rationnels, placés derrière un « voile d’ignorance » qui leur cache leurs avantages personnels, choisiraient des règles de justice justes pour tous. De cette expérience de pensée, il déduit deux principes essentiels dont le principe d’égale liberté où chaque personne doit avoir un droit égal aux libertés fondamentales et le principe de différence où les inégalités économiques et sociales ne sont justes que si elles profitent aux plus désavantagés.  &lt;/p&gt; &lt;p&gt; Il a ensuite  prolongé sa réflexion dans "Political Liberalism" (1993) et "The Law of Peoples" (1999). Dans le premier, il interroge comment un consensus moral peut se former dans des sociétés pluralistes sans imposer une doctrine particulière ; dans le second, il applique ses principes à la &lt;a href="https://www.youtube.com/watch?v=ah7y1xd3bL0" title="JOHN RAWLS : Qu'est-ce que la justice sociale ? par Parole de Philosophe"&gt;justice internationale&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;  Il a profondément marqué la philosophie morale, politique et économique contemporaine et sa pensée inspira la théorie économique critique, avec des débats persistants sur la compatibilité de sa vision avec le libéralisme ou la social-démocratie et il demeure aujourd’hui une référence incontournable pour toute réflexion sur la justice, l’égalité et la démocratie. &lt;/p&gt; &lt;audio controls title=" Avoir raison avec... John Rawls par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-13.07.2020-ITEMA_22381527-2020C35448S0195-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F35" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">"
 Philosophie - John Rawls et le voile d'ignorance" par Coursitout</t>
         </is>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H35" s="9" t="s">
         <v>310</v>
-      </c>
-      <c r="I34" s="9"/>
-      <c r="J34" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libéralisme ; Contractualisme ; Social-démocratie ; Déontologisme</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="n">
-        <v>1922</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Thomas Kuhn : de la routine à la révolution par Eric Finot</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>319</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>320</v>
+        <v>37</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Contractualisme ; Social-démocratie ; Déontologisme</t>
+        </is>
       </c>
       <c r="L35" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>176</v>
+        <v>312</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>325</v>
+        <v>315</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>316</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>327</v>
+        <v>317</v>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Thomas Kuhn : de la routine à la révolution par Eric Finot</t>
+        </is>
       </c>
       <c r="H36" s="9" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="2" t="s">
-        <v>127</v>
+        <v>246</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>330</v>
+        <v>321</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>334</v>
+        <v>324</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Analytique ; Pragmatisme ; Réalisme scientifique ; Cognitivisme ; Essentialisme ; Computationnalisme</t>
-        </is>
+        <v>127</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>176</v>
+        <v>330</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="222" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
         <v>1926</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>344</v>
+        <v>333</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>334</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>347</v>
+        <v>336</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>337</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Pragmatisme ; Réalisme scientifique ; Cognitivisme ; Essentialisme ; Computationnalisme</t>
+        </is>
       </c>
       <c r="L38" s="2" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>176</v>
@@ -3839,42 +3865,40 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="222" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
         <v>1926</v>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>1995</v>
+      <c r="B39" s="7" t="s">
+        <v>341</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libertarianisme ; Anarcho-Capitalisme ; Volontarisme</t>
-        </is>
-      </c>
-      <c r="L39" s="14" t="s">
-        <v>358</v>
+        <v>25</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>176</v>
@@ -3885,40 +3909,40 @@
     </row>
     <row r="40" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>2016</v>
+        <v>1995</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="2" t="s">
-        <v>218</v>
+        <v>356</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Hassidisme</t>
+          <t xml:space="preserve">Libertarianisme ; Anarcho-Capitalisme ; Volontarisme</t>
         </is>
       </c>
       <c r="L40" s="14" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>176</v>
@@ -3927,833 +3951,818 @@
         <v>51</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
-        <v>1930</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>322</v>
+        <v>1928</v>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>2016</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>369</v>
+        <v>360</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>361</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>373</v>
+        <v>218</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Hassidisme</t>
+        </is>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_Rorty" title=" Wikipedia"&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href="https://www.youtube.com/watch?v=lfx4Jag1ic4"  title="Le pragmatisme : définition, exemples par le savoir partagé"&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href="https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism" title=" a bas l'autorité par laviedesidees"&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas "vrais" ou "faux". &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales, on trouve  &lt;a href="https://www.youtube.com/watch?v=MgU0dXZ3umM" title="L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli"&gt;" Contingence, ironie et solidarité "&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans " Achieving Our Country" (1998),  il y appelle la gauche américaine à abandonner le "culturalisme" pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la "post-vérité". Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; </t>
-        </is>
+        <v>368</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>369</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>380</v>
+        <v>371</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>372</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="2" t="s">
-        <v>381</v>
+        <v>127</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
+    <row r="43" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="n">
+        <v>1931</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_Rorty" title=" Wikipedia"&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href="https://www.youtube.com/watch?v=lfx4Jag1ic4"  title="Le pragmatisme : définition, exemples par le savoir partagé"&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href="https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism" title=" a bas l'autorité par laviedesidees"&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas "vrais" ou "faux". &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales, on trouve  &lt;a href="https://www.youtube.com/watch?v=MgU0dXZ3umM" title="L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli"&gt;" Contingence, ironie et solidarité "&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans " Achieving Our Country" (1998),  il y appelle la gauche américaine à abandonner le "culturalisme" pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la "post-vérité". Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="I43" s="9"/>
+      <c r="J43" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="n">
         <v>1932</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B44" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Searle"  title=" Wikipedia"&gt;John SEARLE&lt;/a&gt; était un philosophe américain  connu pour ses travaux influents dans plusieurs domaines, notamment la philosophie du langage, la philosophie de l'esprit et la philosophie sociale. Il  a développé et systématisé la théorie des &lt;a href="https://www.youtube.com/watch?v=pIbkpLfrD6A" title="
 La théorie des actes de langage (2) - John Searle par Heraut du Mont Parnasse"&gt;actes de langage&lt;/a&gt; car, pour lui, parler une langue, ce n'est pas seulement émettre des sons ou des suites de symboles, mais accomplir des actions. &lt;/p&gt; &lt;p&gt; Défenseur du "naturalisme biologique" en philosophie de l'esprit. Il s'oppose au dualisme cartésien tout en refusant le matérialisme réducteur qui nierait l'existence de &lt;a href="https://www.youtube.com/watch?v=EriAhi0mj7w" title=" Conscience et matière grise par TEDx Talks"&gt;la conscience&lt;/a&gt; ou la réduirirait à de simples phénomènes physiques. Pour lui, les états mentaux (douleur, croyances, désirs, conscience) sont des phénomènes  &lt;a href="https://www.youtube.com/watch?v=Bq2bfSzkTfU"  title="John Searle - Une personne peut-elle être une âme ? par Closer To Truth"&gt;biologiques réels&lt;/a&gt;, causés par des processus neuronaux du cerveau, mais ils ne sont pas réductibles à ces processus au sens où ils émergent à un niveau supérieur et possèdent des propriétés irréductibles.&lt;/p&gt; &lt;p&gt; L'une des ses contributions les plus célèbres est son argument de la &lt;a href="https://www.youtube.com/watch?v=P5DtwDr9YEc" title=" La Chambre chinoise par Ian et frank"&gt;Chambre Chinoise&lt;/a&gt;. Cet argument vise à réfuter la thèse de l'IA forte (position selon laquelle un ordinateur programmé de manière appropriée n'est pas seulement un outil pour l'étude de l'esprit, mais qu'il est véritablement un esprit, capable de comprendre et de posséder d'autres états cognitifs) opposé à l'IA faible (position selon laquelle les ordinateurs sont des outils utiles pour étudier l'esprit, mais qu'ils ne sont pas eux-mêmes des esprits). &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://labo.nonmarchand.org/pmwiki/uploads/Textes/JohnSearleLaConstructionDeLaRealiteSociale/JohnSearle_LaConstructionDeLaRealiteSociale.pdf"  title=" La construction e la réalité sociale par nonmarchand"&gt;"La Construction de la Réalité Sociale"&lt;/a&gt;, il étend sa théorie des actes de langage et de l'intentionnalité pour expliquer comment nous construisons des faits institutionnels et sociaux. Il distingue les "Faits bruts" qui existent indépendamment de toute institution humaine (par exemple, la montagne Everest) des "Faits institutionnels" qui n'existent qu'en vertu d'institutions humaines et de l'accord collectif (par exemple, l'argent, le mariage, la propriété). &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G44" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="2" t="s">
+      <c r="I44" s="1"/>
+      <c r="J44" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K44" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="L44" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="n">
-        <v>1933</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="F44" s="7"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P44" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>400</v>
+        <v>322</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>405</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="F45" s="7"/>
+      <c r="G45" s="9"/>
       <c r="H45" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="I45" s="9"/>
+        <v>396</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>397</v>
+      </c>
       <c r="J45" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiers-mondisme ; Théologie de la libération ; Philosophie de la libération ; Pensée décoloniale</t>
-        </is>
+        <v>398</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O45" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
         <v>1934</v>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>2024</v>
+      <c r="B46" s="7" t="s">
+        <v>400</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>410</v>
+        <v>402</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>403</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>413</v>
+        <v>405</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>406</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiers-mondisme ; Théologie de la libération ; Philosophie de la libération ; Pensée décoloniale</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O46" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="I47" s="9"/>
+      <c r="J47" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="K47" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="L47" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B47" s="1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="G47" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="I47" s="1"/>
-      <c r="J47" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="N47" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P47" s="1" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G48" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P48" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="XFC47" s="0"/>
-      <c r="XFD47" s="0"/>
-    </row>
-    <row r="48" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="16" t="n">
+      <c r="XFC48" s="0"/>
+      <c r="XFD48" s="0"/>
+    </row>
+    <row r="49" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="16" t="n">
         <v>1935</v>
       </c>
-      <c r="B48" s="16" t="n">
+      <c r="B49" s="16" t="n">
         <v>2003</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C49" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D49" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E49" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="F48" s="16" t="s">
+      <c r="F49" s="16" t="s">
         <v>428</v>
       </c>
-      <c r="G48" s="18" t="s">
+      <c r="G49" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="I48" s="18"/>
-      <c r="J48" s="2" t="s">
+      <c r="I49" s="18"/>
+      <c r="J49" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="K49" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="L48" s="14" t="s">
+      <c r="L49" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="M48" s="14" t="s">
+      <c r="M49" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N48" s="14" t="s">
+      <c r="N49" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
+    <row r="50" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
         <v>1937</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B50" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C50" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D50" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E50" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F50" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G50" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H50" s="10" t="s">
         <v>438</v>
-      </c>
-      <c r="I49" s="9"/>
-      <c r="J49" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="n">
-        <v>1938</v>
-      </c>
-      <c r="B50" s="7" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>446</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libéralisme ; Minarchisme ; Déontologisme</t>
-        </is>
+        <v>127</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>439</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="N50" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="N50" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
         <v>1938</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>449</v>
+      <c r="B51" s="7" t="n">
+        <v>2002</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>452</v>
+        <v>442</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>443</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>455</v>
+        <v>445</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>446</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Minarchisme ; Déontologisme</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="I52" s="9"/>
+      <c r="J52" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="K52" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L51" s="2" t="s">
+      <c r="L52" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="B52" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saul_Kripke"  title=" Wikipedia"&gt;Saul KRIPKE&lt;/a&gt; était un philosophe américain de la tradition analytique connu pour ses apports décisifs en logique modale, en métaphysique et en philosophie du langage. Très jeune, il révolutionne la logique en introduisant la sémantique des mondes possibles, aujourd’hui appelée &lt;a href="https://www.youtube.com/watch?v=_sIgAdvhruU"title="Qui est Saul Kripke ? par Monsieur Phi"&gt;"cadres de Kripke"&lt;/a&gt;, qui permet de formaliser la modalité (le nécessaire et le possible) de façon rigoureuse. &lt;/p&gt; &lt;p&gt; Son œuvre la plus influente est "Naming and Necessity", où il critique la conception descriptiviste des noms défendue par Frege et Russell. Selon lui, un  &lt;a href="https://www.youtube.com/watch?v=d7-8Avem7EE" title="Saul Kripke, La logique des noms propres. par Jtgrandtour"&gt; nom propre&lt;/a&gt; n’équivaut pas à une description mais fonctionne comme un « désignateur rigide » : il désigne le même individu dans tous les mondes possibles. Cette idée bouleverse la philosophie du langage et entraîne une redéfinition de la notion de référence.&lt;/p&gt; &lt;p&gt;  Il montre également qu’il existe des vérités nécessaires découvertes empiriquement : par exemple, l’identité « l’eau est H₂O » est nécessaire, mais nous ne l’avons apprise qu’a posteriori. Ce concept de nécessité a posteriori a marqué un tournant dans la métaphysique contemporaine. À l’inverse, il identifie la possibilité de certaines vérités contingentes connues a priori, ce qui remet en cause des distinctions classiques entre connaissance et modalité. &lt;/p&gt; &lt;p&gt; Il s’oppose au physicalisme en arguant que l’on peut concevoir un monde où tous les états cérébraux existent sans que la conscience subjective "le qualia" ne soit présente. Cette critique alimente encore aujourd’hui les débats sur la nature de la conscience. Son ouvrage "Wittgenstein on Rules and Private Language" propose une lecture radicale de Wittgenstein, selon laquelle toute règle est sujette à un scepticisme profond sur son application. Bien que controversée, cette interprétation a largement stimulé les discussions en philosophie du langage et en épistémologie. &lt;/p&gt; &lt;p&gt; Connu aussi pour son ouvrage " On two Paradoxes of Knowledge" et son  &lt;a href="https://www.youtube.com/watch?v=AzaUSC--2G0"  title="Le Paradoxe de l'Examen selon Saul Kripke par Silogic"&gt;"paradoxe de l'examen"&lt;/a&gt;. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P52" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="n">
-        <v>1941</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="I53" s="9"/>
+    </row>
+    <row r="53" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saul_Kripke"  title=" Wikipedia"&gt;Saul KRIPKE&lt;/a&gt; était un philosophe américain de la tradition analytique connu pour ses apports décisifs en logique modale, en métaphysique et en philosophie du langage. Très jeune, il révolutionne la logique en introduisant la sémantique des mondes possibles, aujourd’hui appelée &lt;a href="https://www.youtube.com/watch?v=_sIgAdvhruU"title="Qui est Saul Kripke ? par Monsieur Phi"&gt;"cadres de Kripke"&lt;/a&gt;, qui permet de formaliser la modalité (le nécessaire et le possible) de façon rigoureuse. &lt;/p&gt; &lt;p&gt; Son œuvre la plus influente est "Naming and Necessity", où il critique la conception descriptiviste des noms défendue par Frege et Russell. Selon lui, un  &lt;a href="https://www.youtube.com/watch?v=d7-8Avem7EE" title="Saul Kripke, La logique des noms propres. par Jtgrandtour"&gt; nom propre&lt;/a&gt; n’équivaut pas à une description mais fonctionne comme un « désignateur rigide » : il désigne le même individu dans tous les mondes possibles. Cette idée bouleverse la philosophie du langage et entraîne une redéfinition de la notion de référence.&lt;/p&gt; &lt;p&gt;  Il montre également qu’il existe des vérités nécessaires découvertes empiriquement : par exemple, l’identité « l’eau est H₂O » est nécessaire, mais nous ne l’avons apprise qu’a posteriori. Ce concept de nécessité a posteriori a marqué un tournant dans la métaphysique contemporaine. À l’inverse, il identifie la possibilité de certaines vérités contingentes connues a priori, ce qui remet en cause des distinctions classiques entre connaissance et modalité. &lt;/p&gt; &lt;p&gt; Il s’oppose au physicalisme en arguant que l’on peut concevoir un monde où tous les états cérébraux existent sans que la conscience subjective "le qualia" ne soit présente. Cette critique alimente encore aujourd’hui les débats sur la nature de la conscience. Son ouvrage "Wittgenstein on Rules and Private Language" propose une lecture radicale de Wittgenstein, selon laquelle toute règle est sujette à un scepticisme profond sur son application. Bien que controversée, cette interprétation a largement stimulé les discussions en philosophie du langage et en épistémologie. &lt;/p&gt; &lt;p&gt; Connu aussi pour son ouvrage " On two Paradoxes of Knowledge" et son  &lt;a href="https://www.youtube.com/watch?v=AzaUSC--2G0"  title="Le Paradoxe de l'Examen selon Saul Kripke par Silogic"&gt;"paradoxe de l'examen"&lt;/a&gt;. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>463</v>
+      </c>
       <c r="J53" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>475</v>
+        <v>464</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>465</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>476</v>
+        <v>466</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="332.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P53" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>322</v>
+        <v>467</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
-        <v>246</v>
+        <v>474</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="332.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>449</v>
+        <v>322</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>487</v>
+        <v>478</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>479</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="2" t="s">
-        <v>127</v>
+        <v>246</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>28</v>
+        <v>484</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
+    <row r="56" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="I56" s="9"/>
+      <c r="J56" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="n">
         <v>1949</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B57" s="1" t="n">
         <v>2006</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="E56" s="14" t="inlineStr">
+      <c r="E57" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iris_Marion_Young" title=" Wikipedia"&gt;Iris Marion YOUNG&lt;/a&gt; était une philosophe politique américaine majeure, figure centrale du féminisme contemporain et de la théorie de la justice. Professeure à l'Université de Chicago, elle articule phénoménologie existentialiste, marxisme, théorie critique et postmodernisme pour repenser l'oppression, la domination et la démocratie au-delà des approches universalistes traditionnelles. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est sa théorie des &lt;a href="https://www.youtube.com/watch?v=KyOut8zqJRI" title="les cinq visages de l’oppression par Eliot Goodine"&gt; cinq visages de l'oppression,&lt;/a&gt;  qu'elle développe dans Justice and the Politics of Difference (1990) ou elle développe également une,&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2018_num_116_4_8681" title="le féminisme phénoménologique par persée"&gt; phénoménologie féministe &lt;/a&gt; du corps, notamment dans son essai célèbre « Throwing Like a Girl » (1980). Elle y décrit comment les femmes vivent leur corps comme limité, fragmenté et constamment surveillé, ce qui produit une « immanence » sociale qui entrave leur capacité d'action et d'autodétermination. Le corps n'est pas seulement biologique mais politique, façonné par les normes sociales et les rapports de pouvoir. &lt;/p&gt; &lt;p&gt; Elle défend une conception de la justice fondée sur l'inclusion différenciée plutôt que sur l'universalisme abstrait. Pour Young, une société juste doit reconnaître les différences de groupe (genre, race, classe, sexualité) et créer des espaces où chacun puisse participer à la vie démocratique sans être forcé d'abandonner son identité particulière. Elle propose aussi le concept de responsabilité sociale diffuse, selon lequel tous les membres d'une société sont responsables des injustice structurelles, pas seulement les auteurs directs. &lt;/p&gt; &lt;p&gt; Elle évite tout essentialisme en conceptualisant « les femmes » comme un groupe social sériel, au sens de Sartre : un groupe dont les membres ne partagent pas une essence commune mais sont reliés par des conditions sociales similaires et des rapports de pouvoir. Cette approche permet un féminisme pluriel, Alliant diverses luttes (racisme, homophobie, validisme, écologie) dans des coalitions contre les rapports de domination. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G57" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H57" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="J57" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="K57" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="L57" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N56" s="1" t="s">
+      <c r="N57" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
+    <row r="58" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="n">
         <v>1952</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B58" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bell_hooks"  title=" Wikipedia"&gt;Bell HOOKS&lt;/a&gt;, de son vrai nom Gloria Jean Watkins, est une autrice, professeure et militante féministe afro-américaine. Née dans le Kentucky, dans le Sud ségrégationniste, elle prit le nom de son arrière-grand-mère, qu'elle écrivait en minuscules pour que l'attention se porte sur ses idées plutôt que sur sa personne.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ne suis-je pas une femme ?&lt;/em&gt; (1981), elle montre que les femmes noires ont été oubliées à la fois par le mouvement féministe, dominé par des femmes blanches de classe moyenne, et par le mouvement pour les droits civiques, dominé par des hommes. Elle  &lt;a href="https://www.youtube.com/watch?v=pCwMdHBSQgM" title=" bell hooks, un féminisme anticapitaliste et intersectionnel par META "&gt;développe l'idée &lt;/a&gt; que le sexisme, le racisme et l'exploitation économique forment un même système de domination, qu'elle appelle le « patriarcat capitaliste suprémaciste blanc ».&lt;/p&gt; &lt;p&gt;Ses idées ont profondément influencé ce que l'on appelle aujourd'hui l'intersectionnalité, c'est-à-dire l'étude de la manière dont différentes formes de discrimination se croisent et se renforcent. Elle écrivait dans un style simple et direct, refusant le jargon universitaire, pour que ses livres soient lus au-delà des cercles savants. Elle a aussi consacré plusieurs ouvrages à l'amour, qu'elle considérait comme une force politique capable de transformer la société.&lt;/p&gt; &lt;p&gt;Elle a écrit une quarantaine de livres, sur le féminisme, l'amour, les médias, la culture populaire et l'éducation. Dans &lt;em&gt;Apprendre à transgresser&lt;/em&gt; (1994), inspirée par Paulo Freire, elle défend une pédagogie de la liberté où l'enseignement devient une pratique d'émancipation. Pour elle, le féminisme n'est pas une guerre contre les hommes mais un mouvement pour mettre fin à toute forme de domination, porté par une « éthique de l'amour ».&lt;/p&gt;    &lt;audio controls title="Lire bell hooks aujourd’hui par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23875-15.11.2023-ITEMA_23552434-2023C49162S0319-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
 </t>
         </is>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F58" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G58" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H58" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="I57" s="1"/>
-      <c r="J57" s="2" t="s">
+      <c r="I58" s="1"/>
+      <c r="J58" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K57" s="1" t="inlineStr">
+      <c r="K58" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Féminisme ; Wokisme</t>
         </is>
       </c>
-      <c r="L57" s="2" t="s">
+      <c r="L58" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="M58" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="N57" s="1" t="s">
+      <c r="N58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O57" s="1" t="n">
+      <c r="O58" s="1" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0">
+    <row r="59" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0">
         <v>1535</v>
       </c>
-      <c r="B58" s="0" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1616</t>
         </is>
       </c>
-      <c r="C58" s="0" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">vers 1535 – vers 1616</t>
         </is>
       </c>
-      <c r="D58" s="0" t="inlineStr">
+      <c r="D59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Felipe GUAMÁN POMA de Ayala</t>
         </is>
       </c>
-      <c r="E58" s="0" t="inlineStr">
+      <c r="E59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Felipe_Guam%C3%A1n_Poma_de_Ayala" title=" Wikipedia"&gt;Felipe GUAMÁN POMA de Ayala&lt;/a&gt; est un noble andin de langue quechua, auteur de l’un des documents les plus extraordinaires de l’époque coloniale. Né dans la province de Lucanas, au Pérou, peu après la conquête espagnole, il descend par sa mère d’une lignée liée aux souverains de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_inca" title=" Wikipedia"&gt;Empire inca&lt;/a&gt;. Élevé parmi les Espagnols, il apprend leur langue, se fait chrétien et travaille comme interprète auprès d’un prêtre chargé d’extirper les « idolâtries », puis auprès de juges de Huamanga, avant d’être dépouillé de ses terres et banni vers 1600.&lt;/p&gt; &lt;p&gt;Il parcourt alors les Andes pendant des années et rédige, vers 1615, une lettre de près de 1 200 pages adressée au roi d’Espagne Philippe III : la &lt;em&gt;Nouvelle Chronique et bon gouvernement&lt;/em&gt;. Ses quelque 400 dessins à la plume racontent l’histoire des Incas, le calendrier, les travaux des champs, puis les abus des colons : prêtres, corregidors et propriétaires qui exploitent, volent et maltraitent les Indiens. Il y décrit un « monde à l’envers » (&lt;em&gt;mundo al revés&lt;/em&gt;), où l’ordre juste a été renversé par la conquête.&lt;/p&gt; &lt;p&gt;Il ne réclame pas le départ des Espagnols, mais un « bon gouvernement » : que les Andins se gouvernent eux-mêmes sous l’autorité lointaine du roi, et que les colons qui abusent soient chassés des villages. Il défend aussi la valeur de la civilisation andine, qui connaissait selon lui la justice et un ordre moral bien avant l’arrivée des Européens. Le manuscrit, qui n’atteignit sans doute jamais le roi, dormit pendant trois siècles avant d’être découvert en 1908 à la Bibliothèque royale de Copenhague. Il est aujourd’hui une source majeure sur le monde andin et l’une des premières critiques de la colonisation écrites par un colonisé.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F58" s="0"/>
-      <c r="G58" s="0"/>
-      <c r="H58" s="0" t="inlineStr">
+      <c r="F59" s="0"/>
+      <c r="G59" s="0"/>
+      <c r="H59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/guamanpoma-mini.webp</t>
         </is>
       </c>
-      <c r="I58" s="0"/>
-      <c r="J58" s="0" t="inlineStr">
+      <c r="I59" s="0"/>
+      <c r="J59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
-      <c r="K58" s="0" t="inlineStr">
+      <c r="K59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Anticolonialisme</t>
         </is>
       </c>
-      <c r="L58" s="0" t="inlineStr">
+      <c r="L59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">chroniqueur andin, auteur d’une immense lettre illustrée au roi d’Espagne dénonçant la colonisation du Pérou.</t>
         </is>
       </c>
-      <c r="M58" s="0"/>
-      <c r="N58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="O58" s="1">
-        <v>2</v>
-      </c>
-      <c r="P58" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Péruvienne</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1">
-        <v>1853</v>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1895</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1853 – 1895</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">José MARTÍ</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Mart%C3%AD" title=" Wikipedia"&gt;José MARTÍ&lt;/a&gt; est le grand penseur de l’indépendance cubaine et l’une des voix majeures de l’Amérique latine. Né à La Havane de parents espagnols, il est arrêté à seize ans pour ses idées indépendantistes et condamné aux travaux forcés dans une carrière, avant d’être déporté en Espagne, où il étudie le droit et la philosophie à Saragosse. Il vit ensuite au Mexique, au Guatemala et au Venezuela, puis s’installe en 1881 à New York, où il passe près de quinze ans comme journaliste, diplomate et organisateur de l’exil cubain. Il y écrit, pour de grands journaux d’Amérique latine, des chroniques sur la vie nord-américaine.&lt;/p&gt; &lt;p&gt;Dans son essai &lt;em&gt;Notre Amérique&lt;/em&gt; (1891), il appelle les nations latino-américaines à se penser à partir de leur propre réalité, métisse, indienne, noire et paysanne, plutôt qu’en copiant l’Europe ou les États-Unis : « Le gouvernement doit naître du pays. » Il y affirme aussi : « Il n’y a pas de haine des races, parce qu’il n’y a pas de races. » Observateur lucide de la puissance nord-américaine, il met en garde contre les ambitions des États-Unis sur Cuba et sur tout le continent.&lt;/p&gt; &lt;p&gt;Poète novateur, l’un des fondateurs du modernisme hispanique, il écrit les &lt;em&gt;Vers simples&lt;/em&gt; (1891), dont certains forment les paroles de la célèbre chanson &lt;em&gt;Guantanamera&lt;/em&gt;, et une revue pour les enfants, &lt;em&gt;L’Âge d’or&lt;/em&gt;. En 1892, il fonde le Parti révolutionnaire cubain et prépare la &lt;a href="https://fr.wikipedia.org/wiki/Guerre_d%27ind%C3%A9pendance_cubaine" title=" Wikipedia"&gt;guerre d’indépendance&lt;/a&gt;. Débarqué à Cuba avec les insurgés, il est tué au combat à Dos Ríos le 19 mai 1895. Il est considéré à Cuba comme le héros national et « l’Apôtre » de l’indépendance.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/marti-mini.webp</t>
-        </is>
-      </c>
-      <c r="I59" s="1"/>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">politique ; esthetique</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">poète et penseur de l’indépendance cubaine, auteur de « Notre Amérique », héros national de Cuba.</t>
-        </is>
-      </c>
+      <c r="M59" s="0"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
@@ -4762,54 +4771,55 @@
       <c r="O59" s="1">
         <v>2</v>
       </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cubaine</t>
+      <c r="P59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>
     <row r="60" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1">
-        <v>1921</v>
+        <v>1853</v>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1997</t>
+          <t xml:space="preserve">1895</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921 – 1997</t>
+          <t xml:space="preserve">1853 – 1895</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paulo FREIRE</t>
+          <t xml:space="preserve">José MARTÍ</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paulo_Freire" title=" Wikipedia"&gt;Paulo FREIRE&lt;/a&gt; est un pédagogue et philosophe brésilien, l’un des penseurs de l’éducation les plus lus au monde. Né à Recife, dans le Nordeste, il connaît la faim pendant la crise des années 1930, ce qui le marque pour toute sa vie. Formé au droit et à la philosophie, lecteur de Marx comme des penseurs chrétiens, il se consacre à l’&lt;a href="https://fr.wikipedia.org/wiki/Alphab%C3%A9tisation" title=" Wikipedia"&gt;alphabétisation&lt;/a&gt; des adultes pauvres. En 1963, à Angicos, sa méthode permet à 300 travailleurs agricoles d’apprendre à lire et à écrire en une quarantaine d’heures.&lt;/p&gt; &lt;p&gt;Sa méthode part des « mots générateurs » tirés de la vie des apprenants, comme la brique, la terre ou le salaire, et fait de la lecture une prise de conscience : apprendre à lire le mot, c’est apprendre à lire le monde. Après le coup d’État militaire de 1964, il est emprisonné puis contraint à un exil de seize ans. Au Chili, il écrit &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_des_opprim%C3%A9s" title=" Wikipedia"&gt;&lt;em&gt;Pédagogie des opprimés&lt;/em&gt;&lt;/a&gt; (1968), où il critique l’éducation « bancaire », qui dépose des savoirs dans des élèves passifs comme on remplit un coffre, et lui oppose une éducation par le dialogue, où maître et élèves cherchent ensemble.&lt;/p&gt; &lt;p&gt;« Personne n’éduque autrui, personne ne s’éduque seul, les hommes s’éduquent ensemble par l’intermédiaire du monde. » L’éducation n’est jamais neutre : elle maintient l’oppression ou aide les opprimés à s’en libérer, sans devenir à leur tour oppresseurs. Rentré au Brésil en 1980, il dirige l’éducation de la ville de São Paulo. Son œuvre est à l’origine de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_critique" title=" Wikipedia"&gt;pédagogie critique&lt;/a&gt;, et il a été proclamé en 2012 patron de l’éducation brésilienne.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Mart%C3%AD" title=" Wikipedia"&gt;José MARTÍ&lt;/a&gt; est le grand penseur de l’indépendance cubaine et l’une des voix majeures de l’Amérique latine. Né à La Havane de parents espagnols, il est arrêté à seize ans pour ses idées indépendantistes et condamné aux travaux forcés dans une carrière, avant d’être déporté en Espagne, où il étudie le droit et la philosophie à Saragosse. Il vit ensuite au Mexique, au Guatemala et au Venezuela, puis s’installe en 1881 à New York, où il passe près de quinze ans comme journaliste, diplomate et organisateur de l’exil cubain. Il y écrit, pour de grands journaux d’Amérique latine, des chroniques sur la vie nord-américaine.&lt;/p&gt; &lt;p&gt;Dans son essai &lt;em&gt;Notre Amérique&lt;/em&gt; (1891), il appelle les nations latino-américaines à se penser à partir de leur propre réalité, métisse, indienne, noire et paysanne, plutôt qu’en copiant l’Europe ou les États-Unis : « Le gouvernement doit naître du pays. » Il y affirme aussi : « Il n’y a pas de haine des races, parce qu’il n’y a pas de races. » Observateur lucide de la puissance nord-américaine, il met en garde contre les ambitions des États-Unis sur Cuba et sur tout le continent.&lt;/p&gt; &lt;p&gt;Poète novateur, l’un des fondateurs du modernisme hispanique, il écrit les &lt;em&gt;Vers simples&lt;/em&gt; (1891), dont certains forment les paroles de la célèbre chanson &lt;em&gt;Guantanamera&lt;/em&gt;, et une revue pour les enfants, &lt;em&gt;L’Âge d’or&lt;/em&gt;. En 1892, il fonde le Parti révolutionnaire cubain et prépare la &lt;a href="https://fr.wikipedia.org/wiki/Guerre_d%27ind%C3%A9pendance_cubaine" title=" Wikipedia"&gt;guerre d’indépendance&lt;/a&gt;. Débarqué à Cuba avec les insurgés, il est tué au combat à Dos Ríos le 19 mai 1895. Il est considéré à Cuba comme le héros national et « l’Apôtre » de l’indépendance.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/freire-mini.webp</t>
-        </is>
-      </c>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/marti-mini.webp</t>
+        </is>
+      </c>
+      <c r="I60" s="1"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">politique ; esthetique</t>
         </is>
       </c>
       <c r="K60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Marxisme ; Théologie de la libération</t>
+          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pédagogue brésilien, auteur de Pédagogie des opprimés, penseur de l’éducation comme pratique de la liberté.</t>
+          <t xml:space="preserve">poète et penseur de l’indépendance cubaine, auteur de « Notre Amérique », héros national de Cuba.</t>
         </is>
       </c>
       <c r="N60" s="1" t="inlineStr">
@@ -4818,56 +4828,56 @@
         </is>
       </c>
       <c r="O60" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brésilienne</t>
+          <t xml:space="preserve">Cubaine</t>
         </is>
       </c>
     </row>
     <row r="61" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1">
-        <v>1882</v>
+        <v>1921</v>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">1997</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882 – 1959</t>
+          <t xml:space="preserve">1921 – 1997</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">José VASCONCELOS</t>
+          <t xml:space="preserve">Paulo FREIRE</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Vasconcelos" title=" Wikipedia"&gt;José VASCONCELOS&lt;/a&gt; est un philosophe, écrivain et homme politique mexicain, l’un des grands éducateurs de l’Amérique latine. Né à Oaxaca, avocat, il fonde en 1909 avec Antonio Caso et Alfonso Reyes l’Ateneo de la Juventud, cercle de jeunes intellectuels qui rejette le positivisme officiel du régime de Porfirio Díaz. Il prend part à la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_mexicaine" title=" Wikipedia"&gt;révolution mexicaine&lt;/a&gt; aux côtés de Francisco Madero. Recteur de l’université nationale en 1920, il lui donne sa devise, toujours en usage : « Par ma race parlera l’esprit. »&lt;/p&gt; &lt;p&gt;Ministre de l’Éducation de 1921 à 1924, il mène une véritable croisade pour instruire le peuple : écoles rurales, missions culturelles dans les villages, bibliothèques, éditions populaires des grands classiques. Il commande aussi aux peintres &lt;a href="https://fr.wikipedia.org/wiki/Diego_Rivera" title=" Wikipedia"&gt;Diego Rivera&lt;/a&gt; et José Clemente Orozco les fresques murales qui racontent l’histoire du Mexique sur les murs des bâtiments publics. Il est surnommé le « maître de la jeunesse d’Amérique ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Race cosmique&lt;/em&gt; (1925), il prophétise que l’Amérique latine, terre de tous les mélanges, verra naître une « cinquième race », synthèse de toutes les autres, porteuse d’une civilisation de l’amour et de la beauté. Sa philosophie, un « monisme esthétique », voit dans l’émotion esthétique la forme la plus haute de connaissance. Battu en 1929 dans une élection présidentielle qu’il juge truquée, il s’exile, puis évolue vers un conservatisme catholique, au point de manifester en 1940 des sympathies pour l’Allemagne nazie. Il meurt à Mexico en 1959.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paulo_Freire" title=" Wikipedia"&gt;Paulo FREIRE&lt;/a&gt; est un pédagogue et philosophe brésilien, l’un des penseurs de l’éducation les plus lus au monde. Né à Recife, dans le Nordeste, il connaît la faim pendant la crise des années 1930, ce qui le marque pour toute sa vie. Formé au droit et à la philosophie, lecteur de Marx comme des penseurs chrétiens, il se consacre à l’&lt;a href="https://fr.wikipedia.org/wiki/Alphab%C3%A9tisation" title=" Wikipedia"&gt;alphabétisation&lt;/a&gt; des adultes pauvres. En 1963, à Angicos, sa méthode permet à 300 travailleurs agricoles d’apprendre à lire et à écrire en une quarantaine d’heures.&lt;/p&gt; &lt;p&gt;Sa méthode part des « mots générateurs » tirés de la vie des apprenants, comme la brique, la terre ou le salaire, et fait de la lecture une prise de conscience : apprendre à lire le mot, c’est apprendre à lire le monde. Après le coup d’État militaire de 1964, il est emprisonné puis contraint à un exil de seize ans. Au Chili, il écrit &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_des_opprim%C3%A9s" title=" Wikipedia"&gt;&lt;em&gt;Pédagogie des opprimés&lt;/em&gt;&lt;/a&gt; (1968), où il critique l’éducation « bancaire », qui dépose des savoirs dans des élèves passifs comme on remplit un coffre, et lui oppose une éducation par le dialogue, où maître et élèves cherchent ensemble.&lt;/p&gt; &lt;p&gt;« Personne n’éduque autrui, personne ne s’éduque seul, les hommes s’éduquent ensemble par l’intermédiaire du monde. » L’éducation n’est jamais neutre : elle maintient l’oppression ou aide les opprimés à s’en libérer, sans devenir à leur tour oppresseurs. Rentré au Brésil en 1980, il dirige l’éducation de la ville de São Paulo. Son œuvre est à l’origine de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_critique" title=" Wikipedia"&gt;pédagogie critique&lt;/a&gt;, et il a été proclamé en 2012 patron de l’éducation brésilienne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/vasconcelos-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/freire-mini.webp</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; politique</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="K61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monisme ; Spiritualisme</t>
+          <t xml:space="preserve">Humanisme ; Marxisme ; Théologie de la libération</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et ministre mexicain de l’Éducation, auteur de La Race cosmique, penseur du métissage.</t>
+          <t xml:space="preserve">pédagogue brésilien, auteur de Pédagogie des opprimés, penseur de l’éducation comme pratique de la liberté.</t>
         </is>
       </c>
       <c r="N61" s="1" t="inlineStr">
@@ -4876,66 +4886,61 @@
         </is>
       </c>
       <c r="O61" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mexicaine</t>
+          <t xml:space="preserve">Brésilienne</t>
         </is>
       </c>
     </row>
     <row r="62" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1">
-        <v>1907</v>
+        <v>1882</v>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1972</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1907 – 1972</t>
+          <t xml:space="preserve">1882 – 1959</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abraham Joshua HESCHEL</t>
+          <t xml:space="preserve">José VASCONCELOS</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abraham_Joshua_Heschel" title=" Wikipedia"&gt;Abraham Joshua HESCHEL&lt;/a&gt; est un rabbin, théologien et philosophe juif, l’une des grandes voix religieuses du XXe siècle. Né à Varsovie dans une illustre famille du &lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;hassidisme&lt;/a&gt;, il étudie la philosophie à Berlin, où il soutient une thèse sur les prophètes d’Israël. Expulsé d’Allemagne vers la Pologne en 1938, il parvient à quitter Varsovie quelques semaines avant l’invasion allemande et gagne Londres, puis les États-Unis. Sa mère et ses sœurs sont assassinées pendant la Shoah. Il enseigne à partir de 1946 au Séminaire théologique juif de New York.&lt;/p&gt; &lt;p&gt;Pour Heschel, la religion commence par l’« étonnement radical » devant le monde, qui précède toute réflexion. Contre l’idée d’un Dieu impassible des philosophes, il parle du « pathos divin » : le Dieu des prophètes est concerné par le sort des hommes et souffre de l’injustice. La question n’est pas seulement de savoir si l’homme cherche Dieu, mais de comprendre que &lt;em&gt;Dieu est en quête de l’homme&lt;/em&gt;, titre de son livre de 1955. Dans &lt;em&gt;Les Bâtisseurs du temps&lt;/em&gt; (1951), il présente le &lt;a href="https://fr.wikipedia.org/wiki/Shabbat" title=" Wikipedia"&gt;shabbat&lt;/a&gt; comme « une cathédrale dans le temps » : le judaïsme sanctifie des moments plutôt que des lieux. Il consacre aussi un grand livre aux prophètes, témoins de la passion de Dieu pour la justice.&lt;/p&gt; &lt;p&gt;Sa foi le conduit à l’action. En 1965, il marche de Selma à Montgomery aux côtés de Martin Luther King et dira : « J’avais l’impression que mes jambes priaient. » Il s’oppose à la guerre du Vietnam et contribue au dialogue entre juifs et chrétiens lors du concile Vatican II. Il meurt à New York en 1972.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Vasconcelos" title=" Wikipedia"&gt;José VASCONCELOS&lt;/a&gt; est un philosophe, écrivain et homme politique mexicain, l’un des grands éducateurs de l’Amérique latine. Né à Oaxaca, avocat, il fonde en 1909 avec Antonio Caso et Alfonso Reyes l’Ateneo de la Juventud, cercle de jeunes intellectuels qui rejette le positivisme officiel du régime de Porfirio Díaz. Il prend part à la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_mexicaine" title=" Wikipedia"&gt;révolution mexicaine&lt;/a&gt; aux côtés de Francisco Madero. Recteur de l’université nationale en 1920, il lui donne sa devise, toujours en usage : « Par ma race parlera l’esprit. »&lt;/p&gt; &lt;p&gt;Ministre de l’Éducation de 1921 à 1924, il mène une véritable croisade pour instruire le peuple : écoles rurales, missions culturelles dans les villages, bibliothèques, éditions populaires des grands classiques. Il commande aussi aux peintres &lt;a href="https://fr.wikipedia.org/wiki/Diego_Rivera" title=" Wikipedia"&gt;Diego Rivera&lt;/a&gt; et José Clemente Orozco les fresques murales qui racontent l’histoire du Mexique sur les murs des bâtiments publics. Il est surnommé le « maître de la jeunesse d’Amérique ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Race cosmique&lt;/em&gt; (1925), il prophétise que l’Amérique latine, terre de tous les mélanges, verra naître une « cinquième race », synthèse de toutes les autres, porteuse d’une civilisation de l’amour et de la beauté. Sa philosophie, un « monisme esthétique », voit dans l’émotion esthétique la forme la plus haute de connaissance. Battu en 1929 dans une élection présidentielle qu’il juge truquée, il s’exile, puis évolue vers un conservatisme catholique, au point de manifester en 1940 des sympathies pour l’Allemagne nazie. Il meurt à Mexico en 1959.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/heschel-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vasconcelos-mini.webp</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; ethique</t>
+          <t xml:space="preserve">esthetique ; politique</t>
         </is>
       </c>
       <c r="K62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Existentialisme ; Mysticisme ; Hassidisme</t>
+          <t xml:space="preserve">Monisme ; Spiritualisme</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rabbin et philosophe juif, penseur du « pathos divin » et du shabbat, militant des droits civiques.</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">philosophe et ministre mexicain de l’Éducation, auteur de La Race cosmique, penseur du métissage.</t>
         </is>
       </c>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">occident</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="O62" s="1">
@@ -4943,57 +4948,62 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Américaine</t>
+          <t xml:space="preserve">Mexicaine</t>
         </is>
       </c>
     </row>
     <row r="63" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1">
-        <v>1914</v>
+        <v>1907</v>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998</t>
+          <t xml:space="preserve">1972</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914 – 1998</t>
+          <t xml:space="preserve">1907 – 1972</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octavio PAZ</t>
+          <t xml:space="preserve">Abraham Joshua HESCHEL</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Octavio_Paz" title=" Wikipedia"&gt;Octavio PAZ&lt;/a&gt; est un poète, essayiste et diplomate mexicain, prix Nobel de littérature en 1990. Né à Mexico dans une famille marquée par la révolution, son père ayant été le représentant d’Emiliano Zapata aux États-Unis, il soutient les républicains pendant la guerre d’Espagne, puis rompt avec le communisme après l’assassinat de Trotski. Diplomate à Paris après la guerre, il y fréquente les surréalistes et André Breton.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Labyrinthe_de_la_solitude" title=" Wikipedia"&gt;&lt;em&gt;Le Labyrinthe de la solitude&lt;/em&gt;&lt;/a&gt; (1950), il interroge l’identité mexicaine : derrière les masques de la politesse et la violence des fêtes se cache une solitude née de l’histoire, celle d’un peuple issu de la conquête, qui a renié à la fois son passé indien et son passé espagnol. Il y évoque la figure de la &lt;a href="https://fr.wikipedia.org/wiki/La_Malinche" title=" Wikipedia"&gt;Malinche&lt;/a&gt;, compagne indienne de Cortés, symbole ambigu de l’origine métisse du pays. Mais cette solitude est aussi celle de l’homme moderne, et la poésie, l’amour et la fête sont des moyens de la dépasser. Dans &lt;em&gt;L’Arc et la Lyre&lt;/em&gt; (1956), il fait de la poésie une expérience de communion qui révèle l’homme à lui-même.&lt;/p&gt; &lt;p&gt;Ambassadeur du Mexique en Inde de 1962 à 1968, il découvre les philosophies et l’art de l’Orient, qui nourrissent sa poésie. Il démissionne après le &lt;a href="https://fr.wikipedia.org/wiki/Massacre_de_Tlatelolco" title=" Wikipedia"&gt;massacre de Tlatelolco&lt;/a&gt;, où des centaines d’étudiants sont tués par l’armée en 1968. Critique des totalitarismes de droite comme de gauche, il fonde la revue &lt;em&gt;Vuelta&lt;/em&gt; et consacre un grand livre à la poétesse et penseuse Juana Inés de la Cruz. Il meurt à Mexico en 1998, à quatre-vingt-quatre ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abraham_Joshua_Heschel" title=" Wikipedia"&gt;Abraham Joshua HESCHEL&lt;/a&gt; est un rabbin, théologien et philosophe juif, l’une des grandes voix religieuses du XXe siècle. Né à Varsovie dans une illustre famille du &lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;hassidisme&lt;/a&gt;, il étudie la philosophie à Berlin, où il soutient une thèse sur les prophètes d’Israël. Expulsé d’Allemagne vers la Pologne en 1938, il parvient à quitter Varsovie quelques semaines avant l’invasion allemande et gagne Londres, puis les États-Unis. Sa mère et ses sœurs sont assassinées pendant la Shoah. Il enseigne à partir de 1946 au Séminaire théologique juif de New York.&lt;/p&gt; &lt;p&gt;Pour Heschel, la religion commence par l’« étonnement radical » devant le monde, qui précède toute réflexion. Contre l’idée d’un Dieu impassible des philosophes, il parle du « pathos divin » : le Dieu des prophètes est concerné par le sort des hommes et souffre de l’injustice. La question n’est pas seulement de savoir si l’homme cherche Dieu, mais de comprendre que &lt;em&gt;Dieu est en quête de l’homme&lt;/em&gt;, titre de son livre de 1955. Dans &lt;em&gt;Les Bâtisseurs du temps&lt;/em&gt; (1951), il présente le &lt;a href="https://fr.wikipedia.org/wiki/Shabbat" title=" Wikipedia"&gt;shabbat&lt;/a&gt; comme « une cathédrale dans le temps » : le judaïsme sanctifie des moments plutôt que des lieux. Il consacre aussi un grand livre aux prophètes, témoins de la passion de Dieu pour la justice.&lt;/p&gt; &lt;p&gt;Sa foi le conduit à l’action. En 1965, il marche de Selma à Montgomery aux côtés de Martin Luther King et dira : « J’avais l’impression que mes jambes priaient. » Il s’oppose à la guerre du Vietnam et contribue au dialogue entre juifs et chrétiens lors du concile Vatican II. Il meurt à New York en 1972.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/paz-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/heschel-mini.webp</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; politique</t>
+          <t xml:space="preserve">spiritualite ; ethique</t>
         </is>
       </c>
       <c r="K63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme</t>
+          <t xml:space="preserve">Existentialisme ; Mysticisme ; Hassidisme</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">poète et essayiste mexicain, prix Nobel 1990, auteur du Labyrinthe de la solitude.</t>
+          <t xml:space="preserve">rabbin et philosophe juif, penseur du « pathos divin » et du shabbat, militant des droits civiques.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
       <c r="O63" s="1">
@@ -5001,52 +5011,52 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mexicaine</t>
+          <t xml:space="preserve">Américaine</t>
         </is>
       </c>
     </row>
     <row r="64" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1">
-        <v>1783</v>
+        <v>1914</v>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830</t>
+          <t xml:space="preserve">1998</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1783 – 1830</t>
+          <t xml:space="preserve">1914 – 1998</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simón BOLÍVAR</t>
+          <t xml:space="preserve">Octavio PAZ</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sim%C3%B3n_Bol%C3%ADvar" title=" Wikipedia"&gt;Simón BOLÍVAR&lt;/a&gt; est le chef militaire et politique des &lt;a href="https://fr.wikipedia.org/wiki/Guerres_d%27ind%C3%A9pendance_hispano-am%C3%A9ricaines" title=" Wikipedia"&gt;guerres d’indépendance&lt;/a&gt; de l’Amérique du Sud, surnommé le Libertador. Né à Caracas dans une riche famille créole, orphelin jeune, il est formé par son précepteur Simón Rodríguez, disciple de Rousseau, et découvre en Europe les idées des Lumières. À Rome, en 1805, il fait le serment de libérer son continent de la domination espagnole.&lt;/p&gt; &lt;p&gt;De 1813 à 1824, il mène une guerre longue et cruelle qui libère le Venezuela, la Colombie, l’Équateur, le Pérou et la Bolivie, qui porte son nom. Mais il est aussi un penseur politique. Dans sa &lt;a href="https://fr.wikipedia.org/wiki/Lettre_de_Jama%C3%AFque" title=" Wikipedia"&gt;&lt;em&gt;Lettre de Jamaïque&lt;/em&gt;&lt;/a&gt; (1815), écrite en exil, il analyse la situation de l’Amérique espagnole : un peuple ni européen ni indien, maintenu dans l’ignorance et l’inexpérience politique par trois siècles de colonisation. Dans son discours d’Angostura (1819), il plaide pour une république adaptée aux réalités du pays plutôt que copiée sur l’Europe ou les États-Unis, et réclame l’abolition de l’esclavage. Il affranchit ses propres esclaves, sans parvenir à imposer partout l’abolition.&lt;/p&gt; &lt;p&gt;Il rêve d’unir les nouvelles nations en une grande confédération et réunit à cette fin le congrès de Panama en 1826. Mais la &lt;a href="https://fr.wikipedia.org/wiki/Grande_Colombie" title=" Wikipedia"&gt;Grande Colombie&lt;/a&gt; qu’il préside se défait sous l’effet des rivalités régionales, et son autoritarisme croissant lui vaut de nombreux ennemis. Malade et désabusé, il meurt en 1830 à Santa Marta en disant avoir « labouré la mer ». Son rêve d’unité latino-américaine reste une référence majeure du continent.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Octavio_Paz" title=" Wikipedia"&gt;Octavio PAZ&lt;/a&gt; est un poète, essayiste et diplomate mexicain, prix Nobel de littérature en 1990. Né à Mexico dans une famille marquée par la révolution, son père ayant été le représentant d’Emiliano Zapata aux États-Unis, il soutient les républicains pendant la guerre d’Espagne, puis rompt avec le communisme après l’assassinat de Trotski. Diplomate à Paris après la guerre, il y fréquente les surréalistes et André Breton.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Labyrinthe_de_la_solitude" title=" Wikipedia"&gt;&lt;em&gt;Le Labyrinthe de la solitude&lt;/em&gt;&lt;/a&gt; (1950), il interroge l’identité mexicaine : derrière les masques de la politesse et la violence des fêtes se cache une solitude née de l’histoire, celle d’un peuple issu de la conquête, qui a renié à la fois son passé indien et son passé espagnol. Il y évoque la figure de la &lt;a href="https://fr.wikipedia.org/wiki/La_Malinche" title=" Wikipedia"&gt;Malinche&lt;/a&gt;, compagne indienne de Cortés, symbole ambigu de l’origine métisse du pays. Mais cette solitude est aussi celle de l’homme moderne, et la poésie, l’amour et la fête sont des moyens de la dépasser. Dans &lt;em&gt;L’Arc et la Lyre&lt;/em&gt; (1956), il fait de la poésie une expérience de communion qui révèle l’homme à lui-même.&lt;/p&gt; &lt;p&gt;Ambassadeur du Mexique en Inde de 1962 à 1968, il découvre les philosophies et l’art de l’Orient, qui nourrissent sa poésie. Il démissionne après le &lt;a href="https://fr.wikipedia.org/wiki/Massacre_de_Tlatelolco" title=" Wikipedia"&gt;massacre de Tlatelolco&lt;/a&gt;, où des centaines d’étudiants sont tués par l’armée en 1968. Critique des totalitarismes de droite comme de gauche, il fonde la revue &lt;em&gt;Vuelta&lt;/em&gt; et consacre un grand livre à la poétesse et penseuse Juana Inés de la Cruz. Il meurt à Mexico en 1998, à quatre-vingt-quatre ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/bolivar-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/paz-mini.webp</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique</t>
+          <t xml:space="preserve">esthetique ; politique</t>
         </is>
       </c>
       <c r="K64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Républicanisme ; Libéralisme</t>
+          <t xml:space="preserve">Humanisme</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le Libertador, chef des indépendances sud-américaines et penseur de l’unité latino-américaine.</t>
+          <t xml:space="preserve">poète et essayiste mexicain, prix Nobel 1990, auteur du Labyrinthe de la solitude.</t>
         </is>
       </c>
       <c r="N64" s="1" t="inlineStr">
@@ -5059,7 +5069,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vénézuélienne</t>
+          <t xml:space="preserve">Mexicaine</t>
         </is>
       </c>
     </row>
@@ -5707,6 +5717,62 @@
       </c>
       <c r="O75" s="1"/>
       <c r="P75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1">
+        <v>1917</v>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2003</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1917 – 2003</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Donald DAVIDSON</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donald_Davidson" title=" Wikipedia"&gt;Donald DAVIDSON&lt;/a&gt; est un philosophe américain, l’un des plus influents de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; de la seconde moitié du XXe siècle. Né en 1917 à Springfield, dans le Massachusetts, il étudie à Harvard la littérature et les lettres classiques avant de se tourner vers la philosophie sous l’influence de Quine. Après avoir servi dans la marine pendant la guerre, il enseigne notamment à Stanford, à Princeton et à Berkeley.&lt;/p&gt; &lt;p&gt;Dans « Actions, raisons et causes » (1963), il soutient que nos raisons d’agir, nos désirs et nos croyances, sont aussi les causes de nos actions. Dans « Les événements mentaux » (1970), il défend le « monisme anomal » : chaque événement mental est un événement physique, mais il n’existe pas de lois strictes qui relient le mental au physique, car le mental obéit à d’autres principes, ceux de la rationalité. Il réconcilie ainsi le matérialisme avec l’autonomie de la pensée.&lt;/p&gt; &lt;p&gt;Sa théorie de l’« interprétation radicale » prolonge le &lt;a href="https://fr.wikipedia.org/wiki/Holisme" title=" Wikipedia"&gt;holisme&lt;/a&gt; de Quine : pour comprendre un locuteur dont on ignore tout de la langue, il faut lui attribuer en même temps des croyances et des significations, en supposant qu’il pense en grande partie comme nous. C’est le « principe de charité ». Le sens d’un mot dépend du sens de toute la langue, et nos croyances forment un réseau. Il en conclut, dans un article célèbre de 1974, que l’idée de « schèmes conceptuels » radicalement incommensurables n’a pas de sens. Il meurt à Berkeley en 2003.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/donalddavidson-mini.webp</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langage ; epistemologie ; metaphysique</t>
+        </is>
+      </c>
+      <c r="K76" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holisme ; Analytique</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe américain de l’action et du langage, auteur du « monisme anomal ».</t>
+        </is>
+      </c>
+      <c r="N76" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O76" s="1"/>
+      <c r="P76" t="inlineStr">
         <is>
           <t xml:space="preserve">Américaine</t>
         </is>
@@ -5720,42 +5786,42 @@
   <hyperlinks>
     <hyperlink ref="E5" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Andr%C3%A9s_Bello&quot;  title=&quot; Wikipedia&quot;&gt;Andrés BELLO&lt;/a&gt; était un philosophe vénézuélien  devenu une référence majeure au Chili, où il a exercé comme humaniste, juriste, poète et philosophe. Son importance tient moins à une “système” philosophique au sens strict qu’à une pensée de la culture, de l’éducation et du droit, très liée à la construction des jeunes États latino-américains.  &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=i6QyzreorMI&quot; title=&quot;andres bello par liceo augustosantelices par PipaProfe&quot;&gt;Sa philosophie &lt;/a&gt;  est d’abord marquée par l’idée que les sociétés ont besoin de cadres intellectuels solides pour se développer: l’éducation, la langue, les institutions et le droit. Il a ainsi défendu une vision exigeante de l’instruction publique, pensée comme un fondement de la vie civile et de la modernité politique. Il voyait dans la culture lettrée un instrument d’émancipation, mais aussi d’ordre et de stabilité. &lt;/p&gt; &lt;p&gt; Il a également joué un rôle décisif dans la codification du droit en Amérique latine, notamment avec ses travaux sur le droit international et plus largement sur la formation d’un ordre juridique propre au continent. Chez lui, la philosophie n’est pas séparée de l’action: elle sert à donner une forme durable à la nation, à la citoyenneté et à la vie collective. Cette orientation le rapproche d’un humanisme pratique, attentif aux institutions autant qu’aux idées. &lt;/p&gt; &lt;p&gt; Il  était un penseur de la construction culturelle et politique: il cherche à fonder des sociétés libres, mais aussi cultivées, disciplinées et juridiquement cohérentes. &lt;/p&gt; &#10;"/>
     <hyperlink ref="H5" r:id="rId2" display="https://www.laphilo.fr/pho/abello-mini.webp"/>
-    <hyperlink ref="E9" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_Sanders_Peirce&quot; title=&quot; Wikipedia&quot;&gt;Charles SANDERS PIERCE&lt;/a&gt;  était un philosophe, logicien, scientifique américain assez original, fondateur du  &lt;a href=&quot;https://www.youtube.com/watch?v=AGHmKg7wYf0&quot;  title=&quot;Pragmatisme  par robertus&quot;&gt;pragmatisme&lt;/a&gt; , père de la sémiotique moderne (théorie des signes) et un pionnier de la logique. Pourtant, en raison de  &lt;a href=&quot;https://laviedesidees.fr/Chevalier-Peirce-ou-l-invention-de-l-epistemologie&quot; style=&quot;color:#88A1E9&quot; title=&quot;les pepites de Charles s pierce par laviedesidees&quot;&gt;sa personnalité difficile&lt;/a&gt; et de ses idées avant-gardistes, il vécut en marge du monde académique, mourant dans la pauvreté et l'isolement. &lt;/p&gt; &lt;p&gt;  Il cherchait à identifier les catégories les plus fondamentales et universelles de la pensée et de l'être, qu'il nomma Phanéroscopie.Il en déduit trois, présentes dans tous les phénomènes. Elles sont la clé de voûte de tout le système peircien et sont indispensables pour comprendre sa sémiotique et  &lt;a href=&quot;https://hal.science/hal-02953592/document&quot;  title=&quot;Pragmatisme  par hal science&quot;&gt;son pragmatisme&lt;/a&gt;: &lt;/p&gt; &lt;p&gt; - Priméité (Firstness) : C'est la catégorie de la qualité pure, de la potentialité, de la sensation immédiate et brute, existant en elle-même sans référence à quoi que ce soit d'autre. C'est le &quot;sentiment de rouge&quot;, la qualité d'une odeur, la nouveauté d'une idée. C'est le domaine de la possibilité et de la liberté. &lt;/p&gt; &lt;p&gt; - Secondéité (Secondeity) : C'est la catégorie du fait brut, de l'action-réaction, de la résistance et de l'actualité. C'est le choc du &quot;ici et maintenant&quot;, la rencontre avec un autre qui s'impose à nous. Exemples : une collision, la sensation de résistance en poussant une porte, un conflit. C'est le domaine de l'existence et de la dualité. &lt;/p&gt; &lt;p&gt; - Tiercéité (Thirdness) : C'est la catégorie de la médiation, de la loi, de l'habitude, de la généralisation et de la signification. Elle fait le lien entre la Priméité (la qualité) et la Secondéité (le fait) en leur donnant un sens et une régularité. Exemples : une loi scientifique, un symbole linguistique, une tendance, une règle de conduite. C'est le domaine de la pensée, de la continuité et de l'intelligibilité. &lt;/p&gt; &lt;p&gt; Il propose une méthode pour clarifier le sens de nos idées, le Pragmaticisme: le sens d'un concept réside dans ses conséquences pratiques observables. Si deux idées ne produisent aucune différence pratique, elles signifient la même chose. C'est avant tout une méthode logique pour trancher les disputes métaphysiques stériles.&lt;/p&gt; &lt;p&gt; Sa contribution la plus novatrice et la plus influente est &lt;a href=&quot;https://www.persee.fr/doc/lgge_0458-726x_1980_num_14_58_1844&quot; title=&quot;La séméiotique de Charles S. Peirce  par Persée&quot;&gt;la Sémiotique&lt;/a&gt; . Pour lui, &quot;l'homme est un signe&quot; et toute pensée est un &lt;a href=&quot;https://www.youtube.com/watch?v=e1jrx1RlS00&quot; title=&quot;VOIR ET INTERPRÉTER LES SIGNES ! Introduction à la sémiologie CHARLES SANDERS PEIRCE  par Survivreauxscienceshumaines&quot;&gt;processus sémiotique&lt;/a&gt;. Il définit le signe non pas de manière dyadique mais triadique,  Il crée dans l'esprit de la  personne un signe plus développé, appelé l'interprétant. La relation signe-objet-interprétant est fondamentale. Sa classification concerne la relation du signe à son objet : &lt;/p&gt; &lt;dd&gt; - Icône: Le signe ressemble à son objet ou partage des qualités avec lui (une photographie, un diagramme) . &lt;/dd&gt; &lt;dd&gt; - Index: Le signe est physiquement connecté à son objet . la fumée (indice du feu), une girouette (indice de la direction du vent). &lt;/dd&gt; &lt;dd&gt; - Symbole: La relation entre le signe et l'objet est arbitraire et conventionnelle. Elle repose sur une règle ou une habitude sociale. (&quot;arbre&quot; n'a rien d'un arbre). &lt;/dd&gt; &lt;p&gt; Bien que mort dans la misère et méconnu de son vivant, son influence est immense aujourd'hui en philosophie, en sciences cognitives, en linguistique et en sociologie. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E13" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Alejandro_Korn&quot;  title=&quot; Wikipedia&quot;&gt;Alejendro KORN&lt;/a&gt; était un  philosophe, médecin et homme politique argentin considéré comme l’un des fondateurs de la philosophie argentine moderne. Après des études de médecine et une carrière de psychiatre, il se consacra à la philosophie et à l’enseignement, occupant des chaires à l’Université de Buenos Aires et à La Plata, où il contribua à insérer la philosophie dans la vie intellectuelle nationale. &lt;/p&gt; &lt;p&gt; Il  chercha à  &lt;a href=&quot;https://www.youtube.com/watch?v=Fc9frRYHyTU&quot; title=&quot;Alejandro Korn par filo errante&quot;&gt;dépasser le positivisme &lt;/a&gt; dominant en Argentine en affirmant la centralité de la liberté créatrice : pour lui la liberté n’est pas simple absence de contraintes mais un effort conscient de création et d’amélioration de soi et du monde, unissant dimensions économique, sociale et éthique. Il soutint que la philosophie doit partir de la conscience et de l’intuition, tout en reconnaissant la nécessité de la science; ainsi il proposa une synthèse où l’ordre objectif de la science et l’ordre subjectif de la liberté humaine sont intégrés sans se confondre. &lt;/p&gt; &lt;p&gt; En axiologie et théorie des valeurs, il développa une classification des valeurs (biologiques, sociales, culturelles) et une conception relativiste des évaluations historiques, tout en maintenant la possibilité d’objectivité dans les valeurs culturelles supérieures comme la vérité, la beauté et la sainteté; la valeur est pour lui la réponse active du sujet face aux faits de l’existence. Cette orientation le conduisit à défendre une éducation humaniste capable de former des citoyens autonomes, responsables et créateurs, idée qu’il mit en pratique à travers son engagement dans les réformes universitaires et la création d’espaces pour les humanités. &lt;/p&gt; &lt;p&gt; Il   &lt;a href=&quot;https://www.youtube.com/watch?v=-L16KuQgWxE&quot; title=&quot;alejandro korn par filosofia en red&quot;&gt;mêla pensée et action : &lt;/a&gt; il participa à la vie publique, défendit la dignité de la personne et la nécessité d’une culture nationale fondée sur la liberté et la responsabilité, opposant une philosophie de la personne à un positivisme strictement utilitariste; son influence se lit dans les transformations éducatives et institutionnelles argentines du début du XXe siècle. Ses œuvres principales incluent Influencias filosóficas en la evolución nacional, La libertad creadora, Esquema gnoseológico, El concepto de ciencia et Axiología, et son corpus continue d’être étudié comme pierre angulaire de la tradition philosophique argentine. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H13" r:id="rId5" display="https://www.laphilo.fr/pho/akorn-mini.webp"/>
-    <hyperlink ref="E14" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://pt.wikipedia.org/wiki/Raimundo_de_Farias_Brito&quot;  title=&quot; Wikipedia&quot;&gt;Farias BRITO&lt;/a&gt; était un  philosophe brésilien  connu pour avoir développé un spiritualisme philosophique qui a marqué la pensée brésilienne. Sa trajectoire intellectuelle passa par des études de droit et des activités publiques (magistrature, enseignement), avant d’occuper à Rio de Janeiro la chaire de logique du Colégio Pedro II, poste qu’il conserva jusqu’à sa mort, ce qui lui permit de diffuser largement ses idées. &lt;/p&gt; &lt;p&gt; Sur le plan doctrinal, il articula une critique du matérialisme et du positivisme en faveur d’un spiritualisme qui entendait le « esprit » comme la réalité première capable de sentir, connaître et agir; il proposa une métaphysique où la matière est dérivée ou dérivée de la réalité spirituelle. Sa pensée traversa deux grandes phases : d’abord un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Monisme_(spiritualit%C3%A9)&quot; title=&quot;monisme par wikipedia&quot;&gt;monisme panteïste &lt;/a&gt; (avec des accents d’immanence) visible dans certaines œuvres plus anciennes, puis une évolution vers un pluralisme théiste où Dieu apparaît comme cause première personnelle, rapprochement qui le conduisit vers une sensibilité plus nettement religieuse à la fin de sa vie. &lt;/p&gt; &lt;p&gt; Il situa la valeur morale dans la recherche de la vérité et dans l’amélioration intérieure de l’individu; il concevait la conscience comme le lieu décisif de la lutte entre les appels moraux et les instincts, et définissait la liberté comme la capacité de choisir entre conviction et convenance. Pour lui, l’action juste dépend de l’adéquation de l’intellect à la réalité (la vérité) et de la conversion intérieure du sujet, d’où découlent des exigences éducatives et morales importantes pour la société. &lt;/p&gt; &lt;p&gt; Politiquement, il se montra critique envers les conséquences du libéralisme, du démocratisme et des idéologies révolutionnaires qu’il jugeait responsables d’un affaiblissement des croyances traditionnelles et d’une montée du matérialisme social; il prônait au contraire une réforme sociale guidée par des principes moraux et une « grande idée » éthique plutôt que par les seuls intérêts matériels ou la lutte. Cette dimension conservatrice-morale de sa pensée s’articule à son rejet du positivisme excessif et à sa confiance dans la capacité de la philosophie et de l’éducation de corriger la crise culturelle de son époque. &lt;/p&gt; &lt;p&gt; Son œuvre, abondante et variée, comprend des titres sur la métaphysique, la logique, l’éthique et la philosophie de la science — parmi les plus cités figurent A Filosofia como Atividade Permanente do Espírito Humano, A Filosofia Moderna, A Base Física do Espírito et O Mundo Interior — et elle a laissé un héritage durable dans la culture intellectuelle brésilienne, étudiée encore aujourd’hui dans des travaux historiques et critiques. Les recherches contemporaines insistent sur son statut de penseur « pré-moderniste » du Brésil et sur l’originalité de sa tentative de construire une philosophie nationale qui conjugue métaphysique, morale et engagement public. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
-    <hyperlink ref="H14" r:id="rId7" display="https://www.laphilo.fr/pho/fbrito-mini.webp"/>
-    <hyperlink ref="E15" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Carlos_Vaz_Ferreira&quot;  title=&quot; Wikipedia&quot;&gt;Carlos VAS FERREIRA&lt;/a&gt; était un  philosophe uruguayen considéré comme l’une des figures majeures de la pensée hispano‑américaine au début du XXᵉ siècle. Issue d’une famille aux origines portugaise et uruguayenne, sa trajectoire intellectuelle s’inscrit dans un contexte de modernisation de l’Université et de reformulation des idées scientifiques et morales en Amérique du Sud. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=AmRpz8vCejs&quot; title=&quot;Vas Ferreira par Pablo Romero&quot;&gt;Sa philosophie &lt;/a&gt; se situe à la croisée du positivisme, du pragmatisme et de l’empirisme britannique, avec un respect marqué pour Herbert Spencer, John Stuart Mill, William James et Henri Bergson, sans jamais adopter intégralement leurs doctrines. Il critique la rigidité des systèmes logiques et métaphysiques classiques, estimant que le langage et la logique formelle imposent au réel une précision artificielle qui masque la complexité et la fluidité de l’expérience. &lt;/p&gt; &lt;p&gt; Il  développe l’idée d’une &lt;a href=&quot;https://www.youtube.com/watch?v=UeadgG1ud1g&quot; title=&quot;Vas Ferreira y su logica viva par Tribuna Constitucional&quot;&gt;« logique vivante », &lt;/a&gt; c’est‑à‑dire une logique ancrée dans la vie concrète, attentive aux degrés de probabilité et aux limites de nos certitudes plutôt qu’aux schémas abstraits. Pour lui, la raison doit rester souple et vigilante, proche de l’expérience et des données empiriques, afin de ne pas basculer dans des systèmes dogmatiques. &lt;/p&gt; &lt;p&gt; En épistémologie, il défend une vision modeste de la science : les sciences sont des outils puissants mais partiaux, incapables de saisir le tout de la réalité et toujours confrontées à des questions métaphysiques implicites. La philosophie, selon lui, doit clarifier ces présupposés, rappeler les limites symboliques de la science et contrer les « mauvaises métaphysiques » qui surgissent lorsque l’on ignore les questions fondamentales. &lt;/p&gt; &lt;p&gt; Sur le plan éthique et social, il s’intéresse à la liberté, à la morale des intellectuels, aux problèmes sociaux et aux questions de propriété ou de féminisme. Il met en avant une morale sensible à la complexité des situations, où les principes comportent des exceptions et où le choix moral implique souvent des compromis entre des biens et des maux partiels ; tout en affirmant qu’il existe un progrès moral dans l’histoire humaine, marqué par l’élargissement des idéaux et la résistance accrue au mal. &lt;/p&gt; &#10;&#10;&#10;&#10;&#10;"/>
-    <hyperlink ref="H15" r:id="rId9" display="https://www.laphilo.fr/pho/cvferreira-mini.webp"/>
-    <hyperlink ref="E17" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Antonio_Caso&quot;   title=&quot; Wikipedia&quot;&gt;Antonio CASO&lt;/a&gt; était un philosophe mexicain connu pour sa critique du positivisme et pour un  &lt;a href=&quot;https://www.youtube.com/watch?v=YlEoF2CNNxA&quot; title=&quot;&quot;Antonio Caso Andrade - Filósofo y Sociológico Mexicano - Una Mirada Profunda a sus Contribuciones&quot; par Biografías de Filósofos&quot;&gt;humanisme spiritualiste &lt;/a&gt; influent dans la culture intellectuelle mexicaine. Il cofonde en 1910, avec José Vasconcelos et d’autres, l’Ateneo de la Juventud, cercle intellectuel qui s’oppose au positivisme dominant dans le Mexique porfirien. Il défend un christianisme philosophique libéral inspiré notamment de Blaise Pascal et de Tolstoï, mettant en avant la liberté, la vie intérieure et la dimension spirituelle de l’être humain. &lt;/p&gt; &lt;p&gt; Son ouvrage clé,  &lt;a href=&quot;https://filosofiamexicana.org/2013/06/24/la-existencia-como-economia-como-desinteres-y-como-caridad-resena/&quot; title=&quot;La existencia como economía como desinterés y como caridad. par filofiaexicana&quot;&gt;&quot;La existencia como economía, como desinterés y como caridad&quot; &lt;/a&gt; paru en 1916, propose une anthropologie où l’existence humaine se déploie en trois niveaux: l’économie (survie, utilité), le désintéressement (contemplation) et la charité ou amour. Dans cette perspective, il distingue choses, individus et personnes, en attribuant aux personnes la capacité de désintéressement et d’amour, c’est‑à‑dire de créer des valeurs et de dépasser l’égoïsme. &lt;/p&gt; &lt;p&gt; Sa métaphysique met l’accent sur le processus, la liberté, la vie et l’esprit: la réalité est pour lui un dynamisme fluide que le schéma logique traditionnel (sujet‑prédicat) fige et déforme. Il s’inspire surtout d’Henri Bergson, mais aussi de Kant, Schopenhauer, Nietzsche et plus tard Husserl, dont il commente la phénoménologie dans ses écrits tardifs sur la personne humaine et l’État totalitaire. &lt;/p&gt; &lt;p&gt; Il est considéré comme un précurseur de la sociologie au Mexique: il crée la chaire de sociologie à l’université et publie &quot;Sociología genética y sistemática&quot; paru en 1922 puis un manuel de Sociología en 1940, très utilisé dans les universités mexicaines. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E18" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alfonso_Reyes&quot;  title=&quot; Wikipedia&quot;&gt;Alfonso REYES&lt;/a&gt; était un écrivain et philosophe &amp; diplomate  mexicain, souvent considéré comme l’un des grands humanistes de la langue espagnole au XXe siècle.  &lt;a href=&quot;https://www.persee.fr/doc/hispa_0007-4640_1960_num_62_1_3655&quot;  title=&quot; Alfonso Reyes par Persée&quot;&gt;Sa pensée &lt;/a&gt; philosophique est inséparable de son travail d’essayiste, de critique littéraire et de médiateur entre les cultures européennes et latino‑américaines. &lt;/p&gt; &lt;p&gt; Son premier livre important, &quot;Cuestiones estéticas&quot; paru en  1911 est une série de réflexions sur l’esthétique et la critique littéraire, où il articule déjà l’idée que l’expérience artistique est une forme de connaissance privilégiée du monde. Il donne des conférences sur l’&quot;esthétique classique&quot;, qui influenceront durablement l’orientation intellectuelle mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Il n’est pas un philosophe systématique au sens académique, mais un humaniste qui pense la littérature, l’histoire et le mythe comme voies d’accès à la réalité et à l’identité mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &lt;a href=&quot;https://www.youtube.com/watch?v=IeZKZ6PC9H4&quot;  title=&quot; Visión de Anáhuac de Alfonso Reyes par Literatubers&quot;&gt;&quot;Visión de Anáhuac&quot; &lt;/a&gt;  , il propose une méditation poétique et historique sur le Mexique préhispanique et la Conquête, en insistant sur la continuité d’une sensibilité mexicaine à travers les siècles. &lt;/p&gt; &lt;p&gt; Il défend une conception de l’homme formé par les lettres, la philosophie et les sciences, contre les réductions technocratiques ou purement utilitaires du savoir et pense l’Amérique latine comme espace de synthèse entre héritages indigènes, hispaniques et européens, et fait de la traduction et de la critique des instruments de ce dialogue. &lt;/p&gt;"/>
-    <hyperlink ref="E20" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Francisco ROMERO&lt;/a&gt; était un philosophe argentin d’origine espagnole, professeur à l’Université de Buenos Aires et à La Plata, et une figure centrale de la réaction  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ib%C3%A9ro-Am%C3%A9rique&quot;  title=&quot;ibéro-amérique par wikipedia&quot;&gt; ibéro-américaine &lt;/a&gt; contre le positivisme dominant au début du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa production philosophique couvre l’épistémologie, la philosophie de la culture et l’anthropologie philosophique ; son ouvrage majeur en langue espagnole, Teoría del hombre (1952), propose une réflexion systématique sur la condition humaine, la liberté et la créativité culturelle, et a été traduit en anglais sous le titre Theory of Man.https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher) &lt;/p&gt; &lt;p&gt; Il  prit position contre  &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9ductionnisme&quot;  title=&quot;Reductionnisme par wikipedia&quot;&gt; le réductionnisme scientiste &lt;/a&gt; en défendant l’idée que la culture et les créations humaines (art, religion, langage) exigent des méthodes et des concepts propres, distincts des instruments des sciences naturelles ; il chercha donc à articuler rigueur philosophique et sensibilité littéraire. &lt;/p&gt; &lt;p&gt; ur le plan méthodologique, il promut une philosophie qui dialogue avec l’histoire des idées et avec les problèmes concrets de la société ibéro-américaine : ses travaux montrent un intérêt marqué pour la responsabilité sociale des intellectuels et pour la formation culturelle des peuples. &lt;/p&gt; &lt;p&gt; Parmi ses autres ouvrages importants figurent Old and New Concepts of Reality (1932), The Problems of Philosophy of Culture (1938), Man and Culture (1950, traduction de El hombre y la cultura) et History of Modern Philosophy (1959); sa réputation lui valut le surnom de « doyen des philosophes ibéro-américains » et son héritage continue d’être étudié dans les études sur la philosophie latino‑américaine. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H20" r:id="rId13" display="https://www.laphilo.fr/pho/fromero-mini.webp"/>
-    <hyperlink ref="E22" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Susanne_Langer&quot; title=&quot; Wikipedia&quot;&gt;Susanne LANGER&lt;/a&gt; était une philosophe américaine connue pour ses travaux sur le symbole, l’art et la perception. Elle a joué un rôle important dans la philosophie défendant l’idée que la pensée humaine ne se limite pas au langage discursif, mais s’exprime aussi à travers des formes symboliques non verbales, notamment artistiques. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=gwYNyxDTOhQ&quot;   title=&quot; suzanne langer par overthink podcast&quot;&gt;Son œuvre &lt;/a&gt; la plus influente est sans doute Philosophy in a New Key (1942), où elle soutient que l’art n’est pas simplement une décoration ou une émotion brute, mais une forme de connaissance. Pour elle, la musique, la danse, la peinture ou la poésie donnent accès à des structures de sentiment que le langage ordinaire explique mal. Cette idée l’a rendue très importante pour l’esthétique et la théorie des symboles. &lt;/p&gt; &lt;p&gt; Il  s’inscrit dans une tradition marquée par Ernst Cassirer, qui voyait l’être humain comme un animal symbolique. Elle reprend cette intuition en affirmant que l’esprit humain construit le monde au moyen de symboles, et que ces symboles ne sont pas tous de même nature. Elle distingue ainsi les systèmes discursifs, qui avancent par étapes logiques, et les formes présentatives, plus propres à &lt;a href=&quot;https://www.youtube.com/watch?v=BM43-aqdboA&quot;   title=&quot; suzanne langer par philosophy overdose&quot;&gt;l’art et à l’expérience sensible. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Son apport est aussi majeur en philosophie de l’art, car elle refuse de réduire l’œuvre à une simple expression subjective de l’artiste. Au contraire, elle cherche à montrer que l’œuvre organise une forme, un rythme et une structure qui rendent intelligible une expérience affective. Cette approche a eu une influence durable sur l’esthétique, la musique et plusieurs sciences humaines. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="E25" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Herbert_Marcuse&quot;  title=&quot; Wikipedia&quot;&gt;Herbert MARCUSE&lt;/a&gt; était un philosophe germano-américain, figure emblématique de l'École de Francfort et du freudo-marxisme. Né à Berlin dans une famille juive, il a fui &lt;a href=&quot;https://www.nonfiction.fr/article-12550-penser-et-vivre-contre-le-fascisme-avec-herbert-marcuse.htm&quot;  title=&quot;herbert marcuse penser et vivre contre le nfascisme par nonfiction&quot;&gt;l'Allemagne nazie &lt;/a&gt; en 1933 pour s'installer aux États-Unis, où il a travaillé pour l'Institut de recherche sociale et l'Office of Strategic Services pendant la Seconde Guerre mondiale. &lt;/p&gt; &lt;p&gt; Ses premières influences incluent Hegel, Marx, Freud et Heidegger, dont il fut l'assistant à Freiburg. Il a  &lt;a href=&quot;https://www.youtube.com/watch?v=sUjRHvQ6yuY&quot;  title=&quot;herbert marcuse par prneix&quot;&gt;critiqué le capitalisme &lt;/a&gt; avancé et la société de consommation, voyant dans la technologie et la culture de masse des outils de domination subtile. Son engagement politique l'a lié aux mouvements étudiants des années 1960, comme en Mai 68 en France. &lt;/p&gt; &lt;p&gt; Dans Éros et Civilisation (1955), il propose une &quot;sublimation non répressive&quot;, libérant les instincts freudiens des contraintes du principe de performance pour imaginer une société plus érotique et libre. Il dénonce l'aliénation dans les démocraties industrielles, où la liberté formelle masque un contrôle total. Cette œuvre fusionne marxisme et psychanalyse pour critiquer la répression libidinale nécessaire au système productiviste. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1968_num_8_1_3123&quot;  title=&quot;herbert marcuse l’homme unidimentionnel par persée&quot;&gt;L'Homme unidimensionnel &lt;/a&gt; (1964), paru en France en 1968, est son ouvrage le plus célèbre, analysant comment la société d'abondance réduit la pensée critique à une dimension, intégrant les oppositions via la consommation et les médias. Il y voit une &quot;tolérance répressive&quot; qui neutralise la contestation en la récupérant commercialement. Il prône une &quot;grande refus&quot; des marginaux et minorités contre la classe ouvrière intégrée au système. &lt;/p&gt; &lt;p&gt; À la fin de sa vie, professeur en Californie, il reste une icône de la Nouvelle Gauche, influençant hippies et écologistes malgré les critiques sur son utopie. &lt;/p&gt; &lt;audio controls title=&quot;Herbert Marcuse , philosophe de l’espoir par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10471-07.05.1998-ITEMA_23796487-1998C3330E0013-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &#10;&#10;"/>
-    <hyperlink ref="E26" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Paul_Weiss_(philosopher)&quot; title=&quot; Wikipedia&quot;&gt;Paul WEISS&lt;/a&gt; était un philosophe américain connu pour son travail en métaphysique, esthétique, éthique et philosophie sociale, et pour son projet d’une « vision universelle » qui cherche à penser la totalité des réalités concrètes. Il a étudié avec Alfred North Whitehead et Morris Raphael Cohen, a enseigné dans plusieurs universités (notamment Yale) et a fondé la Metaphysical Society of America ainsi que la revue The Review of Metaphysics, contribuant fortement à la vie philosophique américaine du XXe siècle. &lt;/p&gt; &lt;p&gt; Il  est souvent décrit comme un métaphysicien néo-classique et un penseur de processus qui oppose au réductionnisme une réflexion sur les totalités et les finalités; il a proposé une ontologie riche où les entités concrètes, les relations et les valeurs trouvent leur place dans un système englobant. Son œuvre majeure couvre des thèmes très variés — Reality, Modes of Being, The God We Seek, You, I, and the Others — et témoigne   &lt;a href=&quot;https://www.youtube.com/watch?v=hzgN9kCruOE&quot;  title=&quot;Paul Weiss revisited par American Institute of Phlosophy&quot;&gt;d’un intérêt constant &lt;/a&gt; pour la créativité, l’art, la religion et la condition humaine, souvent traité par de vastes collections d’essais et volumes synthétiques. &lt;/p&gt; &lt;p&gt; Il  a défendu une conception qui tient ensemble l’autonomie humaine et l’insertion sociale : la liberté n’est pas pure abstraction mais se réalise dans les contextes institutionnels, moraux et artistiques qui permettent à la personne de se développer vers des fins supérieures. Esthétiquement, il a exploré la nature des arts et de la créativité, soutenant que les actes créatifs manifestent des « ultimates » ou valeurs premières qui orientent l’activité humaine vers des fins non réductibles au pragmatisme scientifique. &lt;/p&gt; &lt;p&gt; Son influence institutionnelle est importante : outre la fondation de sociétés et de revues, Weiss a laissé un corpus vaste (livres, articles, archives) qui a alimenté des débats en métaphysique et en philosophie des arts; il est considéré comme l’un des grands métaphysiciens américains du XXe siècle, reconnu par des volumes comme The Philosophy of Paul Weiss publiés dans la collection Library of Living Philosophers. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H27" r:id="rId17" display="https://www.laphilo.fr/pho/enagel-mini.webp"/>
-    <hyperlink ref="E32" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Leopoldo_Zea_Aguilar&quot; title=&quot; Wikipedia&quot;&gt;Leopoldo ZEA AGUILAR&lt;/a&gt; était un philosophe mexicain , considéré comme l'un des pères fondateurs de la philosophie latino-américaine contemporaine, engagé dans la quête d'une identité culturelle autonome face à l'eurocentrisme et au néocolonialisme. &lt;/p&gt; &lt;p&gt;  Il pose la question centrale : &quot;Peut-on construire une philosophie latino-américaine ?&quot; Réponse affirmative via une dialectique de la conscience : de la dépendance à la libération, où l'homme latino-américain réalise sa liberté par la reconnaissance de sa singularité culturelle. Relativiste culturel sans relativisme absolu, il définit l'homme comme ouvert et pluriel, rejetant l'eurocentrisme comme domination masquée ; la philosophie devient &lt;a href=&quot;https://ensayistas.org/antologia/XXA/zea/zea2.htm&quot; title=&quot;Leopoldo Zea Aguilar | Autopercepción intelectual de un proceso histórico par ensayistas&quot;&gt;&quot;instrument de libération&quot; &lt;/a&gt;, transformant l'histoire en projet éthique-politique de dignité, égalité et solidarité. Précurseur des critiques post-coloniales et postmodernes, il voit 1492 non comme &quot;découverte&quot; mais comme &quot;occultation&quot; culturelle, et la philosophie latino-américaine comme symbiose de nationalisme, christianisme et socialisme anti-impérialiste. &lt;/p&gt; &lt;p&gt; Mentor de générations, il fonde des centres intellectuels en Amérique latine et reçoit des prix mondiaux ; son discours sur la marginalité influence la philosophie de la libération et les études culturelles décoloniales. Il reste &lt;a href=&quot;https://www.youtube.com/watch?v=_kEH9wQFQv4&quot; style=&quot;color:#88A1E9&quot; title=&quot;Leopoldo Zea Aguilar | Doctorado en Educación par Miguel Morales&quot;&gt;une référence &lt;/a&gt; pour une Amérique latine unie, non utopique mais réaliste, affirmant : &quot;Se connaître égal en étant distinct est l'essence des relations humaines et internationales&quot;. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E33" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Roderick_Chisholm&quot;  title=&quot; Wikipedia&quot;&gt;Roderick CHISHOLM&lt;/a&gt; était un philosophe analytique américain reconnu pour ses travaux en épistémologie, métaphysique, philosophie de la conscience et philosophie de la perception. Il a obtenu son doctorat à l'Université de Harvard sous la tutelle de Clarence Irving Lewis et Donald C. Williams, et a enseigné pendant plus de 40 ans à l'Université Brown, après avoir aussi été professeur à Syracuse et à l'Université du Massachusetts à Amherst. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans le platonisme métaphysique de la tradition de Bertrand Russell et le rationalisme de Russell, G.E. Moore et Franz Brentano, dont il a traduit plusieurs œuvres. Il s'est opposé aux conceptions influentes de Willard Van Orman Quine, notamment contre son antiréalisme, comportementalisme et relativisme, défendant plutôt un réalisme métaphysique. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie fondationaliste de la connaissance : toutes les croyances justifiées sont soit « directement évidentes » soit soutenues par des chaînes de croyances justifiées qui finalement conduisent à des croyances directement évidentes. Il a défendu la possibilité du  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1968_num_66_90_5438_t1_0334_0000_3&quot;  title=&quot;Théory of Knowledge  par Persée&quot;&gt;knowledge empirique &lt;/a&gt; en appels à des principes épistémiques a priori, affirmant qu'il est plus raisonnable dans la plupart des situations de se confier aux sens et à la mémoire que de douter d’eux, contre les arguments sceptiques de David Hume. &lt;/p&gt; &lt;p&gt; Sa métaphysique inclut une théorie controversée de l'identité personnelle basée sur la continuité et  &lt;a href=&quot;https://www.youtube.com/watch?v=axFQjuG98AU&quot;  title=&quot;Human freedom and the self par Dillard philosophy&quot;&gt;la coïncidence des propriétés,&lt;/a&gt;  selon laquelle une personne est une substance simple et non décomposable. Il a également défendu une théorie de la volition appelée « agent causation » (causalité de l'agent), similaire à celle de Thomas Reid, et argumenté que le libre arbitre est incompatible avec le déterminisme alors que nous agissons librement - cette combinaison est connue comme  &lt;a href=&quot;https://www.youtube.com/watch?v=qLYgOxb3-E8&quot;  title=&quot;Roderick Chisholm libertarism par Philosophy et Ethics&quot;&gt;libertarianisme métaphysique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il est connu pour son ouvrage majeur Person and Object (1976), dont le titre contraste délibérément avec Word and Object de Quine, et pour sa théorie originale du pensée en première personne où les choses que nous croyons sont propriétés, et les croire est une question d'auto-attribution. Ses autres œuvres importantes incluent Perceiving (1957), Theory of Knowledge (1966, 1977, 1989), The First Person (1981), The Problem of the Criterion, et A Realist Theory of the Categories (1996). Il avait un grand respect pour l'histoire de la philosophie, contrairement à l'indifférence majoritaire des philosophes analytiques, et a contribué au renouveau de la méréologie dans les années 1970. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H33" r:id="rId20" display="https://www.laphilo.fr/pho/rchisholm-mini.webp"/>
-    <hyperlink ref="E34" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_Rawls_(philosophe)&quot;  title=&quot; Wikipedia&quot;&gt;John RAWLS&lt;/a&gt; était un  philosophe politique américain connu grâce à son œuvre majeure &quot;&lt;a href=&quot;https://www.youtube.com/watch?v=OIKwI5qu4y8&quot; style=&quot;color:#88A1E9&quot; title=&quot; La THÉORIE DE LA JUSTICE en 8 minutes ! (John RAWLS) par Culture Philo&quot;&gt; A Theory of Justice&lt;/a&gt;&quot;, publiée en 1971 ou il propose une conception de la  &lt;a href=&quot;https://www.youtube.com/watch?v=2w-AEMAU_EE&quot;  title=&quot; Le libéralisme égalitaire de John Rawls par Philoxime&quot;&gt;&quot;justice comme équité&quot;&lt;/a&gt; . Il s’oppose à l’utilitarisme – doctrine selon laquelle une action est bonne si elle maximise le bonheur collectif – et cherche au contraire à fonder la justice sur des principes garantissant équitablement les libertés et droits fondamentaux pour tous. &lt;/p&gt; &lt;p&gt;  Il imagine une &quot; &lt;a href=&quot;https://www.persee.fr/doc/rfsp_0035-2950_1991_num_41_1_394540&quot;  title=&quot;La Théorie de la justice de John Rawls. Contrat social versus utilitarisme par Persée&quot;&gt;position originelle&lt;/a&gt;&quot;, situation hypothétique où des individus rationnels, placés derrière un « voile d’ignorance » qui leur cache leurs avantages personnels, choisiraient des règles de justice justes pour tous. De cette expérience de pensée, il déduit deux principes essentiels dont le principe d’égale liberté où chaque personne doit avoir un droit égal aux libertés fondamentales et le principe de différence où les inégalités économiques et sociales ne sont justes que si elles profitent aux plus désavantagés.  &lt;/p&gt; &lt;p&gt; Il a ensuite  prolongé sa réflexion dans &quot;Political Liberalism&quot; (1993) et &quot;The Law of Peoples&quot; (1999). Dans le premier, il interroge comment un consensus moral peut se former dans des sociétés pluralistes sans imposer une doctrine particulière ; dans le second, il applique ses principes à la &lt;a href=&quot;https://www.youtube.com/watch?v=ah7y1xd3bL0&quot; title=&quot;JOHN RAWLS : Qu'est-ce que la justice sociale ? par Parole de Philosophe&quot;&gt;justice internationale&lt;/a&gt; . &lt;/p&gt; &lt;p&gt;  Il a profondément marqué la philosophie morale, politique et économique contemporaine et sa pensée inspira la théorie économique critique, avec des débats persistants sur la compatibilité de sa vision avec le libéralisme ou la social-démocratie et il demeure aujourd’hui une référence incontournable pour toute réflexion sur la justice, l’égalité et la démocratie. &lt;/p&gt; &lt;audio controls title=&quot; Avoir raison avec... John Rawls par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-13.07.2020-ITEMA_22381527-2020C35448S0195-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  "/>
-    <hyperlink ref="E35" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Kuhn&quot; title=&quot; Wikipedia&quot;&gt;Thomas KUHN&lt;/a&gt; était un philosophe et historien des sciences américain, célèbre pour son ouvrage  &lt;a href=&quot;https://apprendrelaphilosophie.com/thomas-kuhn-y-a-t-il-des-revolutions-scientifiques/&quot; title=&quot;Kuhn la sctructure des revolutions scientifiques par apprendre la philo&quot;&gt;La Structure des révolutions scientifiques &lt;/a&gt; (1962), l’un des livres les plus influents du XXᵉ siècle en philosophie des sciences. Formé d’abord en physique à Harvard avant de se tourner vers l’histoire et la philosophie des sciences, il a enseigné à Harvard, Berkeley, Princeton et au MIT, et a profondément renouvelé la façon dont on conçoit le progrès scientifique. &lt;/p&gt; &lt;p&gt; Au cœur de sa pensée se trouve le concept de paradigme : un cadre conceptuel partagé par une communauté scientifique, incluant des théories, des méthodes, des expériences canoniques et des normes de résolution de problèmes. Tant  &lt;a href=&quot;https://www.youtube.com/watch?v=_mBS4YbiYcA&quot; title=&quot;Kuhn les paradigmes par le precepteur&quot;&gt;qu’un paradigme domine, &lt;/a&gt; la science fonctionne en mode de « science normale », où les chercheurs résolvent des énigmes à l’intérieur du cadre sans remettre en cause ses fondements. &lt;/p&gt; &lt;p&gt; Il  oppose la science normale à la « science extraordinaire », qui survient quand des anomalies s’accumulent et ébranlent la confiance dans le paradigme dominant. Cela peut mener à une révolution scientifique, c’est-à-dire un changement de paradigme radical : les anciens concepts et méthodes sont abandonnés au profit d’un nouveau cadre inconciliable avec l’ancien. Il explique ainsi que le progrès scientifique n’est pas une accumulation linéaire de connaissances, mais une succession de ruptures révolutionnaires. &lt;/p&gt; &lt;p&gt; Selon lui, les paradigmes successifs ne sont pas toujours comparables de façon neutre : il parle d’« incommensurabilité » entre paradigmes, car leurs concepts, critères de validité et questions légitimes diffèrent profondément. Cela remet en cause l’idée selon laquelle la science progresse uniquement par accumulation objective et rationnelle, indépendante des contextes historiques et sociaux. &lt;/p&gt; &lt;p&gt; Sa philosophie a eu un impact bien au-delà de la science : ses idées sur les paradigmes et les révolutions ont influencé la sociologie, l’économie, les sciences politiques, la gestion et même les sciences humaines. En mettant l’accent sur les dimensions historiques, sociales et communautaires de la science, &lt;a href=&quot;https://www.youtube.com/watch?v=fV-vh9y_TQs&quot; title=&quot;Kuhn speaking par philosophy Overdoser&quot;&gt;il a ouvert la voie &lt;/a&gt;  à une épistémologie plus contextualisée, critique du positivisme logique et de l’idée d’une science totalement neutre et objective. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E36" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/John_B._Cobb&quot;  title=&quot; Wikipedia&quot;&gt;John B. COBB&lt;/a&gt; était un philosophe américain,  figure majeure de la philosophie et de la théologie du process, inspirée par Alfred North Whitehead. Issu d'une famille de missionnaires méthodistes au Japon, il a développé une vision panenthéiste où Dieu est à la fois immanent dans le monde et &lt;a href=&quot;https://books.openedition.org/pum/42552?lang=fr&quot; title=&quot;Réflexions en marge d’un livre de John B. Cobb par OpenEdition&quot;&gt;transcendant, &lt;/a&gt;  influençant profondément les débats sur l'écologie, l'économie durable et le pluralisme religieux. Son œuvre, comptant plus de 50 livres, met l'accent sur l'interdépendance de tous les êtres et la nécessité d'une éthique écologique. &lt;/p&gt; p&gt; Il rejette le théisme classique en affirmant que Dieu évolue avec les créatures, ressent leurs souffrances et n'a pas une prescience absolue des événements futurs, préservant ainsi la liberté humaine. Sa théologie &lt;a href=&quot;https://www.youtube.com/watch?v=ArXAjOlufZs&quot; title=&quot;&#10;John Cobb - Pluralisme religieux : une discussion sur le christianisme transformatif de John Cobb par Center for Process Studies&quot;&gt;du process &lt;/a&gt; voit une valeur intrinsèque en toute chose, y compris les particules comme l'électron, et critique l'anthropocentrisme chrétien traditionnel. Il intègre l'évolution comme un processus de hasard et de nécessité, influencé par Jacques Monod, tout en défendant un monde &quot;originellement bon&quot; dégradé par l'humanité. &lt;/p&gt; &lt;p&gt; Pionnier de l'éthique environnementale, il publie en 1971 &quot;Is It Too Late? A Theology of Ecology&quot;, premier ouvrage individuel sur le sujet, plaidant pour une vision écologique du christianisme. Avec Charles Birch, il coécrit &quot;The Liberation of Life&quot; en 1981, promouvant un modèle écologique contre le mécanisme biologique. &lt;/p&gt; &lt;p&gt;   Il influencera la Chine via ses idées sur la civilisation écologique et est élu en 2014 à l'Académie américaine des arts et des sciences. Il fonde aussi &quot;Progressive Christians Uniting&quot; pour une foi progressiste et engagée socialement. &lt;/p&gt; "/>
-    <hyperlink ref="E38" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Stanley_Cavell&quot;  title=&quot; Wikipedia&quot;&gt;Stanley CAVELL&lt;/a&gt; était un philosophe américain connu pour avoir renouvelé la philosophie du langage ordinaire, la philosophie morale et l’esthétique, notamment à partir de Wittgenstein, Austin, Emerson, Thoreau et du cinéma hollywoodien. Sa pensée est moins centrée sur des systèmes que sur une réflexion vivante sur l’ordinaire, le scepticisme, la voix personnelle et la manière dont la philosophie peut parler à partir de &lt;a href=&quot;https://www.youtube.com/watch?v=bWMncAAj16c&quot; title=&quot; Stanley Cavell par Film &amp; media&quot;&gt;l’expérience vécue. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Il s’intéresse d’abord au langage quotidien, parce qu’il pense que les difficultés philosophiques ne viennent pas seulement d’un manque d’informations, mais d’un trouble plus profond dans notre rapport au monde et aux autres. Pour lui, &lt;a href=&quot;https://www.youtube.com/watch?v=5q50IwBAUKY&quot; title=&quot; Stanley Cavell par philo overdose&quot;&gt;le scepticisme &lt;/a&gt; n’est pas seulement un problème de connaissance, c’est aussi une expérience humaine et parfois tragique : nous pouvons nous sentir séparés du monde, d’autrui, voire de nous-mêmes. &lt;/p&gt; &lt;p&gt; Un thème central chez lui est donc la reconnaissance. Il ne s’agit pas simplement de « savoir » que l’autre existe, mais d’apprendre à le reconnaître, à répondre à sa présence, et à accepter que nos relations humaines comportent toujours une part d’incertitude. C’est pourquoi Cavell relie souvent la philosophie à l’éthique, à la vie quotidienne et aux formes concrètes de l’attention aux autres. &lt;/p&gt; &lt;p&gt; Il est aussi célèbre pour son travail sur le cinéma, qu’il ne considère pas comme un divertissement secondaire mais comme un véritable lieu de pensée. À travers les comédies hollywoodiennes, notamment les « comédies de remariage », il explore des questions de couple, de séparation, de pardon et de seconde chance, c’est-à-dire des problèmes philosophiques aussi bien que narratifs.  &lt;/p&gt; &lt;p&gt; Il est lié à une idée très américaine de la philosophie : une philosophie qui n’oppose pas rigidement le savant et le populaire, qui peut être autobiographique, littéraire et morale à la fois. Son originalité tient à cela : il transforme la philosophie en une &lt;a href=&quot;https://www.liberation.fr/debats/2018/06/20/stanley-cavell-the-end_1660627/&quot; title=&quot; Stanley Cavell par liberation&quot;&gt; enquête sur la vie &lt;/a&gt; ordinaire, les formes de notre voix, et la possibilité de devenir plus juste envers soi-même et envers les autres.  &lt;/p&gt; &#10;&lt;audio controls title=&quot;la pensée américaine Stanley Cavell par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-05.11.2012-ITEMA_20417072-2012C12410S0310-NET_B1E428CD-7648-4739-933D-4C419F0B94C8_FC-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &#10;"/>
-    <hyperlink ref="H38" r:id="rId25" display="https://www.laphilo.fr/pho/scavell-mini.webp"/>
-    <hyperlink ref="H39" r:id="rId26" display="https://www.laphilo.fr/pho/mrothbard-mini.webp"/>
-    <hyperlink ref="H40" r:id="rId27" display="https://www.laphilo.fr/pho/ewiesel-mini.webp"/>
-    <hyperlink ref="H41" r:id="rId28" display="https://www.laphilo.fr/pho/abracken-mini.webp"/>
-    <hyperlink ref="E42" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Rorty&quot; title=&quot; Wikipedia&quot;&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href=&quot;https://www.youtube.com/watch?v=lfx4Jag1ic4&quot;  title=&quot;Le pragmatisme : définition, exemples par le savoir partagé&quot;&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href=&quot;https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism&quot; title=&quot; a bas l'autorité par laviedesidees&quot;&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas &quot;vrais&quot; ou &quot;faux&quot;. &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales , on trouve  &lt;a href=&quot;https://www.youtube.com/watch?v=MgU0dXZ3umM&quot; title=&quot;L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli&quot;&gt;&quot; Contingence, ironie et solidarité &quot;&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans &quot; Achieving Our Country&quot; (1998),  il y appelle la gauche américaine à abandonner le &quot;culturalisme&quot; pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la &quot;post-vérité&quot;. Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; "/>
-    <hyperlink ref="E44" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Charles_Parsons_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Charles Dacre PARSONS&lt;/a&gt; était un philosophe américain connu pour ses travaux en philosophie des mathématiques et en philosophie de Kant. Il a enseigné à Columbia puis à Harvard, où il est devenu professeur émérite. Il s’est formé à Harvard, avec une thèse dirigée par Willard Van Orman Quine, ce qui le place au croisement de la logique, de la philosophie analytique et des fondements des mathématiques. Son parcours intellectuel a été marqué très tôt par la rigueur mathématique, puisqu’il avait d’abord étudié les mathématiques avant de se tourner vers la philosophie. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la philosophie des mathématiques, domaine dans lequel il a travaillé sur la nature des objets mathématiques, la logique, la preuve et l’interprétation constructive des mathématiques prédicatives. Il a aussi beaucoup écrit sur Frege, Gödel, Hilbert et Quine, en lisant ces auteurs à la fois comme philosophes et comme figures majeures des fondements. &lt;/p&gt; &lt;p&gt; Il n’était pas seulement un spécialiste de logique ; il a aussi produit des travaux importants sur Kant, montrant comment les questions de connaissance, d’expérience et de structure de l’esprit se relient aux mathématiques. Cette double compétence, en philosophie des mathématiques et en histoire de la philosophie, explique pourquoi il est souvent vu comme un auteur à la fois technique et très large dans ses intérêts.&lt;/p&gt; &lt;p&gt; Son influence est restée forte dans le monde anglophone, au point d’être décrit comme l’un des philosophes des mathématiques les plus importants de sa génération. En plus de ses livres et articles, il a aussi contribué à l’édition de textes posthumes de Gödel, ce qui a renforcé son rôle dans l’étude contemporaine des fondements des mathématiques. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="I44" r:id="rId31" display="https://www.laphilo.fr/photo/cparsons.webp"/>
-    <hyperlink ref="H46" r:id="rId32" display="https://www.laphilo.fr/pho/dihde-mini.webp"/>
-    <hyperlink ref="E48" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edward_Sa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Edward SAÏD&lt;/a&gt; était un intellectuel palestinien-américain, critique littéraire et professeur de littérature anglaise et comparée à l’université Columbia de New York. D’origine palestinienne et né à Jérusalem, il a grandi entre l’Égypte, les États-Unis et l’Europe, une expérience de déplacement qui a profondément marqué sa pensée sur l’identité, la colonisation et l’altérité.  &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est l’essai &lt;a href=&quot;https://www.youtube.com/watch?v=Ne4WRykmjhA&quot; title=&quot;Edward Said  Orientalisme par HD Doc&quot;&gt;L’Orientalisme : &lt;/a&gt;  L’Orient créé par l’Occident* (1978), considéré comme le texte fondateur des postcolonial studies. Dans cet ouvrage, Saïd montre que l’« Orient » n’est pas une réalité objective mais une invention de l’Occident : un discours façonné par des siècles de domination coloniale pour mieux contrôler et représenter l’Autre. &lt;/p&gt; &lt;p&gt; Pour lui, l’orientalisme est à la fois un savoir et un outil de pouvoir : il ne s’agit pas seulement de décrire l’Orient, mais de le hiérarchiser, de l’essentialiser et de le rendre  &lt;a href=&quot;https://www.youtube.com/watch?v=QBj-yWLnayM&quot; title=&quot;Edward Said writings on Orientalism par Middle East Eye&quot;&gt; inférieur à l’Occident. &lt;/a&gt; Il analyse quatre thèses principales : la domination politique et culturelle de l’Orient par l’Occident, la dépréciation de la langue arabe, la diabolisation de l’arabe et de l’islam, et la défense de la cause palestinienne. &lt;/p&gt; &lt;p&gt; Sa pensée articule critique littéraire, histoire, philosophie et sciences politiques, en s’inspirant notamment de Michel Foucault (discours–pouvoir) et de Jacques Derrida (déconstruction). Il montre que la violence du colonialisme n’est pas seulement matérielle (conquête, pillage), mais aussi épistémique : une violence de la raison qui classe, essentialise et dévalue les « Autres » de l’Occident. &lt;/p&gt; &lt;p&gt;  Intéressé par &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Edward-W-Said-1935-2003.html&quot; title=&quot;Edward Said par lesclesdumoyenorient&quot;&gt; l’engagement politique, &lt;/a&gt; il a aussi défendu la cause palestinienne et la légitimité des revendications d’autodétermination du peuple palestinien, tout en reconnaissance du droit à une patrie juive. Il rejetait le repli identitaire et prônait une vision universelle qui défend les différences et les droits, tissant des liens entre classicisme et excentricité, histoire et actualité. &lt;/p&gt;  &lt;audio controls title=&quot;Edward Said, une conscience morale par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-08.12.2017-ITEMA_21518070-2017C19327S0342-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &#10;&#10;&#10;"/>
-    <hyperlink ref="H48" r:id="rId34" display="https://laphilo.fr/pho/esaid-mini.webp"/>
-    <hyperlink ref="H49" r:id="rId35" display="https://www.laphilo.fr/pho/rmadams-mini.webp"/>
-    <hyperlink ref="E50" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Nozick&quot;  title=&quot; Wikipedia&quot;&gt;Robert NOZICK&lt;/a&gt; était un philosophe américain connu pour &lt;a href=&quot;https://www.youtube.com/watch?v=Q-t3cpFAk4o&quot;  title=&quot; Libertarianisme par Vadim Media&quot;&gt; son libertarianisme &lt;/a&gt; et sa critique des théories égalitaristes comme celle de John Rawls. Professeur à Harvard, il a marqué la philosophie politique, morale et épistémologique par son œuvre principale, Anarchie, État et utopie (1974), qui défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Minarchisme&quot;  title=&quot; Minarchisme par Wikipédia&quot;&gt; Etat Minimal. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il argue que seul l'État minimal, ou &quot;État gardien de nuit&quot;, est légitime, car il se limite à protéger les individus contre la force, la fraude et le vol, sans redistribuer les richesses. Il rejette l'anarcho-capitalisme en montrant, via des agences de protection privée, comment un État dominant émerge naturellement pour monopoliser la coercition légitime, justifié par le droit naturel à la personne. &lt;/p&gt; &lt;p&gt; Contrairement à la justice distributive de Rawls, il propose une théorie de l'entitlement : une acquisition initiale juste et des transferts volontaires rendent la distribution légitime, sans besoin d'égalisation par l'État. Toute intervention redistributive viole les droits individuels, traitant les personnes comme des moyens plutôt que des fins, en écho à Kant. &lt;/p&gt; &lt;p&gt; Dans Anarchie, État et utopie, Il réfute l'utilitarisme via l'expérience de pensée de la &lt;a href=&quot;https://www.youtube.com/watch?v=2FVwXaNWPQ0&quot;  title=&quot; La machine à expérience par Monsieur Phi&quot;&gt;&quot;machine à expérience&quot; :&lt;/a&gt;  même si elle offre un bonheur parfait et indistinguable de la réalité, les gens préfèrent vivre des actions réelles et façonner leur identité plutôt que des simulations. Cela prouve que le bonheur n'est pas le seul bien suprême. &lt;/p&gt; &lt;p&gt; Plus tard, dans Explications philosophiques (1981), il développe une théorie du suivi (tracking theory) en épistémologie, où la connaissance repose sur des conditionnels contrefactuels fiables, contournant le scepticisme sans justification traditionnelle. Son anti-coercitivisme intellectuel invite à une philosophie ouverte, non imposée. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Qui a peur des Libertariens par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-14.06.2022-ITEMA_23058436-2022C12410S0165-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;"/>
-    <hyperlink ref="H56" r:id="rId37" display="https://www.laphilo.fr/pho/imyoung-mini.webp"/>
-    <hyperlink ref="H57" r:id="rId38" display="https://www.laphilo.fr/pho/bhooks-mini.webp"/>
+    <hyperlink ref="E10" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_Sanders_Peirce&quot; title=&quot; Wikipedia&quot;&gt;Charles SANDERS PIERCE&lt;/a&gt;  était un philosophe, logicien, scientifique américain assez original, fondateur du  &lt;a href=&quot;https://www.youtube.com/watch?v=AGHmKg7wYf0&quot;  title=&quot;Pragmatisme  par robertus&quot;&gt;pragmatisme&lt;/a&gt; , père de la sémiotique moderne (théorie des signes) et un pionnier de la logique. Pourtant, en raison de  &lt;a href=&quot;https://laviedesidees.fr/Chevalier-Peirce-ou-l-invention-de-l-epistemologie&quot; style=&quot;color:#88A1E9&quot; title=&quot;les pepites de Charles s pierce par laviedesidees&quot;&gt;sa personnalité difficile&lt;/a&gt; et de ses idées avant-gardistes, il vécut en marge du monde académique, mourant dans la pauvreté et l'isolement. &lt;/p&gt; &lt;p&gt;  Il cherchait à identifier les catégories les plus fondamentales et universelles de la pensée et de l'être, qu'il nomma Phanéroscopie.Il en déduit trois, présentes dans tous les phénomènes. Elles sont la clé de voûte de tout le système peircien et sont indispensables pour comprendre sa sémiotique et  &lt;a href=&quot;https://hal.science/hal-02953592/document&quot;  title=&quot;Pragmatisme  par hal science&quot;&gt;son pragmatisme&lt;/a&gt;: &lt;/p&gt; &lt;p&gt; - Priméité (Firstness) : C'est la catégorie de la qualité pure, de la potentialité, de la sensation immédiate et brute, existant en elle-même sans référence à quoi que ce soit d'autre. C'est le &quot;sentiment de rouge&quot;, la qualité d'une odeur, la nouveauté d'une idée. C'est le domaine de la possibilité et de la liberté. &lt;/p&gt; &lt;p&gt; - Secondéité (Secondeity) : C'est la catégorie du fait brut, de l'action-réaction, de la résistance et de l'actualité. C'est le choc du &quot;ici et maintenant&quot;, la rencontre avec un autre qui s'impose à nous. Exemples : une collision, la sensation de résistance en poussant une porte, un conflit. C'est le domaine de l'existence et de la dualité. &lt;/p&gt; &lt;p&gt; - Tiercéité (Thirdness) : C'est la catégorie de la médiation, de la loi, de l'habitude, de la généralisation et de la signification. Elle fait le lien entre la Priméité (la qualité) et la Secondéité (le fait) en leur donnant un sens et une régularité. Exemples : une loi scientifique, un symbole linguistique, une tendance, une règle de conduite. C'est le domaine de la pensée, de la continuité et de l'intelligibilité. &lt;/p&gt; &lt;p&gt; Il propose une méthode pour clarifier le sens de nos idées, le Pragmaticisme: le sens d'un concept réside dans ses conséquences pratiques observables. Si deux idées ne produisent aucune différence pratique, elles signifient la même chose. C'est avant tout une méthode logique pour trancher les disputes métaphysiques stériles.&lt;/p&gt; &lt;p&gt; Sa contribution la plus novatrice et la plus influente est &lt;a href=&quot;https://www.persee.fr/doc/lgge_0458-726x_1980_num_14_58_1844&quot; title=&quot;La séméiotique de Charles S. Peirce  par Persée&quot;&gt;la Sémiotique&lt;/a&gt; . Pour lui, &quot;l'homme est un signe&quot; et toute pensée est un &lt;a href=&quot;https://www.youtube.com/watch?v=e1jrx1RlS00&quot; title=&quot;VOIR ET INTERPRÉTER LES SIGNES ! Introduction à la sémiologie CHARLES SANDERS PEIRCE  par Survivreauxscienceshumaines&quot;&gt;processus sémiotique&lt;/a&gt;. Il définit le signe non pas de manière dyadique mais triadique,  Il crée dans l'esprit de la  personne un signe plus développé, appelé l'interprétant. La relation signe-objet-interprétant est fondamentale. Sa classification concerne la relation du signe à son objet : &lt;/p&gt; &lt;dd&gt; - Icône: Le signe ressemble à son objet ou partage des qualités avec lui (une photographie, un diagramme) . &lt;/dd&gt; &lt;dd&gt; - Index: Le signe est physiquement connecté à son objet . la fumée (indice du feu), une girouette (indice de la direction du vent). &lt;/dd&gt; &lt;dd&gt; - Symbole: La relation entre le signe et l'objet est arbitraire et conventionnelle. Elle repose sur une règle ou une habitude sociale. (&quot;arbre&quot; n'a rien d'un arbre). &lt;/dd&gt; &lt;p&gt; Bien que mort dans la misère et méconnu de son vivant, son influence est immense aujourd'hui en philosophie, en sciences cognitives, en linguistique et en sociologie. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E14" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Alejandro_Korn&quot;  title=&quot; Wikipedia&quot;&gt;Alejendro KORN&lt;/a&gt; était un  philosophe, médecin et homme politique argentin considéré comme l’un des fondateurs de la philosophie argentine moderne. Après des études de médecine et une carrière de psychiatre, il se consacra à la philosophie et à l’enseignement, occupant des chaires à l’Université de Buenos Aires et à La Plata, où il contribua à insérer la philosophie dans la vie intellectuelle nationale. &lt;/p&gt; &lt;p&gt; Il  chercha à  &lt;a href=&quot;https://www.youtube.com/watch?v=Fc9frRYHyTU&quot; title=&quot;Alejandro Korn par filo errante&quot;&gt;dépasser le positivisme &lt;/a&gt; dominant en Argentine en affirmant la centralité de la liberté créatrice : pour lui la liberté n’est pas simple absence de contraintes mais un effort conscient de création et d’amélioration de soi et du monde, unissant dimensions économique, sociale et éthique. Il soutint que la philosophie doit partir de la conscience et de l’intuition, tout en reconnaissant la nécessité de la science; ainsi il proposa une synthèse où l’ordre objectif de la science et l’ordre subjectif de la liberté humaine sont intégrés sans se confondre. &lt;/p&gt; &lt;p&gt; En axiologie et théorie des valeurs, il développa une classification des valeurs (biologiques, sociales, culturelles) et une conception relativiste des évaluations historiques, tout en maintenant la possibilité d’objectivité dans les valeurs culturelles supérieures comme la vérité, la beauté et la sainteté; la valeur est pour lui la réponse active du sujet face aux faits de l’existence. Cette orientation le conduisit à défendre une éducation humaniste capable de former des citoyens autonomes, responsables et créateurs, idée qu’il mit en pratique à travers son engagement dans les réformes universitaires et la création d’espaces pour les humanités. &lt;/p&gt; &lt;p&gt; Il   &lt;a href=&quot;https://www.youtube.com/watch?v=-L16KuQgWxE&quot; title=&quot;alejandro korn par filosofia en red&quot;&gt;mêla pensée et action : &lt;/a&gt; il participa à la vie publique, défendit la dignité de la personne et la nécessité d’une culture nationale fondée sur la liberté et la responsabilité, opposant une philosophie de la personne à un positivisme strictement utilitariste; son influence se lit dans les transformations éducatives et institutionnelles argentines du début du XXe siècle. Ses œuvres principales incluent Influencias filosóficas en la evolución nacional, La libertad creadora, Esquema gnoseológico, El concepto de ciencia et Axiología, et son corpus continue d’être étudié comme pierre angulaire de la tradition philosophique argentine. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H14" r:id="rId5" display="https://www.laphilo.fr/pho/akorn-mini.webp"/>
+    <hyperlink ref="E15" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://pt.wikipedia.org/wiki/Raimundo_de_Farias_Brito&quot;  title=&quot; Wikipedia&quot;&gt;Farias BRITO&lt;/a&gt; était un  philosophe brésilien  connu pour avoir développé un spiritualisme philosophique qui a marqué la pensée brésilienne. Sa trajectoire intellectuelle passa par des études de droit et des activités publiques (magistrature, enseignement), avant d’occuper à Rio de Janeiro la chaire de logique du Colégio Pedro II, poste qu’il conserva jusqu’à sa mort, ce qui lui permit de diffuser largement ses idées. &lt;/p&gt; &lt;p&gt; Sur le plan doctrinal, il articula une critique du matérialisme et du positivisme en faveur d’un spiritualisme qui entendait le « esprit » comme la réalité première capable de sentir, connaître et agir; il proposa une métaphysique où la matière est dérivée ou dérivée de la réalité spirituelle. Sa pensée traversa deux grandes phases : d’abord un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Monisme_(spiritualit%C3%A9)&quot; title=&quot;monisme par wikipedia&quot;&gt;monisme panteïste &lt;/a&gt; (avec des accents d’immanence) visible dans certaines œuvres plus anciennes, puis une évolution vers un pluralisme théiste où Dieu apparaît comme cause première personnelle, rapprochement qui le conduisit vers une sensibilité plus nettement religieuse à la fin de sa vie. &lt;/p&gt; &lt;p&gt; Il situa la valeur morale dans la recherche de la vérité et dans l’amélioration intérieure de l’individu; il concevait la conscience comme le lieu décisif de la lutte entre les appels moraux et les instincts, et définissait la liberté comme la capacité de choisir entre conviction et convenance. Pour lui, l’action juste dépend de l’adéquation de l’intellect à la réalité (la vérité) et de la conversion intérieure du sujet, d’où découlent des exigences éducatives et morales importantes pour la société. &lt;/p&gt; &lt;p&gt; Politiquement, il se montra critique envers les conséquences du libéralisme, du démocratisme et des idéologies révolutionnaires qu’il jugeait responsables d’un affaiblissement des croyances traditionnelles et d’une montée du matérialisme social; il prônait au contraire une réforme sociale guidée par des principes moraux et une « grande idée » éthique plutôt que par les seuls intérêts matériels ou la lutte. Cette dimension conservatrice-morale de sa pensée s’articule à son rejet du positivisme excessif et à sa confiance dans la capacité de la philosophie et de l’éducation de corriger la crise culturelle de son époque. &lt;/p&gt; &lt;p&gt; Son œuvre, abondante et variée, comprend des titres sur la métaphysique, la logique, l’éthique et la philosophie de la science — parmi les plus cités figurent A Filosofia como Atividade Permanente do Espírito Humano, A Filosofia Moderna, A Base Física do Espírito et O Mundo Interior — et elle a laissé un héritage durable dans la culture intellectuelle brésilienne, étudiée encore aujourd’hui dans des travaux historiques et critiques. Les recherches contemporaines insistent sur son statut de penseur « pré-moderniste » du Brésil et sur l’originalité de sa tentative de construire une philosophie nationale qui conjugue métaphysique, morale et engagement public. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
+    <hyperlink ref="H15" r:id="rId7" display="https://www.laphilo.fr/pho/fbrito-mini.webp"/>
+    <hyperlink ref="E16" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Carlos_Vaz_Ferreira&quot;  title=&quot; Wikipedia&quot;&gt;Carlos VAS FERREIRA&lt;/a&gt; était un  philosophe uruguayen considéré comme l’une des figures majeures de la pensée hispano‑américaine au début du XXᵉ siècle. Issue d’une famille aux origines portugaise et uruguayenne, sa trajectoire intellectuelle s’inscrit dans un contexte de modernisation de l’Université et de reformulation des idées scientifiques et morales en Amérique du Sud. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=AmRpz8vCejs&quot; title=&quot;Vas Ferreira par Pablo Romero&quot;&gt;Sa philosophie &lt;/a&gt; se situe à la croisée du positivisme, du pragmatisme et de l’empirisme britannique, avec un respect marqué pour Herbert Spencer, John Stuart Mill, William James et Henri Bergson, sans jamais adopter intégralement leurs doctrines. Il critique la rigidité des systèmes logiques et métaphysiques classiques, estimant que le langage et la logique formelle imposent au réel une précision artificielle qui masque la complexité et la fluidité de l’expérience. &lt;/p&gt; &lt;p&gt; Il  développe l’idée d’une &lt;a href=&quot;https://www.youtube.com/watch?v=UeadgG1ud1g&quot; title=&quot;Vas Ferreira y su logica viva par Tribuna Constitucional&quot;&gt;« logique vivante », &lt;/a&gt; c’est‑à‑dire une logique ancrée dans la vie concrète, attentive aux degrés de probabilité et aux limites de nos certitudes plutôt qu’aux schémas abstraits. Pour lui, la raison doit rester souple et vigilante, proche de l’expérience et des données empiriques, afin de ne pas basculer dans des systèmes dogmatiques. &lt;/p&gt; &lt;p&gt; En épistémologie, il défend une vision modeste de la science : les sciences sont des outils puissants mais partiaux, incapables de saisir le tout de la réalité et toujours confrontées à des questions métaphysiques implicites. La philosophie, selon lui, doit clarifier ces présupposés, rappeler les limites symboliques de la science et contrer les « mauvaises métaphysiques » qui surgissent lorsque l’on ignore les questions fondamentales. &lt;/p&gt; &lt;p&gt; Sur le plan éthique et social, il s’intéresse à la liberté, à la morale des intellectuels, aux problèmes sociaux et aux questions de propriété ou de féminisme. Il met en avant une morale sensible à la complexité des situations, où les principes comportent des exceptions et où le choix moral implique souvent des compromis entre des biens et des maux partiels ; tout en affirmant qu’il existe un progrès moral dans l’histoire humaine, marqué par l’élargissement des idéaux et la résistance accrue au mal. &lt;/p&gt; &#10;&#10;&#10;&#10;&#10;"/>
+    <hyperlink ref="H16" r:id="rId9" display="https://www.laphilo.fr/pho/cvferreira-mini.webp"/>
+    <hyperlink ref="E18" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Antonio_Caso&quot;   title=&quot; Wikipedia&quot;&gt;Antonio CASO&lt;/a&gt; était un philosophe mexicain connu pour sa critique du positivisme et pour un  &lt;a href=&quot;https://www.youtube.com/watch?v=YlEoF2CNNxA&quot; title=&quot;&quot;Antonio Caso Andrade - Filósofo y Sociológico Mexicano - Una Mirada Profunda a sus Contribuciones&quot; par Biografías de Filósofos&quot;&gt;humanisme spiritualiste &lt;/a&gt; influent dans la culture intellectuelle mexicaine. Il cofonde en 1910, avec José Vasconcelos et d’autres, l’Ateneo de la Juventud, cercle intellectuel qui s’oppose au positivisme dominant dans le Mexique porfirien. Il défend un christianisme philosophique libéral inspiré notamment de Blaise Pascal et de Tolstoï, mettant en avant la liberté, la vie intérieure et la dimension spirituelle de l’être humain. &lt;/p&gt; &lt;p&gt; Son ouvrage clé,  &lt;a href=&quot;https://filosofiamexicana.org/2013/06/24/la-existencia-como-economia-como-desinteres-y-como-caridad-resena/&quot; title=&quot;La existencia como economía como desinterés y como caridad. par filofiaexicana&quot;&gt;&quot;La existencia como economía, como desinterés y como caridad&quot; &lt;/a&gt; paru en 1916, propose une anthropologie où l’existence humaine se déploie en trois niveaux: l’économie (survie, utilité), le désintéressement (contemplation) et la charité ou amour. Dans cette perspective, il distingue choses, individus et personnes, en attribuant aux personnes la capacité de désintéressement et d’amour, c’est‑à‑dire de créer des valeurs et de dépasser l’égoïsme. &lt;/p&gt; &lt;p&gt; Sa métaphysique met l’accent sur le processus, la liberté, la vie et l’esprit: la réalité est pour lui un dynamisme fluide que le schéma logique traditionnel (sujet‑prédicat) fige et déforme. Il s’inspire surtout d’Henri Bergson, mais aussi de Kant, Schopenhauer, Nietzsche et plus tard Husserl, dont il commente la phénoménologie dans ses écrits tardifs sur la personne humaine et l’État totalitaire. &lt;/p&gt; &lt;p&gt; Il est considéré comme un précurseur de la sociologie au Mexique: il crée la chaire de sociologie à l’université et publie &quot;Sociología genética y sistemática&quot; paru en 1922 puis un manuel de Sociología en 1940, très utilisé dans les universités mexicaines. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E19" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alfonso_Reyes&quot;  title=&quot; Wikipedia&quot;&gt;Alfonso REYES&lt;/a&gt; était un écrivain et philosophe &amp; diplomate  mexicain, souvent considéré comme l’un des grands humanistes de la langue espagnole au XXe siècle.  &lt;a href=&quot;https://www.persee.fr/doc/hispa_0007-4640_1960_num_62_1_3655&quot;  title=&quot; Alfonso Reyes par Persée&quot;&gt;Sa pensée &lt;/a&gt; philosophique est inséparable de son travail d’essayiste, de critique littéraire et de médiateur entre les cultures européennes et latino‑américaines. &lt;/p&gt; &lt;p&gt; Son premier livre important, &quot;Cuestiones estéticas&quot; paru en  1911 est une série de réflexions sur l’esthétique et la critique littéraire, où il articule déjà l’idée que l’expérience artistique est une forme de connaissance privilégiée du monde. Il donne des conférences sur l’&quot;esthétique classique&quot;, qui influenceront durablement l’orientation intellectuelle mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Il n’est pas un philosophe systématique au sens académique, mais un humaniste qui pense la littérature, l’histoire et le mythe comme voies d’accès à la réalité et à l’identité mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &lt;a href=&quot;https://www.youtube.com/watch?v=IeZKZ6PC9H4&quot;  title=&quot; Visión de Anáhuac de Alfonso Reyes par Literatubers&quot;&gt;&quot;Visión de Anáhuac&quot; &lt;/a&gt;  , il propose une méditation poétique et historique sur le Mexique préhispanique et la Conquête, en insistant sur la continuité d’une sensibilité mexicaine à travers les siècles. &lt;/p&gt; &lt;p&gt; Il défend une conception de l’homme formé par les lettres, la philosophie et les sciences, contre les réductions technocratiques ou purement utilitaires du savoir et pense l’Amérique latine comme espace de synthèse entre héritages indigènes, hispaniques et européens, et fait de la traduction et de la critique des instruments de ce dialogue. &lt;/p&gt;"/>
+    <hyperlink ref="E21" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Francisco ROMERO&lt;/a&gt; était un philosophe argentin d’origine espagnole, professeur à l’Université de Buenos Aires et à La Plata, et une figure centrale de la réaction  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ib%C3%A9ro-Am%C3%A9rique&quot;  title=&quot;ibéro-amérique par wikipedia&quot;&gt; ibéro-américaine &lt;/a&gt; contre le positivisme dominant au début du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa production philosophique couvre l’épistémologie, la philosophie de la culture et l’anthropologie philosophique ; son ouvrage majeur en langue espagnole, Teoría del hombre (1952), propose une réflexion systématique sur la condition humaine, la liberté et la créativité culturelle, et a été traduit en anglais sous le titre Theory of Man.https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher) &lt;/p&gt; &lt;p&gt; Il  prit position contre  &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9ductionnisme&quot;  title=&quot;Reductionnisme par wikipedia&quot;&gt; le réductionnisme scientiste &lt;/a&gt; en défendant l’idée que la culture et les créations humaines (art, religion, langage) exigent des méthodes et des concepts propres, distincts des instruments des sciences naturelles ; il chercha donc à articuler rigueur philosophique et sensibilité littéraire. &lt;/p&gt; &lt;p&gt; ur le plan méthodologique, il promut une philosophie qui dialogue avec l’histoire des idées et avec les problèmes concrets de la société ibéro-américaine : ses travaux montrent un intérêt marqué pour la responsabilité sociale des intellectuels et pour la formation culturelle des peuples. &lt;/p&gt; &lt;p&gt; Parmi ses autres ouvrages importants figurent Old and New Concepts of Reality (1932), The Problems of Philosophy of Culture (1938), Man and Culture (1950, traduction de El hombre y la cultura) et History of Modern Philosophy (1959); sa réputation lui valut le surnom de « doyen des philosophes ibéro-américains » et son héritage continue d’être étudié dans les études sur la philosophie latino‑américaine. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H21" r:id="rId13" display="https://www.laphilo.fr/pho/fromero-mini.webp"/>
+    <hyperlink ref="E23" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Susanne_Langer&quot; title=&quot; Wikipedia&quot;&gt;Susanne LANGER&lt;/a&gt; était une philosophe américaine connue pour ses travaux sur le symbole, l’art et la perception. Elle a joué un rôle important dans la philosophie défendant l’idée que la pensée humaine ne se limite pas au langage discursif, mais s’exprime aussi à travers des formes symboliques non verbales, notamment artistiques. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=gwYNyxDTOhQ&quot;   title=&quot; suzanne langer par overthink podcast&quot;&gt;Son œuvre &lt;/a&gt; la plus influente est sans doute Philosophy in a New Key (1942), où elle soutient que l’art n’est pas simplement une décoration ou une émotion brute, mais une forme de connaissance. Pour elle, la musique, la danse, la peinture ou la poésie donnent accès à des structures de sentiment que le langage ordinaire explique mal. Cette idée l’a rendue très importante pour l’esthétique et la théorie des symboles. &lt;/p&gt; &lt;p&gt; Il  s’inscrit dans une tradition marquée par Ernst Cassirer, qui voyait l’être humain comme un animal symbolique. Elle reprend cette intuition en affirmant que l’esprit humain construit le monde au moyen de symboles, et que ces symboles ne sont pas tous de même nature. Elle distingue ainsi les systèmes discursifs, qui avancent par étapes logiques, et les formes présentatives, plus propres à &lt;a href=&quot;https://www.youtube.com/watch?v=BM43-aqdboA&quot;   title=&quot; suzanne langer par philosophy overdose&quot;&gt;l’art et à l’expérience sensible. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Son apport est aussi majeur en philosophie de l’art, car elle refuse de réduire l’œuvre à une simple expression subjective de l’artiste. Au contraire, elle cherche à montrer que l’œuvre organise une forme, un rythme et une structure qui rendent intelligible une expérience affective. Cette approche a eu une influence durable sur l’esthétique, la musique et plusieurs sciences humaines. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="E26" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Herbert_Marcuse&quot;  title=&quot; Wikipedia&quot;&gt;Herbert MARCUSE&lt;/a&gt; était un philosophe germano-américain, figure emblématique de l'École de Francfort et du freudo-marxisme. Né à Berlin dans une famille juive, il a fui &lt;a href=&quot;https://www.nonfiction.fr/article-12550-penser-et-vivre-contre-le-fascisme-avec-herbert-marcuse.htm&quot;  title=&quot;herbert marcuse penser et vivre contre le nfascisme par nonfiction&quot;&gt;l'Allemagne nazie &lt;/a&gt; en 1933 pour s'installer aux États-Unis, où il a travaillé pour l'Institut de recherche sociale et l'Office of Strategic Services pendant la Seconde Guerre mondiale. &lt;/p&gt; &lt;p&gt; Ses premières influences incluent Hegel, Marx, Freud et Heidegger, dont il fut l'assistant à Freiburg. Il a  &lt;a href=&quot;https://www.youtube.com/watch?v=sUjRHvQ6yuY&quot;  title=&quot;herbert marcuse par prneix&quot;&gt;critiqué le capitalisme &lt;/a&gt; avancé et la société de consommation, voyant dans la technologie et la culture de masse des outils de domination subtile. Son engagement politique l'a lié aux mouvements étudiants des années 1960, comme en Mai 68 en France. &lt;/p&gt; &lt;p&gt; Dans Éros et Civilisation (1955), il propose une &quot;sublimation non répressive&quot;, libérant les instincts freudiens des contraintes du principe de performance pour imaginer une société plus érotique et libre. Il dénonce l'aliénation dans les démocraties industrielles, où la liberté formelle masque un contrôle total. Cette œuvre fusionne marxisme et psychanalyse pour critiquer la répression libidinale nécessaire au système productiviste. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1968_num_8_1_3123&quot;  title=&quot;herbert marcuse l’homme unidimentionnel par persée&quot;&gt;L'Homme unidimensionnel &lt;/a&gt; (1964), paru en France en 1968, est son ouvrage le plus célèbre, analysant comment la société d'abondance réduit la pensée critique à une dimension, intégrant les oppositions via la consommation et les médias. Il y voit une &quot;tolérance répressive&quot; qui neutralise la contestation en la récupérant commercialement. Il prône une &quot;grande refus&quot; des marginaux et minorités contre la classe ouvrière intégrée au système. &lt;/p&gt; &lt;p&gt; À la fin de sa vie, professeur en Californie, il reste une icône de la Nouvelle Gauche, influençant hippies et écologistes malgré les critiques sur son utopie. &lt;/p&gt; &lt;audio controls title=&quot;Herbert Marcuse , philosophe de l’espoir par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10471-07.05.1998-ITEMA_23796487-1998C3330E0013-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &#10;&#10;"/>
+    <hyperlink ref="E27" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Paul_Weiss_(philosopher)&quot; title=&quot; Wikipedia&quot;&gt;Paul WEISS&lt;/a&gt; était un philosophe américain connu pour son travail en métaphysique, esthétique, éthique et philosophie sociale, et pour son projet d’une « vision universelle » qui cherche à penser la totalité des réalités concrètes. Il a étudié avec Alfred North Whitehead et Morris Raphael Cohen, a enseigné dans plusieurs universités (notamment Yale) et a fondé la Metaphysical Society of America ainsi que la revue The Review of Metaphysics, contribuant fortement à la vie philosophique américaine du XXe siècle. &lt;/p&gt; &lt;p&gt; Il  est souvent décrit comme un métaphysicien néo-classique et un penseur de processus qui oppose au réductionnisme une réflexion sur les totalités et les finalités; il a proposé une ontologie riche où les entités concrètes, les relations et les valeurs trouvent leur place dans un système englobant. Son œuvre majeure couvre des thèmes très variés — Reality, Modes of Being, The God We Seek, You, I, and the Others — et témoigne   &lt;a href=&quot;https://www.youtube.com/watch?v=hzgN9kCruOE&quot;  title=&quot;Paul Weiss revisited par American Institute of Phlosophy&quot;&gt;d’un intérêt constant &lt;/a&gt; pour la créativité, l’art, la religion et la condition humaine, souvent traité par de vastes collections d’essais et volumes synthétiques. &lt;/p&gt; &lt;p&gt; Il  a défendu une conception qui tient ensemble l’autonomie humaine et l’insertion sociale : la liberté n’est pas pure abstraction mais se réalise dans les contextes institutionnels, moraux et artistiques qui permettent à la personne de se développer vers des fins supérieures. Esthétiquement, il a exploré la nature des arts et de la créativité, soutenant que les actes créatifs manifestent des « ultimates » ou valeurs premières qui orientent l’activité humaine vers des fins non réductibles au pragmatisme scientifique. &lt;/p&gt; &lt;p&gt; Son influence institutionnelle est importante : outre la fondation de sociétés et de revues, Weiss a laissé un corpus vaste (livres, articles, archives) qui a alimenté des débats en métaphysique et en philosophie des arts; il est considéré comme l’un des grands métaphysiciens américains du XXe siècle, reconnu par des volumes comme The Philosophy of Paul Weiss publiés dans la collection Library of Living Philosophers. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H28" r:id="rId17" display="https://www.laphilo.fr/pho/enagel-mini.webp"/>
+    <hyperlink ref="E33" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Leopoldo_Zea_Aguilar&quot; title=&quot; Wikipedia&quot;&gt;Leopoldo ZEA AGUILAR&lt;/a&gt; était un philosophe mexicain , considéré comme l'un des pères fondateurs de la philosophie latino-américaine contemporaine, engagé dans la quête d'une identité culturelle autonome face à l'eurocentrisme et au néocolonialisme. &lt;/p&gt; &lt;p&gt;  Il pose la question centrale : &quot;Peut-on construire une philosophie latino-américaine ?&quot; Réponse affirmative via une dialectique de la conscience : de la dépendance à la libération, où l'homme latino-américain réalise sa liberté par la reconnaissance de sa singularité culturelle. Relativiste culturel sans relativisme absolu, il définit l'homme comme ouvert et pluriel, rejetant l'eurocentrisme comme domination masquée ; la philosophie devient &lt;a href=&quot;https://ensayistas.org/antologia/XXA/zea/zea2.htm&quot; title=&quot;Leopoldo Zea Aguilar | Autopercepción intelectual de un proceso histórico par ensayistas&quot;&gt;&quot;instrument de libération&quot; &lt;/a&gt;, transformant l'histoire en projet éthique-politique de dignité, égalité et solidarité. Précurseur des critiques post-coloniales et postmodernes, il voit 1492 non comme &quot;découverte&quot; mais comme &quot;occultation&quot; culturelle, et la philosophie latino-américaine comme symbiose de nationalisme, christianisme et socialisme anti-impérialiste. &lt;/p&gt; &lt;p&gt; Mentor de générations, il fonde des centres intellectuels en Amérique latine et reçoit des prix mondiaux ; son discours sur la marginalité influence la philosophie de la libération et les études culturelles décoloniales. Il reste &lt;a href=&quot;https://www.youtube.com/watch?v=_kEH9wQFQv4&quot; style=&quot;color:#88A1E9&quot; title=&quot;Leopoldo Zea Aguilar | Doctorado en Educación par Miguel Morales&quot;&gt;une référence &lt;/a&gt; pour une Amérique latine unie, non utopique mais réaliste, affirmant : &quot;Se connaître égal en étant distinct est l'essence des relations humaines et internationales&quot;. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E34" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Roderick_Chisholm&quot;  title=&quot; Wikipedia&quot;&gt;Roderick CHISHOLM&lt;/a&gt; était un philosophe analytique américain reconnu pour ses travaux en épistémologie, métaphysique, philosophie de la conscience et philosophie de la perception. Il a obtenu son doctorat à l'Université de Harvard sous la tutelle de Clarence Irving Lewis et Donald C. Williams, et a enseigné pendant plus de 40 ans à l'Université Brown, après avoir aussi été professeur à Syracuse et à l'Université du Massachusetts à Amherst. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans le platonisme métaphysique de la tradition de Bertrand Russell et le rationalisme de Russell, G.E. Moore et Franz Brentano, dont il a traduit plusieurs œuvres. Il s'est opposé aux conceptions influentes de Willard Van Orman Quine, notamment contre son antiréalisme, comportementalisme et relativisme, défendant plutôt un réalisme métaphysique. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie fondationaliste de la connaissance : toutes les croyances justifiées sont soit « directement évidentes » soit soutenues par des chaînes de croyances justifiées qui finalement conduisent à des croyances directement évidentes. Il a défendu la possibilité du  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1968_num_66_90_5438_t1_0334_0000_3&quot;  title=&quot;Théory of Knowledge  par Persée&quot;&gt;knowledge empirique &lt;/a&gt; en appels à des principes épistémiques a priori, affirmant qu'il est plus raisonnable dans la plupart des situations de se confier aux sens et à la mémoire que de douter d’eux, contre les arguments sceptiques de David Hume. &lt;/p&gt; &lt;p&gt; Sa métaphysique inclut une théorie controversée de l'identité personnelle basée sur la continuité et  &lt;a href=&quot;https://www.youtube.com/watch?v=axFQjuG98AU&quot;  title=&quot;Human freedom and the self par Dillard philosophy&quot;&gt;la coïncidence des propriétés,&lt;/a&gt;  selon laquelle une personne est une substance simple et non décomposable. Il a également défendu une théorie de la volition appelée « agent causation » (causalité de l'agent), similaire à celle de Thomas Reid, et argumenté que le libre arbitre est incompatible avec le déterminisme alors que nous agissons librement - cette combinaison est connue comme  &lt;a href=&quot;https://www.youtube.com/watch?v=qLYgOxb3-E8&quot;  title=&quot;Roderick Chisholm libertarism par Philosophy et Ethics&quot;&gt;libertarianisme métaphysique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il est connu pour son ouvrage majeur Person and Object (1976), dont le titre contraste délibérément avec Word and Object de Quine, et pour sa théorie originale du pensée en première personne où les choses que nous croyons sont propriétés, et les croire est une question d'auto-attribution. Ses autres œuvres importantes incluent Perceiving (1957), Theory of Knowledge (1966, 1977, 1989), The First Person (1981), The Problem of the Criterion, et A Realist Theory of the Categories (1996). Il avait un grand respect pour l'histoire de la philosophie, contrairement à l'indifférence majoritaire des philosophes analytiques, et a contribué au renouveau de la méréologie dans les années 1970. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H34" r:id="rId20" display="https://www.laphilo.fr/pho/rchisholm-mini.webp"/>
+    <hyperlink ref="E35" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_Rawls_(philosophe)&quot;  title=&quot; Wikipedia&quot;&gt;John RAWLS&lt;/a&gt; était un  philosophe politique américain connu grâce à son œuvre majeure &quot;&lt;a href=&quot;https://www.youtube.com/watch?v=OIKwI5qu4y8&quot; style=&quot;color:#88A1E9&quot; title=&quot; La THÉORIE DE LA JUSTICE en 8 minutes ! (John RAWLS) par Culture Philo&quot;&gt; A Theory of Justice&lt;/a&gt;&quot;, publiée en 1971 ou il propose une conception de la  &lt;a href=&quot;https://www.youtube.com/watch?v=2w-AEMAU_EE&quot;  title=&quot; Le libéralisme égalitaire de John Rawls par Philoxime&quot;&gt;&quot;justice comme équité&quot;&lt;/a&gt; . Il s’oppose à l’utilitarisme – doctrine selon laquelle une action est bonne si elle maximise le bonheur collectif – et cherche au contraire à fonder la justice sur des principes garantissant équitablement les libertés et droits fondamentaux pour tous. &lt;/p&gt; &lt;p&gt;  Il imagine une &quot; &lt;a href=&quot;https://www.persee.fr/doc/rfsp_0035-2950_1991_num_41_1_394540&quot;  title=&quot;La Théorie de la justice de John Rawls. Contrat social versus utilitarisme par Persée&quot;&gt;position originelle&lt;/a&gt;&quot;, situation hypothétique où des individus rationnels, placés derrière un « voile d’ignorance » qui leur cache leurs avantages personnels, choisiraient des règles de justice justes pour tous. De cette expérience de pensée, il déduit deux principes essentiels dont le principe d’égale liberté où chaque personne doit avoir un droit égal aux libertés fondamentales et le principe de différence où les inégalités économiques et sociales ne sont justes que si elles profitent aux plus désavantagés.  &lt;/p&gt; &lt;p&gt; Il a ensuite  prolongé sa réflexion dans &quot;Political Liberalism&quot; (1993) et &quot;The Law of Peoples&quot; (1999). Dans le premier, il interroge comment un consensus moral peut se former dans des sociétés pluralistes sans imposer une doctrine particulière ; dans le second, il applique ses principes à la &lt;a href=&quot;https://www.youtube.com/watch?v=ah7y1xd3bL0&quot; title=&quot;JOHN RAWLS : Qu'est-ce que la justice sociale ? par Parole de Philosophe&quot;&gt;justice internationale&lt;/a&gt; . &lt;/p&gt; &lt;p&gt;  Il a profondément marqué la philosophie morale, politique et économique contemporaine et sa pensée inspira la théorie économique critique, avec des débats persistants sur la compatibilité de sa vision avec le libéralisme ou la social-démocratie et il demeure aujourd’hui une référence incontournable pour toute réflexion sur la justice, l’égalité et la démocratie. &lt;/p&gt; &lt;audio controls title=&quot; Avoir raison avec... John Rawls par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-13.07.2020-ITEMA_22381527-2020C35448S0195-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  "/>
+    <hyperlink ref="E36" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Kuhn&quot; title=&quot; Wikipedia&quot;&gt;Thomas KUHN&lt;/a&gt; était un philosophe et historien des sciences américain, célèbre pour son ouvrage  &lt;a href=&quot;https://apprendrelaphilosophie.com/thomas-kuhn-y-a-t-il-des-revolutions-scientifiques/&quot; title=&quot;Kuhn la sctructure des revolutions scientifiques par apprendre la philo&quot;&gt;La Structure des révolutions scientifiques &lt;/a&gt; (1962), l’un des livres les plus influents du XXᵉ siècle en philosophie des sciences. Formé d’abord en physique à Harvard avant de se tourner vers l’histoire et la philosophie des sciences, il a enseigné à Harvard, Berkeley, Princeton et au MIT, et a profondément renouvelé la façon dont on conçoit le progrès scientifique. &lt;/p&gt; &lt;p&gt; Au cœur de sa pensée se trouve le concept de paradigme : un cadre conceptuel partagé par une communauté scientifique, incluant des théories, des méthodes, des expériences canoniques et des normes de résolution de problèmes. Tant  &lt;a href=&quot;https://www.youtube.com/watch?v=_mBS4YbiYcA&quot; title=&quot;Kuhn les paradigmes par le precepteur&quot;&gt;qu’un paradigme domine, &lt;/a&gt; la science fonctionne en mode de « science normale », où les chercheurs résolvent des énigmes à l’intérieur du cadre sans remettre en cause ses fondements. &lt;/p&gt; &lt;p&gt; Il  oppose la science normale à la « science extraordinaire », qui survient quand des anomalies s’accumulent et ébranlent la confiance dans le paradigme dominant. Cela peut mener à une révolution scientifique, c’est-à-dire un changement de paradigme radical : les anciens concepts et méthodes sont abandonnés au profit d’un nouveau cadre inconciliable avec l’ancien. Il explique ainsi que le progrès scientifique n’est pas une accumulation linéaire de connaissances, mais une succession de ruptures révolutionnaires. &lt;/p&gt; &lt;p&gt; Selon lui, les paradigmes successifs ne sont pas toujours comparables de façon neutre : il parle d’« incommensurabilité » entre paradigmes, car leurs concepts, critères de validité et questions légitimes diffèrent profondément. Cela remet en cause l’idée selon laquelle la science progresse uniquement par accumulation objective et rationnelle, indépendante des contextes historiques et sociaux. &lt;/p&gt; &lt;p&gt; Sa philosophie a eu un impact bien au-delà de la science : ses idées sur les paradigmes et les révolutions ont influencé la sociologie, l’économie, les sciences politiques, la gestion et même les sciences humaines. En mettant l’accent sur les dimensions historiques, sociales et communautaires de la science, &lt;a href=&quot;https://www.youtube.com/watch?v=fV-vh9y_TQs&quot; title=&quot;Kuhn speaking par philosophy Overdoser&quot;&gt;il a ouvert la voie &lt;/a&gt;  à une épistémologie plus contextualisée, critique du positivisme logique et de l’idée d’une science totalement neutre et objective. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E37" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/John_B._Cobb&quot;  title=&quot; Wikipedia&quot;&gt;John B. COBB&lt;/a&gt; était un philosophe américain,  figure majeure de la philosophie et de la théologie du process, inspirée par Alfred North Whitehead. Issu d'une famille de missionnaires méthodistes au Japon, il a développé une vision panenthéiste où Dieu est à la fois immanent dans le monde et &lt;a href=&quot;https://books.openedition.org/pum/42552?lang=fr&quot; title=&quot;Réflexions en marge d’un livre de John B. Cobb par OpenEdition&quot;&gt;transcendant, &lt;/a&gt;  influençant profondément les débats sur l'écologie, l'économie durable et le pluralisme religieux. Son œuvre, comptant plus de 50 livres, met l'accent sur l'interdépendance de tous les êtres et la nécessité d'une éthique écologique. &lt;/p&gt; p&gt; Il rejette le théisme classique en affirmant que Dieu évolue avec les créatures, ressent leurs souffrances et n'a pas une prescience absolue des événements futurs, préservant ainsi la liberté humaine. Sa théologie &lt;a href=&quot;https://www.youtube.com/watch?v=ArXAjOlufZs&quot; title=&quot;&#10;John Cobb - Pluralisme religieux : une discussion sur le christianisme transformatif de John Cobb par Center for Process Studies&quot;&gt;du process &lt;/a&gt; voit une valeur intrinsèque en toute chose, y compris les particules comme l'électron, et critique l'anthropocentrisme chrétien traditionnel. Il intègre l'évolution comme un processus de hasard et de nécessité, influencé par Jacques Monod, tout en défendant un monde &quot;originellement bon&quot; dégradé par l'humanité. &lt;/p&gt; &lt;p&gt; Pionnier de l'éthique environnementale, il publie en 1971 &quot;Is It Too Late? A Theology of Ecology&quot;, premier ouvrage individuel sur le sujet, plaidant pour une vision écologique du christianisme. Avec Charles Birch, il coécrit &quot;The Liberation of Life&quot; en 1981, promouvant un modèle écologique contre le mécanisme biologique. &lt;/p&gt; &lt;p&gt;   Il influencera la Chine via ses idées sur la civilisation écologique et est élu en 2014 à l'Académie américaine des arts et des sciences. Il fonde aussi &quot;Progressive Christians Uniting&quot; pour une foi progressiste et engagée socialement. &lt;/p&gt; "/>
+    <hyperlink ref="E39" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Stanley_Cavell&quot;  title=&quot; Wikipedia&quot;&gt;Stanley CAVELL&lt;/a&gt; était un philosophe américain connu pour avoir renouvelé la philosophie du langage ordinaire, la philosophie morale et l’esthétique, notamment à partir de Wittgenstein, Austin, Emerson, Thoreau et du cinéma hollywoodien. Sa pensée est moins centrée sur des systèmes que sur une réflexion vivante sur l’ordinaire, le scepticisme, la voix personnelle et la manière dont la philosophie peut parler à partir de &lt;a href=&quot;https://www.youtube.com/watch?v=bWMncAAj16c&quot; title=&quot; Stanley Cavell par Film &amp; media&quot;&gt;l’expérience vécue. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Il s’intéresse d’abord au langage quotidien, parce qu’il pense que les difficultés philosophiques ne viennent pas seulement d’un manque d’informations, mais d’un trouble plus profond dans notre rapport au monde et aux autres. Pour lui, &lt;a href=&quot;https://www.youtube.com/watch?v=5q50IwBAUKY&quot; title=&quot; Stanley Cavell par philo overdose&quot;&gt;le scepticisme &lt;/a&gt; n’est pas seulement un problème de connaissance, c’est aussi une expérience humaine et parfois tragique : nous pouvons nous sentir séparés du monde, d’autrui, voire de nous-mêmes. &lt;/p&gt; &lt;p&gt; Un thème central chez lui est donc la reconnaissance. Il ne s’agit pas simplement de « savoir » que l’autre existe, mais d’apprendre à le reconnaître, à répondre à sa présence, et à accepter que nos relations humaines comportent toujours une part d’incertitude. C’est pourquoi Cavell relie souvent la philosophie à l’éthique, à la vie quotidienne et aux formes concrètes de l’attention aux autres. &lt;/p&gt; &lt;p&gt; Il est aussi célèbre pour son travail sur le cinéma, qu’il ne considère pas comme un divertissement secondaire mais comme un véritable lieu de pensée. À travers les comédies hollywoodiennes, notamment les « comédies de remariage », il explore des questions de couple, de séparation, de pardon et de seconde chance, c’est-à-dire des problèmes philosophiques aussi bien que narratifs.  &lt;/p&gt; &lt;p&gt; Il est lié à une idée très américaine de la philosophie : une philosophie qui n’oppose pas rigidement le savant et le populaire, qui peut être autobiographique, littéraire et morale à la fois. Son originalité tient à cela : il transforme la philosophie en une &lt;a href=&quot;https://www.liberation.fr/debats/2018/06/20/stanley-cavell-the-end_1660627/&quot; title=&quot; Stanley Cavell par liberation&quot;&gt; enquête sur la vie &lt;/a&gt; ordinaire, les formes de notre voix, et la possibilité de devenir plus juste envers soi-même et envers les autres.  &lt;/p&gt; &#10;&lt;audio controls title=&quot;la pensée américaine Stanley Cavell par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-05.11.2012-ITEMA_20417072-2012C12410S0310-NET_B1E428CD-7648-4739-933D-4C419F0B94C8_FC-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &#10;"/>
+    <hyperlink ref="H39" r:id="rId25" display="https://www.laphilo.fr/pho/scavell-mini.webp"/>
+    <hyperlink ref="H40" r:id="rId26" display="https://www.laphilo.fr/pho/mrothbard-mini.webp"/>
+    <hyperlink ref="H41" r:id="rId27" display="https://www.laphilo.fr/pho/ewiesel-mini.webp"/>
+    <hyperlink ref="H42" r:id="rId28" display="https://www.laphilo.fr/pho/abracken-mini.webp"/>
+    <hyperlink ref="E43" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Rorty&quot; title=&quot; Wikipedia&quot;&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href=&quot;https://www.youtube.com/watch?v=lfx4Jag1ic4&quot;  title=&quot;Le pragmatisme : définition, exemples par le savoir partagé&quot;&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href=&quot;https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism&quot; title=&quot; a bas l'autorité par laviedesidees&quot;&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas &quot;vrais&quot; ou &quot;faux&quot;. &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales , on trouve  &lt;a href=&quot;https://www.youtube.com/watch?v=MgU0dXZ3umM&quot; title=&quot;L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli&quot;&gt;&quot; Contingence, ironie et solidarité &quot;&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans &quot; Achieving Our Country&quot; (1998),  il y appelle la gauche américaine à abandonner le &quot;culturalisme&quot; pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la &quot;post-vérité&quot;. Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; "/>
+    <hyperlink ref="E45" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Charles_Parsons_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Charles Dacre PARSONS&lt;/a&gt; était un philosophe américain connu pour ses travaux en philosophie des mathématiques et en philosophie de Kant. Il a enseigné à Columbia puis à Harvard, où il est devenu professeur émérite. Il s’est formé à Harvard, avec une thèse dirigée par Willard Van Orman Quine, ce qui le place au croisement de la logique, de la philosophie analytique et des fondements des mathématiques. Son parcours intellectuel a été marqué très tôt par la rigueur mathématique, puisqu’il avait d’abord étudié les mathématiques avant de se tourner vers la philosophie. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la philosophie des mathématiques, domaine dans lequel il a travaillé sur la nature des objets mathématiques, la logique, la preuve et l’interprétation constructive des mathématiques prédicatives. Il a aussi beaucoup écrit sur Frege, Gödel, Hilbert et Quine, en lisant ces auteurs à la fois comme philosophes et comme figures majeures des fondements. &lt;/p&gt; &lt;p&gt; Il n’était pas seulement un spécialiste de logique ; il a aussi produit des travaux importants sur Kant, montrant comment les questions de connaissance, d’expérience et de structure de l’esprit se relient aux mathématiques. Cette double compétence, en philosophie des mathématiques et en histoire de la philosophie, explique pourquoi il est souvent vu comme un auteur à la fois technique et très large dans ses intérêts.&lt;/p&gt; &lt;p&gt; Son influence est restée forte dans le monde anglophone, au point d’être décrit comme l’un des philosophes des mathématiques les plus importants de sa génération. En plus de ses livres et articles, il a aussi contribué à l’édition de textes posthumes de Gödel, ce qui a renforcé son rôle dans l’étude contemporaine des fondements des mathématiques. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="I45" r:id="rId31" display="https://www.laphilo.fr/photo/cparsons.webp"/>
+    <hyperlink ref="H47" r:id="rId32" display="https://www.laphilo.fr/pho/dihde-mini.webp"/>
+    <hyperlink ref="E49" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edward_Sa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Edward SAÏD&lt;/a&gt; était un intellectuel palestinien-américain, critique littéraire et professeur de littérature anglaise et comparée à l’université Columbia de New York. D’origine palestinienne et né à Jérusalem, il a grandi entre l’Égypte, les États-Unis et l’Europe, une expérience de déplacement qui a profondément marqué sa pensée sur l’identité, la colonisation et l’altérité.  &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est l’essai &lt;a href=&quot;https://www.youtube.com/watch?v=Ne4WRykmjhA&quot; title=&quot;Edward Said  Orientalisme par HD Doc&quot;&gt;L’Orientalisme : &lt;/a&gt;  L’Orient créé par l’Occident* (1978), considéré comme le texte fondateur des postcolonial studies. Dans cet ouvrage, Saïd montre que l’« Orient » n’est pas une réalité objective mais une invention de l’Occident : un discours façonné par des siècles de domination coloniale pour mieux contrôler et représenter l’Autre. &lt;/p&gt; &lt;p&gt; Pour lui, l’orientalisme est à la fois un savoir et un outil de pouvoir : il ne s’agit pas seulement de décrire l’Orient, mais de le hiérarchiser, de l’essentialiser et de le rendre  &lt;a href=&quot;https://www.youtube.com/watch?v=QBj-yWLnayM&quot; title=&quot;Edward Said writings on Orientalism par Middle East Eye&quot;&gt; inférieur à l’Occident. &lt;/a&gt; Il analyse quatre thèses principales : la domination politique et culturelle de l’Orient par l’Occident, la dépréciation de la langue arabe, la diabolisation de l’arabe et de l’islam, et la défense de la cause palestinienne. &lt;/p&gt; &lt;p&gt; Sa pensée articule critique littéraire, histoire, philosophie et sciences politiques, en s’inspirant notamment de Michel Foucault (discours–pouvoir) et de Jacques Derrida (déconstruction). Il montre que la violence du colonialisme n’est pas seulement matérielle (conquête, pillage), mais aussi épistémique : une violence de la raison qui classe, essentialise et dévalue les « Autres » de l’Occident. &lt;/p&gt; &lt;p&gt;  Intéressé par &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Edward-W-Said-1935-2003.html&quot; title=&quot;Edward Said par lesclesdumoyenorient&quot;&gt; l’engagement politique, &lt;/a&gt; il a aussi défendu la cause palestinienne et la légitimité des revendications d’autodétermination du peuple palestinien, tout en reconnaissance du droit à une patrie juive. Il rejetait le repli identitaire et prônait une vision universelle qui défend les différences et les droits, tissant des liens entre classicisme et excentricité, histoire et actualité. &lt;/p&gt;  &lt;audio controls title=&quot;Edward Said, une conscience morale par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-08.12.2017-ITEMA_21518070-2017C19327S0342-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &#10;&#10;&#10;"/>
+    <hyperlink ref="H49" r:id="rId34" display="https://laphilo.fr/pho/esaid-mini.webp"/>
+    <hyperlink ref="H50" r:id="rId35" display="https://www.laphilo.fr/pho/rmadams-mini.webp"/>
+    <hyperlink ref="E51" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Nozick&quot;  title=&quot; Wikipedia&quot;&gt;Robert NOZICK&lt;/a&gt; était un philosophe américain connu pour &lt;a href=&quot;https://www.youtube.com/watch?v=Q-t3cpFAk4o&quot;  title=&quot; Libertarianisme par Vadim Media&quot;&gt; son libertarianisme &lt;/a&gt; et sa critique des théories égalitaristes comme celle de John Rawls. Professeur à Harvard, il a marqué la philosophie politique, morale et épistémologique par son œuvre principale, Anarchie, État et utopie (1974), qui défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Minarchisme&quot;  title=&quot; Minarchisme par Wikipédia&quot;&gt; Etat Minimal. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il argue que seul l'État minimal, ou &quot;État gardien de nuit&quot;, est légitime, car il se limite à protéger les individus contre la force, la fraude et le vol, sans redistribuer les richesses. Il rejette l'anarcho-capitalisme en montrant, via des agences de protection privée, comment un État dominant émerge naturellement pour monopoliser la coercition légitime, justifié par le droit naturel à la personne. &lt;/p&gt; &lt;p&gt; Contrairement à la justice distributive de Rawls, il propose une théorie de l'entitlement : une acquisition initiale juste et des transferts volontaires rendent la distribution légitime, sans besoin d'égalisation par l'État. Toute intervention redistributive viole les droits individuels, traitant les personnes comme des moyens plutôt que des fins, en écho à Kant. &lt;/p&gt; &lt;p&gt; Dans Anarchie, État et utopie, Il réfute l'utilitarisme via l'expérience de pensée de la &lt;a href=&quot;https://www.youtube.com/watch?v=2FVwXaNWPQ0&quot;  title=&quot; La machine à expérience par Monsieur Phi&quot;&gt;&quot;machine à expérience&quot; :&lt;/a&gt;  même si elle offre un bonheur parfait et indistinguable de la réalité, les gens préfèrent vivre des actions réelles et façonner leur identité plutôt que des simulations. Cela prouve que le bonheur n'est pas le seul bien suprême. &lt;/p&gt; &lt;p&gt; Plus tard, dans Explications philosophiques (1981), il développe une théorie du suivi (tracking theory) en épistémologie, où la connaissance repose sur des conditionnels contrefactuels fiables, contournant le scepticisme sans justification traditionnelle. Son anti-coercitivisme intellectuel invite à une philosophie ouverte, non imposée. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Qui a peur des Libertariens par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-14.06.2022-ITEMA_23058436-2022C12410S0165-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;"/>
+    <hyperlink ref="H57" r:id="rId37" display="https://www.laphilo.fr/pho/imyoung-mini.webp"/>
+    <hyperlink ref="H58" r:id="rId38" display="https://www.laphilo.fr/pho/bhooks-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2237,7 +2237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD76"/>
+  <dimension ref="A1:XFD81"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
@@ -5775,6 +5775,291 @@
       <c r="P76" t="inlineStr">
         <is>
           <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1">
+        <v>1880</v>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1973</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880 – 1973</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roy Wood SELLARS</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Roy_Wood_Sellars" title=" Wikipedia"&gt;Roy Wood SELLARS&lt;/a&gt; est un philosophe américain d’origine canadienne. Né en 1880 dans l’Ontario, il grandit dans le Michigan, où son père est médecin de campagne, et fait presque toute sa carrière à l’université du Michigan, à Ann Arbor. Il est le père du philosophe Wilfrid Sellars. Au début du XXe siècle, alors que l’idéalisme domine encore les universités américaines, il fait partie de ceux qui veulent revenir à un &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_%28philosophie%29" title=" Wikipedia"&gt;réalisme&lt;/a&gt; compatible avec les sciences.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Critical Realism&lt;/em&gt; (1916), puis dans un ouvrage collectif de 1920, il défend le « réalisme critique » : nous percevons bien des choses qui existent indépendamment de nous, mais à travers des contenus mentaux qui ne sont pas les choses elles-mêmes. Contre le réalisme naïf, la perception est une interprétation ; contre l’idéalisme, elle nous fait réellement connaître le monde. Dans &lt;em&gt;Evolutionary Naturalism&lt;/em&gt; (1922), il propose un matérialisme non réducteur : la nature produit, au cours de l’évolution, des niveaux d’organisation nouveaux, la vie puis l’esprit, qui ont leurs propres propriétés, sans rien de surnaturel. L’esprit n’est pas une substance à part : il est le cerveau lui-même, considéré à son niveau le plus élevé d’organisation.&lt;/p&gt; &lt;p&gt;Sellars applique ce naturalisme à la religion : dans &lt;em&gt;The Next Step in Religion&lt;/em&gt; (1918), il propose une religion sans Dieu, tournée vers l’accomplissement humain. Il est en 1933 le principal rédacteur du &lt;em&gt;Manifeste humaniste&lt;/em&gt;, qui défend un humanisme religieux sans surnaturel, et signe le second manifeste en 1973. Il meurt à Ann Arbor la même année, à quatre-vingt-treize ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rwsellars-mini.webp</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K77" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturalisme ; Réalisme ; Émergentisme</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe américain d’origine canadienne, théoricien du réalisme critique et du naturalisme évolutionniste.</t>
+        </is>
+      </c>
+      <c r="N77" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O77" s="1"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1">
+        <v>1912</v>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1989</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1912 – 1989</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wilfrid SELLARS</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Wilfrid_Sellars" title=" Wikipedia"&gt;Wilfrid SELLARS&lt;/a&gt; est un philosophe américain, l’un des plus profonds de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; du XXe siècle. Né en 1912 à Ann Arbor, fils du philosophe Roy Wood Sellars, il étudie au Michigan, à Buffalo puis à Oxford. Il enseigne au Minnesota, à Yale, et à partir de 1963 à l’université de Pittsburgh, où il fait école. Avec Herbert Feigl, il fonde en 1950 la revue &lt;em&gt;Philosophical Studies&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Dans « Empirisme et philosophie de l’esprit » (1956), il s’attaque au « mythe du donné » : l’idée, commune aux empiristes, que notre connaissance repose sur des données des sens que nous saisirions immédiatement, sans concepts. Pour Sellars, voir que quelque chose est rouge, c’est déjà savoir ce qu’est le rouge et être capable de le justifier. La connaissance appartient à l’« espace logique des raisons », où l’on donne et demande des justifications, et non à un simple contact causal avec le monde. Même l’observation la plus simple suppose tout un langage et tout un savoir, appris avec lui.&lt;/p&gt; &lt;p&gt;Dans « La philosophie et l’image scientifique de l’homme » (1962), il oppose l’« image manifeste », celle du monde de la vie quotidienne, peuplé de personnes, de couleurs et d’intentions, et l’« image scientifique », faite de particules et de processus. La tâche de la philosophie est de les unir en une seule vision. Pour lui, la science est « la mesure de toutes choses ». Il meurt à Pittsburgh en 1989. Longtemps jugé difficile, il est aujourd’hui l’un des philosophes américains les plus étudiés. Ses idées inspirent Richard Rorty, Robert Brandom et John McDowell.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/wsellars-mini.webp</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; metaphysique ; langage</t>
+        </is>
+      </c>
+      <c r="K78" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Réalisme scientifique</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe américain, critique du « mythe du donné » et penseur de l’« image scientifique » de l’homme.</t>
+        </is>
+      </c>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O78" s="1">
+        <v>2</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1">
+        <v>1924</v>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2013</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1924 – 2013</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arthur DANTO</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arthur_Danto" title=" Wikipedia"&gt;Arthur DANTO&lt;/a&gt; est un philosophe et critique d’art américain. Né en 1924 à Ann Arbor, il grandit à Detroit, sert pendant la Seconde Guerre mondiale en Afrique du Nord et en Italie, puis étudie l’art et la philosophie. D’abord graveur, il enseigne à l’université Columbia, à New York, de 1951 à 1992. Ses premiers livres portent sur la philosophie de l’histoire, où il étudie les « phrases narratives », qui décrivent un événement à la lumière de ce qui l’a suivi, et sur Nietzsche, qu’il fait connaître aux philosophes analytiques.&lt;/p&gt; &lt;p&gt;En 1964, il voit exposées les &lt;em&gt;Brillo Boxes&lt;/em&gt; d’Andy Warhol, des boîtes identiques à celles des supermarchés. Pourquoi l’une est-elle une œuvre d’art, et l’autre non, alors qu’on ne peut pas les distinguer à l’œil ? Dans l’article « Le monde de l’art », il répond que ce qui fait l’œuvre n’est pas une propriété visible, mais une théorie et une histoire de l’art, une atmosphère que seul connaît ce « monde de l’art ». Dans &lt;em&gt;La Transfiguration du banal&lt;/em&gt; (1981), il précise : une œuvre d’art est toujours à propos de quelque chose, et elle incarne ce sens, ce qui la distingue d’une simple chose.&lt;/p&gt; &lt;p&gt;Il en tire en 1984 la thèse de la « fin de l’art » : non que l’on cesse de créer, mais l’art, depuis Warhol, n’a plus d’histoire orientée, et tout est désormais possible. C’est à la &lt;a href="https://fr.wikipedia.org/wiki/Esth%C3%A9tique" title=" Wikipedia"&gt;philosophie&lt;/a&gt;, et non plus à l’art, de dire ce qu’est l’art. Critique d’art à l’hebdomadaire &lt;em&gt;The Nation&lt;/em&gt; de 1984 à 2009, il est l’un des esthéticiens les plus lus de son temps. Il meurt à New York en 2013.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/danto-mini.webp</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K79" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et critique d’art américain, théoricien du « monde de l’art » et de la fin de l’art.</t>
+        </is>
+      </c>
+      <c r="N79" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O79" s="1">
+        <v>2</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1">
+        <v>1929</v>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1929 – 2023</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Harry FRANKFURT</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Harry_Frankfurt" title=" Wikipedia"&gt;Harry FRANKFURT&lt;/a&gt; est un philosophe américain. Né en 1929 à Langhorne, en Pennsylvanie, il étudie à l’université Johns-Hopkins et enseigne à l’université Rockefeller, à Yale, puis à Princeton jusqu’en 2002. Spécialiste de Descartes, il devient surtout l’un des penseurs majeurs de la liberté, de la responsabilité et de la personne, dans un style d’une grande clarté.&lt;/p&gt; &lt;p&gt;En 1969, il imagine des cas, appelés depuis « cas de Frankfurt », pour contester l’idée qu’on n’est responsable d’un acte que si l’on aurait pu agir autrement. Un neurologue malveillant est prêt à intervenir dans le cerveau de Jones pour le forcer à agir, mais Jones fait de lui-même ce qu’on attendait, sans intervention : il est responsable, bien qu’il n’ait pas eu d’autre possibilité. En 1971, il définit la personne par les « désirs de second ordre » : nous ne voulons pas seulement des choses, nous voulons aussi avoir ou ne pas avoir certains désirs. Être libre, c’est agir selon les désirs que l’on approuve. Ces idées font de lui l’un des grands défenseurs du &lt;a href="https://fr.wikipedia.org/wiki/Compatibilisme" title=" Wikipedia"&gt;compatibilisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Son petit essai &lt;em&gt;De l’art de dire des conneries&lt;/em&gt;, écrit en 1986 et publié en livre en 2005, devient un best-seller : le baratineur est plus dangereux que le menteur, car le menteur se soucie encore de la vérité pour la cacher, alors que le baratineur y est indifférent. Dans &lt;em&gt;Les Raisons de l’amour&lt;/em&gt; (2004), il montre que c’est ce que nous aimons qui donne sens à notre vie. Dans &lt;em&gt;On Inequality&lt;/em&gt; (2015), il soutient que l’important n’est pas que chacun ait autant, mais que chacun ait assez. Il meurt à Santa Monica en 2023.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/frankfurt-mini.webp</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; metaphysique</t>
+        </is>
+      </c>
+      <c r="K80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compatibilisme</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe américain de la liberté et de la personne, auteur de « De l’art de dire des conneries ».</t>
+        </is>
+      </c>
+      <c r="N80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O80" s="1">
+        <v>2</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1">
+        <v>1929</v>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1929 – 2024</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newton DA COSTA</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Newton_da_Costa" title=" Wikipedia (en)"&gt;Newton DA COSTA&lt;/a&gt; est un logicien et philosophe brésilien, l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/Logique_paraconsistante" title=" Wikipedia"&gt;logique paraconsistante&lt;/a&gt;. Né en 1929 à Curitiba, il étudie d’abord le génie civil puis les mathématiques, et enseigne à l’université fédérale du Paraná, puis à l’université de São Paulo et à l’université fédérale de Santa Catarina.&lt;/p&gt; &lt;p&gt;Dans la logique classique, une seule contradiction suffit à tout prouver : si l’on admet à la fois une proposition et sa négation, on peut en déduire n’importe quoi. C’est le principe d’« explosion ». Dès sa thèse de 1963, da Costa construit des systèmes logiques, appelés « calculs C », où l’on peut admettre certaines contradictions sans que toute la théorie s’effondre. Le nom de « paraconsistance » leur est donné en 1976 par le philosophe péruvien Francisco Miró Quesada. Ces logiques permettent de raisonner rigoureusement sur des informations contradictoires, comme celles d’une base de données, d’un témoignage ou d’une théorie scientifique en crise.&lt;/p&gt; &lt;p&gt;Da Costa étend ces travaux à la théorie des ensembles et à la philosophie des sciences. Avec Steven French, il développe la notion de « quasi-vérité » : une théorie scientifique peut être partiellement vraie et utile sans être entièrement exacte. Membre de nombreuses académies, il a formé une importante école de logique au Brésil et en Amérique latine. Il meurt en 2024 à Florianópolis.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dacosta-mini.webp</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K81" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logique paraconsistante</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logicien brésilien, l’un des fondateurs des logiques paraconsistantes.</t>
+        </is>
+      </c>
+      <c r="N81" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brésilienne</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -3267,8 +3267,7 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Samuel_Ramos"  title=" Wikipedia"&gt;Samuel RAMOS&lt;/a&gt; était un philosophe mexicain  précurseur de la philosophie de la mexicanité qui analyse le caractère national mexicain à travers une approche psychologique et historiciste. &lt;/p&gt; &lt;p&gt; Il applique le perspectivisme d'Ortega y Gasset et la psychologie adlérienne : le Mexicain souffre d'un complexe d'infériorité structurel se manifestant par dissimulation, susceptibilité, phallocratie et idéalisme primitif. Critique du positivisme porfirien, il lie philosophie à révolution mexicaine  en 1910, murale (Rivera) et Ateneo de la Juventud (Caso, Vasconcelos), prônant une culture créole authentique plutôt que folklorique ou importée. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://fr.slideshare.net/slideshow/samuel-ramos-hacia-un-nuevo-humanismo/15149441"  title="Samuel ramos hacia un nuevo humanismo par slideshare"&gt;Son projet &lt;/a&gt;: construire une "culture à la hauteur du monde civilisé" via éducation et réflexion existentielle, évitant à la fois servilité et isolationnisme. Précurseur de Hiperión (1950, avec Zea, Uranga, Villoro), il fonde l'étude de l'"être mexicain", influençant Paz (Labyrinthe de la solitude), Zea et la philosophie de la libération ; sa quête d'identité universelle mais située ouvre à la décolonialité. &lt;/p&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Samuel_Ramos"  title=" Wikipedia"&gt;Samuel RAMOS&lt;/a&gt; (1897-1959) est un philosophe mexicain, pionnier de la réflexion sur l’identité et la culture du Mexique. Élève d’Antonio Caso, il enseigne à l’Université nationale autonome du Mexique, où il forme plusieurs générations de philosophes. Il est l’un des premiers à se demander ce que peut être une philosophie proprement mexicaine.&lt;/p&gt; &lt;p&gt;Son livre le plus célèbre, &lt;em&gt;Le Profil de l’homme et de la culture au Mexique&lt;/em&gt; (1934), applique au caractère national deux outils venus d’Europe : la philosophie de José Ortega y Gasset, pour qui toute pensée part d’une situation concrète, et la psychologie d’Alfred Adler, qui étudie le sentiment d’infériorité. Ramos soutient que le Mexicain, depuis la conquête et la colonisation, souffre d’un complexe d’infériorité face à l’Europe. Ce complexe se cache derrière des attitudes de compensation : la susceptibilité, la méfiance, le machisme ou l’imitation des modèles étrangers, qu’il appelle une « imitation extralogique ». Il ne s’agit pas pour lui de condamner son peuple, mais de l’aider à prendre conscience de lui-même pour se libérer. Le Mexique doit construire une culture authentique, ni simple copie de l’Europe ni folklore replié sur lui-même, qui assume son histoire tout en s’ouvrant à l’universel. Il écrit aussi la première &lt;em&gt;Histoire de la philosophie au Mexique&lt;/em&gt; (1943). Dans &lt;a href="https://fr.slideshare.net/slideshow/samuel-ramos-hacia-un-nuevo-humanismo/15149441"  title="Samuel ramos hacia un nuevo humanismo par slideshare"&gt;&lt;em&gt;Vers un nouvel humanisme&lt;/em&gt;&lt;/a&gt; (1940), il défend une conception de l’homme qui unit la raison, les valeurs et la culture.&lt;/p&gt; &lt;p&gt;Son œuvre ouvre la voie au groupe Hiperión, à Leopoldo Zea et à Octavio Paz, auteur du &lt;em&gt;Labyrinthe de la solitude&lt;/em&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F25" s="7" t="s">

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2346,8 +2346,11 @@
       <c r="D4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>21</v>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Juana_In%C3%A9s_de_la_Cruz" title=" Wikipedia"&gt;Juana Inès de la CRUZ&lt;/a&gt; était une religieuse et intellectuelle mexicaine, à la fois religieuse, poétesse, dramaturge et défenseure du droit des femmes à apprendre. Elle est aujourd’hui souvent considérée comme une pionnière du féminisme dans le monde hispanique.  &lt;/p&gt; &lt;p&gt;Elle écrit dans un castillan baroque raffiné et est souvent considérée comme la première grande poétesse des Amériques et une autrice majeure du Siècle d’or espagnol. &lt;a href="https://www.youtube.com/watch?v=_k9zqeg-as4"  title="
+Les œuvres de Sor Juana Inés de la Cruz avec Paloma Celis Carbajal par The New York Public Library"&gt;Son œuvre&lt;/a&gt; comprend des poèmes lyriques et philosophiques, des pièces de théâtre, des autos sacramentales (drames religieux) et des textes en prose.​ Parmi ses textes les plus célèbres figurent le long poème philosophique souvent appelé "Premier rêve" et la lettre "Réponse à Sor Filotea", où elle défend avec force le droit des femmes au savoir. Elle aborde aussi des questions religieuses, morales et politiques, tout en critiquant l’hypocrisie et la misogynie de son époque. &lt;/p&gt; &lt;p&gt; Son  &lt;a href="https://www.persee.fr/doc/carav_1147-6753_1996_num_67_1_2706" title="Sor Juana Inés de la Cruz, une expression des élites culturelles mexicaines du XVIIe siècle par Persée"&gt;prestige littéraire&lt;/a&gt; et ses prises de position lui attirent toutefois l’hostilité de certains responsables ecclésiastiques, notamment après sa critique d’un célèbre prédicateur jésuite dans une lettre privée rendue publique en 1690. Sous la pression, elle doit renoncer à ses études, vendre sa bibliothèque et ses instruments, et se consacrer à la vie de charité au couvent.&lt;/p&gt; Enfant prodige, elle apprend à lire à trois ans, et brille à la cour du vice-roi de Nouvelle-Espagne. Elle choisit d’entrer au couvent en 1669 pour pouvoir étudier librement. Elle meurt en 1695 en soignant ses sœurs pendant une épidémie. Octavio Paz lui a consacré un grand livre, &lt;em&gt;Sor Juana ou les pièges de la foi&lt;/em&gt; (1982).  &lt;audio controls title="Sor Juana Inés de la Cruz (vers 1648-1695) par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10199-23.07.2007-ITEMA_20079535-2001C3330E0007-NET_8F3A18C1-7AB9-4319-AC9B-65A0B3536765_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F4" s="7" t="s">
         <v>22</v>
@@ -2501,8 +2504,11 @@
       <c r="D7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>44</v>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ralph_Waldo_Emerson"   title=" Wikipedia"&gt;Ralph Waldo EMERSON&lt;/a&gt; était un philosophe américain  souvent considéré comme le père du  &lt;a href="https://fr.wikipedia.org/wiki/Transcendantalisme_(%C3%89tats-Unis)" title="transcendantalisme par Wikipedia"&gt;transcendantalisme. &lt;/a&gt; Philosophe, essayiste et poète, il a cherché à donner à la pensée américaine une voix autonome, indépendante des modèles européens. &lt;/p&gt; &lt;p&gt; Sa philosophie repose d’abord sur l’idée que la vérité se &lt;a href="https://www.youtube.com/watch?v=lde_E9cGtk8" title="citation Emerson par Murmures d’Or"&gt;découvre par l’intuition, &lt;/a&gt;  l’expérience intérieure et le contact avec la nature, plutôt que par la tradition ou l’autorité. Dans Nature, il défend une relation directe et vivante avec le monde naturel, qui permet à l’individu de se renouveler spirituellement. &lt;/p&gt; &lt;p&gt; Il  insiste aussi sur la confiance en soi et le non-conformisme. Dans Self-Reliance et The American Scholar, il invite chacun à &lt;a href="https://www.youtube.com/watch?v=OZXsWkEy5tY" title="la conduite de la vie par rares livres"&gt;penser par lui-même, &lt;/a&gt;  à ne pas imiter les autres et à forger son propre chemin intellectuel. Pour lui, une personne libre doit suivre sa voix intérieure plutôt que les attentes de la société.  &lt;/p&gt; &lt;p&gt; Il était  un philosophe de l’autonomie, de la nature et de l’élévation de l’individu. Son influence est immense, car il a donné une base spirituelle et intellectuelle à l’idée d’une culture américaine originale, fondée sur la liberté de penser et la confiance en l’esprit humain. Pasteur unitarien à Boston, il quitte l’Église en 1832, voyage en Europe, puis s’installe à Concord, où il accueille le jeune Thoreau. En 1838, son discours aux étudiants en théologie de Harvard, qui invite chacun à trouver Dieu en lui-même plutôt que dans les Églises, fait scandale. Il parle d’une « âme supérieure », présente en chaque être. Nietzsche, son lecteur passionné, et le poète Walt Whitman lui doivent beaucoup. &lt;/p&gt; 
+ &lt;audio controls title="Ralph Waldo Emerson, le premier intellectuel de l’Amérique  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-25.04.2022-ITEMA_23005785-2022C12410S0115-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F7" s="7" t="s">
         <v>45</v>
@@ -3226,8 +3232,10 @@
       <c r="D24" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>206</v>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Hartshorne"  title=" Wikipedia"&gt;Charles HARTSHORNE&lt;/a&gt; était un philosophe américain spécialiste de la philosophie de la religion et de la métaphysique. Il est surtout connu pour avoir développé la philosophie du processus &lt;a href="https://en.wikipedia.org/wiki/Alfred_North_Whitehead" title="d'Alfred North Whitehead par Wikipedia"&gt;d'Alfred North Whitehead&lt;/a&gt; en une théologie du processus, ou panenthéisme. Né dans une famille quaker et fils d'un ministre épiscopalien, il a étudié à Harvard et en Europe auprès de figures comme Husserl et Heidegger. &lt;/p&gt; &lt;p&gt; Il  &lt;a href="https://www.youtube.com/watch?v=s59DOhnuMwI" title="Charles Hartshorne Lecture - The Idea of Dual Transcendence, 1986 par Center for Process Studies"&gt;conçoit Dieu&lt;/a&gt; comme bipolaire : à la fois éternel et temporel, affecté par le monde tout en l'influençant, rejetant l'idée d'un Dieu immuable et omnipotent classique. Il a reformulé l'argument ontologique d'Anselme en une version modale, qu'il jugeait valide, et qui a relancé les débats des logiciens sur cette preuve. Ses &lt;a href="https://www.religion-online.org/article/the-philosophy-of-charles-hartshorne/"  title="The Philosophy of Charles Hartshorne par religion online"&gt;œuvres majeures&lt;/a&gt; incluent "The Divine Relativity  paru en 1948, "The Logic of Perfection" en 1962 et "Omnipotence and Other Theological Mistakes"  paru en 1983. &lt;/p&gt; &lt;p&gt;  Il a présidé l'American Philosophical Association et la Metaphysical Society of America, étendant son influence à la théologie, la psychologie et au-delà. Sa pensée met l'accent sur la créativité, le devenir et l'interdépendance universelle, critiquant des notions comme la via negativa. Assistant de Whitehead à Harvard, il a aussi édité avec Paul Weiss les œuvres de Charles Sanders Peirce, contribuant à faire connaître ce grand logicien. Ornithologue passionné, il a consacré un livre au chant des oiseaux, &lt;em&gt;Born to Sing&lt;/em&gt; (1973), où il soutient que les oiseaux chantent aussi par plaisir esthétique. Il est mort en 2000, à cent trois ans. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F24" s="7" t="s">
         <v>207</v>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2550,8 +2550,10 @@
       <c r="D8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>55</v>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Juan_Bautista_Alberdi"   title=" Wikipedia"&gt;Juan Bautista ALBERTI&lt;/a&gt;    était un philosophe, écrivain et juriste argentin, père intellectuel de la Constitution argentine, un texte visionnaire qui a posé les bases d’un État moderne. C’est en Europe, où il voyage dans les années 1830, qu’il forge sa pensée. Il y découvre les idées libérales, le fédéralisme et l’importance d’une constitution solide. De retour en Amérique du Sud, il s’installe au Chili, où il observe avec inquiétude les luttes de pouvoir entre unitaires et fédéralistes en Argentine. &lt;/p&gt; &lt;p&gt; En 1852, après la chute de Rosas, Alberdi publie son œuvre majeure : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=SztYiPA63Xk" title="Biografías - Juan Bautista Alberdi "El Arquitecto de la Argentina Moderna" par PipaProfe"&gt;"Bases y puntos de partida para la organización política de la República Argentina"&lt;/a&gt;. Ce texte, rédigé depuis son exil chilien, devient la pierre angulaire de la future Constitution.  Ses propositions sont révolutionnaires pour l’époque car il propose un système fédéral équilibré, pour éviter les guerres civiles, la promotion de l’immigration européenne pour peupler et développer le pays et surtout la liberté de commerce et la séparation des pouvoirs. La Constitution de 1853 s’en inspire largement, et bien que modifiée depuis, elle reste le socle institutionnel de l’Argentine. &lt;/p&gt; &lt;p&gt; Pourtant, il ne fait pas l’unanimité. Ses idées libérales et son opposition à la centralisation de Buenos Aires le mettent en conflit avec des figures comme Bartolomé Mitre et Domingo Faustino Sarmiento. Quand la guerre de la Triple Alliance (1865-1870) éclate contre le Paraguay, il la dénonce comme une "guerre fratricide", ce qui le marginalise encore davantage. Il passe ses dernières années en Europe, loin des cercles du pouvoir. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F8" s="7" t="s">
         <v>56</v>
@@ -2637,7 +2639,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Sanders_Peirce" title=" Wikipedia"&gt;Charles Sanders PEIRCE&lt;/a&gt;  était un philosophe, logicien, scientifique américain assez original, fondateur du  &lt;a href="https://www.youtube.com/watch?v=AGHmKg7wYf0"  title="Pragmatisme  par robertus"&gt;pragmatisme&lt;/a&gt;, père de la sémiotique moderne (théorie des signes) et un pionnier de la logique. Pourtant, en raison de  &lt;a href="https://laviedesidees.fr/Chevalier-Peirce-ou-l-invention-de-l-epistemologie" style="color:#88A1E9" title="les pepites de Charles s pierce par laviedesidees"&gt;sa personnalité difficile&lt;/a&gt; et de ses idées avant-gardistes, il vécut en marge du monde académique, mourant dans la pauvreté et l'isolement. &lt;/p&gt; &lt;p&gt;  Il cherchait à identifier les catégories les plus fondamentales et universelles de la pensée et de l'être, qu'il nomma Phanéroscopie.Il en déduit trois, présentes dans tous les phénomènes. Elles sont la clé de voûte de tout le système peircien et sont indispensables pour comprendre sa sémiotique et  &lt;a href="https://hal.science/hal-02953592/document"  title="Pragmatisme  par hal science"&gt;son pragmatisme&lt;/a&gt;: &lt;/p&gt; &lt;p&gt; - Priméité (Firstness) : C'est la catégorie de la qualité pure, de la potentialité, de la sensation immédiate et brute, existant en elle-même sans référence à quoi que ce soit d'autre. C'est le "sentiment de rouge", la qualité d'une odeur, la nouveauté d'une idée. C'est le domaine de la possibilité et de la liberté. &lt;/p&gt; &lt;p&gt; - Secondéité (Secondeity) : C'est la catégorie du fait brut, de l'action-réaction, de la résistance et de l'actualité. C'est le choc du "ici et maintenant", la rencontre avec un autre qui s'impose à nous. Exemples : une collision, la sensation de résistance en poussant une porte, un conflit. C'est le domaine de l'existence et de la dualité. &lt;/p&gt; &lt;p&gt; - Tiercéité (Thirdness) : C'est la catégorie de la médiation, de la loi, de l'habitude, de la généralisation et de la signification. Elle fait le lien entre la Priméité (la qualité) et la Secondéité (le fait) en leur donnant un sens et une régularité. Exemples : une loi scientifique, un symbole linguistique, une tendance, une règle de conduite. C'est le domaine de la pensée, de la continuité et de l'intelligibilité. &lt;/p&gt; &lt;p&gt; Il propose une méthode pour clarifier le sens de nos idées, le Pragmaticisme: le sens d'un concept réside dans ses conséquences pratiques observables. Si deux idées ne produisent aucune différence pratique, elles signifient la même chose. C'est avant tout une méthode logique pour trancher les disputes métaphysiques stériles.&lt;/p&gt; &lt;p&gt; Sa contribution la plus novatrice et la plus influente est &lt;a href="https://www.persee.fr/doc/lgge_0458-726x_1980_num_14_58_1844" title="La séméiotique de Charles S. Peirce  par Persée"&gt;la Sémiotique&lt;/a&gt;. Pour lui, "l'homme est un signe" et toute pensée est un &lt;a href="https://www.youtube.com/watch?v=e1jrx1RlS00" title="VOIR ET INTERPRÉTER LES SIGNES ! Introduction à la sémiologie CHARLES SANDERS PEIRCE  par Survivreauxscienceshumaines"&gt;processus sémiotique&lt;/a&gt;. Il définit le signe non pas de manière dyadique mais triadique,  Il crée dans l'esprit de la  personne un signe plus développé, appelé l'interprétant. La relation signe-objet-interprétant est fondamentale. Sa classification concerne la relation du signe à son objet : &lt;/p&gt; &lt;dd&gt; - Icône: Le signe ressemble à son objet ou partage des qualités avec lui (une photographie, un diagramme). &lt;/dd&gt; &lt;dd&gt; - Index: Le signe est physiquement connecté à son objet : la fumée (indice du feu), une girouette (indice de la direction du vent). &lt;/dd&gt; &lt;dd&gt; - Symbole: La relation entre le signe et l'objet est arbitraire et conventionnelle. Elle repose sur une règle ou une habitude sociale. ("arbre" n'a rien d'un arbre). &lt;/dd&gt; &lt;p&gt; Bien que mort dans la misère et méconnu de son vivant, son influence est immense aujourd'hui en philosophie, en sciences cognitives, en linguistique et en sociologie. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Sanders_Peirce" title=" Wikipedia"&gt;Charles Sanders PEIRCE&lt;/a&gt;  était un philosophe, logicien, scientifique américain assez original, fondateur du  &lt;a href="https://www.youtube.com/watch?v=AGHmKg7wYf0"  title="Pragmatisme  par robertus"&gt;pragmatisme&lt;/a&gt;, père de la sémiotique moderne (théorie des signes) et un pionnier de la logique. Pourtant, en raison de  &lt;a href="https://laviedesidees.fr/Chevalier-Peirce-ou-l-invention-de-l-epistemologie" style="color:#88A1E9" title="les pepites de Charles s pierce par laviedesidees"&gt;sa personnalité difficile&lt;/a&gt; et de ses idées avant-gardistes, il vécut en marge du monde académique, mourant dans la pauvreté et l'isolement. &lt;/p&gt; &lt;p&gt;  Il cherchait à identifier les catégories les plus fondamentales et universelles de la pensée et de l'être, qu'il nomma Phanéroscopie.Il en déduit trois, présentes dans tous les phénomènes. Elles sont la clé de voûte de tout le système peircien et sont indispensables pour comprendre sa sémiotique et  &lt;a href="https://hal.science/hal-02953592/document"  title="Pragmatisme  par hal science"&gt;son pragmatisme&lt;/a&gt;: &lt;/p&gt; &lt;p&gt;Priméité (Firstness) : C'est la catégorie de la qualité pure, de la potentialité, de la sensation immédiate et brute, existant en elle-même sans référence à quoi que ce soit d'autre. C'est le "sentiment de rouge", la qualité d'une odeur, la nouveauté d'une idée. C'est le domaine de la possibilité et de la liberté. &lt;/p&gt; &lt;p&gt;Secondéité (Secondeity) : C'est la catégorie du fait brut, de l'action-réaction, de la résistance et de l'actualité. C'est le choc du "ici et maintenant", la rencontre avec un autre qui s'impose à nous. Exemples : une collision, la sensation de résistance en poussant une porte, un conflit. C'est le domaine de l'existence et de la dualité. &lt;/p&gt; &lt;p&gt;Tiercéité (Thirdness) : C'est la catégorie de la médiation, de la loi, de l'habitude, de la généralisation et de la signification. Elle fait le lien entre la Priméité (la qualité) et la Secondéité (le fait) en leur donnant un sens et une régularité. Exemples : une loi scientifique, un symbole linguistique, une tendance, une règle de conduite. C'est le domaine de la pensée, de la continuité et de l'intelligibilité. &lt;/p&gt; &lt;p&gt; Il propose une méthode pour clarifier le sens de nos idées, le Pragmaticisme: le sens d'un concept réside dans ses conséquences pratiques observables. Si deux idées ne produisent aucune différence pratique, elles signifient la même chose. C'est avant tout une méthode logique pour trancher les disputes métaphysiques stériles.&lt;/p&gt; &lt;p&gt; Sa contribution la plus novatrice et la plus influente est &lt;a href="https://www.persee.fr/doc/lgge_0458-726x_1980_num_14_58_1844" title="La séméiotique de Charles S. Peirce  par Persée"&gt;la Sémiotique&lt;/a&gt;. Pour lui, "l'homme est un signe" et toute pensée est un &lt;a href="https://www.youtube.com/watch?v=e1jrx1RlS00" title="VOIR ET INTERPRÉTER LES SIGNES ! Introduction à la sémiologie CHARLES SANDERS PEIRCE  par Survivreauxscienceshumaines"&gt;processus sémiotique&lt;/a&gt;. Il définit le signe non pas de manière dyadique mais triadique,  Il crée dans l'esprit de la  personne un signe plus développé, appelé l'interprétant. La relation signe-objet-interprétant est fondamentale. Sa classification concerne la relation du signe à son objet : &lt;/p&gt; &lt;p&gt;Icône: Le signe ressemble à son objet ou partage des qualités avec lui (une photographie, un diagramme). &lt;/p&gt; &lt;p&gt;Index: Le signe est physiquement connecté à son objet : la fumée (indice du feu), une girouette (indice de la direction du vent). &lt;/p&gt; &lt;p&gt;Symbole: La relation entre le signe et l'objet est arbitraire et conventionnelle. Elle repose sur une règle ou une habitude sociale. ("arbre" n'a rien d'un arbre). &lt;/p&gt; &lt;p&gt; Bien que mort dans la misère et méconnu de son vivant, son influence est immense aujourd'hui en philosophie, en sciences cognitives, en linguistique et en sociologie. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -2879,11 +2881,16 @@
       <c r="C16" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>133</v>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carlos VAZ-FERREIRA</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Carlos_Vaz_Ferreira"  title=" Wikipedia"&gt;Carlos VAZ FERREIRA&lt;/a&gt; était un  philosophe uruguayen considéré comme l’une des figures majeures de la pensée hispano‑américaine au début du XXᵉ siècle. Issue d’une famille aux origines portugaise et uruguayenne, sa trajectoire intellectuelle s’inscrit dans un contexte de modernisation de l’Université et de reformulation des idées scientifiques et morales en Amérique du Sud. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=AmRpz8vCejs" title="Vas Ferreira par Pablo Romero"&gt;Sa philosophie &lt;/a&gt; se situe à la croisée du positivisme, du pragmatisme et de l’empirisme britannique, avec un respect marqué pour Herbert Spencer, John Stuart Mill, William James et Henri Bergson, sans jamais adopter intégralement leurs doctrines. Il critique la rigidité des systèmes logiques et métaphysiques classiques, estimant que le langage et la logique formelle imposent au réel une précision artificielle qui masque la complexité et la fluidité de l’expérience. &lt;/p&gt; &lt;p&gt; Il  développe l’idée d’une &lt;a href="https://www.youtube.com/watch?v=UeadgG1ud1g" title="Vas Ferreira y su logica viva par Tribuna Constitucional"&gt;« logique vivante », &lt;/a&gt; c’est‑à‑dire une logique ancrée dans la vie concrète, attentive aux degrés de probabilité et aux limites de nos certitudes plutôt qu’aux schémas abstraits. Pour lui, la raison doit rester souple et vigilante, proche de l’expérience et des données empiriques, afin de ne pas basculer dans des systèmes dogmatiques. &lt;/p&gt; &lt;p&gt; En épistémologie, il défend une vision modeste de la science : les sciences sont des outils puissants mais partiaux, incapables de saisir le tout de la réalité et toujours confrontées à des questions métaphysiques implicites. La philosophie, selon lui, doit clarifier ces présupposés, rappeler les limites symboliques de la science et contrer les « mauvaises métaphysiques » qui surgissent lorsque l’on ignore les questions fondamentales. &lt;/p&gt; &lt;p&gt; Sur le plan éthique et social, il s’intéresse à la liberté, à la morale des intellectuels, aux problèmes sociaux et aux questions de propriété ou de féminisme. Il met en avant une morale sensible à la complexité des situations, où les principes comportent des exceptions et où le choix moral implique souvent des compromis entre des biens et des maux partiels ; tout en affirmant qu’il existe un progrès moral dans l’histoire humaine, marqué par l’élargissement des idéaux et la résistance accrue au mal. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F16" s="7" t="s">
         <v>134</v>
@@ -3098,7 +3105,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher)"  title=" Wikipedia"&gt;Francisco ROMERO&lt;/a&gt; était un philosophe argentin d’origine espagnole, professeur à l’Université de Buenos Aires et à La Plata, et une figure centrale de la réaction  &lt;a href="https://fr.wikipedia.org/wiki/Ib%C3%A9ro-Am%C3%A9rique"  title="ibéro-amérique par wikipedia"&gt; ibéro-américaine &lt;/a&gt; contre le positivisme dominant au début du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa production philosophique couvre l’épistémologie, la philosophie de la culture et l’anthropologie philosophique ; son ouvrage majeur en langue espagnole, Teoría del hombre (1952), propose une réflexion systématique sur la condition humaine, la liberté et la créativité culturelle, et a été traduit en anglais sous le titre Theory of Man.https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher) &lt;/p&gt; &lt;p&gt; Il  prit position contre  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9ductionnisme"  title="Reductionnisme par wikipedia"&gt; le réductionnisme scientiste &lt;/a&gt; en défendant l’idée que la culture et les créations humaines (art, religion, langage) exigent des méthodes et des concepts propres, distincts des instruments des sciences naturelles ; il chercha donc à articuler rigueur philosophique et sensibilité littéraire. &lt;/p&gt; &lt;p&gt; Sur le plan méthodologique, il promut une philosophie qui dialogue avec l’histoire des idées et avec les problèmes concrets de la société ibéro-américaine : ses travaux montrent un intérêt marqué pour la responsabilité sociale des intellectuels et pour la formation culturelle des peuples. &lt;/p&gt; &lt;p&gt; Parmi ses autres ouvrages importants figurent Old and New Concepts of Reality (1932), The Problems of Philosophy of Culture (1938), Man and Culture (1950, traduction de El hombre y la cultura) et History of Modern Philosophy (1959); sa réputation lui valut le surnom de « doyen des philosophes ibéro-américains » et son héritage continue d’être étudié dans les études sur la philosophie latino‑américaine. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher)"  title=" Wikipedia"&gt;Francisco ROMERO&lt;/a&gt; était un philosophe argentin d’origine espagnole, professeur à l’Université de Buenos Aires et à La Plata, et une figure centrale de la réaction  &lt;a href="https://fr.wikipedia.org/wiki/Ib%C3%A9ro-Am%C3%A9rique"  title="ibéro-amérique par wikipedia"&gt; ibéro-américaine &lt;/a&gt; contre le positivisme dominant au début du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa production philosophique couvre l’épistémologie, la philosophie de la culture et l’anthropologie philosophique ; son ouvrage majeur en langue espagnole, Teoría del hombre (1952), propose une réflexion systématique sur la condition humaine, la liberté et la créativité culturelle, et a été traduit en anglais sous le titre Theory of Man. &lt;/p&gt; &lt;p&gt; Il  prit position contre  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9ductionnisme"  title="Reductionnisme par wikipedia"&gt; le réductionnisme scientiste &lt;/a&gt; en défendant l’idée que la culture et les créations humaines (art, religion, langage) exigent des méthodes et des concepts propres, distincts des instruments des sciences naturelles ; il chercha donc à articuler rigueur philosophique et sensibilité littéraire. &lt;/p&gt; &lt;p&gt; Sur le plan méthodologique, il promut une philosophie qui dialogue avec l’histoire des idées et avec les problèmes concrets de la société ibéro-américaine : ses travaux montrent un intérêt marqué pour la responsabilité sociale des intellectuels et pour la formation culturelle des peuples. &lt;/p&gt; &lt;p&gt; Parmi ses autres ouvrages importants figurent Old and New Concepts of Reality (1932), The Problems of Philosophy of Culture (1938), Man and Culture (1950, traduction de El hombre y la cultura) et History of Modern Philosophy (1959); sa réputation lui valut le surnom de « doyen des philosophes ibéro-américains » et son héritage continue d’être étudié dans les études sur la philosophie latino‑américaine. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -3492,8 +3499,10 @@
       <c r="D30" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>262</v>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hannah_Arendt"  title=" Wikipedia"&gt;Hannah ARENDT&lt;/a&gt; était une femme philosophe allemande  &lt;a href="https://allemagneenfrance.diplo.de/fr-fr/actualites-nouvelles-d-allemagne/07-culture/2680094-2680094" title="Hannah Arendt, une vie d'exil  par Missions allemandes en France"&gt;naturalisée américaine&lt;/a&gt; et formée dans la tradition philosophique allemande, notamment auprès de Martin Heidegger et de Karl Jaspers. Elle a également été marquée par la phénoménologie (Husserl) et la pensée de Kant, tout en s'éloignant de la philosophie pure pour développer une réflexion ancrée dans le réel. Les &lt;a href="https://scienceetbiencommun.pressbooks.pub/femmessavantes2/chapter/hannah-arendt-philosophe-1906-1975/" style="color:#88A1E9" title="Hannah Arendt par Esbc"&gt;thèmes majeurs&lt;/a&gt; de sa pensée seront : &lt;/p&gt; &lt;p&gt;"Les Origines du totalitarisme" : Elle analyse le nazisme et le stalinisme comme des régimes totalitaires inédits dans l'histoire, caractérisés par la destruction des structures sociales et politiques traditionnelles et avec l'idéologie comme moteur absolu (la race pour les nazis, la lutte des classes pour les staliniens) tout en  semant la terreur systématique et les camps comme laboratoires de la domination totale. &lt;/p&gt; &lt;p&gt;"Eichmann à Jérusalem"  : En couvrant le procès d'Adolf Eichmann, responsable logistique de la Shoah, elle introduit l'idée controversée de la &lt;a href="https://www.youtube.com/watch?v=5iQkmzmkJEs" title="La banalité du mal par digiSchool Lycée"&gt;"banalité du mal"&lt;/a&gt;.  Eichmann n'était pas un monstre, mais un bureaucrate ordinaire, incapable de penser par lui-même, obéissant aveuglément aux ordres. Le mal, dans ce cas, résulte de &lt;a href="https://www.youtube.com/watch?v=fNri0ZxoEQY"  title="la banalité du mal de Hannah Arendt par Alain Bajomée"&gt;l'absence de réflexion&lt;/a&gt; critique. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=5bey28ALopE"  title="la philo de Hannah Arendt par Parole de philosophe"&gt;"Condition de l'homme moderne"&lt;/a&gt; ou elle distingue trois dimensions de l'existence humaine : &lt;p&gt;Le travail : Activité cyclique liée à la survie biologique (production/consommation). &lt;/p&gt; &lt;p&gt;L'œuvre : Création d'un monde durable (art, technique, institutions). &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=lCOxpdXgkHI" title="Hannah Arendt 1973 par olivier-berruter-les-crises"&gt; L'action&lt;/a&gt; : Activité proprement politique, fondée sur la pluralité et la liberté, où les hommes agissent et parlent ensemble pour construire un monde commun. &lt;/p&gt; &lt;p&gt; Dans sa dernière oeuvre  "La Vie de l'esprit" (inachevé), elle explore les facultés de penser, vouloir et juger. Le jugement, en particulier, est crucial pour résister à l'idéologie, il suppose la capacité à voir les choses depuis le point de vue d'autrui (élargissement de l'esprit chez Kant). &lt;/p&gt;   &lt;audio controls title="Hannah Arendt, la passagère par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14373-18.08.2017-ITEMA_21410372-2017C49904E0021-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F30" s="7" t="s">
         <v>263</v>
@@ -3539,8 +3548,12 @@
       <c r="D31" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>272</v>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nelson_Goodman"  title=" Wikipedia"&gt;Nelson GOODMAN&lt;/a&gt; était un philosophe américain connu pour ses contributions à la philosophie analytique, l’esthétique et la philosophie de la science. Il est l’un des grands défenseurs d’un nominalisme contemporain qui remet en question le fondement des ensembles et des classes comme entités réelles, préférant des cadres descriptifs et structurels pour rendre compte du monde. &lt;/p&gt; &lt;p&gt;  Il a aussi développé des réflexions sur l’induction et le problème du diamètre entre nos théories et les phénomènes, parfois illustrés par &lt;a href="https://www.youtube.com/watch?v=vEqZhRcvQME"  title=" Le paradoxe de Goodman (est-ce que toutes les émeraudes sont vertes ?) par Maêl Cavan"&gt; des paradoxes logiques célèbres&lt;/a&gt;. Son œuvre est également marquée par l’esthétique analytique, où il explore la  &lt;a href="https://www.youtube.com/watch?v=hJNmeVrsx5c"  title="Nelson Goodman , peut on parler d'art? par Erème"&gt;nature de l’art&lt;/a&gt; et de l’évaluation esthétique. &lt;/p&gt; &lt;p&gt;Structure de l’apparence paru en 1951 et les orientations autour du reconstructionnisme logique du monde à partir des apparences perceptibles, sans appui ontologique lourd. &lt;/p&gt; &lt;p&gt;L’induction et le paradoxe de Goodman, où il questionne comment les prédictions et les justifications se lisent à travers des exemples comme le paradoxe des "new rickets" (exemple classique), montrant des limites de nos méthodes inductives. &lt;/p&gt; &lt;p&gt;Nominalisme et mereology: avec des penseurs comme Stanisław Leśniewski, il soutient une approche où les entités mathématiques et logiques ne nécessitent pas une base ontologique robuste en dehors des descriptions et des relations que l’on peut formaliser. &lt;/p&gt; &lt;p&gt; Il  a influencé la  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1972_num_70_6_5675_t1_0319_0000_2" title="Nelson Goodman, Languages of art. An approach to a theory of symbols par Persée"&gt;philosophie du langage,&lt;/a&gt; la logique et l’esthétique analytique, et ses idées ont suscité de nombreux débats sur la nature des objets, des propriétés et des cadres de description. Ses étudiants et collègues (dont Noam Chomsky et Hilary Putnam à Harvard) témoignent de son impact durable sur la philosophie analytique américaine. &lt;/p&gt;    &lt;audio controls title="La fabrique des mondes selon Nelson Goodman par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16409-22.06.2007-ITEMA_20075915-2007C6409S0173-NET_BF330E12-B7F0-45F9-9A8C-43C9F305150C_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
+​
+</t>
+        </is>
       </c>
       <c r="F31" s="7" t="s">
         <v>273</v>
@@ -4178,8 +4191,11 @@
       <c r="D46" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E46" s="9" t="s">
-        <v>403</v>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Enrique_Dussel"  title=" Wikipedia"&gt;Enrique DUSSEL&lt;/a&gt; était un philosophe argentin majeurs de la décolonialité et de la philosophie latino-américaine de la liberation.  Jeune intellectuel engagé dans les mouvements étudiants et opposé aux régimes autoritaires, il a été persécuté en Argentine avant de s’exiler au Mexique en 1975, où il a poursuivi sa carrière académique et développé sa pensée. Il élabore une &lt;a href="https://www.youtube.com/watch?v=QGPosp7lYlM" title="Enrique Dussel and the Philosophy of Liberation – Decolonizing Thought par Darina Metreveli"&gt;philosophie de la libération &lt;/a&gt; qui remet en question l’ontologie monologique de la modernité et introduit une approche éthique et alteritaire inspirée par Levinas, souvent décrite sous le nom d’analectique ou de dialectique positive. &lt;/p&gt; &lt;p&gt; Pionnier du décolonialisme latino-américain, il contribue à la construction des cadres Modernité/Colonialité et à l’idée d’une transmodernité, articulant critique de la modernité et invitation à repenser les rapports Nord-Sud et centre-périphérie. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures : &lt;a href="https://www.youtube.com/watch?v=nXNyqKCrKLY" title="Enrique Dussel, métaphysicien de la libération - Emmanuel Lévine par lundimatin"&gt;"Méthode pour une philosophie de la libération" &lt;/a&gt; paru en  1974 et "Filosofía ética latinoamericana" (période majeure)  posent les bases d’une philosophie enracinée dans les expériences des peuples opprimés et des contextes colonisés. &lt;/p&gt; &lt;p&gt; Il est reconnu dans les &lt;a href="https://lestempsquirestent.org/fr/numeros/numero-7/enrique-dussel-un-philosophe-indispensable-pour-decoloniser-la-theologie-politique" title="Enrique Dussel,
+un philosophe indispensable pour décoloniser la théologie politique par les temps qui restent"&gt;milieux décoloniaux &lt;/a&gt; et philosophie de la libération, mais demeure moins connu du grand public français, bien que des traductions et des analyses apparaissent et stimulent l’intérêt académique en France. Son travail nourrit le courant décolonial qui met en évidence l’interdépendance entre modernité et colonialité depuis 1492 et propose des axes pour une pensée transmoderne, dépassant les cadres classiques de la philosophie occidentale. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F46" s="7" t="s">
         <v>404</v>
@@ -4436,8 +4452,10 @@
       <c r="D52" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="E52" s="9" t="s">
-        <v>452</v>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tom_Regan"  title=" Wikipedia"&gt;Tom REGAN&lt;/a&gt; était un philosophe américain   &lt;a href="https://www.youtube.com/watch?v=hgVMf3q4Vh4"  title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Pensées antispécistes par The Critical Vegan"&gt;antispéciste &lt;/a&gt; influent dans le domaine de l'éthique animale, considéré comme un pionnier de la théorie des droits des animaux sur une base déontologique. Il développe une approche abolitionniste opposée à l'utilitarisme de Peter Singer, arguant que les mammifères normaux d'un an ou plus sont des "sujets-d'une-vie" dotés d'une valeur inhérente, méritant des droits moraux fondamentaux indépendamment de leur utilité. Inspiré par Kant mais étendu aux non-humains, il définit ces sujets comme des êtres conscients pour qui leur vie importe intrinsèquement, justifiant l'interdiction absolue de l'exploitation. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales sont : "The Case for Animal Rights" paru en 1983, traduit en français comme  &lt;a href="http://tomregan.free.fr/" title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Les Droits des animaux par Tom Regan"&gt;"Les Droits des animaux" &lt;/a&gt; en 2013 : son magnum opus, salué comme un classique moderne critiquant Descartes et plaidant pour le "principe de respect" envers tout sujet-d'une-vie. "All That Dwell Therein" paru en  1982 : recueil d'essais sur la végétarisme et l'éthique animale. &lt;/p&gt; &lt;p&gt; Ses idées ont profondément marqué le mouvement des droits des animaux, influençant débats sur végétarisme, anti-vivisection et critique de l'environnementalisme indirect, tout en étant cité par des penseurs comme Derrida ou dans des ouvrages comme ceux de Jean-Baptiste Jeangène Vilmer. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F52" s="7" t="s">
         <v>453</v>
@@ -4560,8 +4578,12 @@
       <c r="D55" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="E55" s="9" t="s">
-        <v>479</v>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Daniel_Dennett"  style="color:#6A142A"  title=" Wikipedia"&gt;Daniel DENNETT&lt;/a&gt; était un  philosophe américain, figure importante et  influente de la philosophie de l'esprit, de la biologie et des sciences cognitives. Ses travaux se caractérisent par une volonté d'intégrer les découvertes scientifiques (biologie évolutionniste, neurosciences, intelligence artificielle) à la réflexion philosophique, souvent pour démanteler des intuitions traditionnelles qu'il juge erronées. &lt;/p&gt; &lt;p&gt; La Théorie de l'Esprit comme &lt;a href="https://www.youtube.com/watch?v=LKJJpvdqkFA" style="color:#88A1E9" title="Cette histoire va vous retourner le cerveau. | "Où suis-je" de Daniel Dennett par Monsieur Phi"&gt;"Position Intentionnelle"&lt;/a&gt; est sa contribution majeure. Il propose que pour prédire et expliquer le comportement d'un système (qu'il s'agisse d'un humain, d'un animal, d'un ordinateur ou même d'un thermostat), nous pouvons adopter trois "stances" : &lt;/p&gt; &lt;p&gt;La stance physique : On décrit le système par sa physique et sa chimie. Très difficile pour des systèmes complexes. &lt;/p&gt; &lt;p&gt;La stance du design : On considère le système comme conçu pour une fonction spécifique (ex: "ce thermostat est fait pour réguler la température"). &lt;/p&gt; &lt;p&gt;La stance intentionnelle : On traite le système comme s'il avait des croyances, des désirs et une rationalité. C'est une stratégie de prédiction extrêmement efficace, même si les croyances et désirs ne sont pas "réels" au sens littéral. Pour lui, avoir des croyances, c'est être un système dont le comportement peut être prédit avec succès par la stance intentionnelle. &lt;/p&gt; &lt;p&gt; Il est un matérialiste farouche et  rejette l'idée d'un &lt;a href="https://www.nonfiction.fr/article-1116-daniel_dennett_est_il_le_diable_.htm" title="Daniel Dennett est-il le diable ? par nonfiction"&gt;"théâtre cartésien"&lt;/a&gt;, un endroit dans le cerveau où tout se réunirait pour être "vu" par un &lt;a href="https://www.youtube.com/watch?v=0It9fwSj6xM"  title="Le moi comme illusion (Daniel Dennett, la conscience expliquée 4) par Philosophie Analytique"&gt;"spectateur" (le soi)&lt;/a&gt;. Pour lui, c'est une illusion.
+Il défend plutôt un modèle de "espace de travail global" : la conscience émerge de processus cérébraux parallèles et compétitifs. Une information devient "consciente" lorsqu'elle gagne une compétition pour être diffusée à grande échelle dans le cerveau, rendant ainsi disponible pour d'autres systèmes (mémoire, langage, prise de décision). Il n'y a pas de "centre" unique. &lt;/p&gt; &lt;p&gt; Il  considère que l'idée de la sélection naturelle de Darwin est "l'idée la plus dangereuse de tous les temps" car elle a un pouvoir explicatif immense, bien au-delà de la biologie. Il l'étend à d'autres domaines grâce au concept de "mèmes" (introduit par Richard Dawkins).
+Les mèmes sont des unités de culture (idées, mélodies, modes, concepts) qui se répliquent, mutent et sont sélectionnées dans le "payage" des esprits humains. Le langage,&lt;a href="https://www.youtube.com/shorts/bG3YBavy29Y" title="Cette histoire va vous retourner le cerveau | Daniel Dennett par StopCroyance"&gt; la religion&lt;/a&gt;, la morale peuvent être analysés comme des produits d'un processus darwinien. &lt;/p&gt; &lt;p&gt; Il défend une forme de libre arbitre qu'il estime compatible avec le déterminisme scientifique (le fait que l'univers soit régi par des lois causales). Pour lui, le libre arbitre n'est pas une "causalité magique" qui échapperait aux lois de la nature.  C'est la capacité d'un agent complexe (comme un être humain) à se projeter dans le futur, à évaluer les conséquences de ses actes et à agir en fonction de ses raisons. Ce libre arbitre est le produit de l'évolution et de la culture. Il est réel et précieux, même s'il n'est pas "libre" au sens d'une exemption des lois de la physique. &lt;/p&gt; &lt;audio controls title=" "Daniel Dennett, le penseur qui a révolutionné la philosophie des sciences et de l’esprit" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24419-10.05.2024-ITEMA_23737219-2024C51851S0131-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F55" s="7" t="s">
         <v>480</v>
@@ -4596,11 +4618,16 @@
       <c r="C56" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="D56" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>487</v>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marilyn MCCORD-ADAMS</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marilyn_McCord_Adams" title=" Wikipedia"&gt;Marilyn McCORD ADAMS&lt;/a&gt; était une philosophe américaine et une théologienne anglicane, reconnue pour son travail en philosophie de la religion et en philosophie médiévale. Elle a aussi été ordonnée prêtre épiscopalienne, ce qui donnait à sa réflexion philosophique une forte dimension spirituelle et pastorale. Elle a étudié à l’Université de l’Illinois puis à Cornell, où elle a obtenu son doctorat en philosophie en 1967. Sa carrière universitaire l’a menée à Michigan, UCLA, Yale, Oxford et elle a été la première femme, ainsi que la première Américaine, à occuper la chaire Regius de divinité à Oxford. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://senate.universityofcalifornia.edu/in-memoriam/files/marilyn-adams.html" title="Marilyn Adans par university of california"&gt;Son apport le plus célèbre &lt;/a&gt; concerne l’étude de Guillaume d’Ockham, à qui elle a consacré une grande étude en deux volumes qui a beaucoup compté dans les recherches sur la théologie médiévale. Elle a aussi travaillé sur l’eucharistie, le christologie et d’autres auteurs médiévaux comme Thomas d’Aquin, Gilles de Rome et Duns Scot. &lt;/p&gt; &lt;p&gt; En  &lt;a href="https://www.youtube.com/watch?v=nFRGDG__ELM" title="Marilyn Adans par Real Atheology"&gt;philosophie de la religion, &lt;/a&gt; elle est connue pour ses analyses du mal extrême, qu’elle appelait les horrendous evils. Son idée centrale est qu’une théologie sérieuse doit prendre au sérieux les souffrances qui semblent détruire toute possibilité de sens, et montrer comment elles peuvent malgré tout être intégrées dans une vision de la bonté divine. &lt;/p&gt; &lt;p&gt; Son œuvre a eu une influence durable parce qu’elle relie la rigueur philosophique, l’érudition médiévale et l’expérience religieuse vécue. Elle reste une figure majeure pour comprendre à la fois la philosophie analytique de la religion et la redécouverte moderne de la pensée médiévale. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F56" s="7" t="s">
         <v>488</v>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -4454,7 +4454,7 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tom_Regan"  title=" Wikipedia"&gt;Tom REGAN&lt;/a&gt; était un philosophe américain   &lt;a href="https://www.youtube.com/watch?v=hgVMf3q4Vh4"  title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Pensées antispécistes par The Critical Vegan"&gt;antispéciste &lt;/a&gt; influent dans le domaine de l'éthique animale, considéré comme un pionnier de la théorie des droits des animaux sur une base déontologique. Il développe une approche abolitionniste opposée à l'utilitarisme de Peter Singer, arguant que les mammifères normaux d'un an ou plus sont des "sujets-d'une-vie" dotés d'une valeur inhérente, méritant des droits moraux fondamentaux indépendamment de leur utilité. Inspiré par Kant mais étendu aux non-humains, il définit ces sujets comme des êtres conscients pour qui leur vie importe intrinsèquement, justifiant l'interdiction absolue de l'exploitation. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales sont : "The Case for Animal Rights" paru en 1983, traduit en français comme  &lt;a href="http://tomregan.free.fr/" title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Les Droits des animaux par Tom Regan"&gt;"Les Droits des animaux" &lt;/a&gt; en 2013 : son magnum opus, salué comme un classique moderne critiquant Descartes et plaidant pour le "principe de respect" envers tout sujet-d'une-vie. "All That Dwell Therein" paru en  1982 : recueil d'essais sur la végétarisme et l'éthique animale. &lt;/p&gt; &lt;p&gt; Ses idées ont profondément marqué le mouvement des droits des animaux, influençant débats sur végétarisme, anti-vivisection et critique de l'environnementalisme indirect, tout en étant cité par des penseurs comme Derrida ou dans des ouvrages comme ceux de Jean-Baptiste Jeangène Vilmer. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tom_Regan"  title=" Wikipedia"&gt;Tom REGAN&lt;/a&gt; était un philosophe américain   &lt;a href="https://www.youtube.com/watch?v=hgVMf3q4Vh4"  title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Pensées antispécistes par The Critical Vegan"&gt;antispéciste &lt;/a&gt; influent dans le domaine de l'éthique animale, considéré comme un pionnier de la théorie des droits des animaux sur une base déontologique. Né à Pittsburgh, il enseigne de 1967 à 2001 à l’université d’État de Caroline du Nord. Il développe une approche abolitionniste opposée à l'utilitarisme de Peter Singer, arguant que les mammifères normaux d'un an ou plus sont des "sujets-d'une-vie" dotés d'une valeur inhérente, méritant des droits moraux fondamentaux indépendamment de leur utilité. Inspiré par Kant mais étendu aux non-humains, il définit ces sujets comme des êtres conscients pour qui leur vie importe intrinsèquement, justifiant l'interdiction absolue de l'exploitation. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales sont : "The Case for Animal Rights" paru en 1983, traduit en français comme  &lt;a href="http://tomregan.free.fr/" title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Les Droits des animaux par Tom Regan"&gt;"Les Droits des animaux" &lt;/a&gt; en 2013 : son magnum opus, salué comme un classique moderne critiquant Descartes et plaidant pour le "principe de respect" envers tout sujet-d'une-vie. "All That Dwell Therein" paru en  1982 : recueil d'essais sur le végétarisme et l'éthique animale. &lt;/p&gt; &lt;p&gt; Ses idées ont profondément marqué le mouvement des droits des animaux, influençant débats sur végétarisme, anti-vivisection et critique de l'environnementalisme indirect, tout en étant cité par des penseurs comme Derrida ou dans des ouvrages comme ceux de Jean-Baptiste Jeangène Vilmer. Dans &lt;em&gt;Empty Cages&lt;/em&gt; (2004), destiné au grand public, il résume son combat : il ne s’agit pas d’agrandir les cages, mais de les vider. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F52" s="7" t="s">

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -6063,7 +6063,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Newton_da_Costa" title=" Wikipedia (en)"&gt;Newton DA COSTA&lt;/a&gt; est un logicien et philosophe brésilien, l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/Logique_paraconsistante" title=" Wikipedia"&gt;logique paraconsistante&lt;/a&gt;. Né en 1929 à Curitiba, il étudie d’abord le génie civil puis les mathématiques, et enseigne à l’université fédérale du Paraná, puis à l’université de São Paulo et à l’université fédérale de Santa Catarina.&lt;/p&gt; &lt;p&gt;Dans la logique classique, une seule contradiction suffit à tout prouver : si l’on admet à la fois une proposition et sa négation, on peut en déduire n’importe quoi. C’est le principe d’« explosion ». Dès sa thèse de 1963, da Costa construit des systèmes logiques, appelés « calculs C », où l’on peut admettre certaines contradictions sans que toute la théorie s’effondre. Le nom de « paraconsistance » leur est donné en 1976 par le philosophe péruvien Francisco Miró Quesada. Ces logiques permettent de raisonner rigoureusement sur des informations contradictoires, comme celles d’une base de données, d’un témoignage ou d’une théorie scientifique en crise.&lt;/p&gt; &lt;p&gt;Da Costa étend ces travaux à la théorie des ensembles et à la philosophie des sciences. Avec Steven French, il développe la notion de « quasi-vérité » : une théorie scientifique peut être partiellement vraie et utile sans être entièrement exacte. Membre de nombreuses académies, il a formé une importante école de logique au Brésil et en Amérique latine. Il meurt en 2024 à Florianópolis.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Newton_da_Costa" title=" Wikipedia (en)"&gt;Newton DA COSTA&lt;/a&gt; est un logicien et philosophe brésilien, l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/Logique_paraconsistante" title=" Wikipedia"&gt;logique paraconsistante&lt;/a&gt;. Né en 1929 à Curitiba, il étudie d’abord le génie civil puis les mathématiques, et enseigne à l’université fédérale du Paraná, puis à l’université de São Paulo et à l’université fédérale de Santa Catarina.&lt;/p&gt; &lt;p&gt;Dans la logique classique, une seule contradiction suffit à tout prouver : si l’on admet à la fois une proposition et sa négation, on peut en déduire n’importe quoi. C’est le principe d’« explosion ». Dès sa thèse de 1963, da Costa construit des systèmes logiques, appelés « calculs C », où l’on peut admettre certaines contradictions sans que toute la théorie s’effondre. Le nom de « paraconsistance » leur est donné en 1976 par le philosophe péruvien Francisco Miró Quesada. Ces logiques permettent de raisonner rigoureusement sur des informations contradictoires, comme celles d’une base de données, d’un témoignage ou d’une théorie scientifique en crise.&lt;/p&gt; &lt;p&gt;Da Costa étend ces travaux à la théorie des ensembles et à la philosophie des sciences. Avec Steven French, il développe la notion de « quasi-vérité » : une théorie scientifique peut être partiellement vraie et utile sans être entièrement exacte. Avec Francisco Antônio Dória, il montre en 1991 que certaines questions de la théorie du chaos sont indécidables : aucun calcul ne peut y répondre. Membre de nombreuses académies, il a formé une importante école de logique au Brésil et en Amérique latine. Il meurt en 2024 à Florianópolis.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -3596,8 +3596,10 @@
       <c r="D32" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>281</v>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Willard_Van_Orman_Quine"  title=" Wikipedia"&gt;Williard Van Orman QUINE&lt;/a&gt; était un philosophe américain,  figure centrale de la philosophie analytique. Connu pour son naturalisme radical et sa critique des fondements traditionnels de l'épistémologie, il a profondément influencé la philosophie des sciences, de la logique et du langage. &lt;/p&gt; &lt;p&gt;Il  rejette la distinction analytique-synthétique dans son article célèbre "Two Dogmas of Empiricism" paru en 1951, critiquant l'empirisme logique du Cercle de Vienne. Il défend un holisme épistémique où les &lt;a href="https://www.persee.fr/doc/intel_0769-4113_2015_num_64_2_1016"  title="Le langage et la science chez Quine ou les racines de la rédemption. Compte-rendu du livre de Michel Olivier, Quine, Paris, Belles Lettres par Persée"&gt;théories scientifiques &lt;/a&gt; sont testées globalement face à l'expérience, et non isolément. Son épistémologie naturalisée voit la philosophie comme une branche des sciences empiriques, étudiant comment les humains acquièrent des connaissances via des mécanismes psychologiques. &lt;/p&gt; &lt;p&gt; En logique, il développe "New Foundations" en 1937, un système alternatif à la théorie des types de Russell. Sur l'ontologie, il pose le critère "être, c'est être la "valeur d'une variable"  dans "On What There Is" en 1948, et introduit l'indétermination de la traduction dans Word and Object en 1960, montrant que les significations linguistiques ne sont pas fixées de manière unique par les données empiriques. Il promeut aussi l'ontologie relativiste, où les engagements ontologiques dépendent du cadre théorique. &lt;/p&gt; &lt;p&gt; Parmi ses livres phares figurent "From a Logical Point of View" paru en 1953, "Word and Object" en 1960, "Ontological Relativity" en 1969 et "Quiddities" en 1987. Il influence Kuhn, Putnam et le naturalisme contemporain, insistant que la philosophie doit se subordonner à la science sans présupposés a priori. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F32" s="7" t="s">
         <v>282</v>
@@ -4539,8 +4541,10 @@
       <c r="D54" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="E54" s="9" t="s">
-        <v>470</v>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Lewis_(philosophe)"  title=" Wikipedia"&gt;David LEWIS&lt;/a&gt; était un philosophe américain connu pour sa théorie du  réalisme modal, selon laquelle il existe un nombre infini de mondes possibles concrets et causalement isolés les uns des autres. Son ouvrage majeur   &lt;a href="https://www.youtube.com/watch?v=-QlqLDLifuc" title="David Lewis - "De la pluralité des mondes" - De quoi parle ce livre ? par Philosophie 21"&gt;"On the Plurality of Worlds"&lt;/a&gt;  sortie en 1986, expose cette position révolutionnaire : pour lui, chaque monde possible existe aussi réellement que notre monde actuel, et sert à comprendre la modalité, c'est-à-dire ce qui pourrait être ou ce qui doit être. &lt;/p&gt; &lt;p&gt; Il a également proposé la théorie des contreparties en logique modale : au lieu de supposer que les personnes ou objets existent dans plusieurs mondes possibles, il affirme que chaque individu de notre monde a des « contreparties » dans les autres mondes possibles qui partagent certaines caractéristiques mais ne sont pas identiques à lui. Cette approche constitue une alternative à la logique modale traditionnelle, notamment celle de Saul Kripke. &lt;/p&gt; &lt;p&gt; Sa métaphysique est marquée par une conception atomiste (pointilliste) : la réalité n’est qu’une vaste mosaïque de faits locaux, chaque fait étant centré sur un « point » ayant des propriétés intrinsèques. Ce point de vue s’inspire de David Hume, d’où le nom « survenance humienne », refusant les liens nécessaires entre les faits et privilégiant une juxtaposition de qualités locales. &lt;/p&gt; &lt;p&gt; Il  a beaucoup écrit sur la philosophie du langage, la philosophie de l’esprit, l’épistémologie, la logique philosophique et la philosophie des mathématiques. Son premier grand ouvrage, "Convention" de 1969, analyse les conventions sociales à l’aide de la théorie des jeux, en montrant leur caractère arbitraire et leur diffusion par la connaissance commune et le précédent. Il s a marqué durablement la philosophie analytique.  &lt;a href="https://www.youtube.com/watch?v=g3jQwDP_Lyc" title="David Lewis - "David Lewis Speaks at La Trobe University par TimeSparrow"&gt;"Ses théories&lt;/a&gt; sont incontournables dans les débats sur les mondes possibles, la modalité, la causalité, la convention sociale, et l’atomisme métaphysique. Ses ouvrages, tels que Counterfactuals et Philosophical Papers, restent des références dans l’analyse logique et conceptuelle contemporaine. &lt;/p&gt; &lt;audio controls title=" On dit de David Lewis que c'est le plus grand métaphysicien qu’on ait vu depuis Leibniz par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18292-28.02.2019-ITEMA_21995453-0.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F54" s="7" t="s">
         <v>471</v>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -3451,8 +3451,10 @@
       <c r="D29" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>252</v>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Ayn_Rand" title=" Wikipedia"&gt; Ayn RAND&lt;/a&gt; était une écrivaine, philosophe et théoricienne politique russo-américaine. Elle est née à Saint-Pétersbourg, en Russie, sous le nom d'Alissa Zinovievna Rosenbaum et a vécu une grande partie de sa vie aux États-Unis, où elle a émigré en 1926.   &lt;/p&gt; &lt;p&gt; Son courant de pensée, &lt;a href="https://www.youtube.com/watch?v=w-54oWWvw-k&amp;amp;ab_channel=BiTS%2Cmagazinepresqueculte-ARTE" title="Objectivisme: la philo pour les égoîste par Arte "&gt;l'Objectivisme&lt;/a&gt; met l'accent sur la primauté de la raison, l'éthique de&lt;a href="https://www.youtube.com/watch?v=k2mVwk16ifQ" title="AYN RAND - L'égoïsme est une vertu par Le Précepteur"&gt; l'égoïsme rationnel&lt;/a&gt;, le capitalisme de laissez-faire et la défense des droits individuels. Selon elle, l'individu rationnel est la plus haute valeur morale et la poursuite de son propre intérêt rationnel est le but de la vie. &lt;/p&gt; &lt;p&gt; Connue pour ses deux romans principaux :  &lt;a href="https://fr.wikipedia.org/wiki/La_Source_vive" title="La source vive par Wikipédia "&gt;"La Source vive"&lt;/a&gt; (The Fountainhead), où elle présente un architecte individualiste et indépendant qui se bat pour préserver son intégrité et son travail créatif face à une société qui valorise la conformité et le collectivisme. &lt;/p&gt; &lt;p&gt; Le plus célèbre, &lt;a href="https://www.youtube.com/watch?v=Rti2fNcf10U&amp;amp;ab_channel=Lextopia" title="La grève pour capitalistes par Lextopia "&gt;"La Grève"&lt;/a&gt; (Atlas Shrugged), où elle explore les conséquences d'une société où les esprits créatifs et les entrepreneurs se retirent pour protester contre les politiques gouvernementales oppressives. Ce livre présente également des concepts clés de sa philosophie, tels que la notion de "l'homme qui arrête le moteur du monde" et la croyance en la libre entreprise et en la recherche du  &lt;a href="https://www.youtube.com/watch?v=D-fU2DMB8T0&amp;amp;ab_channel=Kosmos" title="Faut il ne pensée qu'à soi ? par Kosmos "&gt;profit personnel&lt;/a&gt; comme moteurs de progrès. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=MA1gKCD1h30&amp;amp;ab_channel=gio" title="Interview de 1959 par gio "&gt;Ses idées&lt;/a&gt; ont suscité des réactions diverses et passionnées. Ses partisans la considèrent comme une championne de la liberté individuelle, du capitalisme et de la raison. Ses détracteurs la critiquent souvent pour son individualisme radical, son rejet des systèmes de soutien social et son manque d'empathie envers les faibles. &lt;/p&gt;  &lt;audio controls title="Egoïste et fier de l'être par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23118-15.06.2022-ITEMA_23059653-2022C12410S0166-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2960,84 +2960,106 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
+    <row r="18" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1">
+        <v>1880</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1973</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880 – 1973</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roy Wood SELLARS</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Roy_Wood_Sellars" title=" Wikipedia"&gt;Roy Wood SELLARS&lt;/a&gt; est un philosophe américain d’origine canadienne. Né dans l’Ontario, il grandit dans le Michigan, où son père est médecin de campagne, et fait presque toute sa carrière à l’université du Michigan, à Ann Arbor. Il est le père du philosophe Wilfrid Sellars. Au début du XXe siècle, alors que &lt;a href="https://fr.wikipedia.org/wiki/Id%C3%A9alisme_(philosophie)" title=" Wikipedia"&gt;l’idéalisme &lt;/a&gt;domine encore les universités américaines, il fait partie de ceux qui veulent revenir à un &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_%28philosophie%29" title=" Wikipedia"&gt;réalisme&lt;/a&gt; compatible avec les sciences.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Critical Realism&lt;/em&gt; (1916), puis dans un ouvrage collectif de 1920, il défend le &lt;a href="https://www.youtube.com/watch?v=260o2dD4sCk" title="Sellars and the History of Philosophy - W. Sellars, R.W. Sellars and the History of American Realism par Scuola di Scienze umane Università di Padova"&gt;"réalisme critique&lt;/a&gt;" : nous percevons bien des choses qui existent indépendamment de nous, mais à travers des contenus mentaux qui ne sont pas les choses elles-mêmes. Contre le réalisme naïf, la perception est une interprétation ; contre l’idéalisme, elle nous fait réellement connaître le monde. Dans &lt;em&gt;Evolutionary Naturalism&lt;/em&gt; (1922), il propose un matérialisme non réducteur : la nature produit, au cours de l’évolution, des niveaux d’organisation nouveaux, la vie puis l’esprit, qui ont leurs propres propriétés, sans rien de surnaturel. L’esprit n’est pas une substance à part : il est le cerveau lui-même, considéré à son niveau le plus élevé d’organisation.&lt;/p&gt; &lt;p&gt;Il applique ce naturalisme à la religion : dans &lt;em&gt;The Next Step in Religion&lt;/em&gt; (1918), il propose une religion sans Dieu, tournée vers l’accomplissement humain. Il est en 1933 le principal rédacteur du &lt;em&gt;Manifeste humaniste&lt;/em&gt;, qui défend un humanisme religieux sans surnaturel, et signe le second manifeste en 1973. Il meurt à Ann Arbor la même année, à quatre-vingt-treize ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3wVTdJsDjOE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Roy Wood Sellars: Challenging Philosophical Boundaries｜Philosopher Biography" par VIS PHILO.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rwsellars-mini.webp</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturalisme ; Réalisme ; Émergentisme</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe américain d’origine canadienne, théoricien du réalisme critique et du naturalisme évolutionniste.</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
         <v>1883</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B19" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E19" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F19" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G19" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>156</v>
-      </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
-        <v>1889</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alfonso_Reyes"  title=" Wikipedia"&gt;Alfonso REYES&lt;/a&gt; était un écrivain et philosophe &amp; diplomate  mexicain, souvent considéré comme l’un des grands humanistes de la langue espagnole au XXe siècle.  &lt;a href="https://www.persee.fr/doc/hispa_0007-4640_1960_num_62_1_3655"  title=" Alfonso Reyes par Persée"&gt;Sa pensée &lt;/a&gt; philosophique est inséparable de son travail d’essayiste, de critique littéraire et de médiateur entre les cultures européennes et latino‑américaines. &lt;/p&gt; &lt;p&gt; Son premier livre important, "Cuestiones estéticas" paru en  1911 est une série de réflexions sur l’esthétique et la critique littéraire, où il articule déjà l’idée que l’expérience artistique est une forme de connaissance privilégiée du monde. Il donne des conférences sur l’"esthétique classique", qui influenceront durablement l’orientation intellectuelle mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Il n’est pas un philosophe systématique au sens académique, mais un humaniste qui pense la littérature, l’histoire et le mythe comme voies d’accès à la réalité et à l’identité mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &lt;a href="https://www.youtube.com/watch?v=IeZKZ6PC9H4"  title=" Visión de Anáhuac de Alfonso Reyes par Literatubers"&gt;"Visión de Anáhuac"&lt;/a&gt;, il propose une méditation poétique et historique sur le Mexique préhispanique et la Conquête, en insistant sur la continuité d’une sensibilité mexicaine à travers les siècles. &lt;/p&gt; &lt;p&gt; Il défend une conception de l’homme formé par les lettres, la philosophie et les sciences, contre les réductions technocratiques ou purement utilitaires du savoir et pense l’Amérique latine comme espace de synthèse entre héritages indigènes, hispaniques et européens, et fait de la traduction et de la critique des instruments de ce dialogue. &lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>164</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="2" t="s">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>29</v>
@@ -3046,347 +3068,349 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Edward_Bernays" title=" Wikipedia"&gt;Edward BERNAYS&lt;/a&gt;, neveu de Sigmund FREUD était un célèbre publicitaire et consultant en relations publiques américain qui développa le Propogandisme. &lt;/p&gt; &lt;p&gt;  Il est connu pour son livre &lt;a href="https://www.youtube.com/watch?v=-M7E75MAWWM&amp;ab_channel=EcoMan%28i%29a"   title="L'ouvrage Propaganda par Eco Man"&gt; "Propaganda"&lt;/a&gt;, publié en 1928, dans lequel il décrit les techniques qu'il utilisait pour influencer l'opinion publique et manipuler les masses à des fins commerciales et politiques.&lt;/p&gt; &lt;p&gt;  Il a été un pionnier de l'utilisation de la psychologie et de la sociologie pour influencer les opinions et les comportements des consommateurs par la &lt;a href="https://www.vivrelibre.net/wp-content/uploads/2017/07/VL57.pdf"  title="La manipulation des esprits par Michel LEBLANC"&gt; manipulation des esprits&lt;/a&gt;. Il a utilisé des techniques telles que la manipulation des symboles et des images pour renforcer l'association d'un produit avec des valeurs ou des sentiments positifs dans l'esprit des consommateurs. &lt;/p&gt; &lt;p&gt; Il a également joué un rôle important dans la promotion du consumérisme en encourageant les gens à dépenser de l'argent pour des produits inutiles et en stimulant la demande pour de nouveaux produits.  Il a également été impliqué dans des campagnes de relations publiques pour des entreprises et des gouvernements, y compris la promotion du tabac auprès des femmes et la campagne pour la guerre américaine en Irak. &lt;/p&gt; &lt;p&gt;  Il est considéré comme le fondateur de la &lt;a href="https://www.youtube.com/watch?v=UvkhFpb7M7Y&amp;t=342s&amp;ab_channel=LePr%C3%A9cepteur"  title="Comment manipuler l'opinion par le Précepteur"&gt; manipulation de l'opinion &lt;/a&gt; publique moderne, son influence est souvent critiquée pour avoir encouragé une culture de la manipulation et de la tromperie dans les relations publiques et la publicité. &lt;/p&gt;  &lt;audio controls title="Propaganda ou comment manipuler l'opinion publique par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2012/01/s02/NET_e7ddaac9-fb30-445c-9784-f05763b129ef.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        <v>160</v>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alfonso_Reyes"  title=" Wikipedia"&gt;Alfonso REYES&lt;/a&gt; était un écrivain et philosophe &amp; diplomate  mexicain, souvent considéré comme l’un des grands humanistes de la langue espagnole au XXe siècle.  &lt;a href="https://www.persee.fr/doc/hispa_0007-4640_1960_num_62_1_3655"  title=" Alfonso Reyes par Persée"&gt;Sa pensée &lt;/a&gt; philosophique est inséparable de son travail d’essayiste, de critique littéraire et de médiateur entre les cultures européennes et latino‑américaines. &lt;/p&gt; &lt;p&gt; Son premier livre important, "Cuestiones estéticas" paru en  1911 est une série de réflexions sur l’esthétique et la critique littéraire, où il articule déjà l’idée que l’expérience artistique est une forme de connaissance privilégiée du monde. Il donne des conférences sur l’"esthétique classique", qui influenceront durablement l’orientation intellectuelle mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Il n’est pas un philosophe systématique au sens académique, mais un humaniste qui pense la littérature, l’histoire et le mythe comme voies d’accès à la réalité et à l’identité mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &lt;a href="https://www.youtube.com/watch?v=IeZKZ6PC9H4"  title=" Visión de Anáhuac de Alfonso Reyes par Literatubers"&gt;"Visión de Anáhuac"&lt;/a&gt;, il propose une méditation poétique et historique sur le Mexique préhispanique et la Conquête, en insistant sur la continuité d’une sensibilité mexicaine à travers les siècles. &lt;/p&gt; &lt;p&gt; Il défend une conception de l’homme formé par les lettres, la philosophie et les sciences, contre les réductions technocratiques ou purement utilitaires du savoir et pense l’Amérique latine comme espace de synthèse entre héritages indigènes, hispaniques et européens, et fait de la traduction et de la critique des instruments de ce dialogue. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F20" s="7" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="2" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>51</v>
+        <v>29</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
         <v>1891</v>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Edward_Bernays" title=" Wikipedia"&gt;Edward BERNAYS&lt;/a&gt;, neveu de Sigmund FREUD était un célèbre publicitaire et consultant en relations publiques américain qui développa le Propogandisme. &lt;/p&gt; &lt;p&gt;  Il est connu pour son livre &lt;a href="https://www.youtube.com/watch?v=-M7E75MAWWM&amp;ab_channel=EcoMan%28i%29a"   title="L'ouvrage Propaganda par Eco Man"&gt; "Propaganda"&lt;/a&gt;, publié en 1928, dans lequel il décrit les techniques qu'il utilisait pour influencer l'opinion publique et manipuler les masses à des fins commerciales et politiques.&lt;/p&gt; &lt;p&gt;  Il a été un pionnier de l'utilisation de la psychologie et de la sociologie pour influencer les opinions et les comportements des consommateurs par la &lt;a href="https://www.vivrelibre.net/wp-content/uploads/2017/07/VL57.pdf"  title="La manipulation des esprits par Michel LEBLANC"&gt; manipulation des esprits&lt;/a&gt;. Il a utilisé des techniques telles que la manipulation des symboles et des images pour renforcer l'association d'un produit avec des valeurs ou des sentiments positifs dans l'esprit des consommateurs. &lt;/p&gt; &lt;p&gt; Il a également joué un rôle important dans la promotion du consumérisme en encourageant les gens à dépenser de l'argent pour des produits inutiles et en stimulant la demande pour de nouveaux produits.  Il a également été impliqué dans des campagnes de relations publiques pour des entreprises et des gouvernements, y compris la promotion du tabac auprès des femmes et la campagne pour la guerre américaine en Irak. &lt;/p&gt; &lt;p&gt;  Il est considéré comme le fondateur de la &lt;a href="https://www.youtube.com/watch?v=UvkhFpb7M7Y&amp;t=342s&amp;ab_channel=LePr%C3%A9cepteur"  title="Comment manipuler l'opinion par le Précepteur"&gt; manipulation de l'opinion &lt;/a&gt; publique moderne, son influence est souvent critiquée pour avoir encouragé une culture de la manipulation et de la tromperie dans les relations publiques et la publicité. &lt;/p&gt;  &lt;audio controls title="Propaganda ou comment manipuler l'opinion publique par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2012/01/s02/NET_e7ddaac9-fb30-445c-9784-f05763b129ef.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B22" s="7" t="n">
         <v>1962</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D22" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher)"  title=" Wikipedia"&gt;Francisco ROMERO&lt;/a&gt; était un philosophe argentin d’origine espagnole, professeur à l’Université de Buenos Aires et à La Plata, et une figure centrale de la réaction  &lt;a href="https://fr.wikipedia.org/wiki/Ib%C3%A9ro-Am%C3%A9rique"  title="ibéro-amérique par wikipedia"&gt; ibéro-américaine &lt;/a&gt; contre le positivisme dominant au début du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa production philosophique couvre l’épistémologie, la philosophie de la culture et l’anthropologie philosophique ; son ouvrage majeur en langue espagnole, Teoría del hombre (1952), propose une réflexion systématique sur la condition humaine, la liberté et la créativité culturelle, et a été traduit en anglais sous le titre Theory of Man. &lt;/p&gt; &lt;p&gt; Il  prit position contre  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9ductionnisme"  title="Reductionnisme par wikipedia"&gt; le réductionnisme scientiste &lt;/a&gt; en défendant l’idée que la culture et les créations humaines (art, religion, langage) exigent des méthodes et des concepts propres, distincts des instruments des sciences naturelles ; il chercha donc à articuler rigueur philosophique et sensibilité littéraire. &lt;/p&gt; &lt;p&gt; Sur le plan méthodologique, il promut une philosophie qui dialogue avec l’histoire des idées et avec les problèmes concrets de la société ibéro-américaine : ses travaux montrent un intérêt marqué pour la responsabilité sociale des intellectuels et pour la formation culturelle des peuples. &lt;/p&gt; &lt;p&gt; Parmi ses autres ouvrages importants figurent Old and New Concepts of Reality (1932), The Problems of Philosophy of Culture (1938), Man and Culture (1950, traduction de El hombre y la cultura) et History of Modern Philosophy (1959); sa réputation lui valut le surnom de « doyen des philosophes ibéro-américains » et son héritage continue d’être étudié dans les études sur la philosophie latino‑américaine. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F22" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Francisco romero par Biografias de Filosofos</t>
         </is>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H22" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
-        <v>1894</v>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>1930</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="2" t="s">
-        <v>59</v>
+        <v>183</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>191</v>
+        <v>26</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>29</v>
       </c>
       <c r="P22" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="n">
+        <v>1894</v>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>1930</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
+    <row r="24" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
         <v>1895</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B24" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Susanne_Langer" title=" Wikipedia"&gt;Susanne LANGER&lt;/a&gt; était une philosophe américaine connue pour ses travaux sur le symbole, l’art et la perception. Elle a joué un rôle important dans la philosophie défendant l’idée que la pensée humaine ne se limite pas au langage discursif, mais s’exprime aussi à travers des formes symboliques non verbales, notamment artistiques. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=gwYNyxDTOhQ"   title=" suzanne langer par overthink podcast"&gt;Son œuvre &lt;/a&gt; la plus influente est sans doute Philosophy in a New Key (1942), où elle soutient que l’art n’est pas simplement une décoration ou une émotion brute, mais une forme de connaissance. Pour elle, la musique, la danse, la peinture ou la poésie donnent accès à des structures de sentiment que le langage ordinaire explique mal. Cette idée l’a rendue très importante pour l’esthétique et la théorie des symboles. &lt;/p&gt; &lt;p&gt; Elle s’inscrit dans une tradition marquée par Ernst Cassirer, qui voyait l’être humain comme un animal symbolique. Elle reprend cette intuition en affirmant que l’esprit humain construit le monde au moyen de symboles, et que ces symboles ne sont pas tous de même nature. Elle distingue ainsi les systèmes discursifs, qui avancent par étapes logiques, et les formes présentatives, plus propres à &lt;a href="https://www.youtube.com/watch?v=BM43-aqdboA"   title=" suzanne langer par philosophy overdose"&gt;l’art et à l’expérience sensible. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Son apport est aussi majeur en philosophie de l’art, car elle refuse de réduire l’œuvre à une simple expression subjective de l’artiste. Au contraire, elle cherche à montrer que l’œuvre organise une forme, un rythme et une structure qui rendent intelligible une expérience affective. Cette approche a eu une influence durable sur l’esthétique, la musique et plusieurs sciences humaines. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F24" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G24" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H24" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe américaine de l'art et des symboles, pour qui l'art est une forme de connaissance.</t>
-        </is>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
-        <v>1897</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Hartshorne"  title=" Wikipedia"&gt;Charles HARTSHORNE&lt;/a&gt; était un philosophe américain spécialiste de la philosophie de la religion et de la métaphysique. Il est surtout connu pour avoir développé la philosophie du processus &lt;a href="https://en.wikipedia.org/wiki/Alfred_North_Whitehead" title="d'Alfred North Whitehead par Wikipedia"&gt;d'Alfred North Whitehead&lt;/a&gt; en une théologie du processus, ou panenthéisme. Né dans une famille quaker et fils d'un ministre épiscopalien, il a étudié à Harvard et en Europe auprès de figures comme Husserl et Heidegger. &lt;/p&gt; &lt;p&gt; Il  &lt;a href="https://www.youtube.com/watch?v=s59DOhnuMwI" title="Charles Hartshorne Lecture - The Idea of Dual Transcendence, 1986 par Center for Process Studies"&gt;conçoit Dieu&lt;/a&gt; comme bipolaire : à la fois éternel et temporel, affecté par le monde tout en l'influençant, rejetant l'idée d'un Dieu immuable et omnipotent classique. Il a reformulé l'argument ontologique d'Anselme en une version modale, qu'il jugeait valide, et qui a relancé les débats des logiciens sur cette preuve. Ses &lt;a href="https://www.religion-online.org/article/the-philosophy-of-charles-hartshorne/"  title="The Philosophy of Charles Hartshorne par religion online"&gt;œuvres majeures&lt;/a&gt; incluent "The Divine Relativity  paru en 1948, "The Logic of Perfection" en 1962 et "Omnipotence and Other Theological Mistakes"  paru en 1983. &lt;/p&gt; &lt;p&gt;  Il a présidé l'American Philosophical Association et la Metaphysical Society of America, étendant son influence à la théologie, la psychologie et au-delà. Sa pensée met l'accent sur la créativité, le devenir et l'interdépendance universelle, critiquant des notions comme la via negativa. Assistant de Whitehead à Harvard, il a aussi édité avec Paul Weiss les œuvres de Charles Sanders Peirce, contribuant à faire connaître ce grand logicien. Ornithologue passionné, il a consacré un livre au chant des oiseaux, &lt;em&gt;Born to Sing&lt;/em&gt; (1973), où il soutient que les oiseaux chantent aussi par plaisir esthétique. Il est mort en 2000, à cent trois ans. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="2" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe américaine de l'art et des symboles, pour qui l'art est une forme de connaissance.</t>
+        </is>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
         <v>1897</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Samuel_Ramos"  title=" Wikipedia"&gt;Samuel RAMOS&lt;/a&gt; (1897-1959) est un philosophe mexicain, pionnier de la réflexion sur l’identité et la culture du Mexique. Élève d’Antonio Caso, il enseigne à l’Université nationale autonome du Mexique, où il forme plusieurs générations de philosophes. Il est l’un des premiers à se demander ce que peut être une philosophie proprement mexicaine.&lt;/p&gt; &lt;p&gt;Son livre le plus célèbre, &lt;em&gt;Le Profil de l’homme et de la culture au Mexique&lt;/em&gt; (1934), applique au caractère national deux outils venus d’Europe : la philosophie de José Ortega y Gasset, pour qui toute pensée part d’une situation concrète, et la psychologie d’Alfred Adler, qui étudie le sentiment d’infériorité. Ramos soutient que le Mexicain, depuis la conquête et la colonisation, souffre d’un complexe d’infériorité face à l’Europe. Ce complexe se cache derrière des attitudes de compensation : la susceptibilité, la méfiance, le machisme ou l’imitation des modèles étrangers, qu’il appelle une « imitation extralogique ». Il ne s’agit pas pour lui de condamner son peuple, mais de l’aider à prendre conscience de lui-même pour se libérer. Le Mexique doit construire une culture authentique, ni simple copie de l’Europe ni folklore replié sur lui-même, qui assume son histoire tout en s’ouvrant à l’universel. Il écrit aussi la première &lt;em&gt;Histoire de la philosophie au Mexique&lt;/em&gt; (1943). Dans &lt;a href="https://fr.slideshare.net/slideshow/samuel-ramos-hacia-un-nuevo-humanismo/15149441"  title="Samuel ramos hacia un nuevo humanismo par slideshare"&gt;&lt;em&gt;Vers un nouvel humanisme&lt;/em&gt;&lt;/a&gt; (1940), il défend une conception de l’homme qui unit la raison, les valeurs et la culture.&lt;/p&gt; &lt;p&gt;Son œuvre ouvre la voie au groupe Hiperión, à Leopoldo Zea et à Octavio Paz, auteur du &lt;em&gt;Labyrinthe de la solitude&lt;/em&gt;.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Hartshorne"  title=" Wikipedia"&gt;Charles HARTSHORNE&lt;/a&gt; était un philosophe américain spécialiste de la philosophie de la religion et de la métaphysique. Il est surtout connu pour avoir développé la philosophie du processus &lt;a href="https://en.wikipedia.org/wiki/Alfred_North_Whitehead" title="d'Alfred North Whitehead par Wikipedia"&gt;d'Alfred North Whitehead&lt;/a&gt; en une théologie du processus, ou panenthéisme. Né dans une famille quaker et fils d'un ministre épiscopalien, il a étudié à Harvard et en Europe auprès de figures comme Husserl et Heidegger. &lt;/p&gt; &lt;p&gt; Il  &lt;a href="https://www.youtube.com/watch?v=s59DOhnuMwI" title="Charles Hartshorne Lecture - The Idea of Dual Transcendence, 1986 par Center for Process Studies"&gt;conçoit Dieu&lt;/a&gt; comme bipolaire : à la fois éternel et temporel, affecté par le monde tout en l'influençant, rejetant l'idée d'un Dieu immuable et omnipotent classique. Il a reformulé l'argument ontologique d'Anselme en une version modale, qu'il jugeait valide, et qui a relancé les débats des logiciens sur cette preuve. Ses &lt;a href="https://www.religion-online.org/article/the-philosophy-of-charles-hartshorne/"  title="The Philosophy of Charles Hartshorne par religion online"&gt;œuvres majeures&lt;/a&gt; incluent "The Divine Relativity  paru en 1948, "The Logic of Perfection" en 1962 et "Omnipotence and Other Theological Mistakes"  paru en 1983. &lt;/p&gt; &lt;p&gt;  Il a présidé l'American Philosophical Association et la Metaphysical Society of America, étendant son influence à la théologie, la psychologie et au-delà. Sa pensée met l'accent sur la créativité, le devenir et l'interdépendance universelle, critiquant des notions comme la via negativa. Assistant de Whitehead à Harvard, il a aussi édité avec Paul Weiss les œuvres de Charles Sanders Peirce, contribuant à faire connaître ce grand logicien. Ornithologue passionné, il a consacré un livre au chant des oiseaux, &lt;em&gt;Born to Sing&lt;/em&gt; (1973), où il soutient que les oiseaux chantent aussi par plaisir esthétique. Il est mort en 2000, à cent trois ans. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F25" s="7" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="2" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>221</v>
+        <v>158</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>224</v>
+        <v>213</v>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Samuel_Ramos"  title=" Wikipedia"&gt;Samuel RAMOS&lt;/a&gt; (1897-1959) est un philosophe mexicain, pionnier de la réflexion sur l’identité et la culture du Mexique. Élève d’Antonio Caso, il enseigne à l’Université nationale autonome du Mexique, où il forme plusieurs générations de philosophes. Il est l’un des premiers à se demander ce que peut être une philosophie proprement mexicaine.&lt;/p&gt; &lt;p&gt;Son livre le plus célèbre, &lt;em&gt;Le Profil de l’homme et de la culture au Mexique&lt;/em&gt; (1934), applique au caractère national deux outils venus d’Europe : la philosophie de José Ortega y Gasset, pour qui toute pensée part d’une situation concrète, et la psychologie d’Alfred Adler, qui étudie le sentiment d’infériorité. Ramos soutient que le Mexicain, depuis la conquête et la colonisation, souffre d’un complexe d’infériorité face à l’Europe. Ce complexe se cache derrière des attitudes de compensation : la susceptibilité, la méfiance, le machisme ou l’imitation des modèles étrangers, qu’il appelle une « imitation extralogique ». Il ne s’agit pas pour lui de condamner son peuple, mais de l’aider à prendre conscience de lui-même pour se libérer. Le Mexique doit construire une culture authentique, ni simple copie de l’Europe ni folklore replié sur lui-même, qui assume son histoire tout en s’ouvrant à l’universel. Il écrit aussi la première &lt;em&gt;Histoire de la philosophie au Mexique&lt;/em&gt; (1943). Dans &lt;a href="https://fr.slideshare.net/slideshow/samuel-ramos-hacia-un-nuevo-humanismo/15149441"  title="Samuel ramos hacia un nuevo humanismo par slideshare"&gt;&lt;em&gt;Vers un nouvel humanisme&lt;/em&gt;&lt;/a&gt; (1940), il défend une conception de l’homme qui unit la raison, les valeurs et la culture.&lt;/p&gt; &lt;p&gt;Son œuvre ouvre la voie au groupe Hiperión, à Leopoldo Zea et à Octavio Paz, auteur du &lt;em&gt;Labyrinthe de la solitude&lt;/em&gt;.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F26" s="7" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="2" t="s">
-        <v>37</v>
+        <v>218</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>29</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
-        <v>1901</v>
+        <v>1898</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="2" t="s">
-        <v>237</v>
+        <v>37</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>176</v>
@@ -3395,41 +3419,40 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
+    <row r="28" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="n">
         <v>1901</v>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>1985</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ernest nagel on computers, logic and mind par Philosophy Overdose</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>245</v>
-      </c>
+      <c r="B28" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="I28" s="9"/>
       <c r="J28" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>176</v>
@@ -3438,491 +3461,492 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
-        <v>1905</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Ayn_Rand" title=" Wikipedia"&gt; Ayn RAND&lt;/a&gt; était une écrivaine, philosophe et théoricienne politique russo-américaine. Elle est née à Saint-Pétersbourg, en Russie, sous le nom d'Alissa Zinovievna Rosenbaum et a vécu une grande partie de sa vie aux États-Unis, où elle a émigré en 1926.   &lt;/p&gt; &lt;p&gt; Son courant de pensée, &lt;a href="https://www.youtube.com/watch?v=w-54oWWvw-k&amp;amp;ab_channel=BiTS%2Cmagazinepresqueculte-ARTE" title="Objectivisme: la philo pour les égoîste par Arte "&gt;l'Objectivisme&lt;/a&gt; met l'accent sur la primauté de la raison, l'éthique de&lt;a href="https://www.youtube.com/watch?v=k2mVwk16ifQ" title="AYN RAND - L'égoïsme est une vertu par Le Précepteur"&gt; l'égoïsme rationnel&lt;/a&gt;, le capitalisme de laissez-faire et la défense des droits individuels. Selon elle, l'individu rationnel est la plus haute valeur morale et la poursuite de son propre intérêt rationnel est le but de la vie. &lt;/p&gt; &lt;p&gt; Connue pour ses deux romans principaux :  &lt;a href="https://fr.wikipedia.org/wiki/La_Source_vive" title="La source vive par Wikipédia "&gt;"La Source vive"&lt;/a&gt; (The Fountainhead), où elle présente un architecte individualiste et indépendant qui se bat pour préserver son intégrité et son travail créatif face à une société qui valorise la conformité et le collectivisme. &lt;/p&gt; &lt;p&gt; Le plus célèbre, &lt;a href="https://www.youtube.com/watch?v=Rti2fNcf10U&amp;amp;ab_channel=Lextopia" title="La grève pour capitalistes par Lextopia "&gt;"La Grève"&lt;/a&gt; (Atlas Shrugged), où elle explore les conséquences d'une société où les esprits créatifs et les entrepreneurs se retirent pour protester contre les politiques gouvernementales oppressives. Ce livre présente également des concepts clés de sa philosophie, tels que la notion de "l'homme qui arrête le moteur du monde" et la croyance en la libre entreprise et en la recherche du  &lt;a href="https://www.youtube.com/watch?v=D-fU2DMB8T0&amp;amp;ab_channel=Kosmos" title="Faut il ne pensée qu'à soi ? par Kosmos "&gt;profit personnel&lt;/a&gt; comme moteurs de progrès. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=MA1gKCD1h30&amp;amp;ab_channel=gio" title="Interview de 1959 par gio "&gt;Ses idées&lt;/a&gt; ont suscité des réactions diverses et passionnées. Ses partisans la considèrent comme une championne de la liberté individuelle, du capitalisme et de la raison. Ses détracteurs la critiquent souvent pour son individualisme radical, son rejet des systèmes de soutien social et son manque d'empathie envers les faibles. &lt;/p&gt;  &lt;audio controls title="Egoïste et fier de l'être par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23118-15.06.2022-ITEMA_23059653-2022C12410S0166-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D-fU2DMB8T0</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Ayn Rand - Faut-il ne penser qu'à soi ?" par Kosmos</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I29" s="9"/>
+    <row r="29" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>1985</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ernest nagel on computers, logic and mind par Philosophy Overdose</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>245</v>
+      </c>
       <c r="J29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Objectivisme ; Libéralisme ; Minarchisme</t>
-        </is>
+        <v>246</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>258</v>
+        <v>176</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="252" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="n">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hannah_Arendt"  title=" Wikipedia"&gt;Hannah ARENDT&lt;/a&gt; était une femme philosophe allemande  &lt;a href="https://allemagneenfrance.diplo.de/fr-fr/actualites-nouvelles-d-allemagne/07-culture/2680094-2680094" title="Hannah Arendt, une vie d'exil  par Missions allemandes en France"&gt;naturalisée américaine&lt;/a&gt; et formée dans la tradition philosophique allemande, notamment auprès de Martin Heidegger et de Karl Jaspers. Elle a également été marquée par la phénoménologie (Husserl) et la pensée de Kant, tout en s'éloignant de la philosophie pure pour développer une réflexion ancrée dans le réel. Les &lt;a href="https://scienceetbiencommun.pressbooks.pub/femmessavantes2/chapter/hannah-arendt-philosophe-1906-1975/" style="color:#88A1E9" title="Hannah Arendt par Esbc"&gt;thèmes majeurs&lt;/a&gt; de sa pensée seront : &lt;/p&gt; &lt;p&gt;"Les Origines du totalitarisme" : Elle analyse le nazisme et le stalinisme comme des régimes totalitaires inédits dans l'histoire, caractérisés par la destruction des structures sociales et politiques traditionnelles et avec l'idéologie comme moteur absolu (la race pour les nazis, la lutte des classes pour les staliniens) tout en  semant la terreur systématique et les camps comme laboratoires de la domination totale. &lt;/p&gt; &lt;p&gt;"Eichmann à Jérusalem"  : En couvrant le procès d'Adolf Eichmann, responsable logistique de la Shoah, elle introduit l'idée controversée de la &lt;a href="https://www.youtube.com/watch?v=5iQkmzmkJEs" title="La banalité du mal par digiSchool Lycée"&gt;"banalité du mal"&lt;/a&gt;.  Eichmann n'était pas un monstre, mais un bureaucrate ordinaire, incapable de penser par lui-même, obéissant aveuglément aux ordres. Le mal, dans ce cas, résulte de &lt;a href="https://www.youtube.com/watch?v=fNri0ZxoEQY"  title="la banalité du mal de Hannah Arendt par Alain Bajomée"&gt;l'absence de réflexion&lt;/a&gt; critique. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=5bey28ALopE"  title="la philo de Hannah Arendt par Parole de philosophe"&gt;"Condition de l'homme moderne"&lt;/a&gt; ou elle distingue trois dimensions de l'existence humaine : &lt;p&gt;Le travail : Activité cyclique liée à la survie biologique (production/consommation). &lt;/p&gt; &lt;p&gt;L'œuvre : Création d'un monde durable (art, technique, institutions). &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=lCOxpdXgkHI" title="Hannah Arendt 1973 par olivier-berruter-les-crises"&gt; L'action&lt;/a&gt; : Activité proprement politique, fondée sur la pluralité et la liberté, où les hommes agissent et parlent ensemble pour construire un monde commun. &lt;/p&gt; &lt;p&gt; Dans sa dernière oeuvre  "La Vie de l'esprit" (inachevé), elle explore les facultés de penser, vouloir et juger. Le jugement, en particulier, est crucial pour résister à l'idéologie, il suppose la capacité à voir les choses depuis le point de vue d'autrui (élargissement de l'esprit chez Kant). &lt;/p&gt;   &lt;audio controls title="Hannah Arendt, la passagère par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14373-18.08.2017-ITEMA_21410372-2017C49904E0021-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>263</v>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Ayn_Rand" title=" Wikipedia"&gt; Ayn RAND&lt;/a&gt; était une écrivaine, philosophe et théoricienne politique russo-américaine. Elle est née à Saint-Pétersbourg, en Russie, sous le nom d'Alissa Zinovievna Rosenbaum et a vécu une grande partie de sa vie aux États-Unis, où elle a émigré en 1926.   &lt;/p&gt; &lt;p&gt; Son courant de pensée, &lt;a href="https://www.youtube.com/watch?v=w-54oWWvw-k&amp;amp;ab_channel=BiTS%2Cmagazinepresqueculte-ARTE" title="Objectivisme: la philo pour les égoîste par Arte "&gt;l'Objectivisme&lt;/a&gt; met l'accent sur la primauté de la raison, l'éthique de&lt;a href="https://www.youtube.com/watch?v=k2mVwk16ifQ" title="AYN RAND - L'égoïsme est une vertu par Le Précepteur"&gt; l'égoïsme rationnel&lt;/a&gt;, le capitalisme de laissez-faire et la défense des droits individuels. Selon elle, l'individu rationnel est la plus haute valeur morale et la poursuite de son propre intérêt rationnel est le but de la vie. &lt;/p&gt; &lt;p&gt; Connue pour ses deux romans principaux :  &lt;a href="https://fr.wikipedia.org/wiki/La_Source_vive" title="La source vive par Wikipédia "&gt;"La Source vive"&lt;/a&gt; (The Fountainhead), où elle présente un architecte individualiste et indépendant qui se bat pour préserver son intégrité et son travail créatif face à une société qui valorise la conformité et le collectivisme. &lt;/p&gt; &lt;p&gt; Le plus célèbre, &lt;a href="https://www.youtube.com/watch?v=Rti2fNcf10U&amp;amp;ab_channel=Lextopia" title="La grève pour capitalistes par Lextopia "&gt;"La Grève"&lt;/a&gt; (Atlas Shrugged), où elle explore les conséquences d'une société où les esprits créatifs et les entrepreneurs se retirent pour protester contre les politiques gouvernementales oppressives. Ce livre présente également des concepts clés de sa philosophie, tels que la notion de "l'homme qui arrête le moteur du monde" et la croyance en la libre entreprise et en la recherche du  &lt;a href="https://www.youtube.com/watch?v=D-fU2DMB8T0&amp;amp;ab_channel=Kosmos" title="Faut il ne pensée qu'à soi ? par Kosmos "&gt;profit personnel&lt;/a&gt; comme moteurs de progrès. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=MA1gKCD1h30&amp;amp;ab_channel=gio" title="Interview de 1959 par gio "&gt;Ses idées&lt;/a&gt; ont suscité des réactions diverses et passionnées. Ses partisans la considèrent comme une championne de la liberté individuelle, du capitalisme et de la raison. Ses détracteurs la critiquent souvent pour son individualisme radical, son rejet des systèmes de soutien social et son manque d'empathie envers les faibles. &lt;/p&gt;  &lt;audio controls title="Egoïste et fier de l'être par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23118-15.06.2022-ITEMA_23059653-2022C12410S0166-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D-fU2DMB8T0</t>
+        </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Hannah ARENDT: la philosophe par Coursitout</t>
+          <t xml:space="preserve">"Ayn Rand - Faut-il ne penser qu'à soi ?" par Kosmos</t>
         </is>
       </c>
       <c r="H30" s="9" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>266</v>
+        <v>70</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Objectivisme ; Libéralisme ; Minarchisme</t>
+        </is>
       </c>
       <c r="L30" s="2" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O30" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="31" customFormat="false" ht="252" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
         <v>1906</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hannah_Arendt"  title=" Wikipedia"&gt;Hannah ARENDT&lt;/a&gt; était une femme philosophe allemande  &lt;a href="https://allemagneenfrance.diplo.de/fr-fr/actualites-nouvelles-d-allemagne/07-culture/2680094-2680094" title="Hannah Arendt, une vie d'exil  par Missions allemandes en France"&gt;naturalisée américaine&lt;/a&gt; et formée dans la tradition philosophique allemande, notamment auprès de Martin Heidegger et de Karl Jaspers. Elle a également été marquée par la phénoménologie (Husserl) et la pensée de Kant, tout en s'éloignant de la philosophie pure pour développer une réflexion ancrée dans le réel. Les &lt;a href="https://scienceetbiencommun.pressbooks.pub/femmessavantes2/chapter/hannah-arendt-philosophe-1906-1975/" style="color:#88A1E9" title="Hannah Arendt par Esbc"&gt;thèmes majeurs&lt;/a&gt; de sa pensée seront : &lt;/p&gt; &lt;p&gt;"Les Origines du totalitarisme" : Elle analyse le nazisme et le stalinisme comme des régimes totalitaires inédits dans l'histoire, caractérisés par la destruction des structures sociales et politiques traditionnelles et avec l'idéologie comme moteur absolu (la race pour les nazis, la lutte des classes pour les staliniens) tout en  semant la terreur systématique et les camps comme laboratoires de la domination totale. &lt;/p&gt; &lt;p&gt;"Eichmann à Jérusalem"  : En couvrant le procès d'Adolf Eichmann, responsable logistique de la Shoah, elle introduit l'idée controversée de la &lt;a href="https://www.youtube.com/watch?v=5iQkmzmkJEs" title="La banalité du mal par digiSchool Lycée"&gt;"banalité du mal"&lt;/a&gt;.  Eichmann n'était pas un monstre, mais un bureaucrate ordinaire, incapable de penser par lui-même, obéissant aveuglément aux ordres. Le mal, dans ce cas, résulte de &lt;a href="https://www.youtube.com/watch?v=fNri0ZxoEQY"  title="la banalité du mal de Hannah Arendt par Alain Bajomée"&gt;l'absence de réflexion&lt;/a&gt; critique. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=5bey28ALopE"  title="la philo de Hannah Arendt par Parole de philosophe"&gt;"Condition de l'homme moderne"&lt;/a&gt; ou elle distingue trois dimensions de l'existence humaine : &lt;p&gt;Le travail : Activité cyclique liée à la survie biologique (production/consommation). &lt;/p&gt; &lt;p&gt;L'œuvre : Création d'un monde durable (art, technique, institutions). &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=lCOxpdXgkHI" title="Hannah Arendt 1973 par olivier-berruter-les-crises"&gt; L'action&lt;/a&gt; : Activité proprement politique, fondée sur la pluralité et la liberté, où les hommes agissent et parlent ensemble pour construire un monde commun. &lt;/p&gt; &lt;p&gt; Dans sa dernière oeuvre  "La Vie de l'esprit" (inachevé), elle explore les facultés de penser, vouloir et juger. Le jugement, en particulier, est crucial pour résister à l'idéologie, il suppose la capacité à voir les choses depuis le point de vue d'autrui (élargissement de l'esprit chez Kant). &lt;/p&gt;   &lt;audio controls title="Hannah Arendt, la passagère par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14373-18.08.2017-ITEMA_21410372-2017C49904E0021-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Hannah ARENDT: la philosophe par Coursitout</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="I31" s="9"/>
+      <c r="J31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C32" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D32" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nelson_Goodman"  title=" Wikipedia"&gt;Nelson GOODMAN&lt;/a&gt; était un philosophe américain connu pour ses contributions à la philosophie analytique, l’esthétique et la philosophie de la science. Il est l’un des grands défenseurs d’un nominalisme contemporain qui remet en question le fondement des ensembles et des classes comme entités réelles, préférant des cadres descriptifs et structurels pour rendre compte du monde. &lt;/p&gt; &lt;p&gt;  Il a aussi développé des réflexions sur l’induction et le problème du diamètre entre nos théories et les phénomènes, parfois illustrés par &lt;a href="https://www.youtube.com/watch?v=vEqZhRcvQME"  title=" Le paradoxe de Goodman (est-ce que toutes les émeraudes sont vertes ?) par Maêl Cavan"&gt; des paradoxes logiques célèbres&lt;/a&gt;. Son œuvre est également marquée par l’esthétique analytique, où il explore la  &lt;a href="https://www.youtube.com/watch?v=hJNmeVrsx5c"  title="Nelson Goodman , peut on parler d'art? par Erème"&gt;nature de l’art&lt;/a&gt; et de l’évaluation esthétique. &lt;/p&gt; &lt;p&gt;Structure de l’apparence paru en 1951 et les orientations autour du reconstructionnisme logique du monde à partir des apparences perceptibles, sans appui ontologique lourd. &lt;/p&gt; &lt;p&gt;L’induction et le paradoxe de Goodman, où il questionne comment les prédictions et les justifications se lisent à travers des exemples comme le paradoxe des "new rickets" (exemple classique), montrant des limites de nos méthodes inductives. &lt;/p&gt; &lt;p&gt;Nominalisme et mereology: avec des penseurs comme Stanisław Leśniewski, il soutient une approche où les entités mathématiques et logiques ne nécessitent pas une base ontologique robuste en dehors des descriptions et des relations que l’on peut formaliser. &lt;/p&gt; &lt;p&gt; Il  a influencé la  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1972_num_70_6_5675_t1_0319_0000_2" title="Nelson Goodman, Languages of art. An approach to a theory of symbols par Persée"&gt;philosophie du langage,&lt;/a&gt; la logique et l’esthétique analytique, et ses idées ont suscité de nombreux débats sur la nature des objets, des propriétés et des cadres de description. Ses étudiants et collègues (dont Noam Chomsky et Hilary Putnam à Harvard) témoignent de son impact durable sur la philosophie analytique américaine. &lt;/p&gt;    &lt;audio controls title="La fabrique des mondes selon Nelson Goodman par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16409-22.06.2007-ITEMA_20075915-2007C6409S0173-NET_BF330E12-B7F0-45F9-9A8C-43C9F305150C_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
 ​
 </t>
         </is>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F32" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G32" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H32" s="9" t="s">
         <v>275</v>
-      </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Analytique ; Nominalisme ; Méréologie</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="n">
-        <v>1908</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Willard_Van_Orman_Quine"  title=" Wikipedia"&gt;Williard Van Orman QUINE&lt;/a&gt; était un philosophe américain,  figure centrale de la philosophie analytique. Connu pour son naturalisme radical et sa critique des fondements traditionnels de l'épistémologie, il a profondément influencé la philosophie des sciences, de la logique et du langage. &lt;/p&gt; &lt;p&gt;Il  rejette la distinction analytique-synthétique dans son article célèbre "Two Dogmas of Empiricism" paru en 1951, critiquant l'empirisme logique du Cercle de Vienne. Il défend un holisme épistémique où les &lt;a href="https://www.persee.fr/doc/intel_0769-4113_2015_num_64_2_1016"  title="Le langage et la science chez Quine ou les racines de la rédemption. Compte-rendu du livre de Michel Olivier, Quine, Paris, Belles Lettres par Persée"&gt;théories scientifiques &lt;/a&gt; sont testées globalement face à l'expérience, et non isolément. Son épistémologie naturalisée voit la philosophie comme une branche des sciences empiriques, étudiant comment les humains acquièrent des connaissances via des mécanismes psychologiques. &lt;/p&gt; &lt;p&gt; En logique, il développe "New Foundations" en 1937, un système alternatif à la théorie des types de Russell. Sur l'ontologie, il pose le critère "être, c'est être la "valeur d'une variable"  dans "On What There Is" en 1948, et introduit l'indétermination de la traduction dans Word and Object en 1960, montrant que les significations linguistiques ne sont pas fixées de manière unique par les données empiriques. Il promeut aussi l'ontologie relativiste, où les engagements ontologiques dépendent du cadre théorique. &lt;/p&gt; &lt;p&gt; Parmi ses livres phares figurent "From a Logical Point of View" paru en 1953, "Word and Object" en 1960, "Ontological Relativity" en 1969 et "Quiddities" en 1987. Il influence Kuhn, Putnam et le naturalisme contemporain, insistant que la philosophie doit se subordonner à la science sans présupposés a priori. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="2" t="s">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytique ; Nominalisme ; Empirisme ; Holisme ; Ontologie</t>
+          <t xml:space="preserve">Analytique ; Nominalisme ; Méréologie</t>
         </is>
       </c>
       <c r="L32" s="2" t="s">
-        <v>286</v>
+        <v>278</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Willard_Van_Orman_Quine"  title=" Wikipedia"&gt;Williard Van Orman QUINE&lt;/a&gt; était un philosophe américain,  figure centrale de la philosophie analytique. Connu pour son naturalisme radical et sa critique des fondements traditionnels de l'épistémologie, il a profondément influencé la philosophie des sciences, de la logique et du langage. &lt;/p&gt; &lt;p&gt;Il  rejette la distinction analytique-synthétique dans son article célèbre "Two Dogmas of Empiricism" paru en 1951, critiquant l'empirisme logique du Cercle de Vienne. Il défend un holisme épistémique où les &lt;a href="https://www.persee.fr/doc/intel_0769-4113_2015_num_64_2_1016"  title="Le langage et la science chez Quine ou les racines de la rédemption. Compte-rendu du livre de Michel Olivier, Quine, Paris, Belles Lettres par Persée"&gt;théories scientifiques &lt;/a&gt; sont testées globalement face à l'expérience, et non isolément. Son épistémologie naturalisée voit la philosophie comme une branche des sciences empiriques, étudiant comment les humains acquièrent des connaissances via des mécanismes psychologiques. &lt;/p&gt; &lt;p&gt; En logique, il développe "New Foundations" en 1937, un système alternatif à la théorie des types de Russell. Sur l'ontologie, il pose le critère "être, c'est être la "valeur d'une variable"  dans "On What There Is" en 1948, et introduit l'indétermination de la traduction dans Word and Object en 1960, montrant que les significations linguistiques ne sont pas fixées de manière unique par les données empiriques. Il promeut aussi l'ontologie relativiste, où les engagements ontologiques dépendent du cadre théorique. &lt;/p&gt; &lt;p&gt; Parmi ses livres phares figurent "From a Logical Point of View" paru en 1953, "Word and Object" en 1960, "Ontological Relativity" en 1969 et "Quiddities" en 1987. Il influence Kuhn, Putnam et le naturalisme contemporain, insistant que la philosophie doit se subordonner à la science sans présupposés a priori. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="I33" s="9"/>
+      <c r="J33" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Nominalisme ; Empirisme ; Holisme ; Ontologie</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="n">
         <v>1912</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B34" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D34" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leopoldo_Zea_Aguilar" title=" Wikipedia"&gt;Leopoldo ZEA AGUILAR&lt;/a&gt; était un philosophe mexicain, considéré comme l'un des pères fondateurs de la philosophie latino-américaine contemporaine, engagé dans la quête d'une identité culturelle autonome face à l'eurocentrisme et au néocolonialisme. &lt;/p&gt; &lt;p&gt;  Il pose la question centrale : "Peut-on construire une philosophie latino-américaine ?" Réponse affirmative via une dialectique de la conscience : de la dépendance à la libération, où l'homme latino-américain réalise sa liberté par la reconnaissance de sa singularité culturelle. Relativiste culturel sans relativisme absolu, il définit l'homme comme ouvert et pluriel, rejetant l'eurocentrisme comme domination masquée ; la philosophie devient &lt;a href="https://ensayistas.org/antologia/XXA/zea/zea2.htm" title="Leopoldo Zea Aguilar | Autopercepción intelectual de un proceso histórico par ensayistas"&gt;"instrument de libération"&lt;/a&gt;, transformant l'histoire en projet éthique-politique de dignité, égalité et solidarité. Précurseur des critiques post-coloniales et postmodernes, il voit 1492 non comme "découverte" mais comme "occultation" culturelle, et la philosophie latino-américaine comme symbiose de nationalisme, christianisme et socialisme anti-impérialiste. &lt;/p&gt; &lt;p&gt; Mentor de générations, il fonde des centres intellectuels en Amérique latine et reçoit des prix mondiaux ; son discours sur la marginalité influence la philosophie de la libération et les études culturelles décoloniales. Il reste &lt;a href="https://www.youtube.com/watch?v=_kEH9wQFQv4" style="color:#88A1E9" title="Leopoldo Zea Aguilar | Doctorado en Educación par Miguel Morales"&gt;une référence &lt;/a&gt; pour une Amérique latine unie, non utopique mais réaliste, affirmant : "Se connaître égal en étant distinct est l'essence des relations humaines et internationales". &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F34" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G34" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H34" s="9" t="s">
         <v>293</v>
-      </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="n">
-        <v>1916</v>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>1999</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>301</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="n">
+        <v>1916</v>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>1999</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I35" s="9"/>
+      <c r="J35" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Méréologie ; Analytique ; Libertarianisme ; Particularisme ; Incompatibilisme</t>
         </is>
       </c>
-      <c r="L34" s="14" t="s">
+      <c r="L35" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="N35" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="174.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="n">
+    <row r="36" customFormat="false" ht="174.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="n">
         <v>1921</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B36" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D36" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Rawls_(philosophe)"  title=" Wikipedia"&gt;John RAWLS&lt;/a&gt; était un  philosophe politique américain connu grâce à son œuvre majeure "&lt;a href="https://www.youtube.com/watch?v=OIKwI5qu4y8" style="color:#88A1E9" title=" La THÉORIE DE LA JUSTICE en 8 minutes ! (John RAWLS) par Culture Philo"&gt; A Theory of Justice&lt;/a&gt;", publiée en 1971 ou il propose une conception de la  &lt;a href="https://www.youtube.com/watch?v=2w-AEMAU_EE"  title=" Le libéralisme égalitaire de John Rawls par Philoxime"&gt;"justice comme équité"&lt;/a&gt;. Il s’oppose à l’utilitarisme – doctrine selon laquelle une action est bonne si elle maximise le bonheur collectif – et cherche au contraire à fonder la justice sur des principes garantissant équitablement les libertés et droits fondamentaux pour tous. &lt;/p&gt; &lt;p&gt;  Il imagine une " &lt;a href="https://www.persee.fr/doc/rfsp_0035-2950_1991_num_41_1_394540"  title="La Théorie de la justice de John Rawls. Contrat social versus utilitarisme par Persée"&gt;position originelle&lt;/a&gt;", situation hypothétique où des individus rationnels, placés derrière un « voile d’ignorance » qui leur cache leurs avantages personnels, choisiraient des règles de justice justes pour tous. De cette expérience de pensée, il déduit deux principes essentiels dont le principe d’égale liberté où chaque personne doit avoir un droit égal aux libertés fondamentales et le principe de différence où les inégalités économiques et sociales ne sont justes que si elles profitent aux plus désavantagés.  &lt;/p&gt; &lt;p&gt; Il a ensuite  prolongé sa réflexion dans "Political Liberalism" (1993) et "The Law of Peoples" (1999). Dans le premier, il interroge comment un consensus moral peut se former dans des sociétés pluralistes sans imposer une doctrine particulière ; dans le second, il applique ses principes à la &lt;a href="https://www.youtube.com/watch?v=ah7y1xd3bL0" title="JOHN RAWLS : Qu'est-ce que la justice sociale ? par Parole de Philosophe"&gt;justice internationale&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;  Il a profondément marqué la philosophie morale, politique et économique contemporaine et sa pensée inspira la théorie économique critique, avec des débats persistants sur la compatibilité de sa vision avec le libéralisme ou la social-démocratie et il demeure aujourd’hui une référence incontournable pour toute réflexion sur la justice, l’égalité et la démocratie. &lt;/p&gt; &lt;audio controls title=" Avoir raison avec... John Rawls par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-13.07.2020-ITEMA_22381527-2020C35448S0195-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F36" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">"
 Philosophie - John Rawls et le voile d'ignorance" par Coursitout</t>
         </is>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H36" s="9" t="s">
         <v>310</v>
-      </c>
-      <c r="I35" s="9"/>
-      <c r="J35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libéralisme ; Contractualisme ; Social-démocratie ; Déontologisme</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="n">
-        <v>1922</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Thomas Kuhn : de la routine à la révolution par Eric Finot</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>319</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>320</v>
+        <v>37</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Contractualisme ; Social-démocratie ; Déontologisme</t>
+        </is>
       </c>
       <c r="L36" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>176</v>
+        <v>312</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>325</v>
+        <v>315</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>316</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>327</v>
+        <v>317</v>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Thomas Kuhn : de la routine à la révolution par Eric Finot</t>
+        </is>
       </c>
       <c r="H37" s="9" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="2" t="s">
-        <v>127</v>
+        <v>246</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>330</v>
+        <v>321</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>334</v>
+        <v>324</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Analytique ; Pragmatisme ; Réalisme scientifique ; Cognitivisme ; Essentialisme ; Computationnalisme</t>
-        </is>
+        <v>127</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>176</v>
+        <v>330</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="222" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
         <v>1926</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>344</v>
+        <v>333</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>334</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>347</v>
+        <v>336</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>337</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Pragmatisme ; Réalisme scientifique ; Cognitivisme ; Essentialisme ; Computationnalisme</t>
+        </is>
       </c>
       <c r="L39" s="2" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>176</v>
@@ -3931,42 +3955,40 @@
         <v>51</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="222" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
         <v>1926</v>
       </c>
-      <c r="B40" s="7" t="n">
-        <v>1995</v>
+      <c r="B40" s="7" t="s">
+        <v>341</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libertarianisme ; Anarcho-Capitalisme ; Volontarisme</t>
-        </is>
-      </c>
-      <c r="L40" s="14" t="s">
-        <v>358</v>
+        <v>25</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>176</v>
@@ -3977,40 +3999,40 @@
     </row>
     <row r="41" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>2016</v>
+        <v>1995</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="2" t="s">
-        <v>218</v>
+        <v>356</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Hassidisme</t>
+          <t xml:space="preserve">Libertarianisme ; Anarcho-Capitalisme ; Volontarisme</t>
         </is>
       </c>
       <c r="L41" s="14" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>176</v>
@@ -4019,849 +4041,834 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
-        <v>1930</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>322</v>
+        <v>1928</v>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>2016</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>369</v>
+        <v>360</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>361</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>373</v>
+        <v>218</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Hassidisme</t>
+        </is>
+      </c>
+      <c r="L42" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_Rorty" title=" Wikipedia"&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href="https://www.youtube.com/watch?v=lfx4Jag1ic4"  title="Le pragmatisme : définition, exemples par le savoir partagé"&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href="https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism" title=" a bas l'autorité par laviedesidees"&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas "vrais" ou "faux". &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales, on trouve  &lt;a href="https://www.youtube.com/watch?v=MgU0dXZ3umM" title="L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli"&gt;" Contingence, ironie et solidarité "&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans " Achieving Our Country" (1998),  il y appelle la gauche américaine à abandonner le "culturalisme" pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la "post-vérité". Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; </t>
-        </is>
+        <v>368</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>369</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>380</v>
+        <v>371</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>372</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="2" t="s">
-        <v>381</v>
+        <v>127</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
+    <row r="44" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
+        <v>1931</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_Rorty" title=" Wikipedia"&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href="https://www.youtube.com/watch?v=lfx4Jag1ic4"  title="Le pragmatisme : définition, exemples par le savoir partagé"&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href="https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism" title=" a bas l'autorité par laviedesidees"&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas "vrais" ou "faux". &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales, on trouve  &lt;a href="https://www.youtube.com/watch?v=MgU0dXZ3umM" title="L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli"&gt;" Contingence, ironie et solidarité "&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans " Achieving Our Country" (1998),  il y appelle la gauche américaine à abandonner le "culturalisme" pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la "post-vérité". Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="I44" s="9"/>
+      <c r="J44" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="n">
         <v>1932</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B45" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Searle"  title=" Wikipedia"&gt;John SEARLE&lt;/a&gt; était un philosophe américain  connu pour ses travaux influents dans plusieurs domaines, notamment la philosophie du langage, la philosophie de l'esprit et la philosophie sociale. Il  a développé et systématisé la théorie des &lt;a href="https://www.youtube.com/watch?v=pIbkpLfrD6A" title="
 La théorie des actes de langage (2) - John Searle par Heraut du Mont Parnasse"&gt;actes de langage&lt;/a&gt; car, pour lui, parler une langue, ce n'est pas seulement émettre des sons ou des suites de symboles, mais accomplir des actions. &lt;/p&gt; &lt;p&gt; Défenseur du "naturalisme biologique" en philosophie de l'esprit. Il s'oppose au dualisme cartésien tout en refusant le matérialisme réducteur qui nierait l'existence de &lt;a href="https://www.youtube.com/watch?v=EriAhi0mj7w" title=" Conscience et matière grise par TEDx Talks"&gt;la conscience&lt;/a&gt; ou la réduirirait à de simples phénomènes physiques. Pour lui, les états mentaux (douleur, croyances, désirs, conscience) sont des phénomènes  &lt;a href="https://www.youtube.com/watch?v=Bq2bfSzkTfU"  title="John Searle - Une personne peut-elle être une âme ? par Closer To Truth"&gt;biologiques réels&lt;/a&gt;, causés par des processus neuronaux du cerveau, mais ils ne sont pas réductibles à ces processus au sens où ils émergent à un niveau supérieur et possèdent des propriétés irréductibles.&lt;/p&gt; &lt;p&gt; L'une des ses contributions les plus célèbres est son argument de la &lt;a href="https://www.youtube.com/watch?v=P5DtwDr9YEc" title=" La Chambre chinoise par Ian et frank"&gt;Chambre Chinoise&lt;/a&gt;. Cet argument vise à réfuter la thèse de l'IA forte (position selon laquelle un ordinateur programmé de manière appropriée n'est pas seulement un outil pour l'étude de l'esprit, mais qu'il est véritablement un esprit, capable de comprendre et de posséder d'autres états cognitifs) opposé à l'IA faible (position selon laquelle les ordinateurs sont des outils utiles pour étudier l'esprit, mais qu'ils ne sont pas eux-mêmes des esprits). &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://labo.nonmarchand.org/pmwiki/uploads/Textes/JohnSearleLaConstructionDeLaRealiteSociale/JohnSearle_LaConstructionDeLaRealiteSociale.pdf"  title=" La construction e la réalité sociale par nonmarchand"&gt;"La Construction de la Réalité Sociale"&lt;/a&gt;, il étend sa théorie des actes de langage et de l'intentionnalité pour expliquer comment nous construisons des faits institutionnels et sociaux. Il distingue les "Faits bruts" qui existent indépendamment de toute institution humaine (par exemple, la montagne Everest) des "Faits institutionnels" qui n'existent qu'en vertu d'institutions humaines et de l'accord collectif (par exemple, l'argent, le mariage, la propriété). &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G45" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H45" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="I44" s="1"/>
-      <c r="J44" s="2" t="s">
+      <c r="I45" s="1"/>
+      <c r="J45" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="K45" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="L44" s="2" t="s">
+      <c r="L45" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n">
-        <v>1933</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="F45" s="7"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P45" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
+        <v>1933</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="F46" s="7"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
         <v>1934</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B47" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D47" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Enrique_Dussel"  title=" Wikipedia"&gt;Enrique DUSSEL&lt;/a&gt; était un philosophe argentin majeurs de la décolonialité et de la philosophie latino-américaine de la liberation.  Jeune intellectuel engagé dans les mouvements étudiants et opposé aux régimes autoritaires, il a été persécuté en Argentine avant de s’exiler au Mexique en 1975, où il a poursuivi sa carrière académique et développé sa pensée. Il élabore une &lt;a href="https://www.youtube.com/watch?v=QGPosp7lYlM" title="Enrique Dussel and the Philosophy of Liberation – Decolonizing Thought par Darina Metreveli"&gt;philosophie de la libération &lt;/a&gt; qui remet en question l’ontologie monologique de la modernité et introduit une approche éthique et alteritaire inspirée par Levinas, souvent décrite sous le nom d’analectique ou de dialectique positive. &lt;/p&gt; &lt;p&gt; Pionnier du décolonialisme latino-américain, il contribue à la construction des cadres Modernité/Colonialité et à l’idée d’une transmodernité, articulant critique de la modernité et invitation à repenser les rapports Nord-Sud et centre-périphérie. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures : &lt;a href="https://www.youtube.com/watch?v=nXNyqKCrKLY" title="Enrique Dussel, métaphysicien de la libération - Emmanuel Lévine par lundimatin"&gt;"Méthode pour une philosophie de la libération" &lt;/a&gt; paru en  1974 et "Filosofía ética latinoamericana" (période majeure)  posent les bases d’une philosophie enracinée dans les expériences des peuples opprimés et des contextes colonisés. &lt;/p&gt; &lt;p&gt; Il est reconnu dans les &lt;a href="https://lestempsquirestent.org/fr/numeros/numero-7/enrique-dussel-un-philosophe-indispensable-pour-decoloniser-la-theologie-politique" title="Enrique Dussel,
 un philosophe indispensable pour décoloniser la théologie politique par les temps qui restent"&gt;milieux décoloniaux &lt;/a&gt; et philosophie de la libération, mais demeure moins connu du grand public français, bien que des traductions et des analyses apparaissent et stimulent l’intérêt académique en France. Son travail nourrit le courant décolonial qui met en évidence l’interdépendance entre modernité et colonialité depuis 1492 et propose des axes pour une pensée transmoderne, dépassant les cadres classiques de la philosophie occidentale. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F47" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G47" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>406</v>
-      </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiers-mondisme ; Théologie de la libération ; Philosophie de la libération ; Pensée décoloniale</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O46" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B47" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>410</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>413</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiers-mondisme ; Théologie de la libération ; Philosophie de la libération ; Pensée décoloniale</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O47" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="I48" s="9"/>
+      <c r="J48" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="K48" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="L47" s="2" t="s">
+      <c r="L48" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B48" s="1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="G48" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="I48" s="1"/>
-      <c r="J48" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P48" s="1" t="s">
+    </row>
+    <row r="49" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P49" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="XFC48" s="0"/>
-      <c r="XFD48" s="0"/>
-    </row>
-    <row r="49" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="16" t="n">
+      <c r="XFC49" s="0"/>
+      <c r="XFD49" s="0"/>
+    </row>
+    <row r="50" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="16" t="n">
         <v>1935</v>
       </c>
-      <c r="B49" s="16" t="n">
+      <c r="B50" s="16" t="n">
         <v>2003</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C50" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D50" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="E49" s="13" t="s">
+      <c r="E50" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="F49" s="16" t="s">
+      <c r="F50" s="16" t="s">
         <v>428</v>
       </c>
-      <c r="G49" s="18" t="s">
+      <c r="G50" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H50" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="I49" s="18"/>
-      <c r="J49" s="2" t="s">
+      <c r="I50" s="18"/>
+      <c r="J50" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="K50" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="L49" s="14" t="s">
+      <c r="L50" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="M49" s="14" t="s">
+      <c r="M50" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N49" s="14" t="s">
+      <c r="N50" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="n">
+    <row r="51" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="n">
         <v>1937</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B51" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C51" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D51" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E51" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F51" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G51" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>438</v>
-      </c>
-      <c r="I50" s="9"/>
-      <c r="J50" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="n">
-        <v>1938</v>
-      </c>
-      <c r="B51" s="7" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>446</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libéralisme ; Minarchisme ; Déontologisme</t>
-        </is>
+        <v>127</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>439</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="N51" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="N51" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
         <v>1938</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>449</v>
+      <c r="B52" s="7" t="n">
+        <v>2002</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tom_Regan"  title=" Wikipedia"&gt;Tom REGAN&lt;/a&gt; était un philosophe américain   &lt;a href="https://www.youtube.com/watch?v=hgVMf3q4Vh4"  title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Pensées antispécistes par The Critical Vegan"&gt;antispéciste &lt;/a&gt; influent dans le domaine de l'éthique animale, considéré comme un pionnier de la théorie des droits des animaux sur une base déontologique. Né à Pittsburgh, il enseigne de 1967 à 2001 à l’université d’État de Caroline du Nord. Il développe une approche abolitionniste opposée à l'utilitarisme de Peter Singer, arguant que les mammifères normaux d'un an ou plus sont des "sujets-d'une-vie" dotés d'une valeur inhérente, méritant des droits moraux fondamentaux indépendamment de leur utilité. Inspiré par Kant mais étendu aux non-humains, il définit ces sujets comme des êtres conscients pour qui leur vie importe intrinsèquement, justifiant l'interdiction absolue de l'exploitation. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales sont : "The Case for Animal Rights" paru en 1983, traduit en français comme  &lt;a href="http://tomregan.free.fr/" title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Les Droits des animaux par Tom Regan"&gt;"Les Droits des animaux" &lt;/a&gt; en 2013 : son magnum opus, salué comme un classique moderne critiquant Descartes et plaidant pour le "principe de respect" envers tout sujet-d'une-vie. "All That Dwell Therein" paru en  1982 : recueil d'essais sur le végétarisme et l'éthique animale. &lt;/p&gt; &lt;p&gt; Ses idées ont profondément marqué le mouvement des droits des animaux, influençant débats sur végétarisme, anti-vivisection et critique de l'environnementalisme indirect, tout en étant cité par des penseurs comme Derrida ou dans des ouvrages comme ceux de Jean-Baptiste Jeangène Vilmer. Dans &lt;em&gt;Empty Cages&lt;/em&gt; (2004), destiné au grand public, il résume son combat : il ne s’agit pas d’agrandir les cages, mais de les vider. &lt;/p&gt; </t>
-        </is>
+        <v>442</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>443</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>455</v>
+        <v>445</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>446</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Minarchisme ; Déontologisme</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tom_Regan"  title=" Wikipedia"&gt;Tom REGAN&lt;/a&gt; était un philosophe américain   &lt;a href="https://www.youtube.com/watch?v=hgVMf3q4Vh4"  title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Pensées antispécistes par The Critical Vegan"&gt;antispéciste &lt;/a&gt; influent dans le domaine de l'éthique animale, considéré comme un pionnier de la théorie des droits des animaux sur une base déontologique. Né à Pittsburgh, il enseigne de 1967 à 2001 à l’université d’État de Caroline du Nord. Il développe une approche abolitionniste opposée à l'utilitarisme de Peter Singer, arguant que les mammifères normaux d'un an ou plus sont des "sujets-d'une-vie" dotés d'une valeur inhérente, méritant des droits moraux fondamentaux indépendamment de leur utilité. Inspiré par Kant mais étendu aux non-humains, il définit ces sujets comme des êtres conscients pour qui leur vie importe intrinsèquement, justifiant l'interdiction absolue de l'exploitation. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales sont : "The Case for Animal Rights" paru en 1983, traduit en français comme  &lt;a href="http://tomregan.free.fr/" title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Les Droits des animaux par Tom Regan"&gt;"Les Droits des animaux" &lt;/a&gt; en 2013 : son magnum opus, salué comme un classique moderne critiquant Descartes et plaidant pour le "principe de respect" envers tout sujet-d'une-vie. "All That Dwell Therein" paru en  1982 : recueil d'essais sur le végétarisme et l'éthique animale. &lt;/p&gt; &lt;p&gt; Ses idées ont profondément marqué le mouvement des droits des animaux, influençant débats sur végétarisme, anti-vivisection et critique de l'environnementalisme indirect, tout en étant cité par des penseurs comme Derrida ou dans des ouvrages comme ceux de Jean-Baptiste Jeangène Vilmer. Dans &lt;em&gt;Empty Cages&lt;/em&gt; (2004), destiné au grand public, il résume son combat : il ne s’agit pas d’agrandir les cages, mais de les vider. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="I53" s="9"/>
+      <c r="J53" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="K53" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L52" s="2" t="s">
+      <c r="L53" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="B53" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saul_Kripke"  title=" Wikipedia"&gt;Saul KRIPKE&lt;/a&gt; était un philosophe américain de la tradition analytique connu pour ses apports décisifs en logique modale, en métaphysique et en philosophie du langage. Très jeune, il révolutionne la logique en introduisant la sémantique des mondes possibles, aujourd’hui appelée &lt;a href="https://www.youtube.com/watch?v=_sIgAdvhruU"title="Qui est Saul Kripke ? par Monsieur Phi"&gt;"cadres de Kripke"&lt;/a&gt;, qui permet de formaliser la modalité (le nécessaire et le possible) de façon rigoureuse. &lt;/p&gt; &lt;p&gt; Son œuvre la plus influente est "Naming and Necessity", où il critique la conception descriptiviste des noms défendue par Frege et Russell. Selon lui, un  &lt;a href="https://www.youtube.com/watch?v=d7-8Avem7EE" title="Saul Kripke, La logique des noms propres. par Jtgrandtour"&gt; nom propre&lt;/a&gt; n’équivaut pas à une description mais fonctionne comme un « désignateur rigide » : il désigne le même individu dans tous les mondes possibles. Cette idée bouleverse la philosophie du langage et entraîne une redéfinition de la notion de référence.&lt;/p&gt; &lt;p&gt;  Il montre également qu’il existe des vérités nécessaires découvertes empiriquement : par exemple, l’identité « l’eau est H₂O » est nécessaire, mais nous ne l’avons apprise qu’a posteriori. Ce concept de nécessité a posteriori a marqué un tournant dans la métaphysique contemporaine. À l’inverse, il identifie la possibilité de certaines vérités contingentes connues a priori, ce qui remet en cause des distinctions classiques entre connaissance et modalité. &lt;/p&gt; &lt;p&gt; Il s’oppose au physicalisme en arguant que l’on peut concevoir un monde où tous les états cérébraux existent sans que la conscience subjective "le qualia" ne soit présente. Cette critique alimente encore aujourd’hui les débats sur la nature de la conscience. Son ouvrage "Wittgenstein on Rules and Private Language" propose une lecture radicale de Wittgenstein, selon laquelle toute règle est sujette à un scepticisme profond sur son application. Bien que controversée, cette interprétation a largement stimulé les discussions en philosophie du langage et en épistémologie. &lt;/p&gt; &lt;p&gt; Connu aussi pour son ouvrage " On two Paradoxes of Knowledge" et son  &lt;a href="https://www.youtube.com/watch?v=AzaUSC--2G0"  title="Le Paradoxe de l'Examen selon Saul Kripke par Silogic"&gt;"paradoxe de l'examen"&lt;/a&gt;. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P53" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="n">
-        <v>1941</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Lewis_(philosophe)"  title=" Wikipedia"&gt;David LEWIS&lt;/a&gt; était un philosophe américain connu pour sa théorie du  réalisme modal, selon laquelle il existe un nombre infini de mondes possibles concrets et causalement isolés les uns des autres. Son ouvrage majeur   &lt;a href="https://www.youtube.com/watch?v=-QlqLDLifuc" title="David Lewis - "De la pluralité des mondes" - De quoi parle ce livre ? par Philosophie 21"&gt;"On the Plurality of Worlds"&lt;/a&gt;  sortie en 1986, expose cette position révolutionnaire : pour lui, chaque monde possible existe aussi réellement que notre monde actuel, et sert à comprendre la modalité, c'est-à-dire ce qui pourrait être ou ce qui doit être. &lt;/p&gt; &lt;p&gt; Il a également proposé la théorie des contreparties en logique modale : au lieu de supposer que les personnes ou objets existent dans plusieurs mondes possibles, il affirme que chaque individu de notre monde a des « contreparties » dans les autres mondes possibles qui partagent certaines caractéristiques mais ne sont pas identiques à lui. Cette approche constitue une alternative à la logique modale traditionnelle, notamment celle de Saul Kripke. &lt;/p&gt; &lt;p&gt; Sa métaphysique est marquée par une conception atomiste (pointilliste) : la réalité n’est qu’une vaste mosaïque de faits locaux, chaque fait étant centré sur un « point » ayant des propriétés intrinsèques. Ce point de vue s’inspire de David Hume, d’où le nom « survenance humienne », refusant les liens nécessaires entre les faits et privilégiant une juxtaposition de qualités locales. &lt;/p&gt; &lt;p&gt; Il  a beaucoup écrit sur la philosophie du langage, la philosophie de l’esprit, l’épistémologie, la logique philosophique et la philosophie des mathématiques. Son premier grand ouvrage, "Convention" de 1969, analyse les conventions sociales à l’aide de la théorie des jeux, en montrant leur caractère arbitraire et leur diffusion par la connaissance commune et le précédent. Il s a marqué durablement la philosophie analytique.  &lt;a href="https://www.youtube.com/watch?v=g3jQwDP_Lyc" title="David Lewis - "David Lewis Speaks at La Trobe University par TimeSparrow"&gt;"Ses théories&lt;/a&gt; sont incontournables dans les débats sur les mondes possibles, la modalité, la causalité, la convention sociale, et l’atomisme métaphysique. Ses ouvrages, tels que Counterfactuals et Philosophical Papers, restent des références dans l’analyse logique et conceptuelle contemporaine. &lt;/p&gt; &lt;audio controls title=" On dit de David Lewis que c'est le plus grand métaphysicien qu’on ait vu depuis Leibniz par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18292-28.02.2019-ITEMA_21995453-0.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="I54" s="9"/>
+    </row>
+    <row r="54" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saul_Kripke"  title=" Wikipedia"&gt;Saul KRIPKE&lt;/a&gt; était un philosophe américain de la tradition analytique connu pour ses apports décisifs en logique modale, en métaphysique et en philosophie du langage. Très jeune, il révolutionne la logique en introduisant la sémantique des mondes possibles, aujourd’hui appelée &lt;a href="https://www.youtube.com/watch?v=_sIgAdvhruU"title="Qui est Saul Kripke ? par Monsieur Phi"&gt;"cadres de Kripke"&lt;/a&gt;, qui permet de formaliser la modalité (le nécessaire et le possible) de façon rigoureuse. &lt;/p&gt; &lt;p&gt; Son œuvre la plus influente est "Naming and Necessity", où il critique la conception descriptiviste des noms défendue par Frege et Russell. Selon lui, un  &lt;a href="https://www.youtube.com/watch?v=d7-8Avem7EE" title="Saul Kripke, La logique des noms propres. par Jtgrandtour"&gt; nom propre&lt;/a&gt; n’équivaut pas à une description mais fonctionne comme un « désignateur rigide » : il désigne le même individu dans tous les mondes possibles. Cette idée bouleverse la philosophie du langage et entraîne une redéfinition de la notion de référence.&lt;/p&gt; &lt;p&gt;  Il montre également qu’il existe des vérités nécessaires découvertes empiriquement : par exemple, l’identité « l’eau est H₂O » est nécessaire, mais nous ne l’avons apprise qu’a posteriori. Ce concept de nécessité a posteriori a marqué un tournant dans la métaphysique contemporaine. À l’inverse, il identifie la possibilité de certaines vérités contingentes connues a priori, ce qui remet en cause des distinctions classiques entre connaissance et modalité. &lt;/p&gt; &lt;p&gt; Il s’oppose au physicalisme en arguant que l’on peut concevoir un monde où tous les états cérébraux existent sans que la conscience subjective "le qualia" ne soit présente. Cette critique alimente encore aujourd’hui les débats sur la nature de la conscience. Son ouvrage "Wittgenstein on Rules and Private Language" propose une lecture radicale de Wittgenstein, selon laquelle toute règle est sujette à un scepticisme profond sur son application. Bien que controversée, cette interprétation a largement stimulé les discussions en philosophie du langage et en épistémologie. &lt;/p&gt; &lt;p&gt; Connu aussi pour son ouvrage " On two Paradoxes of Knowledge" et son  &lt;a href="https://www.youtube.com/watch?v=AzaUSC--2G0"  title="Le Paradoxe de l'Examen selon Saul Kripke par Silogic"&gt;"paradoxe de l'examen"&lt;/a&gt;. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>463</v>
+      </c>
       <c r="J54" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>475</v>
+        <v>464</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>465</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>476</v>
+        <v>466</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="332.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P54" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
+        <v>1941</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Lewis_(philosophe)"  title=" Wikipedia"&gt;David LEWIS&lt;/a&gt; était un philosophe américain connu pour sa théorie du  réalisme modal, selon laquelle il existe un nombre infini de mondes possibles concrets et causalement isolés les uns des autres. Son ouvrage majeur   &lt;a href="https://www.youtube.com/watch?v=-QlqLDLifuc" title="David Lewis - "De la pluralité des mondes" - De quoi parle ce livre ? par Philosophie 21"&gt;"On the Plurality of Worlds"&lt;/a&gt;  sortie en 1986, expose cette position révolutionnaire : pour lui, chaque monde possible existe aussi réellement que notre monde actuel, et sert à comprendre la modalité, c'est-à-dire ce qui pourrait être ou ce qui doit être. &lt;/p&gt; &lt;p&gt; Il a également proposé la théorie des contreparties en logique modale : au lieu de supposer que les personnes ou objets existent dans plusieurs mondes possibles, il affirme que chaque individu de notre monde a des « contreparties » dans les autres mondes possibles qui partagent certaines caractéristiques mais ne sont pas identiques à lui. Cette approche constitue une alternative à la logique modale traditionnelle, notamment celle de Saul Kripke. &lt;/p&gt; &lt;p&gt; Sa métaphysique est marquée par une conception atomiste (pointilliste) : la réalité n’est qu’une vaste mosaïque de faits locaux, chaque fait étant centré sur un « point » ayant des propriétés intrinsèques. Ce point de vue s’inspire de David Hume, d’où le nom « survenance humienne », refusant les liens nécessaires entre les faits et privilégiant une juxtaposition de qualités locales. &lt;/p&gt; &lt;p&gt; Il  a beaucoup écrit sur la philosophie du langage, la philosophie de l’esprit, l’épistémologie, la logique philosophique et la philosophie des mathématiques. Son premier grand ouvrage, "Convention" de 1969, analyse les conventions sociales à l’aide de la théorie des jeux, en montrant leur caractère arbitraire et leur diffusion par la connaissance commune et le précédent. Il s a marqué durablement la philosophie analytique.  &lt;a href="https://www.youtube.com/watch?v=g3jQwDP_Lyc" title="David Lewis - "David Lewis Speaks at La Trobe University par TimeSparrow"&gt;"Ses théories&lt;/a&gt; sont incontournables dans les débats sur les mondes possibles, la modalité, la causalité, la convention sociale, et l’atomisme métaphysique. Ses ouvrages, tels que Counterfactuals et Philosophical Papers, restent des références dans l’analyse logique et conceptuelle contemporaine. &lt;/p&gt; &lt;audio controls title=" On dit de David Lewis que c'est le plus grand métaphysicien qu’on ait vu depuis Leibniz par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18292-28.02.2019-ITEMA_21995453-0.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="I55" s="9"/>
+      <c r="J55" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="332.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
         <v>1942</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B56" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C56" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D56" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="E55" s="9" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Daniel_Dennett"  style="color:#6A142A"  title=" Wikipedia"&gt;Daniel DENNETT&lt;/a&gt; était un  philosophe américain, figure importante et  influente de la philosophie de l'esprit, de la biologie et des sciences cognitives. Ses travaux se caractérisent par une volonté d'intégrer les découvertes scientifiques (biologie évolutionniste, neurosciences, intelligence artificielle) à la réflexion philosophique, souvent pour démanteler des intuitions traditionnelles qu'il juge erronées. &lt;/p&gt; &lt;p&gt; La Théorie de l'Esprit comme &lt;a href="https://www.youtube.com/watch?v=LKJJpvdqkFA" style="color:#88A1E9" title="Cette histoire va vous retourner le cerveau. | "Où suis-je" de Daniel Dennett par Monsieur Phi"&gt;"Position Intentionnelle"&lt;/a&gt; est sa contribution majeure. Il propose que pour prédire et expliquer le comportement d'un système (qu'il s'agisse d'un humain, d'un animal, d'un ordinateur ou même d'un thermostat), nous pouvons adopter trois "stances" : &lt;/p&gt; &lt;p&gt;La stance physique : On décrit le système par sa physique et sa chimie. Très difficile pour des systèmes complexes. &lt;/p&gt; &lt;p&gt;La stance du design : On considère le système comme conçu pour une fonction spécifique (ex: "ce thermostat est fait pour réguler la température"). &lt;/p&gt; &lt;p&gt;La stance intentionnelle : On traite le système comme s'il avait des croyances, des désirs et une rationalité. C'est une stratégie de prédiction extrêmement efficace, même si les croyances et désirs ne sont pas "réels" au sens littéral. Pour lui, avoir des croyances, c'est être un système dont le comportement peut être prédit avec succès par la stance intentionnelle. &lt;/p&gt; &lt;p&gt; Il est un matérialiste farouche et  rejette l'idée d'un &lt;a href="https://www.nonfiction.fr/article-1116-daniel_dennett_est_il_le_diable_.htm" title="Daniel Dennett est-il le diable ? par nonfiction"&gt;"théâtre cartésien"&lt;/a&gt;, un endroit dans le cerveau où tout se réunirait pour être "vu" par un &lt;a href="https://www.youtube.com/watch?v=0It9fwSj6xM"  title="Le moi comme illusion (Daniel Dennett, la conscience expliquée 4) par Philosophie Analytique"&gt;"spectateur" (le soi)&lt;/a&gt;. Pour lui, c'est une illusion.
 Il défend plutôt un modèle de "espace de travail global" : la conscience émerge de processus cérébraux parallèles et compétitifs. Une information devient "consciente" lorsqu'elle gagne une compétition pour être diffusée à grande échelle dans le cerveau, rendant ainsi disponible pour d'autres systèmes (mémoire, langage, prise de décision). Il n'y a pas de "centre" unique. &lt;/p&gt; &lt;p&gt; Il  considère que l'idée de la sélection naturelle de Darwin est "l'idée la plus dangereuse de tous les temps" car elle a un pouvoir explicatif immense, bien au-delà de la biologie. Il l'étend à d'autres domaines grâce au concept de "mèmes" (introduit par Richard Dawkins).
 Les mèmes sont des unités de culture (idées, mélodies, modes, concepts) qui se répliquent, mutent et sont sélectionnées dans le "payage" des esprits humains. Le langage,&lt;a href="https://www.youtube.com/shorts/bG3YBavy29Y" title="Cette histoire va vous retourner le cerveau | Daniel Dennett par StopCroyance"&gt; la religion&lt;/a&gt;, la morale peuvent être analysés comme des produits d'un processus darwinien. &lt;/p&gt; &lt;p&gt; Il défend une forme de libre arbitre qu'il estime compatible avec le déterminisme scientifique (le fait que l'univers soit régi par des lois causales). Pour lui, le libre arbitre n'est pas une "causalité magique" qui échapperait aux lois de la nature.  C'est la capacité d'un agent complexe (comme un être humain) à se projeter dans le futur, à évaluer les conséquences de ses actes et à agir en fonction de ses raisons. Ce libre arbitre est le produit de l'évolution et de la culture. Il est réel et précieux, même s'il n'est pas "libre" au sens d'une exemption des lois de la physique. &lt;/p&gt; &lt;audio controls title=" "Daniel Dennett, le penseur qui a révolutionné la philosophie des sciences et de l’esprit" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24419-10.05.2024-ITEMA_23737219-2024C51851S0131-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F56" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G56" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="H55" s="9" t="s">
+      <c r="H56" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="I55" s="9"/>
-      <c r="J55" s="2" t="s">
+      <c r="I56" s="9"/>
+      <c r="J56" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="K56" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="L55" s="2" t="s">
+      <c r="L56" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="N55" s="1" t="s">
+      <c r="N56" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="n">
+    <row r="57" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
         <v>1943</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B57" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Marilyn MCCORD-ADAMS</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marilyn_McCord_Adams" title=" Wikipedia"&gt;Marilyn McCORD ADAMS&lt;/a&gt; était une philosophe américaine et une théologienne anglicane, reconnue pour son travail en philosophie de la religion et en philosophie médiévale. Elle a aussi été ordonnée prêtre épiscopalienne, ce qui donnait à sa réflexion philosophique une forte dimension spirituelle et pastorale. Elle a étudié à l’Université de l’Illinois puis à Cornell, où elle a obtenu son doctorat en philosophie en 1967. Sa carrière universitaire l’a menée à Michigan, UCLA, Yale, Oxford et elle a été la première femme, ainsi que la première Américaine, à occuper la chaire Regius de divinité à Oxford. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://senate.universityofcalifornia.edu/in-memoriam/files/marilyn-adams.html" title="Marilyn Adans par university of california"&gt;Son apport le plus célèbre &lt;/a&gt; concerne l’étude de Guillaume d’Ockham, à qui elle a consacré une grande étude en deux volumes qui a beaucoup compté dans les recherches sur la théologie médiévale. Elle a aussi travaillé sur l’eucharistie, le christologie et d’autres auteurs médiévaux comme Thomas d’Aquin, Gilles de Rome et Duns Scot. &lt;/p&gt; &lt;p&gt; En  &lt;a href="https://www.youtube.com/watch?v=nFRGDG__ELM" title="Marilyn Adans par Real Atheology"&gt;philosophie de la religion, &lt;/a&gt; elle est connue pour ses analyses du mal extrême, qu’elle appelait les horrendous evils. Son idée centrale est qu’une théologie sérieuse doit prendre au sérieux les souffrances qui semblent détruire toute possibilité de sens, et montrer comment elles peuvent malgré tout être intégrées dans une vision de la bonté divine. &lt;/p&gt; &lt;p&gt; Son œuvre a eu une influence durable parce qu’elle relie la rigueur philosophique, l’érudition médiévale et l’expérience religieuse vécue. Elle reste une figure majeure pour comprendre à la fois la philosophie analytique de la religion et la redécouverte moderne de la pensée médiévale. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F57" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G57" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="H56" s="9" t="s">
+      <c r="H57" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="I56" s="9"/>
-      <c r="J56" s="2" t="s">
+      <c r="I57" s="9"/>
+      <c r="J57" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="K57" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="L57" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N56" s="1" t="s">
+      <c r="N57" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
+    <row r="58" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="n">
         <v>1949</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B58" s="1" t="n">
         <v>2006</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="E57" s="14" t="inlineStr">
+      <c r="E58" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iris_Marion_Young" title=" Wikipedia"&gt;Iris Marion YOUNG&lt;/a&gt; était une philosophe politique américaine majeure, figure centrale du féminisme contemporain et de la théorie de la justice. Professeure à l'Université de Chicago, elle articule phénoménologie existentialiste, marxisme, théorie critique et postmodernisme pour repenser l'oppression, la domination et la démocratie au-delà des approches universalistes traditionnelles. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est sa théorie des &lt;a href="https://www.youtube.com/watch?v=KyOut8zqJRI" title="les cinq visages de l’oppression par Eliot Goodine"&gt; cinq visages de l'oppression,&lt;/a&gt;  qu'elle développe dans Justice and the Politics of Difference (1990) ou elle développe également une,&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2018_num_116_4_8681" title="le féminisme phénoménologique par persée"&gt; phénoménologie féministe &lt;/a&gt; du corps, notamment dans son essai célèbre « Throwing Like a Girl » (1980). Elle y décrit comment les femmes vivent leur corps comme limité, fragmenté et constamment surveillé, ce qui produit une « immanence » sociale qui entrave leur capacité d'action et d'autodétermination. Le corps n'est pas seulement biologique mais politique, façonné par les normes sociales et les rapports de pouvoir. &lt;/p&gt; &lt;p&gt; Elle défend une conception de la justice fondée sur l'inclusion différenciée plutôt que sur l'universalisme abstrait. Pour Young, une société juste doit reconnaître les différences de groupe (genre, race, classe, sexualité) et créer des espaces où chacun puisse participer à la vie démocratique sans être forcé d'abandonner son identité particulière. Elle propose aussi le concept de responsabilité sociale diffuse, selon lequel tous les membres d'une société sont responsables des injustice structurelles, pas seulement les auteurs directs. &lt;/p&gt; &lt;p&gt; Elle évite tout essentialisme en conceptualisant « les femmes » comme un groupe social sériel, au sens de Sartre : un groupe dont les membres ne partagent pas une essence commune mais sont reliés par des conditions sociales similaires et des rapports de pouvoir. Cette approche permet un féminisme pluriel, Alliant diverses luttes (racisme, homophobie, validisme, écologie) dans des coalitions contre les rapports de domination. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F58" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G58" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H58" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="J57" s="2" t="s">
+      <c r="J58" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K57" s="2" t="s">
+      <c r="K58" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="L57" s="2" t="s">
+      <c r="L58" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="M58" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N57" s="1" t="s">
+      <c r="N58" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
+    <row r="59" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="n">
         <v>1952</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B59" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bell_hooks"  title=" Wikipedia"&gt;Bell HOOKS&lt;/a&gt;, de son vrai nom Gloria Jean Watkins, est une autrice, professeure et militante féministe afro-américaine. Née dans le Kentucky, dans le Sud ségrégationniste, elle prit le nom de son arrière-grand-mère, qu'elle écrivait en minuscules pour que l'attention se porte sur ses idées plutôt que sur sa personne.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ne suis-je pas une femme ?&lt;/em&gt; (1981), elle montre que les femmes noires ont été oubliées à la fois par le mouvement féministe, dominé par des femmes blanches de classe moyenne, et par le mouvement pour les droits civiques, dominé par des hommes. Elle  &lt;a href="https://www.youtube.com/watch?v=pCwMdHBSQgM" title=" bell hooks, un féminisme anticapitaliste et intersectionnel par META "&gt;développe l'idée &lt;/a&gt; que le sexisme, le racisme et l'exploitation économique forment un même système de domination, qu'elle appelle le « patriarcat capitaliste suprémaciste blanc ».&lt;/p&gt; &lt;p&gt;Ses idées ont profondément influencé ce que l'on appelle aujourd'hui l'intersectionnalité, c'est-à-dire l'étude de la manière dont différentes formes de discrimination se croisent et se renforcent. Elle écrivait dans un style simple et direct, refusant le jargon universitaire, pour que ses livres soient lus au-delà des cercles savants. Elle a aussi consacré plusieurs ouvrages à l'amour, qu'elle considérait comme une force politique capable de transformer la société.&lt;/p&gt; &lt;p&gt;Elle a écrit une quarantaine de livres, sur le féminisme, l'amour, les médias, la culture populaire et l'éducation. Dans &lt;em&gt;Apprendre à transgresser&lt;/em&gt; (1994), inspirée par Paulo Freire, elle défend une pédagogie de la liberté où l'enseignement devient une pratique d'émancipation. Pour elle, le féminisme n'est pas une guerre contre les hommes mais un mouvement pour mettre fin à toute forme de domination, porté par une « éthique de l'amour ».&lt;/p&gt;    &lt;audio controls title="Lire bell hooks aujourd’hui par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23875-15.11.2023-ITEMA_23552434-2023C49162S0319-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
 </t>
         </is>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G59" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H59" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="I58" s="1"/>
-      <c r="J58" s="2" t="s">
+      <c r="I59" s="1"/>
+      <c r="J59" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K58" s="1" t="inlineStr">
+      <c r="K59" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Féminisme ; Wokisme</t>
         </is>
       </c>
-      <c r="L58" s="2" t="s">
+      <c r="L59" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="M59" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="N58" s="1" t="s">
+      <c r="N59" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O58" s="1" t="n">
+      <c r="O59" s="1" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0">
+    <row r="60" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0">
         <v>1535</v>
       </c>
-      <c r="B59" s="0" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1616</t>
         </is>
       </c>
-      <c r="C59" s="0" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">vers 1535 – vers 1616</t>
         </is>
       </c>
-      <c r="D59" s="0" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Felipe GUAMÁN POMA de Ayala</t>
         </is>
       </c>
-      <c r="E59" s="0" t="inlineStr">
+      <c r="E60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Felipe_Guam%C3%A1n_Poma_de_Ayala" title=" Wikipedia"&gt;Felipe GUAMÁN POMA de Ayala&lt;/a&gt; est un noble andin de langue quechua, auteur de l’un des documents les plus extraordinaires de l’époque coloniale. Né dans la province de Lucanas, au Pérou, peu après la conquête espagnole, il descend par sa mère d’une lignée liée aux souverains de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_inca" title=" Wikipedia"&gt;Empire inca&lt;/a&gt;. Élevé parmi les Espagnols, il apprend leur langue, se fait chrétien et travaille comme interprète auprès d’un prêtre chargé d’extirper les « idolâtries », puis auprès de juges de Huamanga, avant d’être dépouillé de ses terres et banni vers 1600.&lt;/p&gt; &lt;p&gt;Il parcourt alors les Andes pendant des années et rédige, vers 1615, une lettre de près de 1 200 pages adressée au roi d’Espagne Philippe III : la &lt;em&gt;Nouvelle Chronique et bon gouvernement&lt;/em&gt;. Ses quelque 400 dessins à la plume racontent l’histoire des Incas, le calendrier, les travaux des champs, puis les abus des colons : prêtres, corregidors et propriétaires qui exploitent, volent et maltraitent les Indiens. Il y décrit un « monde à l’envers » (&lt;em&gt;mundo al revés&lt;/em&gt;), où l’ordre juste a été renversé par la conquête.&lt;/p&gt; &lt;p&gt;Il ne réclame pas le départ des Espagnols, mais un « bon gouvernement » : que les Andins se gouvernent eux-mêmes sous l’autorité lointaine du roi, et que les colons qui abusent soient chassés des villages. Il défend aussi la valeur de la civilisation andine, qui connaissait selon lui la justice et un ordre moral bien avant l’arrivée des Européens. Le manuscrit, qui n’atteignit sans doute jamais le roi, dormit pendant trois siècles avant d’être découvert en 1908 à la Bibliothèque royale de Copenhague. Il est aujourd’hui une source majeure sur le monde andin et l’une des premières critiques de la colonisation écrites par un colonisé.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F59" s="0"/>
-      <c r="G59" s="0"/>
-      <c r="H59" s="0" t="inlineStr">
+      <c r="F60" s="0"/>
+      <c r="G60" s="0"/>
+      <c r="H60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/guamanpoma-mini.webp</t>
         </is>
       </c>
-      <c r="I59" s="0"/>
-      <c r="J59" s="0" t="inlineStr">
+      <c r="I60" s="0"/>
+      <c r="J60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
-      <c r="K59" s="0" t="inlineStr">
+      <c r="K60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Anticolonialisme</t>
         </is>
       </c>
-      <c r="L59" s="0" t="inlineStr">
+      <c r="L60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">chroniqueur andin, auteur d’une immense lettre illustrée au roi d’Espagne dénonçant la colonisation du Pérou.</t>
         </is>
       </c>
-      <c r="M59" s="0"/>
-      <c r="N59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="O59" s="1">
-        <v>2</v>
-      </c>
-      <c r="P59" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Péruvienne</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1">
-        <v>1853</v>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1895</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1853 – 1895</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">José MARTÍ</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Mart%C3%AD" title=" Wikipedia"&gt;José MARTÍ&lt;/a&gt; est le grand penseur de l’indépendance cubaine et l’une des voix majeures de l’Amérique latine. Né à La Havane de parents espagnols, il est arrêté à seize ans pour ses idées indépendantistes et condamné aux travaux forcés dans une carrière, avant d’être déporté en Espagne, où il étudie le droit et la philosophie à Saragosse. Il vit ensuite au Mexique, au Guatemala et au Venezuela, puis s’installe en 1881 à New York, où il passe près de quinze ans comme journaliste, diplomate et organisateur de l’exil cubain. Il y écrit, pour de grands journaux d’Amérique latine, des chroniques sur la vie nord-américaine.&lt;/p&gt; &lt;p&gt;Dans son essai &lt;em&gt;Notre Amérique&lt;/em&gt; (1891), il appelle les nations latino-américaines à se penser à partir de leur propre réalité, métisse, indienne, noire et paysanne, plutôt qu’en copiant l’Europe ou les États-Unis : « Le gouvernement doit naître du pays. » Il y affirme aussi : « Il n’y a pas de haine des races, parce qu’il n’y a pas de races. » Observateur lucide de la puissance nord-américaine, il met en garde contre les ambitions des États-Unis sur Cuba et sur tout le continent.&lt;/p&gt; &lt;p&gt;Poète novateur, l’un des fondateurs du modernisme hispanique, il écrit les &lt;em&gt;Vers simples&lt;/em&gt; (1891), dont certains forment les paroles de la célèbre chanson &lt;em&gt;Guantanamera&lt;/em&gt;, et une revue pour les enfants, &lt;em&gt;L’Âge d’or&lt;/em&gt;. En 1892, il fonde le Parti révolutionnaire cubain et prépare la &lt;a href="https://fr.wikipedia.org/wiki/Guerre_d%27ind%C3%A9pendance_cubaine" title=" Wikipedia"&gt;guerre d’indépendance&lt;/a&gt;. Débarqué à Cuba avec les insurgés, il est tué au combat à Dos Ríos le 19 mai 1895. Il est considéré à Cuba comme le héros national et « l’Apôtre » de l’indépendance.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/marti-mini.webp</t>
-        </is>
-      </c>
-      <c r="I60" s="1"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">politique ; esthetique</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">poète et penseur de l’indépendance cubaine, auteur de « Notre Amérique », héros national de Cuba.</t>
-        </is>
-      </c>
+      <c r="M60" s="0"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
@@ -4870,54 +4877,55 @@
       <c r="O60" s="1">
         <v>2</v>
       </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cubaine</t>
+      <c r="P60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>
     <row r="61" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1">
-        <v>1921</v>
+        <v>1853</v>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1997</t>
+          <t xml:space="preserve">1895</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921 – 1997</t>
+          <t xml:space="preserve">1853 – 1895</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paulo FREIRE</t>
+          <t xml:space="preserve">José MARTÍ</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paulo_Freire" title=" Wikipedia"&gt;Paulo FREIRE&lt;/a&gt; est un pédagogue et philosophe brésilien, l’un des penseurs de l’éducation les plus lus au monde. Né à Recife, dans le Nordeste, il connaît la faim pendant la crise des années 1930, ce qui le marque pour toute sa vie. Formé au droit et à la philosophie, lecteur de Marx comme des penseurs chrétiens, il se consacre à l’&lt;a href="https://fr.wikipedia.org/wiki/Alphab%C3%A9tisation" title=" Wikipedia"&gt;alphabétisation&lt;/a&gt; des adultes pauvres. En 1963, à Angicos, sa méthode permet à 300 travailleurs agricoles d’apprendre à lire et à écrire en une quarantaine d’heures.&lt;/p&gt; &lt;p&gt;Sa méthode part des « mots générateurs » tirés de la vie des apprenants, comme la brique, la terre ou le salaire, et fait de la lecture une prise de conscience : apprendre à lire le mot, c’est apprendre à lire le monde. Après le coup d’État militaire de 1964, il est emprisonné puis contraint à un exil de seize ans. Au Chili, il écrit &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_des_opprim%C3%A9s" title=" Wikipedia"&gt;&lt;em&gt;Pédagogie des opprimés&lt;/em&gt;&lt;/a&gt; (1968), où il critique l’éducation « bancaire », qui dépose des savoirs dans des élèves passifs comme on remplit un coffre, et lui oppose une éducation par le dialogue, où maître et élèves cherchent ensemble.&lt;/p&gt; &lt;p&gt;« Personne n’éduque autrui, personne ne s’éduque seul, les hommes s’éduquent ensemble par l’intermédiaire du monde. » L’éducation n’est jamais neutre : elle maintient l’oppression ou aide les opprimés à s’en libérer, sans devenir à leur tour oppresseurs. Rentré au Brésil en 1980, il dirige l’éducation de la ville de São Paulo. Son œuvre est à l’origine de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_critique" title=" Wikipedia"&gt;pédagogie critique&lt;/a&gt;, et il a été proclamé en 2012 patron de l’éducation brésilienne.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Mart%C3%AD" title=" Wikipedia"&gt;José MARTÍ&lt;/a&gt; est le grand penseur de l’indépendance cubaine et l’une des voix majeures de l’Amérique latine. Né à La Havane de parents espagnols, il est arrêté à seize ans pour ses idées indépendantistes et condamné aux travaux forcés dans une carrière, avant d’être déporté en Espagne, où il étudie le droit et la philosophie à Saragosse. Il vit ensuite au Mexique, au Guatemala et au Venezuela, puis s’installe en 1881 à New York, où il passe près de quinze ans comme journaliste, diplomate et organisateur de l’exil cubain. Il y écrit, pour de grands journaux d’Amérique latine, des chroniques sur la vie nord-américaine.&lt;/p&gt; &lt;p&gt;Dans son essai &lt;em&gt;Notre Amérique&lt;/em&gt; (1891), il appelle les nations latino-américaines à se penser à partir de leur propre réalité, métisse, indienne, noire et paysanne, plutôt qu’en copiant l’Europe ou les États-Unis : « Le gouvernement doit naître du pays. » Il y affirme aussi : « Il n’y a pas de haine des races, parce qu’il n’y a pas de races. » Observateur lucide de la puissance nord-américaine, il met en garde contre les ambitions des États-Unis sur Cuba et sur tout le continent.&lt;/p&gt; &lt;p&gt;Poète novateur, l’un des fondateurs du modernisme hispanique, il écrit les &lt;em&gt;Vers simples&lt;/em&gt; (1891), dont certains forment les paroles de la célèbre chanson &lt;em&gt;Guantanamera&lt;/em&gt;, et une revue pour les enfants, &lt;em&gt;L’Âge d’or&lt;/em&gt;. En 1892, il fonde le Parti révolutionnaire cubain et prépare la &lt;a href="https://fr.wikipedia.org/wiki/Guerre_d%27ind%C3%A9pendance_cubaine" title=" Wikipedia"&gt;guerre d’indépendance&lt;/a&gt;. Débarqué à Cuba avec les insurgés, il est tué au combat à Dos Ríos le 19 mai 1895. Il est considéré à Cuba comme le héros national et « l’Apôtre » de l’indépendance.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/freire-mini.webp</t>
-        </is>
-      </c>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/marti-mini.webp</t>
+        </is>
+      </c>
+      <c r="I61" s="1"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">politique ; esthetique</t>
         </is>
       </c>
       <c r="K61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Marxisme ; Théologie de la libération</t>
+          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pédagogue brésilien, auteur de Pédagogie des opprimés, penseur de l’éducation comme pratique de la liberté.</t>
+          <t xml:space="preserve">poète et penseur de l’indépendance cubaine, auteur de « Notre Amérique », héros national de Cuba.</t>
         </is>
       </c>
       <c r="N61" s="1" t="inlineStr">
@@ -4926,56 +4934,56 @@
         </is>
       </c>
       <c r="O61" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brésilienne</t>
+          <t xml:space="preserve">Cubaine</t>
         </is>
       </c>
     </row>
     <row r="62" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1">
-        <v>1882</v>
+        <v>1921</v>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">1997</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882 – 1959</t>
+          <t xml:space="preserve">1921 – 1997</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">José VASCONCELOS</t>
+          <t xml:space="preserve">Paulo FREIRE</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Vasconcelos" title=" Wikipedia"&gt;José VASCONCELOS&lt;/a&gt; est un philosophe, écrivain et homme politique mexicain, l’un des grands éducateurs de l’Amérique latine. Né à Oaxaca, avocat, il fonde en 1909 avec Antonio Caso et Alfonso Reyes l’Ateneo de la Juventud, cercle de jeunes intellectuels qui rejette le positivisme officiel du régime de Porfirio Díaz. Il prend part à la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_mexicaine" title=" Wikipedia"&gt;révolution mexicaine&lt;/a&gt; aux côtés de Francisco Madero. Recteur de l’université nationale en 1920, il lui donne sa devise, toujours en usage : « Par ma race parlera l’esprit. »&lt;/p&gt; &lt;p&gt;Ministre de l’Éducation de 1921 à 1924, il mène une véritable croisade pour instruire le peuple : écoles rurales, missions culturelles dans les villages, bibliothèques, éditions populaires des grands classiques. Il commande aussi aux peintres &lt;a href="https://fr.wikipedia.org/wiki/Diego_Rivera" title=" Wikipedia"&gt;Diego Rivera&lt;/a&gt; et José Clemente Orozco les fresques murales qui racontent l’histoire du Mexique sur les murs des bâtiments publics. Il est surnommé le « maître de la jeunesse d’Amérique ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Race cosmique&lt;/em&gt; (1925), il prophétise que l’Amérique latine, terre de tous les mélanges, verra naître une « cinquième race », synthèse de toutes les autres, porteuse d’une civilisation de l’amour et de la beauté. Sa philosophie, un « monisme esthétique », voit dans l’émotion esthétique la forme la plus haute de connaissance. Battu en 1929 dans une élection présidentielle qu’il juge truquée, il s’exile, puis évolue vers un conservatisme catholique, au point de manifester en 1940 des sympathies pour l’Allemagne nazie. Il meurt à Mexico en 1959.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paulo_Freire" title=" Wikipedia"&gt;Paulo FREIRE&lt;/a&gt; est un pédagogue et philosophe brésilien, l’un des penseurs de l’éducation les plus lus au monde. Né à Recife, dans le Nordeste, il connaît la faim pendant la crise des années 1930, ce qui le marque pour toute sa vie. Formé au droit et à la philosophie, lecteur de Marx comme des penseurs chrétiens, il se consacre à l’&lt;a href="https://fr.wikipedia.org/wiki/Alphab%C3%A9tisation" title=" Wikipedia"&gt;alphabétisation&lt;/a&gt; des adultes pauvres. En 1963, à Angicos, sa méthode permet à 300 travailleurs agricoles d’apprendre à lire et à écrire en une quarantaine d’heures.&lt;/p&gt; &lt;p&gt;Sa méthode part des « mots générateurs » tirés de la vie des apprenants, comme la brique, la terre ou le salaire, et fait de la lecture une prise de conscience : apprendre à lire le mot, c’est apprendre à lire le monde. Après le coup d’État militaire de 1964, il est emprisonné puis contraint à un exil de seize ans. Au Chili, il écrit &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_des_opprim%C3%A9s" title=" Wikipedia"&gt;&lt;em&gt;Pédagogie des opprimés&lt;/em&gt;&lt;/a&gt; (1968), où il critique l’éducation « bancaire », qui dépose des savoirs dans des élèves passifs comme on remplit un coffre, et lui oppose une éducation par le dialogue, où maître et élèves cherchent ensemble.&lt;/p&gt; &lt;p&gt;« Personne n’éduque autrui, personne ne s’éduque seul, les hommes s’éduquent ensemble par l’intermédiaire du monde. » L’éducation n’est jamais neutre : elle maintient l’oppression ou aide les opprimés à s’en libérer, sans devenir à leur tour oppresseurs. Rentré au Brésil en 1980, il dirige l’éducation de la ville de São Paulo. Son œuvre est à l’origine de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_critique" title=" Wikipedia"&gt;pédagogie critique&lt;/a&gt;, et il a été proclamé en 2012 patron de l’éducation brésilienne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/vasconcelos-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/freire-mini.webp</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; politique</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="K62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monisme ; Spiritualisme</t>
+          <t xml:space="preserve">Humanisme ; Marxisme ; Théologie de la libération</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et ministre mexicain de l’Éducation, auteur de La Race cosmique, penseur du métissage.</t>
+          <t xml:space="preserve">pédagogue brésilien, auteur de Pédagogie des opprimés, penseur de l’éducation comme pratique de la liberté.</t>
         </is>
       </c>
       <c r="N62" s="1" t="inlineStr">
@@ -4984,66 +4992,61 @@
         </is>
       </c>
       <c r="O62" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mexicaine</t>
+          <t xml:space="preserve">Brésilienne</t>
         </is>
       </c>
     </row>
     <row r="63" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1">
-        <v>1907</v>
+        <v>1882</v>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1972</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1907 – 1972</t>
+          <t xml:space="preserve">1882 – 1959</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abraham Joshua HESCHEL</t>
+          <t xml:space="preserve">José VASCONCELOS</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abraham_Joshua_Heschel" title=" Wikipedia"&gt;Abraham Joshua HESCHEL&lt;/a&gt; est un rabbin, théologien et philosophe juif, l’une des grandes voix religieuses du XXe siècle. Né à Varsovie dans une illustre famille du &lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;hassidisme&lt;/a&gt;, il étudie la philosophie à Berlin, où il soutient une thèse sur les prophètes d’Israël. Expulsé d’Allemagne vers la Pologne en 1938, il parvient à quitter Varsovie quelques semaines avant l’invasion allemande et gagne Londres, puis les États-Unis. Sa mère et ses sœurs sont assassinées pendant la Shoah. Il enseigne à partir de 1946 au Séminaire théologique juif de New York.&lt;/p&gt; &lt;p&gt;Pour Heschel, la religion commence par l’« étonnement radical » devant le monde, qui précède toute réflexion. Contre l’idée d’un Dieu impassible des philosophes, il parle du « pathos divin » : le Dieu des prophètes est concerné par le sort des hommes et souffre de l’injustice. La question n’est pas seulement de savoir si l’homme cherche Dieu, mais de comprendre que &lt;em&gt;Dieu est en quête de l’homme&lt;/em&gt;, titre de son livre de 1955. Dans &lt;em&gt;Les Bâtisseurs du temps&lt;/em&gt; (1951), il présente le &lt;a href="https://fr.wikipedia.org/wiki/Shabbat" title=" Wikipedia"&gt;shabbat&lt;/a&gt; comme « une cathédrale dans le temps » : le judaïsme sanctifie des moments plutôt que des lieux. Il consacre aussi un grand livre aux prophètes, témoins de la passion de Dieu pour la justice.&lt;/p&gt; &lt;p&gt;Sa foi le conduit à l’action. En 1965, il marche de Selma à Montgomery aux côtés de Martin Luther King et dira : « J’avais l’impression que mes jambes priaient. » Il s’oppose à la guerre du Vietnam et contribue au dialogue entre juifs et chrétiens lors du concile Vatican II. Il meurt à New York en 1972.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Vasconcelos" title=" Wikipedia"&gt;José VASCONCELOS&lt;/a&gt; est un philosophe, écrivain et homme politique mexicain, l’un des grands éducateurs de l’Amérique latine. Né à Oaxaca, avocat, il fonde en 1909 avec Antonio Caso et Alfonso Reyes l’Ateneo de la Juventud, cercle de jeunes intellectuels qui rejette le positivisme officiel du régime de Porfirio Díaz. Il prend part à la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_mexicaine" title=" Wikipedia"&gt;révolution mexicaine&lt;/a&gt; aux côtés de Francisco Madero. Recteur de l’université nationale en 1920, il lui donne sa devise, toujours en usage : « Par ma race parlera l’esprit. »&lt;/p&gt; &lt;p&gt;Ministre de l’Éducation de 1921 à 1924, il mène une véritable croisade pour instruire le peuple : écoles rurales, missions culturelles dans les villages, bibliothèques, éditions populaires des grands classiques. Il commande aussi aux peintres &lt;a href="https://fr.wikipedia.org/wiki/Diego_Rivera" title=" Wikipedia"&gt;Diego Rivera&lt;/a&gt; et José Clemente Orozco les fresques murales qui racontent l’histoire du Mexique sur les murs des bâtiments publics. Il est surnommé le « maître de la jeunesse d’Amérique ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Race cosmique&lt;/em&gt; (1925), il prophétise que l’Amérique latine, terre de tous les mélanges, verra naître une « cinquième race », synthèse de toutes les autres, porteuse d’une civilisation de l’amour et de la beauté. Sa philosophie, un « monisme esthétique », voit dans l’émotion esthétique la forme la plus haute de connaissance. Battu en 1929 dans une élection présidentielle qu’il juge truquée, il s’exile, puis évolue vers un conservatisme catholique, au point de manifester en 1940 des sympathies pour l’Allemagne nazie. Il meurt à Mexico en 1959.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/heschel-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vasconcelos-mini.webp</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; ethique</t>
+          <t xml:space="preserve">esthetique ; politique</t>
         </is>
       </c>
       <c r="K63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Existentialisme ; Mysticisme ; Hassidisme</t>
+          <t xml:space="preserve">Monisme ; Spiritualisme</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rabbin et philosophe juif, penseur du « pathos divin » et du shabbat, militant des droits civiques.</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">philosophe et ministre mexicain de l’Éducation, auteur de La Race cosmique, penseur du métissage.</t>
         </is>
       </c>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">occident</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="O63" s="1">
@@ -5051,57 +5054,62 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Américaine</t>
+          <t xml:space="preserve">Mexicaine</t>
         </is>
       </c>
     </row>
     <row r="64" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1">
-        <v>1914</v>
+        <v>1907</v>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998</t>
+          <t xml:space="preserve">1972</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914 – 1998</t>
+          <t xml:space="preserve">1907 – 1972</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octavio PAZ</t>
+          <t xml:space="preserve">Abraham Joshua HESCHEL</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Octavio_Paz" title=" Wikipedia"&gt;Octavio PAZ&lt;/a&gt; est un poète, essayiste et diplomate mexicain, prix Nobel de littérature en 1990. Né à Mexico dans une famille marquée par la révolution, son père ayant été le représentant d’Emiliano Zapata aux États-Unis, il soutient les républicains pendant la guerre d’Espagne, puis rompt avec le communisme après l’assassinat de Trotski. Diplomate à Paris après la guerre, il y fréquente les surréalistes et André Breton.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Labyrinthe_de_la_solitude" title=" Wikipedia"&gt;&lt;em&gt;Le Labyrinthe de la solitude&lt;/em&gt;&lt;/a&gt; (1950), il interroge l’identité mexicaine : derrière les masques de la politesse et la violence des fêtes se cache une solitude née de l’histoire, celle d’un peuple issu de la conquête, qui a renié à la fois son passé indien et son passé espagnol. Il y évoque la figure de la &lt;a href="https://fr.wikipedia.org/wiki/La_Malinche" title=" Wikipedia"&gt;Malinche&lt;/a&gt;, compagne indienne de Cortés, symbole ambigu de l’origine métisse du pays. Mais cette solitude est aussi celle de l’homme moderne, et la poésie, l’amour et la fête sont des moyens de la dépasser. Dans &lt;em&gt;L’Arc et la Lyre&lt;/em&gt; (1956), il fait de la poésie une expérience de communion qui révèle l’homme à lui-même.&lt;/p&gt; &lt;p&gt;Ambassadeur du Mexique en Inde de 1962 à 1968, il découvre les philosophies et l’art de l’Orient, qui nourrissent sa poésie. Il démissionne après le &lt;a href="https://fr.wikipedia.org/wiki/Massacre_de_Tlatelolco" title=" Wikipedia"&gt;massacre de Tlatelolco&lt;/a&gt;, où des centaines d’étudiants sont tués par l’armée en 1968. Critique des totalitarismes de droite comme de gauche, il fonde la revue &lt;em&gt;Vuelta&lt;/em&gt; et consacre un grand livre à la poétesse et penseuse Juana Inés de la Cruz. Il meurt à Mexico en 1998, à quatre-vingt-quatre ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abraham_Joshua_Heschel" title=" Wikipedia"&gt;Abraham Joshua HESCHEL&lt;/a&gt; est un rabbin, théologien et philosophe juif, l’une des grandes voix religieuses du XXe siècle. Né à Varsovie dans une illustre famille du &lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;hassidisme&lt;/a&gt;, il étudie la philosophie à Berlin, où il soutient une thèse sur les prophètes d’Israël. Expulsé d’Allemagne vers la Pologne en 1938, il parvient à quitter Varsovie quelques semaines avant l’invasion allemande et gagne Londres, puis les États-Unis. Sa mère et ses sœurs sont assassinées pendant la Shoah. Il enseigne à partir de 1946 au Séminaire théologique juif de New York.&lt;/p&gt; &lt;p&gt;Pour Heschel, la religion commence par l’« étonnement radical » devant le monde, qui précède toute réflexion. Contre l’idée d’un Dieu impassible des philosophes, il parle du « pathos divin » : le Dieu des prophètes est concerné par le sort des hommes et souffre de l’injustice. La question n’est pas seulement de savoir si l’homme cherche Dieu, mais de comprendre que &lt;em&gt;Dieu est en quête de l’homme&lt;/em&gt;, titre de son livre de 1955. Dans &lt;em&gt;Les Bâtisseurs du temps&lt;/em&gt; (1951), il présente le &lt;a href="https://fr.wikipedia.org/wiki/Shabbat" title=" Wikipedia"&gt;shabbat&lt;/a&gt; comme « une cathédrale dans le temps » : le judaïsme sanctifie des moments plutôt que des lieux. Il consacre aussi un grand livre aux prophètes, témoins de la passion de Dieu pour la justice.&lt;/p&gt; &lt;p&gt;Sa foi le conduit à l’action. En 1965, il marche de Selma à Montgomery aux côtés de Martin Luther King et dira : « J’avais l’impression que mes jambes priaient. » Il s’oppose à la guerre du Vietnam et contribue au dialogue entre juifs et chrétiens lors du concile Vatican II. Il meurt à New York en 1972.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/paz-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/heschel-mini.webp</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; politique</t>
+          <t xml:space="preserve">spiritualite ; ethique</t>
         </is>
       </c>
       <c r="K64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme</t>
+          <t xml:space="preserve">Existentialisme ; Mysticisme ; Hassidisme</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">poète et essayiste mexicain, prix Nobel 1990, auteur du Labyrinthe de la solitude.</t>
+          <t xml:space="preserve">rabbin et philosophe juif, penseur du « pathos divin » et du shabbat, militant des droits civiques.</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
       <c r="O64" s="1">
@@ -5109,52 +5117,52 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mexicaine</t>
+          <t xml:space="preserve">Américaine</t>
         </is>
       </c>
     </row>
     <row r="65" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1">
-        <v>1871</v>
+        <v>1914</v>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917</t>
+          <t xml:space="preserve">1998</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871 – 1917</t>
+          <t xml:space="preserve">1914 – 1998</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">José Enrique RODÓ</t>
+          <t xml:space="preserve">Octavio PAZ</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Enrique_Rod%C3%B3" title=" Wikipedia"&gt;José Enrique RODÓ&lt;/a&gt; est un écrivain et essayiste uruguayen, l’un des grands maîtres à penser de l’Amérique latine au début du XXe siècle. Né à Montevideo, il doit interrompre ses études après la ruine de sa famille, se forme largement seul et devient professeur de littérature à l’université de Montevideo, puis député. Correspondant de &lt;a href="https://fr.wikipedia.org/wiki/Rub%C3%A9n_Dar%C3%ADo" title=" Wikipedia"&gt;Rubén Darío&lt;/a&gt;, il est le principal théoricien du modernisme, le grand mouvement de renouvellement de la littérature hispano-américaine.&lt;/p&gt; &lt;p&gt;Son essai &lt;em&gt;Ariel&lt;/em&gt; (1900), écrit deux ans après la victoire des États-Unis sur l’Espagne à Cuba, prend la forme d’un dernier cours donné par un vieux maître, Prospero, à ses élèves. Empruntant les personnages de &lt;em&gt;La Tempête&lt;/em&gt; de Shakespeare, il oppose Ariel, l’esprit, la beauté, le désintéressement, à Caliban, la matière, l’utilité, les appétits. Il met en garde la jeunesse latino-américaine contre l’utilitarisme et la « nordomanie », la fascination pour le modèle des États-Unis, puissant mais tourné vers le seul profit.&lt;/p&gt; &lt;p&gt;Rodó invite les jeunes à cultiver toutes les facultés de l’esprit, à préserver un temps libre pour la pensée et la beauté, et à construire une démocratie qui élève chacun au lieu de niveler par le bas. Le livre connut un immense succès et inspira tout un courant, l’« arielisme ». Plus tard, des penseurs comme Roberto Fernández Retamar ont renversé le symbole en faisant de Caliban la figure du colonisé. Dans &lt;em&gt;Motifs de Protée&lt;/em&gt; (1909), il médite sur la transformation continuelle de soi. Rodó meurt à Palerme en 1917, au cours d’un voyage en Europe.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Octavio_Paz" title=" Wikipedia"&gt;Octavio PAZ&lt;/a&gt; est un poète, essayiste et diplomate mexicain, prix Nobel de littérature en 1990. Né à Mexico dans une famille marquée par la révolution, son père ayant été le représentant d’Emiliano Zapata aux États-Unis, il soutient les républicains pendant la guerre d’Espagne, puis rompt avec le communisme après l’assassinat de Trotski. Diplomate à Paris après la guerre, il y fréquente les surréalistes et André Breton.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Labyrinthe_de_la_solitude" title=" Wikipedia"&gt;&lt;em&gt;Le Labyrinthe de la solitude&lt;/em&gt;&lt;/a&gt; (1950), il interroge l’identité mexicaine : derrière les masques de la politesse et la violence des fêtes se cache une solitude née de l’histoire, celle d’un peuple issu de la conquête, qui a renié à la fois son passé indien et son passé espagnol. Il y évoque la figure de la &lt;a href="https://fr.wikipedia.org/wiki/La_Malinche" title=" Wikipedia"&gt;Malinche&lt;/a&gt;, compagne indienne de Cortés, symbole ambigu de l’origine métisse du pays. Mais cette solitude est aussi celle de l’homme moderne, et la poésie, l’amour et la fête sont des moyens de la dépasser. Dans &lt;em&gt;L’Arc et la Lyre&lt;/em&gt; (1956), il fait de la poésie une expérience de communion qui révèle l’homme à lui-même.&lt;/p&gt; &lt;p&gt;Ambassadeur du Mexique en Inde de 1962 à 1968, il découvre les philosophies et l’art de l’Orient, qui nourrissent sa poésie. Il démissionne après le &lt;a href="https://fr.wikipedia.org/wiki/Massacre_de_Tlatelolco" title=" Wikipedia"&gt;massacre de Tlatelolco&lt;/a&gt;, où des centaines d’étudiants sont tués par l’armée en 1968. Critique des totalitarismes de droite comme de gauche, il fonde la revue &lt;em&gt;Vuelta&lt;/em&gt; et consacre un grand livre à la poétesse et penseuse Juana Inés de la Cruz. Il meurt à Mexico en 1998, à quatre-vingt-quatre ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/rodo-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/paz-mini.webp</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; ethique</t>
+          <t xml:space="preserve">esthetique ; politique</t>
         </is>
       </c>
       <c r="K65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Spiritualisme</t>
+          <t xml:space="preserve">Humanisme</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">essayiste uruguayen, auteur d’Ariel, maître à penser de la jeunesse latino-américaine.</t>
+          <t xml:space="preserve">poète et essayiste mexicain, prix Nobel 1990, auteur du Labyrinthe de la solitude.</t>
         </is>
       </c>
       <c r="N65" s="1" t="inlineStr">
@@ -5167,52 +5175,52 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uruguayenne</t>
+          <t xml:space="preserve">Mexicaine</t>
         </is>
       </c>
     </row>
     <row r="66" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1">
-        <v>1922</v>
+        <v>1871</v>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1979</t>
+          <t xml:space="preserve">1917</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922 – 1979</t>
+          <t xml:space="preserve">1871 – 1917</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodolfo KUSCH</t>
+          <t xml:space="preserve">José Enrique RODÓ</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Rodolfo_Kusch" title=" Wikipedia (es)"&gt;Rodolfo KUSCH&lt;/a&gt; est un philosophe et anthropologue argentin qui a cherché à fonder une philosophie à partir de la pensée indigène et populaire de l’Amérique. Né à Buenos Aires de parents allemands, il étudie la philosophie à l’université de Buenos Aires, enseigne l’esthétique et écrit aussi pour le théâtre, notamment sur le tango. Persécuté pour ses sympathies péronistes après 1955, il part pour la Bolivie et le Pérou, puis s’installe dans le nord-ouest de l’Argentine, à Maimará, dans la province de Jujuy.&lt;/p&gt; &lt;p&gt;Au contact des communautés &lt;a href="https://fr.wikipedia.org/wiki/Quechuas" title=" Wikipedia"&gt;quechuas&lt;/a&gt; et &lt;a href="https://fr.wikipedia.org/wiki/Aymaras" title=" Wikipedia"&gt;aymaras&lt;/a&gt; des Andes, il mène de longues enquêtes de terrain, dont il tire &lt;em&gt;L’Amérique profonde&lt;/em&gt; (1962) et &lt;em&gt;La Pensée indigène et populaire en Amérique&lt;/em&gt; (1970). Il y oppose deux attitudes. Celle de l’Occident, l’« être », qui veut dominer le monde, le transformer et accumuler. Et celle de l’Amérique indienne, l’« être là » ou le simple « se tenir » (en espagnol &lt;em&gt;estar&lt;/em&gt;), qui accepte l’incertitude du monde, ses forces et ses menaces, et cherche à vivre en équilibre avec lui.&lt;/p&gt; &lt;p&gt;Pour Kusch, les classes moyennes des villes, qui se veulent européennes, vivent dans la peur de cette « Amérique profonde » qu’elles refoulent. Penser en Amérique, c’est accepter cette part indienne et populaire au lieu de la mépriser. Son œuvre, longtemps marginale, a nourri la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt; et les pensées décoloniales latino-américaines, et elle est aujourd’hui redécouverte. Il parle même de « phagocytose » : la culture populaire finirait par absorber ce que la modernité importée croit lui imposer. Il meurt en 1979 à Maimará, à cinquante-sept ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Enrique_Rod%C3%B3" title=" Wikipedia"&gt;José Enrique RODÓ&lt;/a&gt; est un écrivain et essayiste uruguayen, l’un des grands maîtres à penser de l’Amérique latine au début du XXe siècle. Né à Montevideo, il doit interrompre ses études après la ruine de sa famille, se forme largement seul et devient professeur de littérature à l’université de Montevideo, puis député. Correspondant de &lt;a href="https://fr.wikipedia.org/wiki/Rub%C3%A9n_Dar%C3%ADo" title=" Wikipedia"&gt;Rubén Darío&lt;/a&gt;, il est le principal théoricien du modernisme, le grand mouvement de renouvellement de la littérature hispano-américaine.&lt;/p&gt; &lt;p&gt;Son essai &lt;em&gt;Ariel&lt;/em&gt; (1900), écrit deux ans après la victoire des États-Unis sur l’Espagne à Cuba, prend la forme d’un dernier cours donné par un vieux maître, Prospero, à ses élèves. Empruntant les personnages de &lt;em&gt;La Tempête&lt;/em&gt; de Shakespeare, il oppose Ariel, l’esprit, la beauté, le désintéressement, à Caliban, la matière, l’utilité, les appétits. Il met en garde la jeunesse latino-américaine contre l’utilitarisme et la « nordomanie », la fascination pour le modèle des États-Unis, puissant mais tourné vers le seul profit.&lt;/p&gt; &lt;p&gt;Rodó invite les jeunes à cultiver toutes les facultés de l’esprit, à préserver un temps libre pour la pensée et la beauté, et à construire une démocratie qui élève chacun au lieu de niveler par le bas. Le livre connut un immense succès et inspira tout un courant, l’« arielisme ». Plus tard, des penseurs comme Roberto Fernández Retamar ont renversé le symbole en faisant de Caliban la figure du colonisé. Dans &lt;em&gt;Motifs de Protée&lt;/em&gt; (1909), il médite sur la transformation continuelle de soi. Rodó meurt à Palerme en 1917, au cours d’un voyage en Europe.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/kusch-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rodo-mini.webp</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
+          <t xml:space="preserve">esthetique ; ethique</t>
         </is>
       </c>
       <c r="K66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen Vivir (cosmovision andine) ; Philosophie de la libération</t>
+          <t xml:space="preserve">Humanisme ; Spiritualisme</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et anthropologue argentin, penseur de l’« Amérique profonde » et de la pensée indigène et populaire.</t>
+          <t xml:space="preserve">essayiste uruguayen, auteur d’Ariel, maître à penser de la jeunesse latino-américaine.</t>
         </is>
       </c>
       <c r="N66" s="1" t="inlineStr">
@@ -5225,52 +5233,52 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Argentine</t>
+          <t xml:space="preserve">Uruguayenne</t>
         </is>
       </c>
     </row>
     <row r="67" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974</t>
+          <t xml:space="preserve">1979</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925 – 1974</t>
+          <t xml:space="preserve">1922 – 1979</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Augusto SALAZAR BONDY</t>
+          <t xml:space="preserve">Rodolfo KUSCH</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Augusto_Salazar_Bondy" title=" Wikipedia (es)"&gt;Augusto SALAZAR BONDY&lt;/a&gt; est un philosophe et éducateur péruvien, l’une des figures fondatrices de la philosophie latino-américaine de la libération. Né à Lima, frère cadet de l’écrivain Sebastián Salazar Bondy, il étudie à l’université San Marcos, puis au Mexique auprès de José Gaos et de Leopoldo Zea, et à Paris, où il suit les cours de Jean Wahl, Jean Hyppolite et Gaston Bachelard. Professeur d’éthique à San Marcos, il écrit une grande histoire des idées au Pérou contemporain.&lt;/p&gt; &lt;p&gt;En 1968, il publie &lt;em&gt;Existe-t-il une philosophie de notre Amérique ?&lt;/em&gt;, qui provoque un vif débat avec Leopoldo Zea. Sa réponse est dure : jusqu’ici, il n’existe pas de philosophie latino-américaine authentique, mais seulement des imitations des courants européens, adoptés tour à tour sans être vraiment pensés. Ce n’est pas un manque de talent : c’est la conséquence de la domination et du sous-développement, qui produisent une culture dépendante et « aliénée », incapable de se penser elle-même.&lt;/p&gt; &lt;p&gt;Une philosophie authentique ne pourra naître qu’en prenant pour objet cette situation de domination, et en contribuant à la transformer. La philosophie devient ainsi une tâche de libération, comme le développera la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt;. Engagé dans la réforme de l’éducation sous le gouvernement péruvien de la fin des années 1960, il défend une école qui forme des personnes libres et critiques. Il meurt prématurément à Lima en 1974, à quarante-huit ans. Ses idées ont notamment inspiré Enrique Dussel.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Rodolfo_Kusch" title=" Wikipedia (es)"&gt;Rodolfo KUSCH&lt;/a&gt; est un philosophe et anthropologue argentin qui a cherché à fonder une philosophie à partir de la pensée indigène et populaire de l’Amérique. Né à Buenos Aires de parents allemands, il étudie la philosophie à l’université de Buenos Aires, enseigne l’esthétique et écrit aussi pour le théâtre, notamment sur le tango. Persécuté pour ses sympathies péronistes après 1955, il part pour la Bolivie et le Pérou, puis s’installe dans le nord-ouest de l’Argentine, à Maimará, dans la province de Jujuy.&lt;/p&gt; &lt;p&gt;Au contact des communautés &lt;a href="https://fr.wikipedia.org/wiki/Quechuas" title=" Wikipedia"&gt;quechuas&lt;/a&gt; et &lt;a href="https://fr.wikipedia.org/wiki/Aymaras" title=" Wikipedia"&gt;aymaras&lt;/a&gt; des Andes, il mène de longues enquêtes de terrain, dont il tire &lt;em&gt;L’Amérique profonde&lt;/em&gt; (1962) et &lt;em&gt;La Pensée indigène et populaire en Amérique&lt;/em&gt; (1970). Il y oppose deux attitudes. Celle de l’Occident, l’« être », qui veut dominer le monde, le transformer et accumuler. Et celle de l’Amérique indienne, l’« être là » ou le simple « se tenir » (en espagnol &lt;em&gt;estar&lt;/em&gt;), qui accepte l’incertitude du monde, ses forces et ses menaces, et cherche à vivre en équilibre avec lui.&lt;/p&gt; &lt;p&gt;Pour Kusch, les classes moyennes des villes, qui se veulent européennes, vivent dans la peur de cette « Amérique profonde » qu’elles refoulent. Penser en Amérique, c’est accepter cette part indienne et populaire au lieu de la mépriser. Son œuvre, longtemps marginale, a nourri la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt; et les pensées décoloniales latino-américaines, et elle est aujourd’hui redécouverte. Il parle même de « phagocytose » : la culture populaire finirait par absorber ce que la modernité importée croit lui imposer. Il meurt en 1979 à Maimará, à cinquante-sept ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/salazarbondy-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kusch-mini.webp</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
+          <t xml:space="preserve">Buen Vivir (cosmovision andine) ; Philosophie de la libération</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe péruvien, auteur d’Existe-t-il une philosophie de notre Amérique ?, penseur de la domination.</t>
+          <t xml:space="preserve">philosophe et anthropologue argentin, penseur de l’« Amérique profonde » et de la pensée indigène et populaire.</t>
         </is>
       </c>
       <c r="N67" s="1" t="inlineStr">
@@ -5283,52 +5291,52 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Péruvienne</t>
+          <t xml:space="preserve">Argentine</t>
         </is>
       </c>
     </row>
     <row r="68" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1">
-        <v>1839</v>
+        <v>1925</v>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">1974</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839 – 1903</t>
+          <t xml:space="preserve">1925 – 1974</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eugenio María de HOSTOS</t>
+          <t xml:space="preserve">Augusto SALAZAR BONDY</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Eugenio_Mar%C3%ADa_de_Hostos" title=" Wikipedia (en)"&gt;Eugenio María de HOSTOS&lt;/a&gt; est un philosophe, éducateur, sociologue et écrivain de &lt;a href="https://fr.wikipedia.org/wiki/Porto_Rico" title=" Wikipedia"&gt;Porto Rico&lt;/a&gt;, surnommé « le Grand Citoyen des Amériques ». Né à Mayagüez dans une famille aisée, il fait ses études en Espagne, où il étudie le droit et la philosophie à Madrid et publie en 1863 un roman, &lt;em&gt;Le Pèlerinage de Bayoán&lt;/em&gt;, qui évoque déjà le destin des Antilles. Déçu que la République espagnole refuse l’autonomie de Porto Rico, il quitte l’Espagne en 1869 pour se consacrer à l’indépendance des colonies antillaises.&lt;/p&gt; &lt;p&gt;Il rêve d’une Confédération des Antilles, réunissant Porto Rico, Cuba et la République dominicaine, et parcourt pour la défendre les États-Unis, le Pérou, le Chili, l’Argentine, le Brésil et le Venezuela. Partout, il fonde ou réforme des écoles. En République dominicaine, il crée en 1880 la première école normale, qui forme des instituteurs à une pédagogie scientifique et laïque. Au Chili, il plaide pour que les femmes aient accès à l’enseignement supérieur et aux professions savantes.&lt;/p&gt; &lt;p&gt;Sa &lt;em&gt;Morale sociale&lt;/em&gt; (1888), inspirée du &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt;, fonde les devoirs de l’individu non sur la religion, mais sur la raison et sur les liens qui l’unissent à la famille, à la société et à l’humanité ; l’éducation doit former des consciences libres et responsables. Après la guerre de 1898, qui fait passer Porto Rico sous domination américaine, il milite pour que l’île puisse décider elle-même de son avenir. Il laisse aussi un traité de sociologie, l’un des premiers d’Amérique latine. Il meurt en exil à Saint-Domingue en 1903.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Augusto_Salazar_Bondy" title=" Wikipedia (es)"&gt;Augusto SALAZAR BONDY&lt;/a&gt; est un philosophe et éducateur péruvien, l’une des figures fondatrices de la philosophie latino-américaine de la libération. Né à Lima, frère cadet de l’écrivain Sebastián Salazar Bondy, il étudie à l’université San Marcos, puis au Mexique auprès de José Gaos et de Leopoldo Zea, et à Paris, où il suit les cours de Jean Wahl, Jean Hyppolite et Gaston Bachelard. Professeur d’éthique à San Marcos, il écrit une grande histoire des idées au Pérou contemporain.&lt;/p&gt; &lt;p&gt;En 1968, il publie &lt;em&gt;Existe-t-il une philosophie de notre Amérique ?&lt;/em&gt;, qui provoque un vif débat avec Leopoldo Zea. Sa réponse est dure : jusqu’ici, il n’existe pas de philosophie latino-américaine authentique, mais seulement des imitations des courants européens, adoptés tour à tour sans être vraiment pensés. Ce n’est pas un manque de talent : c’est la conséquence de la domination et du sous-développement, qui produisent une culture dépendante et « aliénée », incapable de se penser elle-même.&lt;/p&gt; &lt;p&gt;Une philosophie authentique ne pourra naître qu’en prenant pour objet cette situation de domination, et en contribuant à la transformer. La philosophie devient ainsi une tâche de libération, comme le développera la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt;. Engagé dans la réforme de l’éducation sous le gouvernement péruvien de la fin des années 1960, il défend une école qui forme des personnes libres et critiques. Il meurt prématurément à Lima en 1974, à quarante-huit ans. Ses idées ont notamment inspiré Enrique Dussel.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/hostos-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/salazarbondy-mini.webp</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="K68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positivisme</t>
+          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">éducateur et penseur portoricain, apôtre d’une confédération des Antilles et d’une morale sociale laïque.</t>
+          <t xml:space="preserve">philosophe péruvien, auteur d’Existe-t-il une philosophie de notre Amérique ?, penseur de la domination.</t>
         </is>
       </c>
       <c r="N68" s="1" t="inlineStr">
@@ -5341,52 +5349,52 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portoricaine</t>
+          <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>
     <row r="69" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1">
-        <v>1925</v>
+        <v>1839</v>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925 – 2008</t>
+          <t xml:space="preserve">1839 – 1903</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orlando FALS BORDA</t>
+          <t xml:space="preserve">Eugenio María de HOSTOS</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Orlando_Fals_Borda" title=" Wikipedia (en)"&gt;Orlando FALS BORDA&lt;/a&gt; est un sociologue colombien, l’un des grands penseurs latino-américains des sciences sociales et le fondateur de la « recherche-action participative ». Né à Barranquilla, sur la côte caraïbe, formé aux États-Unis, il fonde en 1959 à l’Université nationale de Colombie, avec le prêtre Camilo Torres, l’une des premières facultés de sociologie d’Amérique latine. Son livre &lt;em&gt;La Violence en Colombie&lt;/em&gt; (1962), écrit avec Germán Guzmán et Eduardo Umaña, étudie pour la première fois la guerre civile qui ravage les campagnes.&lt;/p&gt; &lt;p&gt;Déçu par une sociologie qui observe les pauvres de l’extérieur sans rien changer à leur sort, il quitte l’université dans les années 1970 pour travailler avec les paysans et les communautés de la côte caraïbe. Il y développe la &lt;a href="https://fr.wikipedia.org/wiki/Recherche-action" title=" Wikipedia"&gt;recherche-action&lt;/a&gt; participative : le chercheur ne doit pas monopoliser le savoir ni imposer sa technique, mais travailler avec les communautés comme avec des partenaires et des co-chercheurs, recueillir leurs savoirs, leur mémoire et leurs récits, et partager les résultats sous une forme que tous peuvent comprendre.&lt;/p&gt; &lt;p&gt;La science n’est pas, selon lui, une affaire d’experts neutres : elle doit servir la transformation de la société et la libération des opprimés. Il parle d’une « subversion positive » qui conteste l’ordre injuste pour en construire un meilleur. Ses idées se sont répandues dans le monde entier, en éducation, en santé et en développement. Il participe aussi à l’Assemblée constituante qui rédige la Constitution colombienne de 1991. Il meurt à Bogotá en 2008.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Eugenio_Mar%C3%ADa_de_Hostos" title=" Wikipedia (en)"&gt;Eugenio María de HOSTOS&lt;/a&gt; est un philosophe, éducateur, sociologue et écrivain de &lt;a href="https://fr.wikipedia.org/wiki/Porto_Rico" title=" Wikipedia"&gt;Porto Rico&lt;/a&gt;, surnommé « le Grand Citoyen des Amériques ». Né à Mayagüez dans une famille aisée, il fait ses études en Espagne, où il étudie le droit et la philosophie à Madrid et publie en 1863 un roman, &lt;em&gt;Le Pèlerinage de Bayoán&lt;/em&gt;, qui évoque déjà le destin des Antilles. Déçu que la République espagnole refuse l’autonomie de Porto Rico, il quitte l’Espagne en 1869 pour se consacrer à l’indépendance des colonies antillaises.&lt;/p&gt; &lt;p&gt;Il rêve d’une Confédération des Antilles, réunissant Porto Rico, Cuba et la République dominicaine, et parcourt pour la défendre les États-Unis, le Pérou, le Chili, l’Argentine, le Brésil et le Venezuela. Partout, il fonde ou réforme des écoles. En République dominicaine, il crée en 1880 la première école normale, qui forme des instituteurs à une pédagogie scientifique et laïque. Au Chili, il plaide pour que les femmes aient accès à l’enseignement supérieur et aux professions savantes.&lt;/p&gt; &lt;p&gt;Sa &lt;em&gt;Morale sociale&lt;/em&gt; (1888), inspirée du &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt;, fonde les devoirs de l’individu non sur la religion, mais sur la raison et sur les liens qui l’unissent à la famille, à la société et à l’humanité ; l’éducation doit former des consciences libres et responsables. Après la guerre de 1898, qui fait passer Porto Rico sous domination américaine, il milite pour que l’île puisse décider elle-même de son avenir. Il laisse aussi un traité de sociologie, l’un des premiers d’Amérique latine. Il meurt en exil à Saint-Domingue en 1903.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/falsborda-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hostos-mini.webp</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; politique</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="K69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiers-mondisme</t>
+          <t xml:space="preserve">Positivisme</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sociologue colombien, fondateur de la recherche-action participative, penseur d’un savoir construit avec le peuple.</t>
+          <t xml:space="preserve">éducateur et penseur portoricain, apôtre d’une confédération des Antilles et d’une morale sociale laïque.</t>
         </is>
       </c>
       <c r="N69" s="1" t="inlineStr">
@@ -5399,62 +5407,57 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colombienne</t>
+          <t xml:space="preserve">Portoricaine</t>
         </is>
       </c>
     </row>
     <row r="70" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021</t>
+          <t xml:space="preserve">2008</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928 – 2021</t>
+          <t xml:space="preserve">1925 – 2008</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humberto MATURANA</t>
+          <t xml:space="preserve">Orlando FALS BORDA</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Humberto_Maturana" title=" Wikipedia"&gt;Humberto MATURANA&lt;/a&gt; est un biologiste et philosophe chilien, l’un des penseurs les plus originaux de la biologie de la connaissance. Né à Santiago, il étudie la médecine et la biologie au Chili, puis en Angleterre et à Harvard. Au Massachusetts Institute of Technology, il participe en 1959 à une étude devenue célèbre sur ce que l’œil de la grenouille transmet à son cerveau, qui montre que la perception n’est pas une simple copie du monde extérieur. Il fonde ensuite à l’université du Chili un laboratoire d’« épistémologie expérimentale ».&lt;/p&gt; &lt;p&gt;Avec son élève Francisco Varela, il propose au début des années 1970 le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, du grec « se produire soi-même » : un être vivant est un système qui produit et renouvelle sans cesse ses propres composants, et maintient ainsi sa propre organisation. La cellule en est le modèle. Le vivant n’est donc pas défini par ce qu’il contient, mais par cette manière de s’entretenir lui-même, en échange constant avec son milieu.&lt;/p&gt; &lt;p&gt;Il en tire une théorie de la connaissance : « Tout ce qui est dit est dit par un observateur. » Connaître n’est pas refléter un monde tout fait, mais une activité du vivant, qui fait émerger un monde à travers son action. Dans &lt;em&gt;L’Arbre de la connaissance&lt;/em&gt; (1984), écrit avec Varela, il montre aussi que le langage et la société naissent de la coordination entre les êtres, et que l’amour, l’acceptation de l’autre, est le fondement biologique de la vie sociale. Ses idées ont nourri le &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_%28%C3%A9pist%C3%A9mologie%29" title=" Wikipedia"&gt;constructivisme&lt;/a&gt;, la thérapie familiale et la théorie des systèmes sociaux de &lt;a href="https://fr.wikipedia.org/wiki/Niklas_Luhmann" title=" Wikipedia"&gt;Niklas Luhmann&lt;/a&gt;. Il meurt à Santiago en 2021.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Orlando_Fals_Borda" title=" Wikipedia (en)"&gt;Orlando FALS BORDA&lt;/a&gt; est un sociologue colombien, l’un des grands penseurs latino-américains des sciences sociales et le fondateur de la « recherche-action participative ». Né à Barranquilla, sur la côte caraïbe, formé aux États-Unis, il fonde en 1959 à l’Université nationale de Colombie, avec le prêtre Camilo Torres, l’une des premières facultés de sociologie d’Amérique latine. Son livre &lt;em&gt;La Violence en Colombie&lt;/em&gt; (1962), écrit avec Germán Guzmán et Eduardo Umaña, étudie pour la première fois la guerre civile qui ravage les campagnes.&lt;/p&gt; &lt;p&gt;Déçu par une sociologie qui observe les pauvres de l’extérieur sans rien changer à leur sort, il quitte l’université dans les années 1970 pour travailler avec les paysans et les communautés de la côte caraïbe. Il y développe la &lt;a href="https://fr.wikipedia.org/wiki/Recherche-action" title=" Wikipedia"&gt;recherche-action&lt;/a&gt; participative : le chercheur ne doit pas monopoliser le savoir ni imposer sa technique, mais travailler avec les communautés comme avec des partenaires et des co-chercheurs, recueillir leurs savoirs, leur mémoire et leurs récits, et partager les résultats sous une forme que tous peuvent comprendre.&lt;/p&gt; &lt;p&gt;La science n’est pas, selon lui, une affaire d’experts neutres : elle doit servir la transformation de la société et la libération des opprimés. Il parle d’une « subversion positive » qui conteste l’ordre injuste pour en construire un meilleur. Ses idées se sont répandues dans le monde entier, en éducation, en santé et en développement. Il participe aussi à l’Assemblée constituante qui rédige la Constitution colombienne de 1991. Il meurt à Bogotá en 2008.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/maturana-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/falsborda-mini.webp</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; metaphysique</t>
+          <t xml:space="preserve">epistemologie ; politique</t>
         </is>
       </c>
       <c r="K70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constructivisme</t>
+          <t xml:space="preserve">Tiers-mondisme</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">biologiste et philosophe chilien, inventeur avec Varela de l’autopoïèse, penseur de la connaissance comme fait biologique.</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
+          <t xml:space="preserve">sociologue colombien, fondateur de la recherche-action participative, penseur d’un savoir construit avec le peuple.</t>
+        </is>
+      </c>
+      <c r="N70" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="N70" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
         </is>
       </c>
       <c r="O70" s="1">
@@ -5462,37 +5465,37 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chilienne</t>
+          <t xml:space="preserve">Colombienne</t>
         </is>
       </c>
     </row>
     <row r="71" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1">
-        <v>1946</v>
+        <v>1928</v>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001</t>
+          <t xml:space="preserve">2021</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946 – 2001</t>
+          <t xml:space="preserve">1928 – 2021</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francisco VARELA</t>
+          <t xml:space="preserve">Humberto MATURANA</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_Varela" title=" Wikipedia"&gt;Francisco VARELA&lt;/a&gt; est un biologiste, neuroscientifique et philosophe chilien, l’un des fondateurs des sciences cognitives « incarnées ». Né à Talcahuano, élève d’Humberto Maturana, il soutient une thèse de biologie à Harvard, puis invente avec son maître le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, qui définit le vivant par sa capacité à se produire lui-même. Après le coup d’État de Pinochet en 1973, il doit s’exiler aux États-Unis. Il s’installe en France en 1986 et dirige jusqu’à sa mort une équipe de recherche au CNRS, à Paris.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Inscription corporelle de l’esprit&lt;/em&gt; (1991), écrit avec Evan Thompson et Eleanor Rosch, il critique l’idée que l’esprit serait un ordinateur qui traite des représentations d’un monde extérieur déjà donné. Il propose à la place l’« &lt;a href="https://fr.wikipedia.org/wiki/%C3%89naction" title=" Wikipedia"&gt;énaction&lt;/a&gt; » : la cognition est une action incarnée, par laquelle un être vivant fait émerger son monde à travers son corps, ses sens et ses gestes. Il fonde aussi la « neurophénoménologie », qui veut unir les mesures du cerveau et la description rigoureuse de l’expérience vécue, à la manière de Husserl et de Merleau-Ponty.&lt;/p&gt; &lt;p&gt;Pratiquant du bouddhisme tibétain depuis les années 1970, il voit dans la méditation une méthode précise pour explorer l’expérience. En 1987, il cofonde le &lt;a href="https://fr.wikipedia.org/wiki/Mind_and_Life_Institute" title=" Wikipedia"&gt;Mind and Life Institute&lt;/a&gt;, qui organise des rencontres entre scientifiques et le dalaï-lama. Il est l’un des inspirateurs de l’idée d’un esprit « incarné », aujourd’hui centrale en &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_l%27esprit" title=" Wikipedia"&gt;philosophie de l’esprit&lt;/a&gt;. Il meurt à Paris en 2001, à cinquante-quatre ans, d’une maladie du foie.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Humberto_Maturana" title=" Wikipedia"&gt;Humberto MATURANA&lt;/a&gt; est un biologiste et philosophe chilien, l’un des penseurs les plus originaux de la biologie de la connaissance. Né à Santiago, il étudie la médecine et la biologie au Chili, puis en Angleterre et à Harvard. Au Massachusetts Institute of Technology, il participe en 1959 à une étude devenue célèbre sur ce que l’œil de la grenouille transmet à son cerveau, qui montre que la perception n’est pas une simple copie du monde extérieur. Il fonde ensuite à l’université du Chili un laboratoire d’« épistémologie expérimentale ».&lt;/p&gt; &lt;p&gt;Avec son élève Francisco Varela, il propose au début des années 1970 le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, du grec « se produire soi-même » : un être vivant est un système qui produit et renouvelle sans cesse ses propres composants, et maintient ainsi sa propre organisation. La cellule en est le modèle. Le vivant n’est donc pas défini par ce qu’il contient, mais par cette manière de s’entretenir lui-même, en échange constant avec son milieu.&lt;/p&gt; &lt;p&gt;Il en tire une théorie de la connaissance : « Tout ce qui est dit est dit par un observateur. » Connaître n’est pas refléter un monde tout fait, mais une activité du vivant, qui fait émerger un monde à travers son action. Dans &lt;em&gt;L’Arbre de la connaissance&lt;/em&gt; (1984), écrit avec Varela, il montre aussi que le langage et la société naissent de la coordination entre les êtres, et que l’amour, l’acceptation de l’autre, est le fondement biologique de la vie sociale. Ses idées ont nourri le &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_%28%C3%A9pist%C3%A9mologie%29" title=" Wikipedia"&gt;constructivisme&lt;/a&gt;, la thérapie familiale et la théorie des systèmes sociaux de &lt;a href="https://fr.wikipedia.org/wiki/Niklas_Luhmann" title=" Wikipedia"&gt;Niklas Luhmann&lt;/a&gt;. Il meurt à Santiago en 2021.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/varela-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/maturana-mini.webp</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -5502,12 +5505,12 @@
       </c>
       <c r="K71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constructivisme ; Phénoménologie</t>
+          <t xml:space="preserve">Constructivisme</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">neurobiologiste et philosophe chilien, penseur de l’énaction et du dialogue entre sciences cognitives et bouddhisme.</t>
+          <t xml:space="preserve">biologiste et philosophe chilien, inventeur avec Varela de l’autopoïèse, penseur de la connaissance comme fait biologique.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5531,46 +5534,46 @@
     </row>
     <row r="72" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1">
-        <v>1868</v>
+        <v>1946</v>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963</t>
+          <t xml:space="preserve">2001</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868 – 1963</t>
+          <t xml:space="preserve">1946 – 2001</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">W. E. B. DU BOIS</t>
+          <t xml:space="preserve">Francisco VARELA</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/W._E._B._Du_Bois" title=" Wikipedia"&gt;W. E. B. DU BOIS&lt;/a&gt; (William Edward Burghardt Du Bois) est un sociologue, historien et militant africain-américain, l’un des plus grands penseurs américains du XXe siècle. Né en 1868 dans le Massachusetts, il étudie à Fisk, à Berlin, puis à Harvard, où il devient en 1895 le premier Africain-Américain à obtenir un doctorat. Son étude &lt;em&gt;The Philadelphia Negro&lt;/em&gt; (1899) est l’une des premières grandes enquêtes de sociologie empirique aux États-Unis.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Les_%C3%82mes_du_peuple_noir" title=" Wikipedia"&gt;&lt;em&gt;Les Âmes du peuple noir&lt;/em&gt;&lt;/a&gt; (1903), il affirme que « le problème du XXe siècle est le problème de la ligne de couleur ». Il y décrit la « double conscience » des Noirs américains : le sentiment de se voir toujours à travers les yeux d’un monde qui les méprise, d’être à la fois américain et noir, « deux âmes, deux pensées, deux combats inconciliables dans un seul corps sombre ». Dans &lt;em&gt;Black Reconstruction&lt;/em&gt; (1935), il réhabilitera le rôle des anciens esclaves dans l’histoire américaine d’après la guerre de Sécession. Il y critique aussi Booker T. Washington, qui conseillait aux Noirs d’accepter la ségrégation en échange du progrès économique.&lt;/p&gt; &lt;p&gt;En 1909, il est l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/National_Association_for_the_Advancement_of_Colored_People" title=" Wikipedia"&gt;NAACP&lt;/a&gt;, la grande organisation de défense des droits civiques, dont il dirige la revue &lt;em&gt;The Crisis&lt;/em&gt;. Il organise plusieurs congrès panafricains et devient le « père du &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; ». Proche du socialisme, persécuté pendant le maccarthysme, il s’installe à la fin de sa vie au &lt;a href="https://fr.wikipedia.org/wiki/Ghana" title=" Wikipedia"&gt;Ghana&lt;/a&gt;, à l’invitation de Kwame Nkrumah, et y meurt en 1963, à la veille de la marche sur Washington de Martin Luther King.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_Varela" title=" Wikipedia"&gt;Francisco VARELA&lt;/a&gt; est un biologiste, neuroscientifique et philosophe chilien, l’un des fondateurs des sciences cognitives « incarnées ». Né à Talcahuano, élève d’Humberto Maturana, il soutient une thèse de biologie à Harvard, puis invente avec son maître le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, qui définit le vivant par sa capacité à se produire lui-même. Après le coup d’État de Pinochet en 1973, il doit s’exiler aux États-Unis. Il s’installe en France en 1986 et dirige jusqu’à sa mort une équipe de recherche au CNRS, à Paris.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Inscription corporelle de l’esprit&lt;/em&gt; (1991), écrit avec Evan Thompson et Eleanor Rosch, il critique l’idée que l’esprit serait un ordinateur qui traite des représentations d’un monde extérieur déjà donné. Il propose à la place l’« &lt;a href="https://fr.wikipedia.org/wiki/%C3%89naction" title=" Wikipedia"&gt;énaction&lt;/a&gt; » : la cognition est une action incarnée, par laquelle un être vivant fait émerger son monde à travers son corps, ses sens et ses gestes. Il fonde aussi la « neurophénoménologie », qui veut unir les mesures du cerveau et la description rigoureuse de l’expérience vécue, à la manière de Husserl et de Merleau-Ponty.&lt;/p&gt; &lt;p&gt;Pratiquant du bouddhisme tibétain depuis les années 1970, il voit dans la méditation une méthode précise pour explorer l’expérience. En 1987, il cofonde le &lt;a href="https://fr.wikipedia.org/wiki/Mind_and_Life_Institute" title=" Wikipedia"&gt;Mind and Life Institute&lt;/a&gt;, qui organise des rencontres entre scientifiques et le dalaï-lama. Il est l’un des inspirateurs de l’idée d’un esprit « incarné », aujourd’hui centrale en &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_l%27esprit" title=" Wikipedia"&gt;philosophie de l’esprit&lt;/a&gt;. Il meurt à Paris en 2001, à cinquante-quatre ans, d’une maladie du foie.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/dubois-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/varela-mini.webp</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
         </is>
       </c>
       <c r="K72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan-africanisme</t>
+          <t xml:space="preserve">Constructivisme ; Phénoménologie</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sociologue et militant africain-américain, penseur de la « double conscience » et père du panafricanisme.</t>
+          <t xml:space="preserve">neurobiologiste et philosophe chilien, penseur de l’énaction et du dialogue entre sciences cognitives et bouddhisme.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5584,69 +5587,74 @@
         </is>
       </c>
       <c r="O72" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Américaine</t>
+          <t xml:space="preserve">Chilienne</t>
         </is>
       </c>
     </row>
     <row r="73" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1">
-        <v>1928</v>
+        <v>1868</v>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024</t>
+          <t xml:space="preserve">1963</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928 – 2024</t>
+          <t xml:space="preserve">1868 – 1963</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustavo GUTIÉRREZ</t>
+          <t xml:space="preserve">W. E. B. DU BOIS</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo GUTIÉRREZ&lt;/a&gt; est un prêtre et théologien péruvien, considéré comme le père de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;théologie de la libération&lt;/a&gt;. Né à Lima en 1928 dans un milieu modeste, il souffre adolescent d’une ostéomyélite qui le cloue longtemps au lit ; il lit alors beaucoup et commence des études de médecine pour devenir psychiatre. À vingt-quatre ans, il choisit la prêtrise et part étudier la philosophie et la psychologie à Louvain, puis la théologie à Lyon.&lt;/p&gt; &lt;p&gt;Ordonné prêtre en 1959, il devient vicaire dans un quartier pauvre de Lima, tout en enseignant à l’université catholique, et repense toute sa théologie au contact de ce peuple. En 1971, il publie &lt;em&gt;Théologie de la libération&lt;/em&gt;, traduit dans une vingtaine de langues. La pauvreté, écrit-il, n’est pas une fatalité mais le fruit d’injustices, et elle est contraire à la volonté de Dieu. La théologie est une « réflexion critique sur la pratique à la lumière de la Parole » : elle vient en second, après l’engagement aux côtés des pauvres. Le salut ne se joue pas seulement dans l’au-delà ; il touche toute l’existence, et la libération sociale et politique en fait partie, sans s’y réduire. Dans &lt;em&gt;Boire à son propre puits&lt;/em&gt; (1983), il montre que cet engagement est aussi une spiritualité, une manière de suivre le Christ.&lt;/p&gt; &lt;p&gt;Ses positions lui valent la méfiance de Rome dans les années 1980, sans condamnation. Entré chez les Dominicains en 1998, il enseigne dans de nombreuses universités d’Europe et des États-Unis. Le pape François le reçoit en 2013, signe de la réhabilitation de son œuvre, et l’« option préférentielle pour les pauvres » est devenue un principe de l’enseignement de l’Église. Il meurt à Lima en 2024, à quatre-vingt-seize ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/W._E._B._Du_Bois" title=" Wikipedia"&gt;W. E. B. DU BOIS&lt;/a&gt; (William Edward Burghardt Du Bois) est un sociologue, historien et militant africain-américain, l’un des plus grands penseurs américains du XXe siècle. Né en 1868 dans le Massachusetts, il étudie à Fisk, à Berlin, puis à Harvard, où il devient en 1895 le premier Africain-Américain à obtenir un doctorat. Son étude &lt;em&gt;The Philadelphia Negro&lt;/em&gt; (1899) est l’une des premières grandes enquêtes de sociologie empirique aux États-Unis.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Les_%C3%82mes_du_peuple_noir" title=" Wikipedia"&gt;&lt;em&gt;Les Âmes du peuple noir&lt;/em&gt;&lt;/a&gt; (1903), il affirme que « le problème du XXe siècle est le problème de la ligne de couleur ». Il y décrit la « double conscience » des Noirs américains : le sentiment de se voir toujours à travers les yeux d’un monde qui les méprise, d’être à la fois américain et noir, « deux âmes, deux pensées, deux combats inconciliables dans un seul corps sombre ». Dans &lt;em&gt;Black Reconstruction&lt;/em&gt; (1935), il réhabilitera le rôle des anciens esclaves dans l’histoire américaine d’après la guerre de Sécession. Il y critique aussi Booker T. Washington, qui conseillait aux Noirs d’accepter la ségrégation en échange du progrès économique.&lt;/p&gt; &lt;p&gt;En 1909, il est l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/National_Association_for_the_Advancement_of_Colored_People" title=" Wikipedia"&gt;NAACP&lt;/a&gt;, la grande organisation de défense des droits civiques, dont il dirige la revue &lt;em&gt;The Crisis&lt;/em&gt;. Il organise plusieurs congrès panafricains et devient le « père du &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; ». Proche du socialisme, persécuté pendant le maccarthysme, il s’installe à la fin de sa vie au &lt;a href="https://fr.wikipedia.org/wiki/Ghana" title=" Wikipedia"&gt;Ghana&lt;/a&gt;, à l’invitation de Kwame Nkrumah, et y meurt en 1963, à la veille de la marche sur Washington de Martin Luther King.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ggutierrez-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dubois-mini.webp</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; politique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="K73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie de la libération</t>
+          <t xml:space="preserve">Pan-africanisme</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prêtre et théologien péruvien, père de la théologie de la libération et de l’« option préférentielle pour les pauvres ».</t>
+          <t xml:space="preserve">sociologue et militant africain-américain, penseur de la « double conscience » et père du panafricanisme.</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
       <c r="O73" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Péruvienne</t>
+          <t xml:space="preserve">Américaine</t>
         </is>
       </c>
     </row>
@@ -5656,42 +5664,42 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018</t>
+          <t xml:space="preserve">2024</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928 – 2018</t>
+          <t xml:space="preserve">1928 – 2024</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aníbal QUIJANO</t>
+          <t xml:space="preserve">Gustavo GUTIÉRREZ</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal QUIJANO&lt;/a&gt; est un sociologue péruvien, l’un des grands penseurs latino-américains du XXe siècle et le fondateur de la pensée décoloniale. Né en 1928 à Yanama, dans les Andes péruviennes, il étudie à l’université de San Marcos, à Lima, où il enseigne ensuite la sociologie. Dans les années 1960 et 1970, il participe aux travaux de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_la_d%C3%A9pendance" title=" Wikipedia"&gt;théorie de la dépendance&lt;/a&gt;, qui explique le sous-développement de l’Amérique latine par sa place subordonnée dans l’économie mondiale, et étudie la condition des populations indiennes et métisses des villes.&lt;/p&gt; &lt;p&gt;En 1992, pour le cinquième centenaire de l’arrivée de Christophe Colomb, il publie l’article « Colonialité et modernité/rationalité », qui forge la notion de « colonialité du pouvoir ». La conquête de l’Amérique a donné naissance à la fois au capitalisme mondial et à une idée nouvelle, celle de « race », qui a permis de classer les peuples en supérieurs et inférieurs et de distribuer entre eux le travail : le salariat pour les Européens, le servage pour les Indiens, l’esclavage pour les Africains. Cette classification a survécu à l’indépendance des colonies : elle structure encore les rapports sociaux, le savoir et la manière dont chacun se perçoit. Quijano critique aussi l’« eurocentrisme », qui fait de l’histoire européenne le modèle de l’histoire universelle.&lt;/p&gt; &lt;p&gt;Professeur à l’université de Binghamton, aux États-Unis, il anime le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt; avec Walter Mignolo et Enrique Dussel. La philosophe argentine &lt;a href="https://fr.wikipedia.org/wiki/Mar%C3%ADa_Lugones" title=" Wikipedia"&gt;María Lugones&lt;/a&gt; a prolongé son concept dans celui de « colonialité du genre ». Il meurt à Lima en 2018.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo GUTIÉRREZ&lt;/a&gt; est un prêtre et théologien péruvien, considéré comme le père de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;théologie de la libération&lt;/a&gt;. Né à Lima en 1928 dans un milieu modeste, il souffre adolescent d’une ostéomyélite qui le cloue longtemps au lit ; il lit alors beaucoup et commence des études de médecine pour devenir psychiatre. À vingt-quatre ans, il choisit la prêtrise et part étudier la philosophie et la psychologie à Louvain, puis la théologie à Lyon.&lt;/p&gt; &lt;p&gt;Ordonné prêtre en 1959, il devient vicaire dans un quartier pauvre de Lima, tout en enseignant à l’université catholique, et repense toute sa théologie au contact de ce peuple. En 1971, il publie &lt;em&gt;Théologie de la libération&lt;/em&gt;, traduit dans une vingtaine de langues. La pauvreté, écrit-il, n’est pas une fatalité mais le fruit d’injustices, et elle est contraire à la volonté de Dieu. La théologie est une « réflexion critique sur la pratique à la lumière de la Parole » : elle vient en second, après l’engagement aux côtés des pauvres. Le salut ne se joue pas seulement dans l’au-delà ; il touche toute l’existence, et la libération sociale et politique en fait partie, sans s’y réduire. Dans &lt;em&gt;Boire à son propre puits&lt;/em&gt; (1983), il montre que cet engagement est aussi une spiritualité, une manière de suivre le Christ.&lt;/p&gt; &lt;p&gt;Ses positions lui valent la méfiance de Rome dans les années 1980, sans condamnation. Entré chez les Dominicains en 1998, il enseigne dans de nombreuses universités d’Europe et des États-Unis. Le pape François le reçoit en 2013, signe de la réhabilitation de son œuvre, et l’« option préférentielle pour les pauvres » est devenue un principe de l’enseignement de l’Église. Il meurt à Lima en 2024, à quatre-vingt-seize ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/quijano-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ggutierrez-mini.webp</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; epistemologie</t>
+          <t xml:space="preserve">spiritualite ; politique</t>
         </is>
       </c>
       <c r="K74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensée décoloniale</t>
+          <t xml:space="preserve">Théologie de la libération</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sociologue péruvien, inventeur de la « colonialité du pouvoir » et fondateur de la pensée décoloniale.</t>
+          <t xml:space="preserve">prêtre et théologien péruvien, père de la théologie de la libération et de l’« option préférentielle pour les pauvres ».</t>
         </is>
       </c>
       <c r="N74" s="1" t="inlineStr">
@@ -5699,7 +5707,9 @@
           <t xml:space="preserve">sud</t>
         </is>
       </c>
-      <c r="O74" s="1"/>
+      <c r="O74" s="1">
+        <v>2</v>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t xml:space="preserve">Péruvienne</t>
@@ -5708,102 +5718,102 @@
     </row>
     <row r="75" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1">
-        <v>1840</v>
+        <v>1928</v>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910</t>
+          <t xml:space="preserve">2018</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840 – 1910</t>
+          <t xml:space="preserve">1928 – 2018</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">William Graham SUMNER</t>
+          <t xml:space="preserve">Aníbal QUIJANO</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/William_Graham_Sumner" title=" Wikipedia"&gt;William Graham SUMNER&lt;/a&gt; est un sociologue et économiste américain, l’un des fondateurs de la sociologie aux États-Unis et la figure majeure de ce qu’on appellera le &lt;a href="https://fr.wikipedia.org/wiki/Darwinisme_social" title=" Wikipedia"&gt;darwinisme social&lt;/a&gt; américain. Né en 1840 à Paterson, dans le New Jersey, fils d’un ouvrier anglais immigré, il étudie à Yale, puis en Europe, et devient d’abord pasteur épiscopalien. En 1872, il est nommé professeur à Yale, où il donne l’un des premiers cours intitulés « sociologie ».&lt;/p&gt; &lt;p&gt;Lecteur de Herbert Spencer, il applique à la société l’idée de lutte pour l’existence. Dans &lt;em&gt;Ce que les classes sociales se doivent les unes aux autres&lt;/em&gt; (1883), il répond : rien, sinon le respect de la liberté et des contrats. L’aide de l’État aux pauvres se fait toujours aux dépens de l’« homme oublié », le travailleur modeste qui paie ses impôts sans rien demander. La richesse récompense le travail, l’épargne et la tempérance, et la réussite des plus capables profite à toute la société. Ces positions ont fait de lui, aux yeux de ses critiques, le défenseur d’un capitalisme sans pitié pour les faibles.&lt;/p&gt; &lt;p&gt;Mais il défend aussi le libre-échange contre les monopoles protégés et s’oppose fermement à l’impérialisme : en 1898, il dénonce la guerre contre l’Espagne et la conquête des Philippines dans &lt;em&gt;La Conquête des États-Unis par l’Espagne&lt;/em&gt;. Dans &lt;em&gt;Folkways&lt;/em&gt; (1906), il étudie les coutumes et les mœurs des sociétés, et forge le mot « ethnocentrisme » pour désigner la tendance de chaque groupe à juger les autres d’après ses propres valeurs. Il meurt en 1910.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal QUIJANO&lt;/a&gt; est un sociologue péruvien, l’un des grands penseurs latino-américains du XXe siècle et le fondateur de la pensée décoloniale. Né en 1928 à Yanama, dans les Andes péruviennes, il étudie à l’université de San Marcos, à Lima, où il enseigne ensuite la sociologie. Dans les années 1960 et 1970, il participe aux travaux de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_la_d%C3%A9pendance" title=" Wikipedia"&gt;théorie de la dépendance&lt;/a&gt;, qui explique le sous-développement de l’Amérique latine par sa place subordonnée dans l’économie mondiale, et étudie la condition des populations indiennes et métisses des villes.&lt;/p&gt; &lt;p&gt;En 1992, pour le cinquième centenaire de l’arrivée de Christophe Colomb, il publie l’article « Colonialité et modernité/rationalité », qui forge la notion de « colonialité du pouvoir ». La conquête de l’Amérique a donné naissance à la fois au capitalisme mondial et à une idée nouvelle, celle de « race », qui a permis de classer les peuples en supérieurs et inférieurs et de distribuer entre eux le travail : le salariat pour les Européens, le servage pour les Indiens, l’esclavage pour les Africains. Cette classification a survécu à l’indépendance des colonies : elle structure encore les rapports sociaux, le savoir et la manière dont chacun se perçoit. Quijano critique aussi l’« eurocentrisme », qui fait de l’histoire européenne le modèle de l’histoire universelle.&lt;/p&gt; &lt;p&gt;Professeur à l’université de Binghamton, aux États-Unis, il anime le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt; avec Walter Mignolo et Enrique Dussel. La philosophe argentine &lt;a href="https://fr.wikipedia.org/wiki/Mar%C3%ADa_Lugones" title=" Wikipedia"&gt;María Lugones&lt;/a&gt; a prolongé son concept dans celui de « colonialité du genre ». Il meurt à Lima en 2018.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/sumner-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/quijano-mini.webp</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">politique ; epistemologie</t>
         </is>
       </c>
       <c r="K75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darwinisme social ; Libéralisme</t>
+          <t xml:space="preserve">Pensée décoloniale</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sociologue américain de Yale, défenseur d’un libéralisme sans État-providence, inventeur du mot « ethnocentrisme ».</t>
+          <t xml:space="preserve">sociologue péruvien, inventeur de la « colonialité du pouvoir » et fondateur de la pensée décoloniale.</t>
         </is>
       </c>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">occident</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="O75" s="1"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Américaine</t>
+          <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>
     <row r="76" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1">
-        <v>1917</v>
+        <v>1840</v>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003</t>
+          <t xml:space="preserve">1910</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917 – 2003</t>
+          <t xml:space="preserve">1840 – 1910</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Donald DAVIDSON</t>
+          <t xml:space="preserve">William Graham SUMNER</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donald_Davidson" title=" Wikipedia"&gt;Donald DAVIDSON&lt;/a&gt; est un philosophe américain, l’un des plus influents de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; de la seconde moitié du XXe siècle. Né en 1917 à Springfield, dans le Massachusetts, il étudie à Harvard la littérature et les lettres classiques avant de se tourner vers la philosophie sous l’influence de Quine. Après avoir servi dans la marine pendant la guerre, il enseigne notamment à Stanford, à Princeton et à Berkeley.&lt;/p&gt; &lt;p&gt;Dans « Actions, raisons et causes » (1963), il soutient que nos raisons d’agir, nos désirs et nos croyances, sont aussi les causes de nos actions. Dans « Les événements mentaux » (1970), il défend le « monisme anomal » : chaque événement mental est un événement physique, mais il n’existe pas de lois strictes qui relient le mental au physique, car le mental obéit à d’autres principes, ceux de la rationalité. Il réconcilie ainsi le matérialisme avec l’autonomie de la pensée.&lt;/p&gt; &lt;p&gt;Sa théorie de l’« interprétation radicale » prolonge le &lt;a href="https://fr.wikipedia.org/wiki/Holisme" title=" Wikipedia"&gt;holisme&lt;/a&gt; de Quine : pour comprendre un locuteur dont on ignore tout de la langue, il faut lui attribuer en même temps des croyances et des significations, en supposant qu’il pense en grande partie comme nous. C’est le « principe de charité ». Le sens d’un mot dépend du sens de toute la langue, et nos croyances forment un réseau. Il en conclut, dans un article célèbre de 1974, que l’idée de « schèmes conceptuels » radicalement incommensurables n’a pas de sens. Il meurt à Berkeley en 2003.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/William_Graham_Sumner" title=" Wikipedia"&gt;William Graham SUMNER&lt;/a&gt; est un sociologue et économiste américain, l’un des fondateurs de la sociologie aux États-Unis et la figure majeure de ce qu’on appellera le &lt;a href="https://fr.wikipedia.org/wiki/Darwinisme_social" title=" Wikipedia"&gt;darwinisme social&lt;/a&gt; américain. Né en 1840 à Paterson, dans le New Jersey, fils d’un ouvrier anglais immigré, il étudie à Yale, puis en Europe, et devient d’abord pasteur épiscopalien. En 1872, il est nommé professeur à Yale, où il donne l’un des premiers cours intitulés « sociologie ».&lt;/p&gt; &lt;p&gt;Lecteur de Herbert Spencer, il applique à la société l’idée de lutte pour l’existence. Dans &lt;em&gt;Ce que les classes sociales se doivent les unes aux autres&lt;/em&gt; (1883), il répond : rien, sinon le respect de la liberté et des contrats. L’aide de l’État aux pauvres se fait toujours aux dépens de l’« homme oublié », le travailleur modeste qui paie ses impôts sans rien demander. La richesse récompense le travail, l’épargne et la tempérance, et la réussite des plus capables profite à toute la société. Ces positions ont fait de lui, aux yeux de ses critiques, le défenseur d’un capitalisme sans pitié pour les faibles.&lt;/p&gt; &lt;p&gt;Mais il défend aussi le libre-échange contre les monopoles protégés et s’oppose fermement à l’impérialisme : en 1898, il dénonce la guerre contre l’Espagne et la conquête des Philippines dans &lt;em&gt;La Conquête des États-Unis par l’Espagne&lt;/em&gt;. Dans &lt;em&gt;Folkways&lt;/em&gt; (1906), il étudie les coutumes et les mœurs des sociétés, et forge le mot « ethnocentrisme » pour désigner la tendance de chaque groupe à juger les autres d’après ses propres valeurs. Il meurt en 1910.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/donalddavidson-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/sumner-mini.webp</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">langage ; epistemologie ; metaphysique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="K76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holisme ; Analytique</t>
+          <t xml:space="preserve">Darwinisme social ; Libéralisme</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe américain de l’action et du langage, auteur du « monisme anomal ».</t>
+          <t xml:space="preserve">sociologue américain de Yale, défenseur d’un libéralisme sans État-providence, inventeur du mot « ethnocentrisme ».</t>
         </is>
       </c>
       <c r="N76" s="1" t="inlineStr">
@@ -5820,46 +5830,46 @@
     </row>
     <row r="77" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1">
-        <v>1880</v>
+        <v>1917</v>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973</t>
+          <t xml:space="preserve">2003</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880 – 1973</t>
+          <t xml:space="preserve">1917 – 2003</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roy Wood SELLARS</t>
+          <t xml:space="preserve">Donald DAVIDSON</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Roy_Wood_Sellars" title=" Wikipedia"&gt;Roy Wood SELLARS&lt;/a&gt; est un philosophe américain d’origine canadienne. Né en 1880 dans l’Ontario, il grandit dans le Michigan, où son père est médecin de campagne, et fait presque toute sa carrière à l’université du Michigan, à Ann Arbor. Il est le père du philosophe Wilfrid Sellars. Au début du XXe siècle, alors que l’idéalisme domine encore les universités américaines, il fait partie de ceux qui veulent revenir à un &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_%28philosophie%29" title=" Wikipedia"&gt;réalisme&lt;/a&gt; compatible avec les sciences.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Critical Realism&lt;/em&gt; (1916), puis dans un ouvrage collectif de 1920, il défend le « réalisme critique » : nous percevons bien des choses qui existent indépendamment de nous, mais à travers des contenus mentaux qui ne sont pas les choses elles-mêmes. Contre le réalisme naïf, la perception est une interprétation ; contre l’idéalisme, elle nous fait réellement connaître le monde. Dans &lt;em&gt;Evolutionary Naturalism&lt;/em&gt; (1922), il propose un matérialisme non réducteur : la nature produit, au cours de l’évolution, des niveaux d’organisation nouveaux, la vie puis l’esprit, qui ont leurs propres propriétés, sans rien de surnaturel. L’esprit n’est pas une substance à part : il est le cerveau lui-même, considéré à son niveau le plus élevé d’organisation.&lt;/p&gt; &lt;p&gt;Sellars applique ce naturalisme à la religion : dans &lt;em&gt;The Next Step in Religion&lt;/em&gt; (1918), il propose une religion sans Dieu, tournée vers l’accomplissement humain. Il est en 1933 le principal rédacteur du &lt;em&gt;Manifeste humaniste&lt;/em&gt;, qui défend un humanisme religieux sans surnaturel, et signe le second manifeste en 1973. Il meurt à Ann Arbor la même année, à quatre-vingt-treize ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donald_Davidson" title=" Wikipedia"&gt;Donald DAVIDSON&lt;/a&gt; est un philosophe américain, l’un des plus influents de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; de la seconde moitié du XXe siècle. Né en 1917 à Springfield, dans le Massachusetts, il étudie à Harvard la littérature et les lettres classiques avant de se tourner vers la philosophie sous l’influence de Quine. Après avoir servi dans la marine pendant la guerre, il enseigne notamment à Stanford, à Princeton et à Berkeley.&lt;/p&gt; &lt;p&gt;Dans « Actions, raisons et causes » (1963), il soutient que nos raisons d’agir, nos désirs et nos croyances, sont aussi les causes de nos actions. Dans « Les événements mentaux » (1970), il défend le « monisme anomal » : chaque événement mental est un événement physique, mais il n’existe pas de lois strictes qui relient le mental au physique, car le mental obéit à d’autres principes, ceux de la rationalité. Il réconcilie ainsi le matérialisme avec l’autonomie de la pensée.&lt;/p&gt; &lt;p&gt;Sa théorie de l’« interprétation radicale » prolonge le &lt;a href="https://fr.wikipedia.org/wiki/Holisme" title=" Wikipedia"&gt;holisme&lt;/a&gt; de Quine : pour comprendre un locuteur dont on ignore tout de la langue, il faut lui attribuer en même temps des croyances et des significations, en supposant qu’il pense en grande partie comme nous. C’est le « principe de charité ». Le sens d’un mot dépend du sens de toute la langue, et nos croyances forment un réseau. Il en conclut, dans un article célèbre de 1974, que l’idée de « schèmes conceptuels » radicalement incommensurables n’a pas de sens. Il meurt à Berkeley en 2003.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/rwsellars-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/donalddavidson-mini.webp</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie ; spiritualite</t>
+          <t xml:space="preserve">langage ; epistemologie ; metaphysique</t>
         </is>
       </c>
       <c r="K77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturalisme ; Réalisme ; Émergentisme</t>
+          <t xml:space="preserve">Holisme ; Analytique</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe américain d’origine canadienne, théoricien du réalisme critique et du naturalisme évolutionniste.</t>
+          <t xml:space="preserve">philosophe américain de l’action et du langage, auteur du « monisme anomal ».</t>
         </is>
       </c>
       <c r="N77" s="1" t="inlineStr">
@@ -6118,35 +6128,35 @@
     <hyperlink ref="H15" r:id="rId7" display="https://www.laphilo.fr/pho/fbrito-mini.webp"/>
     <hyperlink ref="E16" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Carlos_Vaz_Ferreira&quot;  title=&quot; Wikipedia&quot;&gt;Carlos VAS FERREIRA&lt;/a&gt; était un  philosophe uruguayen considéré comme l’une des figures majeures de la pensée hispano‑américaine au début du XXᵉ siècle. Issue d’une famille aux origines portugaise et uruguayenne, sa trajectoire intellectuelle s’inscrit dans un contexte de modernisation de l’Université et de reformulation des idées scientifiques et morales en Amérique du Sud. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=AmRpz8vCejs&quot; title=&quot;Vas Ferreira par Pablo Romero&quot;&gt;Sa philosophie &lt;/a&gt; se situe à la croisée du positivisme, du pragmatisme et de l’empirisme britannique, avec un respect marqué pour Herbert Spencer, John Stuart Mill, William James et Henri Bergson, sans jamais adopter intégralement leurs doctrines. Il critique la rigidité des systèmes logiques et métaphysiques classiques, estimant que le langage et la logique formelle imposent au réel une précision artificielle qui masque la complexité et la fluidité de l’expérience. &lt;/p&gt; &lt;p&gt; Il  développe l’idée d’une &lt;a href=&quot;https://www.youtube.com/watch?v=UeadgG1ud1g&quot; title=&quot;Vas Ferreira y su logica viva par Tribuna Constitucional&quot;&gt;« logique vivante », &lt;/a&gt; c’est‑à‑dire une logique ancrée dans la vie concrète, attentive aux degrés de probabilité et aux limites de nos certitudes plutôt qu’aux schémas abstraits. Pour lui, la raison doit rester souple et vigilante, proche de l’expérience et des données empiriques, afin de ne pas basculer dans des systèmes dogmatiques. &lt;/p&gt; &lt;p&gt; En épistémologie, il défend une vision modeste de la science : les sciences sont des outils puissants mais partiaux, incapables de saisir le tout de la réalité et toujours confrontées à des questions métaphysiques implicites. La philosophie, selon lui, doit clarifier ces présupposés, rappeler les limites symboliques de la science et contrer les « mauvaises métaphysiques » qui surgissent lorsque l’on ignore les questions fondamentales. &lt;/p&gt; &lt;p&gt; Sur le plan éthique et social, il s’intéresse à la liberté, à la morale des intellectuels, aux problèmes sociaux et aux questions de propriété ou de féminisme. Il met en avant une morale sensible à la complexité des situations, où les principes comportent des exceptions et où le choix moral implique souvent des compromis entre des biens et des maux partiels ; tout en affirmant qu’il existe un progrès moral dans l’histoire humaine, marqué par l’élargissement des idéaux et la résistance accrue au mal. &lt;/p&gt; &#10;&#10;&#10;&#10;&#10;"/>
     <hyperlink ref="H16" r:id="rId9" display="https://www.laphilo.fr/pho/cvferreira-mini.webp"/>
-    <hyperlink ref="E18" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Antonio_Caso&quot;   title=&quot; Wikipedia&quot;&gt;Antonio CASO&lt;/a&gt; était un philosophe mexicain connu pour sa critique du positivisme et pour un  &lt;a href=&quot;https://www.youtube.com/watch?v=YlEoF2CNNxA&quot; title=&quot;&quot;Antonio Caso Andrade - Filósofo y Sociológico Mexicano - Una Mirada Profunda a sus Contribuciones&quot; par Biografías de Filósofos&quot;&gt;humanisme spiritualiste &lt;/a&gt; influent dans la culture intellectuelle mexicaine. Il cofonde en 1910, avec José Vasconcelos et d’autres, l’Ateneo de la Juventud, cercle intellectuel qui s’oppose au positivisme dominant dans le Mexique porfirien. Il défend un christianisme philosophique libéral inspiré notamment de Blaise Pascal et de Tolstoï, mettant en avant la liberté, la vie intérieure et la dimension spirituelle de l’être humain. &lt;/p&gt; &lt;p&gt; Son ouvrage clé,  &lt;a href=&quot;https://filosofiamexicana.org/2013/06/24/la-existencia-como-economia-como-desinteres-y-como-caridad-resena/&quot; title=&quot;La existencia como economía como desinterés y como caridad. par filofiaexicana&quot;&gt;&quot;La existencia como economía, como desinterés y como caridad&quot; &lt;/a&gt; paru en 1916, propose une anthropologie où l’existence humaine se déploie en trois niveaux: l’économie (survie, utilité), le désintéressement (contemplation) et la charité ou amour. Dans cette perspective, il distingue choses, individus et personnes, en attribuant aux personnes la capacité de désintéressement et d’amour, c’est‑à‑dire de créer des valeurs et de dépasser l’égoïsme. &lt;/p&gt; &lt;p&gt; Sa métaphysique met l’accent sur le processus, la liberté, la vie et l’esprit: la réalité est pour lui un dynamisme fluide que le schéma logique traditionnel (sujet‑prédicat) fige et déforme. Il s’inspire surtout d’Henri Bergson, mais aussi de Kant, Schopenhauer, Nietzsche et plus tard Husserl, dont il commente la phénoménologie dans ses écrits tardifs sur la personne humaine et l’État totalitaire. &lt;/p&gt; &lt;p&gt; Il est considéré comme un précurseur de la sociologie au Mexique: il crée la chaire de sociologie à l’université et publie &quot;Sociología genética y sistemática&quot; paru en 1922 puis un manuel de Sociología en 1940, très utilisé dans les universités mexicaines. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E19" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alfonso_Reyes&quot;  title=&quot; Wikipedia&quot;&gt;Alfonso REYES&lt;/a&gt; était un écrivain et philosophe &amp; diplomate  mexicain, souvent considéré comme l’un des grands humanistes de la langue espagnole au XXe siècle.  &lt;a href=&quot;https://www.persee.fr/doc/hispa_0007-4640_1960_num_62_1_3655&quot;  title=&quot; Alfonso Reyes par Persée&quot;&gt;Sa pensée &lt;/a&gt; philosophique est inséparable de son travail d’essayiste, de critique littéraire et de médiateur entre les cultures européennes et latino‑américaines. &lt;/p&gt; &lt;p&gt; Son premier livre important, &quot;Cuestiones estéticas&quot; paru en  1911 est une série de réflexions sur l’esthétique et la critique littéraire, où il articule déjà l’idée que l’expérience artistique est une forme de connaissance privilégiée du monde. Il donne des conférences sur l’&quot;esthétique classique&quot;, qui influenceront durablement l’orientation intellectuelle mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Il n’est pas un philosophe systématique au sens académique, mais un humaniste qui pense la littérature, l’histoire et le mythe comme voies d’accès à la réalité et à l’identité mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &lt;a href=&quot;https://www.youtube.com/watch?v=IeZKZ6PC9H4&quot;  title=&quot; Visión de Anáhuac de Alfonso Reyes par Literatubers&quot;&gt;&quot;Visión de Anáhuac&quot; &lt;/a&gt;  , il propose une méditation poétique et historique sur le Mexique préhispanique et la Conquête, en insistant sur la continuité d’une sensibilité mexicaine à travers les siècles. &lt;/p&gt; &lt;p&gt; Il défend une conception de l’homme formé par les lettres, la philosophie et les sciences, contre les réductions technocratiques ou purement utilitaires du savoir et pense l’Amérique latine comme espace de synthèse entre héritages indigènes, hispaniques et européens, et fait de la traduction et de la critique des instruments de ce dialogue. &lt;/p&gt;"/>
-    <hyperlink ref="E21" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Francisco ROMERO&lt;/a&gt; était un philosophe argentin d’origine espagnole, professeur à l’Université de Buenos Aires et à La Plata, et une figure centrale de la réaction  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ib%C3%A9ro-Am%C3%A9rique&quot;  title=&quot;ibéro-amérique par wikipedia&quot;&gt; ibéro-américaine &lt;/a&gt; contre le positivisme dominant au début du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa production philosophique couvre l’épistémologie, la philosophie de la culture et l’anthropologie philosophique ; son ouvrage majeur en langue espagnole, Teoría del hombre (1952), propose une réflexion systématique sur la condition humaine, la liberté et la créativité culturelle, et a été traduit en anglais sous le titre Theory of Man.https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher) &lt;/p&gt; &lt;p&gt; Il  prit position contre  &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9ductionnisme&quot;  title=&quot;Reductionnisme par wikipedia&quot;&gt; le réductionnisme scientiste &lt;/a&gt; en défendant l’idée que la culture et les créations humaines (art, religion, langage) exigent des méthodes et des concepts propres, distincts des instruments des sciences naturelles ; il chercha donc à articuler rigueur philosophique et sensibilité littéraire. &lt;/p&gt; &lt;p&gt; ur le plan méthodologique, il promut une philosophie qui dialogue avec l’histoire des idées et avec les problèmes concrets de la société ibéro-américaine : ses travaux montrent un intérêt marqué pour la responsabilité sociale des intellectuels et pour la formation culturelle des peuples. &lt;/p&gt; &lt;p&gt; Parmi ses autres ouvrages importants figurent Old and New Concepts of Reality (1932), The Problems of Philosophy of Culture (1938), Man and Culture (1950, traduction de El hombre y la cultura) et History of Modern Philosophy (1959); sa réputation lui valut le surnom de « doyen des philosophes ibéro-américains » et son héritage continue d’être étudié dans les études sur la philosophie latino‑américaine. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H21" r:id="rId13" display="https://www.laphilo.fr/pho/fromero-mini.webp"/>
-    <hyperlink ref="E23" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Susanne_Langer&quot; title=&quot; Wikipedia&quot;&gt;Susanne LANGER&lt;/a&gt; était une philosophe américaine connue pour ses travaux sur le symbole, l’art et la perception. Elle a joué un rôle important dans la philosophie défendant l’idée que la pensée humaine ne se limite pas au langage discursif, mais s’exprime aussi à travers des formes symboliques non verbales, notamment artistiques. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=gwYNyxDTOhQ&quot;   title=&quot; suzanne langer par overthink podcast&quot;&gt;Son œuvre &lt;/a&gt; la plus influente est sans doute Philosophy in a New Key (1942), où elle soutient que l’art n’est pas simplement une décoration ou une émotion brute, mais une forme de connaissance. Pour elle, la musique, la danse, la peinture ou la poésie donnent accès à des structures de sentiment que le langage ordinaire explique mal. Cette idée l’a rendue très importante pour l’esthétique et la théorie des symboles. &lt;/p&gt; &lt;p&gt; Il  s’inscrit dans une tradition marquée par Ernst Cassirer, qui voyait l’être humain comme un animal symbolique. Elle reprend cette intuition en affirmant que l’esprit humain construit le monde au moyen de symboles, et que ces symboles ne sont pas tous de même nature. Elle distingue ainsi les systèmes discursifs, qui avancent par étapes logiques, et les formes présentatives, plus propres à &lt;a href=&quot;https://www.youtube.com/watch?v=BM43-aqdboA&quot;   title=&quot; suzanne langer par philosophy overdose&quot;&gt;l’art et à l’expérience sensible. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Son apport est aussi majeur en philosophie de l’art, car elle refuse de réduire l’œuvre à une simple expression subjective de l’artiste. Au contraire, elle cherche à montrer que l’œuvre organise une forme, un rythme et une structure qui rendent intelligible une expérience affective. Cette approche a eu une influence durable sur l’esthétique, la musique et plusieurs sciences humaines. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="E26" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Herbert_Marcuse&quot;  title=&quot; Wikipedia&quot;&gt;Herbert MARCUSE&lt;/a&gt; était un philosophe germano-américain, figure emblématique de l'École de Francfort et du freudo-marxisme. Né à Berlin dans une famille juive, il a fui &lt;a href=&quot;https://www.nonfiction.fr/article-12550-penser-et-vivre-contre-le-fascisme-avec-herbert-marcuse.htm&quot;  title=&quot;herbert marcuse penser et vivre contre le nfascisme par nonfiction&quot;&gt;l'Allemagne nazie &lt;/a&gt; en 1933 pour s'installer aux États-Unis, où il a travaillé pour l'Institut de recherche sociale et l'Office of Strategic Services pendant la Seconde Guerre mondiale. &lt;/p&gt; &lt;p&gt; Ses premières influences incluent Hegel, Marx, Freud et Heidegger, dont il fut l'assistant à Freiburg. Il a  &lt;a href=&quot;https://www.youtube.com/watch?v=sUjRHvQ6yuY&quot;  title=&quot;herbert marcuse par prneix&quot;&gt;critiqué le capitalisme &lt;/a&gt; avancé et la société de consommation, voyant dans la technologie et la culture de masse des outils de domination subtile. Son engagement politique l'a lié aux mouvements étudiants des années 1960, comme en Mai 68 en France. &lt;/p&gt; &lt;p&gt; Dans Éros et Civilisation (1955), il propose une &quot;sublimation non répressive&quot;, libérant les instincts freudiens des contraintes du principe de performance pour imaginer une société plus érotique et libre. Il dénonce l'aliénation dans les démocraties industrielles, où la liberté formelle masque un contrôle total. Cette œuvre fusionne marxisme et psychanalyse pour critiquer la répression libidinale nécessaire au système productiviste. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1968_num_8_1_3123&quot;  title=&quot;herbert marcuse l’homme unidimentionnel par persée&quot;&gt;L'Homme unidimensionnel &lt;/a&gt; (1964), paru en France en 1968, est son ouvrage le plus célèbre, analysant comment la société d'abondance réduit la pensée critique à une dimension, intégrant les oppositions via la consommation et les médias. Il y voit une &quot;tolérance répressive&quot; qui neutralise la contestation en la récupérant commercialement. Il prône une &quot;grande refus&quot; des marginaux et minorités contre la classe ouvrière intégrée au système. &lt;/p&gt; &lt;p&gt; À la fin de sa vie, professeur en Californie, il reste une icône de la Nouvelle Gauche, influençant hippies et écologistes malgré les critiques sur son utopie. &lt;/p&gt; &lt;audio controls title=&quot;Herbert Marcuse , philosophe de l’espoir par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10471-07.05.1998-ITEMA_23796487-1998C3330E0013-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &#10;&#10;"/>
-    <hyperlink ref="E27" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Paul_Weiss_(philosopher)&quot; title=&quot; Wikipedia&quot;&gt;Paul WEISS&lt;/a&gt; était un philosophe américain connu pour son travail en métaphysique, esthétique, éthique et philosophie sociale, et pour son projet d’une « vision universelle » qui cherche à penser la totalité des réalités concrètes. Il a étudié avec Alfred North Whitehead et Morris Raphael Cohen, a enseigné dans plusieurs universités (notamment Yale) et a fondé la Metaphysical Society of America ainsi que la revue The Review of Metaphysics, contribuant fortement à la vie philosophique américaine du XXe siècle. &lt;/p&gt; &lt;p&gt; Il  est souvent décrit comme un métaphysicien néo-classique et un penseur de processus qui oppose au réductionnisme une réflexion sur les totalités et les finalités; il a proposé une ontologie riche où les entités concrètes, les relations et les valeurs trouvent leur place dans un système englobant. Son œuvre majeure couvre des thèmes très variés — Reality, Modes of Being, The God We Seek, You, I, and the Others — et témoigne   &lt;a href=&quot;https://www.youtube.com/watch?v=hzgN9kCruOE&quot;  title=&quot;Paul Weiss revisited par American Institute of Phlosophy&quot;&gt;d’un intérêt constant &lt;/a&gt; pour la créativité, l’art, la religion et la condition humaine, souvent traité par de vastes collections d’essais et volumes synthétiques. &lt;/p&gt; &lt;p&gt; Il  a défendu une conception qui tient ensemble l’autonomie humaine et l’insertion sociale : la liberté n’est pas pure abstraction mais se réalise dans les contextes institutionnels, moraux et artistiques qui permettent à la personne de se développer vers des fins supérieures. Esthétiquement, il a exploré la nature des arts et de la créativité, soutenant que les actes créatifs manifestent des « ultimates » ou valeurs premières qui orientent l’activité humaine vers des fins non réductibles au pragmatisme scientifique. &lt;/p&gt; &lt;p&gt; Son influence institutionnelle est importante : outre la fondation de sociétés et de revues, Weiss a laissé un corpus vaste (livres, articles, archives) qui a alimenté des débats en métaphysique et en philosophie des arts; il est considéré comme l’un des grands métaphysiciens américains du XXe siècle, reconnu par des volumes comme The Philosophy of Paul Weiss publiés dans la collection Library of Living Philosophers. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H28" r:id="rId17" display="https://www.laphilo.fr/pho/enagel-mini.webp"/>
-    <hyperlink ref="E33" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Leopoldo_Zea_Aguilar&quot; title=&quot; Wikipedia&quot;&gt;Leopoldo ZEA AGUILAR&lt;/a&gt; était un philosophe mexicain , considéré comme l'un des pères fondateurs de la philosophie latino-américaine contemporaine, engagé dans la quête d'une identité culturelle autonome face à l'eurocentrisme et au néocolonialisme. &lt;/p&gt; &lt;p&gt;  Il pose la question centrale : &quot;Peut-on construire une philosophie latino-américaine ?&quot; Réponse affirmative via une dialectique de la conscience : de la dépendance à la libération, où l'homme latino-américain réalise sa liberté par la reconnaissance de sa singularité culturelle. Relativiste culturel sans relativisme absolu, il définit l'homme comme ouvert et pluriel, rejetant l'eurocentrisme comme domination masquée ; la philosophie devient &lt;a href=&quot;https://ensayistas.org/antologia/XXA/zea/zea2.htm&quot; title=&quot;Leopoldo Zea Aguilar | Autopercepción intelectual de un proceso histórico par ensayistas&quot;&gt;&quot;instrument de libération&quot; &lt;/a&gt;, transformant l'histoire en projet éthique-politique de dignité, égalité et solidarité. Précurseur des critiques post-coloniales et postmodernes, il voit 1492 non comme &quot;découverte&quot; mais comme &quot;occultation&quot; culturelle, et la philosophie latino-américaine comme symbiose de nationalisme, christianisme et socialisme anti-impérialiste. &lt;/p&gt; &lt;p&gt; Mentor de générations, il fonde des centres intellectuels en Amérique latine et reçoit des prix mondiaux ; son discours sur la marginalité influence la philosophie de la libération et les études culturelles décoloniales. Il reste &lt;a href=&quot;https://www.youtube.com/watch?v=_kEH9wQFQv4&quot; style=&quot;color:#88A1E9&quot; title=&quot;Leopoldo Zea Aguilar | Doctorado en Educación par Miguel Morales&quot;&gt;une référence &lt;/a&gt; pour une Amérique latine unie, non utopique mais réaliste, affirmant : &quot;Se connaître égal en étant distinct est l'essence des relations humaines et internationales&quot;. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E34" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Roderick_Chisholm&quot;  title=&quot; Wikipedia&quot;&gt;Roderick CHISHOLM&lt;/a&gt; était un philosophe analytique américain reconnu pour ses travaux en épistémologie, métaphysique, philosophie de la conscience et philosophie de la perception. Il a obtenu son doctorat à l'Université de Harvard sous la tutelle de Clarence Irving Lewis et Donald C. Williams, et a enseigné pendant plus de 40 ans à l'Université Brown, après avoir aussi été professeur à Syracuse et à l'Université du Massachusetts à Amherst. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans le platonisme métaphysique de la tradition de Bertrand Russell et le rationalisme de Russell, G.E. Moore et Franz Brentano, dont il a traduit plusieurs œuvres. Il s'est opposé aux conceptions influentes de Willard Van Orman Quine, notamment contre son antiréalisme, comportementalisme et relativisme, défendant plutôt un réalisme métaphysique. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie fondationaliste de la connaissance : toutes les croyances justifiées sont soit « directement évidentes » soit soutenues par des chaînes de croyances justifiées qui finalement conduisent à des croyances directement évidentes. Il a défendu la possibilité du  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1968_num_66_90_5438_t1_0334_0000_3&quot;  title=&quot;Théory of Knowledge  par Persée&quot;&gt;knowledge empirique &lt;/a&gt; en appels à des principes épistémiques a priori, affirmant qu'il est plus raisonnable dans la plupart des situations de se confier aux sens et à la mémoire que de douter d’eux, contre les arguments sceptiques de David Hume. &lt;/p&gt; &lt;p&gt; Sa métaphysique inclut une théorie controversée de l'identité personnelle basée sur la continuité et  &lt;a href=&quot;https://www.youtube.com/watch?v=axFQjuG98AU&quot;  title=&quot;Human freedom and the self par Dillard philosophy&quot;&gt;la coïncidence des propriétés,&lt;/a&gt;  selon laquelle une personne est une substance simple et non décomposable. Il a également défendu une théorie de la volition appelée « agent causation » (causalité de l'agent), similaire à celle de Thomas Reid, et argumenté que le libre arbitre est incompatible avec le déterminisme alors que nous agissons librement - cette combinaison est connue comme  &lt;a href=&quot;https://www.youtube.com/watch?v=qLYgOxb3-E8&quot;  title=&quot;Roderick Chisholm libertarism par Philosophy et Ethics&quot;&gt;libertarianisme métaphysique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il est connu pour son ouvrage majeur Person and Object (1976), dont le titre contraste délibérément avec Word and Object de Quine, et pour sa théorie originale du pensée en première personne où les choses que nous croyons sont propriétés, et les croire est une question d'auto-attribution. Ses autres œuvres importantes incluent Perceiving (1957), Theory of Knowledge (1966, 1977, 1989), The First Person (1981), The Problem of the Criterion, et A Realist Theory of the Categories (1996). Il avait un grand respect pour l'histoire de la philosophie, contrairement à l'indifférence majoritaire des philosophes analytiques, et a contribué au renouveau de la méréologie dans les années 1970. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H34" r:id="rId20" display="https://www.laphilo.fr/pho/rchisholm-mini.webp"/>
-    <hyperlink ref="E35" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_Rawls_(philosophe)&quot;  title=&quot; Wikipedia&quot;&gt;John RAWLS&lt;/a&gt; était un  philosophe politique américain connu grâce à son œuvre majeure &quot;&lt;a href=&quot;https://www.youtube.com/watch?v=OIKwI5qu4y8&quot; style=&quot;color:#88A1E9&quot; title=&quot; La THÉORIE DE LA JUSTICE en 8 minutes ! (John RAWLS) par Culture Philo&quot;&gt; A Theory of Justice&lt;/a&gt;&quot;, publiée en 1971 ou il propose une conception de la  &lt;a href=&quot;https://www.youtube.com/watch?v=2w-AEMAU_EE&quot;  title=&quot; Le libéralisme égalitaire de John Rawls par Philoxime&quot;&gt;&quot;justice comme équité&quot;&lt;/a&gt; . Il s’oppose à l’utilitarisme – doctrine selon laquelle une action est bonne si elle maximise le bonheur collectif – et cherche au contraire à fonder la justice sur des principes garantissant équitablement les libertés et droits fondamentaux pour tous. &lt;/p&gt; &lt;p&gt;  Il imagine une &quot; &lt;a href=&quot;https://www.persee.fr/doc/rfsp_0035-2950_1991_num_41_1_394540&quot;  title=&quot;La Théorie de la justice de John Rawls. Contrat social versus utilitarisme par Persée&quot;&gt;position originelle&lt;/a&gt;&quot;, situation hypothétique où des individus rationnels, placés derrière un « voile d’ignorance » qui leur cache leurs avantages personnels, choisiraient des règles de justice justes pour tous. De cette expérience de pensée, il déduit deux principes essentiels dont le principe d’égale liberté où chaque personne doit avoir un droit égal aux libertés fondamentales et le principe de différence où les inégalités économiques et sociales ne sont justes que si elles profitent aux plus désavantagés.  &lt;/p&gt; &lt;p&gt; Il a ensuite  prolongé sa réflexion dans &quot;Political Liberalism&quot; (1993) et &quot;The Law of Peoples&quot; (1999). Dans le premier, il interroge comment un consensus moral peut se former dans des sociétés pluralistes sans imposer une doctrine particulière ; dans le second, il applique ses principes à la &lt;a href=&quot;https://www.youtube.com/watch?v=ah7y1xd3bL0&quot; title=&quot;JOHN RAWLS : Qu'est-ce que la justice sociale ? par Parole de Philosophe&quot;&gt;justice internationale&lt;/a&gt; . &lt;/p&gt; &lt;p&gt;  Il a profondément marqué la philosophie morale, politique et économique contemporaine et sa pensée inspira la théorie économique critique, avec des débats persistants sur la compatibilité de sa vision avec le libéralisme ou la social-démocratie et il demeure aujourd’hui une référence incontournable pour toute réflexion sur la justice, l’égalité et la démocratie. &lt;/p&gt; &lt;audio controls title=&quot; Avoir raison avec... John Rawls par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-13.07.2020-ITEMA_22381527-2020C35448S0195-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  "/>
-    <hyperlink ref="E36" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Kuhn&quot; title=&quot; Wikipedia&quot;&gt;Thomas KUHN&lt;/a&gt; était un philosophe et historien des sciences américain, célèbre pour son ouvrage  &lt;a href=&quot;https://apprendrelaphilosophie.com/thomas-kuhn-y-a-t-il-des-revolutions-scientifiques/&quot; title=&quot;Kuhn la sctructure des revolutions scientifiques par apprendre la philo&quot;&gt;La Structure des révolutions scientifiques &lt;/a&gt; (1962), l’un des livres les plus influents du XXᵉ siècle en philosophie des sciences. Formé d’abord en physique à Harvard avant de se tourner vers l’histoire et la philosophie des sciences, il a enseigné à Harvard, Berkeley, Princeton et au MIT, et a profondément renouvelé la façon dont on conçoit le progrès scientifique. &lt;/p&gt; &lt;p&gt; Au cœur de sa pensée se trouve le concept de paradigme : un cadre conceptuel partagé par une communauté scientifique, incluant des théories, des méthodes, des expériences canoniques et des normes de résolution de problèmes. Tant  &lt;a href=&quot;https://www.youtube.com/watch?v=_mBS4YbiYcA&quot; title=&quot;Kuhn les paradigmes par le precepteur&quot;&gt;qu’un paradigme domine, &lt;/a&gt; la science fonctionne en mode de « science normale », où les chercheurs résolvent des énigmes à l’intérieur du cadre sans remettre en cause ses fondements. &lt;/p&gt; &lt;p&gt; Il  oppose la science normale à la « science extraordinaire », qui survient quand des anomalies s’accumulent et ébranlent la confiance dans le paradigme dominant. Cela peut mener à une révolution scientifique, c’est-à-dire un changement de paradigme radical : les anciens concepts et méthodes sont abandonnés au profit d’un nouveau cadre inconciliable avec l’ancien. Il explique ainsi que le progrès scientifique n’est pas une accumulation linéaire de connaissances, mais une succession de ruptures révolutionnaires. &lt;/p&gt; &lt;p&gt; Selon lui, les paradigmes successifs ne sont pas toujours comparables de façon neutre : il parle d’« incommensurabilité » entre paradigmes, car leurs concepts, critères de validité et questions légitimes diffèrent profondément. Cela remet en cause l’idée selon laquelle la science progresse uniquement par accumulation objective et rationnelle, indépendante des contextes historiques et sociaux. &lt;/p&gt; &lt;p&gt; Sa philosophie a eu un impact bien au-delà de la science : ses idées sur les paradigmes et les révolutions ont influencé la sociologie, l’économie, les sciences politiques, la gestion et même les sciences humaines. En mettant l’accent sur les dimensions historiques, sociales et communautaires de la science, &lt;a href=&quot;https://www.youtube.com/watch?v=fV-vh9y_TQs&quot; title=&quot;Kuhn speaking par philosophy Overdoser&quot;&gt;il a ouvert la voie &lt;/a&gt;  à une épistémologie plus contextualisée, critique du positivisme logique et de l’idée d’une science totalement neutre et objective. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E37" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/John_B._Cobb&quot;  title=&quot; Wikipedia&quot;&gt;John B. COBB&lt;/a&gt; était un philosophe américain,  figure majeure de la philosophie et de la théologie du process, inspirée par Alfred North Whitehead. Issu d'une famille de missionnaires méthodistes au Japon, il a développé une vision panenthéiste où Dieu est à la fois immanent dans le monde et &lt;a href=&quot;https://books.openedition.org/pum/42552?lang=fr&quot; title=&quot;Réflexions en marge d’un livre de John B. Cobb par OpenEdition&quot;&gt;transcendant, &lt;/a&gt;  influençant profondément les débats sur l'écologie, l'économie durable et le pluralisme religieux. Son œuvre, comptant plus de 50 livres, met l'accent sur l'interdépendance de tous les êtres et la nécessité d'une éthique écologique. &lt;/p&gt; p&gt; Il rejette le théisme classique en affirmant que Dieu évolue avec les créatures, ressent leurs souffrances et n'a pas une prescience absolue des événements futurs, préservant ainsi la liberté humaine. Sa théologie &lt;a href=&quot;https://www.youtube.com/watch?v=ArXAjOlufZs&quot; title=&quot;&#10;John Cobb - Pluralisme religieux : une discussion sur le christianisme transformatif de John Cobb par Center for Process Studies&quot;&gt;du process &lt;/a&gt; voit une valeur intrinsèque en toute chose, y compris les particules comme l'électron, et critique l'anthropocentrisme chrétien traditionnel. Il intègre l'évolution comme un processus de hasard et de nécessité, influencé par Jacques Monod, tout en défendant un monde &quot;originellement bon&quot; dégradé par l'humanité. &lt;/p&gt; &lt;p&gt; Pionnier de l'éthique environnementale, il publie en 1971 &quot;Is It Too Late? A Theology of Ecology&quot;, premier ouvrage individuel sur le sujet, plaidant pour une vision écologique du christianisme. Avec Charles Birch, il coécrit &quot;The Liberation of Life&quot; en 1981, promouvant un modèle écologique contre le mécanisme biologique. &lt;/p&gt; &lt;p&gt;   Il influencera la Chine via ses idées sur la civilisation écologique et est élu en 2014 à l'Académie américaine des arts et des sciences. Il fonde aussi &quot;Progressive Christians Uniting&quot; pour une foi progressiste et engagée socialement. &lt;/p&gt; "/>
-    <hyperlink ref="E39" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Stanley_Cavell&quot;  title=&quot; Wikipedia&quot;&gt;Stanley CAVELL&lt;/a&gt; était un philosophe américain connu pour avoir renouvelé la philosophie du langage ordinaire, la philosophie morale et l’esthétique, notamment à partir de Wittgenstein, Austin, Emerson, Thoreau et du cinéma hollywoodien. Sa pensée est moins centrée sur des systèmes que sur une réflexion vivante sur l’ordinaire, le scepticisme, la voix personnelle et la manière dont la philosophie peut parler à partir de &lt;a href=&quot;https://www.youtube.com/watch?v=bWMncAAj16c&quot; title=&quot; Stanley Cavell par Film &amp; media&quot;&gt;l’expérience vécue. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Il s’intéresse d’abord au langage quotidien, parce qu’il pense que les difficultés philosophiques ne viennent pas seulement d’un manque d’informations, mais d’un trouble plus profond dans notre rapport au monde et aux autres. Pour lui, &lt;a href=&quot;https://www.youtube.com/watch?v=5q50IwBAUKY&quot; title=&quot; Stanley Cavell par philo overdose&quot;&gt;le scepticisme &lt;/a&gt; n’est pas seulement un problème de connaissance, c’est aussi une expérience humaine et parfois tragique : nous pouvons nous sentir séparés du monde, d’autrui, voire de nous-mêmes. &lt;/p&gt; &lt;p&gt; Un thème central chez lui est donc la reconnaissance. Il ne s’agit pas simplement de « savoir » que l’autre existe, mais d’apprendre à le reconnaître, à répondre à sa présence, et à accepter que nos relations humaines comportent toujours une part d’incertitude. C’est pourquoi Cavell relie souvent la philosophie à l’éthique, à la vie quotidienne et aux formes concrètes de l’attention aux autres. &lt;/p&gt; &lt;p&gt; Il est aussi célèbre pour son travail sur le cinéma, qu’il ne considère pas comme un divertissement secondaire mais comme un véritable lieu de pensée. À travers les comédies hollywoodiennes, notamment les « comédies de remariage », il explore des questions de couple, de séparation, de pardon et de seconde chance, c’est-à-dire des problèmes philosophiques aussi bien que narratifs.  &lt;/p&gt; &lt;p&gt; Il est lié à une idée très américaine de la philosophie : une philosophie qui n’oppose pas rigidement le savant et le populaire, qui peut être autobiographique, littéraire et morale à la fois. Son originalité tient à cela : il transforme la philosophie en une &lt;a href=&quot;https://www.liberation.fr/debats/2018/06/20/stanley-cavell-the-end_1660627/&quot; title=&quot; Stanley Cavell par liberation&quot;&gt; enquête sur la vie &lt;/a&gt; ordinaire, les formes de notre voix, et la possibilité de devenir plus juste envers soi-même et envers les autres.  &lt;/p&gt; &#10;&lt;audio controls title=&quot;la pensée américaine Stanley Cavell par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-05.11.2012-ITEMA_20417072-2012C12410S0310-NET_B1E428CD-7648-4739-933D-4C419F0B94C8_FC-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &#10;"/>
-    <hyperlink ref="H39" r:id="rId25" display="https://www.laphilo.fr/pho/scavell-mini.webp"/>
-    <hyperlink ref="H40" r:id="rId26" display="https://www.laphilo.fr/pho/mrothbard-mini.webp"/>
-    <hyperlink ref="H41" r:id="rId27" display="https://www.laphilo.fr/pho/ewiesel-mini.webp"/>
-    <hyperlink ref="H42" r:id="rId28" display="https://www.laphilo.fr/pho/abracken-mini.webp"/>
-    <hyperlink ref="E43" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Rorty&quot; title=&quot; Wikipedia&quot;&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href=&quot;https://www.youtube.com/watch?v=lfx4Jag1ic4&quot;  title=&quot;Le pragmatisme : définition, exemples par le savoir partagé&quot;&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href=&quot;https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism&quot; title=&quot; a bas l'autorité par laviedesidees&quot;&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas &quot;vrais&quot; ou &quot;faux&quot;. &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales , on trouve  &lt;a href=&quot;https://www.youtube.com/watch?v=MgU0dXZ3umM&quot; title=&quot;L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli&quot;&gt;&quot; Contingence, ironie et solidarité &quot;&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans &quot; Achieving Our Country&quot; (1998),  il y appelle la gauche américaine à abandonner le &quot;culturalisme&quot; pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la &quot;post-vérité&quot;. Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; "/>
-    <hyperlink ref="E45" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Charles_Parsons_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Charles Dacre PARSONS&lt;/a&gt; était un philosophe américain connu pour ses travaux en philosophie des mathématiques et en philosophie de Kant. Il a enseigné à Columbia puis à Harvard, où il est devenu professeur émérite. Il s’est formé à Harvard, avec une thèse dirigée par Willard Van Orman Quine, ce qui le place au croisement de la logique, de la philosophie analytique et des fondements des mathématiques. Son parcours intellectuel a été marqué très tôt par la rigueur mathématique, puisqu’il avait d’abord étudié les mathématiques avant de se tourner vers la philosophie. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la philosophie des mathématiques, domaine dans lequel il a travaillé sur la nature des objets mathématiques, la logique, la preuve et l’interprétation constructive des mathématiques prédicatives. Il a aussi beaucoup écrit sur Frege, Gödel, Hilbert et Quine, en lisant ces auteurs à la fois comme philosophes et comme figures majeures des fondements. &lt;/p&gt; &lt;p&gt; Il n’était pas seulement un spécialiste de logique ; il a aussi produit des travaux importants sur Kant, montrant comment les questions de connaissance, d’expérience et de structure de l’esprit se relient aux mathématiques. Cette double compétence, en philosophie des mathématiques et en histoire de la philosophie, explique pourquoi il est souvent vu comme un auteur à la fois technique et très large dans ses intérêts.&lt;/p&gt; &lt;p&gt; Son influence est restée forte dans le monde anglophone, au point d’être décrit comme l’un des philosophes des mathématiques les plus importants de sa génération. En plus de ses livres et articles, il a aussi contribué à l’édition de textes posthumes de Gödel, ce qui a renforcé son rôle dans l’étude contemporaine des fondements des mathématiques. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="I45" r:id="rId31" display="https://www.laphilo.fr/photo/cparsons.webp"/>
-    <hyperlink ref="H47" r:id="rId32" display="https://www.laphilo.fr/pho/dihde-mini.webp"/>
-    <hyperlink ref="E49" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edward_Sa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Edward SAÏD&lt;/a&gt; était un intellectuel palestinien-américain, critique littéraire et professeur de littérature anglaise et comparée à l’université Columbia de New York. D’origine palestinienne et né à Jérusalem, il a grandi entre l’Égypte, les États-Unis et l’Europe, une expérience de déplacement qui a profondément marqué sa pensée sur l’identité, la colonisation et l’altérité.  &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est l’essai &lt;a href=&quot;https://www.youtube.com/watch?v=Ne4WRykmjhA&quot; title=&quot;Edward Said  Orientalisme par HD Doc&quot;&gt;L’Orientalisme : &lt;/a&gt;  L’Orient créé par l’Occident* (1978), considéré comme le texte fondateur des postcolonial studies. Dans cet ouvrage, Saïd montre que l’« Orient » n’est pas une réalité objective mais une invention de l’Occident : un discours façonné par des siècles de domination coloniale pour mieux contrôler et représenter l’Autre. &lt;/p&gt; &lt;p&gt; Pour lui, l’orientalisme est à la fois un savoir et un outil de pouvoir : il ne s’agit pas seulement de décrire l’Orient, mais de le hiérarchiser, de l’essentialiser et de le rendre  &lt;a href=&quot;https://www.youtube.com/watch?v=QBj-yWLnayM&quot; title=&quot;Edward Said writings on Orientalism par Middle East Eye&quot;&gt; inférieur à l’Occident. &lt;/a&gt; Il analyse quatre thèses principales : la domination politique et culturelle de l’Orient par l’Occident, la dépréciation de la langue arabe, la diabolisation de l’arabe et de l’islam, et la défense de la cause palestinienne. &lt;/p&gt; &lt;p&gt; Sa pensée articule critique littéraire, histoire, philosophie et sciences politiques, en s’inspirant notamment de Michel Foucault (discours–pouvoir) et de Jacques Derrida (déconstruction). Il montre que la violence du colonialisme n’est pas seulement matérielle (conquête, pillage), mais aussi épistémique : une violence de la raison qui classe, essentialise et dévalue les « Autres » de l’Occident. &lt;/p&gt; &lt;p&gt;  Intéressé par &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Edward-W-Said-1935-2003.html&quot; title=&quot;Edward Said par lesclesdumoyenorient&quot;&gt; l’engagement politique, &lt;/a&gt; il a aussi défendu la cause palestinienne et la légitimité des revendications d’autodétermination du peuple palestinien, tout en reconnaissance du droit à une patrie juive. Il rejetait le repli identitaire et prônait une vision universelle qui défend les différences et les droits, tissant des liens entre classicisme et excentricité, histoire et actualité. &lt;/p&gt;  &lt;audio controls title=&quot;Edward Said, une conscience morale par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-08.12.2017-ITEMA_21518070-2017C19327S0342-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &#10;&#10;&#10;"/>
-    <hyperlink ref="H49" r:id="rId34" display="https://laphilo.fr/pho/esaid-mini.webp"/>
-    <hyperlink ref="H50" r:id="rId35" display="https://www.laphilo.fr/pho/rmadams-mini.webp"/>
-    <hyperlink ref="E51" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Nozick&quot;  title=&quot; Wikipedia&quot;&gt;Robert NOZICK&lt;/a&gt; était un philosophe américain connu pour &lt;a href=&quot;https://www.youtube.com/watch?v=Q-t3cpFAk4o&quot;  title=&quot; Libertarianisme par Vadim Media&quot;&gt; son libertarianisme &lt;/a&gt; et sa critique des théories égalitaristes comme celle de John Rawls. Professeur à Harvard, il a marqué la philosophie politique, morale et épistémologique par son œuvre principale, Anarchie, État et utopie (1974), qui défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Minarchisme&quot;  title=&quot; Minarchisme par Wikipédia&quot;&gt; Etat Minimal. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il argue que seul l'État minimal, ou &quot;État gardien de nuit&quot;, est légitime, car il se limite à protéger les individus contre la force, la fraude et le vol, sans redistribuer les richesses. Il rejette l'anarcho-capitalisme en montrant, via des agences de protection privée, comment un État dominant émerge naturellement pour monopoliser la coercition légitime, justifié par le droit naturel à la personne. &lt;/p&gt; &lt;p&gt; Contrairement à la justice distributive de Rawls, il propose une théorie de l'entitlement : une acquisition initiale juste et des transferts volontaires rendent la distribution légitime, sans besoin d'égalisation par l'État. Toute intervention redistributive viole les droits individuels, traitant les personnes comme des moyens plutôt que des fins, en écho à Kant. &lt;/p&gt; &lt;p&gt; Dans Anarchie, État et utopie, Il réfute l'utilitarisme via l'expérience de pensée de la &lt;a href=&quot;https://www.youtube.com/watch?v=2FVwXaNWPQ0&quot;  title=&quot; La machine à expérience par Monsieur Phi&quot;&gt;&quot;machine à expérience&quot; :&lt;/a&gt;  même si elle offre un bonheur parfait et indistinguable de la réalité, les gens préfèrent vivre des actions réelles et façonner leur identité plutôt que des simulations. Cela prouve que le bonheur n'est pas le seul bien suprême. &lt;/p&gt; &lt;p&gt; Plus tard, dans Explications philosophiques (1981), il développe une théorie du suivi (tracking theory) en épistémologie, où la connaissance repose sur des conditionnels contrefactuels fiables, contournant le scepticisme sans justification traditionnelle. Son anti-coercitivisme intellectuel invite à une philosophie ouverte, non imposée. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Qui a peur des Libertariens par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-14.06.2022-ITEMA_23058436-2022C12410S0165-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;"/>
-    <hyperlink ref="H57" r:id="rId37" display="https://www.laphilo.fr/pho/imyoung-mini.webp"/>
-    <hyperlink ref="H58" r:id="rId38" display="https://www.laphilo.fr/pho/bhooks-mini.webp"/>
+    <hyperlink ref="E19" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Antonio_Caso&quot;   title=&quot; Wikipedia&quot;&gt;Antonio CASO&lt;/a&gt; était un philosophe mexicain connu pour sa critique du positivisme et pour un  &lt;a href=&quot;https://www.youtube.com/watch?v=YlEoF2CNNxA&quot; title=&quot;&quot;Antonio Caso Andrade - Filósofo y Sociológico Mexicano - Una Mirada Profunda a sus Contribuciones&quot; par Biografías de Filósofos&quot;&gt;humanisme spiritualiste &lt;/a&gt; influent dans la culture intellectuelle mexicaine. Il cofonde en 1910, avec José Vasconcelos et d’autres, l’Ateneo de la Juventud, cercle intellectuel qui s’oppose au positivisme dominant dans le Mexique porfirien. Il défend un christianisme philosophique libéral inspiré notamment de Blaise Pascal et de Tolstoï, mettant en avant la liberté, la vie intérieure et la dimension spirituelle de l’être humain. &lt;/p&gt; &lt;p&gt; Son ouvrage clé,  &lt;a href=&quot;https://filosofiamexicana.org/2013/06/24/la-existencia-como-economia-como-desinteres-y-como-caridad-resena/&quot; title=&quot;La existencia como economía como desinterés y como caridad. par filofiaexicana&quot;&gt;&quot;La existencia como economía, como desinterés y como caridad&quot; &lt;/a&gt; paru en 1916, propose une anthropologie où l’existence humaine se déploie en trois niveaux: l’économie (survie, utilité), le désintéressement (contemplation) et la charité ou amour. Dans cette perspective, il distingue choses, individus et personnes, en attribuant aux personnes la capacité de désintéressement et d’amour, c’est‑à‑dire de créer des valeurs et de dépasser l’égoïsme. &lt;/p&gt; &lt;p&gt; Sa métaphysique met l’accent sur le processus, la liberté, la vie et l’esprit: la réalité est pour lui un dynamisme fluide que le schéma logique traditionnel (sujet‑prédicat) fige et déforme. Il s’inspire surtout d’Henri Bergson, mais aussi de Kant, Schopenhauer, Nietzsche et plus tard Husserl, dont il commente la phénoménologie dans ses écrits tardifs sur la personne humaine et l’État totalitaire. &lt;/p&gt; &lt;p&gt; Il est considéré comme un précurseur de la sociologie au Mexique: il crée la chaire de sociologie à l’université et publie &quot;Sociología genética y sistemática&quot; paru en 1922 puis un manuel de Sociología en 1940, très utilisé dans les universités mexicaines. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E20" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alfonso_Reyes&quot;  title=&quot; Wikipedia&quot;&gt;Alfonso REYES&lt;/a&gt; était un écrivain et philosophe &amp; diplomate  mexicain, souvent considéré comme l’un des grands humanistes de la langue espagnole au XXe siècle.  &lt;a href=&quot;https://www.persee.fr/doc/hispa_0007-4640_1960_num_62_1_3655&quot;  title=&quot; Alfonso Reyes par Persée&quot;&gt;Sa pensée &lt;/a&gt; philosophique est inséparable de son travail d’essayiste, de critique littéraire et de médiateur entre les cultures européennes et latino‑américaines. &lt;/p&gt; &lt;p&gt; Son premier livre important, &quot;Cuestiones estéticas&quot; paru en  1911 est une série de réflexions sur l’esthétique et la critique littéraire, où il articule déjà l’idée que l’expérience artistique est une forme de connaissance privilégiée du monde. Il donne des conférences sur l’&quot;esthétique classique&quot;, qui influenceront durablement l’orientation intellectuelle mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Il n’est pas un philosophe systématique au sens académique, mais un humaniste qui pense la littérature, l’histoire et le mythe comme voies d’accès à la réalité et à l’identité mexicaine et latino‑américaine. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &lt;a href=&quot;https://www.youtube.com/watch?v=IeZKZ6PC9H4&quot;  title=&quot; Visión de Anáhuac de Alfonso Reyes par Literatubers&quot;&gt;&quot;Visión de Anáhuac&quot; &lt;/a&gt;  , il propose une méditation poétique et historique sur le Mexique préhispanique et la Conquête, en insistant sur la continuité d’une sensibilité mexicaine à travers les siècles. &lt;/p&gt; &lt;p&gt; Il défend une conception de l’homme formé par les lettres, la philosophie et les sciences, contre les réductions technocratiques ou purement utilitaires du savoir et pense l’Amérique latine comme espace de synthèse entre héritages indigènes, hispaniques et européens, et fait de la traduction et de la critique des instruments de ce dialogue. &lt;/p&gt;"/>
+    <hyperlink ref="E22" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Francisco ROMERO&lt;/a&gt; était un philosophe argentin d’origine espagnole, professeur à l’Université de Buenos Aires et à La Plata, et une figure centrale de la réaction  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ib%C3%A9ro-Am%C3%A9rique&quot;  title=&quot;ibéro-amérique par wikipedia&quot;&gt; ibéro-américaine &lt;/a&gt; contre le positivisme dominant au début du XXe siècle. &lt;/p&gt; &lt;p&gt; Sa production philosophique couvre l’épistémologie, la philosophie de la culture et l’anthropologie philosophique ; son ouvrage majeur en langue espagnole, Teoría del hombre (1952), propose une réflexion systématique sur la condition humaine, la liberté et la créativité culturelle, et a été traduit en anglais sous le titre Theory of Man.https://en.wikipedia.org/wiki/Francisco_Romero_(philosopher) &lt;/p&gt; &lt;p&gt; Il  prit position contre  &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9ductionnisme&quot;  title=&quot;Reductionnisme par wikipedia&quot;&gt; le réductionnisme scientiste &lt;/a&gt; en défendant l’idée que la culture et les créations humaines (art, religion, langage) exigent des méthodes et des concepts propres, distincts des instruments des sciences naturelles ; il chercha donc à articuler rigueur philosophique et sensibilité littéraire. &lt;/p&gt; &lt;p&gt; ur le plan méthodologique, il promut une philosophie qui dialogue avec l’histoire des idées et avec les problèmes concrets de la société ibéro-américaine : ses travaux montrent un intérêt marqué pour la responsabilité sociale des intellectuels et pour la formation culturelle des peuples. &lt;/p&gt; &lt;p&gt; Parmi ses autres ouvrages importants figurent Old and New Concepts of Reality (1932), The Problems of Philosophy of Culture (1938), Man and Culture (1950, traduction de El hombre y la cultura) et History of Modern Philosophy (1959); sa réputation lui valut le surnom de « doyen des philosophes ibéro-américains » et son héritage continue d’être étudié dans les études sur la philosophie latino‑américaine. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H22" r:id="rId13" display="https://www.laphilo.fr/pho/fromero-mini.webp"/>
+    <hyperlink ref="E24" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Susanne_Langer&quot; title=&quot; Wikipedia&quot;&gt;Susanne LANGER&lt;/a&gt; était une philosophe américaine connue pour ses travaux sur le symbole, l’art et la perception. Elle a joué un rôle important dans la philosophie défendant l’idée que la pensée humaine ne se limite pas au langage discursif, mais s’exprime aussi à travers des formes symboliques non verbales, notamment artistiques. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=gwYNyxDTOhQ&quot;   title=&quot; suzanne langer par overthink podcast&quot;&gt;Son œuvre &lt;/a&gt; la plus influente est sans doute Philosophy in a New Key (1942), où elle soutient que l’art n’est pas simplement une décoration ou une émotion brute, mais une forme de connaissance. Pour elle, la musique, la danse, la peinture ou la poésie donnent accès à des structures de sentiment que le langage ordinaire explique mal. Cette idée l’a rendue très importante pour l’esthétique et la théorie des symboles. &lt;/p&gt; &lt;p&gt; Il  s’inscrit dans une tradition marquée par Ernst Cassirer, qui voyait l’être humain comme un animal symbolique. Elle reprend cette intuition en affirmant que l’esprit humain construit le monde au moyen de symboles, et que ces symboles ne sont pas tous de même nature. Elle distingue ainsi les systèmes discursifs, qui avancent par étapes logiques, et les formes présentatives, plus propres à &lt;a href=&quot;https://www.youtube.com/watch?v=BM43-aqdboA&quot;   title=&quot; suzanne langer par philosophy overdose&quot;&gt;l’art et à l’expérience sensible. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Son apport est aussi majeur en philosophie de l’art, car elle refuse de réduire l’œuvre à une simple expression subjective de l’artiste. Au contraire, elle cherche à montrer que l’œuvre organise une forme, un rythme et une structure qui rendent intelligible une expérience affective. Cette approche a eu une influence durable sur l’esthétique, la musique et plusieurs sciences humaines. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="E27" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Herbert_Marcuse&quot;  title=&quot; Wikipedia&quot;&gt;Herbert MARCUSE&lt;/a&gt; était un philosophe germano-américain, figure emblématique de l'École de Francfort et du freudo-marxisme. Né à Berlin dans une famille juive, il a fui &lt;a href=&quot;https://www.nonfiction.fr/article-12550-penser-et-vivre-contre-le-fascisme-avec-herbert-marcuse.htm&quot;  title=&quot;herbert marcuse penser et vivre contre le nfascisme par nonfiction&quot;&gt;l'Allemagne nazie &lt;/a&gt; en 1933 pour s'installer aux États-Unis, où il a travaillé pour l'Institut de recherche sociale et l'Office of Strategic Services pendant la Seconde Guerre mondiale. &lt;/p&gt; &lt;p&gt; Ses premières influences incluent Hegel, Marx, Freud et Heidegger, dont il fut l'assistant à Freiburg. Il a  &lt;a href=&quot;https://www.youtube.com/watch?v=sUjRHvQ6yuY&quot;  title=&quot;herbert marcuse par prneix&quot;&gt;critiqué le capitalisme &lt;/a&gt; avancé et la société de consommation, voyant dans la technologie et la culture de masse des outils de domination subtile. Son engagement politique l'a lié aux mouvements étudiants des années 1960, comme en Mai 68 en France. &lt;/p&gt; &lt;p&gt; Dans Éros et Civilisation (1955), il propose une &quot;sublimation non répressive&quot;, libérant les instincts freudiens des contraintes du principe de performance pour imaginer une société plus érotique et libre. Il dénonce l'aliénation dans les démocraties industrielles, où la liberté formelle masque un contrôle total. Cette œuvre fusionne marxisme et psychanalyse pour critiquer la répression libidinale nécessaire au système productiviste. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1968_num_8_1_3123&quot;  title=&quot;herbert marcuse l’homme unidimentionnel par persée&quot;&gt;L'Homme unidimensionnel &lt;/a&gt; (1964), paru en France en 1968, est son ouvrage le plus célèbre, analysant comment la société d'abondance réduit la pensée critique à une dimension, intégrant les oppositions via la consommation et les médias. Il y voit une &quot;tolérance répressive&quot; qui neutralise la contestation en la récupérant commercialement. Il prône une &quot;grande refus&quot; des marginaux et minorités contre la classe ouvrière intégrée au système. &lt;/p&gt; &lt;p&gt; À la fin de sa vie, professeur en Californie, il reste une icône de la Nouvelle Gauche, influençant hippies et écologistes malgré les critiques sur son utopie. &lt;/p&gt; &lt;audio controls title=&quot;Herbert Marcuse , philosophe de l’espoir par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10471-07.05.1998-ITEMA_23796487-1998C3330E0013-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &#10;&#10;"/>
+    <hyperlink ref="E28" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Paul_Weiss_(philosopher)&quot; title=&quot; Wikipedia&quot;&gt;Paul WEISS&lt;/a&gt; était un philosophe américain connu pour son travail en métaphysique, esthétique, éthique et philosophie sociale, et pour son projet d’une « vision universelle » qui cherche à penser la totalité des réalités concrètes. Il a étudié avec Alfred North Whitehead et Morris Raphael Cohen, a enseigné dans plusieurs universités (notamment Yale) et a fondé la Metaphysical Society of America ainsi que la revue The Review of Metaphysics, contribuant fortement à la vie philosophique américaine du XXe siècle. &lt;/p&gt; &lt;p&gt; Il  est souvent décrit comme un métaphysicien néo-classique et un penseur de processus qui oppose au réductionnisme une réflexion sur les totalités et les finalités; il a proposé une ontologie riche où les entités concrètes, les relations et les valeurs trouvent leur place dans un système englobant. Son œuvre majeure couvre des thèmes très variés — Reality, Modes of Being, The God We Seek, You, I, and the Others — et témoigne   &lt;a href=&quot;https://www.youtube.com/watch?v=hzgN9kCruOE&quot;  title=&quot;Paul Weiss revisited par American Institute of Phlosophy&quot;&gt;d’un intérêt constant &lt;/a&gt; pour la créativité, l’art, la religion et la condition humaine, souvent traité par de vastes collections d’essais et volumes synthétiques. &lt;/p&gt; &lt;p&gt; Il  a défendu une conception qui tient ensemble l’autonomie humaine et l’insertion sociale : la liberté n’est pas pure abstraction mais se réalise dans les contextes institutionnels, moraux et artistiques qui permettent à la personne de se développer vers des fins supérieures. Esthétiquement, il a exploré la nature des arts et de la créativité, soutenant que les actes créatifs manifestent des « ultimates » ou valeurs premières qui orientent l’activité humaine vers des fins non réductibles au pragmatisme scientifique. &lt;/p&gt; &lt;p&gt; Son influence institutionnelle est importante : outre la fondation de sociétés et de revues, Weiss a laissé un corpus vaste (livres, articles, archives) qui a alimenté des débats en métaphysique et en philosophie des arts; il est considéré comme l’un des grands métaphysiciens américains du XXe siècle, reconnu par des volumes comme The Philosophy of Paul Weiss publiés dans la collection Library of Living Philosophers. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H29" r:id="rId17" display="https://www.laphilo.fr/pho/enagel-mini.webp"/>
+    <hyperlink ref="E34" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Leopoldo_Zea_Aguilar&quot; title=&quot; Wikipedia&quot;&gt;Leopoldo ZEA AGUILAR&lt;/a&gt; était un philosophe mexicain , considéré comme l'un des pères fondateurs de la philosophie latino-américaine contemporaine, engagé dans la quête d'une identité culturelle autonome face à l'eurocentrisme et au néocolonialisme. &lt;/p&gt; &lt;p&gt;  Il pose la question centrale : &quot;Peut-on construire une philosophie latino-américaine ?&quot; Réponse affirmative via une dialectique de la conscience : de la dépendance à la libération, où l'homme latino-américain réalise sa liberté par la reconnaissance de sa singularité culturelle. Relativiste culturel sans relativisme absolu, il définit l'homme comme ouvert et pluriel, rejetant l'eurocentrisme comme domination masquée ; la philosophie devient &lt;a href=&quot;https://ensayistas.org/antologia/XXA/zea/zea2.htm&quot; title=&quot;Leopoldo Zea Aguilar | Autopercepción intelectual de un proceso histórico par ensayistas&quot;&gt;&quot;instrument de libération&quot; &lt;/a&gt;, transformant l'histoire en projet éthique-politique de dignité, égalité et solidarité. Précurseur des critiques post-coloniales et postmodernes, il voit 1492 non comme &quot;découverte&quot; mais comme &quot;occultation&quot; culturelle, et la philosophie latino-américaine comme symbiose de nationalisme, christianisme et socialisme anti-impérialiste. &lt;/p&gt; &lt;p&gt; Mentor de générations, il fonde des centres intellectuels en Amérique latine et reçoit des prix mondiaux ; son discours sur la marginalité influence la philosophie de la libération et les études culturelles décoloniales. Il reste &lt;a href=&quot;https://www.youtube.com/watch?v=_kEH9wQFQv4&quot; style=&quot;color:#88A1E9&quot; title=&quot;Leopoldo Zea Aguilar | Doctorado en Educación par Miguel Morales&quot;&gt;une référence &lt;/a&gt; pour une Amérique latine unie, non utopique mais réaliste, affirmant : &quot;Se connaître égal en étant distinct est l'essence des relations humaines et internationales&quot;. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E35" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Roderick_Chisholm&quot;  title=&quot; Wikipedia&quot;&gt;Roderick CHISHOLM&lt;/a&gt; était un philosophe analytique américain reconnu pour ses travaux en épistémologie, métaphysique, philosophie de la conscience et philosophie de la perception. Il a obtenu son doctorat à l'Université de Harvard sous la tutelle de Clarence Irving Lewis et Donald C. Williams, et a enseigné pendant plus de 40 ans à l'Université Brown, après avoir aussi été professeur à Syracuse et à l'Université du Massachusetts à Amherst. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans le platonisme métaphysique de la tradition de Bertrand Russell et le rationalisme de Russell, G.E. Moore et Franz Brentano, dont il a traduit plusieurs œuvres. Il s'est opposé aux conceptions influentes de Willard Van Orman Quine, notamment contre son antiréalisme, comportementalisme et relativisme, défendant plutôt un réalisme métaphysique. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie fondationaliste de la connaissance : toutes les croyances justifiées sont soit « directement évidentes » soit soutenues par des chaînes de croyances justifiées qui finalement conduisent à des croyances directement évidentes. Il a défendu la possibilité du  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1968_num_66_90_5438_t1_0334_0000_3&quot;  title=&quot;Théory of Knowledge  par Persée&quot;&gt;knowledge empirique &lt;/a&gt; en appels à des principes épistémiques a priori, affirmant qu'il est plus raisonnable dans la plupart des situations de se confier aux sens et à la mémoire que de douter d’eux, contre les arguments sceptiques de David Hume. &lt;/p&gt; &lt;p&gt; Sa métaphysique inclut une théorie controversée de l'identité personnelle basée sur la continuité et  &lt;a href=&quot;https://www.youtube.com/watch?v=axFQjuG98AU&quot;  title=&quot;Human freedom and the self par Dillard philosophy&quot;&gt;la coïncidence des propriétés,&lt;/a&gt;  selon laquelle une personne est une substance simple et non décomposable. Il a également défendu une théorie de la volition appelée « agent causation » (causalité de l'agent), similaire à celle de Thomas Reid, et argumenté que le libre arbitre est incompatible avec le déterminisme alors que nous agissons librement - cette combinaison est connue comme  &lt;a href=&quot;https://www.youtube.com/watch?v=qLYgOxb3-E8&quot;  title=&quot;Roderick Chisholm libertarism par Philosophy et Ethics&quot;&gt;libertarianisme métaphysique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il est connu pour son ouvrage majeur Person and Object (1976), dont le titre contraste délibérément avec Word and Object de Quine, et pour sa théorie originale du pensée en première personne où les choses que nous croyons sont propriétés, et les croire est une question d'auto-attribution. Ses autres œuvres importantes incluent Perceiving (1957), Theory of Knowledge (1966, 1977, 1989), The First Person (1981), The Problem of the Criterion, et A Realist Theory of the Categories (1996). Il avait un grand respect pour l'histoire de la philosophie, contrairement à l'indifférence majoritaire des philosophes analytiques, et a contribué au renouveau de la méréologie dans les années 1970. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H35" r:id="rId20" display="https://www.laphilo.fr/pho/rchisholm-mini.webp"/>
+    <hyperlink ref="E36" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_Rawls_(philosophe)&quot;  title=&quot; Wikipedia&quot;&gt;John RAWLS&lt;/a&gt; était un  philosophe politique américain connu grâce à son œuvre majeure &quot;&lt;a href=&quot;https://www.youtube.com/watch?v=OIKwI5qu4y8&quot; style=&quot;color:#88A1E9&quot; title=&quot; La THÉORIE DE LA JUSTICE en 8 minutes ! (John RAWLS) par Culture Philo&quot;&gt; A Theory of Justice&lt;/a&gt;&quot;, publiée en 1971 ou il propose une conception de la  &lt;a href=&quot;https://www.youtube.com/watch?v=2w-AEMAU_EE&quot;  title=&quot; Le libéralisme égalitaire de John Rawls par Philoxime&quot;&gt;&quot;justice comme équité&quot;&lt;/a&gt; . Il s’oppose à l’utilitarisme – doctrine selon laquelle une action est bonne si elle maximise le bonheur collectif – et cherche au contraire à fonder la justice sur des principes garantissant équitablement les libertés et droits fondamentaux pour tous. &lt;/p&gt; &lt;p&gt;  Il imagine une &quot; &lt;a href=&quot;https://www.persee.fr/doc/rfsp_0035-2950_1991_num_41_1_394540&quot;  title=&quot;La Théorie de la justice de John Rawls. Contrat social versus utilitarisme par Persée&quot;&gt;position originelle&lt;/a&gt;&quot;, situation hypothétique où des individus rationnels, placés derrière un « voile d’ignorance » qui leur cache leurs avantages personnels, choisiraient des règles de justice justes pour tous. De cette expérience de pensée, il déduit deux principes essentiels dont le principe d’égale liberté où chaque personne doit avoir un droit égal aux libertés fondamentales et le principe de différence où les inégalités économiques et sociales ne sont justes que si elles profitent aux plus désavantagés.  &lt;/p&gt; &lt;p&gt; Il a ensuite  prolongé sa réflexion dans &quot;Political Liberalism&quot; (1993) et &quot;The Law of Peoples&quot; (1999). Dans le premier, il interroge comment un consensus moral peut se former dans des sociétés pluralistes sans imposer une doctrine particulière ; dans le second, il applique ses principes à la &lt;a href=&quot;https://www.youtube.com/watch?v=ah7y1xd3bL0&quot; title=&quot;JOHN RAWLS : Qu'est-ce que la justice sociale ? par Parole de Philosophe&quot;&gt;justice internationale&lt;/a&gt; . &lt;/p&gt; &lt;p&gt;  Il a profondément marqué la philosophie morale, politique et économique contemporaine et sa pensée inspira la théorie économique critique, avec des débats persistants sur la compatibilité de sa vision avec le libéralisme ou la social-démocratie et il demeure aujourd’hui une référence incontournable pour toute réflexion sur la justice, l’égalité et la démocratie. &lt;/p&gt; &lt;audio controls title=&quot; Avoir raison avec... John Rawls par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-13.07.2020-ITEMA_22381527-2020C35448S0195-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  "/>
+    <hyperlink ref="E37" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Kuhn&quot; title=&quot; Wikipedia&quot;&gt;Thomas KUHN&lt;/a&gt; était un philosophe et historien des sciences américain, célèbre pour son ouvrage  &lt;a href=&quot;https://apprendrelaphilosophie.com/thomas-kuhn-y-a-t-il-des-revolutions-scientifiques/&quot; title=&quot;Kuhn la sctructure des revolutions scientifiques par apprendre la philo&quot;&gt;La Structure des révolutions scientifiques &lt;/a&gt; (1962), l’un des livres les plus influents du XXᵉ siècle en philosophie des sciences. Formé d’abord en physique à Harvard avant de se tourner vers l’histoire et la philosophie des sciences, il a enseigné à Harvard, Berkeley, Princeton et au MIT, et a profondément renouvelé la façon dont on conçoit le progrès scientifique. &lt;/p&gt; &lt;p&gt; Au cœur de sa pensée se trouve le concept de paradigme : un cadre conceptuel partagé par une communauté scientifique, incluant des théories, des méthodes, des expériences canoniques et des normes de résolution de problèmes. Tant  &lt;a href=&quot;https://www.youtube.com/watch?v=_mBS4YbiYcA&quot; title=&quot;Kuhn les paradigmes par le precepteur&quot;&gt;qu’un paradigme domine, &lt;/a&gt; la science fonctionne en mode de « science normale », où les chercheurs résolvent des énigmes à l’intérieur du cadre sans remettre en cause ses fondements. &lt;/p&gt; &lt;p&gt; Il  oppose la science normale à la « science extraordinaire », qui survient quand des anomalies s’accumulent et ébranlent la confiance dans le paradigme dominant. Cela peut mener à une révolution scientifique, c’est-à-dire un changement de paradigme radical : les anciens concepts et méthodes sont abandonnés au profit d’un nouveau cadre inconciliable avec l’ancien. Il explique ainsi que le progrès scientifique n’est pas une accumulation linéaire de connaissances, mais une succession de ruptures révolutionnaires. &lt;/p&gt; &lt;p&gt; Selon lui, les paradigmes successifs ne sont pas toujours comparables de façon neutre : il parle d’« incommensurabilité » entre paradigmes, car leurs concepts, critères de validité et questions légitimes diffèrent profondément. Cela remet en cause l’idée selon laquelle la science progresse uniquement par accumulation objective et rationnelle, indépendante des contextes historiques et sociaux. &lt;/p&gt; &lt;p&gt; Sa philosophie a eu un impact bien au-delà de la science : ses idées sur les paradigmes et les révolutions ont influencé la sociologie, l’économie, les sciences politiques, la gestion et même les sciences humaines. En mettant l’accent sur les dimensions historiques, sociales et communautaires de la science, &lt;a href=&quot;https://www.youtube.com/watch?v=fV-vh9y_TQs&quot; title=&quot;Kuhn speaking par philosophy Overdoser&quot;&gt;il a ouvert la voie &lt;/a&gt;  à une épistémologie plus contextualisée, critique du positivisme logique et de l’idée d’une science totalement neutre et objective. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E38" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/John_B._Cobb&quot;  title=&quot; Wikipedia&quot;&gt;John B. COBB&lt;/a&gt; était un philosophe américain,  figure majeure de la philosophie et de la théologie du process, inspirée par Alfred North Whitehead. Issu d'une famille de missionnaires méthodistes au Japon, il a développé une vision panenthéiste où Dieu est à la fois immanent dans le monde et &lt;a href=&quot;https://books.openedition.org/pum/42552?lang=fr&quot; title=&quot;Réflexions en marge d’un livre de John B. Cobb par OpenEdition&quot;&gt;transcendant, &lt;/a&gt;  influençant profondément les débats sur l'écologie, l'économie durable et le pluralisme religieux. Son œuvre, comptant plus de 50 livres, met l'accent sur l'interdépendance de tous les êtres et la nécessité d'une éthique écologique. &lt;/p&gt; p&gt; Il rejette le théisme classique en affirmant que Dieu évolue avec les créatures, ressent leurs souffrances et n'a pas une prescience absolue des événements futurs, préservant ainsi la liberté humaine. Sa théologie &lt;a href=&quot;https://www.youtube.com/watch?v=ArXAjOlufZs&quot; title=&quot;&#10;John Cobb - Pluralisme religieux : une discussion sur le christianisme transformatif de John Cobb par Center for Process Studies&quot;&gt;du process &lt;/a&gt; voit une valeur intrinsèque en toute chose, y compris les particules comme l'électron, et critique l'anthropocentrisme chrétien traditionnel. Il intègre l'évolution comme un processus de hasard et de nécessité, influencé par Jacques Monod, tout en défendant un monde &quot;originellement bon&quot; dégradé par l'humanité. &lt;/p&gt; &lt;p&gt; Pionnier de l'éthique environnementale, il publie en 1971 &quot;Is It Too Late? A Theology of Ecology&quot;, premier ouvrage individuel sur le sujet, plaidant pour une vision écologique du christianisme. Avec Charles Birch, il coécrit &quot;The Liberation of Life&quot; en 1981, promouvant un modèle écologique contre le mécanisme biologique. &lt;/p&gt; &lt;p&gt;   Il influencera la Chine via ses idées sur la civilisation écologique et est élu en 2014 à l'Académie américaine des arts et des sciences. Il fonde aussi &quot;Progressive Christians Uniting&quot; pour une foi progressiste et engagée socialement. &lt;/p&gt; "/>
+    <hyperlink ref="E40" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Stanley_Cavell&quot;  title=&quot; Wikipedia&quot;&gt;Stanley CAVELL&lt;/a&gt; était un philosophe américain connu pour avoir renouvelé la philosophie du langage ordinaire, la philosophie morale et l’esthétique, notamment à partir de Wittgenstein, Austin, Emerson, Thoreau et du cinéma hollywoodien. Sa pensée est moins centrée sur des systèmes que sur une réflexion vivante sur l’ordinaire, le scepticisme, la voix personnelle et la manière dont la philosophie peut parler à partir de &lt;a href=&quot;https://www.youtube.com/watch?v=bWMncAAj16c&quot; title=&quot; Stanley Cavell par Film &amp; media&quot;&gt;l’expérience vécue. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Il s’intéresse d’abord au langage quotidien, parce qu’il pense que les difficultés philosophiques ne viennent pas seulement d’un manque d’informations, mais d’un trouble plus profond dans notre rapport au monde et aux autres. Pour lui, &lt;a href=&quot;https://www.youtube.com/watch?v=5q50IwBAUKY&quot; title=&quot; Stanley Cavell par philo overdose&quot;&gt;le scepticisme &lt;/a&gt; n’est pas seulement un problème de connaissance, c’est aussi une expérience humaine et parfois tragique : nous pouvons nous sentir séparés du monde, d’autrui, voire de nous-mêmes. &lt;/p&gt; &lt;p&gt; Un thème central chez lui est donc la reconnaissance. Il ne s’agit pas simplement de « savoir » que l’autre existe, mais d’apprendre à le reconnaître, à répondre à sa présence, et à accepter que nos relations humaines comportent toujours une part d’incertitude. C’est pourquoi Cavell relie souvent la philosophie à l’éthique, à la vie quotidienne et aux formes concrètes de l’attention aux autres. &lt;/p&gt; &lt;p&gt; Il est aussi célèbre pour son travail sur le cinéma, qu’il ne considère pas comme un divertissement secondaire mais comme un véritable lieu de pensée. À travers les comédies hollywoodiennes, notamment les « comédies de remariage », il explore des questions de couple, de séparation, de pardon et de seconde chance, c’est-à-dire des problèmes philosophiques aussi bien que narratifs.  &lt;/p&gt; &lt;p&gt; Il est lié à une idée très américaine de la philosophie : une philosophie qui n’oppose pas rigidement le savant et le populaire, qui peut être autobiographique, littéraire et morale à la fois. Son originalité tient à cela : il transforme la philosophie en une &lt;a href=&quot;https://www.liberation.fr/debats/2018/06/20/stanley-cavell-the-end_1660627/&quot; title=&quot; Stanley Cavell par liberation&quot;&gt; enquête sur la vie &lt;/a&gt; ordinaire, les formes de notre voix, et la possibilité de devenir plus juste envers soi-même et envers les autres.  &lt;/p&gt; &#10;&lt;audio controls title=&quot;la pensée américaine Stanley Cavell par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-05.11.2012-ITEMA_20417072-2012C12410S0310-NET_B1E428CD-7648-4739-933D-4C419F0B94C8_FC-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &#10;"/>
+    <hyperlink ref="H40" r:id="rId25" display="https://www.laphilo.fr/pho/scavell-mini.webp"/>
+    <hyperlink ref="H41" r:id="rId26" display="https://www.laphilo.fr/pho/mrothbard-mini.webp"/>
+    <hyperlink ref="H42" r:id="rId27" display="https://www.laphilo.fr/pho/ewiesel-mini.webp"/>
+    <hyperlink ref="H43" r:id="rId28" display="https://www.laphilo.fr/pho/abracken-mini.webp"/>
+    <hyperlink ref="E44" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Rorty&quot; title=&quot; Wikipedia&quot;&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href=&quot;https://www.youtube.com/watch?v=lfx4Jag1ic4&quot;  title=&quot;Le pragmatisme : définition, exemples par le savoir partagé&quot;&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href=&quot;https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism&quot; title=&quot; a bas l'autorité par laviedesidees&quot;&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas &quot;vrais&quot; ou &quot;faux&quot;. &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales , on trouve  &lt;a href=&quot;https://www.youtube.com/watch?v=MgU0dXZ3umM&quot; title=&quot;L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli&quot;&gt;&quot; Contingence, ironie et solidarité &quot;&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans &quot; Achieving Our Country&quot; (1998),  il y appelle la gauche américaine à abandonner le &quot;culturalisme&quot; pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la &quot;post-vérité&quot;. Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; "/>
+    <hyperlink ref="E46" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Charles_Parsons_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Charles Dacre PARSONS&lt;/a&gt; était un philosophe américain connu pour ses travaux en philosophie des mathématiques et en philosophie de Kant. Il a enseigné à Columbia puis à Harvard, où il est devenu professeur émérite. Il s’est formé à Harvard, avec une thèse dirigée par Willard Van Orman Quine, ce qui le place au croisement de la logique, de la philosophie analytique et des fondements des mathématiques. Son parcours intellectuel a été marqué très tôt par la rigueur mathématique, puisqu’il avait d’abord étudié les mathématiques avant de se tourner vers la philosophie. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la philosophie des mathématiques, domaine dans lequel il a travaillé sur la nature des objets mathématiques, la logique, la preuve et l’interprétation constructive des mathématiques prédicatives. Il a aussi beaucoup écrit sur Frege, Gödel, Hilbert et Quine, en lisant ces auteurs à la fois comme philosophes et comme figures majeures des fondements. &lt;/p&gt; &lt;p&gt; Il n’était pas seulement un spécialiste de logique ; il a aussi produit des travaux importants sur Kant, montrant comment les questions de connaissance, d’expérience et de structure de l’esprit se relient aux mathématiques. Cette double compétence, en philosophie des mathématiques et en histoire de la philosophie, explique pourquoi il est souvent vu comme un auteur à la fois technique et très large dans ses intérêts.&lt;/p&gt; &lt;p&gt; Son influence est restée forte dans le monde anglophone, au point d’être décrit comme l’un des philosophes des mathématiques les plus importants de sa génération. En plus de ses livres et articles, il a aussi contribué à l’édition de textes posthumes de Gödel, ce qui a renforcé son rôle dans l’étude contemporaine des fondements des mathématiques. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="I46" r:id="rId31" display="https://www.laphilo.fr/photo/cparsons.webp"/>
+    <hyperlink ref="H48" r:id="rId32" display="https://www.laphilo.fr/pho/dihde-mini.webp"/>
+    <hyperlink ref="E50" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edward_Sa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Edward SAÏD&lt;/a&gt; était un intellectuel palestinien-américain, critique littéraire et professeur de littérature anglaise et comparée à l’université Columbia de New York. D’origine palestinienne et né à Jérusalem, il a grandi entre l’Égypte, les États-Unis et l’Europe, une expérience de déplacement qui a profondément marqué sa pensée sur l’identité, la colonisation et l’altérité.  &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est l’essai &lt;a href=&quot;https://www.youtube.com/watch?v=Ne4WRykmjhA&quot; title=&quot;Edward Said  Orientalisme par HD Doc&quot;&gt;L’Orientalisme : &lt;/a&gt;  L’Orient créé par l’Occident* (1978), considéré comme le texte fondateur des postcolonial studies. Dans cet ouvrage, Saïd montre que l’« Orient » n’est pas une réalité objective mais une invention de l’Occident : un discours façonné par des siècles de domination coloniale pour mieux contrôler et représenter l’Autre. &lt;/p&gt; &lt;p&gt; Pour lui, l’orientalisme est à la fois un savoir et un outil de pouvoir : il ne s’agit pas seulement de décrire l’Orient, mais de le hiérarchiser, de l’essentialiser et de le rendre  &lt;a href=&quot;https://www.youtube.com/watch?v=QBj-yWLnayM&quot; title=&quot;Edward Said writings on Orientalism par Middle East Eye&quot;&gt; inférieur à l’Occident. &lt;/a&gt; Il analyse quatre thèses principales : la domination politique et culturelle de l’Orient par l’Occident, la dépréciation de la langue arabe, la diabolisation de l’arabe et de l’islam, et la défense de la cause palestinienne. &lt;/p&gt; &lt;p&gt; Sa pensée articule critique littéraire, histoire, philosophie et sciences politiques, en s’inspirant notamment de Michel Foucault (discours–pouvoir) et de Jacques Derrida (déconstruction). Il montre que la violence du colonialisme n’est pas seulement matérielle (conquête, pillage), mais aussi épistémique : une violence de la raison qui classe, essentialise et dévalue les « Autres » de l’Occident. &lt;/p&gt; &lt;p&gt;  Intéressé par &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Edward-W-Said-1935-2003.html&quot; title=&quot;Edward Said par lesclesdumoyenorient&quot;&gt; l’engagement politique, &lt;/a&gt; il a aussi défendu la cause palestinienne et la légitimité des revendications d’autodétermination du peuple palestinien, tout en reconnaissance du droit à une patrie juive. Il rejetait le repli identitaire et prônait une vision universelle qui défend les différences et les droits, tissant des liens entre classicisme et excentricité, histoire et actualité. &lt;/p&gt;  &lt;audio controls title=&quot;Edward Said, une conscience morale par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-08.12.2017-ITEMA_21518070-2017C19327S0342-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &#10;&#10;&#10;"/>
+    <hyperlink ref="H50" r:id="rId34" display="https://laphilo.fr/pho/esaid-mini.webp"/>
+    <hyperlink ref="H51" r:id="rId35" display="https://www.laphilo.fr/pho/rmadams-mini.webp"/>
+    <hyperlink ref="E52" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Nozick&quot;  title=&quot; Wikipedia&quot;&gt;Robert NOZICK&lt;/a&gt; était un philosophe américain connu pour &lt;a href=&quot;https://www.youtube.com/watch?v=Q-t3cpFAk4o&quot;  title=&quot; Libertarianisme par Vadim Media&quot;&gt; son libertarianisme &lt;/a&gt; et sa critique des théories égalitaristes comme celle de John Rawls. Professeur à Harvard, il a marqué la philosophie politique, morale et épistémologique par son œuvre principale, Anarchie, État et utopie (1974), qui défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Minarchisme&quot;  title=&quot; Minarchisme par Wikipédia&quot;&gt; Etat Minimal. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il argue que seul l'État minimal, ou &quot;État gardien de nuit&quot;, est légitime, car il se limite à protéger les individus contre la force, la fraude et le vol, sans redistribuer les richesses. Il rejette l'anarcho-capitalisme en montrant, via des agences de protection privée, comment un État dominant émerge naturellement pour monopoliser la coercition légitime, justifié par le droit naturel à la personne. &lt;/p&gt; &lt;p&gt; Contrairement à la justice distributive de Rawls, il propose une théorie de l'entitlement : une acquisition initiale juste et des transferts volontaires rendent la distribution légitime, sans besoin d'égalisation par l'État. Toute intervention redistributive viole les droits individuels, traitant les personnes comme des moyens plutôt que des fins, en écho à Kant. &lt;/p&gt; &lt;p&gt; Dans Anarchie, État et utopie, Il réfute l'utilitarisme via l'expérience de pensée de la &lt;a href=&quot;https://www.youtube.com/watch?v=2FVwXaNWPQ0&quot;  title=&quot; La machine à expérience par Monsieur Phi&quot;&gt;&quot;machine à expérience&quot; :&lt;/a&gt;  même si elle offre un bonheur parfait et indistinguable de la réalité, les gens préfèrent vivre des actions réelles et façonner leur identité plutôt que des simulations. Cela prouve que le bonheur n'est pas le seul bien suprême. &lt;/p&gt; &lt;p&gt; Plus tard, dans Explications philosophiques (1981), il développe une théorie du suivi (tracking theory) en épistémologie, où la connaissance repose sur des conditionnels contrefactuels fiables, contournant le scepticisme sans justification traditionnelle. Son anti-coercitivisme intellectuel invite à une philosophie ouverte, non imposée. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Qui a peur des Libertariens par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-14.06.2022-ITEMA_23058436-2022C12410S0165-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;"/>
+    <hyperlink ref="H58" r:id="rId37" display="https://www.laphilo.fr/pho/imyoung-mini.webp"/>
+    <hyperlink ref="H59" r:id="rId38" display="https://www.laphilo.fr/pho/bhooks-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -4124,810 +4124,807 @@
         <v>51</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="n">
+    <row r="44" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1">
+        <v>1930</v>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2018</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1930 – 2018</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aníbal QUIJANO</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal QUIJANO&lt;/a&gt; est un sociologue péruvien, l’un des grands penseurs latino-américains du XXe siècle et le fondateur de la pensée décoloniale. Né en 1928 à Yanama, dans les Andes péruviennes, il étudie à l’université de San Marcos, à Lima, où il enseigne ensuite la sociologie. Dans les années 1960 et 1970, il participe aux travaux de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_la_d%C3%A9pendance" title=" Wikipedia"&gt;théorie de la dépendance&lt;/a&gt;, qui explique le sous-développement de l’Amérique latine par sa place subordonnée dans l’économie mondiale, et étudie la condition des populations indiennes et métisses des villes.&lt;/p&gt; &lt;p&gt;En 1992, pour le cinquième centenaire de l’arrivée de Christophe Colomb, il publie l’article « Colonialité et modernité/rationalité », qui forge la notion de « colonialité du pouvoir ». La conquête de l’Amérique a donné naissance à la fois au capitalisme mondial et à une idée nouvelle, celle de « race », qui a permis de classer les peuples en supérieurs et inférieurs et de distribuer entre eux le travail : le salariat pour les Européens, le servage pour les Indiens, l’esclavage pour les Africains. Cette classification a survécu à l’indépendance des colonies : elle structure encore les rapports sociaux, le savoir et la manière dont chacun se perçoit. Quijano critique aussi l’« eurocentrisme », qui fait de l’histoire européenne le modèle de l’histoire universelle.&lt;/p&gt; &lt;p&gt;Professeur à l’université de Binghamton, aux États-Unis, il anime le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt; avec Walter Mignolo et Enrique Dussel. La philosophe argentine &lt;a href="https://fr.wikipedia.org/wiki/Mar%C3%ADa_Lugones" title=" Wikipedia"&gt;María Lugones&lt;/a&gt; a prolongé son concept dans celui de « colonialité du genre ». Il meurt à Lima en 2018.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/quijano-mini.webp</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée décoloniale</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sociologue péruvien, inventeur de la « colonialité du pouvoir » et fondateur de la pensée décoloniale.</t>
+        </is>
+      </c>
+      <c r="N44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O44" s="1"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Péruvienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
         <v>1931</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B45" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D45" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_Rorty" title=" Wikipedia"&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href="https://www.youtube.com/watch?v=lfx4Jag1ic4"  title="Le pragmatisme : définition, exemples par le savoir partagé"&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href="https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism" title=" a bas l'autorité par laviedesidees"&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas "vrais" ou "faux". &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales, on trouve  &lt;a href="https://www.youtube.com/watch?v=MgU0dXZ3umM" title="L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli"&gt;" Contingence, ironie et solidarité "&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans " Achieving Our Country" (1998),  il y appelle la gauche américaine à abandonner le "culturalisme" pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la "post-vérité". Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F45" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G45" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H45" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="I44" s="9"/>
-      <c r="J44" s="2" t="s">
+      <c r="I45" s="9"/>
+      <c r="J45" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="K45" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="L44" s="2" t="s">
+      <c r="L45" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="N44" s="1" t="s">
+      <c r="N45" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
+    <row r="46" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="n">
         <v>1932</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B46" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Searle"  title=" Wikipedia"&gt;John SEARLE&lt;/a&gt; était un philosophe américain  connu pour ses travaux influents dans plusieurs domaines, notamment la philosophie du langage, la philosophie de l'esprit et la philosophie sociale. Il  a développé et systématisé la théorie des &lt;a href="https://www.youtube.com/watch?v=pIbkpLfrD6A" title="
 La théorie des actes de langage (2) - John Searle par Heraut du Mont Parnasse"&gt;actes de langage&lt;/a&gt; car, pour lui, parler une langue, ce n'est pas seulement émettre des sons ou des suites de symboles, mais accomplir des actions. &lt;/p&gt; &lt;p&gt; Défenseur du "naturalisme biologique" en philosophie de l'esprit. Il s'oppose au dualisme cartésien tout en refusant le matérialisme réducteur qui nierait l'existence de &lt;a href="https://www.youtube.com/watch?v=EriAhi0mj7w" title=" Conscience et matière grise par TEDx Talks"&gt;la conscience&lt;/a&gt; ou la réduirirait à de simples phénomènes physiques. Pour lui, les états mentaux (douleur, croyances, désirs, conscience) sont des phénomènes  &lt;a href="https://www.youtube.com/watch?v=Bq2bfSzkTfU"  title="John Searle - Une personne peut-elle être une âme ? par Closer To Truth"&gt;biologiques réels&lt;/a&gt;, causés par des processus neuronaux du cerveau, mais ils ne sont pas réductibles à ces processus au sens où ils émergent à un niveau supérieur et possèdent des propriétés irréductibles.&lt;/p&gt; &lt;p&gt; L'une des ses contributions les plus célèbres est son argument de la &lt;a href="https://www.youtube.com/watch?v=P5DtwDr9YEc" title=" La Chambre chinoise par Ian et frank"&gt;Chambre Chinoise&lt;/a&gt;. Cet argument vise à réfuter la thèse de l'IA forte (position selon laquelle un ordinateur programmé de manière appropriée n'est pas seulement un outil pour l'étude de l'esprit, mais qu'il est véritablement un esprit, capable de comprendre et de posséder d'autres états cognitifs) opposé à l'IA faible (position selon laquelle les ordinateurs sont des outils utiles pour étudier l'esprit, mais qu'ils ne sont pas eux-mêmes des esprits). &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://labo.nonmarchand.org/pmwiki/uploads/Textes/JohnSearleLaConstructionDeLaRealiteSociale/JohnSearle_LaConstructionDeLaRealiteSociale.pdf"  title=" La construction e la réalité sociale par nonmarchand"&gt;"La Construction de la Réalité Sociale"&lt;/a&gt;, il étend sa théorie des actes de langage et de l'intentionnalité pour expliquer comment nous construisons des faits institutionnels et sociaux. Il distingue les "Faits bruts" qui existent indépendamment de toute institution humaine (par exemple, la montagne Everest) des "Faits institutionnels" qui n'existent qu'en vertu d'institutions humaines et de l'accord collectif (par exemple, l'argent, le mariage, la propriété). &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G46" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H46" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="I45" s="1"/>
-      <c r="J45" s="2" t="s">
+      <c r="I46" s="1"/>
+      <c r="J46" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="K46" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="L45" s="2" t="s">
+      <c r="L46" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="n">
-        <v>1933</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="F46" s="7"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P46" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
+        <v>1933</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="F47" s="7"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
         <v>1934</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B48" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C48" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D48" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Enrique_Dussel"  title=" Wikipedia"&gt;Enrique DUSSEL&lt;/a&gt; était un philosophe argentin majeurs de la décolonialité et de la philosophie latino-américaine de la liberation.  Jeune intellectuel engagé dans les mouvements étudiants et opposé aux régimes autoritaires, il a été persécuté en Argentine avant de s’exiler au Mexique en 1975, où il a poursuivi sa carrière académique et développé sa pensée. Il élabore une &lt;a href="https://www.youtube.com/watch?v=QGPosp7lYlM" title="Enrique Dussel and the Philosophy of Liberation – Decolonizing Thought par Darina Metreveli"&gt;philosophie de la libération &lt;/a&gt; qui remet en question l’ontologie monologique de la modernité et introduit une approche éthique et alteritaire inspirée par Levinas, souvent décrite sous le nom d’analectique ou de dialectique positive. &lt;/p&gt; &lt;p&gt; Pionnier du décolonialisme latino-américain, il contribue à la construction des cadres Modernité/Colonialité et à l’idée d’une transmodernité, articulant critique de la modernité et invitation à repenser les rapports Nord-Sud et centre-périphérie. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures : &lt;a href="https://www.youtube.com/watch?v=nXNyqKCrKLY" title="Enrique Dussel, métaphysicien de la libération - Emmanuel Lévine par lundimatin"&gt;"Méthode pour une philosophie de la libération" &lt;/a&gt; paru en  1974 et "Filosofía ética latinoamericana" (période majeure)  posent les bases d’une philosophie enracinée dans les expériences des peuples opprimés et des contextes colonisés. &lt;/p&gt; &lt;p&gt; Il est reconnu dans les &lt;a href="https://lestempsquirestent.org/fr/numeros/numero-7/enrique-dussel-un-philosophe-indispensable-pour-decoloniser-la-theologie-politique" title="Enrique Dussel,
 un philosophe indispensable pour décoloniser la théologie politique par les temps qui restent"&gt;milieux décoloniaux &lt;/a&gt; et philosophie de la libération, mais demeure moins connu du grand public français, bien que des traductions et des analyses apparaissent et stimulent l’intérêt académique en France. Son travail nourrit le courant décolonial qui met en évidence l’interdépendance entre modernité et colonialité depuis 1492 et propose des axes pour une pensée transmoderne, dépassant les cadres classiques de la philosophie occidentale. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F48" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G48" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H48" s="9" t="s">
         <v>406</v>
-      </c>
-      <c r="I47" s="9"/>
-      <c r="J47" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiers-mondisme ; Théologie de la libération ; Philosophie de la libération ; Pensée décoloniale</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O47" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B48" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>410</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>413</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiers-mondisme ; Théologie de la libération ; Philosophie de la libération ; Pensée décoloniale</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="I49" s="9"/>
+      <c r="J49" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="K49" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="L48" s="2" t="s">
+      <c r="L49" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B49" s="1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="G49" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="I49" s="1"/>
-      <c r="J49" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="M49" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="N49" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P49" s="1" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G50" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P50" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="XFC49" s="0"/>
-      <c r="XFD49" s="0"/>
-    </row>
-    <row r="50" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16" t="n">
+      <c r="XFC50" s="0"/>
+      <c r="XFD50" s="0"/>
+    </row>
+    <row r="51" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="16" t="n">
         <v>1935</v>
       </c>
-      <c r="B50" s="16" t="n">
+      <c r="B51" s="16" t="n">
         <v>2003</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C51" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D51" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="E50" s="13" t="s">
+      <c r="E51" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="F50" s="16" t="s">
+      <c r="F51" s="16" t="s">
         <v>428</v>
       </c>
-      <c r="G50" s="18" t="s">
+      <c r="G51" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="I50" s="18"/>
-      <c r="J50" s="2" t="s">
+      <c r="I51" s="18"/>
+      <c r="J51" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="K51" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="L50" s="14" t="s">
+      <c r="L51" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="M50" s="14" t="s">
+      <c r="M51" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N50" s="14" t="s">
+      <c r="N51" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="n">
+    <row r="52" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
         <v>1937</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B52" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C52" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D52" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E52" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F52" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G52" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H52" s="10" t="s">
         <v>438</v>
-      </c>
-      <c r="I51" s="9"/>
-      <c r="J51" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="n">
-        <v>1938</v>
-      </c>
-      <c r="B52" s="7" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>446</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libéralisme ; Minarchisme ; Déontologisme</t>
-        </is>
+        <v>127</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>439</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="N52" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="N52" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
         <v>1938</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>449</v>
+      <c r="B53" s="7" t="n">
+        <v>2002</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tom_Regan"  title=" Wikipedia"&gt;Tom REGAN&lt;/a&gt; était un philosophe américain   &lt;a href="https://www.youtube.com/watch?v=hgVMf3q4Vh4"  title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Pensées antispécistes par The Critical Vegan"&gt;antispéciste &lt;/a&gt; influent dans le domaine de l'éthique animale, considéré comme un pionnier de la théorie des droits des animaux sur une base déontologique. Né à Pittsburgh, il enseigne de 1967 à 2001 à l’université d’État de Caroline du Nord. Il développe une approche abolitionniste opposée à l'utilitarisme de Peter Singer, arguant que les mammifères normaux d'un an ou plus sont des "sujets-d'une-vie" dotés d'une valeur inhérente, méritant des droits moraux fondamentaux indépendamment de leur utilité. Inspiré par Kant mais étendu aux non-humains, il définit ces sujets comme des êtres conscients pour qui leur vie importe intrinsèquement, justifiant l'interdiction absolue de l'exploitation. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales sont : "The Case for Animal Rights" paru en 1983, traduit en français comme  &lt;a href="http://tomregan.free.fr/" title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Les Droits des animaux par Tom Regan"&gt;"Les Droits des animaux" &lt;/a&gt; en 2013 : son magnum opus, salué comme un classique moderne critiquant Descartes et plaidant pour le "principe de respect" envers tout sujet-d'une-vie. "All That Dwell Therein" paru en  1982 : recueil d'essais sur le végétarisme et l'éthique animale. &lt;/p&gt; &lt;p&gt; Ses idées ont profondément marqué le mouvement des droits des animaux, influençant débats sur végétarisme, anti-vivisection et critique de l'environnementalisme indirect, tout en étant cité par des penseurs comme Derrida ou dans des ouvrages comme ceux de Jean-Baptiste Jeangène Vilmer. Dans &lt;em&gt;Empty Cages&lt;/em&gt; (2004), destiné au grand public, il résume son combat : il ne s’agit pas d’agrandir les cages, mais de les vider. &lt;/p&gt; </t>
-        </is>
+        <v>442</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>443</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>455</v>
+        <v>445</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>446</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Minarchisme ; Déontologisme</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tom_Regan"  title=" Wikipedia"&gt;Tom REGAN&lt;/a&gt; était un philosophe américain   &lt;a href="https://www.youtube.com/watch?v=hgVMf3q4Vh4"  title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Pensées antispécistes par The Critical Vegan"&gt;antispéciste &lt;/a&gt; influent dans le domaine de l'éthique animale, considéré comme un pionnier de la théorie des droits des animaux sur une base déontologique. Né à Pittsburgh, il enseigne de 1967 à 2001 à l’université d’État de Caroline du Nord. Il développe une approche abolitionniste opposée à l'utilitarisme de Peter Singer, arguant que les mammifères normaux d'un an ou plus sont des "sujets-d'une-vie" dotés d'une valeur inhérente, méritant des droits moraux fondamentaux indépendamment de leur utilité. Inspiré par Kant mais étendu aux non-humains, il définit ces sujets comme des êtres conscients pour qui leur vie importe intrinsèquement, justifiant l'interdiction absolue de l'exploitation. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales sont : "The Case for Animal Rights" paru en 1983, traduit en français comme  &lt;a href="http://tomregan.free.fr/" title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Les Droits des animaux par Tom Regan"&gt;"Les Droits des animaux" &lt;/a&gt; en 2013 : son magnum opus, salué comme un classique moderne critiquant Descartes et plaidant pour le "principe de respect" envers tout sujet-d'une-vie. "All That Dwell Therein" paru en  1982 : recueil d'essais sur le végétarisme et l'éthique animale. &lt;/p&gt; &lt;p&gt; Ses idées ont profondément marqué le mouvement des droits des animaux, influençant débats sur végétarisme, anti-vivisection et critique de l'environnementalisme indirect, tout en étant cité par des penseurs comme Derrida ou dans des ouvrages comme ceux de Jean-Baptiste Jeangène Vilmer. Dans &lt;em&gt;Empty Cages&lt;/em&gt; (2004), destiné au grand public, il résume son combat : il ne s’agit pas d’agrandir les cages, mais de les vider. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="I54" s="9"/>
+      <c r="J54" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="K53" s="2" t="s">
+      <c r="K54" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L53" s="2" t="s">
+      <c r="L54" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="B54" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saul_Kripke"  title=" Wikipedia"&gt;Saul KRIPKE&lt;/a&gt; était un philosophe américain de la tradition analytique connu pour ses apports décisifs en logique modale, en métaphysique et en philosophie du langage. Très jeune, il révolutionne la logique en introduisant la sémantique des mondes possibles, aujourd’hui appelée &lt;a href="https://www.youtube.com/watch?v=_sIgAdvhruU"title="Qui est Saul Kripke ? par Monsieur Phi"&gt;"cadres de Kripke"&lt;/a&gt;, qui permet de formaliser la modalité (le nécessaire et le possible) de façon rigoureuse. &lt;/p&gt; &lt;p&gt; Son œuvre la plus influente est "Naming and Necessity", où il critique la conception descriptiviste des noms défendue par Frege et Russell. Selon lui, un  &lt;a href="https://www.youtube.com/watch?v=d7-8Avem7EE" title="Saul Kripke, La logique des noms propres. par Jtgrandtour"&gt; nom propre&lt;/a&gt; n’équivaut pas à une description mais fonctionne comme un « désignateur rigide » : il désigne le même individu dans tous les mondes possibles. Cette idée bouleverse la philosophie du langage et entraîne une redéfinition de la notion de référence.&lt;/p&gt; &lt;p&gt;  Il montre également qu’il existe des vérités nécessaires découvertes empiriquement : par exemple, l’identité « l’eau est H₂O » est nécessaire, mais nous ne l’avons apprise qu’a posteriori. Ce concept de nécessité a posteriori a marqué un tournant dans la métaphysique contemporaine. À l’inverse, il identifie la possibilité de certaines vérités contingentes connues a priori, ce qui remet en cause des distinctions classiques entre connaissance et modalité. &lt;/p&gt; &lt;p&gt; Il s’oppose au physicalisme en arguant que l’on peut concevoir un monde où tous les états cérébraux existent sans que la conscience subjective "le qualia" ne soit présente. Cette critique alimente encore aujourd’hui les débats sur la nature de la conscience. Son ouvrage "Wittgenstein on Rules and Private Language" propose une lecture radicale de Wittgenstein, selon laquelle toute règle est sujette à un scepticisme profond sur son application. Bien que controversée, cette interprétation a largement stimulé les discussions en philosophie du langage et en épistémologie. &lt;/p&gt; &lt;p&gt; Connu aussi pour son ouvrage " On two Paradoxes of Knowledge" et son  &lt;a href="https://www.youtube.com/watch?v=AzaUSC--2G0"  title="Le Paradoxe de l'Examen selon Saul Kripke par Silogic"&gt;"paradoxe de l'examen"&lt;/a&gt;. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P54" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="n">
-        <v>1941</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Lewis_(philosophe)"  title=" Wikipedia"&gt;David LEWIS&lt;/a&gt; était un philosophe américain connu pour sa théorie du  réalisme modal, selon laquelle il existe un nombre infini de mondes possibles concrets et causalement isolés les uns des autres. Son ouvrage majeur   &lt;a href="https://www.youtube.com/watch?v=-QlqLDLifuc" title="David Lewis - "De la pluralité des mondes" - De quoi parle ce livre ? par Philosophie 21"&gt;"On the Plurality of Worlds"&lt;/a&gt;  sortie en 1986, expose cette position révolutionnaire : pour lui, chaque monde possible existe aussi réellement que notre monde actuel, et sert à comprendre la modalité, c'est-à-dire ce qui pourrait être ou ce qui doit être. &lt;/p&gt; &lt;p&gt; Il a également proposé la théorie des contreparties en logique modale : au lieu de supposer que les personnes ou objets existent dans plusieurs mondes possibles, il affirme que chaque individu de notre monde a des « contreparties » dans les autres mondes possibles qui partagent certaines caractéristiques mais ne sont pas identiques à lui. Cette approche constitue une alternative à la logique modale traditionnelle, notamment celle de Saul Kripke. &lt;/p&gt; &lt;p&gt; Sa métaphysique est marquée par une conception atomiste (pointilliste) : la réalité n’est qu’une vaste mosaïque de faits locaux, chaque fait étant centré sur un « point » ayant des propriétés intrinsèques. Ce point de vue s’inspire de David Hume, d’où le nom « survenance humienne », refusant les liens nécessaires entre les faits et privilégiant une juxtaposition de qualités locales. &lt;/p&gt; &lt;p&gt; Il  a beaucoup écrit sur la philosophie du langage, la philosophie de l’esprit, l’épistémologie, la logique philosophique et la philosophie des mathématiques. Son premier grand ouvrage, "Convention" de 1969, analyse les conventions sociales à l’aide de la théorie des jeux, en montrant leur caractère arbitraire et leur diffusion par la connaissance commune et le précédent. Il s a marqué durablement la philosophie analytique.  &lt;a href="https://www.youtube.com/watch?v=g3jQwDP_Lyc" title="David Lewis - "David Lewis Speaks at La Trobe University par TimeSparrow"&gt;"Ses théories&lt;/a&gt; sont incontournables dans les débats sur les mondes possibles, la modalité, la causalité, la convention sociale, et l’atomisme métaphysique. Ses ouvrages, tels que Counterfactuals et Philosophical Papers, restent des références dans l’analyse logique et conceptuelle contemporaine. &lt;/p&gt; &lt;audio controls title=" On dit de David Lewis que c'est le plus grand métaphysicien qu’on ait vu depuis Leibniz par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18292-28.02.2019-ITEMA_21995453-0.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="I55" s="9"/>
+    </row>
+    <row r="55" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saul_Kripke"  title=" Wikipedia"&gt;Saul KRIPKE&lt;/a&gt; était un philosophe américain de la tradition analytique connu pour ses apports décisifs en logique modale, en métaphysique et en philosophie du langage. Très jeune, il révolutionne la logique en introduisant la sémantique des mondes possibles, aujourd’hui appelée &lt;a href="https://www.youtube.com/watch?v=_sIgAdvhruU"title="Qui est Saul Kripke ? par Monsieur Phi"&gt;"cadres de Kripke"&lt;/a&gt;, qui permet de formaliser la modalité (le nécessaire et le possible) de façon rigoureuse. &lt;/p&gt; &lt;p&gt; Son œuvre la plus influente est "Naming and Necessity", où il critique la conception descriptiviste des noms défendue par Frege et Russell. Selon lui, un  &lt;a href="https://www.youtube.com/watch?v=d7-8Avem7EE" title="Saul Kripke, La logique des noms propres. par Jtgrandtour"&gt; nom propre&lt;/a&gt; n’équivaut pas à une description mais fonctionne comme un « désignateur rigide » : il désigne le même individu dans tous les mondes possibles. Cette idée bouleverse la philosophie du langage et entraîne une redéfinition de la notion de référence.&lt;/p&gt; &lt;p&gt;  Il montre également qu’il existe des vérités nécessaires découvertes empiriquement : par exemple, l’identité « l’eau est H₂O » est nécessaire, mais nous ne l’avons apprise qu’a posteriori. Ce concept de nécessité a posteriori a marqué un tournant dans la métaphysique contemporaine. À l’inverse, il identifie la possibilité de certaines vérités contingentes connues a priori, ce qui remet en cause des distinctions classiques entre connaissance et modalité. &lt;/p&gt; &lt;p&gt; Il s’oppose au physicalisme en arguant que l’on peut concevoir un monde où tous les états cérébraux existent sans que la conscience subjective "le qualia" ne soit présente. Cette critique alimente encore aujourd’hui les débats sur la nature de la conscience. Son ouvrage "Wittgenstein on Rules and Private Language" propose une lecture radicale de Wittgenstein, selon laquelle toute règle est sujette à un scepticisme profond sur son application. Bien que controversée, cette interprétation a largement stimulé les discussions en philosophie du langage et en épistémologie. &lt;/p&gt; &lt;p&gt; Connu aussi pour son ouvrage " On two Paradoxes of Knowledge" et son  &lt;a href="https://www.youtube.com/watch?v=AzaUSC--2G0"  title="Le Paradoxe de l'Examen selon Saul Kripke par Silogic"&gt;"paradoxe de l'examen"&lt;/a&gt;. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>463</v>
+      </c>
       <c r="J55" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>475</v>
+        <v>464</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>465</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>476</v>
+        <v>466</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="332.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P55" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
+        <v>1941</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Lewis_(philosophe)"  title=" Wikipedia"&gt;David LEWIS&lt;/a&gt; était un philosophe américain connu pour sa théorie du  réalisme modal, selon laquelle il existe un nombre infini de mondes possibles concrets et causalement isolés les uns des autres. Son ouvrage majeur   &lt;a href="https://www.youtube.com/watch?v=-QlqLDLifuc" title="David Lewis - "De la pluralité des mondes" - De quoi parle ce livre ? par Philosophie 21"&gt;"On the Plurality of Worlds"&lt;/a&gt;  sortie en 1986, expose cette position révolutionnaire : pour lui, chaque monde possible existe aussi réellement que notre monde actuel, et sert à comprendre la modalité, c'est-à-dire ce qui pourrait être ou ce qui doit être. &lt;/p&gt; &lt;p&gt; Il a également proposé la théorie des contreparties en logique modale : au lieu de supposer que les personnes ou objets existent dans plusieurs mondes possibles, il affirme que chaque individu de notre monde a des « contreparties » dans les autres mondes possibles qui partagent certaines caractéristiques mais ne sont pas identiques à lui. Cette approche constitue une alternative à la logique modale traditionnelle, notamment celle de Saul Kripke. &lt;/p&gt; &lt;p&gt; Sa métaphysique est marquée par une conception atomiste (pointilliste) : la réalité n’est qu’une vaste mosaïque de faits locaux, chaque fait étant centré sur un « point » ayant des propriétés intrinsèques. Ce point de vue s’inspire de David Hume, d’où le nom « survenance humienne », refusant les liens nécessaires entre les faits et privilégiant une juxtaposition de qualités locales. &lt;/p&gt; &lt;p&gt; Il  a beaucoup écrit sur la philosophie du langage, la philosophie de l’esprit, l’épistémologie, la logique philosophique et la philosophie des mathématiques. Son premier grand ouvrage, "Convention" de 1969, analyse les conventions sociales à l’aide de la théorie des jeux, en montrant leur caractère arbitraire et leur diffusion par la connaissance commune et le précédent. Il s a marqué durablement la philosophie analytique.  &lt;a href="https://www.youtube.com/watch?v=g3jQwDP_Lyc" title="David Lewis - "David Lewis Speaks at La Trobe University par TimeSparrow"&gt;"Ses théories&lt;/a&gt; sont incontournables dans les débats sur les mondes possibles, la modalité, la causalité, la convention sociale, et l’atomisme métaphysique. Ses ouvrages, tels que Counterfactuals et Philosophical Papers, restent des références dans l’analyse logique et conceptuelle contemporaine. &lt;/p&gt; &lt;audio controls title=" On dit de David Lewis que c'est le plus grand métaphysicien qu’on ait vu depuis Leibniz par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18292-28.02.2019-ITEMA_21995453-0.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="I56" s="9"/>
+      <c r="J56" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="332.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
         <v>1942</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B57" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D57" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="E56" s="9" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Daniel_Dennett"  style="color:#6A142A"  title=" Wikipedia"&gt;Daniel DENNETT&lt;/a&gt; était un  philosophe américain, figure importante et  influente de la philosophie de l'esprit, de la biologie et des sciences cognitives. Ses travaux se caractérisent par une volonté d'intégrer les découvertes scientifiques (biologie évolutionniste, neurosciences, intelligence artificielle) à la réflexion philosophique, souvent pour démanteler des intuitions traditionnelles qu'il juge erronées. &lt;/p&gt; &lt;p&gt; La Théorie de l'Esprit comme &lt;a href="https://www.youtube.com/watch?v=LKJJpvdqkFA" style="color:#88A1E9" title="Cette histoire va vous retourner le cerveau. | "Où suis-je" de Daniel Dennett par Monsieur Phi"&gt;"Position Intentionnelle"&lt;/a&gt; est sa contribution majeure. Il propose que pour prédire et expliquer le comportement d'un système (qu'il s'agisse d'un humain, d'un animal, d'un ordinateur ou même d'un thermostat), nous pouvons adopter trois "stances" : &lt;/p&gt; &lt;p&gt;La stance physique : On décrit le système par sa physique et sa chimie. Très difficile pour des systèmes complexes. &lt;/p&gt; &lt;p&gt;La stance du design : On considère le système comme conçu pour une fonction spécifique (ex: "ce thermostat est fait pour réguler la température"). &lt;/p&gt; &lt;p&gt;La stance intentionnelle : On traite le système comme s'il avait des croyances, des désirs et une rationalité. C'est une stratégie de prédiction extrêmement efficace, même si les croyances et désirs ne sont pas "réels" au sens littéral. Pour lui, avoir des croyances, c'est être un système dont le comportement peut être prédit avec succès par la stance intentionnelle. &lt;/p&gt; &lt;p&gt; Il est un matérialiste farouche et  rejette l'idée d'un &lt;a href="https://www.nonfiction.fr/article-1116-daniel_dennett_est_il_le_diable_.htm" title="Daniel Dennett est-il le diable ? par nonfiction"&gt;"théâtre cartésien"&lt;/a&gt;, un endroit dans le cerveau où tout se réunirait pour être "vu" par un &lt;a href="https://www.youtube.com/watch?v=0It9fwSj6xM"  title="Le moi comme illusion (Daniel Dennett, la conscience expliquée 4) par Philosophie Analytique"&gt;"spectateur" (le soi)&lt;/a&gt;. Pour lui, c'est une illusion.
 Il défend plutôt un modèle de "espace de travail global" : la conscience émerge de processus cérébraux parallèles et compétitifs. Une information devient "consciente" lorsqu'elle gagne une compétition pour être diffusée à grande échelle dans le cerveau, rendant ainsi disponible pour d'autres systèmes (mémoire, langage, prise de décision). Il n'y a pas de "centre" unique. &lt;/p&gt; &lt;p&gt; Il  considère que l'idée de la sélection naturelle de Darwin est "l'idée la plus dangereuse de tous les temps" car elle a un pouvoir explicatif immense, bien au-delà de la biologie. Il l'étend à d'autres domaines grâce au concept de "mèmes" (introduit par Richard Dawkins).
 Les mèmes sont des unités de culture (idées, mélodies, modes, concepts) qui se répliquent, mutent et sont sélectionnées dans le "payage" des esprits humains. Le langage,&lt;a href="https://www.youtube.com/shorts/bG3YBavy29Y" title="Cette histoire va vous retourner le cerveau | Daniel Dennett par StopCroyance"&gt; la religion&lt;/a&gt;, la morale peuvent être analysés comme des produits d'un processus darwinien. &lt;/p&gt; &lt;p&gt; Il défend une forme de libre arbitre qu'il estime compatible avec le déterminisme scientifique (le fait que l'univers soit régi par des lois causales). Pour lui, le libre arbitre n'est pas une "causalité magique" qui échapperait aux lois de la nature.  C'est la capacité d'un agent complexe (comme un être humain) à se projeter dans le futur, à évaluer les conséquences de ses actes et à agir en fonction de ses raisons. Ce libre arbitre est le produit de l'évolution et de la culture. Il est réel et précieux, même s'il n'est pas "libre" au sens d'une exemption des lois de la physique. &lt;/p&gt; &lt;audio controls title=" "Daniel Dennett, le penseur qui a révolutionné la philosophie des sciences et de l’esprit" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24419-10.05.2024-ITEMA_23737219-2024C51851S0131-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F57" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G57" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="H56" s="9" t="s">
+      <c r="H57" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="I56" s="9"/>
-      <c r="J56" s="2" t="s">
+      <c r="I57" s="9"/>
+      <c r="J57" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="K57" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="L57" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="N56" s="1" t="s">
+      <c r="N57" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="n">
+    <row r="58" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
         <v>1943</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B58" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C58" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Marilyn MCCORD-ADAMS</t>
         </is>
       </c>
-      <c r="E57" s="11" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marilyn_McCord_Adams" title=" Wikipedia"&gt;Marilyn McCORD ADAMS&lt;/a&gt; était une philosophe américaine et une théologienne anglicane, reconnue pour son travail en philosophie de la religion et en philosophie médiévale. Elle a aussi été ordonnée prêtre épiscopalienne, ce qui donnait à sa réflexion philosophique une forte dimension spirituelle et pastorale. Elle a étudié à l’Université de l’Illinois puis à Cornell, où elle a obtenu son doctorat en philosophie en 1967. Sa carrière universitaire l’a menée à Michigan, UCLA, Yale, Oxford et elle a été la première femme, ainsi que la première Américaine, à occuper la chaire Regius de divinité à Oxford. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://senate.universityofcalifornia.edu/in-memoriam/files/marilyn-adams.html" title="Marilyn Adans par university of california"&gt;Son apport le plus célèbre &lt;/a&gt; concerne l’étude de Guillaume d’Ockham, à qui elle a consacré une grande étude en deux volumes qui a beaucoup compté dans les recherches sur la théologie médiévale. Elle a aussi travaillé sur l’eucharistie, le christologie et d’autres auteurs médiévaux comme Thomas d’Aquin, Gilles de Rome et Duns Scot. &lt;/p&gt; &lt;p&gt; En  &lt;a href="https://www.youtube.com/watch?v=nFRGDG__ELM" title="Marilyn Adans par Real Atheology"&gt;philosophie de la religion, &lt;/a&gt; elle est connue pour ses analyses du mal extrême, qu’elle appelait les horrendous evils. Son idée centrale est qu’une théologie sérieuse doit prendre au sérieux les souffrances qui semblent détruire toute possibilité de sens, et montrer comment elles peuvent malgré tout être intégrées dans une vision de la bonté divine. &lt;/p&gt; &lt;p&gt; Son œuvre a eu une influence durable parce qu’elle relie la rigueur philosophique, l’érudition médiévale et l’expérience religieuse vécue. Elle reste une figure majeure pour comprendre à la fois la philosophie analytique de la religion et la redécouverte moderne de la pensée médiévale. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F58" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G58" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="H57" s="9" t="s">
+      <c r="H58" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="I57" s="9"/>
-      <c r="J57" s="2" t="s">
+      <c r="I58" s="9"/>
+      <c r="J58" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="K57" s="2" t="s">
+      <c r="K58" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="L57" s="2" t="s">
+      <c r="L58" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="M58" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N57" s="1" t="s">
+      <c r="N58" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
+    <row r="59" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="n">
         <v>1949</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B59" s="1" t="n">
         <v>2006</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="E58" s="14" t="inlineStr">
+      <c r="E59" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iris_Marion_Young" title=" Wikipedia"&gt;Iris Marion YOUNG&lt;/a&gt; était une philosophe politique américaine majeure, figure centrale du féminisme contemporain et de la théorie de la justice. Professeure à l'Université de Chicago, elle articule phénoménologie existentialiste, marxisme, théorie critique et postmodernisme pour repenser l'oppression, la domination et la démocratie au-delà des approches universalistes traditionnelles. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est sa théorie des &lt;a href="https://www.youtube.com/watch?v=KyOut8zqJRI" title="les cinq visages de l’oppression par Eliot Goodine"&gt; cinq visages de l'oppression,&lt;/a&gt;  qu'elle développe dans Justice and the Politics of Difference (1990) ou elle développe également une,&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2018_num_116_4_8681" title="le féminisme phénoménologique par persée"&gt; phénoménologie féministe &lt;/a&gt; du corps, notamment dans son essai célèbre « Throwing Like a Girl » (1980). Elle y décrit comment les femmes vivent leur corps comme limité, fragmenté et constamment surveillé, ce qui produit une « immanence » sociale qui entrave leur capacité d'action et d'autodétermination. Le corps n'est pas seulement biologique mais politique, façonné par les normes sociales et les rapports de pouvoir. &lt;/p&gt; &lt;p&gt; Elle défend une conception de la justice fondée sur l'inclusion différenciée plutôt que sur l'universalisme abstrait. Pour Young, une société juste doit reconnaître les différences de groupe (genre, race, classe, sexualité) et créer des espaces où chacun puisse participer à la vie démocratique sans être forcé d'abandonner son identité particulière. Elle propose aussi le concept de responsabilité sociale diffuse, selon lequel tous les membres d'une société sont responsables des injustice structurelles, pas seulement les auteurs directs. &lt;/p&gt; &lt;p&gt; Elle évite tout essentialisme en conceptualisant « les femmes » comme un groupe social sériel, au sens de Sartre : un groupe dont les membres ne partagent pas une essence commune mais sont reliés par des conditions sociales similaires et des rapports de pouvoir. Cette approche permet un féminisme pluriel, Alliant diverses luttes (racisme, homophobie, validisme, écologie) dans des coalitions contre les rapports de domination. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G59" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H59" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="J58" s="2" t="s">
+      <c r="J59" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K58" s="2" t="s">
+      <c r="K59" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="L58" s="2" t="s">
+      <c r="L59" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="M59" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N58" s="1" t="s">
+      <c r="N59" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
+    <row r="60" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="n">
         <v>1952</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B60" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bell_hooks"  title=" Wikipedia"&gt;Bell HOOKS&lt;/a&gt;, de son vrai nom Gloria Jean Watkins, est une autrice, professeure et militante féministe afro-américaine. Née dans le Kentucky, dans le Sud ségrégationniste, elle prit le nom de son arrière-grand-mère, qu'elle écrivait en minuscules pour que l'attention se porte sur ses idées plutôt que sur sa personne.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ne suis-je pas une femme ?&lt;/em&gt; (1981), elle montre que les femmes noires ont été oubliées à la fois par le mouvement féministe, dominé par des femmes blanches de classe moyenne, et par le mouvement pour les droits civiques, dominé par des hommes. Elle  &lt;a href="https://www.youtube.com/watch?v=pCwMdHBSQgM" title=" bell hooks, un féminisme anticapitaliste et intersectionnel par META "&gt;développe l'idée &lt;/a&gt; que le sexisme, le racisme et l'exploitation économique forment un même système de domination, qu'elle appelle le « patriarcat capitaliste suprémaciste blanc ».&lt;/p&gt; &lt;p&gt;Ses idées ont profondément influencé ce que l'on appelle aujourd'hui l'intersectionnalité, c'est-à-dire l'étude de la manière dont différentes formes de discrimination se croisent et se renforcent. Elle écrivait dans un style simple et direct, refusant le jargon universitaire, pour que ses livres soient lus au-delà des cercles savants. Elle a aussi consacré plusieurs ouvrages à l'amour, qu'elle considérait comme une force politique capable de transformer la société.&lt;/p&gt; &lt;p&gt;Elle a écrit une quarantaine de livres, sur le féminisme, l'amour, les médias, la culture populaire et l'éducation. Dans &lt;em&gt;Apprendre à transgresser&lt;/em&gt; (1994), inspirée par Paulo Freire, elle défend une pédagogie de la liberté où l'enseignement devient une pratique d'émancipation. Pour elle, le féminisme n'est pas une guerre contre les hommes mais un mouvement pour mettre fin à toute forme de domination, porté par une « éthique de l'amour ».&lt;/p&gt;    &lt;audio controls title="Lire bell hooks aujourd’hui par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23875-15.11.2023-ITEMA_23552434-2023C49162S0319-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
 </t>
         </is>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="H60" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="I59" s="1"/>
-      <c r="J59" s="2" t="s">
+      <c r="I60" s="1"/>
+      <c r="J60" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K59" s="1" t="inlineStr">
+      <c r="K60" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Féminisme ; Wokisme</t>
         </is>
       </c>
-      <c r="L59" s="2" t="s">
+      <c r="L60" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="M59" s="1" t="s">
+      <c r="M60" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="N59" s="1" t="s">
+      <c r="N60" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O59" s="1" t="n">
+      <c r="O60" s="1" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0">
+    <row r="61" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0">
         <v>1535</v>
       </c>
-      <c r="B60" s="0" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1616</t>
         </is>
       </c>
-      <c r="C60" s="0" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">vers 1535 – vers 1616</t>
         </is>
       </c>
-      <c r="D60" s="0" t="inlineStr">
+      <c r="D61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Felipe GUAMÁN POMA de Ayala</t>
         </is>
       </c>
-      <c r="E60" s="0" t="inlineStr">
+      <c r="E61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Felipe_Guam%C3%A1n_Poma_de_Ayala" title=" Wikipedia"&gt;Felipe GUAMÁN POMA de Ayala&lt;/a&gt; est un noble andin de langue quechua, auteur de l’un des documents les plus extraordinaires de l’époque coloniale. Né dans la province de Lucanas, au Pérou, peu après la conquête espagnole, il descend par sa mère d’une lignée liée aux souverains de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_inca" title=" Wikipedia"&gt;Empire inca&lt;/a&gt;. Élevé parmi les Espagnols, il apprend leur langue, se fait chrétien et travaille comme interprète auprès d’un prêtre chargé d’extirper les « idolâtries », puis auprès de juges de Huamanga, avant d’être dépouillé de ses terres et banni vers 1600.&lt;/p&gt; &lt;p&gt;Il parcourt alors les Andes pendant des années et rédige, vers 1615, une lettre de près de 1 200 pages adressée au roi d’Espagne Philippe III : la &lt;em&gt;Nouvelle Chronique et bon gouvernement&lt;/em&gt;. Ses quelque 400 dessins à la plume racontent l’histoire des Incas, le calendrier, les travaux des champs, puis les abus des colons : prêtres, corregidors et propriétaires qui exploitent, volent et maltraitent les Indiens. Il y décrit un « monde à l’envers » (&lt;em&gt;mundo al revés&lt;/em&gt;), où l’ordre juste a été renversé par la conquête.&lt;/p&gt; &lt;p&gt;Il ne réclame pas le départ des Espagnols, mais un « bon gouvernement » : que les Andins se gouvernent eux-mêmes sous l’autorité lointaine du roi, et que les colons qui abusent soient chassés des villages. Il défend aussi la valeur de la civilisation andine, qui connaissait selon lui la justice et un ordre moral bien avant l’arrivée des Européens. Le manuscrit, qui n’atteignit sans doute jamais le roi, dormit pendant trois siècles avant d’être découvert en 1908 à la Bibliothèque royale de Copenhague. Il est aujourd’hui une source majeure sur le monde andin et l’une des premières critiques de la colonisation écrites par un colonisé.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F60" s="0"/>
-      <c r="G60" s="0"/>
-      <c r="H60" s="0" t="inlineStr">
+      <c r="F61" s="0"/>
+      <c r="G61" s="0"/>
+      <c r="H61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/guamanpoma-mini.webp</t>
         </is>
       </c>
-      <c r="I60" s="0"/>
-      <c r="J60" s="0" t="inlineStr">
+      <c r="I61" s="0"/>
+      <c r="J61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
-      <c r="K60" s="0" t="inlineStr">
+      <c r="K61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Anticolonialisme</t>
         </is>
       </c>
-      <c r="L60" s="0" t="inlineStr">
+      <c r="L61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">chroniqueur andin, auteur d’une immense lettre illustrée au roi d’Espagne dénonçant la colonisation du Pérou.</t>
         </is>
       </c>
-      <c r="M60" s="0"/>
-      <c r="N60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="O60" s="1">
-        <v>2</v>
-      </c>
-      <c r="P60" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Péruvienne</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1">
-        <v>1853</v>
-      </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1895</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1853 – 1895</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">José MARTÍ</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Mart%C3%AD" title=" Wikipedia"&gt;José MARTÍ&lt;/a&gt; est le grand penseur de l’indépendance cubaine et l’une des voix majeures de l’Amérique latine. Né à La Havane de parents espagnols, il est arrêté à seize ans pour ses idées indépendantistes et condamné aux travaux forcés dans une carrière, avant d’être déporté en Espagne, où il étudie le droit et la philosophie à Saragosse. Il vit ensuite au Mexique, au Guatemala et au Venezuela, puis s’installe en 1881 à New York, où il passe près de quinze ans comme journaliste, diplomate et organisateur de l’exil cubain. Il y écrit, pour de grands journaux d’Amérique latine, des chroniques sur la vie nord-américaine.&lt;/p&gt; &lt;p&gt;Dans son essai &lt;em&gt;Notre Amérique&lt;/em&gt; (1891), il appelle les nations latino-américaines à se penser à partir de leur propre réalité, métisse, indienne, noire et paysanne, plutôt qu’en copiant l’Europe ou les États-Unis : « Le gouvernement doit naître du pays. » Il y affirme aussi : « Il n’y a pas de haine des races, parce qu’il n’y a pas de races. » Observateur lucide de la puissance nord-américaine, il met en garde contre les ambitions des États-Unis sur Cuba et sur tout le continent.&lt;/p&gt; &lt;p&gt;Poète novateur, l’un des fondateurs du modernisme hispanique, il écrit les &lt;em&gt;Vers simples&lt;/em&gt; (1891), dont certains forment les paroles de la célèbre chanson &lt;em&gt;Guantanamera&lt;/em&gt;, et une revue pour les enfants, &lt;em&gt;L’Âge d’or&lt;/em&gt;. En 1892, il fonde le Parti révolutionnaire cubain et prépare la &lt;a href="https://fr.wikipedia.org/wiki/Guerre_d%27ind%C3%A9pendance_cubaine" title=" Wikipedia"&gt;guerre d’indépendance&lt;/a&gt;. Débarqué à Cuba avec les insurgés, il est tué au combat à Dos Ríos le 19 mai 1895. Il est considéré à Cuba comme le héros national et « l’Apôtre » de l’indépendance.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/marti-mini.webp</t>
-        </is>
-      </c>
-      <c r="I61" s="1"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">politique ; esthetique</t>
-        </is>
-      </c>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">poète et penseur de l’indépendance cubaine, auteur de « Notre Amérique », héros national de Cuba.</t>
-        </is>
-      </c>
+      <c r="M61" s="0"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
@@ -4936,54 +4933,55 @@
       <c r="O61" s="1">
         <v>2</v>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cubaine</t>
+      <c r="P61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>
     <row r="62" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1">
-        <v>1921</v>
+        <v>1853</v>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1997</t>
+          <t xml:space="preserve">1895</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921 – 1997</t>
+          <t xml:space="preserve">1853 – 1895</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paulo FREIRE</t>
+          <t xml:space="preserve">José MARTÍ</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paulo_Freire" title=" Wikipedia"&gt;Paulo FREIRE&lt;/a&gt; est un pédagogue et philosophe brésilien, l’un des penseurs de l’éducation les plus lus au monde. Né à Recife, dans le Nordeste, il connaît la faim pendant la crise des années 1930, ce qui le marque pour toute sa vie. Formé au droit et à la philosophie, lecteur de Marx comme des penseurs chrétiens, il se consacre à l’&lt;a href="https://fr.wikipedia.org/wiki/Alphab%C3%A9tisation" title=" Wikipedia"&gt;alphabétisation&lt;/a&gt; des adultes pauvres. En 1963, à Angicos, sa méthode permet à 300 travailleurs agricoles d’apprendre à lire et à écrire en une quarantaine d’heures.&lt;/p&gt; &lt;p&gt;Sa méthode part des « mots générateurs » tirés de la vie des apprenants, comme la brique, la terre ou le salaire, et fait de la lecture une prise de conscience : apprendre à lire le mot, c’est apprendre à lire le monde. Après le coup d’État militaire de 1964, il est emprisonné puis contraint à un exil de seize ans. Au Chili, il écrit &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_des_opprim%C3%A9s" title=" Wikipedia"&gt;&lt;em&gt;Pédagogie des opprimés&lt;/em&gt;&lt;/a&gt; (1968), où il critique l’éducation « bancaire », qui dépose des savoirs dans des élèves passifs comme on remplit un coffre, et lui oppose une éducation par le dialogue, où maître et élèves cherchent ensemble.&lt;/p&gt; &lt;p&gt;« Personne n’éduque autrui, personne ne s’éduque seul, les hommes s’éduquent ensemble par l’intermédiaire du monde. » L’éducation n’est jamais neutre : elle maintient l’oppression ou aide les opprimés à s’en libérer, sans devenir à leur tour oppresseurs. Rentré au Brésil en 1980, il dirige l’éducation de la ville de São Paulo. Son œuvre est à l’origine de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_critique" title=" Wikipedia"&gt;pédagogie critique&lt;/a&gt;, et il a été proclamé en 2012 patron de l’éducation brésilienne.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Mart%C3%AD" title=" Wikipedia"&gt;José MARTÍ&lt;/a&gt; est le grand penseur de l’indépendance cubaine et l’une des voix majeures de l’Amérique latine. Né à La Havane de parents espagnols, il est arrêté à seize ans pour ses idées indépendantistes et condamné aux travaux forcés dans une carrière, avant d’être déporté en Espagne, où il étudie le droit et la philosophie à Saragosse. Il vit ensuite au Mexique, au Guatemala et au Venezuela, puis s’installe en 1881 à New York, où il passe près de quinze ans comme journaliste, diplomate et organisateur de l’exil cubain. Il y écrit, pour de grands journaux d’Amérique latine, des chroniques sur la vie nord-américaine.&lt;/p&gt; &lt;p&gt;Dans son essai &lt;em&gt;Notre Amérique&lt;/em&gt; (1891), il appelle les nations latino-américaines à se penser à partir de leur propre réalité, métisse, indienne, noire et paysanne, plutôt qu’en copiant l’Europe ou les États-Unis : « Le gouvernement doit naître du pays. » Il y affirme aussi : « Il n’y a pas de haine des races, parce qu’il n’y a pas de races. » Observateur lucide de la puissance nord-américaine, il met en garde contre les ambitions des États-Unis sur Cuba et sur tout le continent.&lt;/p&gt; &lt;p&gt;Poète novateur, l’un des fondateurs du modernisme hispanique, il écrit les &lt;em&gt;Vers simples&lt;/em&gt; (1891), dont certains forment les paroles de la célèbre chanson &lt;em&gt;Guantanamera&lt;/em&gt;, et une revue pour les enfants, &lt;em&gt;L’Âge d’or&lt;/em&gt;. En 1892, il fonde le Parti révolutionnaire cubain et prépare la &lt;a href="https://fr.wikipedia.org/wiki/Guerre_d%27ind%C3%A9pendance_cubaine" title=" Wikipedia"&gt;guerre d’indépendance&lt;/a&gt;. Débarqué à Cuba avec les insurgés, il est tué au combat à Dos Ríos le 19 mai 1895. Il est considéré à Cuba comme le héros national et « l’Apôtre » de l’indépendance.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/freire-mini.webp</t>
-        </is>
-      </c>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/marti-mini.webp</t>
+        </is>
+      </c>
+      <c r="I62" s="1"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">politique ; esthetique</t>
         </is>
       </c>
       <c r="K62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Marxisme ; Théologie de la libération</t>
+          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pédagogue brésilien, auteur de Pédagogie des opprimés, penseur de l’éducation comme pratique de la liberté.</t>
+          <t xml:space="preserve">poète et penseur de l’indépendance cubaine, auteur de « Notre Amérique », héros national de Cuba.</t>
         </is>
       </c>
       <c r="N62" s="1" t="inlineStr">
@@ -4992,56 +4990,56 @@
         </is>
       </c>
       <c r="O62" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brésilienne</t>
+          <t xml:space="preserve">Cubaine</t>
         </is>
       </c>
     </row>
     <row r="63" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1">
-        <v>1882</v>
+        <v>1921</v>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">1997</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882 – 1959</t>
+          <t xml:space="preserve">1921 – 1997</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">José VASCONCELOS</t>
+          <t xml:space="preserve">Paulo FREIRE</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Vasconcelos" title=" Wikipedia"&gt;José VASCONCELOS&lt;/a&gt; est un philosophe, écrivain et homme politique mexicain, l’un des grands éducateurs de l’Amérique latine. Né à Oaxaca, avocat, il fonde en 1909 avec Antonio Caso et Alfonso Reyes l’Ateneo de la Juventud, cercle de jeunes intellectuels qui rejette le positivisme officiel du régime de Porfirio Díaz. Il prend part à la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_mexicaine" title=" Wikipedia"&gt;révolution mexicaine&lt;/a&gt; aux côtés de Francisco Madero. Recteur de l’université nationale en 1920, il lui donne sa devise, toujours en usage : « Par ma race parlera l’esprit. »&lt;/p&gt; &lt;p&gt;Ministre de l’Éducation de 1921 à 1924, il mène une véritable croisade pour instruire le peuple : écoles rurales, missions culturelles dans les villages, bibliothèques, éditions populaires des grands classiques. Il commande aussi aux peintres &lt;a href="https://fr.wikipedia.org/wiki/Diego_Rivera" title=" Wikipedia"&gt;Diego Rivera&lt;/a&gt; et José Clemente Orozco les fresques murales qui racontent l’histoire du Mexique sur les murs des bâtiments publics. Il est surnommé le « maître de la jeunesse d’Amérique ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Race cosmique&lt;/em&gt; (1925), il prophétise que l’Amérique latine, terre de tous les mélanges, verra naître une « cinquième race », synthèse de toutes les autres, porteuse d’une civilisation de l’amour et de la beauté. Sa philosophie, un « monisme esthétique », voit dans l’émotion esthétique la forme la plus haute de connaissance. Battu en 1929 dans une élection présidentielle qu’il juge truquée, il s’exile, puis évolue vers un conservatisme catholique, au point de manifester en 1940 des sympathies pour l’Allemagne nazie. Il meurt à Mexico en 1959.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paulo_Freire" title=" Wikipedia"&gt;Paulo FREIRE&lt;/a&gt; est un pédagogue et philosophe brésilien, l’un des penseurs de l’éducation les plus lus au monde. Né à Recife, dans le Nordeste, il connaît la faim pendant la crise des années 1930, ce qui le marque pour toute sa vie. Formé au droit et à la philosophie, lecteur de Marx comme des penseurs chrétiens, il se consacre à l’&lt;a href="https://fr.wikipedia.org/wiki/Alphab%C3%A9tisation" title=" Wikipedia"&gt;alphabétisation&lt;/a&gt; des adultes pauvres. En 1963, à Angicos, sa méthode permet à 300 travailleurs agricoles d’apprendre à lire et à écrire en une quarantaine d’heures.&lt;/p&gt; &lt;p&gt;Sa méthode part des « mots générateurs » tirés de la vie des apprenants, comme la brique, la terre ou le salaire, et fait de la lecture une prise de conscience : apprendre à lire le mot, c’est apprendre à lire le monde. Après le coup d’État militaire de 1964, il est emprisonné puis contraint à un exil de seize ans. Au Chili, il écrit &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_des_opprim%C3%A9s" title=" Wikipedia"&gt;&lt;em&gt;Pédagogie des opprimés&lt;/em&gt;&lt;/a&gt; (1968), où il critique l’éducation « bancaire », qui dépose des savoirs dans des élèves passifs comme on remplit un coffre, et lui oppose une éducation par le dialogue, où maître et élèves cherchent ensemble.&lt;/p&gt; &lt;p&gt;« Personne n’éduque autrui, personne ne s’éduque seul, les hommes s’éduquent ensemble par l’intermédiaire du monde. » L’éducation n’est jamais neutre : elle maintient l’oppression ou aide les opprimés à s’en libérer, sans devenir à leur tour oppresseurs. Rentré au Brésil en 1980, il dirige l’éducation de la ville de São Paulo. Son œuvre est à l’origine de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_critique" title=" Wikipedia"&gt;pédagogie critique&lt;/a&gt;, et il a été proclamé en 2012 patron de l’éducation brésilienne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/vasconcelos-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/freire-mini.webp</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; politique</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="K63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monisme ; Spiritualisme</t>
+          <t xml:space="preserve">Humanisme ; Marxisme ; Théologie de la libération</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et ministre mexicain de l’Éducation, auteur de La Race cosmique, penseur du métissage.</t>
+          <t xml:space="preserve">pédagogue brésilien, auteur de Pédagogie des opprimés, penseur de l’éducation comme pratique de la liberté.</t>
         </is>
       </c>
       <c r="N63" s="1" t="inlineStr">
@@ -5050,66 +5048,61 @@
         </is>
       </c>
       <c r="O63" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mexicaine</t>
+          <t xml:space="preserve">Brésilienne</t>
         </is>
       </c>
     </row>
     <row r="64" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1">
-        <v>1907</v>
+        <v>1882</v>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1972</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1907 – 1972</t>
+          <t xml:space="preserve">1882 – 1959</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abraham Joshua HESCHEL</t>
+          <t xml:space="preserve">José VASCONCELOS</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abraham_Joshua_Heschel" title=" Wikipedia"&gt;Abraham Joshua HESCHEL&lt;/a&gt; est un rabbin, théologien et philosophe juif, l’une des grandes voix religieuses du XXe siècle. Né à Varsovie dans une illustre famille du &lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;hassidisme&lt;/a&gt;, il étudie la philosophie à Berlin, où il soutient une thèse sur les prophètes d’Israël. Expulsé d’Allemagne vers la Pologne en 1938, il parvient à quitter Varsovie quelques semaines avant l’invasion allemande et gagne Londres, puis les États-Unis. Sa mère et ses sœurs sont assassinées pendant la Shoah. Il enseigne à partir de 1946 au Séminaire théologique juif de New York.&lt;/p&gt; &lt;p&gt;Pour Heschel, la religion commence par l’« étonnement radical » devant le monde, qui précède toute réflexion. Contre l’idée d’un Dieu impassible des philosophes, il parle du « pathos divin » : le Dieu des prophètes est concerné par le sort des hommes et souffre de l’injustice. La question n’est pas seulement de savoir si l’homme cherche Dieu, mais de comprendre que &lt;em&gt;Dieu est en quête de l’homme&lt;/em&gt;, titre de son livre de 1955. Dans &lt;em&gt;Les Bâtisseurs du temps&lt;/em&gt; (1951), il présente le &lt;a href="https://fr.wikipedia.org/wiki/Shabbat" title=" Wikipedia"&gt;shabbat&lt;/a&gt; comme « une cathédrale dans le temps » : le judaïsme sanctifie des moments plutôt que des lieux. Il consacre aussi un grand livre aux prophètes, témoins de la passion de Dieu pour la justice.&lt;/p&gt; &lt;p&gt;Sa foi le conduit à l’action. En 1965, il marche de Selma à Montgomery aux côtés de Martin Luther King et dira : « J’avais l’impression que mes jambes priaient. » Il s’oppose à la guerre du Vietnam et contribue au dialogue entre juifs et chrétiens lors du concile Vatican II. Il meurt à New York en 1972.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Vasconcelos" title=" Wikipedia"&gt;José VASCONCELOS&lt;/a&gt; est un philosophe, écrivain et homme politique mexicain, l’un des grands éducateurs de l’Amérique latine. Né à Oaxaca, avocat, il fonde en 1909 avec Antonio Caso et Alfonso Reyes l’Ateneo de la Juventud, cercle de jeunes intellectuels qui rejette le positivisme officiel du régime de Porfirio Díaz. Il prend part à la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_mexicaine" title=" Wikipedia"&gt;révolution mexicaine&lt;/a&gt; aux côtés de Francisco Madero. Recteur de l’université nationale en 1920, il lui donne sa devise, toujours en usage : « Par ma race parlera l’esprit. »&lt;/p&gt; &lt;p&gt;Ministre de l’Éducation de 1921 à 1924, il mène une véritable croisade pour instruire le peuple : écoles rurales, missions culturelles dans les villages, bibliothèques, éditions populaires des grands classiques. Il commande aussi aux peintres &lt;a href="https://fr.wikipedia.org/wiki/Diego_Rivera" title=" Wikipedia"&gt;Diego Rivera&lt;/a&gt; et José Clemente Orozco les fresques murales qui racontent l’histoire du Mexique sur les murs des bâtiments publics. Il est surnommé le « maître de la jeunesse d’Amérique ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Race cosmique&lt;/em&gt; (1925), il prophétise que l’Amérique latine, terre de tous les mélanges, verra naître une « cinquième race », synthèse de toutes les autres, porteuse d’une civilisation de l’amour et de la beauté. Sa philosophie, un « monisme esthétique », voit dans l’émotion esthétique la forme la plus haute de connaissance. Battu en 1929 dans une élection présidentielle qu’il juge truquée, il s’exile, puis évolue vers un conservatisme catholique, au point de manifester en 1940 des sympathies pour l’Allemagne nazie. Il meurt à Mexico en 1959.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/heschel-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vasconcelos-mini.webp</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; ethique</t>
+          <t xml:space="preserve">esthetique ; politique</t>
         </is>
       </c>
       <c r="K64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Existentialisme ; Mysticisme ; Hassidisme</t>
+          <t xml:space="preserve">Monisme ; Spiritualisme</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rabbin et philosophe juif, penseur du « pathos divin » et du shabbat, militant des droits civiques.</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">philosophe et ministre mexicain de l’Éducation, auteur de La Race cosmique, penseur du métissage.</t>
         </is>
       </c>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">occident</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="O64" s="1">
@@ -5117,57 +5110,62 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Américaine</t>
+          <t xml:space="preserve">Mexicaine</t>
         </is>
       </c>
     </row>
     <row r="65" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1">
-        <v>1914</v>
+        <v>1907</v>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998</t>
+          <t xml:space="preserve">1972</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914 – 1998</t>
+          <t xml:space="preserve">1907 – 1972</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octavio PAZ</t>
+          <t xml:space="preserve">Abraham Joshua HESCHEL</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Octavio_Paz" title=" Wikipedia"&gt;Octavio PAZ&lt;/a&gt; est un poète, essayiste et diplomate mexicain, prix Nobel de littérature en 1990. Né à Mexico dans une famille marquée par la révolution, son père ayant été le représentant d’Emiliano Zapata aux États-Unis, il soutient les républicains pendant la guerre d’Espagne, puis rompt avec le communisme après l’assassinat de Trotski. Diplomate à Paris après la guerre, il y fréquente les surréalistes et André Breton.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Labyrinthe_de_la_solitude" title=" Wikipedia"&gt;&lt;em&gt;Le Labyrinthe de la solitude&lt;/em&gt;&lt;/a&gt; (1950), il interroge l’identité mexicaine : derrière les masques de la politesse et la violence des fêtes se cache une solitude née de l’histoire, celle d’un peuple issu de la conquête, qui a renié à la fois son passé indien et son passé espagnol. Il y évoque la figure de la &lt;a href="https://fr.wikipedia.org/wiki/La_Malinche" title=" Wikipedia"&gt;Malinche&lt;/a&gt;, compagne indienne de Cortés, symbole ambigu de l’origine métisse du pays. Mais cette solitude est aussi celle de l’homme moderne, et la poésie, l’amour et la fête sont des moyens de la dépasser. Dans &lt;em&gt;L’Arc et la Lyre&lt;/em&gt; (1956), il fait de la poésie une expérience de communion qui révèle l’homme à lui-même.&lt;/p&gt; &lt;p&gt;Ambassadeur du Mexique en Inde de 1962 à 1968, il découvre les philosophies et l’art de l’Orient, qui nourrissent sa poésie. Il démissionne après le &lt;a href="https://fr.wikipedia.org/wiki/Massacre_de_Tlatelolco" title=" Wikipedia"&gt;massacre de Tlatelolco&lt;/a&gt;, où des centaines d’étudiants sont tués par l’armée en 1968. Critique des totalitarismes de droite comme de gauche, il fonde la revue &lt;em&gt;Vuelta&lt;/em&gt; et consacre un grand livre à la poétesse et penseuse Juana Inés de la Cruz. Il meurt à Mexico en 1998, à quatre-vingt-quatre ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abraham_Joshua_Heschel" title=" Wikipedia"&gt;Abraham Joshua HESCHEL&lt;/a&gt; est un rabbin, théologien et philosophe juif, l’une des grandes voix religieuses du XXe siècle. Né à Varsovie dans une illustre famille du &lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;hassidisme&lt;/a&gt;, il étudie la philosophie à Berlin, où il soutient une thèse sur les prophètes d’Israël. Expulsé d’Allemagne vers la Pologne en 1938, il parvient à quitter Varsovie quelques semaines avant l’invasion allemande et gagne Londres, puis les États-Unis. Sa mère et ses sœurs sont assassinées pendant la Shoah. Il enseigne à partir de 1946 au Séminaire théologique juif de New York.&lt;/p&gt; &lt;p&gt;Pour Heschel, la religion commence par l’« étonnement radical » devant le monde, qui précède toute réflexion. Contre l’idée d’un Dieu impassible des philosophes, il parle du « pathos divin » : le Dieu des prophètes est concerné par le sort des hommes et souffre de l’injustice. La question n’est pas seulement de savoir si l’homme cherche Dieu, mais de comprendre que &lt;em&gt;Dieu est en quête de l’homme&lt;/em&gt;, titre de son livre de 1955. Dans &lt;em&gt;Les Bâtisseurs du temps&lt;/em&gt; (1951), il présente le &lt;a href="https://fr.wikipedia.org/wiki/Shabbat" title=" Wikipedia"&gt;shabbat&lt;/a&gt; comme « une cathédrale dans le temps » : le judaïsme sanctifie des moments plutôt que des lieux. Il consacre aussi un grand livre aux prophètes, témoins de la passion de Dieu pour la justice.&lt;/p&gt; &lt;p&gt;Sa foi le conduit à l’action. En 1965, il marche de Selma à Montgomery aux côtés de Martin Luther King et dira : « J’avais l’impression que mes jambes priaient. » Il s’oppose à la guerre du Vietnam et contribue au dialogue entre juifs et chrétiens lors du concile Vatican II. Il meurt à New York en 1972.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/paz-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/heschel-mini.webp</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; politique</t>
+          <t xml:space="preserve">spiritualite ; ethique</t>
         </is>
       </c>
       <c r="K65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme</t>
+          <t xml:space="preserve">Existentialisme ; Mysticisme ; Hassidisme</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">poète et essayiste mexicain, prix Nobel 1990, auteur du Labyrinthe de la solitude.</t>
+          <t xml:space="preserve">rabbin et philosophe juif, penseur du « pathos divin » et du shabbat, militant des droits civiques.</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
       <c r="O65" s="1">
@@ -5175,52 +5173,52 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mexicaine</t>
+          <t xml:space="preserve">Américaine</t>
         </is>
       </c>
     </row>
     <row r="66" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1">
-        <v>1871</v>
+        <v>1914</v>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917</t>
+          <t xml:space="preserve">1998</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871 – 1917</t>
+          <t xml:space="preserve">1914 – 1998</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">José Enrique RODÓ</t>
+          <t xml:space="preserve">Octavio PAZ</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Enrique_Rod%C3%B3" title=" Wikipedia"&gt;José Enrique RODÓ&lt;/a&gt; est un écrivain et essayiste uruguayen, l’un des grands maîtres à penser de l’Amérique latine au début du XXe siècle. Né à Montevideo, il doit interrompre ses études après la ruine de sa famille, se forme largement seul et devient professeur de littérature à l’université de Montevideo, puis député. Correspondant de &lt;a href="https://fr.wikipedia.org/wiki/Rub%C3%A9n_Dar%C3%ADo" title=" Wikipedia"&gt;Rubén Darío&lt;/a&gt;, il est le principal théoricien du modernisme, le grand mouvement de renouvellement de la littérature hispano-américaine.&lt;/p&gt; &lt;p&gt;Son essai &lt;em&gt;Ariel&lt;/em&gt; (1900), écrit deux ans après la victoire des États-Unis sur l’Espagne à Cuba, prend la forme d’un dernier cours donné par un vieux maître, Prospero, à ses élèves. Empruntant les personnages de &lt;em&gt;La Tempête&lt;/em&gt; de Shakespeare, il oppose Ariel, l’esprit, la beauté, le désintéressement, à Caliban, la matière, l’utilité, les appétits. Il met en garde la jeunesse latino-américaine contre l’utilitarisme et la « nordomanie », la fascination pour le modèle des États-Unis, puissant mais tourné vers le seul profit.&lt;/p&gt; &lt;p&gt;Rodó invite les jeunes à cultiver toutes les facultés de l’esprit, à préserver un temps libre pour la pensée et la beauté, et à construire une démocratie qui élève chacun au lieu de niveler par le bas. Le livre connut un immense succès et inspira tout un courant, l’« arielisme ». Plus tard, des penseurs comme Roberto Fernández Retamar ont renversé le symbole en faisant de Caliban la figure du colonisé. Dans &lt;em&gt;Motifs de Protée&lt;/em&gt; (1909), il médite sur la transformation continuelle de soi. Rodó meurt à Palerme en 1917, au cours d’un voyage en Europe.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Octavio_Paz" title=" Wikipedia"&gt;Octavio PAZ&lt;/a&gt; est un poète, essayiste et diplomate mexicain, prix Nobel de littérature en 1990. Né à Mexico dans une famille marquée par la révolution, son père ayant été le représentant d’Emiliano Zapata aux États-Unis, il soutient les républicains pendant la guerre d’Espagne, puis rompt avec le communisme après l’assassinat de Trotski. Diplomate à Paris après la guerre, il y fréquente les surréalistes et André Breton.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Labyrinthe_de_la_solitude" title=" Wikipedia"&gt;&lt;em&gt;Le Labyrinthe de la solitude&lt;/em&gt;&lt;/a&gt; (1950), il interroge l’identité mexicaine : derrière les masques de la politesse et la violence des fêtes se cache une solitude née de l’histoire, celle d’un peuple issu de la conquête, qui a renié à la fois son passé indien et son passé espagnol. Il y évoque la figure de la &lt;a href="https://fr.wikipedia.org/wiki/La_Malinche" title=" Wikipedia"&gt;Malinche&lt;/a&gt;, compagne indienne de Cortés, symbole ambigu de l’origine métisse du pays. Mais cette solitude est aussi celle de l’homme moderne, et la poésie, l’amour et la fête sont des moyens de la dépasser. Dans &lt;em&gt;L’Arc et la Lyre&lt;/em&gt; (1956), il fait de la poésie une expérience de communion qui révèle l’homme à lui-même.&lt;/p&gt; &lt;p&gt;Ambassadeur du Mexique en Inde de 1962 à 1968, il découvre les philosophies et l’art de l’Orient, qui nourrissent sa poésie. Il démissionne après le &lt;a href="https://fr.wikipedia.org/wiki/Massacre_de_Tlatelolco" title=" Wikipedia"&gt;massacre de Tlatelolco&lt;/a&gt;, où des centaines d’étudiants sont tués par l’armée en 1968. Critique des totalitarismes de droite comme de gauche, il fonde la revue &lt;em&gt;Vuelta&lt;/em&gt; et consacre un grand livre à la poétesse et penseuse Juana Inés de la Cruz. Il meurt à Mexico en 1998, à quatre-vingt-quatre ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/rodo-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/paz-mini.webp</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; ethique</t>
+          <t xml:space="preserve">esthetique ; politique</t>
         </is>
       </c>
       <c r="K66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Spiritualisme</t>
+          <t xml:space="preserve">Humanisme</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">essayiste uruguayen, auteur d’Ariel, maître à penser de la jeunesse latino-américaine.</t>
+          <t xml:space="preserve">poète et essayiste mexicain, prix Nobel 1990, auteur du Labyrinthe de la solitude.</t>
         </is>
       </c>
       <c r="N66" s="1" t="inlineStr">
@@ -5233,52 +5231,52 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uruguayenne</t>
+          <t xml:space="preserve">Mexicaine</t>
         </is>
       </c>
     </row>
     <row r="67" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1">
-        <v>1922</v>
+        <v>1871</v>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1979</t>
+          <t xml:space="preserve">1917</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922 – 1979</t>
+          <t xml:space="preserve">1871 – 1917</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodolfo KUSCH</t>
+          <t xml:space="preserve">José Enrique RODÓ</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Rodolfo_Kusch" title=" Wikipedia (es)"&gt;Rodolfo KUSCH&lt;/a&gt; est un philosophe et anthropologue argentin qui a cherché à fonder une philosophie à partir de la pensée indigène et populaire de l’Amérique. Né à Buenos Aires de parents allemands, il étudie la philosophie à l’université de Buenos Aires, enseigne l’esthétique et écrit aussi pour le théâtre, notamment sur le tango. Persécuté pour ses sympathies péronistes après 1955, il part pour la Bolivie et le Pérou, puis s’installe dans le nord-ouest de l’Argentine, à Maimará, dans la province de Jujuy.&lt;/p&gt; &lt;p&gt;Au contact des communautés &lt;a href="https://fr.wikipedia.org/wiki/Quechuas" title=" Wikipedia"&gt;quechuas&lt;/a&gt; et &lt;a href="https://fr.wikipedia.org/wiki/Aymaras" title=" Wikipedia"&gt;aymaras&lt;/a&gt; des Andes, il mène de longues enquêtes de terrain, dont il tire &lt;em&gt;L’Amérique profonde&lt;/em&gt; (1962) et &lt;em&gt;La Pensée indigène et populaire en Amérique&lt;/em&gt; (1970). Il y oppose deux attitudes. Celle de l’Occident, l’« être », qui veut dominer le monde, le transformer et accumuler. Et celle de l’Amérique indienne, l’« être là » ou le simple « se tenir » (en espagnol &lt;em&gt;estar&lt;/em&gt;), qui accepte l’incertitude du monde, ses forces et ses menaces, et cherche à vivre en équilibre avec lui.&lt;/p&gt; &lt;p&gt;Pour Kusch, les classes moyennes des villes, qui se veulent européennes, vivent dans la peur de cette « Amérique profonde » qu’elles refoulent. Penser en Amérique, c’est accepter cette part indienne et populaire au lieu de la mépriser. Son œuvre, longtemps marginale, a nourri la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt; et les pensées décoloniales latino-américaines, et elle est aujourd’hui redécouverte. Il parle même de « phagocytose » : la culture populaire finirait par absorber ce que la modernité importée croit lui imposer. Il meurt en 1979 à Maimará, à cinquante-sept ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Enrique_Rod%C3%B3" title=" Wikipedia"&gt;José Enrique RODÓ&lt;/a&gt; est un écrivain et essayiste uruguayen, l’un des grands maîtres à penser de l’Amérique latine au début du XXe siècle. Né à Montevideo, il doit interrompre ses études après la ruine de sa famille, se forme largement seul et devient professeur de littérature à l’université de Montevideo, puis député. Correspondant de &lt;a href="https://fr.wikipedia.org/wiki/Rub%C3%A9n_Dar%C3%ADo" title=" Wikipedia"&gt;Rubén Darío&lt;/a&gt;, il est le principal théoricien du modernisme, le grand mouvement de renouvellement de la littérature hispano-américaine.&lt;/p&gt; &lt;p&gt;Son essai &lt;em&gt;Ariel&lt;/em&gt; (1900), écrit deux ans après la victoire des États-Unis sur l’Espagne à Cuba, prend la forme d’un dernier cours donné par un vieux maître, Prospero, à ses élèves. Empruntant les personnages de &lt;em&gt;La Tempête&lt;/em&gt; de Shakespeare, il oppose Ariel, l’esprit, la beauté, le désintéressement, à Caliban, la matière, l’utilité, les appétits. Il met en garde la jeunesse latino-américaine contre l’utilitarisme et la « nordomanie », la fascination pour le modèle des États-Unis, puissant mais tourné vers le seul profit.&lt;/p&gt; &lt;p&gt;Rodó invite les jeunes à cultiver toutes les facultés de l’esprit, à préserver un temps libre pour la pensée et la beauté, et à construire une démocratie qui élève chacun au lieu de niveler par le bas. Le livre connut un immense succès et inspira tout un courant, l’« arielisme ». Plus tard, des penseurs comme Roberto Fernández Retamar ont renversé le symbole en faisant de Caliban la figure du colonisé. Dans &lt;em&gt;Motifs de Protée&lt;/em&gt; (1909), il médite sur la transformation continuelle de soi. Rodó meurt à Palerme en 1917, au cours d’un voyage en Europe.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/kusch-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rodo-mini.webp</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
+          <t xml:space="preserve">esthetique ; ethique</t>
         </is>
       </c>
       <c r="K67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen Vivir (cosmovision andine) ; Philosophie de la libération</t>
+          <t xml:space="preserve">Humanisme ; Spiritualisme</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et anthropologue argentin, penseur de l’« Amérique profonde » et de la pensée indigène et populaire.</t>
+          <t xml:space="preserve">essayiste uruguayen, auteur d’Ariel, maître à penser de la jeunesse latino-américaine.</t>
         </is>
       </c>
       <c r="N67" s="1" t="inlineStr">
@@ -5291,52 +5289,52 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Argentine</t>
+          <t xml:space="preserve">Uruguayenne</t>
         </is>
       </c>
     </row>
     <row r="68" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974</t>
+          <t xml:space="preserve">1979</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925 – 1974</t>
+          <t xml:space="preserve">1922 – 1979</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Augusto SALAZAR BONDY</t>
+          <t xml:space="preserve">Rodolfo KUSCH</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Augusto_Salazar_Bondy" title=" Wikipedia (es)"&gt;Augusto SALAZAR BONDY&lt;/a&gt; est un philosophe et éducateur péruvien, l’une des figures fondatrices de la philosophie latino-américaine de la libération. Né à Lima, frère cadet de l’écrivain Sebastián Salazar Bondy, il étudie à l’université San Marcos, puis au Mexique auprès de José Gaos et de Leopoldo Zea, et à Paris, où il suit les cours de Jean Wahl, Jean Hyppolite et Gaston Bachelard. Professeur d’éthique à San Marcos, il écrit une grande histoire des idées au Pérou contemporain.&lt;/p&gt; &lt;p&gt;En 1968, il publie &lt;em&gt;Existe-t-il une philosophie de notre Amérique ?&lt;/em&gt;, qui provoque un vif débat avec Leopoldo Zea. Sa réponse est dure : jusqu’ici, il n’existe pas de philosophie latino-américaine authentique, mais seulement des imitations des courants européens, adoptés tour à tour sans être vraiment pensés. Ce n’est pas un manque de talent : c’est la conséquence de la domination et du sous-développement, qui produisent une culture dépendante et « aliénée », incapable de se penser elle-même.&lt;/p&gt; &lt;p&gt;Une philosophie authentique ne pourra naître qu’en prenant pour objet cette situation de domination, et en contribuant à la transformer. La philosophie devient ainsi une tâche de libération, comme le développera la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt;. Engagé dans la réforme de l’éducation sous le gouvernement péruvien de la fin des années 1960, il défend une école qui forme des personnes libres et critiques. Il meurt prématurément à Lima en 1974, à quarante-huit ans. Ses idées ont notamment inspiré Enrique Dussel.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Rodolfo_Kusch" title=" Wikipedia (es)"&gt;Rodolfo KUSCH&lt;/a&gt; est un philosophe et anthropologue argentin qui a cherché à fonder une philosophie à partir de la pensée indigène et populaire de l’Amérique. Né à Buenos Aires de parents allemands, il étudie la philosophie à l’université de Buenos Aires, enseigne l’esthétique et écrit aussi pour le théâtre, notamment sur le tango. Persécuté pour ses sympathies péronistes après 1955, il part pour la Bolivie et le Pérou, puis s’installe dans le nord-ouest de l’Argentine, à Maimará, dans la province de Jujuy.&lt;/p&gt; &lt;p&gt;Au contact des communautés &lt;a href="https://fr.wikipedia.org/wiki/Quechuas" title=" Wikipedia"&gt;quechuas&lt;/a&gt; et &lt;a href="https://fr.wikipedia.org/wiki/Aymaras" title=" Wikipedia"&gt;aymaras&lt;/a&gt; des Andes, il mène de longues enquêtes de terrain, dont il tire &lt;em&gt;L’Amérique profonde&lt;/em&gt; (1962) et &lt;em&gt;La Pensée indigène et populaire en Amérique&lt;/em&gt; (1970). Il y oppose deux attitudes. Celle de l’Occident, l’« être », qui veut dominer le monde, le transformer et accumuler. Et celle de l’Amérique indienne, l’« être là » ou le simple « se tenir » (en espagnol &lt;em&gt;estar&lt;/em&gt;), qui accepte l’incertitude du monde, ses forces et ses menaces, et cherche à vivre en équilibre avec lui.&lt;/p&gt; &lt;p&gt;Pour Kusch, les classes moyennes des villes, qui se veulent européennes, vivent dans la peur de cette « Amérique profonde » qu’elles refoulent. Penser en Amérique, c’est accepter cette part indienne et populaire au lieu de la mépriser. Son œuvre, longtemps marginale, a nourri la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt; et les pensées décoloniales latino-américaines, et elle est aujourd’hui redécouverte. Il parle même de « phagocytose » : la culture populaire finirait par absorber ce que la modernité importée croit lui imposer. Il meurt en 1979 à Maimará, à cinquante-sept ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/salazarbondy-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kusch-mini.webp</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
+          <t xml:space="preserve">Buen Vivir (cosmovision andine) ; Philosophie de la libération</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe péruvien, auteur d’Existe-t-il une philosophie de notre Amérique ?, penseur de la domination.</t>
+          <t xml:space="preserve">philosophe et anthropologue argentin, penseur de l’« Amérique profonde » et de la pensée indigène et populaire.</t>
         </is>
       </c>
       <c r="N68" s="1" t="inlineStr">
@@ -5349,52 +5347,52 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Péruvienne</t>
+          <t xml:space="preserve">Argentine</t>
         </is>
       </c>
     </row>
     <row r="69" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1">
-        <v>1839</v>
+        <v>1925</v>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">1974</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839 – 1903</t>
+          <t xml:space="preserve">1925 – 1974</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eugenio María de HOSTOS</t>
+          <t xml:space="preserve">Augusto SALAZAR BONDY</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Eugenio_Mar%C3%ADa_de_Hostos" title=" Wikipedia (en)"&gt;Eugenio María de HOSTOS&lt;/a&gt; est un philosophe, éducateur, sociologue et écrivain de &lt;a href="https://fr.wikipedia.org/wiki/Porto_Rico" title=" Wikipedia"&gt;Porto Rico&lt;/a&gt;, surnommé « le Grand Citoyen des Amériques ». Né à Mayagüez dans une famille aisée, il fait ses études en Espagne, où il étudie le droit et la philosophie à Madrid et publie en 1863 un roman, &lt;em&gt;Le Pèlerinage de Bayoán&lt;/em&gt;, qui évoque déjà le destin des Antilles. Déçu que la République espagnole refuse l’autonomie de Porto Rico, il quitte l’Espagne en 1869 pour se consacrer à l’indépendance des colonies antillaises.&lt;/p&gt; &lt;p&gt;Il rêve d’une Confédération des Antilles, réunissant Porto Rico, Cuba et la République dominicaine, et parcourt pour la défendre les États-Unis, le Pérou, le Chili, l’Argentine, le Brésil et le Venezuela. Partout, il fonde ou réforme des écoles. En République dominicaine, il crée en 1880 la première école normale, qui forme des instituteurs à une pédagogie scientifique et laïque. Au Chili, il plaide pour que les femmes aient accès à l’enseignement supérieur et aux professions savantes.&lt;/p&gt; &lt;p&gt;Sa &lt;em&gt;Morale sociale&lt;/em&gt; (1888), inspirée du &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt;, fonde les devoirs de l’individu non sur la religion, mais sur la raison et sur les liens qui l’unissent à la famille, à la société et à l’humanité ; l’éducation doit former des consciences libres et responsables. Après la guerre de 1898, qui fait passer Porto Rico sous domination américaine, il milite pour que l’île puisse décider elle-même de son avenir. Il laisse aussi un traité de sociologie, l’un des premiers d’Amérique latine. Il meurt en exil à Saint-Domingue en 1903.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Augusto_Salazar_Bondy" title=" Wikipedia (es)"&gt;Augusto SALAZAR BONDY&lt;/a&gt; est un philosophe et éducateur péruvien, l’une des figures fondatrices de la philosophie latino-américaine de la libération. Né à Lima, frère cadet de l’écrivain Sebastián Salazar Bondy, il étudie à l’université San Marcos, puis au Mexique auprès de José Gaos et de Leopoldo Zea, et à Paris, où il suit les cours de Jean Wahl, Jean Hyppolite et Gaston Bachelard. Professeur d’éthique à San Marcos, il écrit une grande histoire des idées au Pérou contemporain.&lt;/p&gt; &lt;p&gt;En 1968, il publie &lt;em&gt;Existe-t-il une philosophie de notre Amérique ?&lt;/em&gt;, qui provoque un vif débat avec Leopoldo Zea. Sa réponse est dure : jusqu’ici, il n’existe pas de philosophie latino-américaine authentique, mais seulement des imitations des courants européens, adoptés tour à tour sans être vraiment pensés. Ce n’est pas un manque de talent : c’est la conséquence de la domination et du sous-développement, qui produisent une culture dépendante et « aliénée », incapable de se penser elle-même.&lt;/p&gt; &lt;p&gt;Une philosophie authentique ne pourra naître qu’en prenant pour objet cette situation de domination, et en contribuant à la transformer. La philosophie devient ainsi une tâche de libération, comme le développera la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt;. Engagé dans la réforme de l’éducation sous le gouvernement péruvien de la fin des années 1960, il défend une école qui forme des personnes libres et critiques. Il meurt prématurément à Lima en 1974, à quarante-huit ans. Ses idées ont notamment inspiré Enrique Dussel.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/hostos-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/salazarbondy-mini.webp</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="K69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positivisme</t>
+          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">éducateur et penseur portoricain, apôtre d’une confédération des Antilles et d’une morale sociale laïque.</t>
+          <t xml:space="preserve">philosophe péruvien, auteur d’Existe-t-il une philosophie de notre Amérique ?, penseur de la domination.</t>
         </is>
       </c>
       <c r="N69" s="1" t="inlineStr">
@@ -5407,52 +5405,52 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portoricaine</t>
+          <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>
     <row r="70" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1">
-        <v>1925</v>
+        <v>1839</v>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925 – 2008</t>
+          <t xml:space="preserve">1839 – 1903</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orlando FALS BORDA</t>
+          <t xml:space="preserve">Eugenio María de HOSTOS</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Orlando_Fals_Borda" title=" Wikipedia (en)"&gt;Orlando FALS BORDA&lt;/a&gt; est un sociologue colombien, l’un des grands penseurs latino-américains des sciences sociales et le fondateur de la « recherche-action participative ». Né à Barranquilla, sur la côte caraïbe, formé aux États-Unis, il fonde en 1959 à l’Université nationale de Colombie, avec le prêtre Camilo Torres, l’une des premières facultés de sociologie d’Amérique latine. Son livre &lt;em&gt;La Violence en Colombie&lt;/em&gt; (1962), écrit avec Germán Guzmán et Eduardo Umaña, étudie pour la première fois la guerre civile qui ravage les campagnes.&lt;/p&gt; &lt;p&gt;Déçu par une sociologie qui observe les pauvres de l’extérieur sans rien changer à leur sort, il quitte l’université dans les années 1970 pour travailler avec les paysans et les communautés de la côte caraïbe. Il y développe la &lt;a href="https://fr.wikipedia.org/wiki/Recherche-action" title=" Wikipedia"&gt;recherche-action&lt;/a&gt; participative : le chercheur ne doit pas monopoliser le savoir ni imposer sa technique, mais travailler avec les communautés comme avec des partenaires et des co-chercheurs, recueillir leurs savoirs, leur mémoire et leurs récits, et partager les résultats sous une forme que tous peuvent comprendre.&lt;/p&gt; &lt;p&gt;La science n’est pas, selon lui, une affaire d’experts neutres : elle doit servir la transformation de la société et la libération des opprimés. Il parle d’une « subversion positive » qui conteste l’ordre injuste pour en construire un meilleur. Ses idées se sont répandues dans le monde entier, en éducation, en santé et en développement. Il participe aussi à l’Assemblée constituante qui rédige la Constitution colombienne de 1991. Il meurt à Bogotá en 2008.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Eugenio_Mar%C3%ADa_de_Hostos" title=" Wikipedia (en)"&gt;Eugenio María de HOSTOS&lt;/a&gt; est un philosophe, éducateur, sociologue et écrivain de &lt;a href="https://fr.wikipedia.org/wiki/Porto_Rico" title=" Wikipedia"&gt;Porto Rico&lt;/a&gt;, surnommé « le Grand Citoyen des Amériques ». Né à Mayagüez dans une famille aisée, il fait ses études en Espagne, où il étudie le droit et la philosophie à Madrid et publie en 1863 un roman, &lt;em&gt;Le Pèlerinage de Bayoán&lt;/em&gt;, qui évoque déjà le destin des Antilles. Déçu que la République espagnole refuse l’autonomie de Porto Rico, il quitte l’Espagne en 1869 pour se consacrer à l’indépendance des colonies antillaises.&lt;/p&gt; &lt;p&gt;Il rêve d’une Confédération des Antilles, réunissant Porto Rico, Cuba et la République dominicaine, et parcourt pour la défendre les États-Unis, le Pérou, le Chili, l’Argentine, le Brésil et le Venezuela. Partout, il fonde ou réforme des écoles. En République dominicaine, il crée en 1880 la première école normale, qui forme des instituteurs à une pédagogie scientifique et laïque. Au Chili, il plaide pour que les femmes aient accès à l’enseignement supérieur et aux professions savantes.&lt;/p&gt; &lt;p&gt;Sa &lt;em&gt;Morale sociale&lt;/em&gt; (1888), inspirée du &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt;, fonde les devoirs de l’individu non sur la religion, mais sur la raison et sur les liens qui l’unissent à la famille, à la société et à l’humanité ; l’éducation doit former des consciences libres et responsables. Après la guerre de 1898, qui fait passer Porto Rico sous domination américaine, il milite pour que l’île puisse décider elle-même de son avenir. Il laisse aussi un traité de sociologie, l’un des premiers d’Amérique latine. Il meurt en exil à Saint-Domingue en 1903.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/falsborda-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hostos-mini.webp</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; politique</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="K70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiers-mondisme</t>
+          <t xml:space="preserve">Positivisme</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sociologue colombien, fondateur de la recherche-action participative, penseur d’un savoir construit avec le peuple.</t>
+          <t xml:space="preserve">éducateur et penseur portoricain, apôtre d’une confédération des Antilles et d’une morale sociale laïque.</t>
         </is>
       </c>
       <c r="N70" s="1" t="inlineStr">
@@ -5465,62 +5463,57 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colombienne</t>
+          <t xml:space="preserve">Portoricaine</t>
         </is>
       </c>
     </row>
     <row r="71" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021</t>
+          <t xml:space="preserve">2008</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928 – 2021</t>
+          <t xml:space="preserve">1925 – 2008</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humberto MATURANA</t>
+          <t xml:space="preserve">Orlando FALS BORDA</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Humberto_Maturana" title=" Wikipedia"&gt;Humberto MATURANA&lt;/a&gt; est un biologiste et philosophe chilien, l’un des penseurs les plus originaux de la biologie de la connaissance. Né à Santiago, il étudie la médecine et la biologie au Chili, puis en Angleterre et à Harvard. Au Massachusetts Institute of Technology, il participe en 1959 à une étude devenue célèbre sur ce que l’œil de la grenouille transmet à son cerveau, qui montre que la perception n’est pas une simple copie du monde extérieur. Il fonde ensuite à l’université du Chili un laboratoire d’« épistémologie expérimentale ».&lt;/p&gt; &lt;p&gt;Avec son élève Francisco Varela, il propose au début des années 1970 le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, du grec « se produire soi-même » : un être vivant est un système qui produit et renouvelle sans cesse ses propres composants, et maintient ainsi sa propre organisation. La cellule en est le modèle. Le vivant n’est donc pas défini par ce qu’il contient, mais par cette manière de s’entretenir lui-même, en échange constant avec son milieu.&lt;/p&gt; &lt;p&gt;Il en tire une théorie de la connaissance : « Tout ce qui est dit est dit par un observateur. » Connaître n’est pas refléter un monde tout fait, mais une activité du vivant, qui fait émerger un monde à travers son action. Dans &lt;em&gt;L’Arbre de la connaissance&lt;/em&gt; (1984), écrit avec Varela, il montre aussi que le langage et la société naissent de la coordination entre les êtres, et que l’amour, l’acceptation de l’autre, est le fondement biologique de la vie sociale. Ses idées ont nourri le &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_%28%C3%A9pist%C3%A9mologie%29" title=" Wikipedia"&gt;constructivisme&lt;/a&gt;, la thérapie familiale et la théorie des systèmes sociaux de &lt;a href="https://fr.wikipedia.org/wiki/Niklas_Luhmann" title=" Wikipedia"&gt;Niklas Luhmann&lt;/a&gt;. Il meurt à Santiago en 2021.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Orlando_Fals_Borda" title=" Wikipedia (en)"&gt;Orlando FALS BORDA&lt;/a&gt; est un sociologue colombien, l’un des grands penseurs latino-américains des sciences sociales et le fondateur de la « recherche-action participative ». Né à Barranquilla, sur la côte caraïbe, formé aux États-Unis, il fonde en 1959 à l’Université nationale de Colombie, avec le prêtre Camilo Torres, l’une des premières facultés de sociologie d’Amérique latine. Son livre &lt;em&gt;La Violence en Colombie&lt;/em&gt; (1962), écrit avec Germán Guzmán et Eduardo Umaña, étudie pour la première fois la guerre civile qui ravage les campagnes.&lt;/p&gt; &lt;p&gt;Déçu par une sociologie qui observe les pauvres de l’extérieur sans rien changer à leur sort, il quitte l’université dans les années 1970 pour travailler avec les paysans et les communautés de la côte caraïbe. Il y développe la &lt;a href="https://fr.wikipedia.org/wiki/Recherche-action" title=" Wikipedia"&gt;recherche-action&lt;/a&gt; participative : le chercheur ne doit pas monopoliser le savoir ni imposer sa technique, mais travailler avec les communautés comme avec des partenaires et des co-chercheurs, recueillir leurs savoirs, leur mémoire et leurs récits, et partager les résultats sous une forme que tous peuvent comprendre.&lt;/p&gt; &lt;p&gt;La science n’est pas, selon lui, une affaire d’experts neutres : elle doit servir la transformation de la société et la libération des opprimés. Il parle d’une « subversion positive » qui conteste l’ordre injuste pour en construire un meilleur. Ses idées se sont répandues dans le monde entier, en éducation, en santé et en développement. Il participe aussi à l’Assemblée constituante qui rédige la Constitution colombienne de 1991. Il meurt à Bogotá en 2008.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/maturana-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/falsborda-mini.webp</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; metaphysique</t>
+          <t xml:space="preserve">epistemologie ; politique</t>
         </is>
       </c>
       <c r="K71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constructivisme</t>
+          <t xml:space="preserve">Tiers-mondisme</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">biologiste et philosophe chilien, inventeur avec Varela de l’autopoïèse, penseur de la connaissance comme fait biologique.</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
+          <t xml:space="preserve">sociologue colombien, fondateur de la recherche-action participative, penseur d’un savoir construit avec le peuple.</t>
+        </is>
+      </c>
+      <c r="N71" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="N71" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
         </is>
       </c>
       <c r="O71" s="1">
@@ -5528,37 +5521,37 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chilienne</t>
+          <t xml:space="preserve">Colombienne</t>
         </is>
       </c>
     </row>
     <row r="72" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1">
-        <v>1946</v>
+        <v>1928</v>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001</t>
+          <t xml:space="preserve">2021</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946 – 2001</t>
+          <t xml:space="preserve">1928 – 2021</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francisco VARELA</t>
+          <t xml:space="preserve">Humberto MATURANA</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_Varela" title=" Wikipedia"&gt;Francisco VARELA&lt;/a&gt; est un biologiste, neuroscientifique et philosophe chilien, l’un des fondateurs des sciences cognitives « incarnées ». Né à Talcahuano, élève d’Humberto Maturana, il soutient une thèse de biologie à Harvard, puis invente avec son maître le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, qui définit le vivant par sa capacité à se produire lui-même. Après le coup d’État de Pinochet en 1973, il doit s’exiler aux États-Unis. Il s’installe en France en 1986 et dirige jusqu’à sa mort une équipe de recherche au CNRS, à Paris.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Inscription corporelle de l’esprit&lt;/em&gt; (1991), écrit avec Evan Thompson et Eleanor Rosch, il critique l’idée que l’esprit serait un ordinateur qui traite des représentations d’un monde extérieur déjà donné. Il propose à la place l’« &lt;a href="https://fr.wikipedia.org/wiki/%C3%89naction" title=" Wikipedia"&gt;énaction&lt;/a&gt; » : la cognition est une action incarnée, par laquelle un être vivant fait émerger son monde à travers son corps, ses sens et ses gestes. Il fonde aussi la « neurophénoménologie », qui veut unir les mesures du cerveau et la description rigoureuse de l’expérience vécue, à la manière de Husserl et de Merleau-Ponty.&lt;/p&gt; &lt;p&gt;Pratiquant du bouddhisme tibétain depuis les années 1970, il voit dans la méditation une méthode précise pour explorer l’expérience. En 1987, il cofonde le &lt;a href="https://fr.wikipedia.org/wiki/Mind_and_Life_Institute" title=" Wikipedia"&gt;Mind and Life Institute&lt;/a&gt;, qui organise des rencontres entre scientifiques et le dalaï-lama. Il est l’un des inspirateurs de l’idée d’un esprit « incarné », aujourd’hui centrale en &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_l%27esprit" title=" Wikipedia"&gt;philosophie de l’esprit&lt;/a&gt;. Il meurt à Paris en 2001, à cinquante-quatre ans, d’une maladie du foie.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Humberto_Maturana" title=" Wikipedia"&gt;Humberto MATURANA&lt;/a&gt; est un biologiste et philosophe chilien, l’un des penseurs les plus originaux de la biologie de la connaissance. Né à Santiago, il étudie la médecine et la biologie au Chili, puis en Angleterre et à Harvard. Au Massachusetts Institute of Technology, il participe en 1959 à une étude devenue célèbre sur ce que l’œil de la grenouille transmet à son cerveau, qui montre que la perception n’est pas une simple copie du monde extérieur. Il fonde ensuite à l’université du Chili un laboratoire d’« épistémologie expérimentale ».&lt;/p&gt; &lt;p&gt;Avec son élève Francisco Varela, il propose au début des années 1970 le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, du grec « se produire soi-même » : un être vivant est un système qui produit et renouvelle sans cesse ses propres composants, et maintient ainsi sa propre organisation. La cellule en est le modèle. Le vivant n’est donc pas défini par ce qu’il contient, mais par cette manière de s’entretenir lui-même, en échange constant avec son milieu.&lt;/p&gt; &lt;p&gt;Il en tire une théorie de la connaissance : « Tout ce qui est dit est dit par un observateur. » Connaître n’est pas refléter un monde tout fait, mais une activité du vivant, qui fait émerger un monde à travers son action. Dans &lt;em&gt;L’Arbre de la connaissance&lt;/em&gt; (1984), écrit avec Varela, il montre aussi que le langage et la société naissent de la coordination entre les êtres, et que l’amour, l’acceptation de l’autre, est le fondement biologique de la vie sociale. Ses idées ont nourri le &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_%28%C3%A9pist%C3%A9mologie%29" title=" Wikipedia"&gt;constructivisme&lt;/a&gt;, la thérapie familiale et la théorie des systèmes sociaux de &lt;a href="https://fr.wikipedia.org/wiki/Niklas_Luhmann" title=" Wikipedia"&gt;Niklas Luhmann&lt;/a&gt;. Il meurt à Santiago en 2021.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/varela-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/maturana-mini.webp</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -5568,12 +5561,12 @@
       </c>
       <c r="K72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constructivisme ; Phénoménologie</t>
+          <t xml:space="preserve">Constructivisme</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">neurobiologiste et philosophe chilien, penseur de l’énaction et du dialogue entre sciences cognitives et bouddhisme.</t>
+          <t xml:space="preserve">biologiste et philosophe chilien, inventeur avec Varela de l’autopoïèse, penseur de la connaissance comme fait biologique.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5597,46 +5590,46 @@
     </row>
     <row r="73" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1">
-        <v>1868</v>
+        <v>1946</v>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963</t>
+          <t xml:space="preserve">2001</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868 – 1963</t>
+          <t xml:space="preserve">1946 – 2001</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">W. E. B. DU BOIS</t>
+          <t xml:space="preserve">Francisco VARELA</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/W._E._B._Du_Bois" title=" Wikipedia"&gt;W. E. B. DU BOIS&lt;/a&gt; (William Edward Burghardt Du Bois) est un sociologue, historien et militant africain-américain, l’un des plus grands penseurs américains du XXe siècle. Né en 1868 dans le Massachusetts, il étudie à Fisk, à Berlin, puis à Harvard, où il devient en 1895 le premier Africain-Américain à obtenir un doctorat. Son étude &lt;em&gt;The Philadelphia Negro&lt;/em&gt; (1899) est l’une des premières grandes enquêtes de sociologie empirique aux États-Unis.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Les_%C3%82mes_du_peuple_noir" title=" Wikipedia"&gt;&lt;em&gt;Les Âmes du peuple noir&lt;/em&gt;&lt;/a&gt; (1903), il affirme que « le problème du XXe siècle est le problème de la ligne de couleur ». Il y décrit la « double conscience » des Noirs américains : le sentiment de se voir toujours à travers les yeux d’un monde qui les méprise, d’être à la fois américain et noir, « deux âmes, deux pensées, deux combats inconciliables dans un seul corps sombre ». Dans &lt;em&gt;Black Reconstruction&lt;/em&gt; (1935), il réhabilitera le rôle des anciens esclaves dans l’histoire américaine d’après la guerre de Sécession. Il y critique aussi Booker T. Washington, qui conseillait aux Noirs d’accepter la ségrégation en échange du progrès économique.&lt;/p&gt; &lt;p&gt;En 1909, il est l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/National_Association_for_the_Advancement_of_Colored_People" title=" Wikipedia"&gt;NAACP&lt;/a&gt;, la grande organisation de défense des droits civiques, dont il dirige la revue &lt;em&gt;The Crisis&lt;/em&gt;. Il organise plusieurs congrès panafricains et devient le « père du &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; ». Proche du socialisme, persécuté pendant le maccarthysme, il s’installe à la fin de sa vie au &lt;a href="https://fr.wikipedia.org/wiki/Ghana" title=" Wikipedia"&gt;Ghana&lt;/a&gt;, à l’invitation de Kwame Nkrumah, et y meurt en 1963, à la veille de la marche sur Washington de Martin Luther King.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_Varela" title=" Wikipedia"&gt;Francisco VARELA&lt;/a&gt; est un biologiste, neuroscientifique et philosophe chilien, l’un des fondateurs des sciences cognitives « incarnées ». Né à Talcahuano, élève d’Humberto Maturana, il soutient une thèse de biologie à Harvard, puis invente avec son maître le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, qui définit le vivant par sa capacité à se produire lui-même. Après le coup d’État de Pinochet en 1973, il doit s’exiler aux États-Unis. Il s’installe en France en 1986 et dirige jusqu’à sa mort une équipe de recherche au CNRS, à Paris.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Inscription corporelle de l’esprit&lt;/em&gt; (1991), écrit avec Evan Thompson et Eleanor Rosch, il critique l’idée que l’esprit serait un ordinateur qui traite des représentations d’un monde extérieur déjà donné. Il propose à la place l’« &lt;a href="https://fr.wikipedia.org/wiki/%C3%89naction" title=" Wikipedia"&gt;énaction&lt;/a&gt; » : la cognition est une action incarnée, par laquelle un être vivant fait émerger son monde à travers son corps, ses sens et ses gestes. Il fonde aussi la « neurophénoménologie », qui veut unir les mesures du cerveau et la description rigoureuse de l’expérience vécue, à la manière de Husserl et de Merleau-Ponty.&lt;/p&gt; &lt;p&gt;Pratiquant du bouddhisme tibétain depuis les années 1970, il voit dans la méditation une méthode précise pour explorer l’expérience. En 1987, il cofonde le &lt;a href="https://fr.wikipedia.org/wiki/Mind_and_Life_Institute" title=" Wikipedia"&gt;Mind and Life Institute&lt;/a&gt;, qui organise des rencontres entre scientifiques et le dalaï-lama. Il est l’un des inspirateurs de l’idée d’un esprit « incarné », aujourd’hui centrale en &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_l%27esprit" title=" Wikipedia"&gt;philosophie de l’esprit&lt;/a&gt;. Il meurt à Paris en 2001, à cinquante-quatre ans, d’une maladie du foie.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/dubois-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/varela-mini.webp</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
         </is>
       </c>
       <c r="K73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan-africanisme</t>
+          <t xml:space="preserve">Constructivisme ; Phénoménologie</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sociologue et militant africain-américain, penseur de la « double conscience » et père du panafricanisme.</t>
+          <t xml:space="preserve">neurobiologiste et philosophe chilien, penseur de l’énaction et du dialogue entre sciences cognitives et bouddhisme.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5650,69 +5643,74 @@
         </is>
       </c>
       <c r="O73" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Américaine</t>
+          <t xml:space="preserve">Chilienne</t>
         </is>
       </c>
     </row>
     <row r="74" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1">
-        <v>1928</v>
+        <v>1868</v>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024</t>
+          <t xml:space="preserve">1963</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928 – 2024</t>
+          <t xml:space="preserve">1868 – 1963</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustavo GUTIÉRREZ</t>
+          <t xml:space="preserve">W. E. B. DU BOIS</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo GUTIÉRREZ&lt;/a&gt; est un prêtre et théologien péruvien, considéré comme le père de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;théologie de la libération&lt;/a&gt;. Né à Lima en 1928 dans un milieu modeste, il souffre adolescent d’une ostéomyélite qui le cloue longtemps au lit ; il lit alors beaucoup et commence des études de médecine pour devenir psychiatre. À vingt-quatre ans, il choisit la prêtrise et part étudier la philosophie et la psychologie à Louvain, puis la théologie à Lyon.&lt;/p&gt; &lt;p&gt;Ordonné prêtre en 1959, il devient vicaire dans un quartier pauvre de Lima, tout en enseignant à l’université catholique, et repense toute sa théologie au contact de ce peuple. En 1971, il publie &lt;em&gt;Théologie de la libération&lt;/em&gt;, traduit dans une vingtaine de langues. La pauvreté, écrit-il, n’est pas une fatalité mais le fruit d’injustices, et elle est contraire à la volonté de Dieu. La théologie est une « réflexion critique sur la pratique à la lumière de la Parole » : elle vient en second, après l’engagement aux côtés des pauvres. Le salut ne se joue pas seulement dans l’au-delà ; il touche toute l’existence, et la libération sociale et politique en fait partie, sans s’y réduire. Dans &lt;em&gt;Boire à son propre puits&lt;/em&gt; (1983), il montre que cet engagement est aussi une spiritualité, une manière de suivre le Christ.&lt;/p&gt; &lt;p&gt;Ses positions lui valent la méfiance de Rome dans les années 1980, sans condamnation. Entré chez les Dominicains en 1998, il enseigne dans de nombreuses universités d’Europe et des États-Unis. Le pape François le reçoit en 2013, signe de la réhabilitation de son œuvre, et l’« option préférentielle pour les pauvres » est devenue un principe de l’enseignement de l’Église. Il meurt à Lima en 2024, à quatre-vingt-seize ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/W._E._B._Du_Bois" title=" Wikipedia"&gt;W. E. B. DU BOIS&lt;/a&gt; (William Edward Burghardt Du Bois) est un sociologue, historien et militant africain-américain, l’un des plus grands penseurs américains du XXe siècle. Né en 1868 dans le Massachusetts, il étudie à Fisk, à Berlin, puis à Harvard, où il devient en 1895 le premier Africain-Américain à obtenir un doctorat. Son étude &lt;em&gt;The Philadelphia Negro&lt;/em&gt; (1899) est l’une des premières grandes enquêtes de sociologie empirique aux États-Unis.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Les_%C3%82mes_du_peuple_noir" title=" Wikipedia"&gt;&lt;em&gt;Les Âmes du peuple noir&lt;/em&gt;&lt;/a&gt; (1903), il affirme que « le problème du XXe siècle est le problème de la ligne de couleur ». Il y décrit la « double conscience » des Noirs américains : le sentiment de se voir toujours à travers les yeux d’un monde qui les méprise, d’être à la fois américain et noir, « deux âmes, deux pensées, deux combats inconciliables dans un seul corps sombre ». Dans &lt;em&gt;Black Reconstruction&lt;/em&gt; (1935), il réhabilitera le rôle des anciens esclaves dans l’histoire américaine d’après la guerre de Sécession. Il y critique aussi Booker T. Washington, qui conseillait aux Noirs d’accepter la ségrégation en échange du progrès économique.&lt;/p&gt; &lt;p&gt;En 1909, il est l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/National_Association_for_the_Advancement_of_Colored_People" title=" Wikipedia"&gt;NAACP&lt;/a&gt;, la grande organisation de défense des droits civiques, dont il dirige la revue &lt;em&gt;The Crisis&lt;/em&gt;. Il organise plusieurs congrès panafricains et devient le « père du &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; ». Proche du socialisme, persécuté pendant le maccarthysme, il s’installe à la fin de sa vie au &lt;a href="https://fr.wikipedia.org/wiki/Ghana" title=" Wikipedia"&gt;Ghana&lt;/a&gt;, à l’invitation de Kwame Nkrumah, et y meurt en 1963, à la veille de la marche sur Washington de Martin Luther King.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ggutierrez-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dubois-mini.webp</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; politique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="K74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie de la libération</t>
+          <t xml:space="preserve">Pan-africanisme</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prêtre et théologien péruvien, père de la théologie de la libération et de l’« option préférentielle pour les pauvres ».</t>
+          <t xml:space="preserve">sociologue et militant africain-américain, penseur de la « double conscience » et père du panafricanisme.</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
       <c r="O74" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Péruvienne</t>
+          <t xml:space="preserve">Américaine</t>
         </is>
       </c>
     </row>
@@ -5722,42 +5720,42 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018</t>
+          <t xml:space="preserve">2024</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928 – 2018</t>
+          <t xml:space="preserve">1928 – 2024</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aníbal QUIJANO</t>
+          <t xml:space="preserve">Gustavo GUTIÉRREZ</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal QUIJANO&lt;/a&gt; est un sociologue péruvien, l’un des grands penseurs latino-américains du XXe siècle et le fondateur de la pensée décoloniale. Né en 1928 à Yanama, dans les Andes péruviennes, il étudie à l’université de San Marcos, à Lima, où il enseigne ensuite la sociologie. Dans les années 1960 et 1970, il participe aux travaux de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_la_d%C3%A9pendance" title=" Wikipedia"&gt;théorie de la dépendance&lt;/a&gt;, qui explique le sous-développement de l’Amérique latine par sa place subordonnée dans l’économie mondiale, et étudie la condition des populations indiennes et métisses des villes.&lt;/p&gt; &lt;p&gt;En 1992, pour le cinquième centenaire de l’arrivée de Christophe Colomb, il publie l’article « Colonialité et modernité/rationalité », qui forge la notion de « colonialité du pouvoir ». La conquête de l’Amérique a donné naissance à la fois au capitalisme mondial et à une idée nouvelle, celle de « race », qui a permis de classer les peuples en supérieurs et inférieurs et de distribuer entre eux le travail : le salariat pour les Européens, le servage pour les Indiens, l’esclavage pour les Africains. Cette classification a survécu à l’indépendance des colonies : elle structure encore les rapports sociaux, le savoir et la manière dont chacun se perçoit. Quijano critique aussi l’« eurocentrisme », qui fait de l’histoire européenne le modèle de l’histoire universelle.&lt;/p&gt; &lt;p&gt;Professeur à l’université de Binghamton, aux États-Unis, il anime le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt; avec Walter Mignolo et Enrique Dussel. La philosophe argentine &lt;a href="https://fr.wikipedia.org/wiki/Mar%C3%ADa_Lugones" title=" Wikipedia"&gt;María Lugones&lt;/a&gt; a prolongé son concept dans celui de « colonialité du genre ». Il meurt à Lima en 2018.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo GUTIÉRREZ&lt;/a&gt; est un prêtre et théologien péruvien, considéré comme le père de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;théologie de la libération&lt;/a&gt;. Né à Lima en 1928 dans un milieu modeste, il souffre adolescent d’une ostéomyélite qui le cloue longtemps au lit ; il lit alors beaucoup et commence des études de médecine pour devenir psychiatre. À vingt-quatre ans, il choisit la prêtrise et part étudier la philosophie et la psychologie à Louvain, puis la théologie à Lyon.&lt;/p&gt; &lt;p&gt;Ordonné prêtre en 1959, il devient vicaire dans un quartier pauvre de Lima, tout en enseignant à l’université catholique, et repense toute sa théologie au contact de ce peuple. En 1971, il publie &lt;em&gt;Théologie de la libération&lt;/em&gt;, traduit dans une vingtaine de langues. La pauvreté, écrit-il, n’est pas une fatalité mais le fruit d’injustices, et elle est contraire à la volonté de Dieu. La théologie est une « réflexion critique sur la pratique à la lumière de la Parole » : elle vient en second, après l’engagement aux côtés des pauvres. Le salut ne se joue pas seulement dans l’au-delà ; il touche toute l’existence, et la libération sociale et politique en fait partie, sans s’y réduire. Dans &lt;em&gt;Boire à son propre puits&lt;/em&gt; (1983), il montre que cet engagement est aussi une spiritualité, une manière de suivre le Christ.&lt;/p&gt; &lt;p&gt;Ses positions lui valent la méfiance de Rome dans les années 1980, sans condamnation. Entré chez les Dominicains en 1998, il enseigne dans de nombreuses universités d’Europe et des États-Unis. Le pape François le reçoit en 2013, signe de la réhabilitation de son œuvre, et l’« option préférentielle pour les pauvres » est devenue un principe de l’enseignement de l’Église. Il meurt à Lima en 2024, à quatre-vingt-seize ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/quijano-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ggutierrez-mini.webp</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; epistemologie</t>
+          <t xml:space="preserve">spiritualite ; politique</t>
         </is>
       </c>
       <c r="K75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensée décoloniale</t>
+          <t xml:space="preserve">Théologie de la libération</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sociologue péruvien, inventeur de la « colonialité du pouvoir » et fondateur de la pensée décoloniale.</t>
+          <t xml:space="preserve">prêtre et théologien péruvien, père de la théologie de la libération et de l’« option préférentielle pour les pauvres ».</t>
         </is>
       </c>
       <c r="N75" s="1" t="inlineStr">
@@ -5765,7 +5763,9 @@
           <t xml:space="preserve">sud</t>
         </is>
       </c>
-      <c r="O75" s="1"/>
+      <c r="O75" s="1">
+        <v>2</v>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t xml:space="preserve">Péruvienne</t>
@@ -6147,16 +6147,16 @@
     <hyperlink ref="H41" r:id="rId26" display="https://www.laphilo.fr/pho/mrothbard-mini.webp"/>
     <hyperlink ref="H42" r:id="rId27" display="https://www.laphilo.fr/pho/ewiesel-mini.webp"/>
     <hyperlink ref="H43" r:id="rId28" display="https://www.laphilo.fr/pho/abracken-mini.webp"/>
-    <hyperlink ref="E44" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Rorty&quot; title=&quot; Wikipedia&quot;&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href=&quot;https://www.youtube.com/watch?v=lfx4Jag1ic4&quot;  title=&quot;Le pragmatisme : définition, exemples par le savoir partagé&quot;&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href=&quot;https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism&quot; title=&quot; a bas l'autorité par laviedesidees&quot;&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas &quot;vrais&quot; ou &quot;faux&quot;. &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales , on trouve  &lt;a href=&quot;https://www.youtube.com/watch?v=MgU0dXZ3umM&quot; title=&quot;L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli&quot;&gt;&quot; Contingence, ironie et solidarité &quot;&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans &quot; Achieving Our Country&quot; (1998),  il y appelle la gauche américaine à abandonner le &quot;culturalisme&quot; pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la &quot;post-vérité&quot;. Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; "/>
-    <hyperlink ref="E46" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Charles_Parsons_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Charles Dacre PARSONS&lt;/a&gt; était un philosophe américain connu pour ses travaux en philosophie des mathématiques et en philosophie de Kant. Il a enseigné à Columbia puis à Harvard, où il est devenu professeur émérite. Il s’est formé à Harvard, avec une thèse dirigée par Willard Van Orman Quine, ce qui le place au croisement de la logique, de la philosophie analytique et des fondements des mathématiques. Son parcours intellectuel a été marqué très tôt par la rigueur mathématique, puisqu’il avait d’abord étudié les mathématiques avant de se tourner vers la philosophie. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la philosophie des mathématiques, domaine dans lequel il a travaillé sur la nature des objets mathématiques, la logique, la preuve et l’interprétation constructive des mathématiques prédicatives. Il a aussi beaucoup écrit sur Frege, Gödel, Hilbert et Quine, en lisant ces auteurs à la fois comme philosophes et comme figures majeures des fondements. &lt;/p&gt; &lt;p&gt; Il n’était pas seulement un spécialiste de logique ; il a aussi produit des travaux importants sur Kant, montrant comment les questions de connaissance, d’expérience et de structure de l’esprit se relient aux mathématiques. Cette double compétence, en philosophie des mathématiques et en histoire de la philosophie, explique pourquoi il est souvent vu comme un auteur à la fois technique et très large dans ses intérêts.&lt;/p&gt; &lt;p&gt; Son influence est restée forte dans le monde anglophone, au point d’être décrit comme l’un des philosophes des mathématiques les plus importants de sa génération. En plus de ses livres et articles, il a aussi contribué à l’édition de textes posthumes de Gödel, ce qui a renforcé son rôle dans l’étude contemporaine des fondements des mathématiques. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="I46" r:id="rId31" display="https://www.laphilo.fr/photo/cparsons.webp"/>
-    <hyperlink ref="H48" r:id="rId32" display="https://www.laphilo.fr/pho/dihde-mini.webp"/>
-    <hyperlink ref="E50" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edward_Sa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Edward SAÏD&lt;/a&gt; était un intellectuel palestinien-américain, critique littéraire et professeur de littérature anglaise et comparée à l’université Columbia de New York. D’origine palestinienne et né à Jérusalem, il a grandi entre l’Égypte, les États-Unis et l’Europe, une expérience de déplacement qui a profondément marqué sa pensée sur l’identité, la colonisation et l’altérité.  &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est l’essai &lt;a href=&quot;https://www.youtube.com/watch?v=Ne4WRykmjhA&quot; title=&quot;Edward Said  Orientalisme par HD Doc&quot;&gt;L’Orientalisme : &lt;/a&gt;  L’Orient créé par l’Occident* (1978), considéré comme le texte fondateur des postcolonial studies. Dans cet ouvrage, Saïd montre que l’« Orient » n’est pas une réalité objective mais une invention de l’Occident : un discours façonné par des siècles de domination coloniale pour mieux contrôler et représenter l’Autre. &lt;/p&gt; &lt;p&gt; Pour lui, l’orientalisme est à la fois un savoir et un outil de pouvoir : il ne s’agit pas seulement de décrire l’Orient, mais de le hiérarchiser, de l’essentialiser et de le rendre  &lt;a href=&quot;https://www.youtube.com/watch?v=QBj-yWLnayM&quot; title=&quot;Edward Said writings on Orientalism par Middle East Eye&quot;&gt; inférieur à l’Occident. &lt;/a&gt; Il analyse quatre thèses principales : la domination politique et culturelle de l’Orient par l’Occident, la dépréciation de la langue arabe, la diabolisation de l’arabe et de l’islam, et la défense de la cause palestinienne. &lt;/p&gt; &lt;p&gt; Sa pensée articule critique littéraire, histoire, philosophie et sciences politiques, en s’inspirant notamment de Michel Foucault (discours–pouvoir) et de Jacques Derrida (déconstruction). Il montre que la violence du colonialisme n’est pas seulement matérielle (conquête, pillage), mais aussi épistémique : une violence de la raison qui classe, essentialise et dévalue les « Autres » de l’Occident. &lt;/p&gt; &lt;p&gt;  Intéressé par &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Edward-W-Said-1935-2003.html&quot; title=&quot;Edward Said par lesclesdumoyenorient&quot;&gt; l’engagement politique, &lt;/a&gt; il a aussi défendu la cause palestinienne et la légitimité des revendications d’autodétermination du peuple palestinien, tout en reconnaissance du droit à une patrie juive. Il rejetait le repli identitaire et prônait une vision universelle qui défend les différences et les droits, tissant des liens entre classicisme et excentricité, histoire et actualité. &lt;/p&gt;  &lt;audio controls title=&quot;Edward Said, une conscience morale par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-08.12.2017-ITEMA_21518070-2017C19327S0342-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &#10;&#10;&#10;"/>
-    <hyperlink ref="H50" r:id="rId34" display="https://laphilo.fr/pho/esaid-mini.webp"/>
-    <hyperlink ref="H51" r:id="rId35" display="https://www.laphilo.fr/pho/rmadams-mini.webp"/>
-    <hyperlink ref="E52" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Nozick&quot;  title=&quot; Wikipedia&quot;&gt;Robert NOZICK&lt;/a&gt; était un philosophe américain connu pour &lt;a href=&quot;https://www.youtube.com/watch?v=Q-t3cpFAk4o&quot;  title=&quot; Libertarianisme par Vadim Media&quot;&gt; son libertarianisme &lt;/a&gt; et sa critique des théories égalitaristes comme celle de John Rawls. Professeur à Harvard, il a marqué la philosophie politique, morale et épistémologique par son œuvre principale, Anarchie, État et utopie (1974), qui défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Minarchisme&quot;  title=&quot; Minarchisme par Wikipédia&quot;&gt; Etat Minimal. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il argue que seul l'État minimal, ou &quot;État gardien de nuit&quot;, est légitime, car il se limite à protéger les individus contre la force, la fraude et le vol, sans redistribuer les richesses. Il rejette l'anarcho-capitalisme en montrant, via des agences de protection privée, comment un État dominant émerge naturellement pour monopoliser la coercition légitime, justifié par le droit naturel à la personne. &lt;/p&gt; &lt;p&gt; Contrairement à la justice distributive de Rawls, il propose une théorie de l'entitlement : une acquisition initiale juste et des transferts volontaires rendent la distribution légitime, sans besoin d'égalisation par l'État. Toute intervention redistributive viole les droits individuels, traitant les personnes comme des moyens plutôt que des fins, en écho à Kant. &lt;/p&gt; &lt;p&gt; Dans Anarchie, État et utopie, Il réfute l'utilitarisme via l'expérience de pensée de la &lt;a href=&quot;https://www.youtube.com/watch?v=2FVwXaNWPQ0&quot;  title=&quot; La machine à expérience par Monsieur Phi&quot;&gt;&quot;machine à expérience&quot; :&lt;/a&gt;  même si elle offre un bonheur parfait et indistinguable de la réalité, les gens préfèrent vivre des actions réelles et façonner leur identité plutôt que des simulations. Cela prouve que le bonheur n'est pas le seul bien suprême. &lt;/p&gt; &lt;p&gt; Plus tard, dans Explications philosophiques (1981), il développe une théorie du suivi (tracking theory) en épistémologie, où la connaissance repose sur des conditionnels contrefactuels fiables, contournant le scepticisme sans justification traditionnelle. Son anti-coercitivisme intellectuel invite à une philosophie ouverte, non imposée. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Qui a peur des Libertariens par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-14.06.2022-ITEMA_23058436-2022C12410S0165-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;"/>
-    <hyperlink ref="H58" r:id="rId37" display="https://www.laphilo.fr/pho/imyoung-mini.webp"/>
-    <hyperlink ref="H59" r:id="rId38" display="https://www.laphilo.fr/pho/bhooks-mini.webp"/>
+    <hyperlink ref="E45" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Rorty&quot; title=&quot; Wikipedia&quot;&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href=&quot;https://www.youtube.com/watch?v=lfx4Jag1ic4&quot;  title=&quot;Le pragmatisme : définition, exemples par le savoir partagé&quot;&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href=&quot;https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism&quot; title=&quot; a bas l'autorité par laviedesidees&quot;&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas &quot;vrais&quot; ou &quot;faux&quot;. &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales , on trouve  &lt;a href=&quot;https://www.youtube.com/watch?v=MgU0dXZ3umM&quot; title=&quot;L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli&quot;&gt;&quot; Contingence, ironie et solidarité &quot;&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans &quot; Achieving Our Country&quot; (1998),  il y appelle la gauche américaine à abandonner le &quot;culturalisme&quot; pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la &quot;post-vérité&quot;. Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; "/>
+    <hyperlink ref="E47" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Charles_Parsons_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Charles Dacre PARSONS&lt;/a&gt; était un philosophe américain connu pour ses travaux en philosophie des mathématiques et en philosophie de Kant. Il a enseigné à Columbia puis à Harvard, où il est devenu professeur émérite. Il s’est formé à Harvard, avec une thèse dirigée par Willard Van Orman Quine, ce qui le place au croisement de la logique, de la philosophie analytique et des fondements des mathématiques. Son parcours intellectuel a été marqué très tôt par la rigueur mathématique, puisqu’il avait d’abord étudié les mathématiques avant de se tourner vers la philosophie. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la philosophie des mathématiques, domaine dans lequel il a travaillé sur la nature des objets mathématiques, la logique, la preuve et l’interprétation constructive des mathématiques prédicatives. Il a aussi beaucoup écrit sur Frege, Gödel, Hilbert et Quine, en lisant ces auteurs à la fois comme philosophes et comme figures majeures des fondements. &lt;/p&gt; &lt;p&gt; Il n’était pas seulement un spécialiste de logique ; il a aussi produit des travaux importants sur Kant, montrant comment les questions de connaissance, d’expérience et de structure de l’esprit se relient aux mathématiques. Cette double compétence, en philosophie des mathématiques et en histoire de la philosophie, explique pourquoi il est souvent vu comme un auteur à la fois technique et très large dans ses intérêts.&lt;/p&gt; &lt;p&gt; Son influence est restée forte dans le monde anglophone, au point d’être décrit comme l’un des philosophes des mathématiques les plus importants de sa génération. En plus de ses livres et articles, il a aussi contribué à l’édition de textes posthumes de Gödel, ce qui a renforcé son rôle dans l’étude contemporaine des fondements des mathématiques. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="I47" r:id="rId31" display="https://www.laphilo.fr/photo/cparsons.webp"/>
+    <hyperlink ref="H49" r:id="rId32" display="https://www.laphilo.fr/pho/dihde-mini.webp"/>
+    <hyperlink ref="E51" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edward_Sa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Edward SAÏD&lt;/a&gt; était un intellectuel palestinien-américain, critique littéraire et professeur de littérature anglaise et comparée à l’université Columbia de New York. D’origine palestinienne et né à Jérusalem, il a grandi entre l’Égypte, les États-Unis et l’Europe, une expérience de déplacement qui a profondément marqué sa pensée sur l’identité, la colonisation et l’altérité.  &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est l’essai &lt;a href=&quot;https://www.youtube.com/watch?v=Ne4WRykmjhA&quot; title=&quot;Edward Said  Orientalisme par HD Doc&quot;&gt;L’Orientalisme : &lt;/a&gt;  L’Orient créé par l’Occident* (1978), considéré comme le texte fondateur des postcolonial studies. Dans cet ouvrage, Saïd montre que l’« Orient » n’est pas une réalité objective mais une invention de l’Occident : un discours façonné par des siècles de domination coloniale pour mieux contrôler et représenter l’Autre. &lt;/p&gt; &lt;p&gt; Pour lui, l’orientalisme est à la fois un savoir et un outil de pouvoir : il ne s’agit pas seulement de décrire l’Orient, mais de le hiérarchiser, de l’essentialiser et de le rendre  &lt;a href=&quot;https://www.youtube.com/watch?v=QBj-yWLnayM&quot; title=&quot;Edward Said writings on Orientalism par Middle East Eye&quot;&gt; inférieur à l’Occident. &lt;/a&gt; Il analyse quatre thèses principales : la domination politique et culturelle de l’Orient par l’Occident, la dépréciation de la langue arabe, la diabolisation de l’arabe et de l’islam, et la défense de la cause palestinienne. &lt;/p&gt; &lt;p&gt; Sa pensée articule critique littéraire, histoire, philosophie et sciences politiques, en s’inspirant notamment de Michel Foucault (discours–pouvoir) et de Jacques Derrida (déconstruction). Il montre que la violence du colonialisme n’est pas seulement matérielle (conquête, pillage), mais aussi épistémique : une violence de la raison qui classe, essentialise et dévalue les « Autres » de l’Occident. &lt;/p&gt; &lt;p&gt;  Intéressé par &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Edward-W-Said-1935-2003.html&quot; title=&quot;Edward Said par lesclesdumoyenorient&quot;&gt; l’engagement politique, &lt;/a&gt; il a aussi défendu la cause palestinienne et la légitimité des revendications d’autodétermination du peuple palestinien, tout en reconnaissance du droit à une patrie juive. Il rejetait le repli identitaire et prônait une vision universelle qui défend les différences et les droits, tissant des liens entre classicisme et excentricité, histoire et actualité. &lt;/p&gt;  &lt;audio controls title=&quot;Edward Said, une conscience morale par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-08.12.2017-ITEMA_21518070-2017C19327S0342-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &#10;&#10;&#10;"/>
+    <hyperlink ref="H51" r:id="rId34" display="https://laphilo.fr/pho/esaid-mini.webp"/>
+    <hyperlink ref="H52" r:id="rId35" display="https://www.laphilo.fr/pho/rmadams-mini.webp"/>
+    <hyperlink ref="E53" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Nozick&quot;  title=&quot; Wikipedia&quot;&gt;Robert NOZICK&lt;/a&gt; était un philosophe américain connu pour &lt;a href=&quot;https://www.youtube.com/watch?v=Q-t3cpFAk4o&quot;  title=&quot; Libertarianisme par Vadim Media&quot;&gt; son libertarianisme &lt;/a&gt; et sa critique des théories égalitaristes comme celle de John Rawls. Professeur à Harvard, il a marqué la philosophie politique, morale et épistémologique par son œuvre principale, Anarchie, État et utopie (1974), qui défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Minarchisme&quot;  title=&quot; Minarchisme par Wikipédia&quot;&gt; Etat Minimal. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il argue que seul l'État minimal, ou &quot;État gardien de nuit&quot;, est légitime, car il se limite à protéger les individus contre la force, la fraude et le vol, sans redistribuer les richesses. Il rejette l'anarcho-capitalisme en montrant, via des agences de protection privée, comment un État dominant émerge naturellement pour monopoliser la coercition légitime, justifié par le droit naturel à la personne. &lt;/p&gt; &lt;p&gt; Contrairement à la justice distributive de Rawls, il propose une théorie de l'entitlement : une acquisition initiale juste et des transferts volontaires rendent la distribution légitime, sans besoin d'égalisation par l'État. Toute intervention redistributive viole les droits individuels, traitant les personnes comme des moyens plutôt que des fins, en écho à Kant. &lt;/p&gt; &lt;p&gt; Dans Anarchie, État et utopie, Il réfute l'utilitarisme via l'expérience de pensée de la &lt;a href=&quot;https://www.youtube.com/watch?v=2FVwXaNWPQ0&quot;  title=&quot; La machine à expérience par Monsieur Phi&quot;&gt;&quot;machine à expérience&quot; :&lt;/a&gt;  même si elle offre un bonheur parfait et indistinguable de la réalité, les gens préfèrent vivre des actions réelles et façonner leur identité plutôt que des simulations. Cela prouve que le bonheur n'est pas le seul bien suprême. &lt;/p&gt; &lt;p&gt; Plus tard, dans Explications philosophiques (1981), il développe une théorie du suivi (tracking theory) en épistémologie, où la connaissance repose sur des conditionnels contrefactuels fiables, contournant le scepticisme sans justification traditionnelle. Son anti-coercitivisme intellectuel invite à une philosophie ouverte, non imposée. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Qui a peur des Libertariens par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-14.06.2022-ITEMA_23058436-2022C12410S0165-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;"/>
+    <hyperlink ref="H59" r:id="rId37" display="https://www.laphilo.fr/pho/imyoung-mini.webp"/>
+    <hyperlink ref="H60" r:id="rId38" display="https://www.laphilo.fr/pho/bhooks-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2237,7 +2237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD81"/>
+  <dimension ref="A1:XFD88"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
@@ -6110,6 +6110,410 @@
       <c r="P81" t="inlineStr">
         <is>
           <t xml:space="preserve">Brésilienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1">
+        <v>1860</v>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1935</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1860 – 1935</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jane ADDAMS</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jane_Addams" title=" Wikipedia"&gt;Jane ADDAMS&lt;/a&gt; est une philosophe, sociologue et réformatrice sociale américaine. Née en 1860 à Cedarville, dans l’Illinois, fille d’un riche meunier et homme politique, elle fait partie de la première génération de femmes diplômées de l’université. Lors d’un voyage à Londres, elle découvre Toynbee Hall, une maison où des étudiants vivent parmi les pauvres pour les aider. En 1889, avec son amie Ellen Gates Starr, elle fonde à Chicago Hull House, dans un quartier d’immigrés.&lt;/p&gt; &lt;p&gt;Hull House devient un grand centre social, avec crèche, cours du soir, bibliothèque, théâtre et enquêtes sur les conditions de vie. Jane Addams y mène des combats contre le travail des enfants, pour les premiers tribunaux pour mineurs, pour la santé publique et pour le droit de vote des femmes. Amie de John Dewey, qui enseigne à Hull House, elle est une figure du &lt;a href="https://fr.wikipedia.org/wiki/Pragmatisme" title=" Wikipedia"&gt;pragmatisme&lt;/a&gt; : la connaissance doit naître de l’expérience partagée et servir à résoudre les problèmes réels. Dans &lt;em&gt;Démocratie et éthique sociale&lt;/em&gt; (1902), elle soutient que la démocratie n’est pas seulement un régime politique, mais une manière de vivre avec les autres, fondée sur la sympathie et la coopération.&lt;/p&gt; &lt;p&gt;Pacifiste, elle s’oppose à l’entrée des États-Unis dans la Première Guerre mondiale. Elle préside en 1915 le Congrès international des femmes à La Haye, puis la Ligue internationale des femmes pour la paix et la liberté. En 1931, elle est la première Américaine à recevoir le prix Nobel de la paix. Elle meurt à Chicago en 1935.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/addams-mini.webp</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="K82" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pragmatisme ; Féminisme ; Progressisme</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe pragmatiste et réformatrice sociale américaine, fondatrice de Hull House, prix Nobel de la paix.</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N82" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O82"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1">
+        <v>1863</v>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1931</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1863 – 1931</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">George Herbert MEAD</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Herbert_Mead" title=" Wikipedia"&gt;George Herbert MEAD&lt;/a&gt; est un philosophe, sociologue et psychologue américain. Né en 1863 dans le Massachusetts, fils d’un pasteur, il étudie à Harvard auprès de William James, puis en Allemagne, à Leipzig et à Berlin. En 1891, il rejoint John Dewey à l’université du Michigan, puis le suit en 1894 à Chicago, où il enseigne jusqu’à sa mort en 1931. Engagé dans les réformes sociales de la ville, il soutient Hull House, la maison de Jane Addams. Il publie peu : ses livres, comme &lt;em&gt;L’Esprit, le soi et la société&lt;/em&gt; (1934), sont tirés après sa mort des notes de ses étudiants.&lt;/p&gt; &lt;p&gt;Figure du &lt;a href="https://fr.wikipedia.org/wiki/Pragmatisme" title=" Wikipedia"&gt;pragmatisme&lt;/a&gt;, il montre que le soi n’est pas donné à la naissance : il se forme dans les échanges avec les autres. Tout commence par une « conversation de gestes », comme entre deux chiens qui se menacent. Le langage permet d’aller plus loin : en parlant, nous entendons ce que nous disons comme les autres l’entendent, et apprenons ainsi à nous voir de leur point de vue. L’enfant joue d’abord des rôles, la maman, le policier, puis participe à des jeux organisés, où il doit tenir compte de tous les autres à la fois. Il intériorise alors un « autrui généralisé », les attentes de toute la communauté.&lt;/p&gt; &lt;p&gt;Le soi a deux faces : le « moi », ce que les autres ont fait de nous, et le « je », notre réponse personnelle et créatrice. Ses idées sont à l’origine de l’« interactionnisme symbolique », un grand courant de la sociologie.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mead-mini.webp</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; ethique</t>
+        </is>
+      </c>
+      <c r="K83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pragmatisme ; Béhaviorisme</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe pragmatiste et psychologue social américain, pour qui le soi naît des relations avec autrui.</t>
+        </is>
+      </c>
+      <c r="N83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O83"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1">
+        <v>1877</v>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1925</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1877 – 1925</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">José INGENIEROS</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Ingenieros" title=" Wikipedia"&gt;José INGENIEROS&lt;/a&gt; est un médecin, psychiatre et philosophe argentin. Né à Palerme, en Italie, en 1877, sous le nom de Giuseppe Ingegnieri, il arrive enfant à Buenos Aires. Étudiant, il milite au Parti socialiste et fonde un journal révolutionnaire. Médecin, il dirige un institut de criminologie et publie des travaux de psychologie et de psychiatrie. Il fonde en 1915 la &lt;em&gt;Revue de philosophie&lt;/em&gt;, et soutient la Réforme universitaire de Córdoba en 1918, qui démocratise les universités d’Amérique latine. Il meurt à Buenos Aires en 1925.&lt;/p&gt; &lt;p&gt;Disciple du &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt;, il veut fonder la philosophie sur les sciences, en particulier la biologie et la psychologie. La morale n’a pas besoin des dogmes religieux : elle naît de l’expérience sociale et évolue avec elle, comme il l’explique dans &lt;em&gt;Vers une morale sans dogmes&lt;/em&gt; (1917). Il propose une métaphysique nouvelle, qui ne porte plus sur des vérités éternelles, mais sur ce qui échappe encore à l’expérience : elle doit rester ouverte et se corriger avec les progrès du savoir.&lt;/p&gt; &lt;p&gt;Son livre le plus célèbre, &lt;em&gt;L’Homme médiocre&lt;/em&gt; (1913), oppose l’idéaliste, qui imagine un monde meilleur et se bat pour lui, au médiocre, qui se contente d’imiter et de se soumettre. Il est devenu la lecture de générations d’étudiants latino-américains. À la fin de sa vie, il dénonce l’impérialisme des États-Unis et fonde en 1925 l’Union latino-américaine pour défendre l’unité du continent.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ingenieros-mini.webp</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; epistemologie ; politique</t>
+        </is>
+      </c>
+      <c r="K84" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positivisme ; Scientisme</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">médecin, psychiatre et philosophe argentin, auteur de L’Homme médiocre, maître à penser de la jeunesse latino-américaine.</t>
+        </is>
+      </c>
+      <c r="N84" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O84"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentine</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1">
+        <v>1922</v>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2012</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1922 – 2012</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arturo Andrés ROIG</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arturo_Andr%C3%A9s_Roig" title=" Wikipedia"&gt;Arturo Andrés ROIG&lt;/a&gt; est un philosophe et historien des idées argentin. Né à Mendoza en 1922, il étudie la philosophie à l’université de Cuyo, puis à la Sorbonne, et se consacre d’abord à la philosophie antique, en particulier à Platon. Il se tourne ensuite vers l’histoire des idées en Amérique latine. Chassé de l’université par la dictature militaire en 1975, il s’exile en Équateur, à Quito, où il enseigne jusqu’à son retour en Argentine en 1984. Il meurt à Mendoza en 2012.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Théorie et critique de la pensée latino-américaine&lt;/em&gt; (1981), il cherche à quelles conditions une philosophie latino-américaine est possible. Il reprend une idée de Hegel : la philosophie commence quand un peuple « se tient lui-même pour valable ». Il appelle cette condition l’« a priori anthropologique » : pour penser, il faut d’abord s’affirmer comme sujet, capable de dire « nous » et de juger sa propre histoire, au lieu de se voir à travers le regard de l’Europe. L’histoire des idées doit retrouver les moments où les peuples d’Amérique latine se sont ainsi affirmés, depuis les indépendances.&lt;/p&gt; &lt;p&gt;Il étudie aussi les discours, qui peuvent servir à dominer ou à libérer, et la « fonction utopique » du langage, qui ouvre l’avenir. Dans &lt;em&gt;Éthique du pouvoir et moralité de la protestation&lt;/em&gt; (2002), il défend une « morale de l’émergence », celle des opprimés qui refusent leur condition. Il est l’une des grandes figures de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/roig-mini.webp</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K85" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie de la libération</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et historien des idées argentin, théoricien d’une pensée latino-américaine qui s’affirme elle-même.</t>
+        </is>
+      </c>
+      <c r="N85" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O85"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentine</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1">
+        <v>1931</v>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2013</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1931 – 2013</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ronald DWORKIN</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ronald_Dworkin" title=" Wikipedia"&gt;Ronald DWORKIN&lt;/a&gt; est un philosophe du droit et de la politique américain. Né en 1931 dans le Massachusetts, il étudie à Harvard et à Oxford, puis travaille comme avocat à New York. Il enseigne à Yale, puis succède en 1969 à Herbert Hart à la chaire de philosophie du droit d’Oxford, tout en enseignant à l’université de New York, et plus tard à Londres. Grand débatteur, il intervient régulièrement dans la presse sur les grandes questions de son temps. Il meurt à Londres en 2013.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Prendre les droits au sérieux&lt;/em&gt; (1977), il critique le positivisme juridique de Hart, pour qui le droit n’est qu’un ensemble de règles posées par les autorités. Le droit contient aussi des principes moraux, comme « nul ne doit profiter de sa propre faute », que les juges doivent appliquer dans les cas difficiles. Les droits individuels sont des « atouts » : ils l’emportent sur les calculs d’utilité collective. Dans &lt;em&gt;L’Empire du droit&lt;/em&gt; (1986), il compare le juge à l’auteur d’un roman écrit à plusieurs mains, qui doit poursuivre l’histoire de façon cohérente : c’est le « droit comme intégrité ».&lt;/p&gt; &lt;p&gt;En philosophie politique, il défend un &lt;a href="https://fr.wikipedia.org/wiki/Lib%C3%A9ralisme" title=" Wikipedia"&gt;libéralisme&lt;/a&gt; égalitaire : l’État doit traiter tous ses citoyens avec une égale considération. Il propose une « égalité des ressources » : chacun doit être responsable de ses choix, mais non des handicaps et des malchances qu’il n’a pas choisis. Dans &lt;em&gt;Justice pour les hérissons&lt;/em&gt; (2011), il soutient l’unité de toutes les valeurs.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dworkin-mini.webp</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe du droit américain, pour qui les droits sont des « atouts » et le droit une question de principes.</t>
+        </is>
+      </c>
+      <c r="N86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O86">
+        <v>2</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1">
+        <v>1944</v>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1944 – 2020</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">María LUGONES</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mar%C3%ADa_Lugones" title=" Wikipedia"&gt;María LUGONES&lt;/a&gt; est une philosophe féministe argentine. Née en 1944 dans la pampa argentine, dans une famille pauvre, elle part étudier aux États-Unis, en Californie puis à l’université du Wisconsin, où elle soutient sa thèse de philosophie en 1978. Elle enseigne ensuite la philosophie, la littérature comparée et les études de genre à l’université de Binghamton, dans l’État de New York. Militante, elle participe à des projets d’éducation populaire auprès des communautés latino-américaines. Elle meurt en 2020.&lt;/p&gt; &lt;p&gt;Dans un article célèbre de 1987, elle décrit le « voyage entre les mondes » que vivent les femmes de couleur aux États-Unis, qui passent sans cesse d’une culture à une autre. Elle propose de transformer cette expérience en une manière d’aimer les autres : voyager dans leur monde avec une « perception aimante », en jouant, au lieu de les juger depuis le sien avec une « perception arrogante ». Dans &lt;em&gt;Pèlerinages&lt;/em&gt; (2003), elle montre que les oppressions de race, de classe et de genre sont inséparables et s’entremêlent.&lt;/p&gt; &lt;p&gt;Elle prolonge la pensée d’Aníbal Quijano sur la « colonialité du pouvoir » en élaborant la notion de « colonialité du genre ». La colonisation n’a pas seulement imposé une hiérarchie des races : elle a aussi imposé aux peuples colonisés un système de genre européen, fondé sur l’opposition stricte des hommes et des femmes et sur l’hétérosexualité, que bien des sociétés ne connaissaient pas. Elle appelle à un féminisme décolonial. Elle est une figure majeure de la &lt;a href="https://fr.wikipedia.org/wiki/%C3%89tudes_d%C3%A9coloniales" title=" Wikipedia"&gt;pensée décoloniale&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/lugones-mini.webp</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Féminisme ; Pensée décoloniale</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe féministe argentine, théoricienne de la « colonialité du genre ».</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O87"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentine</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1">
+        <v>1935</v>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2014</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1935 – 2014</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ernesto LACLAU</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ernesto_Laclau" title=" Wikipedia"&gt;Ernesto LACLAU&lt;/a&gt; est un philosophe et politologue argentin. Né à Buenos Aires en 1935, il étudie l’histoire et milite dans la gauche nationale argentine. En 1969, à l’invitation de l’historien Eric Hobsbawm, il part en Angleterre, à Oxford, puis enseigne à l’université d’Essex, où il fonde un programme de recherche sur l’idéologie et l’analyse du discours. Il partage sa vie et son travail avec la philosophe belge Chantal Mouffe. Il meurt à Séville en 2014.&lt;/p&gt; &lt;p&gt;Avec elle, il publie en 1985 &lt;em&gt;Hégémonie et stratégie socialiste&lt;/em&gt;, l’un des livres fondateurs du « post-marxisme ». Les classes sociales ne sont pas des acteurs politiques tout faits : les identités politiques sont construites par les discours. Il reprend à Gramsci la notion d’« hégémonie » : une force politique domine quand elle réussit à rassembler des revendications diverses autour d’un projet commun. Dans &lt;em&gt;Émancipation(s)&lt;/em&gt; (1996), il montre que ce rassemblement se fait autour de « signifiants vides », comme « justice » ou « peuple », assez larges pour que chacun y mette ses propres attentes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Raison populiste&lt;/em&gt; (2005), il refuse de voir le &lt;a href="https://fr.wikipedia.org/wiki/Populisme_%28politique%29" title=" Wikipedia"&gt;populisme&lt;/a&gt; comme une maladie de la démocratie. C’est une manière de faire de la politique : des demandes insatisfaites, très différentes, se relient en une « chaîne d’équivalences » et construisent un « peuple » opposé à ceux d’en haut, souvent autour d’un nom ou d’un chef. Ses idées ont inspiré des gouvernements et des partis de gauche en Amérique latine et en Europe.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/laclau-mini.webp</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="K88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post-structuralisme ; Populisme ; Marxisme</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe politique argentin, théoricien de l’hégémonie et de la « raison populiste ».</t>
+        </is>
+      </c>
+      <c r="N88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O88"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentine</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -2237,7 +2237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD88"/>
+  <dimension ref="A1:XFD90"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.06"/>
@@ -2547,12 +2547,14 @@
       <c r="C8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>54</v>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juan Bautista ALBERDI</t>
+        </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Juan_Bautista_Alberdi"   title=" Wikipedia"&gt;Juan Bautista ALBERTI&lt;/a&gt;    était un philosophe, écrivain et juriste argentin, père intellectuel de la Constitution argentine, un texte visionnaire qui a posé les bases d’un État moderne. C’est en Europe, où il voyage dans les années 1830, qu’il forge sa pensée. Il y découvre les idées libérales, le fédéralisme et l’importance d’une constitution solide. De retour en Amérique du Sud, il s’installe au Chili, où il observe avec inquiétude les luttes de pouvoir entre unitaires et fédéralistes en Argentine. &lt;/p&gt; &lt;p&gt; En 1852, après la chute de Rosas, Alberdi publie son œuvre majeure : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=SztYiPA63Xk" title="Biografías - Juan Bautista Alberdi "El Arquitecto de la Argentina Moderna" par PipaProfe"&gt;"Bases y puntos de partida para la organización política de la República Argentina"&lt;/a&gt;. Ce texte, rédigé depuis son exil chilien, devient la pierre angulaire de la future Constitution.  Ses propositions sont révolutionnaires pour l’époque car il propose un système fédéral équilibré, pour éviter les guerres civiles, la promotion de l’immigration européenne pour peupler et développer le pays et surtout la liberté de commerce et la séparation des pouvoirs. La Constitution de 1853 s’en inspire largement, et bien que modifiée depuis, elle reste le socle institutionnel de l’Argentine. &lt;/p&gt; &lt;p&gt; Pourtant, il ne fait pas l’unanimité. Ses idées libérales et son opposition à la centralisation de Buenos Aires le mettent en conflit avec des figures comme Bartolomé Mitre et Domingo Faustino Sarmiento. Quand la guerre de la Triple Alliance (1865-1870) éclate contre le Paraguay, il la dénonce comme une "guerre fratricide", ce qui le marginalise encore davantage. Il passe ses dernières années en Europe, loin des cercles du pouvoir. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Juan_Bautista_Alberdi"   title=" Wikipedia"&gt;Juan Bautista ALBERDI&lt;/a&gt;    était un philosophe, écrivain et juriste argentin, père intellectuel de la Constitution argentine, un texte visionnaire qui a posé les bases d’un État moderne. C’est en Europe, où il voyage dans les années 1830, qu’il forge sa pensée. Il y découvre les idées libérales, le fédéralisme et l’importance d’une constitution solide. De retour en Amérique du Sud, il s’installe au Chili, où il observe avec inquiétude les luttes de pouvoir entre unitaires et fédéralistes en Argentine. &lt;/p&gt; &lt;p&gt; En 1852, après la chute de Rosas, Alberdi publie son œuvre majeure : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=SztYiPA63Xk" title="Biografías - Juan Bautista Alberdi "El Arquitecto de la Argentina Moderna" par PipaProfe"&gt;"Bases y puntos de partida para la organización política de la República Argentina"&lt;/a&gt;. Ce texte, rédigé depuis son exil chilien, devient la pierre angulaire de la future Constitution.  Ses propositions sont révolutionnaires pour l’époque car il propose un système fédéral équilibré, pour éviter les guerres civiles, la promotion de l’immigration européenne pour peupler et développer le pays et surtout la liberté de commerce et la séparation des pouvoirs. La Constitution de 1853 s’en inspire largement, et bien que modifiée depuis, elle reste le socle institutionnel de l’Argentine. &lt;/p&gt; &lt;p&gt; Pourtant, il ne fait pas l’unanimité. Ses idées libérales et son opposition à la centralisation de Buenos Aires le mettent en conflit avec des figures comme Bartolomé Mitre et Domingo Faustino Sarmiento. Quand la guerre de la Triple Alliance (1865-1870) éclate contre le Paraguay, il la dénonce comme une "guerre fratricide", ce qui le marginalise encore davantage. Il passe ses dernières années en Europe, loin des cercles du pouvoir. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F8" s="7" t="s">
@@ -4148,6 +4150,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal QUIJANO&lt;/a&gt; est un sociologue péruvien, l’un des grands penseurs latino-américains du XXe siècle et le fondateur de la pensée décoloniale. Né en 1928 à Yanama, dans les Andes péruviennes, il étudie à l’université de San Marcos, à Lima, où il enseigne ensuite la sociologie. Dans les années 1960 et 1970, il participe aux travaux de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_la_d%C3%A9pendance" title=" Wikipedia"&gt;théorie de la dépendance&lt;/a&gt;, qui explique le sous-développement de l’Amérique latine par sa place subordonnée dans l’économie mondiale, et étudie la condition des populations indiennes et métisses des villes.&lt;/p&gt; &lt;p&gt;En 1992, pour le cinquième centenaire de l’arrivée de Christophe Colomb, il publie l’article « Colonialité et modernité/rationalité », qui forge la notion de « colonialité du pouvoir ». La conquête de l’Amérique a donné naissance à la fois au capitalisme mondial et à une idée nouvelle, celle de « race », qui a permis de classer les peuples en supérieurs et inférieurs et de distribuer entre eux le travail : le salariat pour les Européens, le servage pour les Indiens, l’esclavage pour les Africains. Cette classification a survécu à l’indépendance des colonies : elle structure encore les rapports sociaux, le savoir et la manière dont chacun se perçoit. Quijano critique aussi l’« eurocentrisme », qui fait de l’histoire européenne le modèle de l’histoire universelle.&lt;/p&gt; &lt;p&gt;Professeur à l’université de Binghamton, aux États-Unis, il anime le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt; avec Walter Mignolo et Enrique Dussel. La philosophe argentine &lt;a href="https://fr.wikipedia.org/wiki/Mar%C3%ADa_Lugones" title=" Wikipedia"&gt;María Lugones&lt;/a&gt; a prolongé son concept dans celui de « colonialité du genre ». Il meurt à Lima en 2018.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aibG8RehlTE</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Aníbal Quijano - Colonialidad del Poder" par Filo Errante</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/quijano-mini.webp</t>
@@ -4283,8 +4295,16 @@
       <c r="E47" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="F47" s="7"/>
-      <c r="G47" s="9"/>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OvpUxJQRAbw</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Charles Parsons Intuition and Reason | HUSSERL to GODEL | Mark van Atten" par The Van Leer Jerusalem Institute - מכון ון ליר בירושלים</t>
+        </is>
+      </c>
       <c r="H47" s="9" t="s">
         <v>396</v>
       </c>
@@ -4901,8 +4921,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Felipe_Guam%C3%A1n_Poma_de_Ayala" title=" Wikipedia"&gt;Felipe GUAMÁN POMA de Ayala&lt;/a&gt; est un noble andin de langue quechua, auteur de l’un des documents les plus extraordinaires de l’époque coloniale. Né dans la province de Lucanas, au Pérou, peu après la conquête espagnole, il descend par sa mère d’une lignée liée aux souverains de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_inca" title=" Wikipedia"&gt;Empire inca&lt;/a&gt;. Élevé parmi les Espagnols, il apprend leur langue, se fait chrétien et travaille comme interprète auprès d’un prêtre chargé d’extirper les « idolâtries », puis auprès de juges de Huamanga, avant d’être dépouillé de ses terres et banni vers 1600.&lt;/p&gt; &lt;p&gt;Il parcourt alors les Andes pendant des années et rédige, vers 1615, une lettre de près de 1 200 pages adressée au roi d’Espagne Philippe III : la &lt;em&gt;Nouvelle Chronique et bon gouvernement&lt;/em&gt;. Ses quelque 400 dessins à la plume racontent l’histoire des Incas, le calendrier, les travaux des champs, puis les abus des colons : prêtres, corregidors et propriétaires qui exploitent, volent et maltraitent les Indiens. Il y décrit un « monde à l’envers » (&lt;em&gt;mundo al revés&lt;/em&gt;), où l’ordre juste a été renversé par la conquête.&lt;/p&gt; &lt;p&gt;Il ne réclame pas le départ des Espagnols, mais un « bon gouvernement » : que les Andins se gouvernent eux-mêmes sous l’autorité lointaine du roi, et que les colons qui abusent soient chassés des villages. Il défend aussi la valeur de la civilisation andine, qui connaissait selon lui la justice et un ordre moral bien avant l’arrivée des Européens. Le manuscrit, qui n’atteignit sans doute jamais le roi, dormit pendant trois siècles avant d’être découvert en 1908 à la Bibliothèque royale de Copenhague. Il est aujourd’hui une source majeure sur le monde andin et l’une des premières critiques de la colonisation écrites par un colonisé.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F61" s="0"/>
-      <c r="G61" s="0"/>
+      <c r="F61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">__IaJh6gzA0</t>
+        </is>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"📌Felipe Guamán Poma de Ayala: HISTORIA desde su mirada al mundo andino y la conquista española | EP1" par Gestión Mundo</t>
+        </is>
+      </c>
       <c r="H61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/guamanpoma-mini.webp</t>
@@ -4963,6 +4991,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Mart%C3%AD" title=" Wikipedia"&gt;José MARTÍ&lt;/a&gt; est le grand penseur de l’indépendance cubaine et l’une des voix majeures de l’Amérique latine. Né à La Havane de parents espagnols, il est arrêté à seize ans pour ses idées indépendantistes et condamné aux travaux forcés dans une carrière, avant d’être déporté en Espagne, où il étudie le droit et la philosophie à Saragosse. Il vit ensuite au Mexique, au Guatemala et au Venezuela, puis s’installe en 1881 à New York, où il passe près de quinze ans comme journaliste, diplomate et organisateur de l’exil cubain. Il y écrit, pour de grands journaux d’Amérique latine, des chroniques sur la vie nord-américaine.&lt;/p&gt; &lt;p&gt;Dans son essai &lt;em&gt;Notre Amérique&lt;/em&gt; (1891), il appelle les nations latino-américaines à se penser à partir de leur propre réalité, métisse, indienne, noire et paysanne, plutôt qu’en copiant l’Europe ou les États-Unis : « Le gouvernement doit naître du pays. » Il y affirme aussi : « Il n’y a pas de haine des races, parce qu’il n’y a pas de races. » Observateur lucide de la puissance nord-américaine, il met en garde contre les ambitions des États-Unis sur Cuba et sur tout le continent.&lt;/p&gt; &lt;p&gt;Poète novateur, l’un des fondateurs du modernisme hispanique, il écrit les &lt;em&gt;Vers simples&lt;/em&gt; (1891), dont certains forment les paroles de la célèbre chanson &lt;em&gt;Guantanamera&lt;/em&gt;, et une revue pour les enfants, &lt;em&gt;L’Âge d’or&lt;/em&gt;. En 1892, il fonde le Parti révolutionnaire cubain et prépare la &lt;a href="https://fr.wikipedia.org/wiki/Guerre_d%27ind%C3%A9pendance_cubaine" title=" Wikipedia"&gt;guerre d’indépendance&lt;/a&gt;. Débarqué à Cuba avec les insurgés, il est tué au combat à Dos Ríos le 19 mai 1895. Il est considéré à Cuba comme le héros national et « l’Apôtre » de l’indépendance.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">l5bN92K18g8</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Filosofia Aquí y Ahora IV 5: El Pensamiento de José Martí" par Argen-Man</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/marti-mini.webp</t>
@@ -5022,6 +5060,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paulo_Freire" title=" Wikipedia"&gt;Paulo FREIRE&lt;/a&gt; est un pédagogue et philosophe brésilien, l’un des penseurs de l’éducation les plus lus au monde. Né à Recife, dans le Nordeste, il connaît la faim pendant la crise des années 1930, ce qui le marque pour toute sa vie. Formé au droit et à la philosophie, lecteur de Marx comme des penseurs chrétiens, il se consacre à l’&lt;a href="https://fr.wikipedia.org/wiki/Alphab%C3%A9tisation" title=" Wikipedia"&gt;alphabétisation&lt;/a&gt; des adultes pauvres. En 1963, à Angicos, sa méthode permet à 300 travailleurs agricoles d’apprendre à lire et à écrire en une quarantaine d’heures.&lt;/p&gt; &lt;p&gt;Sa méthode part des « mots générateurs » tirés de la vie des apprenants, comme la brique, la terre ou le salaire, et fait de la lecture une prise de conscience : apprendre à lire le mot, c’est apprendre à lire le monde. Après le coup d’État militaire de 1964, il est emprisonné puis contraint à un exil de seize ans. Au Chili, il écrit &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_des_opprim%C3%A9s" title=" Wikipedia"&gt;&lt;em&gt;Pédagogie des opprimés&lt;/em&gt;&lt;/a&gt; (1968), où il critique l’éducation « bancaire », qui dépose des savoirs dans des élèves passifs comme on remplit un coffre, et lui oppose une éducation par le dialogue, où maître et élèves cherchent ensemble.&lt;/p&gt; &lt;p&gt;« Personne n’éduque autrui, personne ne s’éduque seul, les hommes s’éduquent ensemble par l’intermédiaire du monde. » L’éducation n’est jamais neutre : elle maintient l’oppression ou aide les opprimés à s’en libérer, sans devenir à leur tour oppresseurs. Rentré au Brésil en 1980, il dirige l’éducation de la ville de São Paulo. Son œuvre est à l’origine de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_critique" title=" Wikipedia"&gt;pédagogie critique&lt;/a&gt;, et il a été proclamé en 2012 patron de l’éducation brésilienne.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4FG6diR6fhU</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Une pédagogie pour éduquer au politique, contre l'oppression ? Paulo FREIRE - selon Philippe Meirieu" par Benoit Urgelli</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/freire-mini.webp</t>
@@ -5080,6 +5128,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Vasconcelos" title=" Wikipedia"&gt;José VASCONCELOS&lt;/a&gt; est un philosophe, écrivain et homme politique mexicain, l’un des grands éducateurs de l’Amérique latine. Né à Oaxaca, avocat, il fonde en 1909 avec Antonio Caso et Alfonso Reyes l’Ateneo de la Juventud, cercle de jeunes intellectuels qui rejette le positivisme officiel du régime de Porfirio Díaz. Il prend part à la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_mexicaine" title=" Wikipedia"&gt;révolution mexicaine&lt;/a&gt; aux côtés de Francisco Madero. Recteur de l’université nationale en 1920, il lui donne sa devise, toujours en usage : « Par ma race parlera l’esprit. »&lt;/p&gt; &lt;p&gt;Ministre de l’Éducation de 1921 à 1924, il mène une véritable croisade pour instruire le peuple : écoles rurales, missions culturelles dans les villages, bibliothèques, éditions populaires des grands classiques. Il commande aussi aux peintres &lt;a href="https://fr.wikipedia.org/wiki/Diego_Rivera" title=" Wikipedia"&gt;Diego Rivera&lt;/a&gt; et José Clemente Orozco les fresques murales qui racontent l’histoire du Mexique sur les murs des bâtiments publics. Il est surnommé le « maître de la jeunesse d’Amérique ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Race cosmique&lt;/em&gt; (1925), il prophétise que l’Amérique latine, terre de tous les mélanges, verra naître une « cinquième race », synthèse de toutes les autres, porteuse d’une civilisation de l’amour et de la beauté. Sa philosophie, un « monisme esthétique », voit dans l’émotion esthétique la forme la plus haute de connaissance. Battu en 1929 dans une élection présidentielle qu’il juge truquée, il s’exile, puis évolue vers un conservatisme catholique, au point de manifester en 1940 des sympathies pour l’Allemagne nazie. Il meurt à Mexico en 1959.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B3E3RuPB9qY</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"José Vasconcelos filosofía de México" par Filosofia Corporativa</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/vasconcelos-mini.webp</t>
@@ -5138,6 +5196,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abraham_Joshua_Heschel" title=" Wikipedia"&gt;Abraham Joshua HESCHEL&lt;/a&gt; est un rabbin, théologien et philosophe juif, l’une des grandes voix religieuses du XXe siècle. Né à Varsovie dans une illustre famille du &lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;hassidisme&lt;/a&gt;, il étudie la philosophie à Berlin, où il soutient une thèse sur les prophètes d’Israël. Expulsé d’Allemagne vers la Pologne en 1938, il parvient à quitter Varsovie quelques semaines avant l’invasion allemande et gagne Londres, puis les États-Unis. Sa mère et ses sœurs sont assassinées pendant la Shoah. Il enseigne à partir de 1946 au Séminaire théologique juif de New York.&lt;/p&gt; &lt;p&gt;Pour Heschel, la religion commence par l’« étonnement radical » devant le monde, qui précède toute réflexion. Contre l’idée d’un Dieu impassible des philosophes, il parle du « pathos divin » : le Dieu des prophètes est concerné par le sort des hommes et souffre de l’injustice. La question n’est pas seulement de savoir si l’homme cherche Dieu, mais de comprendre que &lt;em&gt;Dieu est en quête de l’homme&lt;/em&gt;, titre de son livre de 1955. Dans &lt;em&gt;Les Bâtisseurs du temps&lt;/em&gt; (1951), il présente le &lt;a href="https://fr.wikipedia.org/wiki/Shabbat" title=" Wikipedia"&gt;shabbat&lt;/a&gt; comme « une cathédrale dans le temps » : le judaïsme sanctifie des moments plutôt que des lieux. Il consacre aussi un grand livre aux prophètes, témoins de la passion de Dieu pour la justice.&lt;/p&gt; &lt;p&gt;Sa foi le conduit à l’action. En 1965, il marche de Selma à Montgomery aux côtés de Martin Luther King et dira : « J’avais l’impression que mes jambes priaient. » Il s’oppose à la guerre du Vietnam et contribue au dialogue entre juifs et chrétiens lors du concile Vatican II. Il meurt à New York en 1972.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLINbVsBz-Q</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"LA PENSEE D'AVRAHAM YOSHOUA HESCHEL" Rony Akrich"" par רוני אקריש</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/heschel-mini.webp</t>
@@ -5201,6 +5269,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Octavio_Paz" title=" Wikipedia"&gt;Octavio PAZ&lt;/a&gt; est un poète, essayiste et diplomate mexicain, prix Nobel de littérature en 1990. Né à Mexico dans une famille marquée par la révolution, son père ayant été le représentant d’Emiliano Zapata aux États-Unis, il soutient les républicains pendant la guerre d’Espagne, puis rompt avec le communisme après l’assassinat de Trotski. Diplomate à Paris après la guerre, il y fréquente les surréalistes et André Breton.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Labyrinthe_de_la_solitude" title=" Wikipedia"&gt;&lt;em&gt;Le Labyrinthe de la solitude&lt;/em&gt;&lt;/a&gt; (1950), il interroge l’identité mexicaine : derrière les masques de la politesse et la violence des fêtes se cache une solitude née de l’histoire, celle d’un peuple issu de la conquête, qui a renié à la fois son passé indien et son passé espagnol. Il y évoque la figure de la &lt;a href="https://fr.wikipedia.org/wiki/La_Malinche" title=" Wikipedia"&gt;Malinche&lt;/a&gt;, compagne indienne de Cortés, symbole ambigu de l’origine métisse du pays. Mais cette solitude est aussi celle de l’homme moderne, et la poésie, l’amour et la fête sont des moyens de la dépasser. Dans &lt;em&gt;L’Arc et la Lyre&lt;/em&gt; (1956), il fait de la poésie une expérience de communion qui révèle l’homme à lui-même.&lt;/p&gt; &lt;p&gt;Ambassadeur du Mexique en Inde de 1962 à 1968, il découvre les philosophies et l’art de l’Orient, qui nourrissent sa poésie. Il démissionne après le &lt;a href="https://fr.wikipedia.org/wiki/Massacre_de_Tlatelolco" title=" Wikipedia"&gt;massacre de Tlatelolco&lt;/a&gt;, où des centaines d’étudiants sont tués par l’armée en 1968. Critique des totalitarismes de droite comme de gauche, il fonde la revue &lt;em&gt;Vuelta&lt;/em&gt; et consacre un grand livre à la poétesse et penseuse Juana Inés de la Cruz. Il meurt à Mexico en 1998, à quatre-vingt-quatre ans.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZIxDHuVg9TQ</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Octavio PAZ – Un siècle d'écrivains : 1914-1990 (France 3, 2000)" par ÉCLAIR BRUT</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/paz-mini.webp</t>
@@ -5259,6 +5337,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Enrique_Rod%C3%B3" title=" Wikipedia"&gt;José Enrique RODÓ&lt;/a&gt; est un écrivain et essayiste uruguayen, l’un des grands maîtres à penser de l’Amérique latine au début du XXe siècle. Né à Montevideo, il doit interrompre ses études après la ruine de sa famille, se forme largement seul et devient professeur de littérature à l’université de Montevideo, puis député. Correspondant de &lt;a href="https://fr.wikipedia.org/wiki/Rub%C3%A9n_Dar%C3%ADo" title=" Wikipedia"&gt;Rubén Darío&lt;/a&gt;, il est le principal théoricien du modernisme, le grand mouvement de renouvellement de la littérature hispano-américaine.&lt;/p&gt; &lt;p&gt;Son essai &lt;em&gt;Ariel&lt;/em&gt; (1900), écrit deux ans après la victoire des États-Unis sur l’Espagne à Cuba, prend la forme d’un dernier cours donné par un vieux maître, Prospero, à ses élèves. Empruntant les personnages de &lt;em&gt;La Tempête&lt;/em&gt; de Shakespeare, il oppose Ariel, l’esprit, la beauté, le désintéressement, à Caliban, la matière, l’utilité, les appétits. Il met en garde la jeunesse latino-américaine contre l’utilitarisme et la « nordomanie », la fascination pour le modèle des États-Unis, puissant mais tourné vers le seul profit.&lt;/p&gt; &lt;p&gt;Rodó invite les jeunes à cultiver toutes les facultés de l’esprit, à préserver un temps libre pour la pensée et la beauté, et à construire une démocratie qui élève chacun au lieu de niveler par le bas. Le livre connut un immense succès et inspira tout un courant, l’« arielisme ». Plus tard, des penseurs comme Roberto Fernández Retamar ont renversé le symbole en faisant de Caliban la figure du colonisé. Dans &lt;em&gt;Motifs de Protée&lt;/em&gt; (1909), il médite sur la transformation continuelle de soi. Rodó meurt à Palerme en 1917, au cours d’un voyage en Europe.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C2csl4K2CTs</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La Mesa de Filósofos: José Enrique Rodó, su legado a 150 años del nacimiento" par En Perspectiva + VIDEO </t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/rodo-mini.webp</t>
@@ -5317,6 +5405,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Rodolfo_Kusch" title=" Wikipedia (es)"&gt;Rodolfo KUSCH&lt;/a&gt; est un philosophe et anthropologue argentin qui a cherché à fonder une philosophie à partir de la pensée indigène et populaire de l’Amérique. Né à Buenos Aires de parents allemands, il étudie la philosophie à l’université de Buenos Aires, enseigne l’esthétique et écrit aussi pour le théâtre, notamment sur le tango. Persécuté pour ses sympathies péronistes après 1955, il part pour la Bolivie et le Pérou, puis s’installe dans le nord-ouest de l’Argentine, à Maimará, dans la province de Jujuy.&lt;/p&gt; &lt;p&gt;Au contact des communautés &lt;a href="https://fr.wikipedia.org/wiki/Quechuas" title=" Wikipedia"&gt;quechuas&lt;/a&gt; et &lt;a href="https://fr.wikipedia.org/wiki/Aymaras" title=" Wikipedia"&gt;aymaras&lt;/a&gt; des Andes, il mène de longues enquêtes de terrain, dont il tire &lt;em&gt;L’Amérique profonde&lt;/em&gt; (1962) et &lt;em&gt;La Pensée indigène et populaire en Amérique&lt;/em&gt; (1970). Il y oppose deux attitudes. Celle de l’Occident, l’« être », qui veut dominer le monde, le transformer et accumuler. Et celle de l’Amérique indienne, l’« être là » ou le simple « se tenir » (en espagnol &lt;em&gt;estar&lt;/em&gt;), qui accepte l’incertitude du monde, ses forces et ses menaces, et cherche à vivre en équilibre avec lui.&lt;/p&gt; &lt;p&gt;Pour Kusch, les classes moyennes des villes, qui se veulent européennes, vivent dans la peur de cette « Amérique profonde » qu’elles refoulent. Penser en Amérique, c’est accepter cette part indienne et populaire au lieu de la mépriser. Son œuvre, longtemps marginale, a nourri la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt; et les pensées décoloniales latino-américaines, et elle est aujourd’hui redécouverte. Il parle même de « phagocytose » : la culture populaire finirait par absorber ce que la modernité importée croit lui imposer. Il meurt en 1979 à Maimará, à cinquante-sept ans.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xow95qdu2wE</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Podcast filosófico -  Rodolfo Kusch" par Filo Errante</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/kusch-mini.webp</t>
@@ -5375,6 +5473,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Augusto_Salazar_Bondy" title=" Wikipedia (es)"&gt;Augusto SALAZAR BONDY&lt;/a&gt; est un philosophe et éducateur péruvien, l’une des figures fondatrices de la philosophie latino-américaine de la libération. Né à Lima, frère cadet de l’écrivain Sebastián Salazar Bondy, il étudie à l’université San Marcos, puis au Mexique auprès de José Gaos et de Leopoldo Zea, et à Paris, où il suit les cours de Jean Wahl, Jean Hyppolite et Gaston Bachelard. Professeur d’éthique à San Marcos, il écrit une grande histoire des idées au Pérou contemporain.&lt;/p&gt; &lt;p&gt;En 1968, il publie &lt;em&gt;Existe-t-il une philosophie de notre Amérique ?&lt;/em&gt;, qui provoque un vif débat avec Leopoldo Zea. Sa réponse est dure : jusqu’ici, il n’existe pas de philosophie latino-américaine authentique, mais seulement des imitations des courants européens, adoptés tour à tour sans être vraiment pensés. Ce n’est pas un manque de talent : c’est la conséquence de la domination et du sous-développement, qui produisent une culture dépendante et « aliénée », incapable de se penser elle-même.&lt;/p&gt; &lt;p&gt;Une philosophie authentique ne pourra naître qu’en prenant pour objet cette situation de domination, et en contribuant à la transformer. La philosophie devient ainsi une tâche de libération, comme le développera la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt;. Engagé dans la réforme de l’éducation sous le gouvernement péruvien de la fin des années 1960, il défend une école qui forme des personnes libres et critiques. Il meurt prématurément à Lima en 1974, à quarante-huit ans. Ses idées ont notamment inspiré Enrique Dussel.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pKvpeeR1Q4Y</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"El concepto de alienación según Augusto Salazar Bondy" par Libros Peruanos</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/salazarbondy-mini.webp</t>
@@ -5433,6 +5541,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Eugenio_Mar%C3%ADa_de_Hostos" title=" Wikipedia (en)"&gt;Eugenio María de HOSTOS&lt;/a&gt; est un philosophe, éducateur, sociologue et écrivain de &lt;a href="https://fr.wikipedia.org/wiki/Porto_Rico" title=" Wikipedia"&gt;Porto Rico&lt;/a&gt;, surnommé « le Grand Citoyen des Amériques ». Né à Mayagüez dans une famille aisée, il fait ses études en Espagne, où il étudie le droit et la philosophie à Madrid et publie en 1863 un roman, &lt;em&gt;Le Pèlerinage de Bayoán&lt;/em&gt;, qui évoque déjà le destin des Antilles. Déçu que la République espagnole refuse l’autonomie de Porto Rico, il quitte l’Espagne en 1869 pour se consacrer à l’indépendance des colonies antillaises.&lt;/p&gt; &lt;p&gt;Il rêve d’une Confédération des Antilles, réunissant Porto Rico, Cuba et la République dominicaine, et parcourt pour la défendre les États-Unis, le Pérou, le Chili, l’Argentine, le Brésil et le Venezuela. Partout, il fonde ou réforme des écoles. En République dominicaine, il crée en 1880 la première école normale, qui forme des instituteurs à une pédagogie scientifique et laïque. Au Chili, il plaide pour que les femmes aient accès à l’enseignement supérieur et aux professions savantes.&lt;/p&gt; &lt;p&gt;Sa &lt;em&gt;Morale sociale&lt;/em&gt; (1888), inspirée du &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt;, fonde les devoirs de l’individu non sur la religion, mais sur la raison et sur les liens qui l’unissent à la famille, à la société et à l’humanité ; l’éducation doit former des consciences libres et responsables. Après la guerre de 1898, qui fait passer Porto Rico sous domination américaine, il milite pour que l’île puisse décider elle-même de son avenir. Il laisse aussi un traité de sociologie, l’un des premiers d’Amérique latine. Il meurt en exil à Saint-Domingue en 1903.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yxxhyhWr-N4</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Eugenio María de Hostos / intelectual educador, filósofo, sociólogo y escritor puertorriqueño" par Damián S. Vargas</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/hostos-mini.webp</t>
@@ -5491,6 +5609,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Orlando_Fals_Borda" title=" Wikipedia (en)"&gt;Orlando FALS BORDA&lt;/a&gt; est un sociologue colombien, l’un des grands penseurs latino-américains des sciences sociales et le fondateur de la « recherche-action participative ». Né à Barranquilla, sur la côte caraïbe, formé aux États-Unis, il fonde en 1959 à l’Université nationale de Colombie, avec le prêtre Camilo Torres, l’une des premières facultés de sociologie d’Amérique latine. Son livre &lt;em&gt;La Violence en Colombie&lt;/em&gt; (1962), écrit avec Germán Guzmán et Eduardo Umaña, étudie pour la première fois la guerre civile qui ravage les campagnes.&lt;/p&gt; &lt;p&gt;Déçu par une sociologie qui observe les pauvres de l’extérieur sans rien changer à leur sort, il quitte l’université dans les années 1970 pour travailler avec les paysans et les communautés de la côte caraïbe. Il y développe la &lt;a href="https://fr.wikipedia.org/wiki/Recherche-action" title=" Wikipedia"&gt;recherche-action&lt;/a&gt; participative : le chercheur ne doit pas monopoliser le savoir ni imposer sa technique, mais travailler avec les communautés comme avec des partenaires et des co-chercheurs, recueillir leurs savoirs, leur mémoire et leurs récits, et partager les résultats sous une forme que tous peuvent comprendre.&lt;/p&gt; &lt;p&gt;La science n’est pas, selon lui, une affaire d’experts neutres : elle doit servir la transformation de la société et la libération des opprimés. Il parle d’une « subversion positive » qui conteste l’ordre injuste pour en construire un meilleur. Ses idées se sont répandues dans le monde entier, en éducation, en santé et en développement. Il participe aussi à l’Assemblée constituante qui rédige la Constitution colombienne de 1991. Il meurt à Bogotá en 2008.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYIrjf9pID0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The work of Orlando Fals Borda" par stanbrad13</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/falsborda-mini.webp</t>
@@ -5549,6 +5677,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Humberto_Maturana" title=" Wikipedia"&gt;Humberto MATURANA&lt;/a&gt; est un biologiste et philosophe chilien, l’un des penseurs les plus originaux de la biologie de la connaissance. Né à Santiago, il étudie la médecine et la biologie au Chili, puis en Angleterre et à Harvard. Au Massachusetts Institute of Technology, il participe en 1959 à une étude devenue célèbre sur ce que l’œil de la grenouille transmet à son cerveau, qui montre que la perception n’est pas une simple copie du monde extérieur. Il fonde ensuite à l’université du Chili un laboratoire d’« épistémologie expérimentale ».&lt;/p&gt; &lt;p&gt;Avec son élève Francisco Varela, il propose au début des années 1970 le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, du grec « se produire soi-même » : un être vivant est un système qui produit et renouvelle sans cesse ses propres composants, et maintient ainsi sa propre organisation. La cellule en est le modèle. Le vivant n’est donc pas défini par ce qu’il contient, mais par cette manière de s’entretenir lui-même, en échange constant avec son milieu.&lt;/p&gt; &lt;p&gt;Il en tire une théorie de la connaissance : « Tout ce qui est dit est dit par un observateur. » Connaître n’est pas refléter un monde tout fait, mais une activité du vivant, qui fait émerger un monde à travers son action. Dans &lt;em&gt;L’Arbre de la connaissance&lt;/em&gt; (1984), écrit avec Varela, il montre aussi que le langage et la société naissent de la coordination entre les êtres, et que l’amour, l’acceptation de l’autre, est le fondement biologique de la vie sociale. Ses idées ont nourri le &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_%28%C3%A9pist%C3%A9mologie%29" title=" Wikipedia"&gt;constructivisme&lt;/a&gt;, la thérapie familiale et la théorie des systèmes sociaux de &lt;a href="https://fr.wikipedia.org/wiki/Niklas_Luhmann" title=" Wikipedia"&gt;Niklas Luhmann&lt;/a&gt;. Il meurt à Santiago en 2021.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19uV8wKpkZw</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La entrevista al académico Humberto Maturana que inspiró a Mon Laferte | La Belleza de Pensar" par Canal13C</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/maturana-mini.webp</t>
@@ -5612,6 +5750,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_Varela" title=" Wikipedia"&gt;Francisco VARELA&lt;/a&gt; est un biologiste, neuroscientifique et philosophe chilien, l’un des fondateurs des sciences cognitives « incarnées ». Né à Talcahuano, élève d’Humberto Maturana, il soutient une thèse de biologie à Harvard, puis invente avec son maître le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, qui définit le vivant par sa capacité à se produire lui-même. Après le coup d’État de Pinochet en 1973, il doit s’exiler aux États-Unis. Il s’installe en France en 1986 et dirige jusqu’à sa mort une équipe de recherche au CNRS, à Paris.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Inscription corporelle de l’esprit&lt;/em&gt; (1991), écrit avec Evan Thompson et Eleanor Rosch, il critique l’idée que l’esprit serait un ordinateur qui traite des représentations d’un monde extérieur déjà donné. Il propose à la place l’« &lt;a href="https://fr.wikipedia.org/wiki/%C3%89naction" title=" Wikipedia"&gt;énaction&lt;/a&gt; » : la cognition est une action incarnée, par laquelle un être vivant fait émerger son monde à travers son corps, ses sens et ses gestes. Il fonde aussi la « neurophénoménologie », qui veut unir les mesures du cerveau et la description rigoureuse de l’expérience vécue, à la manière de Husserl et de Merleau-Ponty.&lt;/p&gt; &lt;p&gt;Pratiquant du bouddhisme tibétain depuis les années 1970, il voit dans la méditation une méthode précise pour explorer l’expérience. En 1987, il cofonde le &lt;a href="https://fr.wikipedia.org/wiki/Mind_and_Life_Institute" title=" Wikipedia"&gt;Mind and Life Institute&lt;/a&gt;, qui organise des rencontres entre scientifiques et le dalaï-lama. Il est l’un des inspirateurs de l’idée d’un esprit « incarné », aujourd’hui centrale en &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_l%27esprit" title=" Wikipedia"&gt;philosophie de l’esprit&lt;/a&gt;. Il meurt à Paris en 2001, à cinquante-quatre ans, d’une maladie du foie.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HPh_uAetJ8U</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Francisco VARELA 2. COPYRIGHT INA ET FRANCETV" par Catherine BARRY - Au coeur du Bouddhisme</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/varela-mini.webp</t>
@@ -5675,6 +5823,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/W._E._B._Du_Bois" title=" Wikipedia"&gt;W. E. B. DU BOIS&lt;/a&gt; (William Edward Burghardt Du Bois) est un sociologue, historien et militant africain-américain, l’un des plus grands penseurs américains du XXe siècle. Né en 1868 dans le Massachusetts, il étudie à Fisk, à Berlin, puis à Harvard, où il devient en 1895 le premier Africain-Américain à obtenir un doctorat. Son étude &lt;em&gt;The Philadelphia Negro&lt;/em&gt; (1899) est l’une des premières grandes enquêtes de sociologie empirique aux États-Unis.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Les_%C3%82mes_du_peuple_noir" title=" Wikipedia"&gt;&lt;em&gt;Les Âmes du peuple noir&lt;/em&gt;&lt;/a&gt; (1903), il affirme que « le problème du XXe siècle est le problème de la ligne de couleur ». Il y décrit la « double conscience » des Noirs américains : le sentiment de se voir toujours à travers les yeux d’un monde qui les méprise, d’être à la fois américain et noir, « deux âmes, deux pensées, deux combats inconciliables dans un seul corps sombre ». Dans &lt;em&gt;Black Reconstruction&lt;/em&gt; (1935), il réhabilitera le rôle des anciens esclaves dans l’histoire américaine d’après la guerre de Sécession. Il y critique aussi Booker T. Washington, qui conseillait aux Noirs d’accepter la ségrégation en échange du progrès économique.&lt;/p&gt; &lt;p&gt;En 1909, il est l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/National_Association_for_the_Advancement_of_Colored_People" title=" Wikipedia"&gt;NAACP&lt;/a&gt;, la grande organisation de défense des droits civiques, dont il dirige la revue &lt;em&gt;The Crisis&lt;/em&gt;. Il organise plusieurs congrès panafricains et devient le « père du &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; ». Proche du socialisme, persécuté pendant le maccarthysme, il s’installe à la fin de sa vie au &lt;a href="https://fr.wikipedia.org/wiki/Ghana" title=" Wikipedia"&gt;Ghana&lt;/a&gt;, à l’invitation de Kwame Nkrumah, et y meurt en 1963, à la veille de la marche sur Washington de Martin Luther King.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Li9wCyjag3Q</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"W.E.B. Du Bois : Pionnier des Droits Civiques - Une Conférence par Christian Monjou" par Art et Leadership</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/dubois-mini.webp</t>
@@ -5738,6 +5896,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo GUTIÉRREZ&lt;/a&gt; est un prêtre et théologien péruvien, considéré comme le père de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;théologie de la libération&lt;/a&gt;. Né à Lima en 1928 dans un milieu modeste, il souffre adolescent d’une ostéomyélite qui le cloue longtemps au lit ; il lit alors beaucoup et commence des études de médecine pour devenir psychiatre. À vingt-quatre ans, il choisit la prêtrise et part étudier la philosophie et la psychologie à Louvain, puis la théologie à Lyon.&lt;/p&gt; &lt;p&gt;Ordonné prêtre en 1959, il devient vicaire dans un quartier pauvre de Lima, tout en enseignant à l’université catholique, et repense toute sa théologie au contact de ce peuple. En 1971, il publie &lt;em&gt;Théologie de la libération&lt;/em&gt;, traduit dans une vingtaine de langues. La pauvreté, écrit-il, n’est pas une fatalité mais le fruit d’injustices, et elle est contraire à la volonté de Dieu. La théologie est une « réflexion critique sur la pratique à la lumière de la Parole » : elle vient en second, après l’engagement aux côtés des pauvres. Le salut ne se joue pas seulement dans l’au-delà ; il touche toute l’existence, et la libération sociale et politique en fait partie, sans s’y réduire. Dans &lt;em&gt;Boire à son propre puits&lt;/em&gt; (1983), il montre que cet engagement est aussi une spiritualité, une manière de suivre le Christ.&lt;/p&gt; &lt;p&gt;Ses positions lui valent la méfiance de Rome dans les années 1980, sans condamnation. Entré chez les Dominicains en 1998, il enseigne dans de nombreuses universités d’Europe et des États-Unis. Le pape François le reçoit en 2013, signe de la réhabilitation de son œuvre, et l’« option préférentielle pour les pauvres » est devenue un principe de l’enseignement de l’Église. Il meurt à Lima en 2024, à quatre-vingt-seize ans.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mdBvcdTUDRg</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La libération comme espérance chez Gustavo Gutierrez" par Didascale</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/ggutierrez-mini.webp</t>
@@ -5796,6 +5964,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/William_Graham_Sumner" title=" Wikipedia"&gt;William Graham SUMNER&lt;/a&gt; est un sociologue et économiste américain, l’un des fondateurs de la sociologie aux États-Unis et la figure majeure de ce qu’on appellera le &lt;a href="https://fr.wikipedia.org/wiki/Darwinisme_social" title=" Wikipedia"&gt;darwinisme social&lt;/a&gt; américain. Né en 1840 à Paterson, dans le New Jersey, fils d’un ouvrier anglais immigré, il étudie à Yale, puis en Europe, et devient d’abord pasteur épiscopalien. En 1872, il est nommé professeur à Yale, où il donne l’un des premiers cours intitulés « sociologie ».&lt;/p&gt; &lt;p&gt;Lecteur de Herbert Spencer, il applique à la société l’idée de lutte pour l’existence. Dans &lt;em&gt;Ce que les classes sociales se doivent les unes aux autres&lt;/em&gt; (1883), il répond : rien, sinon le respect de la liberté et des contrats. L’aide de l’État aux pauvres se fait toujours aux dépens de l’« homme oublié », le travailleur modeste qui paie ses impôts sans rien demander. La richesse récompense le travail, l’épargne et la tempérance, et la réussite des plus capables profite à toute la société. Ces positions ont fait de lui, aux yeux de ses critiques, le défenseur d’un capitalisme sans pitié pour les faibles.&lt;/p&gt; &lt;p&gt;Mais il défend aussi le libre-échange contre les monopoles protégés et s’oppose fermement à l’impérialisme : en 1898, il dénonce la guerre contre l’Espagne et la conquête des Philippines dans &lt;em&gt;La Conquête des États-Unis par l’Espagne&lt;/em&gt;. Dans &lt;em&gt;Folkways&lt;/em&gt; (1906), il étudie les coutumes et les mœurs des sociétés, et forge le mot « ethnocentrisme » pour désigner la tendance de chaque groupe à juger les autres d’après ses propres valeurs. Il meurt en 1910.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">r-myUjOJ0qY</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Folkways by William Graham Sumner" par Sociologylearners</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/sumner-mini.webp</t>
@@ -5852,6 +6030,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donald_Davidson" title=" Wikipedia"&gt;Donald DAVIDSON&lt;/a&gt; est un philosophe américain, l’un des plus influents de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; de la seconde moitié du XXe siècle. Né en 1917 à Springfield, dans le Massachusetts, il étudie à Harvard la littérature et les lettres classiques avant de se tourner vers la philosophie sous l’influence de Quine. Après avoir servi dans la marine pendant la guerre, il enseigne notamment à Stanford, à Princeton et à Berkeley.&lt;/p&gt; &lt;p&gt;Dans « Actions, raisons et causes » (1963), il soutient que nos raisons d’agir, nos désirs et nos croyances, sont aussi les causes de nos actions. Dans « Les événements mentaux » (1970), il défend le « monisme anomal » : chaque événement mental est un événement physique, mais il n’existe pas de lois strictes qui relient le mental au physique, car le mental obéit à d’autres principes, ceux de la rationalité. Il réconcilie ainsi le matérialisme avec l’autonomie de la pensée.&lt;/p&gt; &lt;p&gt;Sa théorie de l’« interprétation radicale » prolonge le &lt;a href="https://fr.wikipedia.org/wiki/Holisme" title=" Wikipedia"&gt;holisme&lt;/a&gt; de Quine : pour comprendre un locuteur dont on ignore tout de la langue, il faut lui attribuer en même temps des croyances et des significations, en supposant qu’il pense en grande partie comme nous. C’est le « principe de charité ». Le sens d’un mot dépend du sens de toute la langue, et nos croyances forment un réseau. Il en conclut, dans un article célèbre de 1974, que l’idée de « schèmes conceptuels » radicalement incommensurables n’a pas de sens. Il meurt à Berkeley en 2003.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecqO4LMbYvk</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Donald Davidson Interview: Language, Interpretation, &amp; Philosophy (1993)" par Philosophy Overdose</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/donalddavidson-mini.webp</t>
@@ -5908,6 +6096,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Wilfrid_Sellars" title=" Wikipedia"&gt;Wilfrid SELLARS&lt;/a&gt; est un philosophe américain, l’un des plus profonds de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; du XXe siècle. Né en 1912 à Ann Arbor, fils du philosophe Roy Wood Sellars, il étudie au Michigan, à Buffalo puis à Oxford. Il enseigne au Minnesota, à Yale, et à partir de 1963 à l’université de Pittsburgh, où il fait école. Avec Herbert Feigl, il fonde en 1950 la revue &lt;em&gt;Philosophical Studies&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Dans « Empirisme et philosophie de l’esprit » (1956), il s’attaque au « mythe du donné » : l’idée, commune aux empiristes, que notre connaissance repose sur des données des sens que nous saisirions immédiatement, sans concepts. Pour Sellars, voir que quelque chose est rouge, c’est déjà savoir ce qu’est le rouge et être capable de le justifier. La connaissance appartient à l’« espace logique des raisons », où l’on donne et demande des justifications, et non à un simple contact causal avec le monde. Même l’observation la plus simple suppose tout un langage et tout un savoir, appris avec lui.&lt;/p&gt; &lt;p&gt;Dans « La philosophie et l’image scientifique de l’homme » (1962), il oppose l’« image manifeste », celle du monde de la vie quotidienne, peuplé de personnes, de couleurs et d’intentions, et l’« image scientifique », faite de particules et de processus. La tâche de la philosophie est de les unir en une seule vision. Pour lui, la science est « la mesure de toutes choses ». Il meurt à Pittsburgh en 1989. Longtemps jugé difficile, il est aujourd’hui l’un des philosophes américains les plus étudiés. Ses idées inspirent Richard Rorty, Robert Brandom et John McDowell.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eJ_0-_NGXQE</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Wilfrid Sellars : Science et métaphysique (1) - Jacques Bouveresse (2008-2009)" par Lettres, langage, philosophie - Collège de France</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/wsellars-mini.webp</t>
@@ -5966,6 +6164,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arthur_Danto" title=" Wikipedia"&gt;Arthur DANTO&lt;/a&gt; est un philosophe et critique d’art américain. Né en 1924 à Ann Arbor, il grandit à Detroit, sert pendant la Seconde Guerre mondiale en Afrique du Nord et en Italie, puis étudie l’art et la philosophie. D’abord graveur, il enseigne à l’université Columbia, à New York, de 1951 à 1992. Ses premiers livres portent sur la philosophie de l’histoire, où il étudie les « phrases narratives », qui décrivent un événement à la lumière de ce qui l’a suivi, et sur Nietzsche, qu’il fait connaître aux philosophes analytiques.&lt;/p&gt; &lt;p&gt;En 1964, il voit exposées les &lt;em&gt;Brillo Boxes&lt;/em&gt; d’Andy Warhol, des boîtes identiques à celles des supermarchés. Pourquoi l’une est-elle une œuvre d’art, et l’autre non, alors qu’on ne peut pas les distinguer à l’œil ? Dans l’article « Le monde de l’art », il répond que ce qui fait l’œuvre n’est pas une propriété visible, mais une théorie et une histoire de l’art, une atmosphère que seul connaît ce « monde de l’art ». Dans &lt;em&gt;La Transfiguration du banal&lt;/em&gt; (1981), il précise : une œuvre d’art est toujours à propos de quelque chose, et elle incarne ce sens, ce qui la distingue d’une simple chose.&lt;/p&gt; &lt;p&gt;Il en tire en 1984 la thèse de la « fin de l’art » : non que l’on cesse de créer, mais l’art, depuis Warhol, n’a plus d’histoire orientée, et tout est désormais possible. C’est à la &lt;a href="https://fr.wikipedia.org/wiki/Esth%C3%A9tique" title=" Wikipedia"&gt;philosophie&lt;/a&gt;, et non plus à l’art, de dire ce qu’est l’art. Critique d’art à l’hebdomadaire &lt;em&gt;The Nation&lt;/em&gt; de 1984 à 2009, il est l’un des esthéticiens les plus lus de son temps. Il meurt à New York en 2013.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3xVufNOZPqE</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Arthur Danto: La transfiguration du banal. Une philosophie de l'art." par Jtgrandtour</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/danto-mini.webp</t>
@@ -6024,6 +6232,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Harry_Frankfurt" title=" Wikipedia"&gt;Harry FRANKFURT&lt;/a&gt; est un philosophe américain. Né en 1929 à Langhorne, en Pennsylvanie, il étudie à l’université Johns-Hopkins et enseigne à l’université Rockefeller, à Yale, puis à Princeton jusqu’en 2002. Spécialiste de Descartes, il devient surtout l’un des penseurs majeurs de la liberté, de la responsabilité et de la personne, dans un style d’une grande clarté.&lt;/p&gt; &lt;p&gt;En 1969, il imagine des cas, appelés depuis « cas de Frankfurt », pour contester l’idée qu’on n’est responsable d’un acte que si l’on aurait pu agir autrement. Un neurologue malveillant est prêt à intervenir dans le cerveau de Jones pour le forcer à agir, mais Jones fait de lui-même ce qu’on attendait, sans intervention : il est responsable, bien qu’il n’ait pas eu d’autre possibilité. En 1971, il définit la personne par les « désirs de second ordre » : nous ne voulons pas seulement des choses, nous voulons aussi avoir ou ne pas avoir certains désirs. Être libre, c’est agir selon les désirs que l’on approuve. Ces idées font de lui l’un des grands défenseurs du &lt;a href="https://fr.wikipedia.org/wiki/Compatibilisme" title=" Wikipedia"&gt;compatibilisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Son petit essai &lt;em&gt;De l’art de dire des conneries&lt;/em&gt;, écrit en 1986 et publié en livre en 2005, devient un best-seller : le baratineur est plus dangereux que le menteur, car le menteur se soucie encore de la vérité pour la cacher, alors que le baratineur y est indifférent. Dans &lt;em&gt;Les Raisons de l’amour&lt;/em&gt; (2004), il montre que c’est ce que nous aimons qui donne sens à notre vie. Dans &lt;em&gt;On Inequality&lt;/em&gt; (2015), il soutient que l’important n’est pas que chacun ait autant, mais que chacun ait assez. Il meurt à Santa Monica en 2023.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FXewQRCpKAs</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La Rhétorique Toxique et le Bullshit - Harry.G.Frankfurt" par MLHORION</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/frankfurt-mini.webp</t>
@@ -6137,6 +6355,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jane_Addams" title=" Wikipedia"&gt;Jane ADDAMS&lt;/a&gt; est une philosophe, sociologue et réformatrice sociale américaine. Née en 1860 à Cedarville, dans l’Illinois, fille d’un riche meunier et homme politique, elle fait partie de la première génération de femmes diplômées de l’université. Lors d’un voyage à Londres, elle découvre Toynbee Hall, une maison où des étudiants vivent parmi les pauvres pour les aider. En 1889, avec son amie Ellen Gates Starr, elle fonde à Chicago Hull House, dans un quartier d’immigrés.&lt;/p&gt; &lt;p&gt;Hull House devient un grand centre social, avec crèche, cours du soir, bibliothèque, théâtre et enquêtes sur les conditions de vie. Jane Addams y mène des combats contre le travail des enfants, pour les premiers tribunaux pour mineurs, pour la santé publique et pour le droit de vote des femmes. Amie de John Dewey, qui enseigne à Hull House, elle est une figure du &lt;a href="https://fr.wikipedia.org/wiki/Pragmatisme" title=" Wikipedia"&gt;pragmatisme&lt;/a&gt; : la connaissance doit naître de l’expérience partagée et servir à résoudre les problèmes réels. Dans &lt;em&gt;Démocratie et éthique sociale&lt;/em&gt; (1902), elle soutient que la démocratie n’est pas seulement un régime politique, mais une manière de vivre avec les autres, fondée sur la sympathie et la coopération.&lt;/p&gt; &lt;p&gt;Pacifiste, elle s’oppose à l’entrée des États-Unis dans la Première Guerre mondiale. Elle préside en 1915 le Congrès international des femmes à La Haye, puis la Ligue internationale des femmes pour la paix et la liberté. En 1931, elle est la première Américaine à recevoir le prix Nobel de la paix. Elle meurt à Chicago en 1935.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpxwZT9Woac</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"BERNARD JUNG lit Démocratie et éthique sociale, de Jane Addams (éd. RAISON ET PASSIONS)" par LautreLIVRE CA</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/addams-mini.webp</t>
@@ -6198,6 +6426,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Herbert_Mead" title=" Wikipedia"&gt;George Herbert MEAD&lt;/a&gt; est un philosophe, sociologue et psychologue américain. Né en 1863 dans le Massachusetts, fils d’un pasteur, il étudie à Harvard auprès de William James, puis en Allemagne, à Leipzig et à Berlin. En 1891, il rejoint John Dewey à l’université du Michigan, puis le suit en 1894 à Chicago, où il enseigne jusqu’à sa mort en 1931. Engagé dans les réformes sociales de la ville, il soutient Hull House, la maison de Jane Addams. Il publie peu : ses livres, comme &lt;em&gt;L’Esprit, le soi et la société&lt;/em&gt; (1934), sont tirés après sa mort des notes de ses étudiants.&lt;/p&gt; &lt;p&gt;Figure du &lt;a href="https://fr.wikipedia.org/wiki/Pragmatisme" title=" Wikipedia"&gt;pragmatisme&lt;/a&gt;, il montre que le soi n’est pas donné à la naissance : il se forme dans les échanges avec les autres. Tout commence par une « conversation de gestes », comme entre deux chiens qui se menacent. Le langage permet d’aller plus loin : en parlant, nous entendons ce que nous disons comme les autres l’entendent, et apprenons ainsi à nous voir de leur point de vue. L’enfant joue d’abord des rôles, la maman, le policier, puis participe à des jeux organisés, où il doit tenir compte de tous les autres à la fois. Il intériorise alors un « autrui généralisé », les attentes de toute la communauté.&lt;/p&gt; &lt;p&gt;Le soi a deux faces : le « moi », ce que les autres ont fait de nous, et le « je », notre réponse personnelle et créatrice. Ses idées sont à l’origine de l’« interactionnisme symbolique », un grand courant de la sociologie.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ew5mIYw_bk</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"What was George Herbert Mead's philosophy? | Philosophy" par VIS PHILO.</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/mead-mini.webp</t>
@@ -6254,6 +6492,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Ingenieros" title=" Wikipedia"&gt;José INGENIEROS&lt;/a&gt; est un médecin, psychiatre et philosophe argentin. Né à Palerme, en Italie, en 1877, sous le nom de Giuseppe Ingegnieri, il arrive enfant à Buenos Aires. Étudiant, il milite au Parti socialiste et fonde un journal révolutionnaire. Médecin, il dirige un institut de criminologie et publie des travaux de psychologie et de psychiatrie. Il fonde en 1915 la &lt;em&gt;Revue de philosophie&lt;/em&gt;, et soutient la Réforme universitaire de Córdoba en 1918, qui démocratise les universités d’Amérique latine. Il meurt à Buenos Aires en 1925.&lt;/p&gt; &lt;p&gt;Disciple du &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt;, il veut fonder la philosophie sur les sciences, en particulier la biologie et la psychologie. La morale n’a pas besoin des dogmes religieux : elle naît de l’expérience sociale et évolue avec elle, comme il l’explique dans &lt;em&gt;Vers une morale sans dogmes&lt;/em&gt; (1917). Il propose une métaphysique nouvelle, qui ne porte plus sur des vérités éternelles, mais sur ce qui échappe encore à l’expérience : elle doit rester ouverte et se corriger avec les progrès du savoir.&lt;/p&gt; &lt;p&gt;Son livre le plus célèbre, &lt;em&gt;L’Homme médiocre&lt;/em&gt; (1913), oppose l’idéaliste, qui imagine un monde meilleur et se bat pour lui, au médiocre, qui se contente d’imiter et de se soumettre. Il est devenu la lecture de générations d’étudiants latino-américains. À la fin de sa vie, il dénonce l’impérialisme des États-Unis et fonde en 1925 l’Union latino-américaine pour défendre l’unité du continent.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IvEQy_ojmEE</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"José Ingenieros  - Podcast filosófico -" par Filo Errante</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/ingenieros-mini.webp</t>
@@ -6310,6 +6558,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arturo_Andr%C3%A9s_Roig" title=" Wikipedia"&gt;Arturo Andrés ROIG&lt;/a&gt; est un philosophe et historien des idées argentin. Né à Mendoza en 1922, il étudie la philosophie à l’université de Cuyo, puis à la Sorbonne, et se consacre d’abord à la philosophie antique, en particulier à Platon. Il se tourne ensuite vers l’histoire des idées en Amérique latine. Chassé de l’université par la dictature militaire en 1975, il s’exile en Équateur, à Quito, où il enseigne jusqu’à son retour en Argentine en 1984. Il meurt à Mendoza en 2012.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Théorie et critique de la pensée latino-américaine&lt;/em&gt; (1981), il cherche à quelles conditions une philosophie latino-américaine est possible. Il reprend une idée de Hegel : la philosophie commence quand un peuple « se tient lui-même pour valable ». Il appelle cette condition l’« a priori anthropologique » : pour penser, il faut d’abord s’affirmer comme sujet, capable de dire « nous » et de juger sa propre histoire, au lieu de se voir à travers le regard de l’Europe. L’histoire des idées doit retrouver les moments où les peuples d’Amérique latine se sont ainsi affirmés, depuis les indépendances.&lt;/p&gt; &lt;p&gt;Il étudie aussi les discours, qui peuvent servir à dominer ou à libérer, et la « fonction utopique » du langage, qui ouvre l’avenir. Dans &lt;em&gt;Éthique du pouvoir et moralité de la protestation&lt;/em&gt; (2002), il défend une « morale de l’émergence », celle des opprimés qui refusent leur condition. Il est l’une des grandes figures de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hy7Y-rDn1Yc</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Arturo Andrés Roig, pensamiento y unidad latinoamericana." par Roberto Manuel Vecchi</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/roig-mini.webp</t>
@@ -6366,6 +6624,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ronald_Dworkin" title=" Wikipedia"&gt;Ronald DWORKIN&lt;/a&gt; est un philosophe du droit et de la politique américain. Né en 1931 dans le Massachusetts, il étudie à Harvard et à Oxford, puis travaille comme avocat à New York. Il enseigne à Yale, puis succède en 1969 à Herbert Hart à la chaire de philosophie du droit d’Oxford, tout en enseignant à l’université de New York, et plus tard à Londres. Grand débatteur, il intervient régulièrement dans la presse sur les grandes questions de son temps. Il meurt à Londres en 2013.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Prendre les droits au sérieux&lt;/em&gt; (1977), il critique le positivisme juridique de Hart, pour qui le droit n’est qu’un ensemble de règles posées par les autorités. Le droit contient aussi des principes moraux, comme « nul ne doit profiter de sa propre faute », que les juges doivent appliquer dans les cas difficiles. Les droits individuels sont des « atouts » : ils l’emportent sur les calculs d’utilité collective. Dans &lt;em&gt;L’Empire du droit&lt;/em&gt; (1986), il compare le juge à l’auteur d’un roman écrit à plusieurs mains, qui doit poursuivre l’histoire de façon cohérente : c’est le « droit comme intégrité ».&lt;/p&gt; &lt;p&gt;En philosophie politique, il défend un &lt;a href="https://fr.wikipedia.org/wiki/Lib%C3%A9ralisme" title=" Wikipedia"&gt;libéralisme&lt;/a&gt; égalitaire : l’État doit traiter tous ses citoyens avec une égale considération. Il propose une « égalité des ressources » : chacun doit être responsable de ses choix, mais non des handicaps et des malchances qu’il n’a pas choisis. Dans &lt;em&gt;Justice pour les hérissons&lt;/em&gt; (2011), il soutient l’unité de toutes les valeurs.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gySLm3Z1OvA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Philosophy &amp; Politics - Ronald Dworkin &amp; Bryan Magee (1977)" par Philosophy Overdose</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/dworkin-mini.webp</t>
@@ -6424,6 +6692,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mar%C3%ADa_Lugones" title=" Wikipedia"&gt;María LUGONES&lt;/a&gt; est une philosophe féministe argentine. Née en 1944 dans la pampa argentine, dans une famille pauvre, elle part étudier aux États-Unis, en Californie puis à l’université du Wisconsin, où elle soutient sa thèse de philosophie en 1978. Elle enseigne ensuite la philosophie, la littérature comparée et les études de genre à l’université de Binghamton, dans l’État de New York. Militante, elle participe à des projets d’éducation populaire auprès des communautés latino-américaines. Elle meurt en 2020.&lt;/p&gt; &lt;p&gt;Dans un article célèbre de 1987, elle décrit le « voyage entre les mondes » que vivent les femmes de couleur aux États-Unis, qui passent sans cesse d’une culture à une autre. Elle propose de transformer cette expérience en une manière d’aimer les autres : voyager dans leur monde avec une « perception aimante », en jouant, au lieu de les juger depuis le sien avec une « perception arrogante ». Dans &lt;em&gt;Pèlerinages&lt;/em&gt; (2003), elle montre que les oppressions de race, de classe et de genre sont inséparables et s’entremêlent.&lt;/p&gt; &lt;p&gt;Elle prolonge la pensée d’Aníbal Quijano sur la « colonialité du pouvoir » en élaborant la notion de « colonialité du genre ». La colonisation n’a pas seulement imposé une hiérarchie des races : elle a aussi imposé aux peuples colonisés un système de genre européen, fondé sur l’opposition stricte des hommes et des femmes et sur l’hétérosexualité, que bien des sociétés ne connaissaient pas. Elle appelle à un féminisme décolonial. Elle est une figure majeure de la &lt;a href="https://fr.wikipedia.org/wiki/%C3%89tudes_d%C3%A9coloniales" title=" Wikipedia"&gt;pensée décoloniale&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p77WS9gxAx0</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"María Lugones | La colonialité du genre" par La main qui parle</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/lugones-mini.webp</t>
@@ -6485,6 +6763,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ernesto_Laclau" title=" Wikipedia"&gt;Ernesto LACLAU&lt;/a&gt; est un philosophe et politologue argentin. Né à Buenos Aires en 1935, il étudie l’histoire et milite dans la gauche nationale argentine. En 1969, à l’invitation de l’historien Eric Hobsbawm, il part en Angleterre, à Oxford, puis enseigne à l’université d’Essex, où il fonde un programme de recherche sur l’idéologie et l’analyse du discours. Il partage sa vie et son travail avec la philosophe belge Chantal Mouffe. Il meurt à Séville en 2014.&lt;/p&gt; &lt;p&gt;Avec elle, il publie en 1985 &lt;em&gt;Hégémonie et stratégie socialiste&lt;/em&gt;, l’un des livres fondateurs du « post-marxisme ». Les classes sociales ne sont pas des acteurs politiques tout faits : les identités politiques sont construites par les discours. Il reprend à Gramsci la notion d’« hégémonie » : une force politique domine quand elle réussit à rassembler des revendications diverses autour d’un projet commun. Dans &lt;em&gt;Émancipation(s)&lt;/em&gt; (1996), il montre que ce rassemblement se fait autour de « signifiants vides », comme « justice » ou « peuple », assez larges pour que chacun y mette ses propres attentes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Raison populiste&lt;/em&gt; (2005), il refuse de voir le &lt;a href="https://fr.wikipedia.org/wiki/Populisme_%28politique%29" title=" Wikipedia"&gt;populisme&lt;/a&gt; comme une maladie de la démocratie. C’est une manière de faire de la politique : des demandes insatisfaites, très différentes, se relient en une « chaîne d’équivalences » et construisent un « peuple » opposé à ceux d’en haut, souvent autour d’un nom ou d’un chef. Ses idées ont inspiré des gouvernements et des partis de gauche en Amérique latine et en Europe.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">qWqTmyRP4ho</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Qui sont les inspirateurs de Mélenchon ? (sur le "populisme de gauche" de Laclau et Mouffe)" par La Chronique Politique</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/laclau-mini.webp</t>
@@ -6514,6 +6802,138 @@
       <c r="P88" t="inlineStr">
         <is>
           <t xml:space="preserve">Argentine</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1">
+        <v>1811</v>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1888</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1811 – 1888</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Domingo Faustino SARMIENTO</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Domingo_Faustino_Sarmiento" title=" Wikipedia"&gt;Domingo Faustino SARMIENTO&lt;/a&gt; est un écrivain, pédagogue et homme d’État argentin. Né en 1811 à San Juan, au pied des Andes, dans une famille modeste, il apprend surtout seul. Opposant au dictateur Juan Manuel de Rosas, il s’exile au Chili, où il est journaliste et fonde la première école normale d’Amérique du Sud. Le gouvernement chilien l’envoie étudier les systèmes scolaires d’Europe et des États-Unis, où il se lie avec le pédagogue Horace Mann. Après la chute de Rosas, il devient président de l’Argentine de 1868 à 1874. Il meurt en 1888 à Asunción, au Paraguay.&lt;/p&gt; &lt;p&gt;Son livre le plus célèbre, &lt;em&gt;Facundo, ou civilisation et barbarie&lt;/em&gt; (1845), à la fois biographie d’un chef de guerre, essai et tableau de la pampa, oppose deux Argentines : celle des villes, ouvertes sur l’Europe, les lois et les idées, et celle des campagnes, dominée par les caudillos et la violence. Pour lui, la dictature de Rosas est le triomphe de la barbarie. Ce livre fondateur de la littérature argentine est aussi l’un des grands textes politiques de l’Amérique latine.&lt;/p&gt; &lt;p&gt;Convaincu que l’éducation fait les citoyens, il multiplie les écoles, les bibliothèques et les écoles normales, et fait venir des institutrices des États-Unis. Le jour de sa mort, le 11 septembre, est devenu la journée des enseignants dans les Amériques. Son mépris pour les gauchos et les peuples indigènes est aujourd’hui vivement critiqué. Il s’inscrit dans le &lt;a href="https://fr.wikipedia.org/wiki/Lib%C3%A9ralisme" title=" Wikipedia"&gt;libéralisme&lt;/a&gt; du XIXe siècle.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GJy2t9kRpno</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Sarmiento on the Conflict between Civilization and Barbarism" par Nick Nielsen</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/sarmiento-mini.webp</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Romantisme</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain et président argentin, auteur de Facundo, « civilisation et barbarie », et grand bâtisseur de l’école publique.</t>
+        </is>
+      </c>
+      <c r="N89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O89"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentine</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1">
+        <v>1769</v>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1854</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1769 – 1854</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simón RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sim%C3%B3n_Rodr%C3%ADguez" title=" Wikipedia"&gt;Simón RODRÍGUEZ&lt;/a&gt; est un pédagogue et philosophe vénézuélien. Né en 1769 à Caracas, enfant abandonné et recueilli, il devient instituteur et propose très tôt une réforme des écoles de la ville. Il est le précepteur du jeune &lt;a href="https://fr.wikipedia.org/wiki/Sim%C3%B3n_Bol%C3%ADvar" title=" Wikipedia"&gt;Simón Bolívar&lt;/a&gt;, futur libérateur de l’Amérique du Sud. Compromis en 1797 dans une conspiration républicaine contre la couronne d’Espagne, il doit fuir et passe plus de vingt ans en Europe sous le nom de Samuel Robinson. En 1805, à Rome, c’est devant lui que Bolívar jure, sur le mont Sacré, de libérer l’Amérique.&lt;/p&gt; &lt;p&gt;Rentré en Amérique en 1823, il est chargé par Bolívar de l’éducation en Bolivie. Il y fonde des écoles où les enfants des Indiens, des pauvres et des métis, garçons et filles, apprennent ensemble à lire et un métier, ce qui scandalise les élites. Son projet échoue et il passe le reste de sa vie à errer et à enseigner de ville en ville. Pour lui, il n’y a pas de république sans républicains : c’est l’école qui forme des citoyens libres, capables de penser par eux-mêmes et de travailler.&lt;/p&gt; &lt;p&gt;Lecteur de Rousseau, il refuse de copier les institutions de l’Europe ou des États-Unis. Dans &lt;em&gt;Sociétés américaines&lt;/em&gt; (1828), il écrit : « L’Amérique espagnole est originale ; originales doivent être ses institutions et son gouvernement. Ou nous inventons, ou nous errons. » Il meurt en 1854 à Amotape, au Pérou. Il est l’un des précurseurs d’une philosophie propre à l’Amérique latine.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RmuOcYR9ILs</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Simon Rodriguez | El Maestro Universal" par BetzaidaClassroom</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/simonrodriguez-mini.webp</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Républicanisme ; Lumières</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pédagogue et penseur vénézuélien, maître de Bolívar : « Ou nous inventons, ou nous errons ».</t>
+        </is>
+      </c>
+      <c r="N90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O90"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vénézuélienne</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-americains.xlsx
+++ b/data/frise-philosophes-americains.xlsx
@@ -4087,941 +4087,937 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="n">
+    <row r="43" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1">
+        <v>1929</v>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1929 – 2024</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newton DA COSTA</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Newton_da_Costa" title=" Wikipedia (en)"&gt;Newton DA COSTA&lt;/a&gt; est un logicien et philosophe brésilien, l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/Logique_paraconsistante" title=" Wikipedia"&gt;logique paraconsistante&lt;/a&gt;. Né à Curitiba, il étudie d’abord le génie civil puis les mathématiques, et enseigne à l’université fédérale du Paraná, puis à l’université de São Paulo et à l’université fédérale de Santa Catarina.&lt;/p&gt; &lt;p&gt;Dans la logique classique, une seule contradiction suffit à tout prouver : si l’on admet à la fois une proposition et sa négation, on peut en déduire n’importe quoi. C’est le principe d’« explosion ». Dès sa thèse de 1963, il construit des systèmes logiques, appelés « calculs C », où l’on peut admettre certaines contradictions sans que toute la théorie s’effondre. Le nom de « paraconsistance » leur est donné en 1976 par le philosophe péruvien Francisco Miró Quesada. Ces logiques permettent de raisonner rigoureusement sur des informations contradictoires, comme celles d’une base de données, d’un témoignage ou d’une théorie scientifique en crise.&lt;/p&gt; &lt;p&gt;Il &lt;a href="https://www.youtube.com/watch?v=Zo-o_fHnfkA" title="Newton da Costa sobre a leitura par Fábio Salgado de Carvalho"&gt;étend ces travaux &lt;/a&gt;à la théorie des ensembles et à la philosophie des sciences. Avec Steven French, il développe la notion de « quasi-vérité » : une théorie scientifique peut être partiellement vraie et utile sans être entièrement exacte. Avec Francisco Antônio Dória, il montre en 1991 que certaines questions de la théorie du chaos sont indécidables : aucun calcul ne peut y répondre. Membre de nombreuses académies, il a formé une importante école de logique au Brésil et en Amérique latine. Il meurt en 2024 à Florianópolis.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LXOUyxZNuL8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Newton da Costa, o maior pensador brasileiro" par Verve Científica</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dacosta-mini.webp</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logique paraconsistante</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logicien brésilien, l’un des fondateurs des logiques paraconsistantes.</t>
+        </is>
+      </c>
+      <c r="N43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brésilienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
         <v>1930</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B44" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C44" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D44" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E44" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F44" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G44" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H44" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="I43" s="9"/>
-      <c r="J43" s="2" t="s">
+      <c r="I44" s="9"/>
+      <c r="J44" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="K44" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="L44" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="N43" s="1" t="s">
+      <c r="N44" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1">
+    <row r="45" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1">
         <v>1930</v>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2018</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1930 – 2018</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Aníbal QUIJANO</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal QUIJANO&lt;/a&gt; est un sociologue péruvien, l’un des grands penseurs latino-américains du XXe siècle et le fondateur de la pensée décoloniale. Né en 1928 à Yanama, dans les Andes péruviennes, il étudie à l’université de San Marcos, à Lima, où il enseigne ensuite la sociologie. Dans les années 1960 et 1970, il participe aux travaux de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_la_d%C3%A9pendance" title=" Wikipedia"&gt;théorie de la dépendance&lt;/a&gt;, qui explique le sous-développement de l’Amérique latine par sa place subordonnée dans l’économie mondiale, et étudie la condition des populations indiennes et métisses des villes.&lt;/p&gt; &lt;p&gt;En 1992, pour le cinquième centenaire de l’arrivée de Christophe Colomb, il publie l’article « Colonialité et modernité/rationalité », qui forge la notion de « colonialité du pouvoir ». La conquête de l’Amérique a donné naissance à la fois au capitalisme mondial et à une idée nouvelle, celle de « race », qui a permis de classer les peuples en supérieurs et inférieurs et de distribuer entre eux le travail : le salariat pour les Européens, le servage pour les Indiens, l’esclavage pour les Africains. Cette classification a survécu à l’indépendance des colonies : elle structure encore les rapports sociaux, le savoir et la manière dont chacun se perçoit. Quijano critique aussi l’« eurocentrisme », qui fait de l’histoire européenne le modèle de l’histoire universelle.&lt;/p&gt; &lt;p&gt;Professeur à l’université de Binghamton, aux États-Unis, il anime le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt; avec Walter Mignolo et Enrique Dussel. La philosophe argentine &lt;a href="https://fr.wikipedia.org/wiki/Mar%C3%ADa_Lugones" title=" Wikipedia"&gt;María Lugones&lt;/a&gt; a prolongé son concept dans celui de « colonialité du genre ». Il meurt à Lima en 2018.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t xml:space="preserve">aibG8RehlTE</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">"Aníbal Quijano - Colonialidad del Poder" par Filo Errante</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/quijano-mini.webp</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K44" s="1" t="inlineStr">
+      <c r="K45" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Pensée décoloniale</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">sociologue péruvien, inventeur de la « colonialité du pouvoir » et fondateur de la pensée décoloniale.</t>
         </is>
       </c>
-      <c r="N44" s="1" t="inlineStr">
+      <c r="N45" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
         </is>
       </c>
-      <c r="O44" s="1"/>
-      <c r="P44" t="inlineStr">
+      <c r="O45" s="1"/>
+      <c r="P45" t="inlineStr">
         <is>
           <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n">
+    <row r="46" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="n">
         <v>1931</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B46" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C46" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D46" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_Rorty" title=" Wikipedia"&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href="https://www.youtube.com/watch?v=lfx4Jag1ic4"  title="Le pragmatisme : définition, exemples par le savoir partagé"&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href="https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism" title=" a bas l'autorité par laviedesidees"&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas "vrais" ou "faux". &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales, on trouve  &lt;a href="https://www.youtube.com/watch?v=MgU0dXZ3umM" title="L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli"&gt;" Contingence, ironie et solidarité "&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans " Achieving Our Country" (1998),  il y appelle la gauche américaine à abandonner le "culturalisme" pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la "post-vérité". Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F46" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G46" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H46" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="I45" s="9"/>
-      <c r="J45" s="2" t="s">
+      <c r="I46" s="9"/>
+      <c r="J46" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="K46" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="L45" s="2" t="s">
+      <c r="L46" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="N45" s="1" t="s">
+      <c r="N46" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
+    <row r="47" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
         <v>1932</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B47" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Searle"  title=" Wikipedia"&gt;John SEARLE&lt;/a&gt; était un philosophe américain  connu pour ses travaux influents dans plusieurs domaines, notamment la philosophie du langage, la philosophie de l'esprit et la philosophie sociale. Il  a développé et systématisé la théorie des &lt;a href="https://www.youtube.com/watch?v=pIbkpLfrD6A" title="
 La théorie des actes de langage (2) - John Searle par Heraut du Mont Parnasse"&gt;actes de langage&lt;/a&gt; car, pour lui, parler une langue, ce n'est pas seulement émettre des sons ou des suites de symboles, mais accomplir des actions. &lt;/p&gt; &lt;p&gt; Défenseur du "naturalisme biologique" en philosophie de l'esprit. Il s'oppose au dualisme cartésien tout en refusant le matérialisme réducteur qui nierait l'existence de &lt;a href="https://www.youtube.com/watch?v=EriAhi0mj7w" title=" Conscience et matière grise par TEDx Talks"&gt;la conscience&lt;/a&gt; ou la réduirirait à de simples phénomènes physiques. Pour lui, les états mentaux (douleur, croyances, désirs, conscience) sont des phénomènes  &lt;a href="https://www.youtube.com/watch?v=Bq2bfSzkTfU"  title="John Searle - Une personne peut-elle être une âme ? par Closer To Truth"&gt;biologiques réels&lt;/a&gt;, causés par des processus neuronaux du cerveau, mais ils ne sont pas réductibles à ces processus au sens où ils émergent à un niveau supérieur et possèdent des propriétés irréductibles.&lt;/p&gt; &lt;p&gt; L'une des ses contributions les plus célèbres est son argument de la &lt;a href="https://www.youtube.com/watch?v=P5DtwDr9YEc" title=" La Chambre chinoise par Ian et frank"&gt;Chambre Chinoise&lt;/a&gt;. Cet argument vise à réfuter la thèse de l'IA forte (position selon laquelle un ordinateur programmé de manière appropriée n'est pas seulement un outil pour l'étude de l'esprit, mais qu'il est véritablement un esprit, capable de comprendre et de posséder d'autres états cognitifs) opposé à l'IA faible (position selon laquelle les ordinateurs sont des outils utiles pour étudier l'esprit, mais qu'ils ne sont pas eux-mêmes des esprits). &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://labo.nonmarchand.org/pmwiki/uploads/Textes/JohnSearleLaConstructionDeLaRealiteSociale/JohnSearle_LaConstructionDeLaRealiteSociale.pdf"  title=" La construction e la réalité sociale par nonmarchand"&gt;"La Construction de la Réalité Sociale"&lt;/a&gt;, il étend sa théorie des actes de langage et de l'intentionnalité pour expliquer comment nous construisons des faits institutionnels et sociaux. Il distingue les "Faits bruts" qui existent indépendamment de toute institution humaine (par exemple, la montagne Everest) des "Faits institutionnels" qui n'existent qu'en vertu d'institutions humaines et de l'accord collectif (par exemple, l'argent, le mariage, la propriété). &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="H47" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="I46" s="1"/>
-      <c r="J46" s="2" t="s">
+      <c r="I47" s="1"/>
+      <c r="J47" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="K47" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="L47" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n">
-        <v>1933</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OvpUxJQRAbw</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Charles Parsons Intuition and Reason | HUSSERL to GODEL | Mark van Atten" par The Van Leer Jerusalem Institute - מכון ון ליר בירושלים</t>
-        </is>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="N47" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P47" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
+        <v>1933</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OvpUxJQRAbw</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Charles Parsons Intuition and Reason | HUSSERL to GODEL | Mark van Atten" par The Van Leer Jerusalem Institute - מכון ון ליר בירושלים</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
         <v>1934</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B49" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C49" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D49" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Enrique_Dussel"  title=" Wikipedia"&gt;Enrique DUSSEL&lt;/a&gt; était un philosophe argentin majeurs de la décolonialité et de la philosophie latino-américaine de la liberation.  Jeune intellectuel engagé dans les mouvements étudiants et opposé aux régimes autoritaires, il a été persécuté en Argentine avant de s’exiler au Mexique en 1975, où il a poursuivi sa carrière académique et développé sa pensée. Il élabore une &lt;a href="https://www.youtube.com/watch?v=QGPosp7lYlM" title="Enrique Dussel and the Philosophy of Liberation – Decolonizing Thought par Darina Metreveli"&gt;philosophie de la libération &lt;/a&gt; qui remet en question l’ontologie monologique de la modernité et introduit une approche éthique et alteritaire inspirée par Levinas, souvent décrite sous le nom d’analectique ou de dialectique positive. &lt;/p&gt; &lt;p&gt; Pionnier du décolonialisme latino-américain, il contribue à la construction des cadres Modernité/Colonialité et à l’idée d’une transmodernité, articulant critique de la modernité et invitation à repenser les rapports Nord-Sud et centre-périphérie. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures : &lt;a href="https://www.youtube.com/watch?v=nXNyqKCrKLY" title="Enrique Dussel, métaphysicien de la libération - Emmanuel Lévine par lundimatin"&gt;"Méthode pour une philosophie de la libération" &lt;/a&gt; paru en  1974 et "Filosofía ética latinoamericana" (période majeure)  posent les bases d’une philosophie enracinée dans les expériences des peuples opprimés et des contextes colonisés. &lt;/p&gt; &lt;p&gt; Il est reconnu dans les &lt;a href="https://lestempsquirestent.org/fr/numeros/numero-7/enrique-dussel-un-philosophe-indispensable-pour-decoloniser-la-theologie-politique" title="Enrique Dussel,
 un philosophe indispensable pour décoloniser la théologie politique par les temps qui restent"&gt;milieux décoloniaux &lt;/a&gt; et philosophie de la libération, mais demeure moins connu du grand public français, bien que des traductions et des analyses apparaissent et stimulent l’intérêt académique en France. Son travail nourrit le courant décolonial qui met en évidence l’interdépendance entre modernité et colonialité depuis 1492 et propose des axes pour une pensée transmoderne, dépassant les cadres classiques de la philosophie occidentale. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F49" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="G49" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="H48" s="9" t="s">
+      <c r="H49" s="9" t="s">
         <v>406</v>
-      </c>
-      <c r="I48" s="9"/>
-      <c r="J48" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiers-mondisme ; Théologie de la libération ; Philosophie de la libération ; Pensée décoloniale</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O48" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>410</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>413</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiers-mondisme ; Théologie de la libération ; Philosophie de la libération ; Pensée décoloniale</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O49" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="I50" s="9"/>
+      <c r="J50" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="K50" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="L50" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B50" s="1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="G50" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="I50" s="1"/>
-      <c r="J50" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="N50" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P50" s="1" t="s">
+    </row>
+    <row r="51" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G51" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P51" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="XFC50" s="0"/>
-      <c r="XFD50" s="0"/>
-    </row>
-    <row r="51" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16" t="n">
+      <c r="XFC51" s="0"/>
+      <c r="XFD51" s="0"/>
+    </row>
+    <row r="52" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="16" t="n">
         <v>1935</v>
       </c>
-      <c r="B51" s="16" t="n">
+      <c r="B52" s="16" t="n">
         <v>2003</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C52" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D52" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E52" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="F51" s="16" t="s">
+      <c r="F52" s="16" t="s">
         <v>428</v>
       </c>
-      <c r="G51" s="18" t="s">
+      <c r="G52" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H52" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="I51" s="18"/>
-      <c r="J51" s="2" t="s">
+      <c r="I52" s="18"/>
+      <c r="J52" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="K52" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="L51" s="14" t="s">
+      <c r="L52" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="M51" s="14" t="s">
+      <c r="M52" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N51" s="14" t="s">
+      <c r="N52" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="n">
+    <row r="53" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
         <v>1937</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B53" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C53" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D53" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E53" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F53" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G53" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="H52" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>438</v>
-      </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="n">
-        <v>1938</v>
-      </c>
-      <c r="B53" s="7" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>446</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libéralisme ; Minarchisme ; Déontologisme</t>
-        </is>
+        <v>127</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>439</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="N53" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="N53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
         <v>1938</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>449</v>
+      <c r="B54" s="7" t="n">
+        <v>2002</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tom_Regan"  title=" Wikipedia"&gt;Tom REGAN&lt;/a&gt; était un philosophe américain   &lt;a href="https://www.youtube.com/watch?v=hgVMf3q4Vh4"  title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Pensées antispécistes par The Critical Vegan"&gt;antispéciste &lt;/a&gt; influent dans le domaine de l'éthique animale, considéré comme un pionnier de la théorie des droits des animaux sur une base déontologique. Né à Pittsburgh, il enseigne de 1967 à 2001 à l’université d’État de Caroline du Nord. Il développe une approche abolitionniste opposée à l'utilitarisme de Peter Singer, arguant que les mammifères normaux d'un an ou plus sont des "sujets-d'une-vie" dotés d'une valeur inhérente, méritant des droits moraux fondamentaux indépendamment de leur utilité. Inspiré par Kant mais étendu aux non-humains, il définit ces sujets comme des êtres conscients pour qui leur vie importe intrinsèquement, justifiant l'interdiction absolue de l'exploitation. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales sont : "The Case for Animal Rights" paru en 1983, traduit en français comme  &lt;a href="http://tomregan.free.fr/" title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Les Droits des animaux par Tom Regan"&gt;"Les Droits des animaux" &lt;/a&gt; en 2013 : son magnum opus, salué comme un classique moderne critiquant Descartes et plaidant pour le "principe de respect" envers tout sujet-d'une-vie. "All That Dwell Therein" paru en  1982 : recueil d'essais sur le végétarisme et l'éthique animale. &lt;/p&gt; &lt;p&gt; Ses idées ont profondément marqué le mouvement des droits des animaux, influençant débats sur végétarisme, anti-vivisection et critique de l'environnementalisme indirect, tout en étant cité par des penseurs comme Derrida ou dans des ouvrages comme ceux de Jean-Baptiste Jeangène Vilmer. Dans &lt;em&gt;Empty Cages&lt;/em&gt; (2004), destiné au grand public, il résume son combat : il ne s’agit pas d’agrandir les cages, mais de les vider. &lt;/p&gt; </t>
-        </is>
+        <v>442</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>443</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>455</v>
+        <v>445</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>446</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Minarchisme ; Déontologisme</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tom_Regan"  title=" Wikipedia"&gt;Tom REGAN&lt;/a&gt; était un philosophe américain   &lt;a href="https://www.youtube.com/watch?v=hgVMf3q4Vh4"  title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Pensées antispécistes par The Critical Vegan"&gt;antispéciste &lt;/a&gt; influent dans le domaine de l'éthique animale, considéré comme un pionnier de la théorie des droits des animaux sur une base déontologique. Né à Pittsburgh, il enseigne de 1967 à 2001 à l’université d’État de Caroline du Nord. Il développe une approche abolitionniste opposée à l'utilitarisme de Peter Singer, arguant que les mammifères normaux d'un an ou plus sont des "sujets-d'une-vie" dotés d'une valeur inhérente, méritant des droits moraux fondamentaux indépendamment de leur utilité. Inspiré par Kant mais étendu aux non-humains, il définit ces sujets comme des êtres conscients pour qui leur vie importe intrinsèquement, justifiant l'interdiction absolue de l'exploitation. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales sont : "The Case for Animal Rights" paru en 1983, traduit en français comme  &lt;a href="http://tomregan.free.fr/" title=" Les animaux aussi ont une valeur. Valeur inhérente &amp; respect. - Tom Regan - Les Droits des animaux par Tom Regan"&gt;"Les Droits des animaux" &lt;/a&gt; en 2013 : son magnum opus, salué comme un classique moderne critiquant Descartes et plaidant pour le "principe de respect" envers tout sujet-d'une-vie. "All That Dwell Therein" paru en  1982 : recueil d'essais sur le végétarisme et l'éthique animale. &lt;/p&gt; &lt;p&gt; Ses idées ont profondément marqué le mouvement des droits des animaux, influençant débats sur végétarisme, anti-vivisection et critique de l'environnementalisme indirect, tout en étant cité par des penseurs comme Derrida ou dans des ouvrages comme ceux de Jean-Baptiste Jeangène Vilmer. Dans &lt;em&gt;Empty Cages&lt;/em&gt; (2004), destiné au grand public, il résume son combat : il ne s’agit pas d’agrandir les cages, mais de les vider. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="I55" s="9"/>
+      <c r="J55" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="K54" s="2" t="s">
+      <c r="K55" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L54" s="2" t="s">
+      <c r="L55" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="B55" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saul_Kripke"  title=" Wikipedia"&gt;Saul KRIPKE&lt;/a&gt; était un philosophe américain de la tradition analytique connu pour ses apports décisifs en logique modale, en métaphysique et en philosophie du langage. Très jeune, il révolutionne la logique en introduisant la sémantique des mondes possibles, aujourd’hui appelée &lt;a href="https://www.youtube.com/watch?v=_sIgAdvhruU"title="Qui est Saul Kripke ? par Monsieur Phi"&gt;"cadres de Kripke"&lt;/a&gt;, qui permet de formaliser la modalité (le nécessaire et le possible) de façon rigoureuse. &lt;/p&gt; &lt;p&gt; Son œuvre la plus influente est "Naming and Necessity", où il critique la conception descriptiviste des noms défendue par Frege et Russell. Selon lui, un  &lt;a href="https://www.youtube.com/watch?v=d7-8Avem7EE" title="Saul Kripke, La logique des noms propres. par Jtgrandtour"&gt; nom propre&lt;/a&gt; n’équivaut pas à une description mais fonctionne comme un « désignateur rigide » : il désigne le même individu dans tous les mondes possibles. Cette idée bouleverse la philosophie du langage et entraîne une redéfinition de la notion de référence.&lt;/p&gt; &lt;p&gt;  Il montre également qu’il existe des vérités nécessaires découvertes empiriquement : par exemple, l’identité « l’eau est H₂O » est nécessaire, mais nous ne l’avons apprise qu’a posteriori. Ce concept de nécessité a posteriori a marqué un tournant dans la métaphysique contemporaine. À l’inverse, il identifie la possibilité de certaines vérités contingentes connues a priori, ce qui remet en cause des distinctions classiques entre connaissance et modalité. &lt;/p&gt; &lt;p&gt; Il s’oppose au physicalisme en arguant que l’on peut concevoir un monde où tous les états cérébraux existent sans que la conscience subjective "le qualia" ne soit présente. Cette critique alimente encore aujourd’hui les débats sur la nature de la conscience. Son ouvrage "Wittgenstein on Rules and Private Language" propose une lecture radicale de Wittgenstein, selon laquelle toute règle est sujette à un scepticisme profond sur son application. Bien que controversée, cette interprétation a largement stimulé les discussions en philosophie du langage et en épistémologie. &lt;/p&gt; &lt;p&gt; Connu aussi pour son ouvrage " On two Paradoxes of Knowledge" et son  &lt;a href="https://www.youtube.com/watch?v=AzaUSC--2G0"  title="Le Paradoxe de l'Examen selon Saul Kripke par Silogic"&gt;"paradoxe de l'examen"&lt;/a&gt;. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P55" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="n">
-        <v>1941</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Lewis_(philosophe)"  title=" Wikipedia"&gt;David LEWIS&lt;/a&gt; était un philosophe américain connu pour sa théorie du  réalisme modal, selon laquelle il existe un nombre infini de mondes possibles concrets et causalement isolés les uns des autres. Son ouvrage majeur   &lt;a href="https://www.youtube.com/watch?v=-QlqLDLifuc" title="David Lewis - "De la pluralité des mondes" - De quoi parle ce livre ? par Philosophie 21"&gt;"On the Plurality of Worlds"&lt;/a&gt;  sortie en 1986, expose cette position révolutionnaire : pour lui, chaque monde possible existe aussi réellement que notre monde actuel, et sert à comprendre la modalité, c'est-à-dire ce qui pourrait être ou ce qui doit être. &lt;/p&gt; &lt;p&gt; Il a également proposé la théorie des contreparties en logique modale : au lieu de supposer que les personnes ou objets existent dans plusieurs mondes possibles, il affirme que chaque individu de notre monde a des « contreparties » dans les autres mondes possibles qui partagent certaines caractéristiques mais ne sont pas identiques à lui. Cette approche constitue une alternative à la logique modale traditionnelle, notamment celle de Saul Kripke. &lt;/p&gt; &lt;p&gt; Sa métaphysique est marquée par une conception atomiste (pointilliste) : la réalité n’est qu’une vaste mosaïque de faits locaux, chaque fait étant centré sur un « point » ayant des propriétés intrinsèques. Ce point de vue s’inspire de David Hume, d’où le nom « survenance humienne », refusant les liens nécessaires entre les faits et privilégiant une juxtaposition de qualités locales. &lt;/p&gt; &lt;p&gt; Il  a beaucoup écrit sur la philosophie du langage, la philosophie de l’esprit, l’épistémologie, la logique philosophique et la philosophie des mathématiques. Son premier grand ouvrage, "Convention" de 1969, analyse les conventions sociales à l’aide de la théorie des jeux, en montrant leur caractère arbitraire et leur diffusion par la connaissance commune et le précédent. Il s a marqué durablement la philosophie analytique.  &lt;a href="https://www.youtube.com/watch?v=g3jQwDP_Lyc" title="David Lewis - "David Lewis Speaks at La Trobe University par TimeSparrow"&gt;"Ses théories&lt;/a&gt; sont incontournables dans les débats sur les mondes possibles, la modalité, la causalité, la convention sociale, et l’atomisme métaphysique. Ses ouvrages, tels que Counterfactuals et Philosophical Papers, restent des références dans l’analyse logique et conceptuelle contemporaine. &lt;/p&gt; &lt;audio controls title=" On dit de David Lewis que c'est le plus grand métaphysicien qu’on ait vu depuis Leibniz par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18292-28.02.2019-ITEMA_21995453-0.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="I56" s="9"/>
+    </row>
+    <row r="56" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saul_Kripke"  title=" Wikipedia"&gt;Saul KRIPKE&lt;/a&gt; était un philosophe américain de la tradition analytique connu pour ses apports décisifs en logique modale, en métaphysique et en philosophie du langage. Très jeune, il révolutionne la logique en introduisant la sémantique des mondes possibles, aujourd’hui appelée &lt;a href="https://www.youtube.com/watch?v=_sIgAdvhruU"title="Qui est Saul Kripke ? par Monsieur Phi"&gt;"cadres de Kripke"&lt;/a&gt;, qui permet de formaliser la modalité (le nécessaire et le possible) de façon rigoureuse. &lt;/p&gt; &lt;p&gt; Son œuvre la plus influente est "Naming and Necessity", où il critique la conception descriptiviste des noms défendue par Frege et Russell. Selon lui, un  &lt;a href="https://www.youtube.com/watch?v=d7-8Avem7EE" title="Saul Kripke, La logique des noms propres. par Jtgrandtour"&gt; nom propre&lt;/a&gt; n’équivaut pas à une description mais fonctionne comme un « désignateur rigide » : il désigne le même individu dans tous les mondes possibles. Cette idée bouleverse la philosophie du langage et entraîne une redéfinition de la notion de référence.&lt;/p&gt; &lt;p&gt;  Il montre également qu’il existe des vérités nécessaires découvertes empiriquement : par exemple, l’identité « l’eau est H₂O » est nécessaire, mais nous ne l’avons apprise qu’a posteriori. Ce concept de nécessité a posteriori a marqué un tournant dans la métaphysique contemporaine. À l’inverse, il identifie la possibilité de certaines vérités contingentes connues a priori, ce qui remet en cause des distinctions classiques entre connaissance et modalité. &lt;/p&gt; &lt;p&gt; Il s’oppose au physicalisme en arguant que l’on peut concevoir un monde où tous les états cérébraux existent sans que la conscience subjective "le qualia" ne soit présente. Cette critique alimente encore aujourd’hui les débats sur la nature de la conscience. Son ouvrage "Wittgenstein on Rules and Private Language" propose une lecture radicale de Wittgenstein, selon laquelle toute règle est sujette à un scepticisme profond sur son application. Bien que controversée, cette interprétation a largement stimulé les discussions en philosophie du langage et en épistémologie. &lt;/p&gt; &lt;p&gt; Connu aussi pour son ouvrage " On two Paradoxes of Knowledge" et son  &lt;a href="https://www.youtube.com/watch?v=AzaUSC--2G0"  title="Le Paradoxe de l'Examen selon Saul Kripke par Silogic"&gt;"paradoxe de l'examen"&lt;/a&gt;. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>463</v>
+      </c>
       <c r="J56" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>475</v>
+        <v>464</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>465</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>476</v>
+        <v>466</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="N56" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="332.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P56" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
+        <v>1941</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Lewis_(philosophe)"  title=" Wikipedia"&gt;David LEWIS&lt;/a&gt; était un philosophe américain connu pour sa théorie du  réalisme modal, selon laquelle il existe un nombre infini de mondes possibles concrets et causalement isolés les uns des autres. Son ouvrage majeur   &lt;a href="https://www.youtube.com/watch?v=-QlqLDLifuc" title="David Lewis - "De la pluralité des mondes" - De quoi parle ce livre ? par Philosophie 21"&gt;"On the Plurality of Worlds"&lt;/a&gt;  sortie en 1986, expose cette position révolutionnaire : pour lui, chaque monde possible existe aussi réellement que notre monde actuel, et sert à comprendre la modalité, c'est-à-dire ce qui pourrait être ou ce qui doit être. &lt;/p&gt; &lt;p&gt; Il a également proposé la théorie des contreparties en logique modale : au lieu de supposer que les personnes ou objets existent dans plusieurs mondes possibles, il affirme que chaque individu de notre monde a des « contreparties » dans les autres mondes possibles qui partagent certaines caractéristiques mais ne sont pas identiques à lui. Cette approche constitue une alternative à la logique modale traditionnelle, notamment celle de Saul Kripke. &lt;/p&gt; &lt;p&gt; Sa métaphysique est marquée par une conception atomiste (pointilliste) : la réalité n’est qu’une vaste mosaïque de faits locaux, chaque fait étant centré sur un « point » ayant des propriétés intrinsèques. Ce point de vue s’inspire de David Hume, d’où le nom « survenance humienne », refusant les liens nécessaires entre les faits et privilégiant une juxtaposition de qualités locales. &lt;/p&gt; &lt;p&gt; Il  a beaucoup écrit sur la philosophie du langage, la philosophie de l’esprit, l’épistémologie, la logique philosophique et la philosophie des mathématiques. Son premier grand ouvrage, "Convention" de 1969, analyse les conventions sociales à l’aide de la théorie des jeux, en montrant leur caractère arbitraire et leur diffusion par la connaissance commune et le précédent. Il s a marqué durablement la philosophie analytique.  &lt;a href="https://www.youtube.com/watch?v=g3jQwDP_Lyc" title="David Lewis - "David Lewis Speaks at La Trobe University par TimeSparrow"&gt;"Ses théories&lt;/a&gt; sont incontournables dans les débats sur les mondes possibles, la modalité, la causalité, la convention sociale, et l’atomisme métaphysique. Ses ouvrages, tels que Counterfactuals et Philosophical Papers, restent des références dans l’analyse logique et conceptuelle contemporaine. &lt;/p&gt; &lt;audio controls title=" On dit de David Lewis que c'est le plus grand métaphysicien qu’on ait vu depuis Leibniz par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18292-28.02.2019-ITEMA_21995453-0.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="I57" s="9"/>
+      <c r="J57" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="332.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
         <v>1942</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B58" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C58" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D58" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Daniel_Dennett"  style="color:#6A142A"  title=" Wikipedia"&gt;Daniel DENNETT&lt;/a&gt; était un  philosophe américain, figure importante et  influente de la philosophie de l'esprit, de la biologie et des sciences cognitives. Ses travaux se caractérisent par une volonté d'intégrer les découvertes scientifiques (biologie évolutionniste, neurosciences, intelligence artificielle) à la réflexion philosophique, souvent pour démanteler des intuitions traditionnelles qu'il juge erronées. &lt;/p&gt; &lt;p&gt; La Théorie de l'Esprit comme &lt;a href="https://www.youtube.com/watch?v=LKJJpvdqkFA" style="color:#88A1E9" title="Cette histoire va vous retourner le cerveau. | "Où suis-je" de Daniel Dennett par Monsieur Phi"&gt;"Position Intentionnelle"&lt;/a&gt; est sa contribution majeure. Il propose que pour prédire et expliquer le comportement d'un système (qu'il s'agisse d'un humain, d'un animal, d'un ordinateur ou même d'un thermostat), nous pouvons adopter trois "stances" : &lt;/p&gt; &lt;p&gt;La stance physique : On décrit le système par sa physique et sa chimie. Très difficile pour des systèmes complexes. &lt;/p&gt; &lt;p&gt;La stance du design : On considère le système comme conçu pour une fonction spécifique (ex: "ce thermostat est fait pour réguler la température"). &lt;/p&gt; &lt;p&gt;La stance intentionnelle : On traite le système comme s'il avait des croyances, des désirs et une rationalité. C'est une stratégie de prédiction extrêmement efficace, même si les croyances et désirs ne sont pas "réels" au sens littéral. Pour lui, avoir des croyances, c'est être un système dont le comportement peut être prédit avec succès par la stance intentionnelle. &lt;/p&gt; &lt;p&gt; Il est un matérialiste farouche et  rejette l'idée d'un &lt;a href="https://www.nonfiction.fr/article-1116-daniel_dennett_est_il_le_diable_.htm" title="Daniel Dennett est-il le diable ? par nonfiction"&gt;"théâtre cartésien"&lt;/a&gt;, un endroit dans le cerveau où tout se réunirait pour être "vu" par un &lt;a href="https://www.youtube.com/watch?v=0It9fwSj6xM"  title="Le moi comme illusion (Daniel Dennett, la conscience expliquée 4) par Philosophie Analytique"&gt;"spectateur" (le soi)&lt;/a&gt;. Pour lui, c'est une illusion.
 Il défend plutôt un modèle de "espace de travail global" : la conscience émerge de processus cérébraux parallèles et compétitifs. Une information devient "consciente" lorsqu'elle gagne une compétition pour être diffusée à grande échelle dans le cerveau, rendant ainsi disponible pour d'autres systèmes (mémoire, langage, prise de décision). Il n'y a pas de "centre" unique. &lt;/p&gt; &lt;p&gt; Il  considère que l'idée de la sélection naturelle de Darwin est "l'idée la plus dangereuse de tous les temps" car elle a un pouvoir explicatif immense, bien au-delà de la biologie. Il l'étend à d'autres domaines grâce au concept de "mèmes" (introduit par Richard Dawkins).
 Les mèmes sont des unités de culture (idées, mélodies, modes, concepts) qui se répliquent, mutent et sont sélectionnées dans le "payage" des esprits humains. Le langage,&lt;a href="https://www.youtube.com/shorts/bG3YBavy29Y" title="Cette histoire va vous retourner le cerveau | Daniel Dennett par StopCroyance"&gt; la religion&lt;/a&gt;, la morale peuvent être analysés comme des produits d'un processus darwinien. &lt;/p&gt; &lt;p&gt; Il défend une forme de libre arbitre qu'il estime compatible avec le déterminisme scientifique (le fait que l'univers soit régi par des lois causales). Pour lui, le libre arbitre n'est pas une "causalité magique" qui échapperait aux lois de la nature.  C'est la capacité d'un agent complexe (comme un être humain) à se projeter dans le futur, à évaluer les conséquences de ses actes et à agir en fonction de ses raisons. Ce libre arbitre est le produit de l'évolution et de la culture. Il est réel et précieux, même s'il n'est pas "libre" au sens d'une exemption des lois de la physique. &lt;/p&gt; &lt;audio controls title=" "Daniel Dennett, le penseur qui a révolutionné la philosophie des sciences et de l’esprit" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24419-10.05.2024-ITEMA_23737219-2024C51851S0131-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F58" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G58" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="H57" s="9" t="s">
+      <c r="H58" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="I57" s="9"/>
-      <c r="J57" s="2" t="s">
+      <c r="I58" s="9"/>
+      <c r="J58" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K57" s="2" t="s">
+      <c r="K58" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="L57" s="2" t="s">
+      <c r="L58" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="N57" s="1" t="s">
+      <c r="N58" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="n">
+    <row r="59" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="n">
         <v>1943</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B59" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C59" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Marilyn MCCORD-ADAMS</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
+      <c r="E59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marilyn_McCord_Adams" title=" Wikipedia"&gt;Marilyn McCORD ADAMS&lt;/a&gt; était une philosophe américaine et une théologienne anglicane, reconnue pour son travail en philosophie de la religion et en philosophie médiévale. Elle a aussi été ordonnée prêtre épiscopalienne, ce qui donnait à sa réflexion philosophique une forte dimension spirituelle et pastorale. Elle a étudié à l’Université de l’Illinois puis à Cornell, où elle a obtenu son doctorat en philosophie en 1967. Sa carrière universitaire l’a menée à Michigan, UCLA, Yale, Oxford et elle a été la première femme, ainsi que la première Américaine, à occuper la chaire Regius de divinité à Oxford. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://senate.universityofcalifornia.edu/in-memoriam/files/marilyn-adams.html" title="Marilyn Adans par university of california"&gt;Son apport le plus célèbre &lt;/a&gt; concerne l’étude de Guillaume d’Ockham, à qui elle a consacré une grande étude en deux volumes qui a beaucoup compté dans les recherches sur la théologie médiévale. Elle a aussi travaillé sur l’eucharistie, le christologie et d’autres auteurs médiévaux comme Thomas d’Aquin, Gilles de Rome et Duns Scot. &lt;/p&gt; &lt;p&gt; En  &lt;a href="https://www.youtube.com/watch?v=nFRGDG__ELM" title="Marilyn Adans par Real Atheology"&gt;philosophie de la religion, &lt;/a&gt; elle est connue pour ses analyses du mal extrême, qu’elle appelait les horrendous evils. Son idée centrale est qu’une théologie sérieuse doit prendre au sérieux les souffrances qui semblent détruire toute possibilité de sens, et montrer comment elles peuvent malgré tout être intégrées dans une vision de la bonté divine. &lt;/p&gt; &lt;p&gt; Son œuvre a eu une influence durable parce qu’elle relie la rigueur philosophique, l’érudition médiévale et l’expérience religieuse vécue. Elle reste une figure majeure pour comprendre à la fois la philosophie analytique de la religion et la redécouverte moderne de la pensée médiévale. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="F59" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="G58" s="9" t="s">
+      <c r="G59" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="H58" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="I58" s="9"/>
-      <c r="J58" s="2" t="s">
+      <c r="I59" s="9"/>
+      <c r="J59" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="K58" s="2" t="s">
+      <c r="K59" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="L58" s="2" t="s">
+      <c r="L59" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="M59" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N58" s="1" t="s">
+      <c r="N59" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
+    <row r="60" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="n">
         <v>1949</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B60" s="1" t="n">
         <v>2006</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="E59" s="14" t="inlineStr">
+      <c r="E60" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iris_Marion_Young" title=" Wikipedia"&gt;Iris Marion YOUNG&lt;/a&gt; était une philosophe politique américaine majeure, figure centrale du féminisme contemporain et de la théorie de la justice. Professeure à l'Université de Chicago, elle articule phénoménologie existentialiste, marxisme, théorie critique et postmodernisme pour repenser l'oppression, la domination et la démocratie au-delà des approches universalistes traditionnelles. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est sa théorie des &lt;a href="https://www.youtube.com/watch?v=KyOut8zqJRI" title="les cinq visages de l’oppression par Eliot Goodine"&gt; cinq visages de l'oppression,&lt;/a&gt;  qu'elle développe dans Justice and the Politics of Difference (1990) ou elle développe également une,&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2018_num_116_4_8681" title="le féminisme phénoménologique par persée"&gt; phénoménologie féministe &lt;/a&gt; du corps, notamment dans son essai célèbre « Throwing Like a Girl » (1980). Elle y décrit comment les femmes vivent leur corps comme limité, fragmenté et constamment surveillé, ce qui produit une « immanence » sociale qui entrave leur capacité d'action et d'autodétermination. Le corps n'est pas seulement biologique mais politique, façonné par les normes sociales et les rapports de pouvoir. &lt;/p&gt; &lt;p&gt; Elle défend une conception de la justice fondée sur l'inclusion différenciée plutôt que sur l'universalisme abstrait. Pour Young, une société juste doit reconnaître les différences de groupe (genre, race, classe, sexualité) et créer des espaces où chacun puisse participer à la vie démocratique sans être forcé d'abandonner son identité particulière. Elle propose aussi le concept de responsabilité sociale diffuse, selon lequel tous les membres d'une société sont responsables des injustice structurelles, pas seulement les auteurs directs. &lt;/p&gt; &lt;p&gt; Elle évite tout essentialisme en conceptualisant « les femmes » comme un groupe social sériel, au sens de Sartre : un groupe dont les membres ne partagent pas une essence commune mais sont reliés par des conditions sociales similaires et des rapports de pouvoir. Cette approche permet un féminisme pluriel, Alliant diverses luttes (racisme, homophobie, validisme, écologie) dans des coalitions contre les rapports de domination. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="H60" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="J59" s="2" t="s">
+      <c r="J60" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K59" s="2" t="s">
+      <c r="K60" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="L59" s="2" t="s">
+      <c r="L60" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="M59" s="1" t="s">
+      <c r="M60" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N59" s="1" t="s">
+      <c r="N60" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
+    <row r="61" customFormat="false" ht="213" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="n">
         <v>1952</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B61" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bell_hooks"  title=" Wikipedia"&gt;Bell HOOKS&lt;/a&gt;, de son vrai nom Gloria Jean Watkins, est une autrice, professeure et militante féministe afro-américaine. Née dans le Kentucky, dans le Sud ségrégationniste, elle prit le nom de son arrière-grand-mère, qu'elle écrivait en minuscules pour que l'attention se porte sur ses idées plutôt que sur sa personne.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ne suis-je pas une femme ?&lt;/em&gt; (1981), elle montre que les femmes noires ont été oubliées à la fois par le mouvement féministe, dominé par des femmes blanches de classe moyenne, et par le mouvement pour les droits civiques, dominé par des hommes. Elle  &lt;a href="https://www.youtube.com/watch?v=pCwMdHBSQgM" title=" bell hooks, un féminisme anticapitaliste et intersectionnel par META "&gt;développe l'idée &lt;/a&gt; que le sexisme, le racisme et l'exploitation économique forment un même système de domination, qu'elle appelle le « patriarcat capitaliste suprémaciste blanc ».&lt;/p&gt; &lt;p&gt;Ses idées ont profondément influencé ce que l'on appelle aujourd'hui l'intersectionnalité, c'est-à-dire l'étude de la manière dont différentes formes de discrimination se croisent et se renforcent. Elle écrivait dans un style simple et direct, refusant le jargon universitaire, pour que ses livres soient lus au-delà des cercles savants. Elle a aussi consacré plusieurs ouvrages à l'amour, qu'elle considérait comme une force politique capable de transformer la société.&lt;/p&gt; &lt;p&gt;Elle a écrit une quarantaine de livres, sur le féminisme, l'amour, les médias, la culture populaire et l'éducation. Dans &lt;em&gt;Apprendre à transgresser&lt;/em&gt; (1994), inspirée par Paulo Freire, elle défend une pédagogie de la liberté où l'enseignement devient une pratique d'émancipation. Pour elle, le féminisme n'est pas une guerre contre les hommes mais un mouvement pour mettre fin à toute forme de domination, porté par une « éthique de l'amour ».&lt;/p&gt;    &lt;audio controls title="Lire bell hooks aujourd’hui par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23875-15.11.2023-ITEMA_23552434-2023C49162S0319-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
 </t>
         </is>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G61" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="H61" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="I60" s="1"/>
-      <c r="J60" s="2" t="s">
+      <c r="I61" s="1"/>
+      <c r="J61" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K60" s="1" t="inlineStr">
+      <c r="K61" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Féminisme ; Wokisme</t>
         </is>
       </c>
-      <c r="L60" s="2" t="s">
+      <c r="L61" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="M61" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="N60" s="1" t="s">
+      <c r="N61" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O60" s="1" t="n">
+      <c r="O61" s="1" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0">
+    <row r="62" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0">
         <v>1535</v>
       </c>
-      <c r="B61" s="0" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1616</t>
         </is>
       </c>
-      <c r="C61" s="0" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">vers 1535 – vers 1616</t>
         </is>
       </c>
-      <c r="D61" s="0" t="inlineStr">
+      <c r="D62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Felipe GUAMÁN POMA de Ayala</t>
         </is>
       </c>
-      <c r="E61" s="0" t="inlineStr">
+      <c r="E62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Felipe_Guam%C3%A1n_Poma_de_Ayala" title=" Wikipedia"&gt;Felipe GUAMÁN POMA de Ayala&lt;/a&gt; est un noble andin de langue quechua, auteur de l’un des documents les plus extraordinaires de l’époque coloniale. Né dans la province de Lucanas, au Pérou, peu après la conquête espagnole, il descend par sa mère d’une lignée liée aux souverains de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_inca" title=" Wikipedia"&gt;Empire inca&lt;/a&gt;. Élevé parmi les Espagnols, il apprend leur langue, se fait chrétien et travaille comme interprète auprès d’un prêtre chargé d’extirper les « idolâtries », puis auprès de juges de Huamanga, avant d’être dépouillé de ses terres et banni vers 1600.&lt;/p&gt; &lt;p&gt;Il parcourt alors les Andes pendant des années et rédige, vers 1615, une lettre de près de 1 200 pages adressée au roi d’Espagne Philippe III : la &lt;em&gt;Nouvelle Chronique et bon gouvernement&lt;/em&gt;. Ses quelque 400 dessins à la plume racontent l’histoire des Incas, le calendrier, les travaux des champs, puis les abus des colons : prêtres, corregidors et propriétaires qui exploitent, volent et maltraitent les Indiens. Il y décrit un « monde à l’envers » (&lt;em&gt;mundo al revés&lt;/em&gt;), où l’ordre juste a été renversé par la conquête.&lt;/p&gt; &lt;p&gt;Il ne réclame pas le départ des Espagnols, mais un « bon gouvernement » : que les Andins se gouvernent eux-mêmes sous l’autorité lointaine du roi, et que les colons qui abusent soient chassés des villages. Il défend aussi la valeur de la civilisation andine, qui connaissait selon lui la justice et un ordre moral bien avant l’arrivée des Européens. Le manuscrit, qui n’atteignit sans doute jamais le roi, dormit pendant trois siècles avant d’être découvert en 1908 à la Bibliothèque royale de Copenhague. Il est aujourd’hui une source majeure sur le monde andin et l’une des premières critiques de la colonisation écrites par un colonisé.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F61" s="0" t="inlineStr">
+      <c r="F62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">__IaJh6gzA0</t>
         </is>
       </c>
-      <c r="G61" s="0" t="inlineStr">
+      <c r="G62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">"📌Felipe Guamán Poma de Ayala: HISTORIA desde su mirada al mundo andino y la conquista española | EP1" par Gestión Mundo</t>
         </is>
       </c>
-      <c r="H61" s="0" t="inlineStr">
+      <c r="H62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/guamanpoma-mini.webp</t>
         </is>
       </c>
-      <c r="I61" s="0"/>
-      <c r="J61" s="0" t="inlineStr">
+      <c r="I62" s="0"/>
+      <c r="J62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
-      <c r="K61" s="0" t="inlineStr">
+      <c r="K62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Anticolonialisme</t>
         </is>
       </c>
-      <c r="L61" s="0" t="inlineStr">
+      <c r="L62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">chroniqueur andin, auteur d’une immense lettre illustrée au roi d’Espagne dénonçant la colonisation du Pérou.</t>
         </is>
       </c>
-      <c r="M61" s="0"/>
-      <c r="N61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="O61" s="1">
-        <v>2</v>
-      </c>
-      <c r="P61" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Péruvienne</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1">
-        <v>1853</v>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1895</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1853 – 1895</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">José MARTÍ</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Mart%C3%AD" title=" Wikipedia"&gt;José MARTÍ&lt;/a&gt; est le grand penseur de l’indépendance cubaine et l’une des voix majeures de l’Amérique latine. Né à La Havane de parents espagnols, il est arrêté à seize ans pour ses idées indépendantistes et condamné aux travaux forcés dans une carrière, avant d’être déporté en Espagne, où il étudie le droit et la philosophie à Saragosse. Il vit ensuite au Mexique, au Guatemala et au Venezuela, puis s’installe en 1881 à New York, où il passe près de quinze ans comme journaliste, diplomate et organisateur de l’exil cubain. Il y écrit, pour de grands journaux d’Amérique latine, des chroniques sur la vie nord-américaine.&lt;/p&gt; &lt;p&gt;Dans son essai &lt;em&gt;Notre Amérique&lt;/em&gt; (1891), il appelle les nations latino-américaines à se penser à partir de leur propre réalité, métisse, indienne, noire et paysanne, plutôt qu’en copiant l’Europe ou les États-Unis : « Le gouvernement doit naître du pays. » Il y affirme aussi : « Il n’y a pas de haine des races, parce qu’il n’y a pas de races. » Observateur lucide de la puissance nord-américaine, il met en garde contre les ambitions des États-Unis sur Cuba et sur tout le continent.&lt;/p&gt; &lt;p&gt;Poète novateur, l’un des fondateurs du modernisme hispanique, il écrit les &lt;em&gt;Vers simples&lt;/em&gt; (1891), dont certains forment les paroles de la célèbre chanson &lt;em&gt;Guantanamera&lt;/em&gt;, et une revue pour les enfants, &lt;em&gt;L’Âge d’or&lt;/em&gt;. En 1892, il fonde le Parti révolutionnaire cubain et prépare la &lt;a href="https://fr.wikipedia.org/wiki/Guerre_d%27ind%C3%A9pendance_cubaine" title=" Wikipedia"&gt;guerre d’indépendance&lt;/a&gt;. Débarqué à Cuba avec les insurgés, il est tué au combat à Dos Ríos le 19 mai 1895. Il est considéré à Cuba comme le héros national et « l’Apôtre » de l’indépendance.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">l5bN92K18g8</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Filosofia Aquí y Ahora IV 5: El Pensamiento de José Martí" par Argen-Man</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/marti-mini.webp</t>
-        </is>
-      </c>
-      <c r="I62" s="1"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">politique ; esthetique</t>
-        </is>
-      </c>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">poète et penseur de l’indépendance cubaine, auteur de « Notre Amérique », héros national de Cuba.</t>
-        </is>
-      </c>
+      <c r="M62" s="0"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
@@ -5030,64 +5026,65 @@
       <c r="O62" s="1">
         <v>2</v>
       </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cubaine</t>
+      <c r="P62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>
     <row r="63" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1">
-        <v>1921</v>
+        <v>1853</v>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1997</t>
+          <t xml:space="preserve">1895</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921 – 1997</t>
+          <t xml:space="preserve">1853 – 1895</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paulo FREIRE</t>
+          <t xml:space="preserve">José MARTÍ</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paulo_Freire" title=" Wikipedia"&gt;Paulo FREIRE&lt;/a&gt; est un pédagogue et philosophe brésilien, l’un des penseurs de l’éducation les plus lus au monde. Né à Recife, dans le Nordeste, il connaît la faim pendant la crise des années 1930, ce qui le marque pour toute sa vie. Formé au droit et à la philosophie, lecteur de Marx comme des penseurs chrétiens, il se consacre à l’&lt;a href="https://fr.wikipedia.org/wiki/Alphab%C3%A9tisation" title=" Wikipedia"&gt;alphabétisation&lt;/a&gt; des adultes pauvres. En 1963, à Angicos, sa méthode permet à 300 travailleurs agricoles d’apprendre à lire et à écrire en une quarantaine d’heures.&lt;/p&gt; &lt;p&gt;Sa méthode part des « mots générateurs » tirés de la vie des apprenants, comme la brique, la terre ou le salaire, et fait de la lecture une prise de conscience : apprendre à lire le mot, c’est apprendre à lire le monde. Après le coup d’État militaire de 1964, il est emprisonné puis contraint à un exil de seize ans. Au Chili, il écrit &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_des_opprim%C3%A9s" title=" Wikipedia"&gt;&lt;em&gt;Pédagogie des opprimés&lt;/em&gt;&lt;/a&gt; (1968), où il critique l’éducation « bancaire », qui dépose des savoirs dans des élèves passifs comme on remplit un coffre, et lui oppose une éducation par le dialogue, où maître et élèves cherchent ensemble.&lt;/p&gt; &lt;p&gt;« Personne n’éduque autrui, personne ne s’éduque seul, les hommes s’éduquent ensemble par l’intermédiaire du monde. » L’éducation n’est jamais neutre : elle maintient l’oppression ou aide les opprimés à s’en libérer, sans devenir à leur tour oppresseurs. Rentré au Brésil en 1980, il dirige l’éducation de la ville de São Paulo. Son œuvre est à l’origine de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_critique" title=" Wikipedia"&gt;pédagogie critique&lt;/a&gt;, et il a été proclamé en 2012 patron de l’éducation brésilienne.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Mart%C3%AD" title=" Wikipedia"&gt;José MARTÍ&lt;/a&gt; est le grand penseur de l’indépendance cubaine et l’une des voix majeures de l’Amérique latine. Né à La Havane de parents espagnols, il est arrêté à seize ans pour ses idées indépendantistes et condamné aux travaux forcés dans une carrière, avant d’être déporté en Espagne, où il étudie le droit et la philosophie à Saragosse. Il vit ensuite au Mexique, au Guatemala et au Venezuela, puis s’installe en 1881 à New York, où il passe près de quinze ans comme journaliste, diplomate et organisateur de l’exil cubain. Il y écrit, pour de grands journaux d’Amérique latine, des chroniques sur la vie nord-américaine.&lt;/p&gt; &lt;p&gt;Dans son essai &lt;em&gt;Notre Amérique&lt;/em&gt; (1891), il appelle les nations latino-américaines à se penser à partir de leur propre réalité, métisse, indienne, noire et paysanne, plutôt qu’en copiant l’Europe ou les États-Unis : « Le gouvernement doit naître du pays. » Il y affirme aussi : « Il n’y a pas de haine des races, parce qu’il n’y a pas de races. » Observateur lucide de la puissance nord-américaine, il met en garde contre les ambitions des États-Unis sur Cuba et sur tout le continent.&lt;/p&gt; &lt;p&gt;Poète novateur, l’un des fondateurs du modernisme hispanique, il écrit les &lt;em&gt;Vers simples&lt;/em&gt; (1891), dont certains forment les paroles de la célèbre chanson &lt;em&gt;Guantanamera&lt;/em&gt;, et une revue pour les enfants, &lt;em&gt;L’Âge d’or&lt;/em&gt;. En 1892, il fonde le Parti révolutionnaire cubain et prépare la &lt;a href="https://fr.wikipedia.org/wiki/Guerre_d%27ind%C3%A9pendance_cubaine" title=" Wikipedia"&gt;guerre d’indépendance&lt;/a&gt;. Débarqué à Cuba avec les insurgés, il est tué au combat à Dos Ríos le 19 mai 1895. Il est considéré à Cuba comme le héros national et « l’Apôtre » de l’indépendance.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4FG6diR6fhU</t>
+          <t xml:space="preserve">l5bN92K18g8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Une pédagogie pour éduquer au politique, contre l'oppression ? Paulo FREIRE - selon Philippe Meirieu" par Benoit Urgelli</t>
+          <t xml:space="preserve">"Filosofia Aquí y Ahora IV 5: El Pensamiento de José Martí" par Argen-Man</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/freire-mini.webp</t>
-        </is>
-      </c>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/marti-mini.webp</t>
+        </is>
+      </c>
+      <c r="I63" s="1"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">politique ; esthetique</t>
         </is>
       </c>
       <c r="K63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Marxisme ; Théologie de la libération</t>
+          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pédagogue brésilien, auteur de Pédagogie des opprimés, penseur de l’éducation comme pratique de la liberté.</t>
+          <t xml:space="preserve">poète et penseur de l’indépendance cubaine, auteur de « Notre Amérique », héros national de Cuba.</t>
         </is>
       </c>
       <c r="N63" s="1" t="inlineStr">
@@ -5096,66 +5093,66 @@
         </is>
       </c>
       <c r="O63" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brésilienne</t>
+          <t xml:space="preserve">Cubaine</t>
         </is>
       </c>
     </row>
     <row r="64" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1">
-        <v>1882</v>
+        <v>1921</v>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">1997</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882 – 1959</t>
+          <t xml:space="preserve">1921 – 1997</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">José VASCONCELOS</t>
+          <t xml:space="preserve">Paulo FREIRE</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Vasconcelos" title=" Wikipedia"&gt;José VASCONCELOS&lt;/a&gt; est un philosophe, écrivain et homme politique mexicain, l’un des grands éducateurs de l’Amérique latine. Né à Oaxaca, avocat, il fonde en 1909 avec Antonio Caso et Alfonso Reyes l’Ateneo de la Juventud, cercle de jeunes intellectuels qui rejette le positivisme officiel du régime de Porfirio Díaz. Il prend part à la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_mexicaine" title=" Wikipedia"&gt;révolution mexicaine&lt;/a&gt; aux côtés de Francisco Madero. Recteur de l’université nationale en 1920, il lui donne sa devise, toujours en usage : « Par ma race parlera l’esprit. »&lt;/p&gt; &lt;p&gt;Ministre de l’Éducation de 1921 à 1924, il mène une véritable croisade pour instruire le peuple : écoles rurales, missions culturelles dans les villages, bibliothèques, éditions populaires des grands classiques. Il commande aussi aux peintres &lt;a href="https://fr.wikipedia.org/wiki/Diego_Rivera" title=" Wikipedia"&gt;Diego Rivera&lt;/a&gt; et José Clemente Orozco les fresques murales qui racontent l’histoire du Mexique sur les murs des bâtiments publics. Il est surnommé le « maître de la jeunesse d’Amérique ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Race cosmique&lt;/em&gt; (1925), il prophétise que l’Amérique latine, terre de tous les mélanges, verra naître une « cinquième race », synthèse de toutes les autres, porteuse d’une civilisation de l’amour et de la beauté. Sa philosophie, un « monisme esthétique », voit dans l’émotion esthétique la forme la plus haute de connaissance. Battu en 1929 dans une élection présidentielle qu’il juge truquée, il s’exile, puis évolue vers un conservatisme catholique, au point de manifester en 1940 des sympathies pour l’Allemagne nazie. Il meurt à Mexico en 1959.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paulo_Freire" title=" Wikipedia"&gt;Paulo FREIRE&lt;/a&gt; est un pédagogue et philosophe brésilien, l’un des penseurs de l’éducation les plus lus au monde. Né à Recife, dans le Nordeste, il connaît la faim pendant la crise des années 1930, ce qui le marque pour toute sa vie. Formé au droit et à la philosophie, lecteur de Marx comme des penseurs chrétiens, il se consacre à l’&lt;a href="https://fr.wikipedia.org/wiki/Alphab%C3%A9tisation" title=" Wikipedia"&gt;alphabétisation&lt;/a&gt; des adultes pauvres. En 1963, à Angicos, sa méthode permet à 300 travailleurs agricoles d’apprendre à lire et à écrire en une quarantaine d’heures.&lt;/p&gt; &lt;p&gt;Sa méthode part des « mots générateurs » tirés de la vie des apprenants, comme la brique, la terre ou le salaire, et fait de la lecture une prise de conscience : apprendre à lire le mot, c’est apprendre à lire le monde. Après le coup d’État militaire de 1964, il est emprisonné puis contraint à un exil de seize ans. Au Chili, il écrit &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_des_opprim%C3%A9s" title=" Wikipedia"&gt;&lt;em&gt;Pédagogie des opprimés&lt;/em&gt;&lt;/a&gt; (1968), où il critique l’éducation « bancaire », qui dépose des savoirs dans des élèves passifs comme on remplit un coffre, et lui oppose une éducation par le dialogue, où maître et élèves cherchent ensemble.&lt;/p&gt; &lt;p&gt;« Personne n’éduque autrui, personne ne s’éduque seul, les hommes s’éduquent ensemble par l’intermédiaire du monde. » L’éducation n’est jamais neutre : elle maintient l’oppression ou aide les opprimés à s’en libérer, sans devenir à leur tour oppresseurs. Rentré au Brésil en 1980, il dirige l’éducation de la ville de São Paulo. Son œuvre est à l’origine de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9dagogie_critique" title=" Wikipedia"&gt;pédagogie critique&lt;/a&gt;, et il a été proclamé en 2012 patron de l’éducation brésilienne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3E3RuPB9qY</t>
+          <t xml:space="preserve">4FG6diR6fhU</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">"José Vasconcelos filosofía de México" par Filosofia Corporativa</t>
+          <t xml:space="preserve">"Une pédagogie pour éduquer au politique, contre l'oppression ? Paulo FREIRE - selon Philippe Meirieu" par Benoit Urgelli</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/vasconcelos-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/freire-mini.webp</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; politique</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="K64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monisme ; Spiritualisme</t>
+          <t xml:space="preserve">Humanisme ; Marxisme ; Théologie de la libération</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et ministre mexicain de l’Éducation, auteur de La Race cosmique, penseur du métissage.</t>
+          <t xml:space="preserve">pédagogue brésilien, auteur de Pédagogie des opprimés, penseur de l’éducation comme pratique de la liberté.</t>
         </is>
       </c>
       <c r="N64" s="1" t="inlineStr">
@@ -5164,76 +5161,71 @@
         </is>
       </c>
       <c r="O64" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mexicaine</t>
+          <t xml:space="preserve">Brésilienne</t>
         </is>
       </c>
     </row>
     <row r="65" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1">
-        <v>1907</v>
+        <v>1882</v>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1972</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1907 – 1972</t>
+          <t xml:space="preserve">1882 – 1959</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abraham Joshua HESCHEL</t>
+          <t xml:space="preserve">José VASCONCELOS</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abraham_Joshua_Heschel" title=" Wikipedia"&gt;Abraham Joshua HESCHEL&lt;/a&gt; est un rabbin, théologien et philosophe juif, l’une des grandes voix religieuses du XXe siècle. Né à Varsovie dans une illustre famille du &lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;hassidisme&lt;/a&gt;, il étudie la philosophie à Berlin, où il soutient une thèse sur les prophètes d’Israël. Expulsé d’Allemagne vers la Pologne en 1938, il parvient à quitter Varsovie quelques semaines avant l’invasion allemande et gagne Londres, puis les États-Unis. Sa mère et ses sœurs sont assassinées pendant la Shoah. Il enseigne à partir de 1946 au Séminaire théologique juif de New York.&lt;/p&gt; &lt;p&gt;Pour Heschel, la religion commence par l’« étonnement radical » devant le monde, qui précède toute réflexion. Contre l’idée d’un Dieu impassible des philosophes, il parle du « pathos divin » : le Dieu des prophètes est concerné par le sort des hommes et souffre de l’injustice. La question n’est pas seulement de savoir si l’homme cherche Dieu, mais de comprendre que &lt;em&gt;Dieu est en quête de l’homme&lt;/em&gt;, titre de son livre de 1955. Dans &lt;em&gt;Les Bâtisseurs du temps&lt;/em&gt; (1951), il présente le &lt;a href="https://fr.wikipedia.org/wiki/Shabbat" title=" Wikipedia"&gt;shabbat&lt;/a&gt; comme « une cathédrale dans le temps » : le judaïsme sanctifie des moments plutôt que des lieux. Il consacre aussi un grand livre aux prophètes, témoins de la passion de Dieu pour la justice.&lt;/p&gt; &lt;p&gt;Sa foi le conduit à l’action. En 1965, il marche de Selma à Montgomery aux côtés de Martin Luther King et dira : « J’avais l’impression que mes jambes priaient. » Il s’oppose à la guerre du Vietnam et contribue au dialogue entre juifs et chrétiens lors du concile Vatican II. Il meurt à New York en 1972.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Vasconcelos" title=" Wikipedia"&gt;José VASCONCELOS&lt;/a&gt; est un philosophe, écrivain et homme politique mexicain, l’un des grands éducateurs de l’Amérique latine. Né à Oaxaca, avocat, il fonde en 1909 avec Antonio Caso et Alfonso Reyes l’Ateneo de la Juventud, cercle de jeunes intellectuels qui rejette le positivisme officiel du régime de Porfirio Díaz. Il prend part à la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_mexicaine" title=" Wikipedia"&gt;révolution mexicaine&lt;/a&gt; aux côtés de Francisco Madero. Recteur de l’université nationale en 1920, il lui donne sa devise, toujours en usage : « Par ma race parlera l’esprit. »&lt;/p&gt; &lt;p&gt;Ministre de l’Éducation de 1921 à 1924, il mène une véritable croisade pour instruire le peuple : écoles rurales, missions culturelles dans les villages, bibliothèques, éditions populaires des grands classiques. Il commande aussi aux peintres &lt;a href="https://fr.wikipedia.org/wiki/Diego_Rivera" title=" Wikipedia"&gt;Diego Rivera&lt;/a&gt; et José Clemente Orozco les fresques murales qui racontent l’histoire du Mexique sur les murs des bâtiments publics. Il est surnommé le « maître de la jeunesse d’Amérique ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Race cosmique&lt;/em&gt; (1925), il prophétise que l’Amérique latine, terre de tous les mélanges, verra naître une « cinquième race », synthèse de toutes les autres, porteuse d’une civilisation de l’amour et de la beauté. Sa philosophie, un « monisme esthétique », voit dans l’émotion esthétique la forme la plus haute de connaissance. Battu en 1929 dans une élection présidentielle qu’il juge truquée, il s’exile, puis évolue vers un conservatisme catholique, au point de manifester en 1940 des sympathies pour l’Allemagne nazie. Il meurt à Mexico en 1959.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLINbVsBz-Q</t>
+          <t xml:space="preserve">B3E3RuPB9qY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">"LA PENSEE D'AVRAHAM YOSHOUA HESCHEL" Rony Akrich"" par רוני אקריש</t>
+          <t xml:space="preserve">"José Vasconcelos filosofía de México" par Filosofia Corporativa</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/heschel-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vasconcelos-mini.webp</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; ethique</t>
+          <t xml:space="preserve">esthetique ; politique</t>
         </is>
       </c>
       <c r="K65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Existentialisme ; Mysticisme ; Hassidisme</t>
+          <t xml:space="preserve">Monisme ; Spiritualisme</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rabbin et philosophe juif, penseur du « pathos divin » et du shabbat, militant des droits civiques.</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">philosophe et ministre mexicain de l’Éducation, auteur de La Race cosmique, penseur du métissage.</t>
         </is>
       </c>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">occident</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="O65" s="1">
@@ -5241,67 +5233,72 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Américaine</t>
+          <t xml:space="preserve">Mexicaine</t>
         </is>
       </c>
     </row>
     <row r="66" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1">
-        <v>1914</v>
+        <v>1907</v>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998</t>
+          <t xml:space="preserve">1972</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914 – 1998</t>
+          <t xml:space="preserve">1907 – 1972</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octavio PAZ</t>
+          <t xml:space="preserve">Abraham Joshua HESCHEL</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Octavio_Paz" title=" Wikipedia"&gt;Octavio PAZ&lt;/a&gt; est un poète, essayiste et diplomate mexicain, prix Nobel de littérature en 1990. Né à Mexico dans une famille marquée par la révolution, son père ayant été le représentant d’Emiliano Zapata aux États-Unis, il soutient les républicains pendant la guerre d’Espagne, puis rompt avec le communisme après l’assassinat de Trotski. Diplomate à Paris après la guerre, il y fréquente les surréalistes et André Breton.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Labyrinthe_de_la_solitude" title=" Wikipedia"&gt;&lt;em&gt;Le Labyrinthe de la solitude&lt;/em&gt;&lt;/a&gt; (1950), il interroge l’identité mexicaine : derrière les masques de la politesse et la violence des fêtes se cache une solitude née de l’histoire, celle d’un peuple issu de la conquête, qui a renié à la fois son passé indien et son passé espagnol. Il y évoque la figure de la &lt;a href="https://fr.wikipedia.org/wiki/La_Malinche" title=" Wikipedia"&gt;Malinche&lt;/a&gt;, compagne indienne de Cortés, symbole ambigu de l’origine métisse du pays. Mais cette solitude est aussi celle de l’homme moderne, et la poésie, l’amour et la fête sont des moyens de la dépasser. Dans &lt;em&gt;L’Arc et la Lyre&lt;/em&gt; (1956), il fait de la poésie une expérience de communion qui révèle l’homme à lui-même.&lt;/p&gt; &lt;p&gt;Ambassadeur du Mexique en Inde de 1962 à 1968, il découvre les philosophies et l’art de l’Orient, qui nourrissent sa poésie. Il démissionne après le &lt;a href="https://fr.wikipedia.org/wiki/Massacre_de_Tlatelolco" title=" Wikipedia"&gt;massacre de Tlatelolco&lt;/a&gt;, où des centaines d’étudiants sont tués par l’armée en 1968. Critique des totalitarismes de droite comme de gauche, il fonde la revue &lt;em&gt;Vuelta&lt;/em&gt; et consacre un grand livre à la poétesse et penseuse Juana Inés de la Cruz. Il meurt à Mexico en 1998, à quatre-vingt-quatre ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abraham_Joshua_Heschel" title=" Wikipedia"&gt;Abraham Joshua HESCHEL&lt;/a&gt; est un rabbin, théologien et philosophe juif, l’une des grandes voix religieuses du XXe siècle. Né à Varsovie dans une illustre famille du &lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;hassidisme&lt;/a&gt;, il étudie la philosophie à Berlin, où il soutient une thèse sur les prophètes d’Israël. Expulsé d’Allemagne vers la Pologne en 1938, il parvient à quitter Varsovie quelques semaines avant l’invasion allemande et gagne Londres, puis les États-Unis. Sa mère et ses sœurs sont assassinées pendant la Shoah. Il enseigne à partir de 1946 au Séminaire théologique juif de New York.&lt;/p&gt; &lt;p&gt;Pour Heschel, la religion commence par l’« étonnement radical » devant le monde, qui précède toute réflexion. Contre l’idée d’un Dieu impassible des philosophes, il parle du « pathos divin » : le Dieu des prophètes est concerné par le sort des hommes et souffre de l’injustice. La question n’est pas seulement de savoir si l’homme cherche Dieu, mais de comprendre que &lt;em&gt;Dieu est en quête de l’homme&lt;/em&gt;, titre de son livre de 1955. Dans &lt;em&gt;Les Bâtisseurs du temps&lt;/em&gt; (1951), il présente le &lt;a href="https://fr.wikipedia.org/wiki/Shabbat" title=" Wikipedia"&gt;shabbat&lt;/a&gt; comme « une cathédrale dans le temps » : le judaïsme sanctifie des moments plutôt que des lieux. Il consacre aussi un grand livre aux prophètes, témoins de la passion de Dieu pour la justice.&lt;/p&gt; &lt;p&gt;Sa foi le conduit à l’action. En 1965, il marche de Selma à Montgomery aux côtés de Martin Luther King et dira : « J’avais l’impression que mes jambes priaient. » Il s’oppose à la guerre du Vietnam et contribue au dialogue entre juifs et chrétiens lors du concile Vatican II. Il meurt à New York en 1972.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZIxDHuVg9TQ</t>
+          <t xml:space="preserve">SLINbVsBz-Q</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Octavio PAZ – Un siècle d'écrivains : 1914-1990 (France 3, 2000)" par ÉCLAIR BRUT</t>
+          <t xml:space="preserve">"LA PENSEE D'AVRAHAM YOSHOUA HESCHEL" Rony Akrich"" par רוני אקריש</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/paz-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/heschel-mini.webp</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; politique</t>
+          <t xml:space="preserve">spiritualite ; ethique</t>
         </is>
       </c>
       <c r="K66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme</t>
+          <t xml:space="preserve">Existentialisme ; Mysticisme ; Hassidisme</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">poète et essayiste mexicain, prix Nobel 1990, auteur du Labyrinthe de la solitude.</t>
+          <t xml:space="preserve">rabbin et philosophe juif, penseur du « pathos divin » et du shabbat, militant des droits civiques.</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
       <c r="O66" s="1">
@@ -5309,62 +5306,62 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mexicaine</t>
+          <t xml:space="preserve">Américaine</t>
         </is>
       </c>
     </row>
     <row r="67" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1">
-        <v>1871</v>
+        <v>1914</v>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917</t>
+          <t xml:space="preserve">1998</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871 – 1917</t>
+          <t xml:space="preserve">1914 – 1998</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">José Enrique RODÓ</t>
+          <t xml:space="preserve">Octavio PAZ</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Enrique_Rod%C3%B3" title=" Wikipedia"&gt;José Enrique RODÓ&lt;/a&gt; est un écrivain et essayiste uruguayen, l’un des grands maîtres à penser de l’Amérique latine au début du XXe siècle. Né à Montevideo, il doit interrompre ses études après la ruine de sa famille, se forme largement seul et devient professeur de littérature à l’université de Montevideo, puis député. Correspondant de &lt;a href="https://fr.wikipedia.org/wiki/Rub%C3%A9n_Dar%C3%ADo" title=" Wikipedia"&gt;Rubén Darío&lt;/a&gt;, il est le principal théoricien du modernisme, le grand mouvement de renouvellement de la littérature hispano-américaine.&lt;/p&gt; &lt;p&gt;Son essai &lt;em&gt;Ariel&lt;/em&gt; (1900), écrit deux ans après la victoire des États-Unis sur l’Espagne à Cuba, prend la forme d’un dernier cours donné par un vieux maître, Prospero, à ses élèves. Empruntant les personnages de &lt;em&gt;La Tempête&lt;/em&gt; de Shakespeare, il oppose Ariel, l’esprit, la beauté, le désintéressement, à Caliban, la matière, l’utilité, les appétits. Il met en garde la jeunesse latino-américaine contre l’utilitarisme et la « nordomanie », la fascination pour le modèle des États-Unis, puissant mais tourné vers le seul profit.&lt;/p&gt; &lt;p&gt;Rodó invite les jeunes à cultiver toutes les facultés de l’esprit, à préserver un temps libre pour la pensée et la beauté, et à construire une démocratie qui élève chacun au lieu de niveler par le bas. Le livre connut un immense succès et inspira tout un courant, l’« arielisme ». Plus tard, des penseurs comme Roberto Fernández Retamar ont renversé le symbole en faisant de Caliban la figure du colonisé. Dans &lt;em&gt;Motifs de Protée&lt;/em&gt; (1909), il médite sur la transformation continuelle de soi. Rodó meurt à Palerme en 1917, au cours d’un voyage en Europe.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Octavio_Paz" title=" Wikipedia"&gt;Octavio PAZ&lt;/a&gt; est un poète, essayiste et diplomate mexicain, prix Nobel de littérature en 1990. Né à Mexico dans une famille marquée par la révolution, son père ayant été le représentant d’Emiliano Zapata aux États-Unis, il soutient les républicains pendant la guerre d’Espagne, puis rompt avec le communisme après l’assassinat de Trotski. Diplomate à Paris après la guerre, il y fréquente les surréalistes et André Breton.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Labyrinthe_de_la_solitude" title=" Wikipedia"&gt;&lt;em&gt;Le Labyrinthe de la solitude&lt;/em&gt;&lt;/a&gt; (1950), il interroge l’identité mexicaine : derrière les masques de la politesse et la violence des fêtes se cache une solitude née de l’histoire, celle d’un peuple issu de la conquête, qui a renié à la fois son passé indien et son passé espagnol. Il y évoque la figure de la &lt;a href="https://fr.wikipedia.org/wiki/La_Malinche" title=" Wikipedia"&gt;Malinche&lt;/a&gt;, compagne indienne de Cortés, symbole ambigu de l’origine métisse du pays. Mais cette solitude est aussi celle de l’homme moderne, et la poésie, l’amour et la fête sont des moyens de la dépasser. Dans &lt;em&gt;L’Arc et la Lyre&lt;/em&gt; (1956), il fait de la poésie une expérience de communion qui révèle l’homme à lui-même.&lt;/p&gt; &lt;p&gt;Ambassadeur du Mexique en Inde de 1962 à 1968, il découvre les philosophies et l’art de l’Orient, qui nourrissent sa poésie. Il démissionne après le &lt;a href="https://fr.wikipedia.org/wiki/Massacre_de_Tlatelolco" title=" Wikipedia"&gt;massacre de Tlatelolco&lt;/a&gt;, où des centaines d’étudiants sont tués par l’armée en 1968. Critique des totalitarismes de droite comme de gauche, il fonde la revue &lt;em&gt;Vuelta&lt;/em&gt; et consacre un grand livre à la poétesse et penseuse Juana Inés de la Cruz. Il meurt à Mexico en 1998, à quatre-vingt-quatre ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2csl4K2CTs</t>
+          <t xml:space="preserve">ZIxDHuVg9TQ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">"La Mesa de Filósofos: José Enrique Rodó, su legado a 150 años del nacimiento" par En Perspectiva + VIDEO </t>
+          <t xml:space="preserve">"Octavio PAZ – Un siècle d'écrivains : 1914-1990 (France 3, 2000)" par ÉCLAIR BRUT</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/rodo-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/paz-mini.webp</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; ethique</t>
+          <t xml:space="preserve">esthetique ; politique</t>
         </is>
       </c>
       <c r="K67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Spiritualisme</t>
+          <t xml:space="preserve">Humanisme</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">essayiste uruguayen, auteur d’Ariel, maître à penser de la jeunesse latino-américaine.</t>
+          <t xml:space="preserve">poète et essayiste mexicain, prix Nobel 1990, auteur du Labyrinthe de la solitude.</t>
         </is>
       </c>
       <c r="N67" s="1" t="inlineStr">
@@ -5377,62 +5374,62 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uruguayenne</t>
+          <t xml:space="preserve">Mexicaine</t>
         </is>
       </c>
     </row>
     <row r="68" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1">
-        <v>1922</v>
+        <v>1871</v>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1979</t>
+          <t xml:space="preserve">1917</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922 – 1979</t>
+          <t xml:space="preserve">1871 – 1917</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodolfo KUSCH</t>
+          <t xml:space="preserve">José Enrique RODÓ</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Rodolfo_Kusch" title=" Wikipedia (es)"&gt;Rodolfo KUSCH&lt;/a&gt; est un philosophe et anthropologue argentin qui a cherché à fonder une philosophie à partir de la pensée indigène et populaire de l’Amérique. Né à Buenos Aires de parents allemands, il étudie la philosophie à l’université de Buenos Aires, enseigne l’esthétique et écrit aussi pour le théâtre, notamment sur le tango. Persécuté pour ses sympathies péronistes après 1955, il part pour la Bolivie et le Pérou, puis s’installe dans le nord-ouest de l’Argentine, à Maimará, dans la province de Jujuy.&lt;/p&gt; &lt;p&gt;Au contact des communautés &lt;a href="https://fr.wikipedia.org/wiki/Quechuas" title=" Wikipedia"&gt;quechuas&lt;/a&gt; et &lt;a href="https://fr.wikipedia.org/wiki/Aymaras" title=" Wikipedia"&gt;aymaras&lt;/a&gt; des Andes, il mène de longues enquêtes de terrain, dont il tire &lt;em&gt;L’Amérique profonde&lt;/em&gt; (1962) et &lt;em&gt;La Pensée indigène et populaire en Amérique&lt;/em&gt; (1970). Il y oppose deux attitudes. Celle de l’Occident, l’« être », qui veut dominer le monde, le transformer et accumuler. Et celle de l’Amérique indienne, l’« être là » ou le simple « se tenir » (en espagnol &lt;em&gt;estar&lt;/em&gt;), qui accepte l’incertitude du monde, ses forces et ses menaces, et cherche à vivre en équilibre avec lui.&lt;/p&gt; &lt;p&gt;Pour Kusch, les classes moyennes des villes, qui se veulent européennes, vivent dans la peur de cette « Amérique profonde » qu’elles refoulent. Penser en Amérique, c’est accepter cette part indienne et populaire au lieu de la mépriser. Son œuvre, longtemps marginale, a nourri la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt; et les pensées décoloniales latino-américaines, et elle est aujourd’hui redécouverte. Il parle même de « phagocytose » : la culture populaire finirait par absorber ce que la modernité importée croit lui imposer. Il meurt en 1979 à Maimará, à cinquante-sept ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Enrique_Rod%C3%B3" title=" Wikipedia"&gt;José Enrique RODÓ&lt;/a&gt; est un écrivain et essayiste uruguayen, l’un des grands maîtres à penser de l’Amérique latine au début du XXe siècle. Né à Montevideo, il doit interrompre ses études après la ruine de sa famille, se forme largement seul et devient professeur de littérature à l’université de Montevideo, puis député. Correspondant de &lt;a href="https://fr.wikipedia.org/wiki/Rub%C3%A9n_Dar%C3%ADo" title=" Wikipedia"&gt;Rubén Darío&lt;/a&gt;, il est le principal théoricien du modernisme, le grand mouvement de renouvellement de la littérature hispano-américaine.&lt;/p&gt; &lt;p&gt;Son essai &lt;em&gt;Ariel&lt;/em&gt; (1900), écrit deux ans après la victoire des États-Unis sur l’Espagne à Cuba, prend la forme d’un dernier cours donné par un vieux maître, Prospero, à ses élèves. Empruntant les personnages de &lt;em&gt;La Tempête&lt;/em&gt; de Shakespeare, il oppose Ariel, l’esprit, la beauté, le désintéressement, à Caliban, la matière, l’utilité, les appétits. Il met en garde la jeunesse latino-américaine contre l’utilitarisme et la « nordomanie », la fascination pour le modèle des États-Unis, puissant mais tourné vers le seul profit.&lt;/p&gt; &lt;p&gt;Rodó invite les jeunes à cultiver toutes les facultés de l’esprit, à préserver un temps libre pour la pensée et la beauté, et à construire une démocratie qui élève chacun au lieu de niveler par le bas. Le livre connut un immense succès et inspira tout un courant, l’« arielisme ». Plus tard, des penseurs comme Roberto Fernández Retamar ont renversé le symbole en faisant de Caliban la figure du colonisé. Dans &lt;em&gt;Motifs de Protée&lt;/em&gt; (1909), il médite sur la transformation continuelle de soi. Rodó meurt à Palerme en 1917, au cours d’un voyage en Europe.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">xow95qdu2wE</t>
+          <t xml:space="preserve">C2csl4K2CTs</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Podcast filosófico -  Rodolfo Kusch" par Filo Errante</t>
+          <t xml:space="preserve">"La Mesa de Filósofos: José Enrique Rodó, su legado a 150 años del nacimiento" par En Perspectiva + VIDEO </t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/kusch-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rodo-mini.webp</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
+          <t xml:space="preserve">esthetique ; ethique</t>
         </is>
       </c>
       <c r="K68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen Vivir (cosmovision andine) ; Philosophie de la libération</t>
+          <t xml:space="preserve">Humanisme ; Spiritualisme</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et anthropologue argentin, penseur de l’« Amérique profonde » et de la pensée indigène et populaire.</t>
+          <t xml:space="preserve">essayiste uruguayen, auteur d’Ariel, maître à penser de la jeunesse latino-américaine.</t>
         </is>
       </c>
       <c r="N68" s="1" t="inlineStr">
@@ -5445,62 +5442,62 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Argentine</t>
+          <t xml:space="preserve">Uruguayenne</t>
         </is>
       </c>
     </row>
     <row r="69" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974</t>
+          <t xml:space="preserve">1979</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925 – 1974</t>
+          <t xml:space="preserve">1922 – 1979</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Augusto SALAZAR BONDY</t>
+          <t xml:space="preserve">Rodolfo KUSCH</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Augusto_Salazar_Bondy" title=" Wikipedia (es)"&gt;Augusto SALAZAR BONDY&lt;/a&gt; est un philosophe et éducateur péruvien, l’une des figures fondatrices de la philosophie latino-américaine de la libération. Né à Lima, frère cadet de l’écrivain Sebastián Salazar Bondy, il étudie à l’université San Marcos, puis au Mexique auprès de José Gaos et de Leopoldo Zea, et à Paris, où il suit les cours de Jean Wahl, Jean Hyppolite et Gaston Bachelard. Professeur d’éthique à San Marcos, il écrit une grande histoire des idées au Pérou contemporain.&lt;/p&gt; &lt;p&gt;En 1968, il publie &lt;em&gt;Existe-t-il une philosophie de notre Amérique ?&lt;/em&gt;, qui provoque un vif débat avec Leopoldo Zea. Sa réponse est dure : jusqu’ici, il n’existe pas de philosophie latino-américaine authentique, mais seulement des imitations des courants européens, adoptés tour à tour sans être vraiment pensés. Ce n’est pas un manque de talent : c’est la conséquence de la domination et du sous-développement, qui produisent une culture dépendante et « aliénée », incapable de se penser elle-même.&lt;/p&gt; &lt;p&gt;Une philosophie authentique ne pourra naître qu’en prenant pour objet cette situation de domination, et en contribuant à la transformer. La philosophie devient ainsi une tâche de libération, comme le développera la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt;. Engagé dans la réforme de l’éducation sous le gouvernement péruvien de la fin des années 1960, il défend une école qui forme des personnes libres et critiques. Il meurt prématurément à Lima en 1974, à quarante-huit ans. Ses idées ont notamment inspiré Enrique Dussel.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Rodolfo_Kusch" title=" Wikipedia (es)"&gt;Rodolfo KUSCH&lt;/a&gt; est un philosophe et anthropologue argentin qui a cherché à fonder une philosophie à partir de la pensée indigène et populaire de l’Amérique. Né à Buenos Aires de parents allemands, il étudie la philosophie à l’université de Buenos Aires, enseigne l’esthétique et écrit aussi pour le théâtre, notamment sur le tango. Persécuté pour ses sympathies péronistes après 1955, il part pour la Bolivie et le Pérou, puis s’installe dans le nord-ouest de l’Argentine, à Maimará, dans la province de Jujuy.&lt;/p&gt; &lt;p&gt;Au contact des communautés &lt;a href="https://fr.wikipedia.org/wiki/Quechuas" title=" Wikipedia"&gt;quechuas&lt;/a&gt; et &lt;a href="https://fr.wikipedia.org/wiki/Aymaras" title=" Wikipedia"&gt;aymaras&lt;/a&gt; des Andes, il mène de longues enquêtes de terrain, dont il tire &lt;em&gt;L’Amérique profonde&lt;/em&gt; (1962) et &lt;em&gt;La Pensée indigène et populaire en Amérique&lt;/em&gt; (1970). Il y oppose deux attitudes. Celle de l’Occident, l’« être », qui veut dominer le monde, le transformer et accumuler. Et celle de l’Amérique indienne, l’« être là » ou le simple « se tenir » (en espagnol &lt;em&gt;estar&lt;/em&gt;), qui accepte l’incertitude du monde, ses forces et ses menaces, et cherche à vivre en équilibre avec lui.&lt;/p&gt; &lt;p&gt;Pour Kusch, les classes moyennes des villes, qui se veulent européennes, vivent dans la peur de cette « Amérique profonde » qu’elles refoulent. Penser en Amérique, c’est accepter cette part indienne et populaire au lieu de la mépriser. Son œuvre, longtemps marginale, a nourri la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt; et les pensées décoloniales latino-américaines, et elle est aujourd’hui redécouverte. Il parle même de « phagocytose » : la culture populaire finirait par absorber ce que la modernité importée croit lui imposer. Il meurt en 1979 à Maimará, à cinquante-sept ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">pKvpeeR1Q4Y</t>
+          <t xml:space="preserve">xow95qdu2wE</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">"El concepto de alienación según Augusto Salazar Bondy" par Libros Peruanos</t>
+          <t xml:space="preserve">"Podcast filosófico -  Rodolfo Kusch" par Filo Errante</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/salazarbondy-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kusch-mini.webp</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
+          <t xml:space="preserve">Buen Vivir (cosmovision andine) ; Philosophie de la libération</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe péruvien, auteur d’Existe-t-il une philosophie de notre Amérique ?, penseur de la domination.</t>
+          <t xml:space="preserve">philosophe et anthropologue argentin, penseur de l’« Amérique profonde » et de la pensée indigène et populaire.</t>
         </is>
       </c>
       <c r="N69" s="1" t="inlineStr">
@@ -5513,62 +5510,62 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Péruvienne</t>
+          <t xml:space="preserve">Argentine</t>
         </is>
       </c>
     </row>
     <row r="70" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1">
-        <v>1839</v>
+        <v>1925</v>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">1974</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839 – 1903</t>
+          <t xml:space="preserve">1925 – 1974</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eugenio María de HOSTOS</t>
+          <t xml:space="preserve">Augusto SALAZAR BONDY</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Eugenio_Mar%C3%ADa_de_Hostos" title=" Wikipedia (en)"&gt;Eugenio María de HOSTOS&lt;/a&gt; est un philosophe, éducateur, sociologue et écrivain de &lt;a href="https://fr.wikipedia.org/wiki/Porto_Rico" title=" Wikipedia"&gt;Porto Rico&lt;/a&gt;, surnommé « le Grand Citoyen des Amériques ». Né à Mayagüez dans une famille aisée, il fait ses études en Espagne, où il étudie le droit et la philosophie à Madrid et publie en 1863 un roman, &lt;em&gt;Le Pèlerinage de Bayoán&lt;/em&gt;, qui évoque déjà le destin des Antilles. Déçu que la République espagnole refuse l’autonomie de Porto Rico, il quitte l’Espagne en 1869 pour se consacrer à l’indépendance des colonies antillaises.&lt;/p&gt; &lt;p&gt;Il rêve d’une Confédération des Antilles, réunissant Porto Rico, Cuba et la République dominicaine, et parcourt pour la défendre les États-Unis, le Pérou, le Chili, l’Argentine, le Brésil et le Venezuela. Partout, il fonde ou réforme des écoles. En République dominicaine, il crée en 1880 la première école normale, qui forme des instituteurs à une pédagogie scientifique et laïque. Au Chili, il plaide pour que les femmes aient accès à l’enseignement supérieur et aux professions savantes.&lt;/p&gt; &lt;p&gt;Sa &lt;em&gt;Morale sociale&lt;/em&gt; (1888), inspirée du &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt;, fonde les devoirs de l’individu non sur la religion, mais sur la raison et sur les liens qui l’unissent à la famille, à la société et à l’humanité ; l’éducation doit former des consciences libres et responsables. Après la guerre de 1898, qui fait passer Porto Rico sous domination américaine, il milite pour que l’île puisse décider elle-même de son avenir. Il laisse aussi un traité de sociologie, l’un des premiers d’Amérique latine. Il meurt en exil à Saint-Domingue en 1903.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Augusto_Salazar_Bondy" title=" Wikipedia (es)"&gt;Augusto SALAZAR BONDY&lt;/a&gt; est un philosophe et éducateur péruvien, l’une des figures fondatrices de la philosophie latino-américaine de la libération. Né à Lima, frère cadet de l’écrivain Sebastián Salazar Bondy, il étudie à l’université San Marcos, puis au Mexique auprès de José Gaos et de Leopoldo Zea, et à Paris, où il suit les cours de Jean Wahl, Jean Hyppolite et Gaston Bachelard. Professeur d’éthique à San Marcos, il écrit une grande histoire des idées au Pérou contemporain.&lt;/p&gt; &lt;p&gt;En 1968, il publie &lt;em&gt;Existe-t-il une philosophie de notre Amérique ?&lt;/em&gt;, qui provoque un vif débat avec Leopoldo Zea. Sa réponse est dure : jusqu’ici, il n’existe pas de philosophie latino-américaine authentique, mais seulement des imitations des courants européens, adoptés tour à tour sans être vraiment pensés. Ce n’est pas un manque de talent : c’est la conséquence de la domination et du sous-développement, qui produisent une culture dépendante et « aliénée », incapable de se penser elle-même.&lt;/p&gt; &lt;p&gt;Une philosophie authentique ne pourra naître qu’en prenant pour objet cette situation de domination, et en contribuant à la transformer. La philosophie devient ainsi une tâche de libération, comme le développera la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;philosophie de la libération&lt;/a&gt;. Engagé dans la réforme de l’éducation sous le gouvernement péruvien de la fin des années 1960, il défend une école qui forme des personnes libres et critiques. Il meurt prématurément à Lima en 1974, à quarante-huit ans. Ses idées ont notamment inspiré Enrique Dussel.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">yxxhyhWr-N4</t>
+          <t xml:space="preserve">pKvpeeR1Q4Y</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Eugenio María de Hostos / intelectual educador, filósofo, sociólogo y escritor puertorriqueño" par Damián S. Vargas</t>
+          <t xml:space="preserve">"El concepto de alienación según Augusto Salazar Bondy" par Libros Peruanos</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/hostos-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/salazarbondy-mini.webp</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="K70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positivisme</t>
+          <t xml:space="preserve">Tiers-mondisme ; Philosophie de la libération</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">éducateur et penseur portoricain, apôtre d’une confédération des Antilles et d’une morale sociale laïque.</t>
+          <t xml:space="preserve">philosophe péruvien, auteur d’Existe-t-il une philosophie de notre Amérique ?, penseur de la domination.</t>
         </is>
       </c>
       <c r="N70" s="1" t="inlineStr">
@@ -5581,62 +5578,62 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portoricaine</t>
+          <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>
     <row r="71" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1">
-        <v>1925</v>
+        <v>1839</v>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925 – 2008</t>
+          <t xml:space="preserve">1839 – 1903</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orlando FALS BORDA</t>
+          <t xml:space="preserve">Eugenio María de HOSTOS</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Orlando_Fals_Borda" title=" Wikipedia (en)"&gt;Orlando FALS BORDA&lt;/a&gt; est un sociologue colombien, l’un des grands penseurs latino-américains des sciences sociales et le fondateur de la « recherche-action participative ». Né à Barranquilla, sur la côte caraïbe, formé aux États-Unis, il fonde en 1959 à l’Université nationale de Colombie, avec le prêtre Camilo Torres, l’une des premières facultés de sociologie d’Amérique latine. Son livre &lt;em&gt;La Violence en Colombie&lt;/em&gt; (1962), écrit avec Germán Guzmán et Eduardo Umaña, étudie pour la première fois la guerre civile qui ravage les campagnes.&lt;/p&gt; &lt;p&gt;Déçu par une sociologie qui observe les pauvres de l’extérieur sans rien changer à leur sort, il quitte l’université dans les années 1970 pour travailler avec les paysans et les communautés de la côte caraïbe. Il y développe la &lt;a href="https://fr.wikipedia.org/wiki/Recherche-action" title=" Wikipedia"&gt;recherche-action&lt;/a&gt; participative : le chercheur ne doit pas monopoliser le savoir ni imposer sa technique, mais travailler avec les communautés comme avec des partenaires et des co-chercheurs, recueillir leurs savoirs, leur mémoire et leurs récits, et partager les résultats sous une forme que tous peuvent comprendre.&lt;/p&gt; &lt;p&gt;La science n’est pas, selon lui, une affaire d’experts neutres : elle doit servir la transformation de la société et la libération des opprimés. Il parle d’une « subversion positive » qui conteste l’ordre injuste pour en construire un meilleur. Ses idées se sont répandues dans le monde entier, en éducation, en santé et en développement. Il participe aussi à l’Assemblée constituante qui rédige la Constitution colombienne de 1991. Il meurt à Bogotá en 2008.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Eugenio_Mar%C3%ADa_de_Hostos" title=" Wikipedia (en)"&gt;Eugenio María de HOSTOS&lt;/a&gt; est un philosophe, éducateur, sociologue et écrivain de &lt;a href="https://fr.wikipedia.org/wiki/Porto_Rico" title=" Wikipedia"&gt;Porto Rico&lt;/a&gt;, surnommé « le Grand Citoyen des Amériques ». Né à Mayagüez dans une famille aisée, il fait ses études en Espagne, où il étudie le droit et la philosophie à Madrid et publie en 1863 un roman, &lt;em&gt;Le Pèlerinage de Bayoán&lt;/em&gt;, qui évoque déjà le destin des Antilles. Déçu que la République espagnole refuse l’autonomie de Porto Rico, il quitte l’Espagne en 1869 pour se consacrer à l’indépendance des colonies antillaises.&lt;/p&gt; &lt;p&gt;Il rêve d’une Confédération des Antilles, réunissant Porto Rico, Cuba et la République dominicaine, et parcourt pour la défendre les États-Unis, le Pérou, le Chili, l’Argentine, le Brésil et le Venezuela. Partout, il fonde ou réforme des écoles. En République dominicaine, il crée en 1880 la première école normale, qui forme des instituteurs à une pédagogie scientifique et laïque. Au Chili, il plaide pour que les femmes aient accès à l’enseignement supérieur et aux professions savantes.&lt;/p&gt; &lt;p&gt;Sa &lt;em&gt;Morale sociale&lt;/em&gt; (1888), inspirée du &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt;, fonde les devoirs de l’individu non sur la religion, mais sur la raison et sur les liens qui l’unissent à la famille, à la société et à l’humanité ; l’éducation doit former des consciences libres et responsables. Après la guerre de 1898, qui fait passer Porto Rico sous domination américaine, il milite pour que l’île puisse décider elle-même de son avenir. Il laisse aussi un traité de sociologie, l’un des premiers d’Amérique latine. Il meurt en exil à Saint-Domingue en 1903.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYIrjf9pID0</t>
+          <t xml:space="preserve">yxxhyhWr-N4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">"The work of Orlando Fals Borda" par stanbrad13</t>
+          <t xml:space="preserve">"Eugenio María de Hostos / intelectual educador, filósofo, sociólogo y escritor puertorriqueño" par Damián S. Vargas</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/falsborda-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hostos-mini.webp</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; politique</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="K71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiers-mondisme</t>
+          <t xml:space="preserve">Positivisme</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sociologue colombien, fondateur de la recherche-action participative, penseur d’un savoir construit avec le peuple.</t>
+          <t xml:space="preserve">éducateur et penseur portoricain, apôtre d’une confédération des Antilles et d’une morale sociale laïque.</t>
         </is>
       </c>
       <c r="N71" s="1" t="inlineStr">
@@ -5649,72 +5646,67 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colombienne</t>
+          <t xml:space="preserve">Portoricaine</t>
         </is>
       </c>
     </row>
     <row r="72" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021</t>
+          <t xml:space="preserve">2008</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928 – 2021</t>
+          <t xml:space="preserve">1925 – 2008</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humberto MATURANA</t>
+          <t xml:space="preserve">Orlando FALS BORDA</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Humberto_Maturana" title=" Wikipedia"&gt;Humberto MATURANA&lt;/a&gt; est un biologiste et philosophe chilien, l’un des penseurs les plus originaux de la biologie de la connaissance. Né à Santiago, il étudie la médecine et la biologie au Chili, puis en Angleterre et à Harvard. Au Massachusetts Institute of Technology, il participe en 1959 à une étude devenue célèbre sur ce que l’œil de la grenouille transmet à son cerveau, qui montre que la perception n’est pas une simple copie du monde extérieur. Il fonde ensuite à l’université du Chili un laboratoire d’« épistémologie expérimentale ».&lt;/p&gt; &lt;p&gt;Avec son élève Francisco Varela, il propose au début des années 1970 le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, du grec « se produire soi-même » : un être vivant est un système qui produit et renouvelle sans cesse ses propres composants, et maintient ainsi sa propre organisation. La cellule en est le modèle. Le vivant n’est donc pas défini par ce qu’il contient, mais par cette manière de s’entretenir lui-même, en échange constant avec son milieu.&lt;/p&gt; &lt;p&gt;Il en tire une théorie de la connaissance : « Tout ce qui est dit est dit par un observateur. » Connaître n’est pas refléter un monde tout fait, mais une activité du vivant, qui fait émerger un monde à travers son action. Dans &lt;em&gt;L’Arbre de la connaissance&lt;/em&gt; (1984), écrit avec Varela, il montre aussi que le langage et la société naissent de la coordination entre les êtres, et que l’amour, l’acceptation de l’autre, est le fondement biologique de la vie sociale. Ses idées ont nourri le &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_%28%C3%A9pist%C3%A9mologie%29" title=" Wikipedia"&gt;constructivisme&lt;/a&gt;, la thérapie familiale et la théorie des systèmes sociaux de &lt;a href="https://fr.wikipedia.org/wiki/Niklas_Luhmann" title=" Wikipedia"&gt;Niklas Luhmann&lt;/a&gt;. Il meurt à Santiago en 2021.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Orlando_Fals_Borda" title=" Wikipedia (en)"&gt;Orlando FALS BORDA&lt;/a&gt; est un sociologue colombien, l’un des grands penseurs latino-américains des sciences sociales et le fondateur de la « recherche-action participative ». Né à Barranquilla, sur la côte caraïbe, formé aux États-Unis, il fonde en 1959 à l’Université nationale de Colombie, avec le prêtre Camilo Torres, l’une des premières facultés de sociologie d’Amérique latine. Son livre &lt;em&gt;La Violence en Colombie&lt;/em&gt; (1962), écrit avec Germán Guzmán et Eduardo Umaña, étudie pour la première fois la guerre civile qui ravage les campagnes.&lt;/p&gt; &lt;p&gt;Déçu par une sociologie qui observe les pauvres de l’extérieur sans rien changer à leur sort, il quitte l’université dans les années 1970 pour travailler avec les paysans et les communautés de la côte caraïbe. Il y développe la &lt;a href="https://fr.wikipedia.org/wiki/Recherche-action" title=" Wikipedia"&gt;recherche-action&lt;/a&gt; participative : le chercheur ne doit pas monopoliser le savoir ni imposer sa technique, mais travailler avec les communautés comme avec des partenaires et des co-chercheurs, recueillir leurs savoirs, leur mémoire et leurs récits, et partager les résultats sous une forme que tous peuvent comprendre.&lt;/p&gt; &lt;p&gt;La science n’est pas, selon lui, une affaire d’experts neutres : elle doit servir la transformation de la société et la libération des opprimés. Il parle d’une « subversion positive » qui conteste l’ordre injuste pour en construire un meilleur. Ses idées se sont répandues dans le monde entier, en éducation, en santé et en développement. Il participe aussi à l’Assemblée constituante qui rédige la Constitution colombienne de 1991. Il meurt à Bogotá en 2008.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">19uV8wKpkZw</t>
+          <t xml:space="preserve">CYIrjf9pID0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">"La entrevista al académico Humberto Maturana que inspiró a Mon Laferte | La Belleza de Pensar" par Canal13C</t>
+          <t xml:space="preserve">"The work of Orlando Fals Borda" par stanbrad13</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/maturana-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/falsborda-mini.webp</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; metaphysique</t>
+          <t xml:space="preserve">epistemologie ; politique</t>
         </is>
       </c>
       <c r="K72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constructivisme</t>
+          <t xml:space="preserve">Tiers-mondisme</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">biologiste et philosophe chilien, inventeur avec Varela de l’autopoïèse, penseur de la connaissance comme fait biologique.</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
+          <t xml:space="preserve">sociologue colombien, fondateur de la recherche-action participative, penseur d’un savoir construit avec le peuple.</t>
+        </is>
+      </c>
+      <c r="N72" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="N72" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
         </is>
       </c>
       <c r="O72" s="1">
@@ -5722,47 +5714,47 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chilienne</t>
+          <t xml:space="preserve">Colombienne</t>
         </is>
       </c>
     </row>
     <row r="73" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1">
-        <v>1946</v>
+        <v>1928</v>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001</t>
+          <t xml:space="preserve">2021</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946 – 2001</t>
+          <t xml:space="preserve">1928 – 2021</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francisco VARELA</t>
+          <t xml:space="preserve">Humberto MATURANA</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_Varela" title=" Wikipedia"&gt;Francisco VARELA&lt;/a&gt; est un biologiste, neuroscientifique et philosophe chilien, l’un des fondateurs des sciences cognitives « incarnées ». Né à Talcahuano, élève d’Humberto Maturana, il soutient une thèse de biologie à Harvard, puis invente avec son maître le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, qui définit le vivant par sa capacité à se produire lui-même. Après le coup d’État de Pinochet en 1973, il doit s’exiler aux États-Unis. Il s’installe en France en 1986 et dirige jusqu’à sa mort une équipe de recherche au CNRS, à Paris.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Inscription corporelle de l’esprit&lt;/em&gt; (1991), écrit avec Evan Thompson et Eleanor Rosch, il critique l’idée que l’esprit serait un ordinateur qui traite des représentations d’un monde extérieur déjà donné. Il propose à la place l’« &lt;a href="https://fr.wikipedia.org/wiki/%C3%89naction" title=" Wikipedia"&gt;énaction&lt;/a&gt; » : la cognition est une action incarnée, par laquelle un être vivant fait émerger son monde à travers son corps, ses sens et ses gestes. Il fonde aussi la « neurophénoménologie », qui veut unir les mesures du cerveau et la description rigoureuse de l’expérience vécue, à la manière de Husserl et de Merleau-Ponty.&lt;/p&gt; &lt;p&gt;Pratiquant du bouddhisme tibétain depuis les années 1970, il voit dans la méditation une méthode précise pour explorer l’expérience. En 1987, il cofonde le &lt;a href="https://fr.wikipedia.org/wiki/Mind_and_Life_Institute" title=" Wikipedia"&gt;Mind and Life Institute&lt;/a&gt;, qui organise des rencontres entre scientifiques et le dalaï-lama. Il est l’un des inspirateurs de l’idée d’un esprit « incarné », aujourd’hui centrale en &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_l%27esprit" title=" Wikipedia"&gt;philosophie de l’esprit&lt;/a&gt;. Il meurt à Paris en 2001, à cinquante-quatre ans, d’une maladie du foie.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Humberto_Maturana" title=" Wikipedia"&gt;Humberto MATURANA&lt;/a&gt; est un biologiste et philosophe chilien, l’un des penseurs les plus originaux de la biologie de la connaissance. Né à Santiago, il étudie la médecine et la biologie au Chili, puis en Angleterre et à Harvard. Au Massachusetts Institute of Technology, il participe en 1959 à une étude devenue célèbre sur ce que l’œil de la grenouille transmet à son cerveau, qui montre que la perception n’est pas une simple copie du monde extérieur. Il fonde ensuite à l’université du Chili un laboratoire d’« épistémologie expérimentale ».&lt;/p&gt; &lt;p&gt;Avec son élève Francisco Varela, il propose au début des années 1970 le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, du grec « se produire soi-même » : un être vivant est un système qui produit et renouvelle sans cesse ses propres composants, et maintient ainsi sa propre organisation. La cellule en est le modèle. Le vivant n’est donc pas défini par ce qu’il contient, mais par cette manière de s’entretenir lui-même, en échange constant avec son milieu.&lt;/p&gt; &lt;p&gt;Il en tire une théorie de la connaissance : « Tout ce qui est dit est dit par un observateur. » Connaître n’est pas refléter un monde tout fait, mais une activité du vivant, qui fait émerger un monde à travers son action. Dans &lt;em&gt;L’Arbre de la connaissance&lt;/em&gt; (1984), écrit avec Varela, il montre aussi que le langage et la société naissent de la coordination entre les êtres, et que l’amour, l’acceptation de l’autre, est le fondement biologique de la vie sociale. Ses idées ont nourri le &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_%28%C3%A9pist%C3%A9mologie%29" title=" Wikipedia"&gt;constructivisme&lt;/a&gt;, la thérapie familiale et la théorie des systèmes sociaux de &lt;a href="https://fr.wikipedia.org/wiki/Niklas_Luhmann" title=" Wikipedia"&gt;Niklas Luhmann&lt;/a&gt;. Il meurt à Santiago en 2021.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HPh_uAetJ8U</t>
+          <t xml:space="preserve">19uV8wKpkZw</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Francisco VARELA 2. COPYRIGHT INA ET FRANCETV" par Catherine BARRY - Au coeur du Bouddhisme</t>
+          <t xml:space="preserve">"La entrevista al académico Humberto Maturana que inspiró a Mon Laferte | La Belleza de Pensar" par Canal13C</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/varela-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/maturana-mini.webp</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -5772,12 +5764,12 @@
       </c>
       <c r="K73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constructivisme ; Phénoménologie</t>
+          <t xml:space="preserve">Constructivisme</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">neurobiologiste et philosophe chilien, penseur de l’énaction et du dialogue entre sciences cognitives et bouddhisme.</t>
+          <t xml:space="preserve">biologiste et philosophe chilien, inventeur avec Varela de l’autopoïèse, penseur de la connaissance comme fait biologique.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5801,56 +5793,56 @@
     </row>
     <row r="74" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1">
-        <v>1868</v>
+        <v>1946</v>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963</t>
+          <t xml:space="preserve">2001</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868 – 1963</t>
+          <t xml:space="preserve">1946 – 2001</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">W. E. B. DU BOIS</t>
+          <t xml:space="preserve">Francisco VARELA</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/W._E._B._Du_Bois" title=" Wikipedia"&gt;W. E. B. DU BOIS&lt;/a&gt; (William Edward Burghardt Du Bois) est un sociologue, historien et militant africain-américain, l’un des plus grands penseurs américains du XXe siècle. Né en 1868 dans le Massachusetts, il étudie à Fisk, à Berlin, puis à Harvard, où il devient en 1895 le premier Africain-Américain à obtenir un doctorat. Son étude &lt;em&gt;The Philadelphia Negro&lt;/em&gt; (1899) est l’une des premières grandes enquêtes de sociologie empirique aux États-Unis.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Les_%C3%82mes_du_peuple_noir" title=" Wikipedia"&gt;&lt;em&gt;Les Âmes du peuple noir&lt;/em&gt;&lt;/a&gt; (1903), il affirme que « le problème du XXe siècle est le problème de la ligne de couleur ». Il y décrit la « double conscience » des Noirs américains : le sentiment de se voir toujours à travers les yeux d’un monde qui les méprise, d’être à la fois américain et noir, « deux âmes, deux pensées, deux combats inconciliables dans un seul corps sombre ». Dans &lt;em&gt;Black Reconstruction&lt;/em&gt; (1935), il réhabilitera le rôle des anciens esclaves dans l’histoire américaine d’après la guerre de Sécession. Il y critique aussi Booker T. Washington, qui conseillait aux Noirs d’accepter la ségrégation en échange du progrès économique.&lt;/p&gt; &lt;p&gt;En 1909, il est l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/National_Association_for_the_Advancement_of_Colored_People" title=" Wikipedia"&gt;NAACP&lt;/a&gt;, la grande organisation de défense des droits civiques, dont il dirige la revue &lt;em&gt;The Crisis&lt;/em&gt;. Il organise plusieurs congrès panafricains et devient le « père du &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; ». Proche du socialisme, persécuté pendant le maccarthysme, il s’installe à la fin de sa vie au &lt;a href="https://fr.wikipedia.org/wiki/Ghana" title=" Wikipedia"&gt;Ghana&lt;/a&gt;, à l’invitation de Kwame Nkrumah, et y meurt en 1963, à la veille de la marche sur Washington de Martin Luther King.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_Varela" title=" Wikipedia"&gt;Francisco VARELA&lt;/a&gt; est un biologiste, neuroscientifique et philosophe chilien, l’un des fondateurs des sciences cognitives « incarnées ». Né à Talcahuano, élève d’Humberto Maturana, il soutient une thèse de biologie à Harvard, puis invente avec son maître le concept d’&lt;a href="https://fr.wikipedia.org/wiki/Autopo%C3%AF%C3%A8se" title=" Wikipedia"&gt;autopoïèse&lt;/a&gt;, qui définit le vivant par sa capacité à se produire lui-même. Après le coup d’État de Pinochet en 1973, il doit s’exiler aux États-Unis. Il s’installe en France en 1986 et dirige jusqu’à sa mort une équipe de recherche au CNRS, à Paris.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Inscription corporelle de l’esprit&lt;/em&gt; (1991), écrit avec Evan Thompson et Eleanor Rosch, il critique l’idée que l’esprit serait un ordinateur qui traite des représentations d’un monde extérieur déjà donné. Il propose à la place l’« &lt;a href="https://fr.wikipedia.org/wiki/%C3%89naction" title=" Wikipedia"&gt;énaction&lt;/a&gt; » : la cognition est une action incarnée, par laquelle un être vivant fait émerger son monde à travers son corps, ses sens et ses gestes. Il fonde aussi la « neurophénoménologie », qui veut unir les mesures du cerveau et la description rigoureuse de l’expérience vécue, à la manière de Husserl et de Merleau-Ponty.&lt;/p&gt; &lt;p&gt;Pratiquant du bouddhisme tibétain depuis les années 1970, il voit dans la méditation une méthode précise pour explorer l’expérience. En 1987, il cofonde le &lt;a href="https://fr.wikipedia.org/wiki/Mind_and_Life_Institute" title=" Wikipedia"&gt;Mind and Life Institute&lt;/a&gt;, qui organise des rencontres entre scientifiques et le dalaï-lama. Il est l’un des inspirateurs de l’idée d’un esprit « incarné », aujourd’hui centrale en &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_l%27esprit" title=" Wikipedia"&gt;philosophie de l’esprit&lt;/a&gt;. Il meurt à Paris en 2001, à cinquante-quatre ans, d’une maladie du foie.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Li9wCyjag3Q</t>
+          <t xml:space="preserve">HPh_uAetJ8U</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">"W.E.B. Du Bois : Pionnier des Droits Civiques - Une Conférence par Christian Monjou" par Art et Leadership</t>
+          <t xml:space="preserve">"Francisco VARELA 2. COPYRIGHT INA ET FRANCETV" par Catherine BARRY - Au coeur du Bouddhisme</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/dubois-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/varela-mini.webp</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
         </is>
       </c>
       <c r="K74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan-africanisme</t>
+          <t xml:space="preserve">Constructivisme ; Phénoménologie</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sociologue et militant africain-américain, penseur de la « double conscience » et père du panafricanisme.</t>
+          <t xml:space="preserve">neurobiologiste et philosophe chilien, penseur de l’énaction et du dialogue entre sciences cognitives et bouddhisme.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -5864,200 +5856,207 @@
         </is>
       </c>
       <c r="O74" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Américaine</t>
+          <t xml:space="preserve">Chilienne</t>
         </is>
       </c>
     </row>
     <row r="75" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1">
-        <v>1928</v>
+        <v>1868</v>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024</t>
+          <t xml:space="preserve">1963</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928 – 2024</t>
+          <t xml:space="preserve">1868 – 1963</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustavo GUTIÉRREZ</t>
+          <t xml:space="preserve">W. E. B. DU BOIS</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo GUTIÉRREZ&lt;/a&gt; est un prêtre et théologien péruvien, considéré comme le père de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;théologie de la libération&lt;/a&gt;. Né à Lima en 1928 dans un milieu modeste, il souffre adolescent d’une ostéomyélite qui le cloue longtemps au lit ; il lit alors beaucoup et commence des études de médecine pour devenir psychiatre. À vingt-quatre ans, il choisit la prêtrise et part étudier la philosophie et la psychologie à Louvain, puis la théologie à Lyon.&lt;/p&gt; &lt;p&gt;Ordonné prêtre en 1959, il devient vicaire dans un quartier pauvre de Lima, tout en enseignant à l’université catholique, et repense toute sa théologie au contact de ce peuple. En 1971, il publie &lt;em&gt;Théologie de la libération&lt;/em&gt;, traduit dans une vingtaine de langues. La pauvreté, écrit-il, n’est pas une fatalité mais le fruit d’injustices, et elle est contraire à la volonté de Dieu. La théologie est une « réflexion critique sur la pratique à la lumière de la Parole » : elle vient en second, après l’engagement aux côtés des pauvres. Le salut ne se joue pas seulement dans l’au-delà ; il touche toute l’existence, et la libération sociale et politique en fait partie, sans s’y réduire. Dans &lt;em&gt;Boire à son propre puits&lt;/em&gt; (1983), il montre que cet engagement est aussi une spiritualité, une manière de suivre le Christ.&lt;/p&gt; &lt;p&gt;Ses positions lui valent la méfiance de Rome dans les années 1980, sans condamnation. Entré chez les Dominicains en 1998, il enseigne dans de nombreuses universités d’Europe et des États-Unis. Le pape François le reçoit en 2013, signe de la réhabilitation de son œuvre, et l’« option préférentielle pour les pauvres » est devenue un principe de l’enseignement de l’Église. Il meurt à Lima en 2024, à quatre-vingt-seize ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/W._E._B._Du_Bois" title=" Wikipedia"&gt;W. E. B. DU BOIS&lt;/a&gt; (William Edward Burghardt Du Bois) est un sociologue, historien et militant africain-américain, l’un des plus grands penseurs américains du XXe siècle. Né en 1868 dans le Massachusetts, il étudie à Fisk, à Berlin, puis à Harvard, où il devient en 1895 le premier Africain-Américain à obtenir un doctorat. Son étude &lt;em&gt;The Philadelphia Negro&lt;/em&gt; (1899) est l’une des premières grandes enquêtes de sociologie empirique aux États-Unis.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Les_%C3%82mes_du_peuple_noir" title=" Wikipedia"&gt;&lt;em&gt;Les Âmes du peuple noir&lt;/em&gt;&lt;/a&gt; (1903), il affirme que « le problème du XXe siècle est le problème de la ligne de couleur ». Il y décrit la « double conscience » des Noirs américains : le sentiment de se voir toujours à travers les yeux d’un monde qui les méprise, d’être à la fois américain et noir, « deux âmes, deux pensées, deux combats inconciliables dans un seul corps sombre ». Dans &lt;em&gt;Black Reconstruction&lt;/em&gt; (1935), il réhabilitera le rôle des anciens esclaves dans l’histoire américaine d’après la guerre de Sécession. Il y critique aussi Booker T. Washington, qui conseillait aux Noirs d’accepter la ségrégation en échange du progrès économique.&lt;/p&gt; &lt;p&gt;En 1909, il est l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/National_Association_for_the_Advancement_of_Colored_People" title=" Wikipedia"&gt;NAACP&lt;/a&gt;, la grande organisation de défense des droits civiques, dont il dirige la revue &lt;em&gt;The Crisis&lt;/em&gt;. Il organise plusieurs congrès panafricains et devient le « père du &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; ». Proche du socialisme, persécuté pendant le maccarthysme, il s’installe à la fin de sa vie au &lt;a href="https://fr.wikipedia.org/wiki/Ghana" title=" Wikipedia"&gt;Ghana&lt;/a&gt;, à l’invitation de Kwame Nkrumah, et y meurt en 1963, à la veille de la marche sur Washington de Martin Luther King.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">mdBvcdTUDRg</t>
+          <t xml:space="preserve">Li9wCyjag3Q</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">"La libération comme espérance chez Gustavo Gutierrez" par Didascale</t>
+          <t xml:space="preserve">"W.E.B. Du Bois : Pionnier des Droits Civiques - Une Conférence par Christian Monjou" par Art et Leadership</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ggutierrez-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dubois-mini.webp</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; politique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="K75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie de la libération</t>
+          <t xml:space="preserve">Pan-africanisme</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prêtre et théologien péruvien, père de la théologie de la libération et de l’« option préférentielle pour les pauvres ».</t>
+          <t xml:space="preserve">sociologue et militant africain-américain, penseur de la « double conscience » et père du panafricanisme.</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
       <c r="O75" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Péruvienne</t>
+          <t xml:space="preserve">Américaine</t>
         </is>
       </c>
     </row>
     <row r="76" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1">
-        <v>1840</v>
+        <v>1928</v>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910</t>
+          <t xml:space="preserve">2024</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840 – 1910</t>
+          <t xml:space="preserve">1928 – 2024</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">William Graham SUMNER</t>
+          <t xml:space="preserve">Gustavo GUTIÉRREZ</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/William_Graham_Sumner" title=" Wikipedia"&gt;William Graham SUMNER&lt;/a&gt; est un sociologue et économiste américain, l’un des fondateurs de la sociologie aux États-Unis et la figure majeure de ce qu’on appellera le &lt;a href="https://fr.wikipedia.org/wiki/Darwinisme_social" title=" Wikipedia"&gt;darwinisme social&lt;/a&gt; américain. Né en 1840 à Paterson, dans le New Jersey, fils d’un ouvrier anglais immigré, il étudie à Yale, puis en Europe, et devient d’abord pasteur épiscopalien. En 1872, il est nommé professeur à Yale, où il donne l’un des premiers cours intitulés « sociologie ».&lt;/p&gt; &lt;p&gt;Lecteur de Herbert Spencer, il applique à la société l’idée de lutte pour l’existence. Dans &lt;em&gt;Ce que les classes sociales se doivent les unes aux autres&lt;/em&gt; (1883), il répond : rien, sinon le respect de la liberté et des contrats. L’aide de l’État aux pauvres se fait toujours aux dépens de l’« homme oublié », le travailleur modeste qui paie ses impôts sans rien demander. La richesse récompense le travail, l’épargne et la tempérance, et la réussite des plus capables profite à toute la société. Ces positions ont fait de lui, aux yeux de ses critiques, le défenseur d’un capitalisme sans pitié pour les faibles.&lt;/p&gt; &lt;p&gt;Mais il défend aussi le libre-échange contre les monopoles protégés et s’oppose fermement à l’impérialisme : en 1898, il dénonce la guerre contre l’Espagne et la conquête des Philippines dans &lt;em&gt;La Conquête des États-Unis par l’Espagne&lt;/em&gt;. Dans &lt;em&gt;Folkways&lt;/em&gt; (1906), il étudie les coutumes et les mœurs des sociétés, et forge le mot « ethnocentrisme » pour désigner la tendance de chaque groupe à juger les autres d’après ses propres valeurs. Il meurt en 1910.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo GUTIÉRREZ&lt;/a&gt; est un prêtre et théologien péruvien, considéré comme le père de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;théologie de la libération&lt;/a&gt;. Né à Lima en 1928 dans un milieu modeste, il souffre adolescent d’une ostéomyélite qui le cloue longtemps au lit ; il lit alors beaucoup et commence des études de médecine pour devenir psychiatre. À vingt-quatre ans, il choisit la prêtrise et part étudier la philosophie et la psychologie à Louvain, puis la théologie à Lyon.&lt;/p&gt; &lt;p&gt;Ordonné prêtre en 1959, il devient vicaire dans un quartier pauvre de Lima, tout en enseignant à l’université catholique, et repense toute sa théologie au contact de ce peuple. En 1971, il publie &lt;em&gt;Théologie de la libération&lt;/em&gt;, traduit dans une vingtaine de langues. La pauvreté, écrit-il, n’est pas une fatalité mais le fruit d’injustices, et elle est contraire à la volonté de Dieu. La théologie est une « réflexion critique sur la pratique à la lumière de la Parole » : elle vient en second, après l’engagement aux côtés des pauvres. Le salut ne se joue pas seulement dans l’au-delà ; il touche toute l’existence, et la libération sociale et politique en fait partie, sans s’y réduire. Dans &lt;em&gt;Boire à son propre puits&lt;/em&gt; (1983), il montre que cet engagement est aussi une spiritualité, une manière de suivre le Christ.&lt;/p&gt; &lt;p&gt;Ses positions lui valent la méfiance de Rome dans les années 1980, sans condamnation. Entré chez les Dominicains en 1998, il enseigne dans de nombreuses universités d’Europe et des États-Unis. Le pape François le reçoit en 2013, signe de la réhabilitation de son œuvre, et l’« option préférentielle pour les pauvres » est devenue un principe de l’enseignement de l’Église. Il meurt à Lima en 2024, à quatre-vingt-seize ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">r-myUjOJ0qY</t>
+          <t xml:space="preserve">mdBvcdTUDRg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Folkways by William Graham Sumner" par Sociologylearners</t>
+          <t xml:space="preserve">"La libération comme espérance chez Gustavo Gutierrez" par Didascale</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/sumner-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ggutierrez-mini.webp</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">spiritualite ; politique</t>
         </is>
       </c>
       <c r="K76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darwinisme social ; Libéralisme</t>
+          <t xml:space="preserve">Théologie de la libération</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sociologue américain de Yale, défenseur d’un libéralisme sans État-providence, inventeur du mot « ethnocentrisme ».</t>
+          <t xml:space="preserve">prêtre et théologien péruvien, père de la théologie de la libération et de l’« option préférentielle pour les pauvres ».</t>
         </is>
       </c>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O76" s="1"/>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O76" s="1">
+        <v>2</v>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Américaine</t>
+          <t xml:space="preserve">Péruvienne</t>
         </is>
       </c>
     </row>
     <row r="77" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1">
-        <v>1917</v>
+        <v>1840</v>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003</t>
+          <t xml:space="preserve">1910</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917 – 2003</t>
+          <t xml:space="preserve">1840 – 1910</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Donald DAVIDSON</t>
+          <t xml:space="preserve">William Graham SUMNER</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donald_Davidson" title=" Wikipedia"&gt;Donald DAVIDSON&lt;/a&gt; est un philosophe américain, l’un des plus influents de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; de la seconde moitié du XXe siècle. Né en 1917 à Springfield, dans le Massachusetts, il étudie à Harvard la littérature et les lettres classiques avant de se tourner vers la philosophie sous l’influence de Quine. Après avoir servi dans la marine pendant la guerre, il enseigne notamment à Stanford, à Princeton et à Berkeley.&lt;/p&gt; &lt;p&gt;Dans « Actions, raisons et causes » (1963), il soutient que nos raisons d’agir, nos désirs et nos croyances, sont aussi les causes de nos actions. Dans « Les événements mentaux » (1970), il défend le « monisme anomal » : chaque événement mental est un événement physique, mais il n’existe pas de lois strictes qui relient le mental au physique, car le mental obéit à d’autres principes, ceux de la rationalité. Il réconcilie ainsi le matérialisme avec l’autonomie de la pensée.&lt;/p&gt; &lt;p&gt;Sa théorie de l’« interprétation radicale » prolonge le &lt;a href="https://fr.wikipedia.org/wiki/Holisme" title=" Wikipedia"&gt;holisme&lt;/a&gt; de Quine : pour comprendre un locuteur dont on ignore tout de la langue, il faut lui attribuer en même temps des croyances et des significations, en supposant qu’il pense en grande partie comme nous. C’est le « principe de charité ». Le sens d’un mot dépend du sens de toute la langue, et nos croyances forment un réseau. Il en conclut, dans un article célèbre de 1974, que l’idée de « schèmes conceptuels » radicalement incommensurables n’a pas de sens. Il meurt à Berkeley en 2003.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/William_Graham_Sumner" title=" Wikipedia"&gt;William Graham SUMNER&lt;/a&gt; est un sociologue et économiste américain, l’un des fondateurs de la sociologie aux États-Unis et la figure majeure de ce qu’on appellera le &lt;a href="https://fr.wikipedia.org/wiki/Darwinisme_social" title=" Wikipedia"&gt;darwinisme social&lt;/a&gt; américain. Né en 1840 à Paterson, dans le New Jersey, fils d’un ouvrier anglais immigré, il étudie à Yale, puis en Europe, et devient d’abord pasteur épiscopalien. En 1872, il est nommé professeur à Yale, où il donne l’un des premiers cours intitulés « sociologie ».&lt;/p&gt; &lt;p&gt;Lecteur de Herbert Spencer, il applique à la société l’idée de lutte pour l’existence. Dans &lt;em&gt;Ce que les classes sociales se doivent les unes aux autres&lt;/em&gt; (1883), il répond : rien, sinon le respect de la liberté et des contrats. L’aide de l’État aux pauvres se fait toujours aux dépens de l’« homme oublié », le travailleur modeste qui paie ses impôts sans rien demander. La richesse récompense le travail, l’épargne et la tempérance, et la réussite des plus capables profite à toute la société. Ces positions ont fait de lui, aux yeux de ses critiques, le défenseur d’un capitalisme sans pitié pour les faibles.&lt;/p&gt; &lt;p&gt;Mais il défend aussi le libre-échange contre les monopoles protégés et s’oppose fermement à l’impérialisme : en 1898, il dénonce la guerre contre l’Espagne et la conquête des Philippines dans &lt;em&gt;La Conquête des États-Unis par l’Espagne&lt;/em&gt;. Dans &lt;em&gt;Folkways&lt;/em&gt; (1906), il étudie les coutumes et les mœurs des sociétés, et forge le mot « ethnocentrisme » pour désigner la tendance de chaque groupe à juger les autres d’après ses propres valeurs. Il meurt en 1910.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecqO4LMbYvk</t>
+          <t xml:space="preserve">r-myUjOJ0qY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Donald Davidson Interview: Language, Interpretation, &amp; Philosophy (1993)" par Philosophy Overdose</t>
+          <t xml:space="preserve">"Folkways by William Graham Sumner" par Sociologylearners</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/donalddavidson-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/sumner-mini.webp</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">langage ; epistemologie ; metaphysique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="K77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holisme ; Analytique</t>
+          <t xml:space="preserve">Darwinisme social ; Libéralisme</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe américain de l’action et du langage, auteur du « monisme anomal ».</t>
+          <t xml:space="preserve">sociologue américain de Yale, défenseur d’un libéralisme sans État-providence, inventeur du mot « ethnocentrisme ».</t>
         </is>
       </c>
       <c r="N77" s="1" t="inlineStr">
@@ -6074,56 +6073,56 @@
     </row>
     <row r="78" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1">
-        <v>1912</v>
+        <v>1917</v>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1989</t>
+          <t xml:space="preserve">2003</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912 – 1989</t>
+          <t xml:space="preserve">1917 – 2003</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wilfrid SELLARS</t>
+          <t xml:space="preserve">Donald DAVIDSON</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Wilfrid_Sellars" title=" Wikipedia"&gt;Wilfrid SELLARS&lt;/a&gt; est un philosophe américain, l’un des plus profonds de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; du XXe siècle. Né en 1912 à Ann Arbor, fils du philosophe Roy Wood Sellars, il étudie au Michigan, à Buffalo puis à Oxford. Il enseigne au Minnesota, à Yale, et à partir de 1963 à l’université de Pittsburgh, où il fait école. Avec Herbert Feigl, il fonde en 1950 la revue &lt;em&gt;Philosophical Studies&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Dans « Empirisme et philosophie de l’esprit » (1956), il s’attaque au « mythe du donné » : l’idée, commune aux empiristes, que notre connaissance repose sur des données des sens que nous saisirions immédiatement, sans concepts. Pour Sellars, voir que quelque chose est rouge, c’est déjà savoir ce qu’est le rouge et être capable de le justifier. La connaissance appartient à l’« espace logique des raisons », où l’on donne et demande des justifications, et non à un simple contact causal avec le monde. Même l’observation la plus simple suppose tout un langage et tout un savoir, appris avec lui.&lt;/p&gt; &lt;p&gt;Dans « La philosophie et l’image scientifique de l’homme » (1962), il oppose l’« image manifeste », celle du monde de la vie quotidienne, peuplé de personnes, de couleurs et d’intentions, et l’« image scientifique », faite de particules et de processus. La tâche de la philosophie est de les unir en une seule vision. Pour lui, la science est « la mesure de toutes choses ». Il meurt à Pittsburgh en 1989. Longtemps jugé difficile, il est aujourd’hui l’un des philosophes américains les plus étudiés. Ses idées inspirent Richard Rorty, Robert Brandom et John McDowell.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donald_Davidson" title=" Wikipedia"&gt;Donald DAVIDSON&lt;/a&gt; est un philosophe américain, l’un des plus influents de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; de la seconde moitié du XXe siècle. Né en 1917 à Springfield, dans le Massachusetts, il étudie à Harvard la littérature et les lettres classiques avant de se tourner vers la philosophie sous l’influence de Quine. Après avoir servi dans la marine pendant la guerre, il enseigne notamment à Stanford, à Princeton et à Berkeley.&lt;/p&gt; &lt;p&gt;Dans « Actions, raisons et causes » (1963), il soutient que nos raisons d’agir, nos désirs et nos croyances, sont aussi les causes de nos actions. Dans « Les événements mentaux » (1970), il défend le « monisme anomal » : chaque événement mental est un événement physique, mais il n’existe pas de lois strictes qui relient le mental au physique, car le mental obéit à d’autres principes, ceux de la rationalité. Il réconcilie ainsi le matérialisme avec l’autonomie de la pensée.&lt;/p&gt; &lt;p&gt;Sa théorie de l’« interprétation radicale » prolonge le &lt;a href="https://fr.wikipedia.org/wiki/Holisme" title=" Wikipedia"&gt;holisme&lt;/a&gt; de Quine : pour comprendre un locuteur dont on ignore tout de la langue, il faut lui attribuer en même temps des croyances et des significations, en supposant qu’il pense en grande partie comme nous. C’est le « principe de charité ». Le sens d’un mot dépend du sens de toute la langue, et nos croyances forment un réseau. Il en conclut, dans un article célèbre de 1974, que l’idée de « schèmes conceptuels » radicalement incommensurables n’a pas de sens. Il meurt à Berkeley en 2003.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">eJ_0-_NGXQE</t>
+          <t xml:space="preserve">ecqO4LMbYvk</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Wilfrid Sellars : Science et métaphysique (1) - Jacques Bouveresse (2008-2009)" par Lettres, langage, philosophie - Collège de France</t>
+          <t xml:space="preserve">"Donald Davidson Interview: Language, Interpretation, &amp; Philosophy (1993)" par Philosophy Overdose</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/wsellars-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/donalddavidson-mini.webp</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; metaphysique ; langage</t>
+          <t xml:space="preserve">langage ; epistemologie ; metaphysique</t>
         </is>
       </c>
       <c r="K78" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytique ; Réalisme scientifique</t>
+          <t xml:space="preserve">Holisme ; Analytique</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe américain, critique du « mythe du donné » et penseur de l’« image scientifique » de l’homme.</t>
+          <t xml:space="preserve">philosophe américain de l’action et du langage, auteur du « monisme anomal ».</t>
         </is>
       </c>
       <c r="N78" s="1" t="inlineStr">
@@ -6131,9 +6130,7 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O78" s="1">
-        <v>2</v>
-      </c>
+      <c r="O78" s="1"/>
       <c r="P78" t="inlineStr">
         <is>
           <t xml:space="preserve">Américaine</t>
@@ -6142,56 +6139,56 @@
     </row>
     <row r="79" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1">
-        <v>1924</v>
+        <v>1912</v>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013</t>
+          <t xml:space="preserve">1989</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924 – 2013</t>
+          <t xml:space="preserve">1912 – 1989</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arthur DANTO</t>
+          <t xml:space="preserve">Wilfrid SELLARS</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arthur_Danto" title=" Wikipedia"&gt;Arthur DANTO&lt;/a&gt; est un philosophe et critique d’art américain. Né en 1924 à Ann Arbor, il grandit à Detroit, sert pendant la Seconde Guerre mondiale en Afrique du Nord et en Italie, puis étudie l’art et la philosophie. D’abord graveur, il enseigne à l’université Columbia, à New York, de 1951 à 1992. Ses premiers livres portent sur la philosophie de l’histoire, où il étudie les « phrases narratives », qui décrivent un événement à la lumière de ce qui l’a suivi, et sur Nietzsche, qu’il fait connaître aux philosophes analytiques.&lt;/p&gt; &lt;p&gt;En 1964, il voit exposées les &lt;em&gt;Brillo Boxes&lt;/em&gt; d’Andy Warhol, des boîtes identiques à celles des supermarchés. Pourquoi l’une est-elle une œuvre d’art, et l’autre non, alors qu’on ne peut pas les distinguer à l’œil ? Dans l’article « Le monde de l’art », il répond que ce qui fait l’œuvre n’est pas une propriété visible, mais une théorie et une histoire de l’art, une atmosphère que seul connaît ce « monde de l’art ». Dans &lt;em&gt;La Transfiguration du banal&lt;/em&gt; (1981), il précise : une œuvre d’art est toujours à propos de quelque chose, et elle incarne ce sens, ce qui la distingue d’une simple chose.&lt;/p&gt; &lt;p&gt;Il en tire en 1984 la thèse de la « fin de l’art » : non que l’on cesse de créer, mais l’art, depuis Warhol, n’a plus d’histoire orientée, et tout est désormais possible. C’est à la &lt;a href="https://fr.wikipedia.org/wiki/Esth%C3%A9tique" title=" Wikipedia"&gt;philosophie&lt;/a&gt;, et non plus à l’art, de dire ce qu’est l’art. Critique d’art à l’hebdomadaire &lt;em&gt;The Nation&lt;/em&gt; de 1984 à 2009, il est l’un des esthéticiens les plus lus de son temps. Il meurt à New York en 2013.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Wilfrid_Sellars" title=" Wikipedia"&gt;Wilfrid SELLARS&lt;/a&gt; est un philosophe américain, l’un des plus profonds de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; du XXe siècle. Né en 1912 à Ann Arbor, fils du philosophe Roy Wood Sellars, il étudie au Michigan, à Buffalo puis à Oxford. Il enseigne au Minnesota, à Yale, et à partir de 1963 à l’université de Pittsburgh, où il fait école. Avec Herbert Feigl, il fonde en 1950 la revue &lt;em&gt;Philosophical Studies&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Dans « Empirisme et philosophie de l’esprit » (1956), il s’attaque au « mythe du donné » : l’idée, commune aux empiristes, que notre connaissance repose sur des données des sens que nous saisirions immédiatement, sans concepts. Pour Sellars, voir que quelque chose est rouge, c’est déjà savoir ce qu’est le rouge et être capable de le justifier. La connaissance appartient à l’« espace logique des raisons », où l’on donne et demande des justifications, et non à un simple contact causal avec le monde. Même l’observation la plus simple suppose tout un langage et tout un savoir, appris avec lui.&lt;/p&gt; &lt;p&gt;Dans « La philosophie et l’image scientifique de l’homme » (1962), il oppose l’« image manifeste », celle du monde de la vie quotidienne, peuplé de personnes, de couleurs et d’intentions, et l’« image scientifique », faite de particules et de processus. La tâche de la philosophie est de les unir en une seule vision. Pour lui, la science est « la mesure de toutes choses ». Il meurt à Pittsburgh en 1989. Longtemps jugé difficile, il est aujourd’hui l’un des philosophes américains les plus étudiés. Ses idées inspirent Richard Rorty, Robert Brandom et John McDowell.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3xVufNOZPqE</t>
+          <t xml:space="preserve">eJ_0-_NGXQE</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Arthur Danto: La transfiguration du banal. Une philosophie de l'art." par Jtgrandtour</t>
+          <t xml:space="preserve">"Wilfrid Sellars : Science et métaphysique (1) - Jacques Bouveresse (2008-2009)" par Lettres, langage, philosophie - Collège de France</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/danto-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/wsellars-mini.webp</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; epistemologie</t>
+          <t xml:space="preserve">epistemologie ; metaphysique ; langage</t>
         </is>
       </c>
       <c r="K79" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytique</t>
+          <t xml:space="preserve">Analytique ; Réalisme scientifique</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et critique d’art américain, théoricien du « monde de l’art » et de la fin de l’art.</t>
+          <t xml:space="preserve">philosophe américain, critique du « mythe du donné » et penseur de l’« image scientifique » de l’homme.</t>
         </is>
       </c>
       <c r="N79" s="1" t="inlineStr">
@@ -6210,56 +6207,56 @@
     </row>
     <row r="80" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1">
-        <v>1929</v>
+        <v>1924</v>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023</t>
+          <t xml:space="preserve">2013</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929 – 2023</t>
+          <t xml:space="preserve">1924 – 2013</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harry FRANKFURT</t>
+          <t xml:space="preserve">Arthur DANTO</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Harry_Frankfurt" title=" Wikipedia"&gt;Harry FRANKFURT&lt;/a&gt; est un philosophe américain. Né en 1929 à Langhorne, en Pennsylvanie, il étudie à l’université Johns-Hopkins et enseigne à l’université Rockefeller, à Yale, puis à Princeton jusqu’en 2002. Spécialiste de Descartes, il devient surtout l’un des penseurs majeurs de la liberté, de la responsabilité et de la personne, dans un style d’une grande clarté.&lt;/p&gt; &lt;p&gt;En 1969, il imagine des cas, appelés depuis « cas de Frankfurt », pour contester l’idée qu’on n’est responsable d’un acte que si l’on aurait pu agir autrement. Un neurologue malveillant est prêt à intervenir dans le cerveau de Jones pour le forcer à agir, mais Jones fait de lui-même ce qu’on attendait, sans intervention : il est responsable, bien qu’il n’ait pas eu d’autre possibilité. En 1971, il définit la personne par les « désirs de second ordre » : nous ne voulons pas seulement des choses, nous voulons aussi avoir ou ne pas avoir certains désirs. Être libre, c’est agir selon les désirs que l’on approuve. Ces idées font de lui l’un des grands défenseurs du &lt;a href="https://fr.wikipedia.org/wiki/Compatibilisme" title=" Wikipedia"&gt;compatibilisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Son petit essai &lt;em&gt;De l’art de dire des conneries&lt;/em&gt;, écrit en 1986 et publié en livre en 2005, devient un best-seller : le baratineur est plus dangereux que le menteur, car le menteur se soucie encore de la vérité pour la cacher, alors que le baratineur y est indifférent. Dans &lt;em&gt;Les Raisons de l’amour&lt;/em&gt; (2004), il montre que c’est ce que nous aimons qui donne sens à notre vie. Dans &lt;em&gt;On Inequality&lt;/em&gt; (2015), il soutient que l’important n’est pas que chacun ait autant, mais que chacun ait assez. Il meurt à Santa Monica en 2023.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arthur_Danto" title=" Wikipedia"&gt;Arthur DANTO&lt;/a&gt; est un philosophe et critique d’art américain. Né en 1924 à Ann Arbor, il grandit à Detroit, sert pendant la Seconde Guerre mondiale en Afrique du Nord et en Italie, puis étudie l’art et la philosophie. D’abord graveur, il enseigne à l’université Columbia, à New York, de 1951 à 1992. Ses premiers livres portent sur la philosophie de l’histoire, où il étudie les « phrases narratives », qui décrivent un événement à la lumière de ce qui l’a suivi, et sur Nietzsche, qu’il fait connaître aux philosophes analytiques.&lt;/p&gt; &lt;p&gt;En 1964, il voit exposées les &lt;em&gt;Brillo Boxes&lt;/em&gt; d’Andy Warhol, des boîtes identiques à celles des supermarchés. Pourquoi l’une est-elle une œuvre d’art, et l’autre non, alors qu’on ne peut pas les distinguer à l’œil ? Dans l’article « Le monde de l’art », il répond que ce qui fait l’œuvre n’est pas une propriété visible, mais une théorie et une histoire de l’art, une atmosphère que seul connaît ce « monde de l’art ». Dans &lt;em&gt;La Transfiguration du banal&lt;/em&gt; (1981), il précise : une œuvre d’art est toujours à propos de quelque chose, et elle incarne ce sens, ce qui la distingue d’une simple chose.&lt;/p&gt; &lt;p&gt;Il en tire en 1984 la thèse de la « fin de l’art » : non que l’on cesse de créer, mais l’art, depuis Warhol, n’a plus d’histoire orientée, et tout est désormais possible. C’est à la &lt;a href="https://fr.wikipedia.org/wiki/Esth%C3%A9tique" title=" Wikipedia"&gt;philosophie&lt;/a&gt;, et non plus à l’art, de dire ce qu’est l’art. Critique d’art à l’hebdomadaire &lt;em&gt;The Nation&lt;/em&gt; de 1984 à 2009, il est l’un des esthéticiens les plus lus de son temps. Il meurt à New York en 2013.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">FXewQRCpKAs</t>
+          <t xml:space="preserve">3xVufNOZPqE</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">"La Rhétorique Toxique et le Bullshit - Harry.G.Frankfurt" par MLHORION</t>
+          <t xml:space="preserve">"Arthur Danto: La transfiguration du banal. Une philosophie de l'art." par Jtgrandtour</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/frankfurt-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/danto-mini.webp</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; metaphysique</t>
+          <t xml:space="preserve">esthetique ; epistemologie</t>
         </is>
       </c>
       <c r="K80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compatibilisme</t>
+          <t xml:space="preserve">Analytique</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe américain de la liberté et de la personne, auteur de « De l’art de dire des conneries ».</t>
+          <t xml:space="preserve">philosophe et critique d’art américain, théoricien du « monde de l’art » et de la fin de l’art.</t>
         </is>
       </c>
       <c r="N80" s="1" t="inlineStr">
@@ -6282,52 +6279,65 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024</t>
+          <t xml:space="preserve">2023</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929 – 2024</t>
+          <t xml:space="preserve">1929 – 2023</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newton DA COSTA</t>
+          <t xml:space="preserve">Harry FRANKFURT</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Newton_da_Costa" title=" Wikipedia (en)"&gt;Newton DA COSTA&lt;/a&gt; est un logicien et philosophe brésilien, l’un des fondateurs de la &lt;a href="https://fr.wikipedia.org/wiki/Logique_paraconsistante" title=" Wikipedia"&gt;logique paraconsistante&lt;/a&gt;. Né en 1929 à Curitiba, il étudie d’abord le génie civil puis les mathématiques, et enseigne à l’université fédérale du Paraná, puis à l’université de São Paulo et à l’université fédérale de Santa Catarina.&lt;/p&gt; &lt;p&gt;Dans la logique classique, une seule contradiction suffit à tout prouver : si l’on admet à la fois une proposition et sa négation, on peut en déduire n’importe quoi. C’est le principe d’« explosion ». Dès sa thèse de 1963, da Costa construit des systèmes logiques, appelés « calculs C », où l’on peut admettre certaines contradictions sans que toute la théorie s’effondre. Le nom de « paraconsistance » leur est donné en 1976 par le philosophe péruvien Francisco Miró Quesada. Ces logiques permettent de raisonner rigoureusement sur des informations contradictoires, comme celles d’une base de données, d’un témoignage ou d’une théorie scientifique en crise.&lt;/p&gt; &lt;p&gt;Da Costa étend ces travaux à la théorie des ensembles et à la philosophie des sciences. Avec Steven French, il développe la notion de « quasi-vérité » : une théorie scientifique peut être partiellement vraie et utile sans être entièrement exacte. Avec Francisco Antônio Dória, il montre en 1991 que certaines questions de la théorie du chaos sont indécidables : aucun calcul ne peut y répondre. Membre de nombreuses académies, il a formé une importante école de logique au Brésil et en Amérique latine. Il meurt en 2024 à Florianópolis.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Harry_Frankfurt" title=" Wikipedia"&gt;Harry FRANKFURT&lt;/a&gt; est un philosophe américain. Né en 1929 à Langhorne, en Pennsylvanie, il étudie à l’université Johns-Hopkins et enseigne à l’université Rockefeller, à Yale, puis à Princeton jusqu’en 2002. Spécialiste de Descartes, il devient surtout l’un des penseurs majeurs de la liberté, de la responsabilité et de la personne, dans un style d’une grande clarté.&lt;/p&gt; &lt;p&gt;En 1969, il imagine des cas, appelés depuis « cas de Frankfurt », pour contester l’idée qu’on n’est responsable d’un acte que si l’on aurait pu agir autrement. Un neurologue malveillant est prêt à intervenir dans le cerveau de Jones pour le forcer à agir, mais Jones fait de lui-même ce qu’on attendait, sans intervention : il est responsable, bien qu’il n’ait pas eu d’autre possibilité. En 1971, il définit la personne par les « désirs de second ordre » : nous ne voulons pas seulement des choses, nous voulons aussi avoir ou ne pas avoir certains désirs. Être libre, c’est agir selon les désirs que l’on approuve. Ces idées font de lui l’un des grands défenseurs du &lt;a href="https://fr.wikipedia.org/wiki/Compatibilisme" title=" Wikipedia"&gt;compatibilisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Son petit essai &lt;em&gt;De l’art de dire des conneries&lt;/em&gt;, écrit en 1986 et publié en livre en 2005, devient un best-seller : le baratineur est plus dangereux que le menteur, car le menteur se soucie encore de la vérité pour la cacher, alors que le baratineur y est indifférent. Dans &lt;em&gt;Les Raisons de l’amour&lt;/em&gt; (2004), il montre que c’est ce que nous aimons qui donne sens à notre vie. Dans &lt;em&gt;On Inequality&lt;/em&gt; (2015), il soutient que l’important n’est pas que chacun ait autant, mais que chacun ait assez. Il meurt à Santa Monica en 2023.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FXewQRCpKAs</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La Rhétorique Toxique et le Bullshit - Harry.G.Frankfurt" par MLHORION</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/dacosta-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/frankfurt-mini.webp</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">logique ; epistemologie</t>
+          <t xml:space="preserve">ethique ; metaphysique</t>
         </is>
       </c>
       <c r="K81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logique paraconsistante</t>
+          <t xml:space="preserve">Compatibilisme</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">logicien brésilien, l’un des fondateurs des logiques paraconsistantes.</t>
+          <t xml:space="preserve">philosophe américain de la liberté et de la personne, auteur de « De l’art de dire des conneries ».</t>
         </is>
       </c>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
-        </is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O81" s="1">
+        <v>2</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brésilienne</t>
+          <t xml:space="preserve">Américaine</t>
         </is>
       </c>
     </row>
@@ -6970,17 +6980,17 @@
     <hyperlink ref="H40" r:id="rId25" display="https://www.laphilo.fr/pho/scavell-mini.webp"/>
     <hyperlink ref="H41" r:id="rId26" display="https://www.laphilo.fr/pho/mrothbard-mini.webp"/>
     <hyperlink ref="H42" r:id="rId27" display="https://www.laphilo.fr/pho/ewiesel-mini.webp"/>
-    <hyperlink ref="H43" r:id="rId28" display="https://www.laphilo.fr/pho/abracken-mini.webp"/>
-    <hyperlink ref="E45" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Rorty&quot; title=&quot; Wikipedia&quot;&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href=&quot;https://www.youtube.com/watch?v=lfx4Jag1ic4&quot;  title=&quot;Le pragmatisme : définition, exemples par le savoir partagé&quot;&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href=&quot;https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism&quot; title=&quot; a bas l'autorité par laviedesidees&quot;&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas &quot;vrais&quot; ou &quot;faux&quot;. &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales , on trouve  &lt;a href=&quot;https://www.youtube.com/watch?v=MgU0dXZ3umM&quot; title=&quot;L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli&quot;&gt;&quot; Contingence, ironie et solidarité &quot;&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans &quot; Achieving Our Country&quot; (1998),  il y appelle la gauche américaine à abandonner le &quot;culturalisme&quot; pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la &quot;post-vérité&quot;. Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; "/>
-    <hyperlink ref="E47" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Charles_Parsons_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Charles Dacre PARSONS&lt;/a&gt; était un philosophe américain connu pour ses travaux en philosophie des mathématiques et en philosophie de Kant. Il a enseigné à Columbia puis à Harvard, où il est devenu professeur émérite. Il s’est formé à Harvard, avec une thèse dirigée par Willard Van Orman Quine, ce qui le place au croisement de la logique, de la philosophie analytique et des fondements des mathématiques. Son parcours intellectuel a été marqué très tôt par la rigueur mathématique, puisqu’il avait d’abord étudié les mathématiques avant de se tourner vers la philosophie. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la philosophie des mathématiques, domaine dans lequel il a travaillé sur la nature des objets mathématiques, la logique, la preuve et l’interprétation constructive des mathématiques prédicatives. Il a aussi beaucoup écrit sur Frege, Gödel, Hilbert et Quine, en lisant ces auteurs à la fois comme philosophes et comme figures majeures des fondements. &lt;/p&gt; &lt;p&gt; Il n’était pas seulement un spécialiste de logique ; il a aussi produit des travaux importants sur Kant, montrant comment les questions de connaissance, d’expérience et de structure de l’esprit se relient aux mathématiques. Cette double compétence, en philosophie des mathématiques et en histoire de la philosophie, explique pourquoi il est souvent vu comme un auteur à la fois technique et très large dans ses intérêts.&lt;/p&gt; &lt;p&gt; Son influence est restée forte dans le monde anglophone, au point d’être décrit comme l’un des philosophes des mathématiques les plus importants de sa génération. En plus de ses livres et articles, il a aussi contribué à l’édition de textes posthumes de Gödel, ce qui a renforcé son rôle dans l’étude contemporaine des fondements des mathématiques. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="I47" r:id="rId31" display="https://www.laphilo.fr/photo/cparsons.webp"/>
-    <hyperlink ref="H49" r:id="rId32" display="https://www.laphilo.fr/pho/dihde-mini.webp"/>
-    <hyperlink ref="E51" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edward_Sa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Edward SAÏD&lt;/a&gt; était un intellectuel palestinien-américain, critique littéraire et professeur de littérature anglaise et comparée à l’université Columbia de New York. D’origine palestinienne et né à Jérusalem, il a grandi entre l’Égypte, les États-Unis et l’Europe, une expérience de déplacement qui a profondément marqué sa pensée sur l’identité, la colonisation et l’altérité.  &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est l’essai &lt;a href=&quot;https://www.youtube.com/watch?v=Ne4WRykmjhA&quot; title=&quot;Edward Said  Orientalisme par HD Doc&quot;&gt;L’Orientalisme : &lt;/a&gt;  L’Orient créé par l’Occident* (1978), considéré comme le texte fondateur des postcolonial studies. Dans cet ouvrage, Saïd montre que l’« Orient » n’est pas une réalité objective mais une invention de l’Occident : un discours façonné par des siècles de domination coloniale pour mieux contrôler et représenter l’Autre. &lt;/p&gt; &lt;p&gt; Pour lui, l’orientalisme est à la fois un savoir et un outil de pouvoir : il ne s’agit pas seulement de décrire l’Orient, mais de le hiérarchiser, de l’essentialiser et de le rendre  &lt;a href=&quot;https://www.youtube.com/watch?v=QBj-yWLnayM&quot; title=&quot;Edward Said writings on Orientalism par Middle East Eye&quot;&gt; inférieur à l’Occident. &lt;/a&gt; Il analyse quatre thèses principales : la domination politique et culturelle de l’Orient par l’Occident, la dépréciation de la langue arabe, la diabolisation de l’arabe et de l’islam, et la défense de la cause palestinienne. &lt;/p&gt; &lt;p&gt; Sa pensée articule critique littéraire, histoire, philosophie et sciences politiques, en s’inspirant notamment de Michel Foucault (discours–pouvoir) et de Jacques Derrida (déconstruction). Il montre que la violence du colonialisme n’est pas seulement matérielle (conquête, pillage), mais aussi épistémique : une violence de la raison qui classe, essentialise et dévalue les « Autres » de l’Occident. &lt;/p&gt; &lt;p&gt;  Intéressé par &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Edward-W-Said-1935-2003.html&quot; title=&quot;Edward Said par lesclesdumoyenorient&quot;&gt; l’engagement politique, &lt;/a&gt; il a aussi défendu la cause palestinienne et la légitimité des revendications d’autodétermination du peuple palestinien, tout en reconnaissance du droit à une patrie juive. Il rejetait le repli identitaire et prônait une vision universelle qui défend les différences et les droits, tissant des liens entre classicisme et excentricité, histoire et actualité. &lt;/p&gt;  &lt;audio controls title=&quot;Edward Said, une conscience morale par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-08.12.2017-ITEMA_21518070-2017C19327S0342-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &#10;&#10;&#10;"/>
-    <hyperlink ref="H51" r:id="rId34" display="https://laphilo.fr/pho/esaid-mini.webp"/>
-    <hyperlink ref="H52" r:id="rId35" display="https://www.laphilo.fr/pho/rmadams-mini.webp"/>
-    <hyperlink ref="E53" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Nozick&quot;  title=&quot; Wikipedia&quot;&gt;Robert NOZICK&lt;/a&gt; était un philosophe américain connu pour &lt;a href=&quot;https://www.youtube.com/watch?v=Q-t3cpFAk4o&quot;  title=&quot; Libertarianisme par Vadim Media&quot;&gt; son libertarianisme &lt;/a&gt; et sa critique des théories égalitaristes comme celle de John Rawls. Professeur à Harvard, il a marqué la philosophie politique, morale et épistémologique par son œuvre principale, Anarchie, État et utopie (1974), qui défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Minarchisme&quot;  title=&quot; Minarchisme par Wikipédia&quot;&gt; Etat Minimal. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il argue que seul l'État minimal, ou &quot;État gardien de nuit&quot;, est légitime, car il se limite à protéger les individus contre la force, la fraude et le vol, sans redistribuer les richesses. Il rejette l'anarcho-capitalisme en montrant, via des agences de protection privée, comment un État dominant émerge naturellement pour monopoliser la coercition légitime, justifié par le droit naturel à la personne. &lt;/p&gt; &lt;p&gt; Contrairement à la justice distributive de Rawls, il propose une théorie de l'entitlement : une acquisition initiale juste et des transferts volontaires rendent la distribution légitime, sans besoin d'égalisation par l'État. Toute intervention redistributive viole les droits individuels, traitant les personnes comme des moyens plutôt que des fins, en écho à Kant. &lt;/p&gt; &lt;p&gt; Dans Anarchie, État et utopie, Il réfute l'utilitarisme via l'expérience de pensée de la &lt;a href=&quot;https://www.youtube.com/watch?v=2FVwXaNWPQ0&quot;  title=&quot; La machine à expérience par Monsieur Phi&quot;&gt;&quot;machine à expérience&quot; :&lt;/a&gt;  même si elle offre un bonheur parfait et indistinguable de la réalité, les gens préfèrent vivre des actions réelles et façonner leur identité plutôt que des simulations. Cela prouve que le bonheur n'est pas le seul bien suprême. &lt;/p&gt; &lt;p&gt; Plus tard, dans Explications philosophiques (1981), il développe une théorie du suivi (tracking theory) en épistémologie, où la connaissance repose sur des conditionnels contrefactuels fiables, contournant le scepticisme sans justification traditionnelle. Son anti-coercitivisme intellectuel invite à une philosophie ouverte, non imposée. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Qui a peur des Libertariens par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-14.06.2022-ITEMA_23058436-2022C12410S0165-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;"/>
-    <hyperlink ref="H59" r:id="rId37" display="https://www.laphilo.fr/pho/imyoung-mini.webp"/>
-    <hyperlink ref="H60" r:id="rId38" display="https://www.laphilo.fr/pho/bhooks-mini.webp"/>
+    <hyperlink ref="H44" r:id="rId28" display="https://www.laphilo.fr/pho/abracken-mini.webp"/>
+    <hyperlink ref="E46" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Rorty&quot; title=&quot; Wikipedia&quot;&gt;Richard RORTY&lt;/a&gt; était un  philosophe américain, figure majeure du  &lt;a href=&quot;https://www.youtube.com/watch?v=lfx4Jag1ic4&quot;  title=&quot;Le pragmatisme : définition, exemples par le savoir partagé&quot;&gt;pragmatisme&lt;/a&gt; et du postmodernisme, il a remis en cause les fondements de la philosophie occidentale et proposé une &lt;a href=&quot;https://laviedesidees.fr/Rorty-Pragmatism-Anti-Authoritarianism&quot; title=&quot; a bas l'autorité par laviedesidees&quot;&gt;vision radicale&lt;/a&gt;  de la vérité, de la culture et de la société. Il rejette l'idée que la vérité soit une correspondance entre le langage et la réalité. Pour lui, la vérité est simplement ce qui est utile ou avantageux à croire dans une communauté donnée et il propose d'abandonner la quête de fondements absolus de la connaissance, jugée vaine. &lt;/p&gt; &lt;p&gt; Inspiré par Wittgenstein et Davidson, il considère le langage non pas comme un miroir de la réalité, mais comme un ensemble d'outils pour résoudre des problèmes pratiques.  Les vocabularies que nous utilisons sont historiquement et culturellement contingents, non pas &quot;vrais&quot; ou &quot;faux&quot;. &lt;/p&gt; &lt;p&gt; Dans ces oeuvres principales , on trouve  &lt;a href=&quot;https://www.youtube.com/watch?v=MgU0dXZ3umM&quot; title=&quot;L’ironiste libéral chez Rorty : Contingence, ironie et solidarité par Darina Metreveli&quot;&gt;&quot; Contingence, ironie et solidarité &quot;&lt;/a&gt; (1989) ou il décrit l'ironiste comme quelqu'un qui doute de ses propres croyances tout en œuvrant pour une société plus juste. Dans &quot; Achieving Our Country&quot; (1998),  il y appelle la gauche américaine à abandonner le &quot;culturalisme&quot; pour se recentrer sur les inégalités économiques et sociales. Cet ouvrage est souvent cité pour avoir anticipé les crises politiques du XXIe siècle. &lt;/p&gt; &lt;p&gt;  Ses thèses sur la contingence de la vérité sont souvent invoquées pour analyser l'ère de la &quot;post-vérité&quot;. Son insistance sur la conversation comme fondement du lien social influence la philosophie politique contemporaine. Il  a bouleversé la philosophie en démystifiant ses prétentions à la vérité absolue. Son œuvre, à la fois provocante et humaniste, invite à remplacer la quête métaphysique par un engagement en faveur d'une société plus juste et plus inclusive. &lt;/p&gt; "/>
+    <hyperlink ref="E48" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Charles_Parsons_(philosopher)&quot;  title=&quot; Wikipedia&quot;&gt;Charles Dacre PARSONS&lt;/a&gt; était un philosophe américain connu pour ses travaux en philosophie des mathématiques et en philosophie de Kant. Il a enseigné à Columbia puis à Harvard, où il est devenu professeur émérite. Il s’est formé à Harvard, avec une thèse dirigée par Willard Van Orman Quine, ce qui le place au croisement de la logique, de la philosophie analytique et des fondements des mathématiques. Son parcours intellectuel a été marqué très tôt par la rigueur mathématique, puisqu’il avait d’abord étudié les mathématiques avant de se tourner vers la philosophie. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la philosophie des mathématiques, domaine dans lequel il a travaillé sur la nature des objets mathématiques, la logique, la preuve et l’interprétation constructive des mathématiques prédicatives. Il a aussi beaucoup écrit sur Frege, Gödel, Hilbert et Quine, en lisant ces auteurs à la fois comme philosophes et comme figures majeures des fondements. &lt;/p&gt; &lt;p&gt; Il n’était pas seulement un spécialiste de logique ; il a aussi produit des travaux importants sur Kant, montrant comment les questions de connaissance, d’expérience et de structure de l’esprit se relient aux mathématiques. Cette double compétence, en philosophie des mathématiques et en histoire de la philosophie, explique pourquoi il est souvent vu comme un auteur à la fois technique et très large dans ses intérêts.&lt;/p&gt; &lt;p&gt; Son influence est restée forte dans le monde anglophone, au point d’être décrit comme l’un des philosophes des mathématiques les plus importants de sa génération. En plus de ses livres et articles, il a aussi contribué à l’édition de textes posthumes de Gödel, ce qui a renforcé son rôle dans l’étude contemporaine des fondements des mathématiques. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="I48" r:id="rId31" display="https://www.laphilo.fr/photo/cparsons.webp"/>
+    <hyperlink ref="H50" r:id="rId32" display="https://www.laphilo.fr/pho/dihde-mini.webp"/>
+    <hyperlink ref="E52" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edward_Sa%C3%AFd&quot;  title=&quot; Wikipedia&quot;&gt;Edward SAÏD&lt;/a&gt; était un intellectuel palestinien-américain, critique littéraire et professeur de littérature anglaise et comparée à l’université Columbia de New York. D’origine palestinienne et né à Jérusalem, il a grandi entre l’Égypte, les États-Unis et l’Europe, une expérience de déplacement qui a profondément marqué sa pensée sur l’identité, la colonisation et l’altérité.  &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est l’essai &lt;a href=&quot;https://www.youtube.com/watch?v=Ne4WRykmjhA&quot; title=&quot;Edward Said  Orientalisme par HD Doc&quot;&gt;L’Orientalisme : &lt;/a&gt;  L’Orient créé par l’Occident* (1978), considéré comme le texte fondateur des postcolonial studies. Dans cet ouvrage, Saïd montre que l’« Orient » n’est pas une réalité objective mais une invention de l’Occident : un discours façonné par des siècles de domination coloniale pour mieux contrôler et représenter l’Autre. &lt;/p&gt; &lt;p&gt; Pour lui, l’orientalisme est à la fois un savoir et un outil de pouvoir : il ne s’agit pas seulement de décrire l’Orient, mais de le hiérarchiser, de l’essentialiser et de le rendre  &lt;a href=&quot;https://www.youtube.com/watch?v=QBj-yWLnayM&quot; title=&quot;Edward Said writings on Orientalism par Middle East Eye&quot;&gt; inférieur à l’Occident. &lt;/a&gt; Il analyse quatre thèses principales : la domination politique et culturelle de l’Orient par l’Occident, la dépréciation de la langue arabe, la diabolisation de l’arabe et de l’islam, et la défense de la cause palestinienne. &lt;/p&gt; &lt;p&gt; Sa pensée articule critique littéraire, histoire, philosophie et sciences politiques, en s’inspirant notamment de Michel Foucault (discours–pouvoir) et de Jacques Derrida (déconstruction). Il montre que la violence du colonialisme n’est pas seulement matérielle (conquête, pillage), mais aussi épistémique : une violence de la raison qui classe, essentialise et dévalue les « Autres » de l’Occident. &lt;/p&gt; &lt;p&gt;  Intéressé par &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Edward-W-Said-1935-2003.html&quot; title=&quot;Edward Said par lesclesdumoyenorient&quot;&gt; l’engagement politique, &lt;/a&gt; il a aussi défendu la cause palestinienne et la légitimité des revendications d’autodétermination du peuple palestinien, tout en reconnaissance du droit à une patrie juive. Il rejetait le repli identitaire et prônait une vision universelle qui défend les différences et les droits, tissant des liens entre classicisme et excentricité, histoire et actualité. &lt;/p&gt;  &lt;audio controls title=&quot;Edward Said, une conscience morale par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-08.12.2017-ITEMA_21518070-2017C19327S0342-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &#10;&#10;&#10;"/>
+    <hyperlink ref="H52" r:id="rId34" display="https://laphilo.fr/pho/esaid-mini.webp"/>
+    <hyperlink ref="H53" r:id="rId35" display="https://www.laphilo.fr/pho/rmadams-mini.webp"/>
+    <hyperlink ref="E54" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Nozick&quot;  title=&quot; Wikipedia&quot;&gt;Robert NOZICK&lt;/a&gt; était un philosophe américain connu pour &lt;a href=&quot;https://www.youtube.com/watch?v=Q-t3cpFAk4o&quot;  title=&quot; Libertarianisme par Vadim Media&quot;&gt; son libertarianisme &lt;/a&gt; et sa critique des théories égalitaristes comme celle de John Rawls. Professeur à Harvard, il a marqué la philosophie politique, morale et épistémologique par son œuvre principale, Anarchie, État et utopie (1974), qui défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Minarchisme&quot;  title=&quot; Minarchisme par Wikipédia&quot;&gt; Etat Minimal. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il argue que seul l'État minimal, ou &quot;État gardien de nuit&quot;, est légitime, car il se limite à protéger les individus contre la force, la fraude et le vol, sans redistribuer les richesses. Il rejette l'anarcho-capitalisme en montrant, via des agences de protection privée, comment un État dominant émerge naturellement pour monopoliser la coercition légitime, justifié par le droit naturel à la personne. &lt;/p&gt; &lt;p&gt; Contrairement à la justice distributive de Rawls, il propose une théorie de l'entitlement : une acquisition initiale juste et des transferts volontaires rendent la distribution légitime, sans besoin d'égalisation par l'État. Toute intervention redistributive viole les droits individuels, traitant les personnes comme des moyens plutôt que des fins, en écho à Kant. &lt;/p&gt; &lt;p&gt; Dans Anarchie, État et utopie, Il réfute l'utilitarisme via l'expérience de pensée de la &lt;a href=&quot;https://www.youtube.com/watch?v=2FVwXaNWPQ0&quot;  title=&quot; La machine à expérience par Monsieur Phi&quot;&gt;&quot;machine à expérience&quot; :&lt;/a&gt;  même si elle offre un bonheur parfait et indistinguable de la réalité, les gens préfèrent vivre des actions réelles et façonner leur identité plutôt que des simulations. Cela prouve que le bonheur n'est pas le seul bien suprême. &lt;/p&gt; &lt;p&gt; Plus tard, dans Explications philosophiques (1981), il développe une théorie du suivi (tracking theory) en épistémologie, où la connaissance repose sur des conditionnels contrefactuels fiables, contournant le scepticisme sans justification traditionnelle. Son anti-coercitivisme intellectuel invite à une philosophie ouverte, non imposée. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Qui a peur des Libertariens par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-14.06.2022-ITEMA_23058436-2022C12410S0165-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;&#10;"/>
+    <hyperlink ref="H60" r:id="rId37" display="https://www.laphilo.fr/pho/imyoung-mini.webp"/>
+    <hyperlink ref="H61" r:id="rId38" display="https://www.laphilo.fr/pho/bhooks-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
